--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="91">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,52 +214,46 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.8 → 33.1</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>44.6 → 52.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>26.8</t>
-  </si>
-  <si>
-    <t>33.1</t>
-  </si>
-  <si>
-    <t>28.1 → 35.9</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>35.9</t>
-  </si>
-  <si>
-    <t>29.7 → 36.6</t>
-  </si>
-  <si>
-    <t>29.7</t>
-  </si>
-  <si>
-    <t>36.6</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>73.0 → 58.5</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>73.0</t>
-  </si>
-  <si>
-    <t>58.5</t>
+    <t>44.6</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>49.1 → 53.9</t>
+  </si>
+  <si>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>40.8 → 51.1</t>
+  </si>
+  <si>
+    <t>40.8</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>44.0 → 52.7</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>52.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -311,7 +305,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,20 +346,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -393,12 +380,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -474,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -482,15 +463,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -499,7 +479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -998,10 +978,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>713.4</v>
+        <v>726.65</v>
       </c>
       <c r="D2">
-        <v>-0.22</v>
+        <v>1.86</v>
       </c>
       <c r="E2">
         <v>790.85</v>
@@ -1010,46 +990,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-9.789999999999999</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="H2">
-        <v>24.95</v>
+        <v>27.27</v>
       </c>
       <c r="I2">
-        <v>-0.92</v>
+        <v>0.54</v>
       </c>
       <c r="J2">
-        <v>-0.92</v>
+        <v>1.06</v>
       </c>
       <c r="K2">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="L2">
-        <v>-7.82</v>
+        <v>-6.56</v>
       </c>
       <c r="M2">
-        <v>36.82</v>
+        <v>38.42</v>
       </c>
       <c r="N2">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>717.08</v>
+        <v>717.86</v>
       </c>
       <c r="Q2">
-        <v>722.5599999999999</v>
+        <v>722.73</v>
       </c>
       <c r="R2">
-        <v>728.54</v>
+        <v>728.62</v>
       </c>
       <c r="S2">
-        <v>688.39</v>
+        <v>688.3</v>
       </c>
       <c r="T2">
-        <v>3.63</v>
+        <v>5.57</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1064,34 +1044,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.65</v>
+        <v>52.26</v>
       </c>
       <c r="Z2">
-        <v>-2.92</v>
+        <v>-2.12</v>
       </c>
       <c r="AA2">
-        <v>-1.98</v>
+        <v>-2.01</v>
       </c>
       <c r="AB2">
-        <v>-0.93</v>
+        <v>-0.1</v>
       </c>
       <c r="AC2">
-        <v>46.74</v>
+        <v>55.44</v>
       </c>
       <c r="AD2">
-        <v>49.98</v>
+        <v>50.24</v>
       </c>
       <c r="AE2">
-        <v>14.84</v>
+        <v>15.02</v>
       </c>
       <c r="AF2">
-        <v>-31.89</v>
+        <v>10.29</v>
       </c>
       <c r="AG2">
-        <v>738.7</v>
+        <v>738.97</v>
       </c>
       <c r="AH2">
-        <v>706.42</v>
+        <v>706.48</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1100,7 +1080,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>15.55</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1111,10 +1091,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>938.05</v>
+        <v>965.25</v>
       </c>
       <c r="D3">
-        <v>1.49</v>
+        <v>2.9</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1123,46 +1103,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-13.26</v>
+        <v>-10.75</v>
       </c>
       <c r="H3">
-        <v>85.62</v>
+        <v>91</v>
       </c>
       <c r="I3">
-        <v>-3.6</v>
+        <v>0.73</v>
       </c>
       <c r="J3">
-        <v>-13.26</v>
+        <v>1.73</v>
       </c>
       <c r="K3">
-        <v>26.1</v>
+        <v>10.71</v>
       </c>
       <c r="L3">
-        <v>14.89</v>
+        <v>13.44</v>
       </c>
       <c r="M3">
-        <v>12.19</v>
+        <v>13.87</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>941.09</v>
+        <v>942.48</v>
       </c>
       <c r="Q3">
-        <v>934.48</v>
+        <v>937.23</v>
       </c>
       <c r="R3">
-        <v>942.97</v>
+        <v>944.55</v>
       </c>
       <c r="S3">
-        <v>756.84</v>
+        <v>757.4400000000001</v>
       </c>
       <c r="T3">
-        <v>23.94</v>
+        <v>27.44</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1177,34 +1157,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>49.15</v>
+        <v>53.85</v>
       </c>
       <c r="Z3">
-        <v>-1.94</v>
+        <v>0.15</v>
       </c>
       <c r="AA3">
-        <v>-0.5600000000000001</v>
+        <v>-0.42</v>
       </c>
       <c r="AB3">
-        <v>-1.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC3">
-        <v>41.02</v>
+        <v>51.37</v>
       </c>
       <c r="AD3">
-        <v>46.4</v>
+        <v>44.14</v>
       </c>
       <c r="AE3">
-        <v>45.58</v>
+        <v>45.25</v>
       </c>
       <c r="AF3">
-        <v>-53.57</v>
+        <v>-55.34</v>
       </c>
       <c r="AG3">
-        <v>972.9</v>
+        <v>976.2</v>
       </c>
       <c r="AH3">
-        <v>896.0599999999999</v>
+        <v>898.27</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1213,7 +1193,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>15.46</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1224,10 +1204,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>202.65</v>
+        <v>204.14</v>
       </c>
       <c r="D4">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="E4">
         <v>335.45</v>
@@ -1236,25 +1216,25 @@
         <v>200.82</v>
       </c>
       <c r="G4">
-        <v>-39.59</v>
+        <v>-39.14</v>
       </c>
       <c r="H4">
-        <v>0.91</v>
+        <v>1.65</v>
       </c>
       <c r="I4">
-        <v>-1.29</v>
+        <v>0.06</v>
       </c>
       <c r="J4">
-        <v>-4.63</v>
+        <v>-4.28</v>
       </c>
       <c r="K4">
-        <v>-11.13</v>
+        <v>-10.64</v>
       </c>
       <c r="L4">
-        <v>-38.73</v>
+        <v>-37.83</v>
       </c>
       <c r="M4">
-        <v>-6.01</v>
+        <v>-5.79</v>
       </c>
       <c r="N4">
         <v>26</v>
@@ -1263,19 +1243,19 @@
         <v>16</v>
       </c>
       <c r="P4">
-        <v>202.51</v>
+        <v>202.53</v>
       </c>
       <c r="Q4">
-        <v>208.06</v>
+        <v>207.68</v>
       </c>
       <c r="R4">
-        <v>215.97</v>
+        <v>215.59</v>
       </c>
       <c r="S4">
-        <v>243.19</v>
+        <v>242.91</v>
       </c>
       <c r="T4">
-        <v>-16.67</v>
+        <v>-15.96</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1290,34 +1270,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.1</v>
+        <v>37.83</v>
       </c>
       <c r="Z4">
-        <v>-3.81</v>
+        <v>-3.61</v>
       </c>
       <c r="AA4">
-        <v>-3.52</v>
+        <v>-3.54</v>
       </c>
       <c r="AB4">
-        <v>-0.29</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC4">
-        <v>15.11</v>
+        <v>41.46</v>
       </c>
       <c r="AD4">
-        <v>5.04</v>
+        <v>18.85</v>
       </c>
       <c r="AE4">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="AF4">
-        <v>-0.23</v>
+        <v>-12.55</v>
       </c>
       <c r="AG4">
-        <v>216.12</v>
+        <v>215.73</v>
       </c>
       <c r="AH4">
-        <v>200.01</v>
+        <v>199.64</v>
       </c>
       <c r="AI4">
         <v>214.01</v>
@@ -1326,7 +1306,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>31.65</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1337,10 +1317,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>731.8</v>
+        <v>779.3</v>
       </c>
       <c r="D5">
-        <v>-0.42</v>
+        <v>6.49</v>
       </c>
       <c r="E5">
         <v>989.9299999999999</v>
@@ -1349,46 +1329,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-26.08</v>
+        <v>-21.28</v>
       </c>
       <c r="H5">
-        <v>27.4</v>
+        <v>35.67</v>
       </c>
       <c r="I5">
-        <v>20.42</v>
+        <v>29.23</v>
       </c>
       <c r="J5">
-        <v>9.119999999999999</v>
+        <v>19.34</v>
       </c>
       <c r="K5">
-        <v>0.38</v>
+        <v>6.37</v>
       </c>
       <c r="L5">
-        <v>-23.26</v>
+        <v>-17.68</v>
       </c>
       <c r="M5">
-        <v>-1.9</v>
+        <v>-0.17</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>658.55</v>
+        <v>693.8</v>
       </c>
       <c r="Q5">
-        <v>638.96</v>
+        <v>646.11</v>
       </c>
       <c r="R5">
-        <v>665.85</v>
+        <v>667.23</v>
       </c>
       <c r="S5">
-        <v>704.2</v>
+        <v>704.16</v>
       </c>
       <c r="T5">
-        <v>3.92</v>
+        <v>10.67</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1403,43 +1383,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>71.25</v>
+        <v>77.08</v>
       </c>
       <c r="Z5">
-        <v>2.12</v>
+        <v>11.95</v>
       </c>
       <c r="AA5">
-        <v>-9.77</v>
+        <v>-5.43</v>
       </c>
       <c r="AB5">
-        <v>11.89</v>
+        <v>17.38</v>
       </c>
       <c r="AC5">
-        <v>81.55</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AD5">
-        <v>60.06</v>
+        <v>81.2</v>
       </c>
       <c r="AE5">
-        <v>28.13</v>
+        <v>33.78</v>
       </c>
       <c r="AF5">
-        <v>4261.14</v>
+        <v>701.4</v>
       </c>
       <c r="AG5">
-        <v>709.02</v>
+        <v>740.12</v>
       </c>
       <c r="AH5">
-        <v>568.9</v>
+        <v>552.1</v>
       </c>
       <c r="AI5">
-        <v>666.1900000000001</v>
+        <v>677.03</v>
       </c>
       <c r="AJ5" t="s">
         <v>56</v>
       </c>
       <c r="AK5">
-        <v>31.39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1450,10 +1430,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1799.3</v>
+        <v>1791.6</v>
       </c>
       <c r="D6">
-        <v>2.92</v>
+        <v>-0.43</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1462,46 +1442,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-12.73</v>
+        <v>-13.1</v>
       </c>
       <c r="H6">
-        <v>33.49</v>
+        <v>32.92</v>
       </c>
       <c r="I6">
-        <v>2.65</v>
+        <v>1.06</v>
       </c>
       <c r="J6">
-        <v>5.11</v>
+        <v>6.02</v>
       </c>
       <c r="K6">
-        <v>-5.29</v>
+        <v>-7.74</v>
       </c>
       <c r="L6">
-        <v>13.64</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>6.67</v>
+        <v>6.21</v>
       </c>
       <c r="N6">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="O6">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P6">
-        <v>1769.26</v>
+        <v>1773.02</v>
       </c>
       <c r="Q6">
-        <v>1718.61</v>
+        <v>1725.19</v>
       </c>
       <c r="R6">
-        <v>1757.36</v>
+        <v>1755.46</v>
       </c>
       <c r="S6">
-        <v>1712.68</v>
+        <v>1712.56</v>
       </c>
       <c r="T6">
-        <v>5.06</v>
+        <v>4.62</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1516,34 +1496,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>59.6</v>
+        <v>58.07</v>
       </c>
       <c r="Z6">
-        <v>6.63</v>
+        <v>9.5</v>
       </c>
       <c r="AA6">
-        <v>-5.23</v>
+        <v>-2.28</v>
       </c>
       <c r="AB6">
-        <v>11.86</v>
+        <v>11.78</v>
       </c>
       <c r="AC6">
-        <v>89.42</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AD6">
-        <v>90.25</v>
+        <v>88.61</v>
       </c>
       <c r="AE6">
-        <v>48.91</v>
+        <v>49.73</v>
       </c>
       <c r="AF6">
-        <v>20.9</v>
+        <v>16.86</v>
       </c>
       <c r="AG6">
-        <v>1804.02</v>
+        <v>1811.86</v>
       </c>
       <c r="AH6">
-        <v>1633.2</v>
+        <v>1638.52</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1552,7 +1532,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>29.29</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1563,10 +1543,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>1000.1</v>
+        <v>1013.7</v>
       </c>
       <c r="D7">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1575,46 +1555,46 @@
         <v>986.1</v>
       </c>
       <c r="G7">
-        <v>-20.65</v>
+        <v>-19.57</v>
       </c>
       <c r="H7">
-        <v>1.42</v>
+        <v>2.8</v>
       </c>
       <c r="I7">
-        <v>-1.38</v>
+        <v>1.27</v>
       </c>
       <c r="J7">
-        <v>-6.76</v>
+        <v>-4.51</v>
       </c>
       <c r="K7">
-        <v>-11.06</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L7">
-        <v>-8.75</v>
+        <v>-7.39</v>
       </c>
       <c r="M7">
-        <v>3.59</v>
+        <v>3.86</v>
       </c>
       <c r="N7">
         <v>50</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P7">
-        <v>995.5599999999999</v>
+        <v>998.1</v>
       </c>
       <c r="Q7">
-        <v>1027.11</v>
+        <v>1024.39</v>
       </c>
       <c r="R7">
-        <v>1065.19</v>
+        <v>1063.67</v>
       </c>
       <c r="S7">
-        <v>1117.73</v>
+        <v>1116.98</v>
       </c>
       <c r="T7">
-        <v>-10.52</v>
+        <v>-9.25</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1629,34 +1609,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.91</v>
+        <v>42.45</v>
       </c>
       <c r="Z7">
-        <v>-22.1</v>
+        <v>-20.2</v>
       </c>
       <c r="AA7">
-        <v>-20.26</v>
+        <v>-20.24</v>
       </c>
       <c r="AB7">
-        <v>-1.84</v>
+        <v>0.05</v>
       </c>
       <c r="AC7">
-        <v>23.41</v>
+        <v>56.75</v>
       </c>
       <c r="AD7">
-        <v>7.8</v>
+        <v>26.72</v>
       </c>
       <c r="AE7">
-        <v>18.21</v>
+        <v>18.43</v>
       </c>
       <c r="AF7">
-        <v>43.91</v>
+        <v>74.61</v>
       </c>
       <c r="AG7">
-        <v>1078.1</v>
+        <v>1071.88</v>
       </c>
       <c r="AH7">
-        <v>976.12</v>
+        <v>976.91</v>
       </c>
       <c r="AI7">
         <v>1045.9</v>
@@ -1665,7 +1645,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>64.12</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1676,10 +1656,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3373</v>
+        <v>3381.8</v>
       </c>
       <c r="D8">
-        <v>-1.95</v>
+        <v>0.26</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1688,46 +1668,46 @@
         <v>3373</v>
       </c>
       <c r="G8">
-        <v>-41.34</v>
+        <v>-41.18</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="I8">
-        <v>-3.41</v>
+        <v>-0.04</v>
       </c>
       <c r="J8">
-        <v>-10.59</v>
+        <v>-7.65</v>
       </c>
       <c r="K8">
-        <v>-17.62</v>
+        <v>-17.84</v>
       </c>
       <c r="L8">
-        <v>-40.31</v>
+        <v>-39.83</v>
       </c>
       <c r="M8">
-        <v>-7.18</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>9</v>
       </c>
       <c r="P8">
-        <v>3397.6</v>
+        <v>3397.36</v>
       </c>
       <c r="Q8">
-        <v>3563.79</v>
+        <v>3549.9</v>
       </c>
       <c r="R8">
-        <v>3616.2</v>
+        <v>3611.36</v>
       </c>
       <c r="S8">
-        <v>4326.1</v>
+        <v>4317.68</v>
       </c>
       <c r="T8">
-        <v>-22.03</v>
+        <v>-21.68</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1742,43 +1722,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>33.45</v>
+        <v>34.44</v>
       </c>
       <c r="Z8">
-        <v>-79.98</v>
+        <v>-82.01000000000001</v>
       </c>
       <c r="AA8">
-        <v>-59.3</v>
+        <v>-63.84</v>
       </c>
       <c r="AB8">
-        <v>-20.68</v>
+        <v>-18.17</v>
       </c>
       <c r="AC8">
-        <v>23.78</v>
+        <v>29.81</v>
       </c>
       <c r="AD8">
-        <v>17.88</v>
+        <v>25.16</v>
       </c>
       <c r="AE8">
-        <v>89.25</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="AF8">
-        <v>1.89</v>
+        <v>-32.88</v>
       </c>
       <c r="AG8">
-        <v>3792.01</v>
+        <v>3787.19</v>
       </c>
       <c r="AH8">
-        <v>3335.58</v>
+        <v>3312.61</v>
       </c>
       <c r="AI8">
-        <v>3646.88</v>
+        <v>3636.04</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>35.03</v>
+        <v>33.73</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1789,10 +1769,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>681.95</v>
+        <v>719.3</v>
       </c>
       <c r="D9">
-        <v>-5.07</v>
+        <v>5.48</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1801,46 +1781,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-35.21</v>
+        <v>-31.66</v>
       </c>
       <c r="H9">
-        <v>26.67</v>
+        <v>33.61</v>
       </c>
       <c r="I9">
-        <v>9.630000000000001</v>
+        <v>16.24</v>
       </c>
       <c r="J9">
-        <v>4.19</v>
+        <v>11.14</v>
       </c>
       <c r="K9">
-        <v>0.93</v>
+        <v>3.62</v>
       </c>
       <c r="L9">
-        <v>-0.08</v>
+        <v>5.13</v>
       </c>
       <c r="M9">
-        <v>41.63</v>
+        <v>42.77</v>
       </c>
       <c r="N9">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="O9">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P9">
-        <v>663.03</v>
+        <v>683.13</v>
       </c>
       <c r="Q9">
-        <v>645.3200000000001</v>
+        <v>648.64</v>
       </c>
       <c r="R9">
-        <v>659.0599999999999</v>
+        <v>660.1799999999999</v>
       </c>
       <c r="S9">
-        <v>664.11</v>
+        <v>663.99</v>
       </c>
       <c r="T9">
-        <v>2.69</v>
+        <v>8.33</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1855,34 +1835,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>58.48</v>
+        <v>65.97</v>
       </c>
       <c r="Z9">
-        <v>2.22</v>
+        <v>7.16</v>
       </c>
       <c r="AA9">
-        <v>-5.08</v>
+        <v>-2.63</v>
       </c>
       <c r="AB9">
-        <v>7.29</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AC9">
-        <v>88.31999999999999</v>
+        <v>82.66</v>
       </c>
       <c r="AD9">
-        <v>85</v>
+        <v>90.33</v>
       </c>
       <c r="AE9">
-        <v>23.78</v>
+        <v>26.61</v>
       </c>
       <c r="AF9">
-        <v>182.6</v>
+        <v>92.64</v>
       </c>
       <c r="AG9">
-        <v>688.91</v>
+        <v>703.36</v>
       </c>
       <c r="AH9">
-        <v>601.73</v>
+        <v>593.92</v>
       </c>
       <c r="AI9">
         <v>660.59</v>
@@ -1891,7 +1871,7 @@
         <v>56</v>
       </c>
       <c r="AK9">
-        <v>32.52</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1902,10 +1882,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>360.4</v>
+        <v>369</v>
       </c>
       <c r="D10">
-        <v>-0.72</v>
+        <v>2.39</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1914,46 +1894,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-21.96</v>
+        <v>-20.1</v>
       </c>
       <c r="H10">
-        <v>4.39</v>
+        <v>6.88</v>
       </c>
       <c r="I10">
-        <v>-1.41</v>
+        <v>-0.27</v>
       </c>
       <c r="J10">
-        <v>-5.53</v>
+        <v>-3.15</v>
       </c>
       <c r="K10">
-        <v>-10.24</v>
+        <v>-8.41</v>
       </c>
       <c r="L10">
-        <v>-7.14</v>
+        <v>-4.47</v>
       </c>
       <c r="M10">
-        <v>21.45</v>
+        <v>22.44</v>
       </c>
       <c r="N10">
         <v>56</v>
       </c>
       <c r="O10">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P10">
-        <v>365.01</v>
+        <v>364.81</v>
       </c>
       <c r="Q10">
-        <v>364.6</v>
+        <v>364.1</v>
       </c>
       <c r="R10">
-        <v>373.24</v>
+        <v>373.18</v>
       </c>
       <c r="S10">
-        <v>387.64</v>
+        <v>387.53</v>
       </c>
       <c r="T10">
-        <v>-7.03</v>
+        <v>-4.78</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1968,34 +1948,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>40.81</v>
+        <v>51.08</v>
       </c>
       <c r="Z10">
-        <v>-3.29</v>
+        <v>-2.68</v>
       </c>
       <c r="AA10">
-        <v>-3.92</v>
+        <v>-3.67</v>
       </c>
       <c r="AB10">
-        <v>0.63</v>
+        <v>0.99</v>
       </c>
       <c r="AC10">
-        <v>75.95</v>
+        <v>81.89</v>
       </c>
       <c r="AD10">
-        <v>83.19</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="AE10">
-        <v>7.36</v>
+        <v>7.56</v>
       </c>
       <c r="AF10">
-        <v>-44.71</v>
+        <v>-45.63</v>
       </c>
       <c r="AG10">
-        <v>381.93</v>
+        <v>380.24</v>
       </c>
       <c r="AH10">
-        <v>347.27</v>
+        <v>347.97</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -2004,7 +1984,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>33.55</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2015,10 +1995,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>183</v>
+        <v>187.29</v>
       </c>
       <c r="D11">
-        <v>-0.35</v>
+        <v>2.34</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2027,46 +2007,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-15.54</v>
+        <v>-13.56</v>
       </c>
       <c r="H11">
-        <v>16.25</v>
+        <v>18.97</v>
       </c>
       <c r="I11">
-        <v>-0.62</v>
+        <v>-0.77</v>
       </c>
       <c r="J11">
-        <v>-1.61</v>
+        <v>0.96</v>
       </c>
       <c r="K11">
-        <v>-8.039999999999999</v>
+        <v>-6.6</v>
       </c>
       <c r="L11">
-        <v>10.25</v>
+        <v>12.59</v>
       </c>
       <c r="M11">
-        <v>8.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="N11">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O11">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P11">
-        <v>185.04</v>
+        <v>184.74</v>
       </c>
       <c r="Q11">
-        <v>185.26</v>
+        <v>185.43</v>
       </c>
       <c r="R11">
-        <v>186.37</v>
+        <v>186.36</v>
       </c>
       <c r="S11">
-        <v>190.69</v>
+        <v>190.8</v>
       </c>
       <c r="T11">
-        <v>-4.03</v>
+        <v>-1.84</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2081,34 +2061,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>44.04</v>
+        <v>52.71</v>
       </c>
       <c r="Z11">
-        <v>-0.75</v>
+        <v>-0.51</v>
       </c>
       <c r="AA11">
-        <v>-0.62</v>
+        <v>-0.6</v>
       </c>
       <c r="AB11">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="AC11">
-        <v>12.52</v>
+        <v>34.84</v>
       </c>
       <c r="AD11">
-        <v>32</v>
+        <v>25.57</v>
       </c>
       <c r="AE11">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AF11">
-        <v>1.47</v>
+        <v>-1.65</v>
       </c>
       <c r="AG11">
-        <v>189.15</v>
+        <v>189.36</v>
       </c>
       <c r="AH11">
-        <v>181.38</v>
+        <v>181.49</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2117,7 +2097,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>21.26</v>
+        <v>21.89</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2128,10 +2108,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2188.8</v>
+        <v>2190</v>
       </c>
       <c r="D12">
-        <v>-2.76</v>
+        <v>0.05</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2140,46 +2120,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-32.06</v>
+        <v>-32.03</v>
       </c>
       <c r="H12">
-        <v>10.4</v>
+        <v>10.46</v>
       </c>
       <c r="I12">
-        <v>-2.96</v>
+        <v>-0.82</v>
       </c>
       <c r="J12">
-        <v>-5.38</v>
+        <v>-3.95</v>
       </c>
       <c r="K12">
-        <v>-1.54</v>
+        <v>-0.6</v>
       </c>
       <c r="L12">
-        <v>-27.43</v>
+        <v>-27.6</v>
       </c>
       <c r="M12">
-        <v>-8.48</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="N12">
         <v>44</v>
       </c>
       <c r="O12">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P12">
-        <v>2210.54</v>
+        <v>2206.94</v>
       </c>
       <c r="Q12">
-        <v>2282.42</v>
+        <v>2277.47</v>
       </c>
       <c r="R12">
-        <v>2294.07</v>
+        <v>2296.72</v>
       </c>
       <c r="S12">
-        <v>2538.41</v>
+        <v>2534.16</v>
       </c>
       <c r="T12">
-        <v>-13.77</v>
+        <v>-13.58</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2194,34 +2174,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>39.24</v>
+        <v>39.41</v>
       </c>
       <c r="Z12">
-        <v>-27.29</v>
+        <v>-30.3</v>
       </c>
       <c r="AA12">
-        <v>-13.46</v>
+        <v>-16.83</v>
       </c>
       <c r="AB12">
-        <v>-13.83</v>
+        <v>-13.47</v>
       </c>
       <c r="AC12">
-        <v>13.55</v>
+        <v>15.63</v>
       </c>
       <c r="AD12">
-        <v>8.43</v>
+        <v>13.64</v>
       </c>
       <c r="AE12">
-        <v>63.68</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AF12">
-        <v>6.61</v>
+        <v>25.9</v>
       </c>
       <c r="AG12">
-        <v>2396.69</v>
+        <v>2398.89</v>
       </c>
       <c r="AH12">
-        <v>2168.14</v>
+        <v>2156.04</v>
       </c>
       <c r="AI12">
         <v>2377.09</v>
@@ -2230,7 +2210,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>27.11</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2241,10 +2221,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4908.5</v>
+        <v>4841</v>
       </c>
       <c r="D13">
-        <v>1.08</v>
+        <v>-1.38</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2253,46 +2233,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-5.04</v>
+        <v>-6.35</v>
       </c>
       <c r="H13">
-        <v>47.52</v>
+        <v>45.49</v>
       </c>
       <c r="I13">
-        <v>-1.57</v>
+        <v>-3.28</v>
       </c>
       <c r="J13">
-        <v>-2.92</v>
+        <v>-4.11</v>
       </c>
       <c r="K13">
-        <v>12.05</v>
+        <v>10.33</v>
       </c>
       <c r="L13">
-        <v>36.95</v>
+        <v>35.53</v>
       </c>
       <c r="M13">
-        <v>18.72</v>
+        <v>18.54</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P13">
-        <v>4960</v>
+        <v>4927.2</v>
       </c>
       <c r="Q13">
-        <v>5044.49</v>
+        <v>5033.14</v>
       </c>
       <c r="R13">
-        <v>4910.92</v>
+        <v>4916.02</v>
       </c>
       <c r="S13">
-        <v>4356.61</v>
+        <v>4361.27</v>
       </c>
       <c r="T13">
-        <v>12.67</v>
+        <v>11</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2307,43 +2287,43 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>42.46</v>
+        <v>37.44</v>
       </c>
       <c r="Z13">
-        <v>2.35</v>
+        <v>-9.69</v>
       </c>
       <c r="AA13">
-        <v>35.56</v>
+        <v>26.51</v>
       </c>
       <c r="AB13">
-        <v>-33.21</v>
+        <v>-36.2</v>
       </c>
       <c r="AC13">
-        <v>9.199999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="AD13">
-        <v>10.14</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AE13">
-        <v>80.69</v>
+        <v>80.42</v>
       </c>
       <c r="AF13">
-        <v>-23.94</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AG13">
-        <v>5194.14</v>
+        <v>5207.65</v>
       </c>
       <c r="AH13">
-        <v>4894.84</v>
+        <v>4858.63</v>
       </c>
       <c r="AI13">
-        <v>5125.31</v>
+        <v>5118.27</v>
       </c>
       <c r="AJ13" t="s">
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>47.37</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2354,10 +2334,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2769.7</v>
+        <v>2789</v>
       </c>
       <c r="D14">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
       <c r="E14">
         <v>5189.83</v>
@@ -2366,46 +2346,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-46.63</v>
+        <v>-46.26</v>
       </c>
       <c r="H14">
-        <v>26.24</v>
+        <v>27.12</v>
       </c>
       <c r="I14">
-        <v>-0.86</v>
+        <v>-1.1</v>
       </c>
       <c r="J14">
-        <v>-5.98</v>
+        <v>-5.2</v>
       </c>
       <c r="K14">
-        <v>-10.74</v>
+        <v>-12.29</v>
       </c>
       <c r="L14">
-        <v>-46.36</v>
+        <v>-45.55</v>
       </c>
       <c r="M14">
-        <v>22.82</v>
+        <v>23.32</v>
       </c>
       <c r="N14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O14">
         <v>10</v>
       </c>
       <c r="P14">
-        <v>2788.16</v>
+        <v>2781.96</v>
       </c>
       <c r="Q14">
-        <v>2858.57</v>
+        <v>2850.37</v>
       </c>
       <c r="R14">
-        <v>2917.06</v>
+        <v>2914.36</v>
       </c>
       <c r="S14">
-        <v>2935.25</v>
+        <v>2927.97</v>
       </c>
       <c r="T14">
-        <v>-5.64</v>
+        <v>-4.75</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2420,34 +2400,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>36.64</v>
+        <v>39.76</v>
       </c>
       <c r="Z14">
-        <v>-50.47</v>
+        <v>-48.93</v>
       </c>
       <c r="AA14">
-        <v>-42.44</v>
+        <v>-43.74</v>
       </c>
       <c r="AB14">
-        <v>-8.029999999999999</v>
+        <v>-5.19</v>
       </c>
       <c r="AC14">
-        <v>29.44</v>
+        <v>47.09</v>
       </c>
       <c r="AD14">
-        <v>32.39</v>
+        <v>34.12</v>
       </c>
       <c r="AE14">
-        <v>60.94</v>
+        <v>60.23</v>
       </c>
       <c r="AF14">
-        <v>1.02</v>
+        <v>-24.72</v>
       </c>
       <c r="AG14">
-        <v>2985.47</v>
+        <v>2972.69</v>
       </c>
       <c r="AH14">
-        <v>2731.67</v>
+        <v>2728.05</v>
       </c>
       <c r="AI14">
         <v>2944.37</v>
@@ -2456,7 +2436,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>45.53</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2467,10 +2447,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>213.97</v>
+        <v>219.49</v>
       </c>
       <c r="D15">
-        <v>0.46</v>
+        <v>2.58</v>
       </c>
       <c r="E15">
         <v>392.75</v>
@@ -2479,46 +2459,46 @@
         <v>213</v>
       </c>
       <c r="G15">
-        <v>-45.52</v>
+        <v>-44.11</v>
       </c>
       <c r="H15">
-        <v>0.46</v>
+        <v>3.05</v>
       </c>
       <c r="I15">
-        <v>-7.36</v>
+        <v>-4.06</v>
       </c>
       <c r="J15">
-        <v>-7.26</v>
+        <v>-5.03</v>
       </c>
       <c r="K15">
-        <v>-8.220000000000001</v>
+        <v>-7.21</v>
       </c>
       <c r="L15">
-        <v>-32.92</v>
+        <v>-32.04</v>
       </c>
       <c r="M15">
-        <v>11.78</v>
+        <v>12.88</v>
       </c>
       <c r="N15">
         <v>32</v>
       </c>
       <c r="O15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P15">
-        <v>219.72</v>
+        <v>217.86</v>
       </c>
       <c r="Q15">
-        <v>227.13</v>
+        <v>226.65</v>
       </c>
       <c r="R15">
-        <v>231.7</v>
+        <v>231.57</v>
       </c>
       <c r="S15">
-        <v>254.09</v>
+        <v>253.64</v>
       </c>
       <c r="T15">
-        <v>-15.79</v>
+        <v>-13.46</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2533,34 +2513,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>32.87</v>
+        <v>41.24</v>
       </c>
       <c r="Z15">
-        <v>-3.53</v>
+        <v>-3.59</v>
       </c>
       <c r="AA15">
-        <v>-2.01</v>
+        <v>-2.33</v>
       </c>
       <c r="AB15">
-        <v>-1.51</v>
+        <v>-1.26</v>
       </c>
       <c r="AC15">
-        <v>7.16</v>
+        <v>14.85</v>
       </c>
       <c r="AD15">
-        <v>12.66</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AE15">
-        <v>7.95</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AF15">
-        <v>27.33</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AG15">
-        <v>238.8</v>
+        <v>238.77</v>
       </c>
       <c r="AH15">
-        <v>215.46</v>
+        <v>214.54</v>
       </c>
       <c r="AI15">
         <v>239.5</v>
@@ -2569,7 +2549,7 @@
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>23.63</v>
+        <v>24.83</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2580,10 +2560,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>35.22</v>
+        <v>36.64</v>
       </c>
       <c r="D16">
-        <v>-2.57</v>
+        <v>4.03</v>
       </c>
       <c r="E16">
         <v>58.79</v>
@@ -2592,46 +2572,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-40.09</v>
+        <v>-37.68</v>
       </c>
       <c r="H16">
-        <v>12.31</v>
+        <v>16.84</v>
       </c>
       <c r="I16">
-        <v>-3.48</v>
+        <v>1.41</v>
       </c>
       <c r="J16">
-        <v>-8.73</v>
+        <v>-3.2</v>
       </c>
       <c r="K16">
-        <v>-22.54</v>
+        <v>-18.38</v>
       </c>
       <c r="L16">
-        <v>-38.41</v>
+        <v>-35.81</v>
       </c>
       <c r="M16">
-        <v>-0.49</v>
+        <v>-0.28</v>
       </c>
       <c r="N16">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="O16">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P16">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="Q16">
-        <v>37.23</v>
+        <v>37.18</v>
       </c>
       <c r="R16">
-        <v>38.72</v>
+        <v>38.65</v>
       </c>
       <c r="S16">
-        <v>42.55</v>
+        <v>42.48</v>
       </c>
       <c r="T16">
-        <v>-17.23</v>
+        <v>-13.74</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2646,34 +2626,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>31.8</v>
+        <v>44.17</v>
       </c>
       <c r="Z16">
-        <v>-0.89</v>
+        <v>-0.82</v>
       </c>
       <c r="AA16">
-        <v>-0.73</v>
+        <v>-0.75</v>
       </c>
       <c r="AB16">
-        <v>-0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC16">
-        <v>25.89</v>
+        <v>42.02</v>
       </c>
       <c r="AD16">
-        <v>25.01</v>
+        <v>31.55</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>-50.61</v>
+        <v>-17.07</v>
       </c>
       <c r="AG16">
-        <v>39.35</v>
+        <v>39.31</v>
       </c>
       <c r="AH16">
-        <v>35.11</v>
+        <v>35.05</v>
       </c>
       <c r="AI16">
         <v>38.7</v>
@@ -2682,7 +2662,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>22.03</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2693,10 +2673,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D17">
-        <v>-0.53</v>
+        <v>0.35</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2705,46 +2685,46 @@
         <v>1131</v>
       </c>
       <c r="G17">
-        <v>-27.33</v>
+        <v>-27.08</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I17">
-        <v>-1.21</v>
+        <v>-0.77</v>
       </c>
       <c r="J17">
-        <v>-10.73</v>
+        <v>-9.41</v>
       </c>
       <c r="K17">
         <v>-16.4</v>
       </c>
       <c r="L17">
-        <v>-18.69</v>
+        <v>-18.88</v>
       </c>
       <c r="M17">
-        <v>-1.49</v>
+        <v>-1.52</v>
       </c>
       <c r="N17">
         <v>38</v>
       </c>
       <c r="O17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P17">
-        <v>1147.06</v>
+        <v>1145.3</v>
       </c>
       <c r="Q17">
-        <v>1187.19</v>
+        <v>1182.79</v>
       </c>
       <c r="R17">
-        <v>1262.09</v>
+        <v>1259.71</v>
       </c>
       <c r="S17">
-        <v>1342.98</v>
+        <v>1341.79</v>
       </c>
       <c r="T17">
-        <v>-15.78</v>
+        <v>-15.41</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2759,43 +2739,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>31.49</v>
+        <v>32.88</v>
       </c>
       <c r="Z17">
-        <v>-35.5</v>
+        <v>-35.25</v>
       </c>
       <c r="AA17">
-        <v>-33.51</v>
+        <v>-33.85</v>
       </c>
       <c r="AB17">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="AC17">
-        <v>53.78</v>
+        <v>47.36</v>
       </c>
       <c r="AD17">
-        <v>54.5</v>
+        <v>53.63</v>
       </c>
       <c r="AE17">
-        <v>28.97</v>
+        <v>28.05</v>
       </c>
       <c r="AF17">
-        <v>-51.36</v>
+        <v>-50.87</v>
       </c>
       <c r="AG17">
-        <v>1260.82</v>
+        <v>1257.92</v>
       </c>
       <c r="AH17">
-        <v>1113.56</v>
+        <v>1107.66</v>
       </c>
       <c r="AI17">
-        <v>1226.77</v>
+        <v>1217.3</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>40.66</v>
+        <v>38.82</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +2956,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2996,7 +2976,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>64</v>
@@ -3016,7 +2996,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>64</v>
@@ -3035,28 +3015,28 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3068,2311 +3048,2311 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="6">
         <v>-0.92</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.23</v>
+      <c r="D10" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
+        <v>-13.26</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1.73</v>
+      </c>
+      <c r="E11" s="7">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.63</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="D13" s="6">
+        <v>19.34</v>
+      </c>
+      <c r="E13" s="7">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>5.11</v>
+      </c>
+      <c r="D14" s="6">
+        <v>6.02</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-6.76</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.51</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-10.59</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-7.65</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>4.19</v>
+      </c>
+      <c r="D17" s="6">
+        <v>11.14</v>
+      </c>
+      <c r="E17" s="7">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-5.53</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.15</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.61</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-5.38</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-3.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-2.92</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-4.11</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-5.98</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-5.2</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-7.26</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-5.03</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-8.73</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.2</v>
+      </c>
+      <c r="E24" s="7">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-10.73</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-9.41</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.54</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-3.6</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="6">
+        <v>20.42</v>
+      </c>
+      <c r="D29" s="6">
+        <v>29.23</v>
+      </c>
+      <c r="E29" s="7">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2.65</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1.27</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-3.41</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-0.04</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="6">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="D33" s="6">
+        <v>16.24</v>
+      </c>
+      <c r="E33" s="7">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-1.41</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-0.27</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-0.62</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-2.96</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-0.82</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-1.57</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-3.28</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-0.86</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-1.1</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-7.36</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-4.06</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-3.48</v>
+      </c>
+      <c r="D40" s="6">
+        <v>1.41</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4.89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-1.21</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-7.82</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-6.56</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="6">
+        <v>14.89</v>
+      </c>
+      <c r="D43" s="6">
+        <v>13.44</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-38.73</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-37.83</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-23.26</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-17.68</v>
+      </c>
+      <c r="E45" s="7">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="6">
+        <v>13.64</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-8.75</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-7.39</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-40.31</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-39.83</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-0.08</v>
+      </c>
+      <c r="D49" s="6">
+        <v>5.13</v>
+      </c>
+      <c r="E49" s="7">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-7.14</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-4.47</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="6">
+        <v>10.25</v>
+      </c>
+      <c r="D51" s="6">
+        <v>12.59</v>
+      </c>
+      <c r="E51" s="7">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-27.43</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-27.6</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="6">
+        <v>36.95</v>
+      </c>
+      <c r="D53" s="6">
+        <v>35.53</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-46.36</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-45.55</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="6">
+        <v>-32.92</v>
+      </c>
+      <c r="D55" s="6">
+        <v>-32.04</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-38.41</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-35.81</v>
+      </c>
+      <c r="E56" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-18.69</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-18.88</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="6">
+        <v>2.05</v>
+      </c>
+      <c r="D58" s="6">
+        <v>2.28</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="6">
+        <v>26.1</v>
+      </c>
+      <c r="D59" s="6">
+        <v>10.71</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-15.39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-11.13</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-10.64</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D61" s="6">
+        <v>6.37</v>
+      </c>
+      <c r="E61" s="7">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-5.29</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-7.74</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-11.06</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="E63" s="7">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-17.62</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-17.84</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="D65" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="E65" s="7">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-10.24</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-8.41</v>
+      </c>
+      <c r="E66" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-6.6</v>
+      </c>
+      <c r="E67" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-1.54</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="6">
+        <v>12.05</v>
+      </c>
+      <c r="D69" s="6">
+        <v>10.33</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-10.74</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-12.29</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-7.21</v>
+      </c>
+      <c r="E71" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-22.54</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-18.38</v>
+      </c>
+      <c r="E72" s="7">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="6">
         <v>-9.789999999999999</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D73" s="6">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="E73" s="7">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="6">
         <v>-13.26</v>
       </c>
-      <c r="E11" s="8">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="D74" s="6">
+        <v>-10.75</v>
+      </c>
+      <c r="E74" s="7">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-5.49</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-4.63</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-39.59</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-39.14</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>9.58</v>
-      </c>
-      <c r="D13" s="7">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-26.08</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-21.28</v>
+      </c>
+      <c r="E76" s="7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1.75</v>
-      </c>
-      <c r="D14" s="7">
-        <v>5.11</v>
-      </c>
-      <c r="E14" s="9">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-12.73</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-13.1</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-8.65</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-6.76</v>
-      </c>
-      <c r="E15" s="9">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-20.65</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-19.57</v>
+      </c>
+      <c r="E78" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-8.82</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-10.59</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-41.34</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-41.18</v>
+      </c>
+      <c r="E79" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>7.65</v>
-      </c>
-      <c r="D17" s="7">
-        <v>4.19</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-35.21</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-31.66</v>
+      </c>
+      <c r="E80" s="7">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-4.99</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-5.53</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-21.96</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-20.1</v>
+      </c>
+      <c r="E81" s="7">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.08</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.61</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-15.54</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-13.56</v>
+      </c>
+      <c r="E82" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-5.38</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6">
+        <v>-32.06</v>
+      </c>
+      <c r="D83" s="6">
+        <v>-32.03</v>
+      </c>
+      <c r="E83" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-3.96</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-2.92</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="D84" s="6">
+        <v>-6.35</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-8.33</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-5.98</v>
-      </c>
-      <c r="E22" s="9">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6">
+        <v>-46.63</v>
+      </c>
+      <c r="D85" s="6">
+        <v>-46.26</v>
+      </c>
+      <c r="E85" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-7.68</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-7.26</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="6">
+        <v>-45.52</v>
+      </c>
+      <c r="D86" s="6">
+        <v>-44.11</v>
+      </c>
+      <c r="E86" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-6.32</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-8.73</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="6">
+        <v>-40.09</v>
+      </c>
+      <c r="D87" s="6">
+        <v>-37.68</v>
+      </c>
+      <c r="E87" s="7">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-13.9</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-10.73</v>
-      </c>
-      <c r="E25" s="9">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B88" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="6">
+        <v>-27.33</v>
+      </c>
+      <c r="D88" s="6">
+        <v>-27.08</v>
+      </c>
+      <c r="E88" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-0.17</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.92</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B89" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="6">
+        <v>713.4</v>
+      </c>
+      <c r="D89" s="6">
+        <v>726.65</v>
+      </c>
+      <c r="E89" s="7">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-0.95</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-3.6</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B90" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="6">
+        <v>938.05</v>
+      </c>
+      <c r="D90" s="6">
+        <v>965.25</v>
+      </c>
+      <c r="E90" s="7">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-2.59</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-1.29</v>
-      </c>
-      <c r="E28" s="9">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B91" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="6">
+        <v>202.65</v>
+      </c>
+      <c r="D91" s="6">
+        <v>204.14</v>
+      </c>
+      <c r="E91" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="7">
-        <v>19.82</v>
-      </c>
-      <c r="D29" s="7">
-        <v>20.42</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B92" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="6">
+        <v>731.8</v>
+      </c>
+      <c r="D92" s="6">
+        <v>779.3</v>
+      </c>
+      <c r="E92" s="7">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D30" s="7">
-        <v>2.65</v>
-      </c>
-      <c r="E30" s="9">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B93" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C93" s="6">
+        <v>1799.3</v>
+      </c>
+      <c r="D93" s="6">
+        <v>1791.6</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-2.85</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-1.38</v>
-      </c>
-      <c r="E31" s="9">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B94" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="6">
+        <v>1000.1</v>
+      </c>
+      <c r="D94" s="6">
+        <v>1013.7</v>
+      </c>
+      <c r="E94" s="7">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-1.63</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-3.41</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B95" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" s="6">
+        <v>3373</v>
+      </c>
+      <c r="D95" s="6">
+        <v>3381.8</v>
+      </c>
+      <c r="E95" s="7">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="7">
-        <v>14.42</v>
-      </c>
-      <c r="D33" s="7">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-4.79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B96" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C96" s="6">
+        <v>681.95</v>
+      </c>
+      <c r="D96" s="6">
+        <v>719.3</v>
+      </c>
+      <c r="E96" s="7">
+        <v>37.35</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-0.74</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-1.41</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B97" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="6">
+        <v>360.4</v>
+      </c>
+      <c r="D97" s="6">
+        <v>369</v>
+      </c>
+      <c r="E97" s="7">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-1.06</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-0.62</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B98" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C98" s="6">
+        <v>183</v>
+      </c>
+      <c r="D98" s="6">
+        <v>187.29</v>
+      </c>
+      <c r="E98" s="7">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-0.84</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-2.96</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B99" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C99" s="6">
+        <v>2188.8</v>
+      </c>
+      <c r="D99" s="6">
+        <v>2190</v>
+      </c>
+      <c r="E99" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-2.78</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-1.57</v>
-      </c>
-      <c r="E37" s="9">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B100" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100" s="6">
+        <v>4908.5</v>
+      </c>
+      <c r="D100" s="6">
+        <v>4841</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-67.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-3</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-0.86</v>
-      </c>
-      <c r="E38" s="9">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B101" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="6">
+        <v>2769.7</v>
+      </c>
+      <c r="D101" s="6">
+        <v>2789</v>
+      </c>
+      <c r="E101" s="7">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-9.41</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-7.36</v>
-      </c>
-      <c r="E39" s="9">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B102" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C102" s="6">
+        <v>213.97</v>
+      </c>
+      <c r="D102" s="6">
+        <v>219.49</v>
+      </c>
+      <c r="E102" s="7">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B103" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="6">
+        <v>35.22</v>
+      </c>
+      <c r="D103" s="6">
+        <v>36.64</v>
+      </c>
+      <c r="E103" s="7">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-2.59</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-1.21</v>
-      </c>
-      <c r="E41" s="9">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B104" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" s="6">
+        <v>1131</v>
+      </c>
+      <c r="D104" s="6">
+        <v>1135</v>
+      </c>
+      <c r="E104" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-7.8</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-7.82</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="7">
-        <v>13.81</v>
-      </c>
-      <c r="D43" s="7">
-        <v>14.89</v>
-      </c>
-      <c r="E43" s="9">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-40.29</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-38.73</v>
-      </c>
-      <c r="E44" s="9">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-21.04</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-23.26</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="7">
-        <v>10.46</v>
-      </c>
-      <c r="D46" s="7">
-        <v>13.64</v>
-      </c>
-      <c r="E46" s="9">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-9.68</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-8.75</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-40.08</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-40.31</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="7">
-        <v>6.81</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-0.08</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-6.89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-6.08</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-7.14</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="7">
-        <v>10.63</v>
-      </c>
-      <c r="D51" s="7">
-        <v>10.25</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-25.03</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-27.43</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="7">
-        <v>34.12</v>
-      </c>
-      <c r="D53" s="7">
-        <v>36.95</v>
-      </c>
-      <c r="E53" s="9">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-47.35</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-46.36</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-32.95</v>
-      </c>
-      <c r="D55" s="7">
-        <v>-32.92</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="7">
-        <v>-36.67</v>
-      </c>
-      <c r="D56" s="7">
-        <v>-38.41</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="7">
-        <v>-18.23</v>
-      </c>
-      <c r="D57" s="7">
-        <v>-18.69</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="7">
-        <v>2.97</v>
-      </c>
-      <c r="D58" s="7">
-        <v>2.05</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="7">
-        <v>27.38</v>
-      </c>
-      <c r="D59" s="7">
-        <v>26.1</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="7">
-        <v>-12.44</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-11.13</v>
-      </c>
-      <c r="E60" s="9">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="D61" s="7">
-        <v>0.38</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-8.640000000000001</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-5.29</v>
-      </c>
-      <c r="E62" s="9">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-12.8</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-11.06</v>
-      </c>
-      <c r="E63" s="9">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-16.48</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-17.62</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="7">
-        <v>6.75</v>
-      </c>
-      <c r="D65" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-5.82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-9.76</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-10.24</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-6.3</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="7">
-        <v>2.36</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-1.54</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="7">
-        <v>11.94</v>
-      </c>
-      <c r="D69" s="7">
-        <v>12.05</v>
-      </c>
-      <c r="E69" s="9">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="7">
-        <v>-5.79</v>
-      </c>
-      <c r="D70" s="7">
-        <v>-10.74</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="7">
-        <v>-8.84</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E71" s="9">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-19.33</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-22.54</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-14.36</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-16.4</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-9.59</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-9.789999999999999</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-14.54</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-13.26</v>
-      </c>
-      <c r="E75" s="9">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-40.13</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-39.59</v>
-      </c>
-      <c r="E76" s="9">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-25.76</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-26.08</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-15.21</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-12.73</v>
-      </c>
-      <c r="E78" s="9">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-21.76</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-20.65</v>
-      </c>
-      <c r="E79" s="9">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-40.17</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-41.34</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-31.75</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-35.21</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-21.39</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-21.96</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-15.24</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-15.54</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-30.13</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-32.06</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="7">
-        <v>-6.06</v>
-      </c>
-      <c r="D85" s="7">
-        <v>-5.04</v>
-      </c>
-      <c r="E85" s="9">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="7">
-        <v>-47.4</v>
-      </c>
-      <c r="D86" s="7">
-        <v>-46.63</v>
-      </c>
-      <c r="E86" s="9">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="7">
-        <v>-45.77</v>
-      </c>
-      <c r="D87" s="7">
-        <v>-45.52</v>
-      </c>
-      <c r="E87" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="7">
-        <v>-38.51</v>
-      </c>
-      <c r="D88" s="7">
-        <v>-40.09</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="7">
-        <v>-26.95</v>
-      </c>
-      <c r="D89" s="7">
-        <v>-27.33</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C90" s="7">
-        <v>715</v>
-      </c>
-      <c r="D90" s="7">
-        <v>713.4</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C91" s="7">
-        <v>924.3</v>
-      </c>
-      <c r="D91" s="7">
-        <v>938.05</v>
-      </c>
-      <c r="E91" s="9">
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C92" s="7">
-        <v>200.82</v>
-      </c>
-      <c r="D92" s="7">
-        <v>202.65</v>
-      </c>
-      <c r="E92" s="9">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C93" s="7">
-        <v>734.9</v>
-      </c>
-      <c r="D93" s="7">
-        <v>731.8</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C94" s="7">
-        <v>1748.2</v>
-      </c>
-      <c r="D94" s="7">
-        <v>1799.3</v>
-      </c>
-      <c r="E94" s="9">
-        <v>51.1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C95" s="7">
-        <v>986.1</v>
-      </c>
-      <c r="D95" s="7">
-        <v>1000.1</v>
-      </c>
-      <c r="E95" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C96" s="7">
-        <v>3440</v>
-      </c>
-      <c r="D96" s="7">
-        <v>3373</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-67</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C97" s="7">
-        <v>718.35</v>
-      </c>
-      <c r="D97" s="7">
-        <v>681.95</v>
-      </c>
-      <c r="E97" s="8">
-        <v>-36.4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C98" s="7">
-        <v>363</v>
-      </c>
-      <c r="D98" s="7">
-        <v>360.4</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C99" s="7">
-        <v>183.65</v>
-      </c>
-      <c r="D99" s="7">
-        <v>183</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C100" s="7">
-        <v>2251</v>
-      </c>
-      <c r="D100" s="7">
-        <v>2188.8</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-62.2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C101" s="7">
-        <v>4856</v>
-      </c>
-      <c r="D101" s="7">
-        <v>4908.5</v>
-      </c>
-      <c r="E101" s="9">
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C102" s="7">
-        <v>2730</v>
-      </c>
-      <c r="D102" s="7">
-        <v>2769.7</v>
-      </c>
-      <c r="E102" s="9">
-        <v>39.7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C103" s="7">
-        <v>213</v>
-      </c>
-      <c r="D103" s="7">
-        <v>213.97</v>
-      </c>
-      <c r="E103" s="9">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C104" s="7">
-        <v>36.15</v>
-      </c>
-      <c r="D104" s="7">
-        <v>35.22</v>
-      </c>
-      <c r="E104" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C105" s="7">
-        <v>1137</v>
-      </c>
-      <c r="D105" s="7">
-        <v>1131</v>
+      <c r="B105" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" s="6">
+        <v>68</v>
+      </c>
+      <c r="D105" s="6">
+        <v>62</v>
       </c>
       <c r="E105" s="8">
         <v>-6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="6">
+        <v>62</v>
+      </c>
+      <c r="D106" s="6">
+        <v>68</v>
+      </c>
+      <c r="E106" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B107" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C106" s="7">
+      <c r="C107" s="6">
+        <v>87</v>
+      </c>
+      <c r="D107" s="6">
         <v>74</v>
       </c>
-      <c r="D106" s="7">
+      <c r="E107" s="8">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="6">
+        <v>13</v>
+      </c>
+      <c r="D108" s="6">
+        <v>7</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="6">
+        <v>81</v>
+      </c>
+      <c r="D109" s="6">
         <v>87</v>
       </c>
-      <c r="E106" s="9">
+      <c r="E109" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B107" s="6" t="s">
+      <c r="C110" s="6">
+        <v>74</v>
+      </c>
+      <c r="D110" s="6">
+        <v>81</v>
+      </c>
+      <c r="E110" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C107" s="7">
-        <v>44</v>
-      </c>
-      <c r="D107" s="7">
-        <v>50</v>
-      </c>
-      <c r="E107" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B108" s="6" t="s">
+      <c r="C111" s="6">
+        <v>19</v>
+      </c>
+      <c r="D111" s="6">
         <v>13</v>
-      </c>
-      <c r="C108" s="7">
-        <v>7</v>
-      </c>
-      <c r="D108" s="7">
-        <v>13</v>
-      </c>
-      <c r="E108" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" s="7">
-        <v>87</v>
-      </c>
-      <c r="D109" s="7">
-        <v>81</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C110" s="7">
-        <v>81</v>
-      </c>
-      <c r="D110" s="7">
-        <v>74</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" s="7">
-        <v>50</v>
-      </c>
-      <c r="D111" s="7">
-        <v>44</v>
       </c>
       <c r="E111" s="8">
         <v>-6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C112" s="7">
-        <v>13</v>
-      </c>
-      <c r="D112" s="7">
+      <c r="C112" s="6">
         <v>7</v>
       </c>
-      <c r="E112" s="8">
-        <v>-6</v>
+      <c r="D112" s="6">
+        <v>19</v>
+      </c>
+      <c r="E112" s="7">
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C113" s="7">
-        <v>45.46</v>
-      </c>
-      <c r="D113" s="7">
+      <c r="C113" s="6">
         <v>44.65</v>
       </c>
-      <c r="E113" s="8">
-        <v>-0.8100000000000001</v>
+      <c r="D113" s="6">
+        <v>52.26</v>
+      </c>
+      <c r="E113" s="7">
+        <v>7.61</v>
       </c>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C114" s="7">
-        <v>46.6</v>
-      </c>
-      <c r="D114" s="7">
+      <c r="C114" s="6">
         <v>49.15</v>
       </c>
-      <c r="E114" s="9">
-        <v>2.55</v>
+      <c r="D114" s="6">
+        <v>53.85</v>
+      </c>
+      <c r="E114" s="7">
+        <v>4.7</v>
       </c>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C115" s="7">
-        <v>26.76</v>
-      </c>
-      <c r="D115" s="7">
+      <c r="C115" s="6">
         <v>33.1</v>
       </c>
-      <c r="E115" s="9">
-        <v>6.34</v>
+      <c r="D115" s="6">
+        <v>37.83</v>
+      </c>
+      <c r="E115" s="7">
+        <v>4.73</v>
       </c>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C116" s="7">
-        <v>72.37</v>
-      </c>
-      <c r="D116" s="7">
+      <c r="C116" s="6">
         <v>71.25</v>
       </c>
-      <c r="E116" s="8">
-        <v>-1.12</v>
+      <c r="D116" s="6">
+        <v>77.08</v>
+      </c>
+      <c r="E116" s="7">
+        <v>5.83</v>
       </c>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C117" s="7">
-        <v>51.74</v>
-      </c>
-      <c r="D117" s="7">
+      <c r="C117" s="6">
         <v>59.6</v>
       </c>
-      <c r="E117" s="9">
-        <v>7.86</v>
+      <c r="D117" s="6">
+        <v>58.07</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C118" s="7">
-        <v>28.09</v>
-      </c>
-      <c r="D118" s="7">
+      <c r="C118" s="6">
         <v>35.91</v>
       </c>
-      <c r="E118" s="9">
-        <v>7.82</v>
+      <c r="D118" s="6">
+        <v>42.45</v>
+      </c>
+      <c r="E118" s="7">
+        <v>6.54</v>
       </c>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C119" s="7">
-        <v>37.45</v>
-      </c>
-      <c r="D119" s="7">
+      <c r="C119" s="6">
         <v>33.45</v>
       </c>
-      <c r="E119" s="8">
-        <v>-4</v>
+      <c r="D119" s="6">
+        <v>34.44</v>
+      </c>
+      <c r="E119" s="7">
+        <v>0.99</v>
       </c>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C120" s="7">
-        <v>73.04000000000001</v>
-      </c>
-      <c r="D120" s="7">
+      <c r="C120" s="6">
         <v>58.48</v>
       </c>
-      <c r="E120" s="8">
-        <v>-14.56</v>
+      <c r="D120" s="6">
+        <v>65.97</v>
+      </c>
+      <c r="E120" s="7">
+        <v>7.49</v>
       </c>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C121" s="7">
-        <v>43.36</v>
-      </c>
-      <c r="D121" s="7">
+      <c r="C121" s="6">
         <v>40.81</v>
       </c>
-      <c r="E121" s="8">
-        <v>-2.55</v>
+      <c r="D121" s="6">
+        <v>51.08</v>
+      </c>
+      <c r="E121" s="7">
+        <v>10.27</v>
       </c>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C122" s="7">
-        <v>45.21</v>
-      </c>
-      <c r="D122" s="7">
+      <c r="C122" s="6">
         <v>44.04</v>
       </c>
-      <c r="E122" s="8">
-        <v>-1.17</v>
+      <c r="D122" s="6">
+        <v>52.71</v>
+      </c>
+      <c r="E122" s="7">
+        <v>8.67</v>
       </c>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C123" s="7">
-        <v>45.35</v>
-      </c>
-      <c r="D123" s="7">
+      <c r="C123" s="6">
         <v>39.24</v>
       </c>
-      <c r="E123" s="8">
-        <v>-6.11</v>
+      <c r="D123" s="6">
+        <v>39.41</v>
+      </c>
+      <c r="E123" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="B124" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C124" s="7">
-        <v>36.29</v>
-      </c>
-      <c r="D124" s="7">
+      <c r="C124" s="6">
         <v>42.46</v>
       </c>
-      <c r="E124" s="9">
-        <v>6.17</v>
+      <c r="D124" s="6">
+        <v>37.44</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-5.02</v>
       </c>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B125" s="6" t="s">
+      <c r="B125" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C125" s="7">
-        <v>29.71</v>
-      </c>
-      <c r="D125" s="7">
+      <c r="C125" s="6">
         <v>36.64</v>
       </c>
-      <c r="E125" s="9">
-        <v>6.93</v>
+      <c r="D125" s="6">
+        <v>39.76</v>
+      </c>
+      <c r="E125" s="7">
+        <v>3.12</v>
       </c>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B126" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C126" s="7">
-        <v>31.27</v>
-      </c>
-      <c r="D126" s="7">
+      <c r="C126" s="6">
         <v>32.87</v>
       </c>
-      <c r="E126" s="9">
-        <v>1.6</v>
+      <c r="D126" s="6">
+        <v>41.24</v>
+      </c>
+      <c r="E126" s="7">
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B127" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C127" s="7">
-        <v>36.75</v>
-      </c>
-      <c r="D127" s="7">
+      <c r="C127" s="6">
         <v>31.8</v>
       </c>
-      <c r="E127" s="8">
-        <v>-4.95</v>
+      <c r="D127" s="6">
+        <v>44.17</v>
+      </c>
+      <c r="E127" s="7">
+        <v>12.37</v>
       </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B128" s="6" t="s">
+      <c r="B128" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C128" s="7">
-        <v>32.42</v>
-      </c>
-      <c r="D128" s="7">
+      <c r="C128" s="6">
         <v>31.49</v>
       </c>
-      <c r="E128" s="8">
-        <v>-0.93</v>
+      <c r="D128" s="6">
+        <v>32.88</v>
+      </c>
+      <c r="E128" s="7">
+        <v>1.39</v>
       </c>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C129" s="7">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="D129" s="7">
+      <c r="C129" s="6">
         <v>-31.89</v>
       </c>
-      <c r="E129" s="8">
-        <v>-96.43000000000001</v>
+      <c r="D129" s="6">
+        <v>10.29</v>
+      </c>
+      <c r="E129" s="7">
+        <v>42.18</v>
       </c>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B130" s="6" t="s">
+      <c r="B130" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C130" s="7">
-        <v>-55.13</v>
-      </c>
-      <c r="D130" s="7">
+      <c r="C130" s="6">
         <v>-53.57</v>
       </c>
-      <c r="E130" s="9">
-        <v>1.56</v>
+      <c r="D130" s="6">
+        <v>-55.34</v>
+      </c>
+      <c r="E130" s="8">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="6" t="s">
+      <c r="A131" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B131" s="6" t="s">
+      <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="7">
-        <v>68.79000000000001</v>
-      </c>
-      <c r="D131" s="7">
+      <c r="C131" s="6">
         <v>-0.23</v>
       </c>
+      <c r="D131" s="6">
+        <v>-12.55</v>
+      </c>
       <c r="E131" s="8">
-        <v>-69.02</v>
+        <v>-12.32</v>
       </c>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B132" s="6" t="s">
+      <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C132" s="7">
-        <v>253.98</v>
-      </c>
-      <c r="D132" s="7">
+      <c r="C132" s="6">
         <v>4261.14</v>
       </c>
-      <c r="E132" s="9">
-        <v>4007.16</v>
+      <c r="D132" s="6">
+        <v>701.4</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-3559.74</v>
       </c>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B133" s="6" t="s">
+      <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C133" s="7">
-        <v>9.92</v>
-      </c>
-      <c r="D133" s="7">
+      <c r="C133" s="6">
         <v>20.9</v>
       </c>
-      <c r="E133" s="9">
-        <v>10.98</v>
+      <c r="D133" s="6">
+        <v>16.86</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B134" s="6" t="s">
+      <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C134" s="7">
-        <v>46.75</v>
-      </c>
-      <c r="D134" s="7">
+      <c r="C134" s="6">
         <v>43.91</v>
       </c>
-      <c r="E134" s="8">
-        <v>-2.84</v>
+      <c r="D134" s="6">
+        <v>74.61</v>
+      </c>
+      <c r="E134" s="7">
+        <v>30.7</v>
       </c>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="6" t="s">
+      <c r="A135" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B135" s="6" t="s">
+      <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C135" s="7">
-        <v>154.59</v>
-      </c>
-      <c r="D135" s="7">
+      <c r="C135" s="6">
         <v>1.89</v>
       </c>
+      <c r="D135" s="6">
+        <v>-32.88</v>
+      </c>
       <c r="E135" s="8">
-        <v>-152.7</v>
+        <v>-34.77</v>
       </c>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B136" s="6" t="s">
+      <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C136" s="7">
-        <v>4295.66</v>
-      </c>
-      <c r="D136" s="7">
+      <c r="C136" s="6">
         <v>182.6</v>
       </c>
+      <c r="D136" s="6">
+        <v>92.64</v>
+      </c>
       <c r="E136" s="8">
-        <v>-4113.06</v>
+        <v>-89.95999999999999</v>
       </c>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C137" s="7">
-        <v>-32.04</v>
-      </c>
-      <c r="D137" s="7">
+      <c r="C137" s="6">
         <v>-44.71</v>
       </c>
+      <c r="D137" s="6">
+        <v>-45.63</v>
+      </c>
       <c r="E137" s="8">
-        <v>-12.67</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C138" s="7">
-        <v>12.56</v>
-      </c>
-      <c r="D138" s="7">
+      <c r="C138" s="6">
         <v>1.47</v>
       </c>
+      <c r="D138" s="6">
+        <v>-1.65</v>
+      </c>
       <c r="E138" s="8">
-        <v>-11.09</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="6" t="s">
+      <c r="A139" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C139" s="7">
-        <v>121.48</v>
-      </c>
-      <c r="D139" s="7">
+      <c r="C139" s="6">
         <v>6.61</v>
       </c>
-      <c r="E139" s="8">
-        <v>-114.87</v>
+      <c r="D139" s="6">
+        <v>25.9</v>
+      </c>
+      <c r="E139" s="7">
+        <v>19.29</v>
       </c>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C140" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="D140" s="7">
+      <c r="C140" s="6">
         <v>-23.94</v>
       </c>
-      <c r="E140" s="8">
-        <v>-25.14</v>
+      <c r="D140" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E140" s="7">
+        <v>24.75</v>
       </c>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="B141" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C141" s="7">
-        <v>-26.06</v>
-      </c>
-      <c r="D141" s="7">
+      <c r="C141" s="6">
         <v>1.02</v>
       </c>
-      <c r="E141" s="9">
-        <v>27.08</v>
+      <c r="D141" s="6">
+        <v>-24.72</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-25.74</v>
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="6" t="s">
+      <c r="A142" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B142" s="6" t="s">
+      <c r="B142" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C142" s="7">
-        <v>358.6</v>
-      </c>
-      <c r="D142" s="7">
+      <c r="C142" s="6">
         <v>27.33</v>
       </c>
-      <c r="E142" s="8">
-        <v>-331.27</v>
+      <c r="D142" s="6">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="E142" s="7">
+        <v>45.82</v>
       </c>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C143" s="7">
-        <v>-23.42</v>
-      </c>
-      <c r="D143" s="7">
+      <c r="C143" s="6">
         <v>-50.61</v>
       </c>
-      <c r="E143" s="8">
-        <v>-27.19</v>
+      <c r="D143" s="6">
+        <v>-17.07</v>
+      </c>
+      <c r="E143" s="7">
+        <v>33.54</v>
       </c>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B144" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C144" s="7">
-        <v>-54.54</v>
-      </c>
-      <c r="D144" s="7">
+      <c r="C144" s="6">
         <v>-51.36</v>
       </c>
-      <c r="E144" s="9">
-        <v>3.18</v>
+      <c r="D144" s="6">
+        <v>-50.87</v>
+      </c>
+      <c r="E144" s="7">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -5398,60 +5378,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>47.24</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>16</v>
       </c>
-      <c r="D2" s="12">
-        <v>42.8</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="12">
-        <v>-4.1</v>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="G2" s="11">
         <v>-5.1</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <v>53.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -5553,107 +5533,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="15">
-        <v>0.4163</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3682</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2282</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2145</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1872</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1219</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.1178</v>
-      </c>
-      <c r="H2" s="15">
-        <v>0.08109999999999999</v>
-      </c>
-      <c r="I2" s="15">
-        <v>0.0667</v>
-      </c>
-      <c r="J2" s="15">
-        <v>0.0359</v>
+      <c r="A2" s="14">
+        <v>0.4277</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3842</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2332</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2244</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1854</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1387</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1288</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.094</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0.0621</v>
+      </c>
+      <c r="J2" s="14">
+        <v>0.0386</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="15">
-        <v>-0.0049</v>
-      </c>
-      <c r="B4" s="15">
-        <v>-0.0149</v>
-      </c>
-      <c r="C4" s="15">
-        <v>-0.019</v>
-      </c>
-      <c r="D4" s="15">
-        <v>-0.0601</v>
-      </c>
-      <c r="E4" s="15">
-        <v>-0.0718</v>
-      </c>
-      <c r="F4" s="15">
-        <v>-0.0848</v>
+      <c r="A4" s="14">
+        <v>-0.0017</v>
+      </c>
+      <c r="B4" s="14">
+        <v>-0.0028</v>
+      </c>
+      <c r="C4" s="14">
+        <v>-0.0152</v>
+      </c>
+      <c r="D4" s="14">
+        <v>-0.0579</v>
+      </c>
+      <c r="E4" s="14">
+        <v>-0.08119999999999999</v>
+      </c>
+      <c r="F4" s="14">
+        <v>-0.083</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="93">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,34 +214,52 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>77.1 → 55.2</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>77.1</t>
-  </si>
-  <si>
-    <t>55.2</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.5 → 30.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>29.1 → 39.0</t>
+  </si>
+  <si>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>39.0</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.7 → 49.4</t>
+    <t>55.8 → 47.4</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.7</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>55.8</t>
+  </si>
+  <si>
+    <t>47.4</t>
+  </si>
+  <si>
+    <t>56.5 → 48.8</t>
+  </si>
+  <si>
+    <t>56.5</t>
+  </si>
+  <si>
+    <t>48.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -293,7 +311,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,7 +345,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -339,15 +357,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -374,19 +385,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,12 +472,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -481,7 +486,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -828,7 +833,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="3" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -979,10 +985,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>732.75</v>
+        <v>745</v>
       </c>
       <c r="D2">
-        <v>0.84</v>
+        <v>1.67</v>
       </c>
       <c r="E2">
         <v>782.05</v>
@@ -991,46 +997,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-6.3</v>
+        <v>-4.74</v>
       </c>
       <c r="H2">
-        <v>28.34</v>
+        <v>30.48</v>
       </c>
       <c r="I2">
-        <v>2.38</v>
+        <v>3.69</v>
       </c>
       <c r="J2">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="K2">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="L2">
-        <v>-7.35</v>
+        <v>-4.32</v>
       </c>
       <c r="M2">
-        <v>36.57</v>
+        <v>36.41</v>
       </c>
       <c r="N2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>721.26</v>
+        <v>726.5599999999999</v>
       </c>
       <c r="Q2">
-        <v>722.5700000000001</v>
+        <v>723.3200000000001</v>
       </c>
       <c r="R2">
-        <v>728.65</v>
+        <v>728.5</v>
       </c>
       <c r="S2">
-        <v>688.22</v>
+        <v>688.23</v>
       </c>
       <c r="T2">
-        <v>6.47</v>
+        <v>8.25</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1045,34 +1051,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.31</v>
+        <v>60.74</v>
       </c>
       <c r="Z2">
-        <v>-0.98</v>
+        <v>0.91</v>
       </c>
       <c r="AA2">
-        <v>-1.8</v>
+        <v>-1.26</v>
       </c>
       <c r="AB2">
-        <v>0.83</v>
+        <v>2.17</v>
       </c>
       <c r="AC2">
-        <v>71.44</v>
+        <v>91.12</v>
       </c>
       <c r="AD2">
-        <v>57.87</v>
+        <v>72.66</v>
       </c>
       <c r="AE2">
-        <v>15.4</v>
+        <v>15.89</v>
       </c>
       <c r="AF2">
-        <v>107.97</v>
+        <v>77.73</v>
       </c>
       <c r="AG2">
-        <v>738.34</v>
+        <v>741.77</v>
       </c>
       <c r="AH2">
-        <v>706.8</v>
+        <v>704.87</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1081,7 +1087,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>21.69</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1092,10 +1098,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>1011.85</v>
+        <v>986.35</v>
       </c>
       <c r="D3">
-        <v>4.83</v>
+        <v>-2.52</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1104,46 +1110,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-6.44</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H3">
-        <v>100.22</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I3">
-        <v>7.92</v>
+        <v>4.13</v>
       </c>
       <c r="J3">
-        <v>11.18</v>
+        <v>8.15</v>
       </c>
       <c r="K3">
-        <v>7.6</v>
+        <v>6.62</v>
       </c>
       <c r="L3">
-        <v>19.83</v>
+        <v>17.2</v>
       </c>
       <c r="M3">
-        <v>13.85</v>
+        <v>12.16</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>957.34</v>
+        <v>965.16</v>
       </c>
       <c r="Q3">
-        <v>942.23</v>
+        <v>946.21</v>
       </c>
       <c r="R3">
-        <v>946.86</v>
+        <v>948.78</v>
       </c>
       <c r="S3">
-        <v>758.28</v>
+        <v>759.0599999999999</v>
       </c>
       <c r="T3">
-        <v>33.44</v>
+        <v>29.94</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1158,34 +1164,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>60.58</v>
+        <v>55.79</v>
       </c>
       <c r="Z3">
-        <v>5.49</v>
+        <v>7.59</v>
       </c>
       <c r="AA3">
-        <v>0.77</v>
+        <v>2.13</v>
       </c>
       <c r="AB3">
-        <v>4.73</v>
+        <v>5.46</v>
       </c>
       <c r="AC3">
-        <v>77.78</v>
+        <v>86.36</v>
       </c>
       <c r="AD3">
-        <v>56.72</v>
+        <v>71.84</v>
       </c>
       <c r="AE3">
-        <v>45.89</v>
+        <v>45.29</v>
       </c>
       <c r="AF3">
-        <v>94.31999999999999</v>
+        <v>-39.9</v>
       </c>
       <c r="AG3">
-        <v>991.74</v>
+        <v>996.5</v>
       </c>
       <c r="AH3">
-        <v>892.72</v>
+        <v>895.92</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1194,7 +1200,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>17.96</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1205,10 +1211,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>203.8</v>
+        <v>202.15</v>
       </c>
       <c r="D4">
-        <v>-0.17</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E4">
         <v>335.45</v>
@@ -1217,46 +1223,46 @@
         <v>200.82</v>
       </c>
       <c r="G4">
-        <v>-39.25</v>
+        <v>-39.74</v>
       </c>
       <c r="H4">
-        <v>1.48</v>
+        <v>0.66</v>
       </c>
       <c r="I4">
-        <v>0.36</v>
+        <v>0.08</v>
       </c>
       <c r="J4">
-        <v>-3.74</v>
+        <v>-5.03</v>
       </c>
       <c r="K4">
-        <v>-11.31</v>
+        <v>-13.48</v>
       </c>
       <c r="L4">
-        <v>-38.66</v>
+        <v>-39.65</v>
       </c>
       <c r="M4">
-        <v>-5.52</v>
+        <v>-5.68</v>
       </c>
       <c r="N4">
         <v>26</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>202.68</v>
+        <v>202.71</v>
       </c>
       <c r="Q4">
-        <v>207.23</v>
+        <v>206.73</v>
       </c>
       <c r="R4">
-        <v>215.2</v>
+        <v>214.66</v>
       </c>
       <c r="S4">
-        <v>242.62</v>
+        <v>242.32</v>
       </c>
       <c r="T4">
-        <v>-16</v>
+        <v>-16.58</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1271,34 +1277,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.18</v>
+        <v>34.14</v>
       </c>
       <c r="Z4">
-        <v>-3.44</v>
+        <v>-3.4</v>
       </c>
       <c r="AA4">
-        <v>-3.52</v>
+        <v>-3.49</v>
       </c>
       <c r="AB4">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AC4">
-        <v>66.27</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="AD4">
-        <v>40.95</v>
+        <v>58.82</v>
       </c>
       <c r="AE4">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="AF4">
-        <v>-24.33</v>
+        <v>-37.74</v>
       </c>
       <c r="AG4">
-        <v>215.06</v>
+        <v>214.51</v>
       </c>
       <c r="AH4">
-        <v>199.4</v>
+        <v>198.95</v>
       </c>
       <c r="AI4">
         <v>214.01</v>
@@ -1307,7 +1313,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>24.06</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1318,10 +1324,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>693.25</v>
+        <v>694.7</v>
       </c>
       <c r="D5">
-        <v>-11.04</v>
+        <v>0.21</v>
       </c>
       <c r="E5">
         <v>989.9299999999999</v>
@@ -1330,46 +1336,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-29.97</v>
+        <v>-29.82</v>
       </c>
       <c r="H5">
-        <v>20.69</v>
+        <v>20.94</v>
       </c>
       <c r="I5">
-        <v>13.55</v>
+        <v>13.43</v>
       </c>
       <c r="J5">
-        <v>8.949999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="K5">
-        <v>-4.92</v>
+        <v>-5.28</v>
       </c>
       <c r="L5">
-        <v>-27.83</v>
+        <v>-28.21</v>
       </c>
       <c r="M5">
-        <v>-1.41</v>
+        <v>-1.42</v>
       </c>
       <c r="N5">
         <v>50</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P5">
-        <v>710.34</v>
+        <v>726.79</v>
       </c>
       <c r="Q5">
-        <v>649.05</v>
+        <v>652.4400000000001</v>
       </c>
       <c r="R5">
-        <v>666.8200000000001</v>
+        <v>666.29</v>
       </c>
       <c r="S5">
-        <v>703.71</v>
+        <v>703.29</v>
       </c>
       <c r="T5">
-        <v>-1.49</v>
+        <v>-1.22</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1384,34 +1390,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>55.24</v>
+        <v>55.47</v>
       </c>
       <c r="Z5">
-        <v>12.65</v>
+        <v>13.18</v>
       </c>
       <c r="AA5">
-        <v>-1.81</v>
+        <v>1.19</v>
       </c>
       <c r="AB5">
-        <v>14.46</v>
+        <v>11.99</v>
       </c>
       <c r="AC5">
-        <v>84.09</v>
+        <v>70.05</v>
       </c>
       <c r="AD5">
-        <v>88.27</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="AE5">
-        <v>37.95</v>
+        <v>37.38</v>
       </c>
       <c r="AF5">
-        <v>474.73</v>
+        <v>4.99</v>
       </c>
       <c r="AG5">
-        <v>745.1799999999999</v>
+        <v>750.05</v>
       </c>
       <c r="AH5">
-        <v>552.92</v>
+        <v>554.84</v>
       </c>
       <c r="AI5">
         <v>677.03</v>
@@ -1420,7 +1426,7 @@
         <v>56</v>
       </c>
       <c r="AK5">
-        <v>39.69</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1431,10 +1437,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1780.1</v>
+        <v>1732.7</v>
       </c>
       <c r="D6">
-        <v>-0.64</v>
+        <v>-2.66</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1443,46 +1449,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-13.66</v>
+        <v>-15.96</v>
       </c>
       <c r="H6">
-        <v>32.06</v>
+        <v>28.55</v>
       </c>
       <c r="I6">
-        <v>0.89</v>
+        <v>-1.64</v>
       </c>
       <c r="J6">
-        <v>7.23</v>
+        <v>3.29</v>
       </c>
       <c r="K6">
-        <v>-10.49</v>
+        <v>-15.96</v>
       </c>
       <c r="L6">
-        <v>6.57</v>
+        <v>1.1</v>
       </c>
       <c r="M6">
-        <v>6.24</v>
+        <v>5.26</v>
       </c>
       <c r="N6">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O6">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>1776.16</v>
+        <v>1770.38</v>
       </c>
       <c r="Q6">
-        <v>1730.32</v>
+        <v>1734.19</v>
       </c>
       <c r="R6">
-        <v>1753.66</v>
+        <v>1751.19</v>
       </c>
       <c r="S6">
-        <v>1712.28</v>
+        <v>1711.7</v>
       </c>
       <c r="T6">
-        <v>3.96</v>
+        <v>1.23</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1497,34 +1503,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>55.76</v>
+        <v>47.39</v>
       </c>
       <c r="Z6">
-        <v>10.72</v>
+        <v>7.77</v>
       </c>
       <c r="AA6">
-        <v>0.32</v>
+        <v>1.81</v>
       </c>
       <c r="AB6">
-        <v>10.4</v>
+        <v>5.96</v>
       </c>
       <c r="AC6">
-        <v>88.20999999999999</v>
+        <v>61.07</v>
       </c>
       <c r="AD6">
-        <v>89.02</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="AE6">
-        <v>50.58</v>
+        <v>51.58</v>
       </c>
       <c r="AF6">
-        <v>170.92</v>
+        <v>-60.93</v>
       </c>
       <c r="AG6">
-        <v>1817.25</v>
+        <v>1813.64</v>
       </c>
       <c r="AH6">
-        <v>1643.39</v>
+        <v>1654.73</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1533,7 +1539,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>29.79</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1544,10 +1550,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>996</v>
+        <v>1000.6</v>
       </c>
       <c r="D7">
-        <v>-1.75</v>
+        <v>0.46</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1556,46 +1562,46 @@
         <v>986.1</v>
       </c>
       <c r="G7">
-        <v>-20.97</v>
+        <v>-20.61</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>1.47</v>
       </c>
       <c r="I7">
-        <v>-0.36</v>
+        <v>0.97</v>
       </c>
       <c r="J7">
-        <v>-6.74</v>
+        <v>-5.27</v>
       </c>
       <c r="K7">
-        <v>-10.39</v>
+        <v>-10.09</v>
       </c>
       <c r="L7">
-        <v>-8.9</v>
+        <v>-7.6</v>
       </c>
       <c r="M7">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>997.38</v>
+        <v>999.3</v>
       </c>
       <c r="Q7">
-        <v>1021.38</v>
+        <v>1018.96</v>
       </c>
       <c r="R7">
-        <v>1061.46</v>
+        <v>1059.23</v>
       </c>
       <c r="S7">
-        <v>1116.19</v>
+        <v>1115.43</v>
       </c>
       <c r="T7">
-        <v>-10.77</v>
+        <v>-10.3</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1610,34 +1616,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.14</v>
+        <v>39.27</v>
       </c>
       <c r="Z7">
-        <v>-19.89</v>
+        <v>-19.05</v>
       </c>
       <c r="AA7">
-        <v>-20.17</v>
+        <v>-19.95</v>
       </c>
       <c r="AB7">
-        <v>0.29</v>
+        <v>0.9</v>
       </c>
       <c r="AC7">
-        <v>77.73999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="AD7">
-        <v>52.63</v>
+        <v>71.59</v>
       </c>
       <c r="AE7">
-        <v>18.73</v>
+        <v>18.79</v>
       </c>
       <c r="AF7">
-        <v>76.68000000000001</v>
+        <v>-43.37</v>
       </c>
       <c r="AG7">
-        <v>1067.98</v>
+        <v>1064.54</v>
       </c>
       <c r="AH7">
-        <v>974.78</v>
+        <v>973.38</v>
       </c>
       <c r="AI7">
         <v>1045.9</v>
@@ -1646,7 +1652,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>51.79</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1657,10 +1663,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3266.7</v>
+        <v>3287</v>
       </c>
       <c r="D8">
-        <v>-3.4</v>
+        <v>0.62</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1669,46 +1675,46 @@
         <v>3266.7</v>
       </c>
       <c r="G8">
-        <v>-43.19</v>
+        <v>-42.83</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="I8">
-        <v>-4.17</v>
+        <v>-2.84</v>
       </c>
       <c r="J8">
-        <v>-10.74</v>
+        <v>-10.19</v>
       </c>
       <c r="K8">
-        <v>-19.65</v>
+        <v>-20.13</v>
       </c>
       <c r="L8">
-        <v>-41.51</v>
+        <v>-41.37</v>
       </c>
       <c r="M8">
-        <v>-10.03</v>
+        <v>-9.24</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>3368.9</v>
+        <v>3349.7</v>
       </c>
       <c r="Q8">
-        <v>3530.23</v>
+        <v>3509.18</v>
       </c>
       <c r="R8">
-        <v>3604.27</v>
+        <v>3596.2</v>
       </c>
       <c r="S8">
-        <v>4308.85</v>
+        <v>4300.1</v>
       </c>
       <c r="T8">
-        <v>-24.19</v>
+        <v>-23.56</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1723,43 +1729,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>28.47</v>
+        <v>30.75</v>
       </c>
       <c r="Z8">
-        <v>-91.84</v>
+        <v>-96.88</v>
       </c>
       <c r="AA8">
-        <v>-69.44</v>
+        <v>-74.93000000000001</v>
       </c>
       <c r="AB8">
-        <v>-22.4</v>
+        <v>-21.96</v>
       </c>
       <c r="AC8">
-        <v>15.86</v>
+        <v>13.14</v>
       </c>
       <c r="AD8">
-        <v>23.15</v>
+        <v>19.6</v>
       </c>
       <c r="AE8">
-        <v>90.48</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="AF8">
-        <v>64.37</v>
+        <v>79</v>
       </c>
       <c r="AG8">
-        <v>3792.93</v>
+        <v>3779.27</v>
       </c>
       <c r="AH8">
-        <v>3267.54</v>
+        <v>3239.1</v>
       </c>
       <c r="AI8">
-        <v>3604.29</v>
+        <v>3555.4</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>34.82</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1770,10 +1776,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>702.35</v>
+        <v>680.5</v>
       </c>
       <c r="D9">
-        <v>-2.36</v>
+        <v>-3.11</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1782,46 +1788,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-33.27</v>
+        <v>-35.35</v>
       </c>
       <c r="H9">
-        <v>30.46</v>
+        <v>26.4</v>
       </c>
       <c r="I9">
-        <v>8.869999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="J9">
-        <v>7.57</v>
+        <v>4.8</v>
       </c>
       <c r="K9">
-        <v>1.64</v>
+        <v>-1.36</v>
       </c>
       <c r="L9">
-        <v>2.43</v>
+        <v>-2.83</v>
       </c>
       <c r="M9">
-        <v>43.1</v>
+        <v>41.91</v>
       </c>
       <c r="N9">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O9">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="P9">
-        <v>694.5700000000001</v>
+        <v>700.49</v>
       </c>
       <c r="Q9">
-        <v>651.29</v>
+        <v>652.92</v>
       </c>
       <c r="R9">
-        <v>660.53</v>
+        <v>660.26</v>
       </c>
       <c r="S9">
-        <v>663.8</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="T9">
-        <v>5.81</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1836,34 +1842,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>60.63</v>
+        <v>54.49</v>
       </c>
       <c r="Z9">
-        <v>9.6</v>
+        <v>9.66</v>
       </c>
       <c r="AA9">
-        <v>-0.19</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>9.779999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="AC9">
-        <v>72.70999999999999</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="AD9">
-        <v>81.23</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AE9">
-        <v>27.34</v>
+        <v>27.13</v>
       </c>
       <c r="AF9">
-        <v>12.19</v>
+        <v>-73.23999999999999</v>
       </c>
       <c r="AG9">
-        <v>711.05</v>
+        <v>714.05</v>
       </c>
       <c r="AH9">
-        <v>591.53</v>
+        <v>591.78</v>
       </c>
       <c r="AI9">
         <v>660.59</v>
@@ -1872,7 +1878,7 @@
         <v>56</v>
       </c>
       <c r="AK9">
-        <v>37.51</v>
+        <v>38.85</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1883,10 +1889,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>374.8</v>
+        <v>367.15</v>
       </c>
       <c r="D10">
-        <v>1.57</v>
+        <v>-2.04</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1895,46 +1901,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-18.84</v>
+        <v>-20.5</v>
       </c>
       <c r="H10">
-        <v>8.56</v>
+        <v>6.34</v>
       </c>
       <c r="I10">
-        <v>2.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J10">
-        <v>-1.08</v>
+        <v>-2.16</v>
       </c>
       <c r="K10">
-        <v>-6.85</v>
+        <v>-9.56</v>
       </c>
       <c r="L10">
-        <v>-3.4</v>
+        <v>-7.3</v>
       </c>
       <c r="M10">
-        <v>23.5</v>
+        <v>22.68</v>
       </c>
       <c r="N10">
         <v>62</v>
       </c>
       <c r="O10">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P10">
-        <v>366.37</v>
+        <v>366.87</v>
       </c>
       <c r="Q10">
-        <v>364.08</v>
+        <v>363.72</v>
       </c>
       <c r="R10">
-        <v>373.16</v>
+        <v>372.88</v>
       </c>
       <c r="S10">
-        <v>387.46</v>
+        <v>387.35</v>
       </c>
       <c r="T10">
-        <v>-3.27</v>
+        <v>-5.22</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1949,34 +1955,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>56.55</v>
+        <v>48.8</v>
       </c>
       <c r="Z10">
-        <v>-1.7</v>
+        <v>-1.53</v>
       </c>
       <c r="AA10">
-        <v>-3.27</v>
+        <v>-2.93</v>
       </c>
       <c r="AB10">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AC10">
-        <v>89.59</v>
+        <v>91.66</v>
       </c>
       <c r="AD10">
-        <v>82.47</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="AE10">
-        <v>8.02</v>
+        <v>8.1</v>
       </c>
       <c r="AF10">
-        <v>-2.97</v>
+        <v>-45.92</v>
       </c>
       <c r="AG10">
-        <v>380.15</v>
+        <v>379.14</v>
       </c>
       <c r="AH10">
-        <v>348.01</v>
+        <v>348.31</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -1985,7 +1991,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>38.19</v>
+        <v>40.55</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1996,10 +2002,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>185.54</v>
+        <v>183.4</v>
       </c>
       <c r="D11">
-        <v>-0.93</v>
+        <v>-1.15</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2008,46 +2014,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-14.36</v>
+        <v>-15.35</v>
       </c>
       <c r="H11">
-        <v>17.86</v>
+        <v>16.5</v>
       </c>
       <c r="I11">
-        <v>-0.66</v>
+        <v>0.22</v>
       </c>
       <c r="J11">
-        <v>0.84</v>
+        <v>-0.05</v>
       </c>
       <c r="K11">
-        <v>-6.75</v>
+        <v>-7.83</v>
       </c>
       <c r="L11">
-        <v>11.9</v>
+        <v>8.82</v>
       </c>
       <c r="M11">
-        <v>11.43</v>
+        <v>10.48</v>
       </c>
       <c r="N11">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="O11">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P11">
-        <v>184.5</v>
+        <v>184.58</v>
       </c>
       <c r="Q11">
-        <v>185.53</v>
+        <v>185.55</v>
       </c>
       <c r="R11">
-        <v>186.31</v>
+        <v>186.15</v>
       </c>
       <c r="S11">
-        <v>190.9</v>
+        <v>191</v>
       </c>
       <c r="T11">
-        <v>-2.81</v>
+        <v>-3.98</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2062,34 +2068,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>49.35</v>
+        <v>45.53</v>
       </c>
       <c r="Z11">
-        <v>-0.46</v>
+        <v>-0.58</v>
       </c>
       <c r="AA11">
         <v>-0.57</v>
       </c>
       <c r="AB11">
-        <v>0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="AC11">
-        <v>45.26</v>
+        <v>49</v>
       </c>
       <c r="AD11">
-        <v>30.88</v>
+        <v>43.03</v>
       </c>
       <c r="AE11">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="AF11">
-        <v>-4.68</v>
+        <v>-68.03</v>
       </c>
       <c r="AG11">
-        <v>189.36</v>
+        <v>189.33</v>
       </c>
       <c r="AH11">
-        <v>181.7</v>
+        <v>181.77</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2098,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>22.44</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2109,10 +2115,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2105</v>
+        <v>2128.7</v>
       </c>
       <c r="D12">
-        <v>-3.88</v>
+        <v>1.13</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2121,46 +2127,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-34.66</v>
+        <v>-33.93</v>
       </c>
       <c r="H12">
-        <v>6.17</v>
+        <v>7.37</v>
       </c>
       <c r="I12">
-        <v>-4.5</v>
+        <v>-3.28</v>
       </c>
       <c r="J12">
-        <v>-8.039999999999999</v>
+        <v>-7.37</v>
       </c>
       <c r="K12">
-        <v>-0.9399999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="L12">
-        <v>-29.93</v>
+        <v>-29.91</v>
       </c>
       <c r="M12">
-        <v>-8.83</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="N12">
         <v>44</v>
       </c>
       <c r="O12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P12">
-        <v>2187.12</v>
+        <v>2172.7</v>
       </c>
       <c r="Q12">
-        <v>2267.82</v>
+        <v>2259.15</v>
       </c>
       <c r="R12">
-        <v>2297.83</v>
+        <v>2299.03</v>
       </c>
       <c r="S12">
-        <v>2529.5</v>
+        <v>2524.95</v>
       </c>
       <c r="T12">
-        <v>-16.78</v>
+        <v>-15.69</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2175,43 +2181,43 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>32.49</v>
+        <v>35.87</v>
       </c>
       <c r="Z12">
-        <v>-39.1</v>
+        <v>-43.65</v>
       </c>
       <c r="AA12">
-        <v>-21.28</v>
+        <v>-25.76</v>
       </c>
       <c r="AB12">
-        <v>-17.81</v>
+        <v>-17.89</v>
       </c>
       <c r="AC12">
-        <v>3.89</v>
+        <v>7.06</v>
       </c>
       <c r="AD12">
-        <v>11.03</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AE12">
-        <v>67.95999999999999</v>
+        <v>68.08</v>
       </c>
       <c r="AF12">
-        <v>155.75</v>
+        <v>-18.33</v>
       </c>
       <c r="AG12">
-        <v>2411.08</v>
+        <v>2414.19</v>
       </c>
       <c r="AH12">
-        <v>2124.55</v>
+        <v>2104.11</v>
       </c>
       <c r="AI12">
-        <v>2343.12</v>
+        <v>2314.39</v>
       </c>
       <c r="AJ12" t="s">
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>28.74</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2222,10 +2228,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4798.5</v>
+        <v>4875</v>
       </c>
       <c r="D13">
-        <v>-0.88</v>
+        <v>1.59</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2234,46 +2240,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-7.17</v>
+        <v>-5.69</v>
       </c>
       <c r="H13">
-        <v>44.22</v>
+        <v>46.52</v>
       </c>
       <c r="I13">
-        <v>-4.43</v>
+        <v>-2.68</v>
       </c>
       <c r="J13">
-        <v>-5.32</v>
+        <v>-3.81</v>
       </c>
       <c r="K13">
-        <v>8.57</v>
+        <v>11.49</v>
       </c>
       <c r="L13">
-        <v>35.78</v>
+        <v>37.06</v>
       </c>
       <c r="M13">
-        <v>18.56</v>
+        <v>18.82</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P13">
-        <v>4882.7</v>
+        <v>4855.8</v>
       </c>
       <c r="Q13">
-        <v>5019.66</v>
+        <v>5009.11</v>
       </c>
       <c r="R13">
-        <v>4920.87</v>
+        <v>4926.68</v>
       </c>
       <c r="S13">
-        <v>4365.79</v>
+        <v>4370.74</v>
       </c>
       <c r="T13">
-        <v>9.91</v>
+        <v>11.54</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2288,34 +2294,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>34.66</v>
+        <v>42.88</v>
       </c>
       <c r="Z13">
-        <v>-22.41</v>
+        <v>-26.01</v>
       </c>
       <c r="AA13">
-        <v>16.73</v>
+        <v>8.18</v>
       </c>
       <c r="AB13">
-        <v>-39.13</v>
+        <v>-34.19</v>
       </c>
       <c r="AC13">
-        <v>6.77</v>
+        <v>12.59</v>
       </c>
       <c r="AD13">
-        <v>7.58</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AE13">
-        <v>81.29000000000001</v>
+        <v>82.62</v>
       </c>
       <c r="AF13">
-        <v>116.76</v>
+        <v>27.2</v>
       </c>
       <c r="AG13">
-        <v>5222.21</v>
+        <v>5218.95</v>
       </c>
       <c r="AH13">
-        <v>4817.12</v>
+        <v>4799.27</v>
       </c>
       <c r="AI13">
         <v>5062.11</v>
@@ -2324,7 +2330,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>54.63</v>
+        <v>56.29</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2335,10 +2341,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2824</v>
+        <v>2815.5</v>
       </c>
       <c r="D14">
-        <v>1.25</v>
+        <v>-0.3</v>
       </c>
       <c r="E14">
         <v>5189.83</v>
@@ -2347,46 +2353,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-45.59</v>
+        <v>-45.75</v>
       </c>
       <c r="H14">
-        <v>28.72</v>
+        <v>28.33</v>
       </c>
       <c r="I14">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="J14">
-        <v>-4.37</v>
+        <v>-5.2</v>
       </c>
       <c r="K14">
-        <v>-11.91</v>
+        <v>-11.48</v>
       </c>
       <c r="L14">
-        <v>-44.9</v>
+        <v>-45.22</v>
       </c>
       <c r="M14">
-        <v>23.74</v>
+        <v>23.44</v>
       </c>
       <c r="N14">
         <v>19</v>
       </c>
       <c r="O14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>2783.02</v>
+        <v>2785.64</v>
       </c>
       <c r="Q14">
-        <v>2843.07</v>
+        <v>2837.64</v>
       </c>
       <c r="R14">
-        <v>2912.76</v>
+        <v>2911.02</v>
       </c>
       <c r="S14">
-        <v>2921.05</v>
+        <v>2914.02</v>
       </c>
       <c r="T14">
-        <v>-3.32</v>
+        <v>-3.38</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2401,34 +2407,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>45.03</v>
+        <v>44.02</v>
       </c>
       <c r="Z14">
-        <v>-44.37</v>
+        <v>-40.97</v>
       </c>
       <c r="AA14">
-        <v>-43.86</v>
+        <v>-43.29</v>
       </c>
       <c r="AB14">
-        <v>-0.5</v>
+        <v>2.32</v>
       </c>
       <c r="AC14">
-        <v>80.42</v>
+        <v>92.33</v>
       </c>
       <c r="AD14">
-        <v>52.32</v>
+        <v>73.28</v>
       </c>
       <c r="AE14">
-        <v>59.35</v>
+        <v>57.67</v>
       </c>
       <c r="AF14">
-        <v>54.69</v>
+        <v>-4.22</v>
       </c>
       <c r="AG14">
-        <v>2952.03</v>
+        <v>2940.26</v>
       </c>
       <c r="AH14">
-        <v>2734.11</v>
+        <v>2735.03</v>
       </c>
       <c r="AI14">
         <v>2944.37</v>
@@ -2437,7 +2443,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>44.12</v>
+        <v>40.89</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2448,10 +2454,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>215.25</v>
+        <v>216.43</v>
       </c>
       <c r="D15">
-        <v>-1.93</v>
+        <v>0.55</v>
       </c>
       <c r="E15">
         <v>392.75</v>
@@ -2460,46 +2466,46 @@
         <v>213</v>
       </c>
       <c r="G15">
-        <v>-45.19</v>
+        <v>-44.89</v>
       </c>
       <c r="H15">
-        <v>1.06</v>
+        <v>1.61</v>
       </c>
       <c r="I15">
-        <v>-2.51</v>
+        <v>-2.53</v>
       </c>
       <c r="J15">
-        <v>-6.02</v>
+        <v>-6.37</v>
       </c>
       <c r="K15">
-        <v>-7.93</v>
+        <v>-6.9</v>
       </c>
       <c r="L15">
-        <v>-33.7</v>
+        <v>-33.87</v>
       </c>
       <c r="M15">
-        <v>12.51</v>
+        <v>12.72</v>
       </c>
       <c r="N15">
         <v>32</v>
       </c>
       <c r="O15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P15">
-        <v>216.75</v>
+        <v>215.63</v>
       </c>
       <c r="Q15">
-        <v>225.86</v>
+        <v>225.16</v>
       </c>
       <c r="R15">
-        <v>231.21</v>
+        <v>230.84</v>
       </c>
       <c r="S15">
-        <v>253.15</v>
+        <v>252.68</v>
       </c>
       <c r="T15">
-        <v>-14.97</v>
+        <v>-14.35</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2514,34 +2520,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>37.39</v>
+        <v>39.09</v>
       </c>
       <c r="Z15">
-        <v>-3.94</v>
+        <v>-4.07</v>
       </c>
       <c r="AA15">
-        <v>-2.65</v>
+        <v>-2.93</v>
       </c>
       <c r="AB15">
-        <v>-1.29</v>
+        <v>-1.13</v>
       </c>
       <c r="AC15">
-        <v>22.69</v>
+        <v>30.68</v>
       </c>
       <c r="AD15">
-        <v>14.9</v>
+        <v>22.74</v>
       </c>
       <c r="AE15">
-        <v>8.460000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="AF15">
-        <v>-25.21</v>
+        <v>-27.29</v>
       </c>
       <c r="AG15">
-        <v>238.79</v>
+        <v>238.56</v>
       </c>
       <c r="AH15">
-        <v>212.93</v>
+        <v>211.76</v>
       </c>
       <c r="AI15">
         <v>239.5</v>
@@ -2550,7 +2556,7 @@
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>25.86</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2561,58 +2567,58 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>35.73</v>
+        <v>35.36</v>
       </c>
       <c r="D16">
-        <v>-2.48</v>
+        <v>-1.04</v>
       </c>
       <c r="E16">
-        <v>58.79</v>
+        <v>58.68</v>
       </c>
       <c r="F16">
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-39.22</v>
+        <v>-39.74</v>
       </c>
       <c r="H16">
-        <v>13.93</v>
+        <v>12.76</v>
       </c>
       <c r="I16">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="J16">
-        <v>-5.15</v>
+        <v>-5.58</v>
       </c>
       <c r="K16">
-        <v>-19.14</v>
+        <v>-20.82</v>
       </c>
       <c r="L16">
-        <v>-38.12</v>
+        <v>-39.85</v>
       </c>
       <c r="M16">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="N16">
         <v>13</v>
       </c>
       <c r="O16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>35.87</v>
+        <v>35.82</v>
       </c>
       <c r="Q16">
-        <v>37.09</v>
+        <v>36.97</v>
       </c>
       <c r="R16">
-        <v>38.56</v>
+        <v>38.44</v>
       </c>
       <c r="S16">
-        <v>42.39</v>
+        <v>42.31</v>
       </c>
       <c r="T16">
-        <v>-15.72</v>
+        <v>-16.43</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2627,34 +2633,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>39.26</v>
+        <v>37.43</v>
       </c>
       <c r="Z16">
-        <v>-0.83</v>
+        <v>-0.86</v>
       </c>
       <c r="AA16">
-        <v>-0.77</v>
+        <v>-0.79</v>
       </c>
       <c r="AB16">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC16">
-        <v>42.15</v>
+        <v>46.04</v>
       </c>
       <c r="AD16">
-        <v>36.69</v>
+        <v>43.4</v>
       </c>
       <c r="AE16">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>-61.87</v>
+        <v>-77.5</v>
       </c>
       <c r="AG16">
-        <v>39.31</v>
+        <v>39.3</v>
       </c>
       <c r="AH16">
-        <v>34.88</v>
+        <v>34.65</v>
       </c>
       <c r="AI16">
         <v>38.7</v>
@@ -2663,7 +2669,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>20.68</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2674,10 +2680,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1110.9</v>
+        <v>1142.1</v>
       </c>
       <c r="D17">
-        <v>-2.12</v>
+        <v>2.81</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2686,46 +2692,46 @@
         <v>1110.9</v>
       </c>
       <c r="G17">
-        <v>-28.62</v>
+        <v>-26.62</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="I17">
-        <v>-4.11</v>
+        <v>-1.97</v>
       </c>
       <c r="J17">
-        <v>-9.17</v>
+        <v>-6.35</v>
       </c>
       <c r="K17">
-        <v>-17.31</v>
+        <v>-15.65</v>
       </c>
       <c r="L17">
-        <v>-21.29</v>
+        <v>-19.01</v>
       </c>
       <c r="M17">
-        <v>-1.42</v>
+        <v>-0.93</v>
       </c>
       <c r="N17">
         <v>38</v>
       </c>
       <c r="O17">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P17">
-        <v>1135.78</v>
+        <v>1131.2</v>
       </c>
       <c r="Q17">
-        <v>1177.36</v>
+        <v>1172.72</v>
       </c>
       <c r="R17">
-        <v>1256.54</v>
+        <v>1253.65</v>
       </c>
       <c r="S17">
-        <v>1340.56</v>
+        <v>1339.53</v>
       </c>
       <c r="T17">
-        <v>-17.13</v>
+        <v>-14.74</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2740,34 +2746,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>29.05</v>
+        <v>38.96</v>
       </c>
       <c r="Z17">
-        <v>-36.58</v>
+        <v>-34.71</v>
       </c>
       <c r="AA17">
-        <v>-34.4</v>
+        <v>-34.46</v>
       </c>
       <c r="AB17">
-        <v>-2.18</v>
+        <v>-0.25</v>
       </c>
       <c r="AC17">
-        <v>35.42</v>
+        <v>55.72</v>
       </c>
       <c r="AD17">
-        <v>45.52</v>
+        <v>46.17</v>
       </c>
       <c r="AE17">
-        <v>28.5</v>
+        <v>29.89</v>
       </c>
       <c r="AF17">
-        <v>-19.65</v>
+        <v>23.94</v>
       </c>
       <c r="AG17">
-        <v>1256.88</v>
+        <v>1248.84</v>
       </c>
       <c r="AH17">
-        <v>1097.84</v>
+        <v>1096.59</v>
       </c>
       <c r="AI17">
         <v>1213.61</v>
@@ -2776,7 +2782,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>39</v>
+        <v>36.03</v>
       </c>
     </row>
   </sheetData>
@@ -2957,7 +2963,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2976,1783 +2982,1789 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>73</v>
       </c>
+      <c r="D5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="E6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1.06</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.3</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1.73</v>
-      </c>
-      <c r="D9" s="7">
-        <v>11.18</v>
-      </c>
-      <c r="E9" s="8">
-        <v>9.449999999999999</v>
+      <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-4.28</v>
+        <v>1.3</v>
       </c>
       <c r="D10" s="7">
-        <v>-3.74</v>
+        <v>1.24</v>
       </c>
       <c r="E10" s="8">
-        <v>0.54</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>19.34</v>
+        <v>11.18</v>
       </c>
       <c r="D11" s="7">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-10.39</v>
+        <v>8.15</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>6.02</v>
+        <v>-3.74</v>
       </c>
       <c r="D12" s="7">
-        <v>7.23</v>
+        <v>-5.03</v>
       </c>
       <c r="E12" s="8">
-        <v>1.21</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-4.51</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="D13" s="7">
-        <v>-6.74</v>
+        <v>9.49</v>
       </c>
       <c r="E13" s="9">
-        <v>-2.23</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-7.65</v>
+        <v>7.23</v>
       </c>
       <c r="D14" s="7">
-        <v>-10.74</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-3.09</v>
+        <v>3.29</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-3.94</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>11.14</v>
+        <v>-6.74</v>
       </c>
       <c r="D15" s="7">
-        <v>7.57</v>
+        <v>-5.27</v>
       </c>
       <c r="E15" s="9">
-        <v>-3.57</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-3.15</v>
+        <v>-10.74</v>
       </c>
       <c r="D16" s="7">
-        <v>-1.08</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.07</v>
+        <v>-10.19</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.55</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>0.96</v>
+        <v>7.57</v>
       </c>
       <c r="D17" s="7">
-        <v>0.84</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.12</v>
+        <v>4.8</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-3.95</v>
+        <v>-1.08</v>
       </c>
       <c r="D18" s="7">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-4.09</v>
+        <v>-2.16</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>-4.11</v>
+        <v>0.84</v>
       </c>
       <c r="D19" s="7">
-        <v>-5.32</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.21</v>
+        <v>-0.05</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>-5.2</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="D20" s="7">
-        <v>-4.37</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.83</v>
+        <v>-7.37</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.67</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-5.03</v>
+        <v>-5.32</v>
       </c>
       <c r="D21" s="7">
-        <v>-6.02</v>
+        <v>-3.81</v>
       </c>
       <c r="E21" s="9">
-        <v>-0.99</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>-3.2</v>
+        <v>-4.37</v>
       </c>
       <c r="D22" s="7">
-        <v>-5.15</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.95</v>
+        <v>-5.2</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>-9.41</v>
+        <v>-6.02</v>
       </c>
       <c r="D23" s="7">
-        <v>-9.17</v>
+        <v>-6.37</v>
       </c>
       <c r="E23" s="8">
-        <v>0.24</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>0.54</v>
+        <v>-5.15</v>
       </c>
       <c r="D24" s="7">
-        <v>2.38</v>
+        <v>-5.58</v>
       </c>
       <c r="E24" s="8">
-        <v>1.84</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>0.73</v>
+        <v>-9.17</v>
       </c>
       <c r="D25" s="7">
-        <v>7.92</v>
-      </c>
-      <c r="E25" s="8">
-        <v>7.19</v>
+        <v>-6.35</v>
+      </c>
+      <c r="E25" s="9">
+        <v>2.82</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>0.06</v>
+        <v>2.38</v>
       </c>
       <c r="D26" s="7">
-        <v>0.36</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.3</v>
+        <v>3.69</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.31</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>29.23</v>
+        <v>7.92</v>
       </c>
       <c r="D27" s="7">
-        <v>13.55</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-15.68</v>
+        <v>4.13</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-3.79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="7">
-        <v>1.06</v>
+        <v>0.36</v>
       </c>
       <c r="D28" s="7">
-        <v>0.89</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.17</v>
+        <v>0.08</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="7">
-        <v>1.27</v>
+        <v>13.55</v>
       </c>
       <c r="D29" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-1.63</v>
+        <v>13.43</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>-0.04</v>
+        <v>0.89</v>
       </c>
       <c r="D30" s="7">
-        <v>-4.17</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-4.13</v>
+        <v>-1.64</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>16.24</v>
+        <v>-0.36</v>
       </c>
       <c r="D31" s="7">
-        <v>8.869999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="E31" s="9">
-        <v>-7.37</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>-0.27</v>
+        <v>-4.17</v>
       </c>
       <c r="D32" s="7">
-        <v>2.13</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.4</v>
+        <v>-2.84</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1.33</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>-0.77</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="D33" s="7">
-        <v>-0.66</v>
+        <v>4.55</v>
       </c>
       <c r="E33" s="8">
-        <v>0.11</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>-0.82</v>
+        <v>2.13</v>
       </c>
       <c r="D34" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-3.68</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>-3.28</v>
+        <v>-0.66</v>
       </c>
       <c r="D35" s="7">
-        <v>-4.43</v>
+        <v>0.22</v>
       </c>
       <c r="E35" s="9">
-        <v>-1.15</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-1.1</v>
+        <v>-4.5</v>
       </c>
       <c r="D36" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.29</v>
+        <v>-3.28</v>
+      </c>
+      <c r="E36" s="9">
+        <v>1.22</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-4.06</v>
+        <v>-4.43</v>
       </c>
       <c r="D37" s="7">
-        <v>-2.51</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.55</v>
+        <v>-2.68</v>
+      </c>
+      <c r="E37" s="9">
+        <v>1.75</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>1.41</v>
+        <v>0.19</v>
       </c>
       <c r="D38" s="7">
-        <v>-0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E38" s="9">
-        <v>-1.91</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-0.77</v>
+        <v>-2.51</v>
       </c>
       <c r="D39" s="7">
-        <v>-4.11</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-3.34</v>
+        <v>-2.53</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>-6.56</v>
+        <v>-0.5</v>
       </c>
       <c r="D40" s="7">
-        <v>-7.35</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.79</v>
+        <v>-0.67</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>13.44</v>
+        <v>-4.11</v>
       </c>
       <c r="D41" s="7">
-        <v>19.83</v>
-      </c>
-      <c r="E41" s="8">
-        <v>6.39</v>
+        <v>-1.97</v>
+      </c>
+      <c r="E41" s="9">
+        <v>2.14</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="7">
-        <v>-37.83</v>
+        <v>-7.35</v>
       </c>
       <c r="D42" s="7">
-        <v>-38.66</v>
+        <v>-4.32</v>
       </c>
       <c r="E42" s="9">
-        <v>-0.83</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="7">
-        <v>-17.68</v>
+        <v>19.83</v>
       </c>
       <c r="D43" s="7">
-        <v>-27.83</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-10.15</v>
+        <v>17.2</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.63</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="7">
-        <v>11</v>
+        <v>-38.66</v>
       </c>
       <c r="D44" s="7">
-        <v>6.57</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-4.43</v>
+        <v>-39.65</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="7">
-        <v>-7.39</v>
+        <v>-27.83</v>
       </c>
       <c r="D45" s="7">
-        <v>-8.9</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.51</v>
+        <v>-28.21</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="7">
-        <v>-39.83</v>
+        <v>6.57</v>
       </c>
       <c r="D46" s="7">
-        <v>-41.51</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-1.68</v>
+        <v>1.1</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-5.47</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="7">
-        <v>5.13</v>
+        <v>-8.9</v>
       </c>
       <c r="D47" s="7">
-        <v>2.43</v>
+        <v>-7.6</v>
       </c>
       <c r="E47" s="9">
-        <v>-2.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="7">
-        <v>-4.47</v>
+        <v>-41.51</v>
       </c>
       <c r="D48" s="7">
-        <v>-3.4</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.07</v>
+        <v>-41.37</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.14</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="7">
-        <v>12.59</v>
+        <v>2.43</v>
       </c>
       <c r="D49" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.6899999999999999</v>
+        <v>-2.83</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-5.26</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>-27.6</v>
+        <v>-3.4</v>
       </c>
       <c r="D50" s="7">
-        <v>-29.93</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-2.33</v>
+        <v>-7.3</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-3.9</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>35.53</v>
+        <v>11.9</v>
       </c>
       <c r="D51" s="7">
-        <v>35.78</v>
+        <v>8.82</v>
       </c>
       <c r="E51" s="8">
-        <v>0.25</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>-45.55</v>
+        <v>-29.93</v>
       </c>
       <c r="D52" s="7">
-        <v>-44.9</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.65</v>
+        <v>-29.91</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>-32.04</v>
+        <v>35.78</v>
       </c>
       <c r="D53" s="7">
-        <v>-33.7</v>
+        <v>37.06</v>
       </c>
       <c r="E53" s="9">
-        <v>-1.66</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>-35.81</v>
+        <v>-44.9</v>
       </c>
       <c r="D54" s="7">
-        <v>-38.12</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-2.31</v>
+        <v>-45.22</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-18.88</v>
+        <v>-33.7</v>
       </c>
       <c r="D55" s="7">
-        <v>-21.29</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-2.41</v>
+        <v>-33.87</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>2.28</v>
+        <v>-38.12</v>
       </c>
       <c r="D56" s="7">
-        <v>1.1</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-1.18</v>
+        <v>-39.85</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>10.71</v>
+        <v>-21.29</v>
       </c>
       <c r="D57" s="7">
-        <v>7.6</v>
+        <v>-19.01</v>
       </c>
       <c r="E57" s="9">
-        <v>-3.11</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="7">
-        <v>-10.64</v>
+        <v>1.1</v>
       </c>
       <c r="D58" s="7">
-        <v>-11.31</v>
+        <v>1.64</v>
       </c>
       <c r="E58" s="9">
-        <v>-0.67</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="7">
-        <v>6.37</v>
+        <v>7.6</v>
       </c>
       <c r="D59" s="7">
-        <v>-4.92</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-11.29</v>
+        <v>6.62</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="7">
-        <v>-7.74</v>
+        <v>-11.31</v>
       </c>
       <c r="D60" s="7">
-        <v>-10.49</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-2.75</v>
+        <v>-13.48</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="7">
-        <v>-8.789999999999999</v>
+        <v>-4.92</v>
       </c>
       <c r="D61" s="7">
-        <v>-10.39</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-1.6</v>
+        <v>-5.28</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="7">
-        <v>-17.84</v>
+        <v>-10.49</v>
       </c>
       <c r="D62" s="7">
-        <v>-19.65</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-1.81</v>
+        <v>-15.96</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-5.47</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="7">
-        <v>3.62</v>
+        <v>-10.39</v>
       </c>
       <c r="D63" s="7">
-        <v>1.64</v>
+        <v>-10.09</v>
       </c>
       <c r="E63" s="9">
-        <v>-1.98</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="7">
-        <v>-8.41</v>
+        <v>-19.65</v>
       </c>
       <c r="D64" s="7">
-        <v>-6.85</v>
+        <v>-20.13</v>
       </c>
       <c r="E64" s="8">
-        <v>1.56</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="7">
-        <v>-6.6</v>
+        <v>1.64</v>
       </c>
       <c r="D65" s="7">
-        <v>-6.75</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-0.15</v>
+        <v>-1.36</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-3</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="7">
-        <v>-0.6</v>
+        <v>-6.85</v>
       </c>
       <c r="D66" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-0.34</v>
+        <v>-9.56</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="7">
-        <v>10.33</v>
+        <v>-6.75</v>
       </c>
       <c r="D67" s="7">
-        <v>8.57</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-1.76</v>
+        <v>-7.83</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="7">
-        <v>-12.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D68" s="7">
-        <v>-11.91</v>
-      </c>
-      <c r="E68" s="8">
-        <v>0.38</v>
+        <v>0.04</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.98</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>-7.21</v>
+        <v>8.57</v>
       </c>
       <c r="D69" s="7">
-        <v>-7.93</v>
+        <v>11.49</v>
       </c>
       <c r="E69" s="9">
-        <v>-0.72</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>-18.38</v>
+        <v>-11.91</v>
       </c>
       <c r="D70" s="7">
-        <v>-19.14</v>
+        <v>-11.48</v>
       </c>
       <c r="E70" s="9">
-        <v>-0.76</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>-16.4</v>
+        <v>-7.93</v>
       </c>
       <c r="D71" s="7">
-        <v>-17.31</v>
+        <v>-6.9</v>
       </c>
       <c r="E71" s="9">
-        <v>-0.91</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>-8.119999999999999</v>
+        <v>-19.14</v>
       </c>
       <c r="D72" s="7">
-        <v>-6.3</v>
+        <v>-20.82</v>
       </c>
       <c r="E72" s="8">
-        <v>1.82</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>-10.75</v>
+        <v>-17.31</v>
       </c>
       <c r="D73" s="7">
-        <v>-6.44</v>
-      </c>
-      <c r="E73" s="8">
-        <v>4.31</v>
+        <v>-15.65</v>
+      </c>
+      <c r="E73" s="9">
+        <v>1.66</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="7">
-        <v>-39.14</v>
+        <v>-6.3</v>
       </c>
       <c r="D74" s="7">
-        <v>-39.25</v>
+        <v>-4.74</v>
       </c>
       <c r="E74" s="9">
-        <v>-0.11</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="7">
-        <v>-21.28</v>
+        <v>-6.44</v>
       </c>
       <c r="D75" s="7">
-        <v>-29.97</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-8.69</v>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="7">
-        <v>-13.1</v>
+        <v>-39.25</v>
       </c>
       <c r="D76" s="7">
-        <v>-13.66</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-0.5600000000000001</v>
+        <v>-39.74</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="7">
-        <v>-19.57</v>
+        <v>-29.97</v>
       </c>
       <c r="D77" s="7">
-        <v>-20.97</v>
+        <v>-29.82</v>
       </c>
       <c r="E77" s="9">
-        <v>-1.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="7">
-        <v>-41.18</v>
+        <v>-13.66</v>
       </c>
       <c r="D78" s="7">
-        <v>-43.19</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-2.01</v>
+        <v>-15.96</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="7">
-        <v>-31.66</v>
+        <v>-20.97</v>
       </c>
       <c r="D79" s="7">
-        <v>-33.27</v>
+        <v>-20.61</v>
       </c>
       <c r="E79" s="9">
-        <v>-1.61</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="7">
-        <v>-20.1</v>
+        <v>-43.19</v>
       </c>
       <c r="D80" s="7">
-        <v>-18.84</v>
-      </c>
-      <c r="E80" s="8">
-        <v>1.26</v>
+        <v>-42.83</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0.36</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="7">
-        <v>-13.56</v>
+        <v>-33.27</v>
       </c>
       <c r="D81" s="7">
-        <v>-14.36</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-0.8</v>
+        <v>-35.35</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="7">
-        <v>-32.03</v>
+        <v>-18.84</v>
       </c>
       <c r="D82" s="7">
-        <v>-34.66</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-2.63</v>
+        <v>-20.5</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="7">
-        <v>-6.35</v>
+        <v>-14.36</v>
       </c>
       <c r="D83" s="7">
-        <v>-7.17</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-0.82</v>
+        <v>-15.35</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="7">
-        <v>-46.26</v>
+        <v>-34.66</v>
       </c>
       <c r="D84" s="7">
-        <v>-45.59</v>
-      </c>
-      <c r="E84" s="8">
-        <v>0.67</v>
+        <v>-33.93</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0.73</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="7">
-        <v>-44.11</v>
+        <v>-7.17</v>
       </c>
       <c r="D85" s="7">
-        <v>-45.19</v>
+        <v>-5.69</v>
       </c>
       <c r="E85" s="9">
-        <v>-1.08</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="7">
-        <v>-37.68</v>
+        <v>-45.59</v>
       </c>
       <c r="D86" s="7">
-        <v>-39.22</v>
-      </c>
-      <c r="E86" s="9">
-        <v>-1.54</v>
+        <v>-45.75</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="7">
-        <v>-27.08</v>
+        <v>-45.19</v>
       </c>
       <c r="D87" s="7">
-        <v>-28.62</v>
+        <v>-44.89</v>
       </c>
       <c r="E87" s="9">
-        <v>-1.54</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7">
-        <v>726.65</v>
+        <v>-39.22</v>
       </c>
       <c r="D88" s="7">
-        <v>732.75</v>
+        <v>-39.74</v>
       </c>
       <c r="E88" s="8">
-        <v>6.1</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B89" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="7">
+        <v>-28.62</v>
+      </c>
+      <c r="D89" s="7">
+        <v>-26.62</v>
+      </c>
+      <c r="E89" s="9">
         <v>2</v>
-      </c>
-      <c r="C89" s="7">
-        <v>965.25</v>
-      </c>
-      <c r="D89" s="7">
-        <v>1011.85</v>
-      </c>
-      <c r="E89" s="8">
-        <v>46.6</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="7">
-        <v>204.14</v>
+        <v>732.75</v>
       </c>
       <c r="D90" s="7">
-        <v>203.8</v>
+        <v>745</v>
       </c>
       <c r="E90" s="9">
-        <v>-0.34</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="7">
-        <v>779.3</v>
+        <v>1011.85</v>
       </c>
       <c r="D91" s="7">
-        <v>693.25</v>
-      </c>
-      <c r="E91" s="9">
-        <v>-86.05</v>
+        <v>986.35</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-25.5</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="7">
-        <v>1791.6</v>
+        <v>203.8</v>
       </c>
       <c r="D92" s="7">
-        <v>1780.1</v>
-      </c>
-      <c r="E92" s="9">
-        <v>-11.5</v>
+        <v>202.15</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="7">
-        <v>1013.7</v>
+        <v>693.25</v>
       </c>
       <c r="D93" s="7">
-        <v>996</v>
+        <v>694.7</v>
       </c>
       <c r="E93" s="9">
-        <v>-17.7</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="7">
-        <v>3381.8</v>
+        <v>1780.1</v>
       </c>
       <c r="D94" s="7">
-        <v>3266.7</v>
-      </c>
-      <c r="E94" s="9">
-        <v>-115.1</v>
+        <v>1732.7</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-47.4</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="7">
-        <v>719.3</v>
+        <v>996</v>
       </c>
       <c r="D95" s="7">
-        <v>702.35</v>
+        <v>1000.6</v>
       </c>
       <c r="E95" s="9">
-        <v>-16.95</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="7">
-        <v>369</v>
+        <v>3266.7</v>
       </c>
       <c r="D96" s="7">
-        <v>374.8</v>
-      </c>
-      <c r="E96" s="8">
-        <v>5.8</v>
+        <v>3287</v>
+      </c>
+      <c r="E96" s="9">
+        <v>20.3</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="7">
-        <v>187.29</v>
+        <v>702.35</v>
       </c>
       <c r="D97" s="7">
-        <v>185.54</v>
-      </c>
-      <c r="E97" s="9">
-        <v>-1.75</v>
+        <v>680.5</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-21.85</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="7">
-        <v>2190</v>
+        <v>374.8</v>
       </c>
       <c r="D98" s="7">
-        <v>2105</v>
-      </c>
-      <c r="E98" s="9">
-        <v>-85</v>
+        <v>367.15</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-7.65</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="7">
-        <v>4841</v>
+        <v>185.54</v>
       </c>
       <c r="D99" s="7">
-        <v>4798.5</v>
-      </c>
-      <c r="E99" s="9">
-        <v>-42.5</v>
+        <v>183.4</v>
+      </c>
+      <c r="E99" s="8">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="7">
-        <v>2789</v>
+        <v>2105</v>
       </c>
       <c r="D100" s="7">
-        <v>2824</v>
-      </c>
-      <c r="E100" s="8">
-        <v>35</v>
+        <v>2128.7</v>
+      </c>
+      <c r="E100" s="9">
+        <v>23.7</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="7">
-        <v>219.49</v>
+        <v>4798.5</v>
       </c>
       <c r="D101" s="7">
-        <v>215.25</v>
+        <v>4875</v>
       </c>
       <c r="E101" s="9">
-        <v>-4.24</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="7">
-        <v>36.64</v>
+        <v>2824</v>
       </c>
       <c r="D102" s="7">
-        <v>35.73</v>
-      </c>
-      <c r="E102" s="9">
-        <v>-0.91</v>
+        <v>2815.5</v>
+      </c>
+      <c r="E102" s="8">
+        <v>-8.5</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="7">
-        <v>1135</v>
+        <v>215.25</v>
       </c>
       <c r="D103" s="7">
-        <v>1110.9</v>
+        <v>216.43</v>
       </c>
       <c r="E103" s="9">
-        <v>-24.1</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C104" s="7">
-        <v>62</v>
+        <v>35.73</v>
       </c>
       <c r="D104" s="7">
-        <v>68</v>
+        <v>35.36</v>
       </c>
       <c r="E104" s="8">
-        <v>6</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C105" s="7">
-        <v>68</v>
+        <v>1110.9</v>
       </c>
       <c r="D105" s="7">
-        <v>50</v>
+        <v>1142.1</v>
       </c>
       <c r="E105" s="9">
-        <v>-18</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="7">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D106" s="7">
-        <v>56</v>
-      </c>
-      <c r="E106" s="8">
+        <v>74</v>
+      </c>
+      <c r="E106" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="7">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D107" s="7">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E107" s="8">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="7">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="D108" s="7">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="E108" s="8">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="7">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="D109" s="7">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="E109" s="9">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -4763,13 +4775,13 @@
         <v>24</v>
       </c>
       <c r="C110" s="7">
-        <v>52.26</v>
+        <v>55.31</v>
       </c>
       <c r="D110" s="7">
-        <v>55.31</v>
-      </c>
-      <c r="E110" s="8">
-        <v>3.05</v>
+        <v>60.74</v>
+      </c>
+      <c r="E110" s="9">
+        <v>5.43</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -4780,13 +4792,13 @@
         <v>24</v>
       </c>
       <c r="C111" s="7">
-        <v>53.85</v>
+        <v>60.58</v>
       </c>
       <c r="D111" s="7">
-        <v>60.58</v>
+        <v>55.79</v>
       </c>
       <c r="E111" s="8">
-        <v>6.73</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -4797,13 +4809,13 @@
         <v>24</v>
       </c>
       <c r="C112" s="7">
-        <v>37.83</v>
+        <v>37.18</v>
       </c>
       <c r="D112" s="7">
-        <v>37.18</v>
-      </c>
-      <c r="E112" s="9">
-        <v>-0.65</v>
+        <v>34.14</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-3.04</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -4814,13 +4826,13 @@
         <v>24</v>
       </c>
       <c r="C113" s="7">
-        <v>77.08</v>
+        <v>55.24</v>
       </c>
       <c r="D113" s="7">
-        <v>55.24</v>
+        <v>55.47</v>
       </c>
       <c r="E113" s="9">
-        <v>-21.84</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4831,13 +4843,13 @@
         <v>24</v>
       </c>
       <c r="C114" s="7">
-        <v>58.07</v>
+        <v>55.76</v>
       </c>
       <c r="D114" s="7">
-        <v>55.76</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-2.31</v>
+        <v>47.39</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4848,13 +4860,13 @@
         <v>24</v>
       </c>
       <c r="C115" s="7">
-        <v>42.45</v>
+        <v>37.14</v>
       </c>
       <c r="D115" s="7">
-        <v>37.14</v>
+        <v>39.27</v>
       </c>
       <c r="E115" s="9">
-        <v>-5.31</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -4865,13 +4877,13 @@
         <v>24</v>
       </c>
       <c r="C116" s="7">
-        <v>34.44</v>
+        <v>28.47</v>
       </c>
       <c r="D116" s="7">
-        <v>28.47</v>
+        <v>30.75</v>
       </c>
       <c r="E116" s="9">
-        <v>-5.97</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4882,13 +4894,13 @@
         <v>24</v>
       </c>
       <c r="C117" s="7">
-        <v>65.97</v>
+        <v>60.63</v>
       </c>
       <c r="D117" s="7">
-        <v>60.63</v>
-      </c>
-      <c r="E117" s="9">
-        <v>-5.34</v>
+        <v>54.49</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-6.14</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4899,13 +4911,13 @@
         <v>24</v>
       </c>
       <c r="C118" s="7">
-        <v>51.08</v>
+        <v>56.55</v>
       </c>
       <c r="D118" s="7">
-        <v>56.55</v>
+        <v>48.8</v>
       </c>
       <c r="E118" s="8">
-        <v>5.47</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4916,13 +4928,13 @@
         <v>24</v>
       </c>
       <c r="C119" s="7">
-        <v>52.71</v>
+        <v>49.35</v>
       </c>
       <c r="D119" s="7">
-        <v>49.35</v>
-      </c>
-      <c r="E119" s="9">
-        <v>-3.36</v>
+        <v>45.53</v>
+      </c>
+      <c r="E119" s="8">
+        <v>-3.82</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4933,13 +4945,13 @@
         <v>24</v>
       </c>
       <c r="C120" s="7">
-        <v>39.41</v>
+        <v>32.49</v>
       </c>
       <c r="D120" s="7">
-        <v>32.49</v>
+        <v>35.87</v>
       </c>
       <c r="E120" s="9">
-        <v>-6.92</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4950,13 +4962,13 @@
         <v>24</v>
       </c>
       <c r="C121" s="7">
-        <v>37.44</v>
+        <v>34.66</v>
       </c>
       <c r="D121" s="7">
-        <v>34.66</v>
+        <v>42.88</v>
       </c>
       <c r="E121" s="9">
-        <v>-2.78</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4967,13 +4979,13 @@
         <v>24</v>
       </c>
       <c r="C122" s="7">
-        <v>39.76</v>
+        <v>45.03</v>
       </c>
       <c r="D122" s="7">
-        <v>45.03</v>
+        <v>44.02</v>
       </c>
       <c r="E122" s="8">
-        <v>5.27</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4984,13 +4996,13 @@
         <v>24</v>
       </c>
       <c r="C123" s="7">
-        <v>41.24</v>
+        <v>37.39</v>
       </c>
       <c r="D123" s="7">
-        <v>37.39</v>
+        <v>39.09</v>
       </c>
       <c r="E123" s="9">
-        <v>-3.85</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5001,13 +5013,13 @@
         <v>24</v>
       </c>
       <c r="C124" s="7">
-        <v>44.17</v>
+        <v>39.26</v>
       </c>
       <c r="D124" s="7">
-        <v>39.26</v>
-      </c>
-      <c r="E124" s="9">
-        <v>-4.91</v>
+        <v>37.43</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -5018,13 +5030,13 @@
         <v>24</v>
       </c>
       <c r="C125" s="7">
-        <v>32.88</v>
+        <v>29.05</v>
       </c>
       <c r="D125" s="7">
-        <v>29.05</v>
+        <v>38.96</v>
       </c>
       <c r="E125" s="9">
-        <v>-3.83</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -5035,13 +5047,13 @@
         <v>31</v>
       </c>
       <c r="C126" s="7">
-        <v>10.29</v>
+        <v>107.97</v>
       </c>
       <c r="D126" s="7">
-        <v>107.97</v>
+        <v>77.73</v>
       </c>
       <c r="E126" s="8">
-        <v>97.68000000000001</v>
+        <v>-30.24</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -5052,13 +5064,13 @@
         <v>31</v>
       </c>
       <c r="C127" s="7">
-        <v>-55.34</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="D127" s="7">
-        <v>94.31999999999999</v>
+        <v>-39.9</v>
       </c>
       <c r="E127" s="8">
-        <v>149.66</v>
+        <v>-134.22</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -5069,13 +5081,13 @@
         <v>31</v>
       </c>
       <c r="C128" s="7">
-        <v>-12.55</v>
+        <v>-24.33</v>
       </c>
       <c r="D128" s="7">
-        <v>-24.33</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-11.78</v>
+        <v>-37.74</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-13.41</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5086,13 +5098,13 @@
         <v>31</v>
       </c>
       <c r="C129" s="7">
-        <v>701.4</v>
+        <v>474.73</v>
       </c>
       <c r="D129" s="7">
-        <v>474.73</v>
-      </c>
-      <c r="E129" s="9">
-        <v>-226.67</v>
+        <v>4.99</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-469.74</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5103,13 +5115,13 @@
         <v>31</v>
       </c>
       <c r="C130" s="7">
-        <v>16.86</v>
+        <v>170.92</v>
       </c>
       <c r="D130" s="7">
-        <v>170.92</v>
+        <v>-60.93</v>
       </c>
       <c r="E130" s="8">
-        <v>154.06</v>
+        <v>-231.85</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5120,13 +5132,13 @@
         <v>31</v>
       </c>
       <c r="C131" s="7">
-        <v>74.61</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="D131" s="7">
-        <v>76.68000000000001</v>
+        <v>-43.37</v>
       </c>
       <c r="E131" s="8">
-        <v>2.07</v>
+        <v>-120.05</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5137,13 +5149,13 @@
         <v>31</v>
       </c>
       <c r="C132" s="7">
-        <v>-32.88</v>
+        <v>64.37</v>
       </c>
       <c r="D132" s="7">
-        <v>64.37</v>
-      </c>
-      <c r="E132" s="8">
-        <v>97.25</v>
+        <v>79</v>
+      </c>
+      <c r="E132" s="9">
+        <v>14.63</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -5154,13 +5166,13 @@
         <v>31</v>
       </c>
       <c r="C133" s="7">
-        <v>92.64</v>
+        <v>12.19</v>
       </c>
       <c r="D133" s="7">
-        <v>12.19</v>
-      </c>
-      <c r="E133" s="9">
-        <v>-80.45</v>
+        <v>-73.23999999999999</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-85.43000000000001</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -5171,13 +5183,13 @@
         <v>31</v>
       </c>
       <c r="C134" s="7">
-        <v>-45.63</v>
+        <v>-2.97</v>
       </c>
       <c r="D134" s="7">
-        <v>-2.97</v>
+        <v>-45.92</v>
       </c>
       <c r="E134" s="8">
-        <v>42.66</v>
+        <v>-42.95</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -5188,13 +5200,13 @@
         <v>31</v>
       </c>
       <c r="C135" s="7">
-        <v>-1.65</v>
+        <v>-4.68</v>
       </c>
       <c r="D135" s="7">
-        <v>-4.68</v>
-      </c>
-      <c r="E135" s="9">
-        <v>-3.03</v>
+        <v>-68.03</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-63.35</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -5205,13 +5217,13 @@
         <v>31</v>
       </c>
       <c r="C136" s="7">
-        <v>25.9</v>
+        <v>155.75</v>
       </c>
       <c r="D136" s="7">
-        <v>155.75</v>
+        <v>-18.33</v>
       </c>
       <c r="E136" s="8">
-        <v>129.85</v>
+        <v>-174.08</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -5222,13 +5234,13 @@
         <v>31</v>
       </c>
       <c r="C137" s="7">
-        <v>0.8100000000000001</v>
+        <v>116.76</v>
       </c>
       <c r="D137" s="7">
-        <v>116.76</v>
+        <v>27.2</v>
       </c>
       <c r="E137" s="8">
-        <v>115.95</v>
+        <v>-89.56</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -5239,13 +5251,13 @@
         <v>31</v>
       </c>
       <c r="C138" s="7">
-        <v>-24.72</v>
+        <v>54.69</v>
       </c>
       <c r="D138" s="7">
-        <v>54.69</v>
+        <v>-4.22</v>
       </c>
       <c r="E138" s="8">
-        <v>79.41</v>
+        <v>-58.91</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -5256,13 +5268,13 @@
         <v>31</v>
       </c>
       <c r="C139" s="7">
-        <v>73.15000000000001</v>
+        <v>-25.21</v>
       </c>
       <c r="D139" s="7">
-        <v>-25.21</v>
-      </c>
-      <c r="E139" s="9">
-        <v>-98.36</v>
+        <v>-27.29</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -5273,13 +5285,13 @@
         <v>31</v>
       </c>
       <c r="C140" s="7">
-        <v>-17.07</v>
+        <v>-61.87</v>
       </c>
       <c r="D140" s="7">
-        <v>-61.87</v>
-      </c>
-      <c r="E140" s="9">
-        <v>-44.8</v>
+        <v>-77.5</v>
+      </c>
+      <c r="E140" s="8">
+        <v>-15.63</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -5290,19 +5302,19 @@
         <v>31</v>
       </c>
       <c r="C141" s="7">
-        <v>-50.87</v>
+        <v>-19.65</v>
       </c>
       <c r="D141" s="7">
-        <v>-19.65</v>
-      </c>
-      <c r="E141" s="8">
-        <v>31.22</v>
+        <v>23.94</v>
+      </c>
+      <c r="E141" s="9">
+        <v>43.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5326,28 +5338,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5361,16 +5373,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="12">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="E2" s="12">
         <v>30</v>
       </c>
       <c r="F2" s="12">
-        <v>-1.5</v>
+        <v>-1.9</v>
       </c>
       <c r="G2" s="12">
-        <v>-6.8</v>
+        <v>-7.4</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -5493,10 +5505,10 @@
         <v>48</v>
       </c>
       <c r="F1" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>38</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>46</v>
@@ -5510,34 +5522,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.431</v>
+        <v>0.4191</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3657</v>
+        <v>0.3641</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2374</v>
+        <v>0.2344</v>
       </c>
       <c r="D2" s="15">
-        <v>0.235</v>
+        <v>0.2268</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1856</v>
+        <v>0.1882</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1385</v>
+        <v>0.1272</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1251</v>
+        <v>0.1216</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1143</v>
+        <v>0.1048</v>
       </c>
       <c r="I2" s="15">
-        <v>0.0624</v>
+        <v>0.0526</v>
       </c>
       <c r="J2" s="15">
-        <v>0.0391</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5545,10 +5557,10 @@
         <v>51</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>39</v>
@@ -5562,22 +5574,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0013</v>
+        <v>0.0009</v>
       </c>
       <c r="B4" s="15">
-        <v>-0.0141</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="C4" s="15">
         <v>-0.0142</v>
       </c>
       <c r="D4" s="15">
-        <v>-0.0552</v>
+        <v>-0.0568</v>
       </c>
       <c r="E4" s="15">
-        <v>-0.0883</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="F4" s="15">
-        <v>-0.1003</v>
+        <v>-0.0924</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="85">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,19 +214,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.6 → 50.7</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>48.6</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>48.7 → 58.3</t>
+  </si>
+  <si>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>58.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -438,8 +447,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -950,58 +959,58 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>736.25</v>
+        <v>743.7</v>
       </c>
       <c r="D2">
-        <v>-1.17</v>
+        <v>1.01</v>
       </c>
       <c r="E2">
-        <v>782.05</v>
+        <v>775.55</v>
       </c>
       <c r="F2">
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-5.86</v>
+        <v>-4.11</v>
       </c>
       <c r="H2">
-        <v>28.95</v>
+        <v>30.26</v>
       </c>
       <c r="I2">
-        <v>2.97</v>
+        <v>4.25</v>
       </c>
       <c r="J2">
-        <v>0.86</v>
+        <v>2.03</v>
       </c>
       <c r="K2">
-        <v>1.68</v>
+        <v>2.51</v>
       </c>
       <c r="L2">
-        <v>-5.64</v>
+        <v>-4.9</v>
       </c>
       <c r="M2">
-        <v>34.69</v>
+        <v>33.33</v>
       </c>
       <c r="N2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>730.8099999999999</v>
+        <v>736.87</v>
       </c>
       <c r="Q2">
-        <v>723.6900000000001</v>
+        <v>724.37</v>
       </c>
       <c r="R2">
-        <v>728.45</v>
+        <v>728.66</v>
       </c>
       <c r="S2">
-        <v>688.24</v>
+        <v>688.3099999999999</v>
       </c>
       <c r="T2">
-        <v>6.98</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1016,34 +1025,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.55</v>
+        <v>58.78</v>
       </c>
       <c r="Z2">
-        <v>1.67</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
-        <v>-0.68</v>
+        <v>0.03</v>
       </c>
       <c r="AB2">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="AC2">
-        <v>86.97</v>
+        <v>85.2</v>
       </c>
       <c r="AD2">
-        <v>83.18000000000001</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="AE2">
-        <v>15.73</v>
+        <v>15.17</v>
       </c>
       <c r="AF2">
-        <v>-27.69</v>
+        <v>-26.52</v>
       </c>
       <c r="AG2">
-        <v>742.89</v>
+        <v>745.41</v>
       </c>
       <c r="AH2">
-        <v>704.49</v>
+        <v>703.34</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1052,7 +1061,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>28.9</v>
+        <v>30.89</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1063,10 +1072,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>1011.75</v>
+        <v>1020.75</v>
       </c>
       <c r="D3">
-        <v>2.58</v>
+        <v>0.89</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1075,46 +1084,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-6.45</v>
+        <v>-5.62</v>
       </c>
       <c r="H3">
-        <v>100.2</v>
+        <v>101.98</v>
       </c>
       <c r="I3">
-        <v>9.460000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="J3">
-        <v>11.59</v>
+        <v>11.52</v>
       </c>
       <c r="K3">
-        <v>14.87</v>
+        <v>18.03</v>
       </c>
       <c r="L3">
-        <v>19.5</v>
+        <v>12.17</v>
       </c>
       <c r="M3">
-        <v>13.19</v>
+        <v>12.85</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P3">
-        <v>982.65</v>
+        <v>999.1900000000001</v>
       </c>
       <c r="Q3">
-        <v>951.03</v>
+        <v>955.79</v>
       </c>
       <c r="R3">
-        <v>950.99</v>
+        <v>953.52</v>
       </c>
       <c r="S3">
-        <v>759.9299999999999</v>
+        <v>760.9</v>
       </c>
       <c r="T3">
-        <v>33.14</v>
+        <v>34.15</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1129,34 +1138,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>59.24</v>
+        <v>60.42</v>
       </c>
       <c r="Z3">
-        <v>11.17</v>
+        <v>14.56</v>
       </c>
       <c r="AA3">
-        <v>3.94</v>
+        <v>6.06</v>
       </c>
       <c r="AB3">
-        <v>7.23</v>
+        <v>8.5</v>
       </c>
       <c r="AC3">
-        <v>87.40000000000001</v>
+        <v>87.09</v>
       </c>
       <c r="AD3">
-        <v>83.84999999999999</v>
+        <v>86.95</v>
       </c>
       <c r="AE3">
-        <v>45.17</v>
+        <v>45.31</v>
       </c>
       <c r="AF3">
-        <v>33.71</v>
+        <v>55.75</v>
       </c>
       <c r="AG3">
-        <v>1007.01</v>
+        <v>1018.45</v>
       </c>
       <c r="AH3">
-        <v>895.05</v>
+        <v>893.13</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1165,7 +1174,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>23.71</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1176,58 +1185,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>201.95</v>
+        <v>202.62</v>
       </c>
       <c r="D4">
-        <v>-0.1</v>
+        <v>0.33</v>
       </c>
       <c r="E4">
-        <v>335.45</v>
+        <v>331.45</v>
       </c>
       <c r="F4">
         <v>200.82</v>
       </c>
       <c r="G4">
-        <v>-39.8</v>
+        <v>-38.87</v>
       </c>
       <c r="H4">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>0.5600000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="J4">
-        <v>-4.82</v>
+        <v>-4.12</v>
       </c>
       <c r="K4">
-        <v>-11.64</v>
+        <v>-12.03</v>
       </c>
       <c r="L4">
-        <v>-39.5</v>
+        <v>-39.6</v>
       </c>
       <c r="M4">
-        <v>-5.95</v>
+        <v>-5.64</v>
       </c>
       <c r="N4">
         <v>32</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>202.94</v>
+        <v>202.93</v>
       </c>
       <c r="Q4">
-        <v>206.26</v>
+        <v>205.75</v>
       </c>
       <c r="R4">
-        <v>214.08</v>
+        <v>213.52</v>
       </c>
       <c r="S4">
-        <v>242.04</v>
+        <v>241.79</v>
       </c>
       <c r="T4">
-        <v>-16.56</v>
+        <v>-16.2</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1242,31 +1251,31 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.78</v>
+        <v>36.21</v>
       </c>
       <c r="Z4">
-        <v>-3.35</v>
+        <v>-3.22</v>
       </c>
       <c r="AA4">
-        <v>-3.47</v>
+        <v>-3.42</v>
       </c>
       <c r="AB4">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="AC4">
-        <v>59.1</v>
+        <v>56.79</v>
       </c>
       <c r="AD4">
-        <v>64.7</v>
+        <v>61.54</v>
       </c>
       <c r="AE4">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AF4">
-        <v>-15.64</v>
+        <v>-57.16</v>
       </c>
       <c r="AG4">
-        <v>214.01</v>
+        <v>212.98</v>
       </c>
       <c r="AH4">
         <v>198.51</v>
@@ -1278,7 +1287,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>20.57</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1289,10 +1298,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>674</v>
+        <v>669.9</v>
       </c>
       <c r="D5">
-        <v>-2.98</v>
+        <v>-0.61</v>
       </c>
       <c r="E5">
         <v>978.55</v>
@@ -1301,46 +1310,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-31.12</v>
+        <v>-31.54</v>
       </c>
       <c r="H5">
-        <v>17.34</v>
+        <v>16.62</v>
       </c>
       <c r="I5">
-        <v>-8.289999999999999</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="J5">
-        <v>7.54</v>
+        <v>6.85</v>
       </c>
       <c r="K5">
-        <v>-7.75</v>
+        <v>-8.02</v>
       </c>
       <c r="L5">
-        <v>-31.91</v>
+        <v>-31.24</v>
       </c>
       <c r="M5">
-        <v>-2.58</v>
+        <v>-3.21</v>
       </c>
       <c r="N5">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O5">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P5">
-        <v>714.61</v>
+        <v>702.23</v>
       </c>
       <c r="Q5">
-        <v>654.8</v>
+        <v>656.98</v>
       </c>
       <c r="R5">
-        <v>665.48</v>
+        <v>664.84</v>
       </c>
       <c r="S5">
-        <v>702.8</v>
+        <v>702.3</v>
       </c>
       <c r="T5">
-        <v>-4.1</v>
+        <v>-4.61</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1355,43 +1364,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>51.42</v>
+        <v>50.64</v>
       </c>
       <c r="Z5">
-        <v>11.78</v>
+        <v>10.23</v>
       </c>
       <c r="AA5">
-        <v>3.31</v>
+        <v>4.69</v>
       </c>
       <c r="AB5">
-        <v>8.48</v>
+        <v>5.54</v>
       </c>
       <c r="AC5">
-        <v>52.36</v>
+        <v>49.19</v>
       </c>
       <c r="AD5">
-        <v>68.83</v>
+        <v>57.2</v>
       </c>
       <c r="AE5">
-        <v>36.43</v>
+        <v>34.6</v>
       </c>
       <c r="AF5">
-        <v>-50.96</v>
+        <v>-64.14</v>
       </c>
       <c r="AG5">
-        <v>752.08</v>
+        <v>753.52</v>
       </c>
       <c r="AH5">
-        <v>557.51</v>
+        <v>560.4299999999999</v>
       </c>
       <c r="AI5">
-        <v>794.3099999999999</v>
+        <v>776.29</v>
       </c>
       <c r="AJ5" t="s">
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>39.16</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1402,10 +1411,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1692.4</v>
+        <v>1700.6</v>
       </c>
       <c r="D6">
-        <v>-2.33</v>
+        <v>0.48</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1414,46 +1423,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-17.91</v>
+        <v>-17.51</v>
       </c>
       <c r="H6">
-        <v>25.56</v>
+        <v>26.17</v>
       </c>
       <c r="I6">
-        <v>-3.19</v>
+        <v>-5.49</v>
       </c>
       <c r="J6">
-        <v>2.24</v>
+        <v>0.72</v>
       </c>
       <c r="K6">
-        <v>-16.35</v>
+        <v>-16.16</v>
       </c>
       <c r="L6">
-        <v>-0.04</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="N6">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O6">
         <v>48</v>
       </c>
       <c r="P6">
-        <v>1759.22</v>
+        <v>1739.48</v>
       </c>
       <c r="Q6">
-        <v>1734.38</v>
+        <v>1734.42</v>
       </c>
       <c r="R6">
-        <v>1748.33</v>
+        <v>1745.37</v>
       </c>
       <c r="S6">
-        <v>1710.84</v>
+        <v>1710.11</v>
       </c>
       <c r="T6">
-        <v>-1.08</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1468,34 +1477,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>41.66</v>
+        <v>43.16</v>
       </c>
       <c r="Z6">
-        <v>2.15</v>
+        <v>-1.62</v>
       </c>
       <c r="AA6">
-        <v>1.87</v>
+        <v>1.18</v>
       </c>
       <c r="AB6">
-        <v>0.28</v>
+        <v>-2.79</v>
       </c>
       <c r="AC6">
-        <v>30.99</v>
+        <v>8.99</v>
       </c>
       <c r="AD6">
-        <v>60.09</v>
+        <v>33.69</v>
       </c>
       <c r="AE6">
-        <v>52.11</v>
+        <v>50.35</v>
       </c>
       <c r="AF6">
-        <v>-51.08</v>
+        <v>-43.3</v>
       </c>
       <c r="AG6">
-        <v>1813.38</v>
+        <v>1813.35</v>
       </c>
       <c r="AH6">
-        <v>1655.38</v>
+        <v>1655.48</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1504,7 +1513,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>26.76</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1515,10 +1524,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>984.1</v>
+        <v>994.3</v>
       </c>
       <c r="D7">
-        <v>-1.65</v>
+        <v>1.04</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1527,46 +1536,46 @@
         <v>984.1</v>
       </c>
       <c r="G7">
-        <v>-21.92</v>
+        <v>-21.11</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>-0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="J7">
-        <v>-6.19</v>
+        <v>-6.42</v>
       </c>
       <c r="K7">
-        <v>-10.84</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L7">
-        <v>-12.66</v>
+        <v>-11.21</v>
       </c>
       <c r="M7">
-        <v>3.73</v>
+        <v>4.03</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P7">
-        <v>998.9</v>
+        <v>997.74</v>
       </c>
       <c r="Q7">
-        <v>1015.04</v>
+        <v>1011.73</v>
       </c>
       <c r="R7">
-        <v>1056.94</v>
+        <v>1054.88</v>
       </c>
       <c r="S7">
-        <v>1114.7</v>
+        <v>1113.98</v>
       </c>
       <c r="T7">
-        <v>-11.72</v>
+        <v>-10.74</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1581,34 +1590,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>34.72</v>
+        <v>39.39</v>
       </c>
       <c r="Z7">
-        <v>-19.5</v>
+        <v>-18.81</v>
       </c>
       <c r="AA7">
-        <v>-19.86</v>
+        <v>-19.65</v>
       </c>
       <c r="AB7">
-        <v>0.36</v>
+        <v>0.84</v>
       </c>
       <c r="AC7">
-        <v>62.33</v>
+        <v>67.56</v>
       </c>
       <c r="AD7">
-        <v>73.45</v>
+        <v>70.05</v>
       </c>
       <c r="AE7">
-        <v>19.01</v>
+        <v>18.58</v>
       </c>
       <c r="AF7">
-        <v>-41.5</v>
+        <v>-25.8</v>
       </c>
       <c r="AG7">
-        <v>1058.28</v>
+        <v>1050.19</v>
       </c>
       <c r="AH7">
-        <v>971.8</v>
+        <v>973.27</v>
       </c>
       <c r="AI7">
         <v>1045.9</v>
@@ -1617,7 +1626,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>46.59</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1628,58 +1637,58 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3220</v>
+        <v>3212</v>
       </c>
       <c r="D8">
-        <v>-2.04</v>
+        <v>-0.25</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
       </c>
       <c r="F8">
-        <v>3220</v>
+        <v>3212</v>
       </c>
       <c r="G8">
-        <v>-44</v>
+        <v>-44.14</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-6.4</v>
+        <v>-4.77</v>
       </c>
       <c r="J8">
-        <v>-13.16</v>
+        <v>-12.56</v>
       </c>
       <c r="K8">
-        <v>-21</v>
+        <v>-20.21</v>
       </c>
       <c r="L8">
-        <v>-42.32</v>
+        <v>-42.97</v>
       </c>
       <c r="M8">
-        <v>-9.49</v>
+        <v>-10</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>3305.7</v>
+        <v>3273.5</v>
       </c>
       <c r="Q8">
-        <v>3486.51</v>
+        <v>3463.82</v>
       </c>
       <c r="R8">
-        <v>3584.13</v>
+        <v>3574.42</v>
       </c>
       <c r="S8">
-        <v>4290.78</v>
+        <v>4281.22</v>
       </c>
       <c r="T8">
-        <v>-24.96</v>
+        <v>-24.97</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1694,43 +1703,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>27.62</v>
+        <v>27.26</v>
       </c>
       <c r="Z8">
-        <v>-105.07</v>
+        <v>-110.93</v>
       </c>
       <c r="AA8">
-        <v>-80.95999999999999</v>
+        <v>-86.95</v>
       </c>
       <c r="AB8">
-        <v>-24.12</v>
+        <v>-23.98</v>
       </c>
       <c r="AC8">
         <v>4.36</v>
       </c>
       <c r="AD8">
-        <v>11.12</v>
+        <v>7.29</v>
       </c>
       <c r="AE8">
-        <v>88.20999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="AF8">
-        <v>173.16</v>
+        <v>-23.71</v>
       </c>
       <c r="AG8">
-        <v>3774.09</v>
+        <v>3763.19</v>
       </c>
       <c r="AH8">
-        <v>3198.93</v>
+        <v>3164.44</v>
       </c>
       <c r="AI8">
-        <v>3512.12</v>
+        <v>3486.43</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>38.16</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1741,10 +1750,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>682.25</v>
+        <v>674.3</v>
       </c>
       <c r="D9">
-        <v>0.26</v>
+        <v>-1.17</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1753,46 +1762,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-35.18</v>
+        <v>-35.94</v>
       </c>
       <c r="H9">
-        <v>26.73</v>
+        <v>25.25</v>
       </c>
       <c r="I9">
-        <v>-5.03</v>
+        <v>-1.12</v>
       </c>
       <c r="J9">
-        <v>5.29</v>
+        <v>4.39</v>
       </c>
       <c r="K9">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="L9">
-        <v>-2.61</v>
+        <v>-9.66</v>
       </c>
       <c r="M9">
-        <v>41.74</v>
+        <v>41.18</v>
       </c>
       <c r="N9">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O9">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P9">
-        <v>693.27</v>
+        <v>691.74</v>
       </c>
       <c r="Q9">
-        <v>654.73</v>
+        <v>656.23</v>
       </c>
       <c r="R9">
-        <v>660.1799999999999</v>
+        <v>660.29</v>
       </c>
       <c r="S9">
-        <v>663.37</v>
+        <v>663.1799999999999</v>
       </c>
       <c r="T9">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1807,34 +1816,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>54.89</v>
+        <v>52.66</v>
       </c>
       <c r="Z9">
-        <v>9.73</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AA9">
-        <v>3.37</v>
+        <v>4.51</v>
       </c>
       <c r="AB9">
-        <v>6.36</v>
+        <v>4.54</v>
       </c>
       <c r="AC9">
-        <v>60.62</v>
+        <v>54.23</v>
       </c>
       <c r="AD9">
-        <v>67.61</v>
+        <v>61.45</v>
       </c>
       <c r="AE9">
-        <v>26.62</v>
+        <v>25.71</v>
       </c>
       <c r="AF9">
-        <v>-67.31999999999999</v>
+        <v>-83.44</v>
       </c>
       <c r="AG9">
-        <v>717.14</v>
+        <v>719.03</v>
       </c>
       <c r="AH9">
-        <v>592.3200000000001</v>
+        <v>593.4299999999999</v>
       </c>
       <c r="AI9">
         <v>660.59</v>
@@ -1843,7 +1852,7 @@
         <v>56</v>
       </c>
       <c r="AK9">
-        <v>39.86</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1854,10 +1863,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D10">
-        <v>-0.04</v>
+        <v>0.54</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1866,46 +1875,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-20.53</v>
+        <v>-20.1</v>
       </c>
       <c r="H10">
-        <v>6.3</v>
+        <v>6.88</v>
       </c>
       <c r="I10">
-        <v>1.1</v>
+        <v>2.39</v>
       </c>
       <c r="J10">
-        <v>-1.95</v>
+        <v>-1.2</v>
       </c>
       <c r="K10">
-        <v>-7.86</v>
+        <v>-6.13</v>
       </c>
       <c r="L10">
-        <v>-7.01</v>
+        <v>-6.13</v>
       </c>
       <c r="M10">
-        <v>22.31</v>
+        <v>21.44</v>
       </c>
       <c r="N10">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O10">
         <v>49</v>
       </c>
       <c r="P10">
-        <v>367.67</v>
+        <v>369.39</v>
       </c>
       <c r="Q10">
-        <v>363.4</v>
+        <v>363.32</v>
       </c>
       <c r="R10">
-        <v>372.66</v>
+        <v>372.49</v>
       </c>
       <c r="S10">
-        <v>387.27</v>
+        <v>387.19</v>
       </c>
       <c r="T10">
-        <v>-5.23</v>
+        <v>-4.7</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1920,34 +1929,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>48.65</v>
+        <v>50.7</v>
       </c>
       <c r="Z10">
-        <v>-1.39</v>
+        <v>-1.11</v>
       </c>
       <c r="AA10">
-        <v>-2.62</v>
+        <v>-2.32</v>
       </c>
       <c r="AB10">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AC10">
-        <v>74.94</v>
+        <v>62.55</v>
       </c>
       <c r="AD10">
-        <v>85.40000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="AE10">
-        <v>7.81</v>
+        <v>7.46</v>
       </c>
       <c r="AF10">
-        <v>-51.99</v>
+        <v>-72.62</v>
       </c>
       <c r="AG10">
-        <v>378.21</v>
+        <v>377.98</v>
       </c>
       <c r="AH10">
-        <v>348.59</v>
+        <v>348.65</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -1956,7 +1965,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>42.7</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1967,10 +1976,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>184.97</v>
+        <v>190.82</v>
       </c>
       <c r="D11">
-        <v>0.86</v>
+        <v>3.16</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1979,46 +1988,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-14.63</v>
+        <v>-11.93</v>
       </c>
       <c r="H11">
-        <v>17.5</v>
+        <v>21.22</v>
       </c>
       <c r="I11">
-        <v>0.72</v>
+        <v>4.27</v>
       </c>
       <c r="J11">
-        <v>1.08</v>
+        <v>2.43</v>
       </c>
       <c r="K11">
-        <v>-4.44</v>
+        <v>0.35</v>
       </c>
       <c r="L11">
-        <v>10.17</v>
+        <v>13.21</v>
       </c>
       <c r="M11">
-        <v>10.44</v>
+        <v>10.91</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P11">
-        <v>184.84</v>
+        <v>186.4</v>
       </c>
       <c r="Q11">
-        <v>185.48</v>
+        <v>185.68</v>
       </c>
       <c r="R11">
-        <v>186.11</v>
+        <v>186.16</v>
       </c>
       <c r="S11">
-        <v>191.11</v>
+        <v>191.24</v>
       </c>
       <c r="T11">
-        <v>-3.21</v>
+        <v>-0.22</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2033,34 +2042,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>48.67</v>
+        <v>58.32</v>
       </c>
       <c r="Z11">
-        <v>-0.54</v>
+        <v>-0.04</v>
       </c>
       <c r="AA11">
-        <v>-0.57</v>
+        <v>-0.46</v>
       </c>
       <c r="AB11">
-        <v>0.02</v>
+        <v>0.42</v>
       </c>
       <c r="AC11">
-        <v>38.85</v>
+        <v>55.46</v>
       </c>
       <c r="AD11">
-        <v>44.37</v>
+        <v>47.77</v>
       </c>
       <c r="AE11">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="AF11">
-        <v>-42.56</v>
+        <v>32.26</v>
       </c>
       <c r="AG11">
-        <v>189.25</v>
+        <v>190.1</v>
       </c>
       <c r="AH11">
-        <v>181.71</v>
+        <v>181.25</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2069,7 +2078,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>18.55</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2080,10 +2089,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2105</v>
+        <v>2089.6</v>
       </c>
       <c r="D12">
-        <v>-1.11</v>
+        <v>-0.73</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2092,46 +2101,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-34.66</v>
+        <v>-35.14</v>
       </c>
       <c r="H12">
-        <v>6.17</v>
+        <v>5.4</v>
       </c>
       <c r="I12">
-        <v>-6.49</v>
+        <v>-4.53</v>
       </c>
       <c r="J12">
-        <v>-8.56</v>
+        <v>-8.52</v>
       </c>
       <c r="K12">
-        <v>2.2</v>
+        <v>-0.92</v>
       </c>
       <c r="L12">
-        <v>-31.28</v>
+        <v>-31.86</v>
       </c>
       <c r="M12">
-        <v>-9</v>
+        <v>-9.17</v>
       </c>
       <c r="N12">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P12">
-        <v>2143.5</v>
+        <v>2123.66</v>
       </c>
       <c r="Q12">
-        <v>2250.2</v>
+        <v>2239.87</v>
       </c>
       <c r="R12">
-        <v>2297.5</v>
+        <v>2295.28</v>
       </c>
       <c r="S12">
-        <v>2520.07</v>
+        <v>2514.87</v>
       </c>
       <c r="T12">
-        <v>-16.47</v>
+        <v>-16.91</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2146,43 +2155,43 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>34.04</v>
+        <v>32.86</v>
       </c>
       <c r="Z12">
-        <v>-48.61</v>
+        <v>-53.17</v>
       </c>
       <c r="AA12">
-        <v>-30.33</v>
+        <v>-34.9</v>
       </c>
       <c r="AB12">
-        <v>-18.28</v>
+        <v>-18.27</v>
       </c>
       <c r="AC12">
-        <v>7.51</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AD12">
-        <v>6.15</v>
+        <v>7.59</v>
       </c>
       <c r="AE12">
-        <v>65.86</v>
+        <v>63.11</v>
       </c>
       <c r="AF12">
-        <v>26.97</v>
+        <v>-24.34</v>
       </c>
       <c r="AG12">
-        <v>2419.23</v>
+        <v>2421.82</v>
       </c>
       <c r="AH12">
-        <v>2081.16</v>
+        <v>2057.91</v>
       </c>
       <c r="AI12">
-        <v>2314.28</v>
+        <v>2280.24</v>
       </c>
       <c r="AJ12" t="s">
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>33.3</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2193,10 +2202,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4928.5</v>
+        <v>4880</v>
       </c>
       <c r="D13">
-        <v>1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2205,46 +2214,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-4.66</v>
+        <v>-5.59</v>
       </c>
       <c r="H13">
-        <v>48.12</v>
+        <v>46.67</v>
       </c>
       <c r="I13">
-        <v>1.49</v>
+        <v>-0.58</v>
       </c>
       <c r="J13">
-        <v>-3.1</v>
+        <v>-3.92</v>
       </c>
       <c r="K13">
-        <v>14.48</v>
+        <v>12.86</v>
       </c>
       <c r="L13">
-        <v>39.89</v>
+        <v>38.98</v>
       </c>
       <c r="M13">
-        <v>19.13</v>
+        <v>18.62</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P13">
-        <v>4870.3</v>
+        <v>4864.6</v>
       </c>
       <c r="Q13">
-        <v>5001.58</v>
+        <v>4989.34</v>
       </c>
       <c r="R13">
-        <v>4933.22</v>
+        <v>4939.35</v>
       </c>
       <c r="S13">
-        <v>4376.29</v>
+        <v>4381.69</v>
       </c>
       <c r="T13">
-        <v>12.62</v>
+        <v>11.37</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2259,34 +2268,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>47.82</v>
+        <v>44.1</v>
       </c>
       <c r="Z13">
-        <v>-24.27</v>
+        <v>-26.5</v>
       </c>
       <c r="AA13">
-        <v>1.69</v>
+        <v>-3.95</v>
       </c>
       <c r="AB13">
-        <v>-25.96</v>
+        <v>-22.55</v>
       </c>
       <c r="AC13">
-        <v>29.97</v>
+        <v>47.02</v>
       </c>
       <c r="AD13">
-        <v>16.44</v>
+        <v>29.86</v>
       </c>
       <c r="AE13">
-        <v>85.26000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="AF13">
-        <v>135.7</v>
+        <v>35.65</v>
       </c>
       <c r="AG13">
-        <v>5211.66</v>
+        <v>5197.71</v>
       </c>
       <c r="AH13">
-        <v>4791.51</v>
+        <v>4780.98</v>
       </c>
       <c r="AI13">
         <v>5062.11</v>
@@ -2295,7 +2304,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>49.72</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2306,58 +2315,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2782.9</v>
+        <v>2774</v>
       </c>
       <c r="D14">
-        <v>-1.16</v>
+        <v>-0.32</v>
       </c>
       <c r="E14">
-        <v>5136.41</v>
+        <v>5072.5</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-45.82</v>
+        <v>-45.31</v>
       </c>
       <c r="H14">
-        <v>26.84</v>
+        <v>26.44</v>
       </c>
       <c r="I14">
-        <v>1.94</v>
+        <v>0.16</v>
       </c>
       <c r="J14">
-        <v>-4.83</v>
+        <v>-4.51</v>
       </c>
       <c r="K14">
-        <v>-11.45</v>
+        <v>-14.57</v>
       </c>
       <c r="L14">
-        <v>-46.38</v>
+        <v>-45.99</v>
       </c>
       <c r="M14">
-        <v>23.24</v>
+        <v>22.59</v>
       </c>
       <c r="N14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>2796.22</v>
+        <v>2797.08</v>
       </c>
       <c r="Q14">
-        <v>2831.54</v>
+        <v>2823.74</v>
       </c>
       <c r="R14">
-        <v>2908.67</v>
+        <v>2906.77</v>
       </c>
       <c r="S14">
-        <v>2907.03</v>
+        <v>2899.85</v>
       </c>
       <c r="T14">
-        <v>-4.27</v>
+        <v>-4.34</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2372,34 +2381,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>40.3</v>
+        <v>39.32</v>
       </c>
       <c r="Z14">
-        <v>-40.44</v>
+        <v>-40.27</v>
       </c>
       <c r="AA14">
-        <v>-42.72</v>
+        <v>-42.23</v>
       </c>
       <c r="AB14">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AC14">
-        <v>87.51000000000001</v>
+        <v>75.09</v>
       </c>
       <c r="AD14">
-        <v>86.75</v>
+        <v>84.98</v>
       </c>
       <c r="AE14">
-        <v>60.25</v>
+        <v>58.08</v>
       </c>
       <c r="AF14">
-        <v>20.9</v>
+        <v>30.51</v>
       </c>
       <c r="AG14">
-        <v>2931.78</v>
+        <v>2915.65</v>
       </c>
       <c r="AH14">
-        <v>2731.3</v>
+        <v>2731.83</v>
       </c>
       <c r="AI14">
         <v>2944.37</v>
@@ -2408,7 +2417,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>41.24</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2419,10 +2428,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>216.06</v>
+        <v>216.31</v>
       </c>
       <c r="D15">
-        <v>-0.17</v>
+        <v>0.12</v>
       </c>
       <c r="E15">
         <v>380.65</v>
@@ -2431,46 +2440,46 @@
         <v>213</v>
       </c>
       <c r="G15">
-        <v>-43.24</v>
+        <v>-43.17</v>
       </c>
       <c r="H15">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="I15">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="J15">
-        <v>-6.23</v>
+        <v>-5.95</v>
       </c>
       <c r="K15">
-        <v>-13.77</v>
+        <v>-12.77</v>
       </c>
       <c r="L15">
-        <v>-44.99</v>
+        <v>-42.54</v>
       </c>
       <c r="M15">
-        <v>12.55</v>
+        <v>12.11</v>
       </c>
       <c r="N15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O15">
         <v>12</v>
       </c>
       <c r="P15">
-        <v>216.24</v>
+        <v>216.71</v>
       </c>
       <c r="Q15">
-        <v>224.46</v>
+        <v>223.69</v>
       </c>
       <c r="R15">
-        <v>230.35</v>
+        <v>229.63</v>
       </c>
       <c r="S15">
-        <v>252.24</v>
+        <v>251.81</v>
       </c>
       <c r="T15">
-        <v>-14.34</v>
+        <v>-14.1</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2485,34 +2494,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>38.74</v>
+        <v>39.14</v>
       </c>
       <c r="Z15">
-        <v>-4.15</v>
+        <v>-4.16</v>
       </c>
       <c r="AA15">
-        <v>-3.18</v>
+        <v>-3.37</v>
       </c>
       <c r="AB15">
-        <v>-0.98</v>
+        <v>-0.78</v>
       </c>
       <c r="AC15">
-        <v>27.46</v>
+        <v>29.72</v>
       </c>
       <c r="AD15">
-        <v>26.95</v>
+        <v>29.29</v>
       </c>
       <c r="AE15">
-        <v>7.93</v>
+        <v>7.89</v>
       </c>
       <c r="AF15">
-        <v>-59.62</v>
+        <v>-10.95</v>
       </c>
       <c r="AG15">
-        <v>238.25</v>
+        <v>237.5</v>
       </c>
       <c r="AH15">
-        <v>210.68</v>
+        <v>209.89</v>
       </c>
       <c r="AI15">
         <v>239.5</v>
@@ -2521,7 +2530,7 @@
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>27.53</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2532,10 +2541,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>35.62</v>
+        <v>35.63</v>
       </c>
       <c r="D16">
-        <v>0.74</v>
+        <v>0.03</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2544,25 +2553,25 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-39.3</v>
+        <v>-39.28</v>
       </c>
       <c r="H16">
-        <v>13.58</v>
+        <v>13.62</v>
       </c>
       <c r="I16">
-        <v>-1.47</v>
+        <v>1.16</v>
       </c>
       <c r="J16">
-        <v>-5.72</v>
+        <v>-4.66</v>
       </c>
       <c r="K16">
-        <v>-18.1</v>
+        <v>-17.12</v>
       </c>
       <c r="L16">
-        <v>-38.93</v>
+        <v>-38.36</v>
       </c>
       <c r="M16">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="N16">
         <v>26</v>
@@ -2571,19 +2580,19 @@
         <v>11</v>
       </c>
       <c r="P16">
-        <v>35.71</v>
+        <v>35.8</v>
       </c>
       <c r="Q16">
-        <v>36.89</v>
+        <v>36.79</v>
       </c>
       <c r="R16">
-        <v>38.33</v>
+        <v>38.23</v>
       </c>
       <c r="S16">
-        <v>42.24</v>
+        <v>42.16</v>
       </c>
       <c r="T16">
-        <v>-15.66</v>
+        <v>-15.49</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2598,34 +2607,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>39.56</v>
+        <v>39.64</v>
       </c>
       <c r="Z16">
-        <v>-0.85</v>
+        <v>-0.83</v>
       </c>
       <c r="AA16">
         <v>-0.8</v>
       </c>
       <c r="AB16">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AC16">
-        <v>44.96</v>
+        <v>52.07</v>
       </c>
       <c r="AD16">
-        <v>44.38</v>
+        <v>47.69</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>-70.22</v>
+        <v>-72.76000000000001</v>
       </c>
       <c r="AG16">
-        <v>39.28</v>
+        <v>39.22</v>
       </c>
       <c r="AH16">
-        <v>34.49</v>
+        <v>34.36</v>
       </c>
       <c r="AI16">
         <v>38.7</v>
@@ -2634,7 +2643,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>18.07</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2645,10 +2654,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1100.8</v>
+        <v>1130</v>
       </c>
       <c r="D17">
-        <v>-3.62</v>
+        <v>2.65</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2657,46 +2666,46 @@
         <v>1100.8</v>
       </c>
       <c r="G17">
-        <v>-29.27</v>
+        <v>-27.4</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="I17">
-        <v>-3.18</v>
+        <v>-0.09</v>
       </c>
       <c r="J17">
-        <v>-10.87</v>
+        <v>-9.02</v>
       </c>
       <c r="K17">
-        <v>-17.07</v>
+        <v>-13.75</v>
       </c>
       <c r="L17">
-        <v>-21.79</v>
+        <v>-20.52</v>
       </c>
       <c r="M17">
-        <v>-1.88</v>
+        <v>-1.52</v>
       </c>
       <c r="N17">
         <v>38</v>
       </c>
       <c r="O17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P17">
-        <v>1123.96</v>
+        <v>1123.76</v>
       </c>
       <c r="Q17">
-        <v>1165.66</v>
+        <v>1160.01</v>
       </c>
       <c r="R17">
-        <v>1248.68</v>
+        <v>1244.1</v>
       </c>
       <c r="S17">
-        <v>1338.38</v>
+        <v>1337.4</v>
       </c>
       <c r="T17">
-        <v>-17.75</v>
+        <v>-15.51</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2711,43 +2720,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>32.49</v>
+        <v>40.07</v>
       </c>
       <c r="Z17">
-        <v>-36.15</v>
+        <v>-34.53</v>
       </c>
       <c r="AA17">
-        <v>-34.8</v>
+        <v>-34.74</v>
       </c>
       <c r="AB17">
-        <v>-1.35</v>
+        <v>0.21</v>
       </c>
       <c r="AC17">
-        <v>51.76</v>
+        <v>80.67</v>
       </c>
       <c r="AD17">
-        <v>47.63</v>
+        <v>62.72</v>
       </c>
       <c r="AE17">
-        <v>30.83</v>
+        <v>31.53</v>
       </c>
       <c r="AF17">
-        <v>54.14</v>
+        <v>7.92</v>
       </c>
       <c r="AG17">
-        <v>1240.91</v>
+        <v>1227.37</v>
       </c>
       <c r="AH17">
-        <v>1090.4</v>
+        <v>1092.64</v>
       </c>
       <c r="AI17">
-        <v>1213.61</v>
+        <v>1205.69</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>36.38</v>
+        <v>37.51</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2928,7 +2937,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2940,2343 +2949,2374 @@
         <v>66</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2.03</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>1.24</v>
+        <v>11.59</v>
       </c>
       <c r="D9" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.38</v>
+        <v>11.52</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>8.15</v>
+        <v>-4.82</v>
       </c>
       <c r="D10" s="6">
-        <v>11.59</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.44</v>
+        <v>-4.12</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.03</v>
+        <v>7.54</v>
       </c>
       <c r="D11" s="6">
-        <v>-4.82</v>
+        <v>6.85</v>
       </c>
       <c r="E11" s="8">
-        <v>0.21</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>9.49</v>
+        <v>2.24</v>
       </c>
       <c r="D12" s="6">
-        <v>7.54</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.95</v>
+        <v>0.72</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>3.29</v>
+        <v>-6.19</v>
       </c>
       <c r="D13" s="6">
-        <v>2.24</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.05</v>
+        <v>-6.42</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.27</v>
+        <v>-13.16</v>
       </c>
       <c r="D14" s="6">
-        <v>-6.19</v>
+        <v>-12.56</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.92</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-10.19</v>
+        <v>5.29</v>
       </c>
       <c r="D15" s="6">
-        <v>-13.16</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.97</v>
+        <v>4.39</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>4.8</v>
+        <v>-1.95</v>
       </c>
       <c r="D16" s="6">
-        <v>5.29</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.49</v>
+        <v>-1.2</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.16</v>
+        <v>1.08</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.21</v>
+        <v>2.43</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.05</v>
+        <v>-8.56</v>
       </c>
       <c r="D18" s="6">
-        <v>1.08</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.13</v>
+        <v>-8.52</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.04</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.37</v>
+        <v>-3.1</v>
       </c>
       <c r="D19" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.19</v>
+        <v>-3.92</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.81</v>
+        <v>-4.83</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.71</v>
+        <v>-4.51</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-5.2</v>
+        <v>-6.23</v>
       </c>
       <c r="D21" s="6">
-        <v>-4.83</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.37</v>
+        <v>-5.95</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-6.37</v>
+        <v>-5.72</v>
       </c>
       <c r="D22" s="6">
-        <v>-6.23</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.14</v>
+        <v>-4.66</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-5.58</v>
+        <v>-10.87</v>
       </c>
       <c r="D23" s="6">
-        <v>-5.72</v>
+        <v>-9.02</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.14</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-6.35</v>
+        <v>2.97</v>
       </c>
       <c r="D24" s="6">
-        <v>-10.87</v>
+        <v>4.25</v>
       </c>
       <c r="E24" s="7">
-        <v>-4.52</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>3.69</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="D25" s="6">
-        <v>2.97</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.72</v>
+        <v>8.82</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>4.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D26" s="6">
-        <v>9.460000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E26" s="8">
-        <v>5.33</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>0.08</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="D27" s="6">
-        <v>0.5600000000000001</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E27" s="8">
-        <v>0.48</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>13.43</v>
+        <v>-3.19</v>
       </c>
       <c r="D28" s="6">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-21.72</v>
+        <v>-5.49</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-1.64</v>
+        <v>-0.2</v>
       </c>
       <c r="D29" s="6">
-        <v>-3.19</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.55</v>
+        <v>-0.58</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>0.97</v>
+        <v>-6.4</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.2</v>
+        <v>-4.77</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.17</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.84</v>
+        <v>-5.03</v>
       </c>
       <c r="D31" s="6">
-        <v>-6.4</v>
+        <v>-1.12</v>
       </c>
       <c r="E31" s="7">
-        <v>-3.56</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>4.55</v>
+        <v>1.1</v>
       </c>
       <c r="D32" s="6">
-        <v>-5.03</v>
+        <v>2.39</v>
       </c>
       <c r="E32" s="7">
-        <v>-9.58</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="D33" s="6">
-        <v>1.1</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.41</v>
+        <v>4.27</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.55</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>0.22</v>
+        <v>-6.49</v>
       </c>
       <c r="D34" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.5</v>
+        <v>-4.53</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.96</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-3.28</v>
+        <v>1.49</v>
       </c>
       <c r="D35" s="6">
-        <v>-6.49</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.21</v>
+        <v>-0.58</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-2.68</v>
+        <v>1.94</v>
       </c>
       <c r="D36" s="6">
-        <v>1.49</v>
+        <v>0.16</v>
       </c>
       <c r="E36" s="8">
-        <v>4.17</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>0.47</v>
+        <v>1.44</v>
       </c>
       <c r="D37" s="6">
-        <v>1.94</v>
+        <v>1.09</v>
       </c>
       <c r="E37" s="8">
-        <v>1.47</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-2.53</v>
+        <v>-1.47</v>
       </c>
       <c r="D38" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="E38" s="8">
-        <v>3.97</v>
+        <v>1.16</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.63</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.67</v>
+        <v>-3.18</v>
       </c>
       <c r="D39" s="6">
-        <v>-1.47</v>
+        <v>-0.09</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.8</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.97</v>
+        <v>-5.64</v>
       </c>
       <c r="D40" s="6">
-        <v>-3.18</v>
+        <v>-4.9</v>
       </c>
       <c r="E40" s="7">
-        <v>-1.21</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>-4.32</v>
+        <v>19.5</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.64</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.32</v>
+        <v>12.17</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-7.33</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>17.2</v>
+        <v>-39.5</v>
       </c>
       <c r="D42" s="6">
-        <v>19.5</v>
+        <v>-39.6</v>
       </c>
       <c r="E42" s="8">
-        <v>2.3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-39.65</v>
+        <v>-31.91</v>
       </c>
       <c r="D43" s="6">
-        <v>-39.5</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.15</v>
+        <v>-31.24</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-28.21</v>
+        <v>-0.04</v>
       </c>
       <c r="D44" s="6">
-        <v>-31.91</v>
+        <v>1.01</v>
       </c>
       <c r="E44" s="7">
-        <v>-3.7</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>1.1</v>
+        <v>-12.66</v>
       </c>
       <c r="D45" s="6">
-        <v>-0.04</v>
+        <v>-11.21</v>
       </c>
       <c r="E45" s="7">
-        <v>-1.14</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-7.6</v>
+        <v>-42.32</v>
       </c>
       <c r="D46" s="6">
-        <v>-12.66</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-5.06</v>
+        <v>-42.97</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-41.37</v>
+        <v>-2.61</v>
       </c>
       <c r="D47" s="6">
-        <v>-42.32</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.95</v>
+        <v>-9.66</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-7.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-2.83</v>
+        <v>-7.01</v>
       </c>
       <c r="D48" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.22</v>
+        <v>-6.13</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-7.3</v>
+        <v>10.17</v>
       </c>
       <c r="D49" s="6">
-        <v>-7.01</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.29</v>
+        <v>13.21</v>
+      </c>
+      <c r="E49" s="7">
+        <v>3.04</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>8.82</v>
+        <v>-31.28</v>
       </c>
       <c r="D50" s="6">
-        <v>10.17</v>
+        <v>-31.86</v>
       </c>
       <c r="E50" s="8">
-        <v>1.35</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-29.91</v>
+        <v>39.89</v>
       </c>
       <c r="D51" s="6">
-        <v>-31.28</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.37</v>
+        <v>38.98</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>37.06</v>
+        <v>-46.38</v>
       </c>
       <c r="D52" s="6">
-        <v>39.89</v>
-      </c>
-      <c r="E52" s="8">
-        <v>2.83</v>
+        <v>-45.99</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.39</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-45.22</v>
+        <v>-44.99</v>
       </c>
       <c r="D53" s="6">
-        <v>-46.38</v>
+        <v>-42.54</v>
       </c>
       <c r="E53" s="7">
-        <v>-1.16</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-33.87</v>
+        <v>-38.93</v>
       </c>
       <c r="D54" s="6">
-        <v>-44.99</v>
+        <v>-38.36</v>
       </c>
       <c r="E54" s="7">
-        <v>-11.12</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-39.85</v>
+        <v>-21.79</v>
       </c>
       <c r="D55" s="6">
-        <v>-38.93</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.92</v>
+        <v>-20.52</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.27</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="6">
-        <v>-19.01</v>
+        <v>1.68</v>
       </c>
       <c r="D56" s="6">
-        <v>-21.79</v>
+        <v>2.51</v>
       </c>
       <c r="E56" s="7">
-        <v>-2.78</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>1.64</v>
+        <v>14.87</v>
       </c>
       <c r="D57" s="6">
-        <v>1.68</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.04</v>
+        <v>18.03</v>
+      </c>
+      <c r="E57" s="7">
+        <v>3.16</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>6.62</v>
+        <v>-11.64</v>
       </c>
       <c r="D58" s="6">
-        <v>14.87</v>
+        <v>-12.03</v>
       </c>
       <c r="E58" s="8">
-        <v>8.25</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-13.48</v>
+        <v>-7.75</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.64</v>
+        <v>-8.02</v>
       </c>
       <c r="E59" s="8">
-        <v>1.84</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-5.28</v>
+        <v>-16.35</v>
       </c>
       <c r="D60" s="6">
-        <v>-7.75</v>
+        <v>-16.16</v>
       </c>
       <c r="E60" s="7">
-        <v>-2.47</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-15.96</v>
+        <v>-10.84</v>
       </c>
       <c r="D61" s="6">
-        <v>-16.35</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="E61" s="7">
-        <v>-0.39</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-10.09</v>
+        <v>-21</v>
       </c>
       <c r="D62" s="6">
-        <v>-10.84</v>
+        <v>-20.21</v>
       </c>
       <c r="E62" s="7">
-        <v>-0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-20.13</v>
+        <v>0.48</v>
       </c>
       <c r="D63" s="6">
-        <v>-21</v>
+        <v>0.61</v>
       </c>
       <c r="E63" s="7">
-        <v>-0.87</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-1.36</v>
+        <v>-7.86</v>
       </c>
       <c r="D64" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="E64" s="8">
-        <v>1.84</v>
+        <v>-6.13</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.73</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-9.56</v>
+        <v>-4.44</v>
       </c>
       <c r="D65" s="6">
-        <v>-7.86</v>
-      </c>
-      <c r="E65" s="8">
-        <v>1.7</v>
+        <v>0.35</v>
+      </c>
+      <c r="E65" s="7">
+        <v>4.79</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-7.83</v>
+        <v>2.2</v>
       </c>
       <c r="D66" s="6">
-        <v>-4.44</v>
+        <v>-0.92</v>
       </c>
       <c r="E66" s="8">
-        <v>3.39</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>0.04</v>
+        <v>14.48</v>
       </c>
       <c r="D67" s="6">
-        <v>2.2</v>
+        <v>12.86</v>
       </c>
       <c r="E67" s="8">
-        <v>2.16</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>11.49</v>
+        <v>-11.45</v>
       </c>
       <c r="D68" s="6">
-        <v>14.48</v>
+        <v>-14.57</v>
       </c>
       <c r="E68" s="8">
-        <v>2.99</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-11.48</v>
+        <v>-13.77</v>
       </c>
       <c r="D69" s="6">
-        <v>-11.45</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.03</v>
+        <v>-12.77</v>
+      </c>
+      <c r="E69" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-6.9</v>
+        <v>-18.1</v>
       </c>
       <c r="D70" s="6">
-        <v>-13.77</v>
+        <v>-17.12</v>
       </c>
       <c r="E70" s="7">
-        <v>-6.87</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-20.82</v>
+        <v>-17.07</v>
       </c>
       <c r="D71" s="6">
-        <v>-18.1</v>
-      </c>
-      <c r="E71" s="8">
-        <v>2.72</v>
+        <v>-13.75</v>
+      </c>
+      <c r="E71" s="7">
+        <v>3.32</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-15.65</v>
+        <v>-5.86</v>
       </c>
       <c r="D72" s="6">
-        <v>-17.07</v>
+        <v>-4.11</v>
       </c>
       <c r="E72" s="7">
-        <v>-1.42</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-4.74</v>
+        <v>-6.45</v>
       </c>
       <c r="D73" s="6">
-        <v>-5.86</v>
+        <v>-5.62</v>
       </c>
       <c r="E73" s="7">
-        <v>-1.12</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-8.800000000000001</v>
+        <v>-39.8</v>
       </c>
       <c r="D74" s="6">
-        <v>-6.45</v>
-      </c>
-      <c r="E74" s="8">
-        <v>2.35</v>
+        <v>-38.87</v>
+      </c>
+      <c r="E74" s="7">
+        <v>0.93</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-39.74</v>
+        <v>-31.12</v>
       </c>
       <c r="D75" s="6">
-        <v>-39.8</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-0.06</v>
+        <v>-31.54</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-29.82</v>
+        <v>-17.91</v>
       </c>
       <c r="D76" s="6">
-        <v>-31.12</v>
+        <v>-17.51</v>
       </c>
       <c r="E76" s="7">
-        <v>-1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-15.96</v>
+        <v>-21.92</v>
       </c>
       <c r="D77" s="6">
-        <v>-17.91</v>
+        <v>-21.11</v>
       </c>
       <c r="E77" s="7">
-        <v>-1.95</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-20.61</v>
+        <v>-44</v>
       </c>
       <c r="D78" s="6">
-        <v>-21.92</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-1.31</v>
+        <v>-44.14</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-42.83</v>
+        <v>-35.18</v>
       </c>
       <c r="D79" s="6">
-        <v>-44</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-1.17</v>
+        <v>-35.94</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-35.35</v>
+        <v>-20.53</v>
       </c>
       <c r="D80" s="6">
-        <v>-35.18</v>
-      </c>
-      <c r="E80" s="8">
-        <v>0.17</v>
+        <v>-20.1</v>
+      </c>
+      <c r="E80" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-20.5</v>
+        <v>-14.63</v>
       </c>
       <c r="D81" s="6">
-        <v>-20.53</v>
+        <v>-11.93</v>
       </c>
       <c r="E81" s="7">
-        <v>-0.03</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-15.35</v>
+        <v>-34.66</v>
       </c>
       <c r="D82" s="6">
-        <v>-14.63</v>
+        <v>-35.14</v>
       </c>
       <c r="E82" s="8">
-        <v>0.72</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-33.93</v>
+        <v>-4.66</v>
       </c>
       <c r="D83" s="6">
-        <v>-34.66</v>
-      </c>
-      <c r="E83" s="7">
-        <v>-0.73</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-5.69</v>
+        <v>-45.82</v>
       </c>
       <c r="D84" s="6">
-        <v>-4.66</v>
-      </c>
-      <c r="E84" s="8">
-        <v>1.03</v>
+        <v>-45.31</v>
+      </c>
+      <c r="E84" s="7">
+        <v>0.51</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-45.75</v>
+        <v>-43.24</v>
       </c>
       <c r="D85" s="6">
-        <v>-45.82</v>
+        <v>-43.17</v>
       </c>
       <c r="E85" s="7">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-44.89</v>
+        <v>-39.3</v>
       </c>
       <c r="D86" s="6">
-        <v>-43.24</v>
-      </c>
-      <c r="E86" s="8">
-        <v>1.65</v>
+        <v>-39.28</v>
+      </c>
+      <c r="E86" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-39.74</v>
+        <v>-29.27</v>
       </c>
       <c r="D87" s="6">
-        <v>-39.3</v>
-      </c>
-      <c r="E87" s="8">
-        <v>0.44</v>
+        <v>-27.4</v>
+      </c>
+      <c r="E87" s="7">
+        <v>1.87</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>-26.62</v>
+        <v>736.25</v>
       </c>
       <c r="D88" s="6">
-        <v>-29.27</v>
+        <v>743.7</v>
       </c>
       <c r="E88" s="7">
-        <v>-2.65</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>745</v>
+        <v>1011.75</v>
       </c>
       <c r="D89" s="6">
-        <v>736.25</v>
+        <v>1020.75</v>
       </c>
       <c r="E89" s="7">
-        <v>-8.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>986.35</v>
+        <v>201.95</v>
       </c>
       <c r="D90" s="6">
-        <v>1011.75</v>
-      </c>
-      <c r="E90" s="8">
-        <v>25.4</v>
+        <v>202.62</v>
+      </c>
+      <c r="E90" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>202.15</v>
+        <v>674</v>
       </c>
       <c r="D91" s="6">
-        <v>201.95</v>
-      </c>
-      <c r="E91" s="7">
-        <v>-0.2</v>
+        <v>669.9</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-4.1</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>694.7</v>
+        <v>1692.4</v>
       </c>
       <c r="D92" s="6">
-        <v>674</v>
+        <v>1700.6</v>
       </c>
       <c r="E92" s="7">
-        <v>-20.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>1732.7</v>
+        <v>984.1</v>
       </c>
       <c r="D93" s="6">
-        <v>1692.4</v>
+        <v>994.3</v>
       </c>
       <c r="E93" s="7">
-        <v>-40.3</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>1000.6</v>
+        <v>3220</v>
       </c>
       <c r="D94" s="6">
-        <v>984.1</v>
-      </c>
-      <c r="E94" s="7">
-        <v>-16.5</v>
+        <v>3212</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-8</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>3287</v>
+        <v>682.25</v>
       </c>
       <c r="D95" s="6">
-        <v>3220</v>
-      </c>
-      <c r="E95" s="7">
-        <v>-67</v>
+        <v>674.3</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-7.95</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>680.5</v>
+        <v>367</v>
       </c>
       <c r="D96" s="6">
-        <v>682.25</v>
-      </c>
-      <c r="E96" s="8">
-        <v>1.75</v>
+        <v>369</v>
+      </c>
+      <c r="E96" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>367.15</v>
+        <v>184.97</v>
       </c>
       <c r="D97" s="6">
-        <v>367</v>
+        <v>190.82</v>
       </c>
       <c r="E97" s="7">
-        <v>-0.15</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>183.4</v>
+        <v>2105</v>
       </c>
       <c r="D98" s="6">
-        <v>184.97</v>
+        <v>2089.6</v>
       </c>
       <c r="E98" s="8">
-        <v>1.57</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>2128.7</v>
+        <v>4928.5</v>
       </c>
       <c r="D99" s="6">
-        <v>2105</v>
-      </c>
-      <c r="E99" s="7">
-        <v>-23.7</v>
+        <v>4880</v>
+      </c>
+      <c r="E99" s="8">
+        <v>-48.5</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>4875</v>
+        <v>2782.9</v>
       </c>
       <c r="D100" s="6">
-        <v>4928.5</v>
+        <v>2774</v>
       </c>
       <c r="E100" s="8">
-        <v>53.5</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>2815.5</v>
+        <v>216.06</v>
       </c>
       <c r="D101" s="6">
-        <v>2782.9</v>
+        <v>216.31</v>
       </c>
       <c r="E101" s="7">
-        <v>-32.6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>216.43</v>
+        <v>35.62</v>
       </c>
       <c r="D102" s="6">
-        <v>216.06</v>
+        <v>35.63</v>
       </c>
       <c r="E102" s="7">
-        <v>-0.37</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="6">
-        <v>35.36</v>
+        <v>1100.8</v>
       </c>
       <c r="D103" s="6">
-        <v>35.62</v>
-      </c>
-      <c r="E103" s="8">
-        <v>0.26</v>
+        <v>1130</v>
+      </c>
+      <c r="E103" s="7">
+        <v>29.2</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C104" s="6">
-        <v>1142.1</v>
+        <v>74</v>
       </c>
       <c r="D104" s="6">
-        <v>1100.8</v>
+        <v>81</v>
       </c>
       <c r="E104" s="7">
-        <v>-41.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C105" s="6">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D105" s="6">
-        <v>32</v>
-      </c>
-      <c r="E105" s="8">
+        <v>50</v>
+      </c>
+      <c r="E105" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D106" s="6">
-        <v>44</v>
-      </c>
-      <c r="E106" s="7">
+        <v>62</v>
+      </c>
+      <c r="E106" s="8">
         <v>-6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="D107" s="6">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E107" s="8">
-        <v>6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="D108" s="6">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="E108" s="7">
-        <v>-19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="6">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D109" s="6">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E109" s="8">
-        <v>13</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C110" s="6">
-        <v>60.74</v>
+        <v>19</v>
       </c>
       <c r="D110" s="6">
-        <v>55.55</v>
-      </c>
-      <c r="E110" s="7">
-        <v>-5.19</v>
+        <v>13</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="6">
-        <v>55.79</v>
+        <v>13</v>
       </c>
       <c r="D111" s="6">
-        <v>59.24</v>
-      </c>
-      <c r="E111" s="8">
-        <v>3.45</v>
+        <v>19</v>
+      </c>
+      <c r="E111" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>34.14</v>
+        <v>55.55</v>
       </c>
       <c r="D112" s="6">
-        <v>33.78</v>
+        <v>58.78</v>
       </c>
       <c r="E112" s="7">
-        <v>-0.36</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>55.47</v>
+        <v>59.24</v>
       </c>
       <c r="D113" s="6">
-        <v>51.42</v>
+        <v>60.42</v>
       </c>
       <c r="E113" s="7">
-        <v>-4.05</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>47.39</v>
+        <v>33.78</v>
       </c>
       <c r="D114" s="6">
-        <v>41.66</v>
+        <v>36.21</v>
       </c>
       <c r="E114" s="7">
-        <v>-5.73</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>39.27</v>
+        <v>51.42</v>
       </c>
       <c r="D115" s="6">
-        <v>34.72</v>
-      </c>
-      <c r="E115" s="7">
-        <v>-4.55</v>
+        <v>50.64</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>30.75</v>
+        <v>41.66</v>
       </c>
       <c r="D116" s="6">
-        <v>27.62</v>
+        <v>43.16</v>
       </c>
       <c r="E116" s="7">
-        <v>-3.13</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>54.49</v>
+        <v>34.72</v>
       </c>
       <c r="D117" s="6">
-        <v>54.89</v>
-      </c>
-      <c r="E117" s="8">
-        <v>0.4</v>
+        <v>39.39</v>
+      </c>
+      <c r="E117" s="7">
+        <v>4.67</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>48.8</v>
+        <v>27.62</v>
       </c>
       <c r="D118" s="6">
-        <v>48.65</v>
-      </c>
-      <c r="E118" s="7">
-        <v>-0.15</v>
+        <v>27.26</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>45.53</v>
+        <v>54.89</v>
       </c>
       <c r="D119" s="6">
-        <v>48.67</v>
+        <v>52.66</v>
       </c>
       <c r="E119" s="8">
-        <v>3.14</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>35.87</v>
+        <v>48.65</v>
       </c>
       <c r="D120" s="6">
-        <v>34.04</v>
+        <v>50.7</v>
       </c>
       <c r="E120" s="7">
-        <v>-1.83</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>42.88</v>
+        <v>48.67</v>
       </c>
       <c r="D121" s="6">
-        <v>47.82</v>
-      </c>
-      <c r="E121" s="8">
-        <v>4.94</v>
+        <v>58.32</v>
+      </c>
+      <c r="E121" s="7">
+        <v>9.65</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>44.02</v>
+        <v>34.04</v>
       </c>
       <c r="D122" s="6">
-        <v>40.3</v>
-      </c>
-      <c r="E122" s="7">
-        <v>-3.72</v>
+        <v>32.86</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>39.09</v>
+        <v>47.82</v>
       </c>
       <c r="D123" s="6">
-        <v>38.74</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-0.35</v>
+        <v>44.1</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-3.72</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>37.43</v>
+        <v>40.3</v>
       </c>
       <c r="D124" s="6">
-        <v>39.56</v>
+        <v>39.32</v>
       </c>
       <c r="E124" s="8">
-        <v>2.13</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="6">
-        <v>38.96</v>
+        <v>38.74</v>
       </c>
       <c r="D125" s="6">
-        <v>32.49</v>
+        <v>39.14</v>
       </c>
       <c r="E125" s="7">
-        <v>-6.47</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C126" s="6">
-        <v>77.73</v>
+        <v>39.56</v>
       </c>
       <c r="D126" s="6">
-        <v>-27.69</v>
+        <v>39.64</v>
       </c>
       <c r="E126" s="7">
-        <v>-105.42</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="6">
-        <v>-39.9</v>
+        <v>32.49</v>
       </c>
       <c r="D127" s="6">
-        <v>33.71</v>
-      </c>
-      <c r="E127" s="8">
-        <v>73.61</v>
+        <v>40.07</v>
+      </c>
+      <c r="E127" s="7">
+        <v>7.58</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>-37.74</v>
+        <v>-27.69</v>
       </c>
       <c r="D128" s="6">
-        <v>-15.64</v>
-      </c>
-      <c r="E128" s="8">
-        <v>22.1</v>
+        <v>-26.52</v>
+      </c>
+      <c r="E128" s="7">
+        <v>1.17</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>4.99</v>
+        <v>33.71</v>
       </c>
       <c r="D129" s="6">
-        <v>-50.96</v>
+        <v>55.75</v>
       </c>
       <c r="E129" s="7">
-        <v>-55.95</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>-60.93</v>
+        <v>-15.64</v>
       </c>
       <c r="D130" s="6">
-        <v>-51.08</v>
+        <v>-57.16</v>
       </c>
       <c r="E130" s="8">
-        <v>9.85</v>
+        <v>-41.52</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>-43.37</v>
+        <v>-50.96</v>
       </c>
       <c r="D131" s="6">
-        <v>-41.5</v>
+        <v>-64.14</v>
       </c>
       <c r="E131" s="8">
-        <v>1.87</v>
+        <v>-13.18</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>79</v>
+        <v>-51.08</v>
       </c>
       <c r="D132" s="6">
-        <v>173.16</v>
-      </c>
-      <c r="E132" s="8">
-        <v>94.16</v>
+        <v>-43.3</v>
+      </c>
+      <c r="E132" s="7">
+        <v>7.78</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>-73.23999999999999</v>
+        <v>-41.5</v>
       </c>
       <c r="D133" s="6">
-        <v>-67.31999999999999</v>
-      </c>
-      <c r="E133" s="8">
-        <v>5.92</v>
+        <v>-25.8</v>
+      </c>
+      <c r="E133" s="7">
+        <v>15.7</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-45.92</v>
+        <v>173.16</v>
       </c>
       <c r="D134" s="6">
-        <v>-51.99</v>
-      </c>
-      <c r="E134" s="7">
-        <v>-6.07</v>
+        <v>-23.71</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-196.87</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>-68.03</v>
+        <v>-67.31999999999999</v>
       </c>
       <c r="D135" s="6">
-        <v>-42.56</v>
+        <v>-83.44</v>
       </c>
       <c r="E135" s="8">
-        <v>25.47</v>
+        <v>-16.12</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-18.33</v>
+        <v>-51.99</v>
       </c>
       <c r="D136" s="6">
-        <v>26.97</v>
+        <v>-72.62</v>
       </c>
       <c r="E136" s="8">
-        <v>45.3</v>
+        <v>-20.63</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>27.2</v>
+        <v>-42.56</v>
       </c>
       <c r="D137" s="6">
-        <v>135.7</v>
-      </c>
-      <c r="E137" s="8">
-        <v>108.5</v>
+        <v>32.26</v>
+      </c>
+      <c r="E137" s="7">
+        <v>74.81999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>-4.22</v>
+        <v>26.97</v>
       </c>
       <c r="D138" s="6">
-        <v>20.9</v>
+        <v>-24.34</v>
       </c>
       <c r="E138" s="8">
-        <v>25.12</v>
+        <v>-51.31</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>-27.29</v>
+        <v>135.7</v>
       </c>
       <c r="D139" s="6">
-        <v>-59.62</v>
-      </c>
-      <c r="E139" s="7">
-        <v>-32.33</v>
+        <v>35.65</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-100.05</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="6">
-        <v>-77.5</v>
+        <v>20.9</v>
       </c>
       <c r="D140" s="6">
-        <v>-70.22</v>
-      </c>
-      <c r="E140" s="8">
-        <v>7.28</v>
+        <v>30.51</v>
+      </c>
+      <c r="E140" s="7">
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="6">
-        <v>23.94</v>
+        <v>-59.62</v>
       </c>
       <c r="D141" s="6">
+        <v>-10.95</v>
+      </c>
+      <c r="E141" s="7">
+        <v>48.67</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="6">
+        <v>-70.22</v>
+      </c>
+      <c r="D142" s="6">
+        <v>-72.76000000000001</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6">
         <v>54.14</v>
       </c>
-      <c r="E141" s="8">
-        <v>30.2</v>
+      <c r="D143" s="6">
+        <v>7.92</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-46.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5300,28 +5340,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5335,16 +5375,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>43.1</v>
+        <v>44.5</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.7</v>
+        <v>-6</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5484,34 +5524,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.4174</v>
+        <v>0.4118</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3469</v>
+        <v>0.3333</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2324</v>
+        <v>0.2259</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2231</v>
+        <v>0.2144</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1913</v>
+        <v>0.1862</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1319</v>
+        <v>0.1285</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1255</v>
+        <v>0.1211</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1044</v>
+        <v>0.1091</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0436</v>
+        <v>0.043</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0373</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5536,22 +5576,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0027</v>
+        <v>0.0021</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0188</v>
+        <v>-0.0152</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0258</v>
+        <v>-0.0321</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0595</v>
+        <v>-0.0564</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.09</v>
+        <v>-0.0917</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.0949</v>
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="88">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,25 +217,34 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.6 → 50.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.6</t>
+    <t>50.6 → 47.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>52.7 → 48.4</t>
+  </si>
+  <si>
+    <t>52.7</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>50.7 → 45.3</t>
   </si>
   <si>
     <t>50.7</t>
   </si>
   <si>
-    <t>48.7 → 58.3</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>58.3</t>
+    <t>45.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -321,14 +330,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -361,13 +370,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -808,7 +817,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="3" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -959,37 +969,37 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>743.7</v>
+        <v>728.8</v>
       </c>
       <c r="D2">
-        <v>1.01</v>
+        <v>-2</v>
       </c>
       <c r="E2">
-        <v>775.55</v>
+        <v>769.4</v>
       </c>
       <c r="F2">
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-4.11</v>
+        <v>-5.28</v>
       </c>
       <c r="H2">
-        <v>30.26</v>
+        <v>27.65</v>
       </c>
       <c r="I2">
-        <v>4.25</v>
+        <v>0.3</v>
       </c>
       <c r="J2">
-        <v>2.03</v>
+        <v>-0.16</v>
       </c>
       <c r="K2">
-        <v>2.51</v>
+        <v>1.13</v>
       </c>
       <c r="L2">
-        <v>-4.9</v>
+        <v>-6.03</v>
       </c>
       <c r="M2">
-        <v>33.33</v>
+        <v>33.55</v>
       </c>
       <c r="N2">
         <v>81</v>
@@ -998,19 +1008,19 @@
         <v>56</v>
       </c>
       <c r="P2">
-        <v>736.87</v>
+        <v>737.3</v>
       </c>
       <c r="Q2">
-        <v>724.37</v>
+        <v>724.76</v>
       </c>
       <c r="R2">
-        <v>728.66</v>
+        <v>728.37</v>
       </c>
       <c r="S2">
-        <v>688.3099999999999</v>
+        <v>688.3</v>
       </c>
       <c r="T2">
-        <v>8.050000000000001</v>
+        <v>5.88</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1025,34 +1035,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.78</v>
+        <v>50.83</v>
       </c>
       <c r="Z2">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="AA2">
-        <v>0.03</v>
+        <v>0.53</v>
       </c>
       <c r="AB2">
-        <v>2.82</v>
+        <v>2.01</v>
       </c>
       <c r="AC2">
-        <v>85.2</v>
+        <v>64.67</v>
       </c>
       <c r="AD2">
-        <v>87.76000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="AE2">
-        <v>15.17</v>
+        <v>15.25</v>
       </c>
       <c r="AF2">
-        <v>-26.52</v>
+        <v>-35.84</v>
       </c>
       <c r="AG2">
-        <v>745.41</v>
+        <v>745.8200000000001</v>
       </c>
       <c r="AH2">
-        <v>703.34</v>
+        <v>703.7</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1061,7 +1071,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>30.89</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1082,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>1020.75</v>
+        <v>993.05</v>
       </c>
       <c r="D3">
-        <v>0.89</v>
+        <v>-2.71</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1084,46 +1094,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-5.62</v>
+        <v>-8.18</v>
       </c>
       <c r="H3">
-        <v>101.98</v>
+        <v>96.5</v>
       </c>
       <c r="I3">
-        <v>8.82</v>
+        <v>2.88</v>
       </c>
       <c r="J3">
-        <v>11.52</v>
+        <v>7.29</v>
       </c>
       <c r="K3">
-        <v>18.03</v>
+        <v>15.06</v>
       </c>
       <c r="L3">
-        <v>12.17</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M3">
-        <v>12.85</v>
+        <v>11.14</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>999.1900000000001</v>
+        <v>1004.75</v>
       </c>
       <c r="Q3">
-        <v>955.79</v>
+        <v>958.64</v>
       </c>
       <c r="R3">
-        <v>953.52</v>
+        <v>956.13</v>
       </c>
       <c r="S3">
-        <v>760.9</v>
+        <v>761.8200000000001</v>
       </c>
       <c r="T3">
-        <v>34.15</v>
+        <v>30.35</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1138,34 +1148,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>60.42</v>
+        <v>55.13</v>
       </c>
       <c r="Z3">
-        <v>14.56</v>
+        <v>14.85</v>
       </c>
       <c r="AA3">
-        <v>6.06</v>
+        <v>7.82</v>
       </c>
       <c r="AB3">
-        <v>8.5</v>
+        <v>7.03</v>
       </c>
       <c r="AC3">
-        <v>87.09</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="AD3">
-        <v>86.95</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="AE3">
-        <v>45.31</v>
+        <v>45.21</v>
       </c>
       <c r="AF3">
-        <v>55.75</v>
+        <v>-47.21</v>
       </c>
       <c r="AG3">
-        <v>1018.45</v>
+        <v>1022.68</v>
       </c>
       <c r="AH3">
-        <v>893.13</v>
+        <v>894.6</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1174,7 +1184,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>27.92</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,37 +1195,37 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>202.62</v>
+        <v>200.36</v>
       </c>
       <c r="D4">
-        <v>0.33</v>
+        <v>-1.12</v>
       </c>
       <c r="E4">
-        <v>331.45</v>
+        <v>324.39</v>
       </c>
       <c r="F4">
-        <v>200.82</v>
+        <v>200.36</v>
       </c>
       <c r="G4">
-        <v>-38.87</v>
+        <v>-38.23</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.01</v>
+        <v>-1.85</v>
       </c>
       <c r="J4">
-        <v>-4.12</v>
+        <v>-5.9</v>
       </c>
       <c r="K4">
-        <v>-12.03</v>
+        <v>-11.94</v>
       </c>
       <c r="L4">
-        <v>-39.6</v>
+        <v>-39.55</v>
       </c>
       <c r="M4">
-        <v>-5.64</v>
+        <v>-5.83</v>
       </c>
       <c r="N4">
         <v>32</v>
@@ -1224,19 +1234,19 @@
         <v>13</v>
       </c>
       <c r="P4">
-        <v>202.93</v>
+        <v>202.18</v>
       </c>
       <c r="Q4">
-        <v>205.75</v>
+        <v>205.07</v>
       </c>
       <c r="R4">
-        <v>213.52</v>
+        <v>212.76</v>
       </c>
       <c r="S4">
-        <v>241.79</v>
+        <v>241.53</v>
       </c>
       <c r="T4">
-        <v>-16.2</v>
+        <v>-17.04</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1251,43 +1261,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.21</v>
+        <v>31.95</v>
       </c>
       <c r="Z4">
-        <v>-3.22</v>
+        <v>-3.26</v>
       </c>
       <c r="AA4">
-        <v>-3.42</v>
+        <v>-3.38</v>
       </c>
       <c r="AB4">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="AC4">
-        <v>56.79</v>
+        <v>53.45</v>
       </c>
       <c r="AD4">
-        <v>61.54</v>
+        <v>56.44</v>
       </c>
       <c r="AE4">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="AF4">
-        <v>-57.16</v>
+        <v>-16.44</v>
       </c>
       <c r="AG4">
-        <v>212.98</v>
+        <v>211.58</v>
       </c>
       <c r="AH4">
-        <v>198.51</v>
+        <v>198.56</v>
       </c>
       <c r="AI4">
-        <v>214.01</v>
+        <v>213.5</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>19.42</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,58 +1308,58 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>669.9</v>
+        <v>652.2</v>
       </c>
       <c r="D5">
-        <v>-0.61</v>
+        <v>-2.64</v>
       </c>
       <c r="E5">
-        <v>978.55</v>
+        <v>959.2</v>
       </c>
       <c r="F5">
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-31.54</v>
+        <v>-32.01</v>
       </c>
       <c r="H5">
-        <v>16.62</v>
+        <v>13.54</v>
       </c>
       <c r="I5">
-        <v>-8.460000000000001</v>
+        <v>-16.31</v>
       </c>
       <c r="J5">
-        <v>6.85</v>
+        <v>4.13</v>
       </c>
       <c r="K5">
-        <v>-8.02</v>
+        <v>-12.6</v>
       </c>
       <c r="L5">
-        <v>-31.24</v>
+        <v>-33.35</v>
       </c>
       <c r="M5">
-        <v>-3.21</v>
+        <v>-4.56</v>
       </c>
       <c r="N5">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P5">
-        <v>702.23</v>
+        <v>676.8099999999999</v>
       </c>
       <c r="Q5">
-        <v>656.98</v>
+        <v>657.7</v>
       </c>
       <c r="R5">
-        <v>664.84</v>
+        <v>663.91</v>
       </c>
       <c r="S5">
-        <v>702.3</v>
+        <v>701.75</v>
       </c>
       <c r="T5">
-        <v>-4.61</v>
+        <v>-7.06</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1364,43 +1374,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>50.64</v>
+        <v>47.27</v>
       </c>
       <c r="Z5">
-        <v>10.23</v>
+        <v>7.49</v>
       </c>
       <c r="AA5">
-        <v>4.69</v>
+        <v>5.25</v>
       </c>
       <c r="AB5">
-        <v>5.54</v>
+        <v>2.24</v>
       </c>
       <c r="AC5">
-        <v>49.19</v>
+        <v>43.54</v>
       </c>
       <c r="AD5">
-        <v>57.2</v>
+        <v>48.36</v>
       </c>
       <c r="AE5">
-        <v>34.6</v>
+        <v>33.56</v>
       </c>
       <c r="AF5">
-        <v>-64.14</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="AG5">
-        <v>753.52</v>
+        <v>753.86</v>
       </c>
       <c r="AH5">
-        <v>560.4299999999999</v>
+        <v>561.55</v>
       </c>
       <c r="AI5">
-        <v>776.29</v>
+        <v>760.65</v>
       </c>
       <c r="AJ5" t="s">
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>38.3</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1421,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1700.6</v>
+        <v>1670</v>
       </c>
       <c r="D6">
-        <v>0.48</v>
+        <v>-1.8</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1423,22 +1433,22 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-17.51</v>
+        <v>-19</v>
       </c>
       <c r="H6">
-        <v>26.17</v>
+        <v>23.9</v>
       </c>
       <c r="I6">
-        <v>-5.49</v>
+        <v>-6.79</v>
       </c>
       <c r="J6">
-        <v>0.72</v>
+        <v>-1.76</v>
       </c>
       <c r="K6">
         <v>-16.16</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>-0.85</v>
       </c>
       <c r="M6">
         <v>4.3</v>
@@ -1447,22 +1457,22 @@
         <v>62</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>1739.48</v>
+        <v>1715.16</v>
       </c>
       <c r="Q6">
-        <v>1734.42</v>
+        <v>1735.45</v>
       </c>
       <c r="R6">
-        <v>1745.37</v>
+        <v>1741.65</v>
       </c>
       <c r="S6">
-        <v>1710.11</v>
+        <v>1709.27</v>
       </c>
       <c r="T6">
-        <v>-0.5600000000000001</v>
+        <v>-2.3</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1477,34 +1487,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>43.16</v>
+        <v>39.11</v>
       </c>
       <c r="Z6">
-        <v>-1.62</v>
+        <v>-6.99</v>
       </c>
       <c r="AA6">
-        <v>1.18</v>
+        <v>-0.46</v>
       </c>
       <c r="AB6">
-        <v>-2.79</v>
+        <v>-6.53</v>
       </c>
       <c r="AC6">
-        <v>8.99</v>
+        <v>2.8</v>
       </c>
       <c r="AD6">
-        <v>33.69</v>
+        <v>14.26</v>
       </c>
       <c r="AE6">
-        <v>50.35</v>
+        <v>49.21</v>
       </c>
       <c r="AF6">
-        <v>-43.3</v>
+        <v>-59.44</v>
       </c>
       <c r="AG6">
-        <v>1813.35</v>
+        <v>1810.12</v>
       </c>
       <c r="AH6">
-        <v>1655.48</v>
+        <v>1660.78</v>
       </c>
       <c r="AI6">
         <v>1813.9</v>
@@ -1513,7 +1523,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>27.36</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1534,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>994.3</v>
+        <v>986.3</v>
       </c>
       <c r="D7">
-        <v>1.04</v>
+        <v>-0.8</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1536,46 +1546,46 @@
         <v>984.1</v>
       </c>
       <c r="G7">
-        <v>-21.11</v>
+        <v>-21.74</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>0.22</v>
       </c>
       <c r="I7">
-        <v>-0.58</v>
+        <v>-2.7</v>
       </c>
       <c r="J7">
-        <v>-6.42</v>
+        <v>-7</v>
       </c>
       <c r="K7">
-        <v>-9.449999999999999</v>
+        <v>-12.82</v>
       </c>
       <c r="L7">
-        <v>-11.21</v>
+        <v>-11.73</v>
       </c>
       <c r="M7">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P7">
-        <v>997.74</v>
+        <v>992.26</v>
       </c>
       <c r="Q7">
-        <v>1011.73</v>
+        <v>1008.69</v>
       </c>
       <c r="R7">
-        <v>1054.88</v>
+        <v>1052.89</v>
       </c>
       <c r="S7">
-        <v>1113.98</v>
+        <v>1113.15</v>
       </c>
       <c r="T7">
-        <v>-10.74</v>
+        <v>-11.4</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1590,43 +1600,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>39.39</v>
+        <v>37.15</v>
       </c>
       <c r="Z7">
-        <v>-18.81</v>
+        <v>-18.7</v>
       </c>
       <c r="AA7">
-        <v>-19.65</v>
+        <v>-19.46</v>
       </c>
       <c r="AB7">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="AC7">
-        <v>67.56</v>
+        <v>62.65</v>
       </c>
       <c r="AD7">
-        <v>70.05</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AE7">
-        <v>18.58</v>
+        <v>18.06</v>
       </c>
       <c r="AF7">
-        <v>-25.8</v>
+        <v>-11.71</v>
       </c>
       <c r="AG7">
-        <v>1050.19</v>
+        <v>1044.92</v>
       </c>
       <c r="AH7">
-        <v>973.27</v>
+        <v>972.46</v>
       </c>
       <c r="AI7">
-        <v>1045.9</v>
+        <v>1041.68</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>46.03</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,37 +1647,37 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3212</v>
+        <v>3183.8</v>
       </c>
       <c r="D8">
-        <v>-0.25</v>
+        <v>-0.88</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
       </c>
       <c r="F8">
-        <v>3212</v>
+        <v>3183.8</v>
       </c>
       <c r="G8">
-        <v>-44.14</v>
+        <v>-44.63</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.77</v>
+        <v>-5.85</v>
       </c>
       <c r="J8">
-        <v>-12.56</v>
+        <v>-13.15</v>
       </c>
       <c r="K8">
-        <v>-20.21</v>
+        <v>-20.96</v>
       </c>
       <c r="L8">
-        <v>-42.97</v>
+        <v>-43.37</v>
       </c>
       <c r="M8">
-        <v>-10</v>
+        <v>-10.59</v>
       </c>
       <c r="N8">
         <v>7</v>
@@ -1676,19 +1686,19 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>3273.5</v>
+        <v>3233.9</v>
       </c>
       <c r="Q8">
-        <v>3463.82</v>
+        <v>3440.51</v>
       </c>
       <c r="R8">
-        <v>3574.42</v>
+        <v>3567.69</v>
       </c>
       <c r="S8">
-        <v>4281.22</v>
+        <v>4271.51</v>
       </c>
       <c r="T8">
-        <v>-24.97</v>
+        <v>-25.46</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1703,43 +1713,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>27.26</v>
+        <v>25.99</v>
       </c>
       <c r="Z8">
-        <v>-110.93</v>
+        <v>-116.51</v>
       </c>
       <c r="AA8">
-        <v>-86.95</v>
+        <v>-92.86</v>
       </c>
       <c r="AB8">
-        <v>-23.98</v>
+        <v>-23.64</v>
       </c>
       <c r="AC8">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>7.29</v>
+        <v>2.91</v>
       </c>
       <c r="AE8">
-        <v>84.98</v>
+        <v>83.62</v>
       </c>
       <c r="AF8">
-        <v>-23.71</v>
+        <v>6.62</v>
       </c>
       <c r="AG8">
-        <v>3763.19</v>
+        <v>3751.22</v>
       </c>
       <c r="AH8">
-        <v>3164.44</v>
+        <v>3129.79</v>
       </c>
       <c r="AI8">
-        <v>3486.43</v>
+        <v>3452.86</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>40.25</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1750,10 +1760,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>674.3</v>
+        <v>658.35</v>
       </c>
       <c r="D9">
-        <v>-1.17</v>
+        <v>-2.37</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1762,46 +1772,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-35.94</v>
+        <v>-37.45</v>
       </c>
       <c r="H9">
-        <v>25.25</v>
+        <v>22.29</v>
       </c>
       <c r="I9">
-        <v>-1.12</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="J9">
-        <v>4.39</v>
+        <v>2.17</v>
       </c>
       <c r="K9">
-        <v>0.61</v>
+        <v>-3.02</v>
       </c>
       <c r="L9">
-        <v>-9.66</v>
+        <v>-9.76</v>
       </c>
       <c r="M9">
-        <v>41.18</v>
+        <v>40.48</v>
       </c>
       <c r="N9">
         <v>74</v>
       </c>
       <c r="O9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P9">
-        <v>691.74</v>
+        <v>679.55</v>
       </c>
       <c r="Q9">
-        <v>656.23</v>
+        <v>656.92</v>
       </c>
       <c r="R9">
-        <v>660.29</v>
+        <v>660.01</v>
       </c>
       <c r="S9">
-        <v>663.1799999999999</v>
+        <v>662.95</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1813,46 +1823,46 @@
         <v>54</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>52.66</v>
+        <v>48.41</v>
       </c>
       <c r="Z9">
-        <v>9.050000000000001</v>
+        <v>7.13</v>
       </c>
       <c r="AA9">
-        <v>4.51</v>
+        <v>5.03</v>
       </c>
       <c r="AB9">
-        <v>4.54</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>54.23</v>
+        <v>49.35</v>
       </c>
       <c r="AD9">
-        <v>61.45</v>
+        <v>54.73</v>
       </c>
       <c r="AE9">
-        <v>25.71</v>
+        <v>25.21</v>
       </c>
       <c r="AF9">
-        <v>-83.44</v>
+        <v>-85.69</v>
       </c>
       <c r="AG9">
-        <v>719.03</v>
+        <v>719.48</v>
       </c>
       <c r="AH9">
-        <v>593.4299999999999</v>
+        <v>594.37</v>
       </c>
       <c r="AI9">
-        <v>660.59</v>
+        <v>739.54</v>
       </c>
       <c r="AJ9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK9">
-        <v>39.82</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1873,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>369</v>
+        <v>363.45</v>
       </c>
       <c r="D10">
-        <v>0.54</v>
+        <v>-1.5</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1875,46 +1885,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-20.1</v>
+        <v>-21.3</v>
       </c>
       <c r="H10">
-        <v>6.88</v>
+        <v>5.27</v>
       </c>
       <c r="I10">
-        <v>2.39</v>
+        <v>-1.5</v>
       </c>
       <c r="J10">
-        <v>-1.2</v>
+        <v>-1.93</v>
       </c>
       <c r="K10">
-        <v>-6.13</v>
+        <v>-6.56</v>
       </c>
       <c r="L10">
-        <v>-6.13</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="M10">
-        <v>21.44</v>
+        <v>21.85</v>
       </c>
       <c r="N10">
         <v>68</v>
       </c>
       <c r="O10">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P10">
-        <v>369.39</v>
+        <v>368.28</v>
       </c>
       <c r="Q10">
-        <v>363.32</v>
+        <v>363.29</v>
       </c>
       <c r="R10">
-        <v>372.49</v>
+        <v>372.14</v>
       </c>
       <c r="S10">
-        <v>387.19</v>
+        <v>387.09</v>
       </c>
       <c r="T10">
-        <v>-4.7</v>
+        <v>-6.11</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1929,34 +1939,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>50.7</v>
+        <v>45.31</v>
       </c>
       <c r="Z10">
-        <v>-1.11</v>
+        <v>-1.31</v>
       </c>
       <c r="AA10">
-        <v>-2.32</v>
+        <v>-2.12</v>
       </c>
       <c r="AB10">
-        <v>1.21</v>
+        <v>0.8</v>
       </c>
       <c r="AC10">
-        <v>62.55</v>
+        <v>47.08</v>
       </c>
       <c r="AD10">
-        <v>76.38</v>
+        <v>61.52</v>
       </c>
       <c r="AE10">
-        <v>7.46</v>
+        <v>7.36</v>
       </c>
       <c r="AF10">
-        <v>-72.62</v>
+        <v>-46.51</v>
       </c>
       <c r="AG10">
-        <v>377.98</v>
+        <v>377.95</v>
       </c>
       <c r="AH10">
-        <v>348.65</v>
+        <v>348.63</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -1965,7 +1975,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>44.57</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1976,10 +1986,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>190.82</v>
+        <v>188.02</v>
       </c>
       <c r="D11">
-        <v>3.16</v>
+        <v>-1.47</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1988,46 +1998,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-11.93</v>
+        <v>-13.22</v>
       </c>
       <c r="H11">
-        <v>21.22</v>
+        <v>19.44</v>
       </c>
       <c r="I11">
-        <v>4.27</v>
+        <v>0.39</v>
       </c>
       <c r="J11">
-        <v>2.43</v>
+        <v>0.58</v>
       </c>
       <c r="K11">
-        <v>0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="L11">
-        <v>13.21</v>
+        <v>11.9</v>
       </c>
       <c r="M11">
-        <v>10.91</v>
+        <v>11.38</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P11">
-        <v>186.4</v>
+        <v>186.55</v>
       </c>
       <c r="Q11">
         <v>185.68</v>
       </c>
       <c r="R11">
-        <v>186.16</v>
+        <v>186.22</v>
       </c>
       <c r="S11">
-        <v>191.24</v>
+        <v>191.36</v>
       </c>
       <c r="T11">
-        <v>-0.22</v>
+        <v>-1.75</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2042,31 +2052,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>58.32</v>
+        <v>53.17</v>
       </c>
       <c r="Z11">
-        <v>-0.04</v>
+        <v>0.13</v>
       </c>
       <c r="AA11">
-        <v>-0.46</v>
+        <v>-0.34</v>
       </c>
       <c r="AB11">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="AC11">
-        <v>55.46</v>
+        <v>69.83</v>
       </c>
       <c r="AD11">
-        <v>47.77</v>
+        <v>54.71</v>
       </c>
       <c r="AE11">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
       <c r="AF11">
-        <v>32.26</v>
+        <v>-48.15</v>
       </c>
       <c r="AG11">
-        <v>190.1</v>
+        <v>190.11</v>
       </c>
       <c r="AH11">
         <v>181.25</v>
@@ -2078,7 +2088,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>21.13</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2089,10 +2099,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2089.6</v>
+        <v>2087</v>
       </c>
       <c r="D12">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2101,46 +2111,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-35.14</v>
+        <v>-35.22</v>
       </c>
       <c r="H12">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="I12">
-        <v>-4.53</v>
+        <v>-4.7</v>
       </c>
       <c r="J12">
-        <v>-8.52</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="K12">
-        <v>-0.92</v>
+        <v>-0.37</v>
       </c>
       <c r="L12">
-        <v>-31.86</v>
+        <v>-31.79</v>
       </c>
       <c r="M12">
-        <v>-9.17</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="N12">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P12">
-        <v>2123.66</v>
+        <v>2103.06</v>
       </c>
       <c r="Q12">
-        <v>2239.87</v>
+        <v>2230.72</v>
       </c>
       <c r="R12">
-        <v>2295.28</v>
+        <v>2293.23</v>
       </c>
       <c r="S12">
-        <v>2514.87</v>
+        <v>2509.62</v>
       </c>
       <c r="T12">
-        <v>-16.91</v>
+        <v>-16.84</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2155,43 +2165,43 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>32.86</v>
+        <v>32.65</v>
       </c>
       <c r="Z12">
-        <v>-53.17</v>
+        <v>-56.35</v>
       </c>
       <c r="AA12">
-        <v>-34.9</v>
+        <v>-39.19</v>
       </c>
       <c r="AB12">
-        <v>-18.27</v>
+        <v>-17.16</v>
       </c>
       <c r="AC12">
-        <v>8.220000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="AD12">
-        <v>7.59</v>
+        <v>6.44</v>
       </c>
       <c r="AE12">
-        <v>63.11</v>
+        <v>60.73</v>
       </c>
       <c r="AF12">
-        <v>-24.34</v>
+        <v>-40.84</v>
       </c>
       <c r="AG12">
-        <v>2421.82</v>
+        <v>2424.32</v>
       </c>
       <c r="AH12">
-        <v>2057.91</v>
+        <v>2037.11</v>
       </c>
       <c r="AI12">
-        <v>2280.24</v>
+        <v>2264.2</v>
       </c>
       <c r="AJ12" t="s">
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>35.8</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2202,10 +2212,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4880</v>
+        <v>4832.5</v>
       </c>
       <c r="D13">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2214,46 +2224,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-5.59</v>
+        <v>-6.51</v>
       </c>
       <c r="H13">
-        <v>46.67</v>
+        <v>45.24</v>
       </c>
       <c r="I13">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="J13">
-        <v>-3.92</v>
+        <v>-5.7</v>
       </c>
       <c r="K13">
-        <v>12.86</v>
+        <v>12.61</v>
       </c>
       <c r="L13">
-        <v>38.98</v>
+        <v>39.38</v>
       </c>
       <c r="M13">
-        <v>18.62</v>
+        <v>18.53</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P13">
-        <v>4864.6</v>
+        <v>4862.9</v>
       </c>
       <c r="Q13">
-        <v>4989.34</v>
+        <v>4975.97</v>
       </c>
       <c r="R13">
-        <v>4939.35</v>
+        <v>4944.41</v>
       </c>
       <c r="S13">
-        <v>4381.69</v>
+        <v>4386.79</v>
       </c>
       <c r="T13">
-        <v>11.37</v>
+        <v>10.16</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2268,34 +2278,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>44.1</v>
+        <v>40.75</v>
       </c>
       <c r="Z13">
-        <v>-26.5</v>
+        <v>-31.73</v>
       </c>
       <c r="AA13">
-        <v>-3.95</v>
+        <v>-9.5</v>
       </c>
       <c r="AB13">
-        <v>-22.55</v>
+        <v>-22.23</v>
       </c>
       <c r="AC13">
-        <v>47.02</v>
+        <v>46.75</v>
       </c>
       <c r="AD13">
-        <v>29.86</v>
+        <v>41.25</v>
       </c>
       <c r="AE13">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AF13">
-        <v>35.65</v>
+        <v>-14.85</v>
       </c>
       <c r="AG13">
-        <v>5197.71</v>
+        <v>5188.73</v>
       </c>
       <c r="AH13">
-        <v>4780.98</v>
+        <v>4763.21</v>
       </c>
       <c r="AI13">
         <v>5062.11</v>
@@ -2304,7 +2314,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>44.5</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2315,58 +2325,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2774</v>
+        <v>2700</v>
       </c>
       <c r="D14">
-        <v>-0.32</v>
+        <v>-2.67</v>
       </c>
       <c r="E14">
-        <v>5072.5</v>
+        <v>5003.11</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-45.31</v>
+        <v>-46.03</v>
       </c>
       <c r="H14">
-        <v>26.44</v>
+        <v>23.07</v>
       </c>
       <c r="I14">
-        <v>0.16</v>
+        <v>-3.19</v>
       </c>
       <c r="J14">
-        <v>-4.51</v>
+        <v>-7.85</v>
       </c>
       <c r="K14">
-        <v>-14.57</v>
+        <v>-16.05</v>
       </c>
       <c r="L14">
-        <v>-45.99</v>
+        <v>-46.77</v>
       </c>
       <c r="M14">
-        <v>22.59</v>
+        <v>22.4</v>
       </c>
       <c r="N14">
         <v>13</v>
       </c>
       <c r="O14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>2797.08</v>
+        <v>2779.28</v>
       </c>
       <c r="Q14">
-        <v>2823.74</v>
+        <v>2813.33</v>
       </c>
       <c r="R14">
-        <v>2906.77</v>
+        <v>2903.42</v>
       </c>
       <c r="S14">
-        <v>2899.85</v>
+        <v>2892.46</v>
       </c>
       <c r="T14">
-        <v>-4.34</v>
+        <v>-6.65</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2381,43 +2391,43 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>39.32</v>
+        <v>32.3</v>
       </c>
       <c r="Z14">
-        <v>-40.27</v>
+        <v>-45.59</v>
       </c>
       <c r="AA14">
-        <v>-42.23</v>
+        <v>-42.9</v>
       </c>
       <c r="AB14">
-        <v>1.96</v>
+        <v>-2.69</v>
       </c>
       <c r="AC14">
-        <v>75.09</v>
+        <v>49.58</v>
       </c>
       <c r="AD14">
-        <v>84.98</v>
+        <v>70.72</v>
       </c>
       <c r="AE14">
-        <v>58.08</v>
+        <v>59.22</v>
       </c>
       <c r="AF14">
-        <v>30.51</v>
+        <v>-15.54</v>
       </c>
       <c r="AG14">
-        <v>2915.65</v>
+        <v>2911.89</v>
       </c>
       <c r="AH14">
-        <v>2731.83</v>
+        <v>2714.77</v>
       </c>
       <c r="AI14">
-        <v>2944.37</v>
+        <v>2911.37</v>
       </c>
       <c r="AJ14" t="s">
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>41.55</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2428,10 +2438,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>216.31</v>
+        <v>215.13</v>
       </c>
       <c r="D15">
-        <v>0.12</v>
+        <v>-0.55</v>
       </c>
       <c r="E15">
         <v>380.65</v>
@@ -2440,46 +2450,46 @@
         <v>213</v>
       </c>
       <c r="G15">
-        <v>-43.17</v>
+        <v>-43.48</v>
       </c>
       <c r="H15">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>1.09</v>
+        <v>-1.99</v>
       </c>
       <c r="J15">
-        <v>-5.95</v>
+        <v>-7.15</v>
       </c>
       <c r="K15">
-        <v>-12.77</v>
+        <v>-12.68</v>
       </c>
       <c r="L15">
-        <v>-42.54</v>
+        <v>-40.77</v>
       </c>
       <c r="M15">
-        <v>12.11</v>
+        <v>11.57</v>
       </c>
       <c r="N15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P15">
-        <v>216.71</v>
+        <v>215.84</v>
       </c>
       <c r="Q15">
-        <v>223.69</v>
+        <v>222.95</v>
       </c>
       <c r="R15">
-        <v>229.63</v>
+        <v>228.82</v>
       </c>
       <c r="S15">
-        <v>251.81</v>
+        <v>251.42</v>
       </c>
       <c r="T15">
-        <v>-14.1</v>
+        <v>-14.43</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2494,43 +2504,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>39.14</v>
+        <v>37.87</v>
       </c>
       <c r="Z15">
-        <v>-4.16</v>
+        <v>-4.2</v>
       </c>
       <c r="AA15">
-        <v>-3.37</v>
+        <v>-3.54</v>
       </c>
       <c r="AB15">
-        <v>-0.78</v>
+        <v>-0.66</v>
       </c>
       <c r="AC15">
-        <v>29.72</v>
+        <v>28.15</v>
       </c>
       <c r="AD15">
-        <v>29.29</v>
+        <v>28.44</v>
       </c>
       <c r="AE15">
-        <v>7.89</v>
+        <v>7.81</v>
       </c>
       <c r="AF15">
-        <v>-10.95</v>
+        <v>4.72</v>
       </c>
       <c r="AG15">
-        <v>237.5</v>
+        <v>236.93</v>
       </c>
       <c r="AH15">
-        <v>209.89</v>
+        <v>208.97</v>
       </c>
       <c r="AI15">
-        <v>239.5</v>
+        <v>239.07</v>
       </c>
       <c r="AJ15" t="s">
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>29.47</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2541,10 +2551,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>35.63</v>
+        <v>35.02</v>
       </c>
       <c r="D16">
-        <v>0.03</v>
+        <v>-1.71</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2553,46 +2563,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-39.28</v>
+        <v>-40.32</v>
       </c>
       <c r="H16">
-        <v>13.62</v>
+        <v>11.67</v>
       </c>
       <c r="I16">
-        <v>1.16</v>
+        <v>-4.42</v>
       </c>
       <c r="J16">
-        <v>-4.66</v>
+        <v>-6.74</v>
       </c>
       <c r="K16">
-        <v>-17.12</v>
+        <v>-18.14</v>
       </c>
       <c r="L16">
-        <v>-38.36</v>
+        <v>-39.31</v>
       </c>
       <c r="M16">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="N16">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>35.8</v>
+        <v>35.47</v>
       </c>
       <c r="Q16">
-        <v>36.79</v>
+        <v>36.67</v>
       </c>
       <c r="R16">
-        <v>38.23</v>
+        <v>38.11</v>
       </c>
       <c r="S16">
-        <v>42.16</v>
+        <v>42.09</v>
       </c>
       <c r="T16">
-        <v>-15.49</v>
+        <v>-16.8</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2607,43 +2617,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>39.64</v>
+        <v>36.29</v>
       </c>
       <c r="Z16">
-        <v>-0.83</v>
+        <v>-0.86</v>
       </c>
       <c r="AA16">
-        <v>-0.8</v>
+        <v>-0.82</v>
       </c>
       <c r="AB16">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AC16">
-        <v>52.07</v>
+        <v>55</v>
       </c>
       <c r="AD16">
-        <v>47.69</v>
+        <v>50.68</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>-72.76000000000001</v>
+        <v>-75.41</v>
       </c>
       <c r="AG16">
-        <v>39.22</v>
+        <v>39.21</v>
       </c>
       <c r="AH16">
-        <v>34.36</v>
+        <v>34.13</v>
       </c>
       <c r="AI16">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>17.42</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2654,10 +2664,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1130</v>
+        <v>1113.4</v>
       </c>
       <c r="D17">
-        <v>2.65</v>
+        <v>-1.47</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2666,46 +2676,46 @@
         <v>1100.8</v>
       </c>
       <c r="G17">
-        <v>-27.4</v>
+        <v>-28.46</v>
       </c>
       <c r="H17">
-        <v>2.65</v>
+        <v>1.14</v>
       </c>
       <c r="I17">
-        <v>-0.09</v>
+        <v>-1.9</v>
       </c>
       <c r="J17">
-        <v>-9.02</v>
+        <v>-10.43</v>
       </c>
       <c r="K17">
-        <v>-13.75</v>
+        <v>-14.51</v>
       </c>
       <c r="L17">
-        <v>-20.52</v>
+        <v>-21.34</v>
       </c>
       <c r="M17">
-        <v>-1.52</v>
+        <v>-1.5</v>
       </c>
       <c r="N17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="O17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P17">
-        <v>1123.76</v>
+        <v>1119.44</v>
       </c>
       <c r="Q17">
-        <v>1160.01</v>
+        <v>1154.83</v>
       </c>
       <c r="R17">
-        <v>1244.1</v>
+        <v>1238.82</v>
       </c>
       <c r="S17">
-        <v>1337.4</v>
+        <v>1336.35</v>
       </c>
       <c r="T17">
-        <v>-15.51</v>
+        <v>-16.68</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2720,34 +2730,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>40.07</v>
+        <v>37.49</v>
       </c>
       <c r="Z17">
-        <v>-34.53</v>
+        <v>-34.19</v>
       </c>
       <c r="AA17">
-        <v>-34.74</v>
+        <v>-34.63</v>
       </c>
       <c r="AB17">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="AC17">
-        <v>80.67</v>
+        <v>72.88</v>
       </c>
       <c r="AD17">
-        <v>62.72</v>
+        <v>68.44</v>
       </c>
       <c r="AE17">
-        <v>31.53</v>
+        <v>30.93</v>
       </c>
       <c r="AF17">
-        <v>7.92</v>
+        <v>-27.9</v>
       </c>
       <c r="AG17">
-        <v>1227.37</v>
+        <v>1219.62</v>
       </c>
       <c r="AH17">
-        <v>1092.64</v>
+        <v>1090.03</v>
       </c>
       <c r="AI17">
         <v>1205.69</v>
@@ -2756,7 +2766,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>37.51</v>
+        <v>38.48</v>
       </c>
     </row>
   </sheetData>
@@ -2897,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2937,7 +2947,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2957,7 +2967,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>64</v>
@@ -2975,931 +2985,934 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="D8" s="6">
-        <v>2.03</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.17</v>
+      <c r="C8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>11.59</v>
+        <v>2.03</v>
       </c>
       <c r="D9" s="6">
-        <v>11.52</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-0.16</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.82</v>
+        <v>11.52</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.12</v>
+        <v>7.29</v>
       </c>
       <c r="E10" s="7">
-        <v>0.7</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>7.54</v>
+        <v>-4.12</v>
       </c>
       <c r="D11" s="6">
-        <v>6.85</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-5.9</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>2.24</v>
+        <v>6.85</v>
       </c>
       <c r="D12" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.52</v>
+        <v>4.13</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.72</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.19</v>
+        <v>0.72</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.42</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.23</v>
+        <v>-1.76</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-13.16</v>
+        <v>-6.42</v>
       </c>
       <c r="D14" s="6">
-        <v>-12.56</v>
+        <v>-7</v>
       </c>
       <c r="E14" s="7">
-        <v>0.6</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>5.29</v>
+        <v>-12.56</v>
       </c>
       <c r="D15" s="6">
-        <v>4.39</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.9</v>
+        <v>-13.15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.95</v>
+        <v>4.39</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.2</v>
+        <v>2.17</v>
       </c>
       <c r="E16" s="7">
-        <v>0.75</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>1.08</v>
+        <v>-1.2</v>
       </c>
       <c r="D17" s="6">
-        <v>2.43</v>
+        <v>-1.93</v>
       </c>
       <c r="E17" s="7">
-        <v>1.35</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-8.56</v>
+        <v>2.43</v>
       </c>
       <c r="D18" s="6">
-        <v>-8.52</v>
+        <v>0.58</v>
       </c>
       <c r="E18" s="7">
-        <v>0.04</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.1</v>
+        <v>-8.52</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.92</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.82</v>
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.83</v>
+        <v>-3.92</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.51</v>
+        <v>-5.7</v>
       </c>
       <c r="E20" s="7">
-        <v>0.32</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-6.23</v>
+        <v>-4.51</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.95</v>
+        <v>-7.85</v>
       </c>
       <c r="E21" s="7">
-        <v>0.28</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.72</v>
+        <v>-5.95</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.66</v>
+        <v>-7.15</v>
       </c>
       <c r="E22" s="7">
-        <v>1.06</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-10.87</v>
+        <v>-4.66</v>
       </c>
       <c r="D23" s="6">
-        <v>-9.02</v>
+        <v>-6.74</v>
       </c>
       <c r="E23" s="7">
-        <v>1.85</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>2.97</v>
+        <v>-9.02</v>
       </c>
       <c r="D24" s="6">
-        <v>4.25</v>
+        <v>-10.43</v>
       </c>
       <c r="E24" s="7">
-        <v>1.28</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>9.460000000000001</v>
+        <v>4.25</v>
       </c>
       <c r="D25" s="6">
-        <v>8.82</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.64</v>
+        <v>0.3</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-3.95</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>0.5600000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="D26" s="6">
-        <v>-0.01</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.57</v>
+        <v>2.88</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.94</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-8.289999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="D27" s="6">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.17</v>
+        <v>-1.85</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-3.19</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="D28" s="6">
-        <v>-5.49</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.3</v>
+        <v>-16.31</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-7.85</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.2</v>
+        <v>-5.49</v>
       </c>
       <c r="D29" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.38</v>
+        <v>-6.79</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-6.4</v>
+        <v>-0.58</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.77</v>
+        <v>-2.7</v>
       </c>
       <c r="E30" s="7">
-        <v>1.63</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-5.03</v>
+        <v>-4.77</v>
       </c>
       <c r="D31" s="6">
-        <v>-1.12</v>
+        <v>-5.85</v>
       </c>
       <c r="E31" s="7">
-        <v>3.91</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>1.1</v>
+        <v>-1.12</v>
       </c>
       <c r="D32" s="6">
-        <v>2.39</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="E32" s="7">
-        <v>1.29</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>0.72</v>
+        <v>2.39</v>
       </c>
       <c r="D33" s="6">
-        <v>4.27</v>
+        <v>-1.5</v>
       </c>
       <c r="E33" s="7">
-        <v>3.55</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-6.49</v>
+        <v>4.27</v>
       </c>
       <c r="D34" s="6">
-        <v>-4.53</v>
+        <v>0.39</v>
       </c>
       <c r="E34" s="7">
-        <v>1.96</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>1.49</v>
+        <v>-4.53</v>
       </c>
       <c r="D35" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2.07</v>
+        <v>-4.7</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>1.94</v>
+        <v>-0.58</v>
       </c>
       <c r="D36" s="6">
-        <v>0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="E36" s="8">
-        <v>-1.78</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>1.44</v>
+        <v>0.16</v>
       </c>
       <c r="D37" s="6">
-        <v>1.09</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.35</v>
+        <v>-3.19</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.47</v>
+        <v>1.09</v>
       </c>
       <c r="D38" s="6">
-        <v>1.16</v>
+        <v>-1.99</v>
       </c>
       <c r="E38" s="7">
-        <v>2.63</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-3.18</v>
+        <v>1.16</v>
       </c>
       <c r="D39" s="6">
-        <v>-0.09</v>
+        <v>-4.42</v>
       </c>
       <c r="E39" s="7">
-        <v>3.09</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>-5.64</v>
+        <v>-0.09</v>
       </c>
       <c r="D40" s="6">
-        <v>-4.9</v>
+        <v>-1.9</v>
       </c>
       <c r="E40" s="7">
-        <v>0.74</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>19.5</v>
+        <v>-4.9</v>
       </c>
       <c r="D41" s="6">
-        <v>12.17</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-7.33</v>
+        <v>-6.03</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>-39.5</v>
+        <v>12.17</v>
       </c>
       <c r="D42" s="6">
-        <v>-39.6</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.1</v>
+        <v>9.220000000000001</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-31.91</v>
+        <v>-39.6</v>
       </c>
       <c r="D43" s="6">
-        <v>-31.24</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.67</v>
+        <v>-39.55</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-0.04</v>
+        <v>-31.24</v>
       </c>
       <c r="D44" s="6">
-        <v>1.01</v>
+        <v>-33.35</v>
       </c>
       <c r="E44" s="7">
-        <v>1.05</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-12.66</v>
+        <v>1.01</v>
       </c>
       <c r="D45" s="6">
-        <v>-11.21</v>
+        <v>-0.85</v>
       </c>
       <c r="E45" s="7">
-        <v>1.45</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-42.32</v>
+        <v>-11.21</v>
       </c>
       <c r="D46" s="6">
-        <v>-42.97</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.65</v>
+        <v>-11.73</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-2.61</v>
+        <v>-42.97</v>
       </c>
       <c r="D47" s="6">
-        <v>-9.66</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-7.05</v>
+        <v>-43.37</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-7.01</v>
+        <v>-9.66</v>
       </c>
       <c r="D48" s="6">
-        <v>-6.13</v>
+        <v>-9.76</v>
       </c>
       <c r="E48" s="7">
-        <v>0.88</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>10.17</v>
+        <v>-6.13</v>
       </c>
       <c r="D49" s="6">
-        <v>13.21</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="E49" s="7">
-        <v>3.04</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-31.28</v>
+        <v>13.21</v>
       </c>
       <c r="D50" s="6">
-        <v>-31.86</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.58</v>
+        <v>11.9</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>39.89</v>
+        <v>-31.86</v>
       </c>
       <c r="D51" s="6">
-        <v>38.98</v>
+        <v>-31.79</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.91</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-46.38</v>
+        <v>38.98</v>
       </c>
       <c r="D52" s="6">
-        <v>-45.99</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.39</v>
+        <v>39.38</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-44.99</v>
+        <v>-45.99</v>
       </c>
       <c r="D53" s="6">
-        <v>-42.54</v>
+        <v>-46.77</v>
       </c>
       <c r="E53" s="7">
-        <v>2.45</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-38.93</v>
+        <v>-42.54</v>
       </c>
       <c r="D54" s="6">
-        <v>-38.36</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.57</v>
+        <v>-40.77</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1.77</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-21.79</v>
+        <v>-38.36</v>
       </c>
       <c r="D55" s="6">
-        <v>-20.52</v>
+        <v>-39.31</v>
       </c>
       <c r="E55" s="7">
-        <v>1.27</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>1.68</v>
+        <v>-20.52</v>
       </c>
       <c r="D56" s="6">
-        <v>2.51</v>
+        <v>-21.34</v>
       </c>
       <c r="E56" s="7">
-        <v>0.83</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>14.87</v>
+        <v>2.51</v>
       </c>
       <c r="D57" s="6">
-        <v>18.03</v>
+        <v>1.13</v>
       </c>
       <c r="E57" s="7">
-        <v>3.16</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-11.64</v>
+        <v>18.03</v>
       </c>
       <c r="D58" s="6">
-        <v>-12.03</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.39</v>
+        <v>15.06</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-2.97</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-7.75</v>
+        <v>-12.03</v>
       </c>
       <c r="D59" s="6">
-        <v>-8.02</v>
+        <v>-11.94</v>
       </c>
       <c r="E59" s="8">
-        <v>-0.27</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-16.35</v>
+        <v>-8.02</v>
       </c>
       <c r="D60" s="6">
-        <v>-16.16</v>
+        <v>-12.6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.19</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3910,13 +3923,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-10.84</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="D61" s="6">
-        <v>-9.449999999999999</v>
+        <v>-12.82</v>
       </c>
       <c r="E61" s="7">
-        <v>1.39</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3927,13 +3940,13 @@
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-21</v>
+        <v>-20.21</v>
       </c>
       <c r="D62" s="6">
-        <v>-20.21</v>
+        <v>-20.96</v>
       </c>
       <c r="E62" s="7">
-        <v>0.79</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3944,13 +3957,13 @@
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="D63" s="6">
-        <v>0.61</v>
+        <v>-3.02</v>
       </c>
       <c r="E63" s="7">
-        <v>0.13</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3961,13 +3974,13 @@
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-7.86</v>
+        <v>-6.13</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.13</v>
+        <v>-6.56</v>
       </c>
       <c r="E64" s="7">
-        <v>1.73</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3978,13 +3991,13 @@
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-4.44</v>
+        <v>0.35</v>
       </c>
       <c r="D65" s="6">
-        <v>0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="E65" s="7">
-        <v>4.79</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3995,13 +4008,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>2.2</v>
+        <v>-0.92</v>
       </c>
       <c r="D66" s="6">
-        <v>-0.92</v>
+        <v>-0.37</v>
       </c>
       <c r="E66" s="8">
-        <v>-3.12</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4012,13 +4025,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>14.48</v>
+        <v>12.86</v>
       </c>
       <c r="D67" s="6">
-        <v>12.86</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-1.62</v>
+        <v>12.61</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4029,13 +4042,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-11.45</v>
+        <v>-14.57</v>
       </c>
       <c r="D68" s="6">
-        <v>-14.57</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-3.12</v>
+        <v>-16.05</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4046,13 +4059,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-13.77</v>
+        <v>-12.77</v>
       </c>
       <c r="D69" s="6">
-        <v>-12.77</v>
-      </c>
-      <c r="E69" s="7">
-        <v>1</v>
+        <v>-12.68</v>
+      </c>
+      <c r="E69" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4063,13 +4076,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-18.1</v>
+        <v>-17.12</v>
       </c>
       <c r="D70" s="6">
-        <v>-17.12</v>
+        <v>-18.14</v>
       </c>
       <c r="E70" s="7">
-        <v>0.98</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4080,13 +4093,13 @@
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-17.07</v>
+        <v>-13.75</v>
       </c>
       <c r="D71" s="6">
-        <v>-13.75</v>
+        <v>-14.51</v>
       </c>
       <c r="E71" s="7">
-        <v>3.32</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4097,13 +4110,13 @@
         <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-5.86</v>
+        <v>-4.11</v>
       </c>
       <c r="D72" s="6">
-        <v>-4.11</v>
+        <v>-5.28</v>
       </c>
       <c r="E72" s="7">
-        <v>1.75</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4114,13 +4127,13 @@
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-6.45</v>
+        <v>-5.62</v>
       </c>
       <c r="D73" s="6">
-        <v>-5.62</v>
+        <v>-8.18</v>
       </c>
       <c r="E73" s="7">
-        <v>0.83</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4131,13 +4144,13 @@
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-39.8</v>
+        <v>-38.87</v>
       </c>
       <c r="D74" s="6">
-        <v>-38.87</v>
-      </c>
-      <c r="E74" s="7">
-        <v>0.93</v>
+        <v>-38.23</v>
+      </c>
+      <c r="E74" s="8">
+        <v>0.64</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4148,13 +4161,13 @@
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-31.12</v>
+        <v>-31.54</v>
       </c>
       <c r="D75" s="6">
-        <v>-31.54</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-0.42</v>
+        <v>-32.01</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4165,13 +4178,13 @@
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-17.91</v>
+        <v>-17.51</v>
       </c>
       <c r="D76" s="6">
-        <v>-17.51</v>
+        <v>-19</v>
       </c>
       <c r="E76" s="7">
-        <v>0.4</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4182,13 +4195,13 @@
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-21.92</v>
+        <v>-21.11</v>
       </c>
       <c r="D77" s="6">
-        <v>-21.11</v>
+        <v>-21.74</v>
       </c>
       <c r="E77" s="7">
-        <v>0.8100000000000001</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4199,13 +4212,13 @@
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-44</v>
+        <v>-44.14</v>
       </c>
       <c r="D78" s="6">
-        <v>-44.14</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-0.14</v>
+        <v>-44.63</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4216,13 +4229,13 @@
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-35.18</v>
+        <v>-35.94</v>
       </c>
       <c r="D79" s="6">
-        <v>-35.94</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.76</v>
+        <v>-37.45</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4233,13 +4246,13 @@
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-20.53</v>
+        <v>-20.1</v>
       </c>
       <c r="D80" s="6">
-        <v>-20.1</v>
+        <v>-21.3</v>
       </c>
       <c r="E80" s="7">
-        <v>0.43</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4250,13 +4263,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-14.63</v>
+        <v>-11.93</v>
       </c>
       <c r="D81" s="6">
-        <v>-11.93</v>
+        <v>-13.22</v>
       </c>
       <c r="E81" s="7">
-        <v>2.7</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4267,13 +4280,13 @@
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-34.66</v>
+        <v>-35.14</v>
       </c>
       <c r="D82" s="6">
-        <v>-35.14</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-0.48</v>
+        <v>-35.22</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4284,13 +4297,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-4.66</v>
+        <v>-5.59</v>
       </c>
       <c r="D83" s="6">
-        <v>-5.59</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.93</v>
+        <v>-6.51</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4301,13 +4314,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-45.82</v>
+        <v>-45.31</v>
       </c>
       <c r="D84" s="6">
-        <v>-45.31</v>
+        <v>-46.03</v>
       </c>
       <c r="E84" s="7">
-        <v>0.51</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4318,13 +4331,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-43.24</v>
+        <v>-43.17</v>
       </c>
       <c r="D85" s="6">
-        <v>-43.17</v>
+        <v>-43.48</v>
       </c>
       <c r="E85" s="7">
-        <v>0.07000000000000001</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4335,13 +4348,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-39.3</v>
+        <v>-39.28</v>
       </c>
       <c r="D86" s="6">
-        <v>-39.28</v>
+        <v>-40.32</v>
       </c>
       <c r="E86" s="7">
-        <v>0.02</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4352,13 +4365,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-29.27</v>
+        <v>-27.4</v>
       </c>
       <c r="D87" s="6">
-        <v>-27.4</v>
+        <v>-28.46</v>
       </c>
       <c r="E87" s="7">
-        <v>1.87</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4369,13 +4382,13 @@
         <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>736.25</v>
+        <v>743.7</v>
       </c>
       <c r="D88" s="6">
-        <v>743.7</v>
+        <v>728.8</v>
       </c>
       <c r="E88" s="7">
-        <v>7.45</v>
+        <v>-14.9</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4386,13 +4399,13 @@
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>1011.75</v>
+        <v>1020.75</v>
       </c>
       <c r="D89" s="6">
-        <v>1020.75</v>
+        <v>993.05</v>
       </c>
       <c r="E89" s="7">
-        <v>9</v>
+        <v>-27.7</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4403,13 +4416,13 @@
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>201.95</v>
+        <v>202.62</v>
       </c>
       <c r="D90" s="6">
-        <v>202.62</v>
+        <v>200.36</v>
       </c>
       <c r="E90" s="7">
-        <v>0.67</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4420,13 +4433,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>674</v>
+        <v>669.9</v>
       </c>
       <c r="D91" s="6">
-        <v>669.9</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-4.1</v>
+        <v>652.2</v>
+      </c>
+      <c r="E91" s="7">
+        <v>-17.7</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4437,13 +4450,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>1692.4</v>
+        <v>1700.6</v>
       </c>
       <c r="D92" s="6">
-        <v>1700.6</v>
+        <v>1670</v>
       </c>
       <c r="E92" s="7">
-        <v>8.199999999999999</v>
+        <v>-30.6</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4454,13 +4467,13 @@
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>984.1</v>
+        <v>994.3</v>
       </c>
       <c r="D93" s="6">
-        <v>994.3</v>
+        <v>986.3</v>
       </c>
       <c r="E93" s="7">
-        <v>10.2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4471,13 +4484,13 @@
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>3220</v>
+        <v>3212</v>
       </c>
       <c r="D94" s="6">
-        <v>3212</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-8</v>
+        <v>3183.8</v>
+      </c>
+      <c r="E94" s="7">
+        <v>-28.2</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4488,13 +4501,13 @@
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>682.25</v>
+        <v>674.3</v>
       </c>
       <c r="D95" s="6">
-        <v>674.3</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-7.95</v>
+        <v>658.35</v>
+      </c>
+      <c r="E95" s="7">
+        <v>-15.95</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4505,13 +4518,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D96" s="6">
-        <v>369</v>
+        <v>363.45</v>
       </c>
       <c r="E96" s="7">
-        <v>2</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4522,13 +4535,13 @@
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>184.97</v>
+        <v>190.82</v>
       </c>
       <c r="D97" s="6">
-        <v>190.82</v>
+        <v>188.02</v>
       </c>
       <c r="E97" s="7">
-        <v>5.85</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4539,13 +4552,13 @@
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>2105</v>
+        <v>2089.6</v>
       </c>
       <c r="D98" s="6">
-        <v>2089.6</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-15.4</v>
+        <v>2087</v>
+      </c>
+      <c r="E98" s="7">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4556,13 +4569,13 @@
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>4928.5</v>
+        <v>4880</v>
       </c>
       <c r="D99" s="6">
-        <v>4880</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-48.5</v>
+        <v>4832.5</v>
+      </c>
+      <c r="E99" s="7">
+        <v>-47.5</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4573,13 +4586,13 @@
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>2782.9</v>
+        <v>2774</v>
       </c>
       <c r="D100" s="6">
-        <v>2774</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-8.9</v>
+        <v>2700</v>
+      </c>
+      <c r="E100" s="7">
+        <v>-74</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4590,13 +4603,13 @@
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>216.06</v>
+        <v>216.31</v>
       </c>
       <c r="D101" s="6">
-        <v>216.31</v>
+        <v>215.13</v>
       </c>
       <c r="E101" s="7">
-        <v>0.25</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4607,13 +4620,13 @@
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>35.62</v>
+        <v>35.63</v>
       </c>
       <c r="D102" s="6">
-        <v>35.63</v>
+        <v>35.02</v>
       </c>
       <c r="E102" s="7">
-        <v>0.01</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4624,35 +4637,35 @@
         <v>2</v>
       </c>
       <c r="C103" s="6">
-        <v>1100.8</v>
+        <v>1130</v>
       </c>
       <c r="D103" s="6">
-        <v>1130</v>
+        <v>1113.4</v>
       </c>
       <c r="E103" s="7">
-        <v>29.2</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C104" s="6">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D104" s="6">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E104" s="7">
-        <v>7</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>13</v>
@@ -4663,660 +4676,609 @@
       <c r="D105" s="6">
         <v>50</v>
       </c>
-      <c r="E105" s="7">
+      <c r="E105" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D106" s="6">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="E106" s="8">
-        <v>-6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="D107" s="6">
-        <v>74</v>
-      </c>
-      <c r="E107" s="8">
+        <v>19</v>
+      </c>
+      <c r="E107" s="7">
         <v>-7</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D108" s="6">
-        <v>68</v>
-      </c>
-      <c r="E108" s="7">
+        <v>44</v>
+      </c>
+      <c r="E108" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C109" s="6">
-        <v>50</v>
+        <v>58.78</v>
       </c>
       <c r="D109" s="6">
-        <v>44</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-6</v>
+        <v>50.83</v>
+      </c>
+      <c r="E109" s="7">
+        <v>-7.95</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C110" s="6">
-        <v>19</v>
+        <v>60.42</v>
       </c>
       <c r="D110" s="6">
-        <v>13</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-6</v>
+        <v>55.13</v>
+      </c>
+      <c r="E110" s="7">
+        <v>-5.29</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C111" s="6">
-        <v>13</v>
+        <v>36.21</v>
       </c>
       <c r="D111" s="6">
-        <v>19</v>
+        <v>31.95</v>
       </c>
       <c r="E111" s="7">
-        <v>6</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>55.55</v>
+        <v>50.64</v>
       </c>
       <c r="D112" s="6">
-        <v>58.78</v>
+        <v>47.27</v>
       </c>
       <c r="E112" s="7">
-        <v>3.23</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>59.24</v>
+        <v>43.16</v>
       </c>
       <c r="D113" s="6">
-        <v>60.42</v>
+        <v>39.11</v>
       </c>
       <c r="E113" s="7">
-        <v>1.18</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>33.78</v>
+        <v>39.39</v>
       </c>
       <c r="D114" s="6">
-        <v>36.21</v>
+        <v>37.15</v>
       </c>
       <c r="E114" s="7">
-        <v>2.43</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>51.42</v>
+        <v>27.26</v>
       </c>
       <c r="D115" s="6">
-        <v>50.64</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-0.78</v>
+        <v>25.99</v>
+      </c>
+      <c r="E115" s="7">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>41.66</v>
+        <v>52.66</v>
       </c>
       <c r="D116" s="6">
-        <v>43.16</v>
+        <v>48.41</v>
       </c>
       <c r="E116" s="7">
-        <v>1.5</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>34.72</v>
+        <v>50.7</v>
       </c>
       <c r="D117" s="6">
-        <v>39.39</v>
+        <v>45.31</v>
       </c>
       <c r="E117" s="7">
-        <v>4.67</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>27.62</v>
+        <v>58.32</v>
       </c>
       <c r="D118" s="6">
-        <v>27.26</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-0.36</v>
+        <v>53.17</v>
+      </c>
+      <c r="E118" s="7">
+        <v>-5.15</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>54.89</v>
+        <v>32.86</v>
       </c>
       <c r="D119" s="6">
-        <v>52.66</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-2.23</v>
+        <v>32.65</v>
+      </c>
+      <c r="E119" s="7">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>48.65</v>
+        <v>44.1</v>
       </c>
       <c r="D120" s="6">
-        <v>50.7</v>
+        <v>40.75</v>
       </c>
       <c r="E120" s="7">
-        <v>2.05</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>48.67</v>
+        <v>39.32</v>
       </c>
       <c r="D121" s="6">
-        <v>58.32</v>
+        <v>32.3</v>
       </c>
       <c r="E121" s="7">
-        <v>9.65</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>34.04</v>
+        <v>39.14</v>
       </c>
       <c r="D122" s="6">
-        <v>32.86</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-1.18</v>
+        <v>37.87</v>
+      </c>
+      <c r="E122" s="7">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>47.82</v>
+        <v>39.64</v>
       </c>
       <c r="D123" s="6">
-        <v>44.1</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-3.72</v>
+        <v>36.29</v>
+      </c>
+      <c r="E123" s="7">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>40.3</v>
+        <v>40.07</v>
       </c>
       <c r="D124" s="6">
-        <v>39.32</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-0.98</v>
+        <v>37.49</v>
+      </c>
+      <c r="E124" s="7">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C125" s="6">
-        <v>38.74</v>
+        <v>-26.52</v>
       </c>
       <c r="D125" s="6">
-        <v>39.14</v>
+        <v>-35.84</v>
       </c>
       <c r="E125" s="7">
-        <v>0.4</v>
+        <v>-9.32</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C126" s="6">
-        <v>39.56</v>
+        <v>55.75</v>
       </c>
       <c r="D126" s="6">
-        <v>39.64</v>
+        <v>-47.21</v>
       </c>
       <c r="E126" s="7">
-        <v>0.08</v>
+        <v>-102.96</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C127" s="6">
-        <v>32.49</v>
+        <v>-57.16</v>
       </c>
       <c r="D127" s="6">
-        <v>40.07</v>
-      </c>
-      <c r="E127" s="7">
-        <v>7.58</v>
+        <v>-16.44</v>
+      </c>
+      <c r="E127" s="8">
+        <v>40.72</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>-27.69</v>
+        <v>-64.14</v>
       </c>
       <c r="D128" s="6">
-        <v>-26.52</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="E128" s="7">
-        <v>1.17</v>
+        <v>-12.82</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>33.71</v>
+        <v>-43.3</v>
       </c>
       <c r="D129" s="6">
-        <v>55.75</v>
+        <v>-59.44</v>
       </c>
       <c r="E129" s="7">
-        <v>22.04</v>
+        <v>-16.14</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>-15.64</v>
+        <v>-25.8</v>
       </c>
       <c r="D130" s="6">
-        <v>-57.16</v>
+        <v>-11.71</v>
       </c>
       <c r="E130" s="8">
-        <v>-41.52</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>-50.96</v>
+        <v>-23.71</v>
       </c>
       <c r="D131" s="6">
-        <v>-64.14</v>
+        <v>6.62</v>
       </c>
       <c r="E131" s="8">
-        <v>-13.18</v>
+        <v>30.33</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>-51.08</v>
+        <v>-83.44</v>
       </c>
       <c r="D132" s="6">
-        <v>-43.3</v>
+        <v>-85.69</v>
       </c>
       <c r="E132" s="7">
-        <v>7.78</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>-41.5</v>
+        <v>-72.62</v>
       </c>
       <c r="D133" s="6">
-        <v>-25.8</v>
-      </c>
-      <c r="E133" s="7">
-        <v>15.7</v>
+        <v>-46.51</v>
+      </c>
+      <c r="E133" s="8">
+        <v>26.11</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>173.16</v>
+        <v>32.26</v>
       </c>
       <c r="D134" s="6">
-        <v>-23.71</v>
-      </c>
-      <c r="E134" s="8">
-        <v>-196.87</v>
+        <v>-48.15</v>
+      </c>
+      <c r="E134" s="7">
+        <v>-80.41</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>-67.31999999999999</v>
+        <v>-24.34</v>
       </c>
       <c r="D135" s="6">
-        <v>-83.44</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-16.12</v>
+        <v>-40.84</v>
+      </c>
+      <c r="E135" s="7">
+        <v>-16.5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-51.99</v>
+        <v>35.65</v>
       </c>
       <c r="D136" s="6">
-        <v>-72.62</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-20.63</v>
+        <v>-14.85</v>
+      </c>
+      <c r="E136" s="7">
+        <v>-50.5</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>-42.56</v>
+        <v>30.51</v>
       </c>
       <c r="D137" s="6">
-        <v>32.26</v>
+        <v>-15.54</v>
       </c>
       <c r="E137" s="7">
-        <v>74.81999999999999</v>
+        <v>-46.05</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>26.97</v>
+        <v>-10.95</v>
       </c>
       <c r="D138" s="6">
-        <v>-24.34</v>
+        <v>4.72</v>
       </c>
       <c r="E138" s="8">
-        <v>-51.31</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>135.7</v>
+        <v>-72.76000000000001</v>
       </c>
       <c r="D139" s="6">
-        <v>35.65</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-100.05</v>
+        <v>-75.41</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="6">
-        <v>20.9</v>
+        <v>7.92</v>
       </c>
       <c r="D140" s="6">
-        <v>30.51</v>
+        <v>-27.9</v>
       </c>
       <c r="E140" s="7">
-        <v>9.609999999999999</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C141" s="6">
-        <v>-59.62</v>
-      </c>
-      <c r="D141" s="6">
-        <v>-10.95</v>
-      </c>
-      <c r="E141" s="7">
-        <v>48.67</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C142" s="6">
-        <v>-70.22</v>
-      </c>
-      <c r="D142" s="6">
-        <v>-72.76000000000001</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C143" s="6">
-        <v>54.14</v>
-      </c>
-      <c r="D143" s="6">
-        <v>7.92</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-46.22</v>
+        <v>-35.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5340,28 +5302,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5375,16 +5337,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>44.5</v>
+        <v>40.7</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.1</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-6</v>
+        <v>-7.3</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5507,13 +5469,13 @@
         <v>48</v>
       </c>
       <c r="F1" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>41</v>
@@ -5524,34 +5486,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.4118</v>
+        <v>0.4048</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3333</v>
+        <v>0.3355</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2259</v>
+        <v>0.224</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2144</v>
+        <v>0.2185</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1862</v>
+        <v>0.1853</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1285</v>
+        <v>0.1157</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1211</v>
+        <v>0.1138</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1091</v>
+        <v>0.1114</v>
       </c>
       <c r="I2" s="14">
         <v>0.043</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0403</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5576,22 +5538,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0021</v>
+        <v>-0.0005</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0152</v>
+        <v>-0.015</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0321</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0564</v>
+        <v>-0.0583</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.0917</v>
+        <v>-0.092</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1</v>
+        <v>-0.1059</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,34 +217,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.6 → 47.3</t>
+    <t>50.8 → 49.9</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>47.3</t>
-  </si>
-  <si>
-    <t>52.7 → 48.4</t>
-  </si>
-  <si>
-    <t>52.7</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>50.7 → 45.3</t>
-  </si>
-  <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>45.3</t>
+    <t>50.8</t>
+  </si>
+  <si>
+    <t>49.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -456,8 +438,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -836,7 +818,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -969,58 +951,58 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>728.8</v>
+        <v>726.8</v>
       </c>
       <c r="D2">
-        <v>-2</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
-        <v>769.4</v>
+        <v>752.3</v>
       </c>
       <c r="F2">
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-5.28</v>
+        <v>-3.39</v>
       </c>
       <c r="H2">
-        <v>27.65</v>
+        <v>27.3</v>
       </c>
       <c r="I2">
-        <v>0.3</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J2">
-        <v>-0.16</v>
+        <v>0.8</v>
       </c>
       <c r="K2">
-        <v>1.13</v>
+        <v>2.79</v>
       </c>
       <c r="L2">
-        <v>-6.03</v>
+        <v>-5.54</v>
       </c>
       <c r="M2">
-        <v>33.55</v>
+        <v>31.99</v>
       </c>
       <c r="N2">
         <v>81</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>737.3</v>
+        <v>736.11</v>
       </c>
       <c r="Q2">
-        <v>724.76</v>
+        <v>725.1799999999999</v>
       </c>
       <c r="R2">
-        <v>728.37</v>
+        <v>728.28</v>
       </c>
       <c r="S2">
-        <v>688.3</v>
+        <v>688.34</v>
       </c>
       <c r="T2">
-        <v>5.88</v>
+        <v>5.59</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1035,34 +1017,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>50.83</v>
+        <v>49.85</v>
       </c>
       <c r="Z2">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="AA2">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
       <c r="AB2">
-        <v>2.01</v>
+        <v>1.27</v>
       </c>
       <c r="AC2">
-        <v>64.67</v>
+        <v>52.87</v>
       </c>
       <c r="AD2">
-        <v>78.95</v>
+        <v>67.58</v>
       </c>
       <c r="AE2">
-        <v>15.25</v>
+        <v>14.82</v>
       </c>
       <c r="AF2">
-        <v>-35.84</v>
+        <v>-13.77</v>
       </c>
       <c r="AG2">
-        <v>745.8200000000001</v>
+        <v>746.05</v>
       </c>
       <c r="AH2">
-        <v>703.7</v>
+        <v>704.3099999999999</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1071,7 +1053,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>29.33</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1082,10 +1064,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>993.05</v>
+        <v>976.5</v>
       </c>
       <c r="D3">
-        <v>-2.71</v>
+        <v>-1.67</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1094,46 +1076,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-8.18</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="H3">
-        <v>96.5</v>
+        <v>93.23</v>
       </c>
       <c r="I3">
-        <v>2.88</v>
+        <v>-3.49</v>
       </c>
       <c r="J3">
-        <v>7.29</v>
+        <v>4.33</v>
       </c>
       <c r="K3">
-        <v>15.06</v>
+        <v>9.81</v>
       </c>
       <c r="L3">
-        <v>9.220000000000001</v>
+        <v>11.45</v>
       </c>
       <c r="M3">
-        <v>11.14</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N3">
         <v>93</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>1004.75</v>
+        <v>997.6799999999999</v>
       </c>
       <c r="Q3">
-        <v>958.64</v>
+        <v>959.45</v>
       </c>
       <c r="R3">
-        <v>956.13</v>
+        <v>958.34</v>
       </c>
       <c r="S3">
-        <v>761.8200000000001</v>
+        <v>762.8200000000001</v>
       </c>
       <c r="T3">
-        <v>30.35</v>
+        <v>28.01</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1148,34 +1130,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>55.13</v>
+        <v>52.19</v>
       </c>
       <c r="Z3">
-        <v>14.85</v>
+        <v>13.58</v>
       </c>
       <c r="AA3">
-        <v>7.82</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AB3">
-        <v>7.03</v>
+        <v>4.61</v>
       </c>
       <c r="AC3">
-        <v>85.73999999999999</v>
+        <v>68.47</v>
       </c>
       <c r="AD3">
-        <v>86.73999999999999</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="AE3">
-        <v>45.21</v>
+        <v>44.17</v>
       </c>
       <c r="AF3">
-        <v>-47.21</v>
+        <v>-62.82</v>
       </c>
       <c r="AG3">
-        <v>1022.68</v>
+        <v>1023.99</v>
       </c>
       <c r="AH3">
-        <v>894.6</v>
+        <v>894.91</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1184,7 +1166,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>27.91</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1195,10 +1177,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>200.36</v>
+        <v>200.38</v>
       </c>
       <c r="D4">
-        <v>-1.12</v>
+        <v>0.01</v>
       </c>
       <c r="E4">
         <v>324.39</v>
@@ -1210,43 +1192,43 @@
         <v>-38.23</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I4">
-        <v>-1.85</v>
+        <v>-1.68</v>
       </c>
       <c r="J4">
-        <v>-5.9</v>
+        <v>-6.33</v>
       </c>
       <c r="K4">
-        <v>-11.94</v>
+        <v>-10.78</v>
       </c>
       <c r="L4">
-        <v>-39.55</v>
+        <v>-38</v>
       </c>
       <c r="M4">
-        <v>-5.83</v>
+        <v>-5.76</v>
       </c>
       <c r="N4">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>202.18</v>
+        <v>201.49</v>
       </c>
       <c r="Q4">
-        <v>205.07</v>
+        <v>204.58</v>
       </c>
       <c r="R4">
-        <v>212.76</v>
+        <v>212.05</v>
       </c>
       <c r="S4">
-        <v>241.53</v>
+        <v>241.32</v>
       </c>
       <c r="T4">
-        <v>-17.04</v>
+        <v>-16.96</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1261,43 +1243,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.95</v>
+        <v>32.02</v>
       </c>
       <c r="Z4">
-        <v>-3.26</v>
+        <v>-3.25</v>
       </c>
       <c r="AA4">
-        <v>-3.38</v>
+        <v>-3.36</v>
       </c>
       <c r="AB4">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AC4">
-        <v>53.45</v>
+        <v>52.59</v>
       </c>
       <c r="AD4">
-        <v>56.44</v>
+        <v>54.27</v>
       </c>
       <c r="AE4">
-        <v>4.23</v>
+        <v>4.11</v>
       </c>
       <c r="AF4">
-        <v>-16.44</v>
+        <v>-41.09</v>
       </c>
       <c r="AG4">
-        <v>211.58</v>
+        <v>210.93</v>
       </c>
       <c r="AH4">
-        <v>198.56</v>
+        <v>198.22</v>
       </c>
       <c r="AI4">
-        <v>213.5</v>
+        <v>211.77</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>20.25</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1308,58 +1290,58 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>652.2</v>
+        <v>643.75</v>
       </c>
       <c r="D5">
-        <v>-2.64</v>
+        <v>-1.3</v>
       </c>
       <c r="E5">
-        <v>959.2</v>
+        <v>949.55</v>
       </c>
       <c r="F5">
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-32.01</v>
+        <v>-32.2</v>
       </c>
       <c r="H5">
-        <v>13.54</v>
+        <v>12.07</v>
       </c>
       <c r="I5">
-        <v>-16.31</v>
+        <v>-7.14</v>
       </c>
       <c r="J5">
-        <v>4.13</v>
+        <v>0.96</v>
       </c>
       <c r="K5">
-        <v>-12.6</v>
+        <v>-11.77</v>
       </c>
       <c r="L5">
-        <v>-33.35</v>
+        <v>-32.89</v>
       </c>
       <c r="M5">
-        <v>-4.56</v>
+        <v>-5.44</v>
       </c>
       <c r="N5">
         <v>38</v>
       </c>
       <c r="O5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P5">
-        <v>676.8099999999999</v>
+        <v>666.91</v>
       </c>
       <c r="Q5">
-        <v>657.7</v>
+        <v>657.6799999999999</v>
       </c>
       <c r="R5">
-        <v>663.91</v>
+        <v>662.89</v>
       </c>
       <c r="S5">
-        <v>701.75</v>
+        <v>701.21</v>
       </c>
       <c r="T5">
-        <v>-7.06</v>
+        <v>-8.19</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1374,43 +1356,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>47.27</v>
+        <v>45.71</v>
       </c>
       <c r="Z5">
-        <v>7.49</v>
+        <v>4.58</v>
       </c>
       <c r="AA5">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="AB5">
-        <v>2.24</v>
+        <v>-0.54</v>
       </c>
       <c r="AC5">
-        <v>43.54</v>
+        <v>39.6</v>
       </c>
       <c r="AD5">
-        <v>48.36</v>
+        <v>44.11</v>
       </c>
       <c r="AE5">
-        <v>33.56</v>
+        <v>32.66</v>
       </c>
       <c r="AF5">
-        <v>-76.95999999999999</v>
+        <v>-66.17</v>
       </c>
       <c r="AG5">
-        <v>753.86</v>
+        <v>753.85</v>
       </c>
       <c r="AH5">
-        <v>561.55</v>
+        <v>561.52</v>
       </c>
       <c r="AI5">
-        <v>760.65</v>
+        <v>742.12</v>
       </c>
       <c r="AJ5" t="s">
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>35.67</v>
+        <v>31.72</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1421,10 +1403,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1670</v>
+        <v>1666.5</v>
       </c>
       <c r="D6">
-        <v>-1.8</v>
+        <v>-0.21</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1433,46 +1415,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-19</v>
+        <v>-19.17</v>
       </c>
       <c r="H6">
-        <v>23.9</v>
+        <v>23.64</v>
       </c>
       <c r="I6">
-        <v>-6.79</v>
+        <v>-6.38</v>
       </c>
       <c r="J6">
-        <v>-1.76</v>
+        <v>1.04</v>
       </c>
       <c r="K6">
-        <v>-16.16</v>
+        <v>-16.4</v>
       </c>
       <c r="L6">
-        <v>-0.85</v>
+        <v>0.82</v>
       </c>
       <c r="M6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N6">
         <v>62</v>
       </c>
       <c r="O6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>1715.16</v>
+        <v>1692.44</v>
       </c>
       <c r="Q6">
-        <v>1735.45</v>
+        <v>1734.3</v>
       </c>
       <c r="R6">
-        <v>1741.65</v>
+        <v>1738.19</v>
       </c>
       <c r="S6">
-        <v>1709.27</v>
+        <v>1708.54</v>
       </c>
       <c r="T6">
-        <v>-2.3</v>
+        <v>-2.46</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1487,43 +1469,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39.11</v>
+        <v>38.66</v>
       </c>
       <c r="Z6">
-        <v>-6.99</v>
+        <v>-11.4</v>
       </c>
       <c r="AA6">
-        <v>-0.46</v>
+        <v>-2.65</v>
       </c>
       <c r="AB6">
-        <v>-6.53</v>
+        <v>-8.76</v>
       </c>
       <c r="AC6">
         <v>2.8</v>
       </c>
       <c r="AD6">
-        <v>14.26</v>
+        <v>4.86</v>
       </c>
       <c r="AE6">
-        <v>49.21</v>
+        <v>47.97</v>
       </c>
       <c r="AF6">
-        <v>-59.44</v>
+        <v>-51.44</v>
       </c>
       <c r="AG6">
-        <v>1810.12</v>
+        <v>1812.58</v>
       </c>
       <c r="AH6">
-        <v>1660.78</v>
+        <v>1656.01</v>
       </c>
       <c r="AI6">
-        <v>1813.9</v>
+        <v>1809.97</v>
       </c>
       <c r="AJ6" t="s">
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>28.94</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1534,58 +1516,58 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>986.3</v>
+        <v>983.2</v>
       </c>
       <c r="D7">
-        <v>-0.8</v>
+        <v>-0.31</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
       </c>
       <c r="F7">
-        <v>984.1</v>
+        <v>983.2</v>
       </c>
       <c r="G7">
-        <v>-21.74</v>
+        <v>-21.99</v>
       </c>
       <c r="H7">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-2.7</v>
+        <v>-1.29</v>
       </c>
       <c r="J7">
-        <v>-7</v>
+        <v>-6.1</v>
       </c>
       <c r="K7">
-        <v>-12.82</v>
+        <v>-11.65</v>
       </c>
       <c r="L7">
-        <v>-11.73</v>
+        <v>-12.26</v>
       </c>
       <c r="M7">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>992.26</v>
+        <v>989.7</v>
       </c>
       <c r="Q7">
-        <v>1008.69</v>
+        <v>1005.75</v>
       </c>
       <c r="R7">
-        <v>1052.89</v>
+        <v>1050.79</v>
       </c>
       <c r="S7">
-        <v>1113.15</v>
+        <v>1112.38</v>
       </c>
       <c r="T7">
-        <v>-11.4</v>
+        <v>-11.61</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1600,43 +1582,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.15</v>
+        <v>36.29</v>
       </c>
       <c r="Z7">
-        <v>-18.7</v>
+        <v>-18.64</v>
       </c>
       <c r="AA7">
-        <v>-19.46</v>
+        <v>-19.3</v>
       </c>
       <c r="AB7">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="AC7">
-        <v>62.65</v>
+        <v>66.27</v>
       </c>
       <c r="AD7">
-        <v>64.18000000000001</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="AE7">
-        <v>18.06</v>
+        <v>17.53</v>
       </c>
       <c r="AF7">
-        <v>-11.71</v>
+        <v>-22.9</v>
       </c>
       <c r="AG7">
-        <v>1044.92</v>
+        <v>1040.09</v>
       </c>
       <c r="AH7">
-        <v>972.46</v>
+        <v>971.41</v>
       </c>
       <c r="AI7">
-        <v>1041.68</v>
+        <v>1037.15</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>45.98</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1647,10 +1629,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3183.8</v>
+        <v>3186.9</v>
       </c>
       <c r="D8">
-        <v>-0.88</v>
+        <v>0.1</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1659,46 +1641,46 @@
         <v>3183.8</v>
       </c>
       <c r="G8">
-        <v>-44.63</v>
+        <v>-44.57</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I8">
-        <v>-5.85</v>
+        <v>-2.44</v>
       </c>
       <c r="J8">
-        <v>-13.15</v>
+        <v>-12.69</v>
       </c>
       <c r="K8">
-        <v>-20.96</v>
+        <v>-19.94</v>
       </c>
       <c r="L8">
-        <v>-43.37</v>
+        <v>-42.14</v>
       </c>
       <c r="M8">
-        <v>-10.59</v>
+        <v>-10.13</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>3233.9</v>
+        <v>3217.94</v>
       </c>
       <c r="Q8">
-        <v>3440.51</v>
+        <v>3418.19</v>
       </c>
       <c r="R8">
-        <v>3567.69</v>
+        <v>3560.67</v>
       </c>
       <c r="S8">
-        <v>4271.51</v>
+        <v>4262.71</v>
       </c>
       <c r="T8">
-        <v>-25.46</v>
+        <v>-25.24</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1713,43 +1695,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>25.99</v>
+        <v>26.4</v>
       </c>
       <c r="Z8">
-        <v>-116.51</v>
+        <v>-119.3</v>
       </c>
       <c r="AA8">
-        <v>-92.86</v>
+        <v>-98.15000000000001</v>
       </c>
       <c r="AB8">
-        <v>-23.64</v>
+        <v>-21.15</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8">
-        <v>2.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE8">
-        <v>83.62</v>
+        <v>81.72</v>
       </c>
       <c r="AF8">
-        <v>6.62</v>
+        <v>-15.56</v>
       </c>
       <c r="AG8">
-        <v>3751.22</v>
+        <v>3734.69</v>
       </c>
       <c r="AH8">
-        <v>3129.79</v>
+        <v>3101.69</v>
       </c>
       <c r="AI8">
-        <v>3452.86</v>
+        <v>3417.66</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>42.94</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1760,10 +1742,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>658.35</v>
+        <v>651.6</v>
       </c>
       <c r="D9">
-        <v>-2.37</v>
+        <v>-1.03</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1772,46 +1754,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-37.45</v>
+        <v>-38.09</v>
       </c>
       <c r="H9">
-        <v>22.29</v>
+        <v>21.03</v>
       </c>
       <c r="I9">
-        <v>-8.470000000000001</v>
+        <v>-7.23</v>
       </c>
       <c r="J9">
-        <v>2.17</v>
+        <v>1.11</v>
       </c>
       <c r="K9">
-        <v>-3.02</v>
+        <v>-2.21</v>
       </c>
       <c r="L9">
-        <v>-9.76</v>
+        <v>-10.04</v>
       </c>
       <c r="M9">
-        <v>40.48</v>
+        <v>40.1</v>
       </c>
       <c r="N9">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O9">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="P9">
-        <v>679.55</v>
+        <v>669.4</v>
       </c>
       <c r="Q9">
-        <v>656.92</v>
+        <v>657.4</v>
       </c>
       <c r="R9">
-        <v>660.01</v>
+        <v>659.72</v>
       </c>
       <c r="S9">
-        <v>662.95</v>
+        <v>662.64</v>
       </c>
       <c r="T9">
-        <v>-0.6899999999999999</v>
+        <v>-1.67</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1826,43 +1808,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>48.41</v>
+        <v>46.7</v>
       </c>
       <c r="Z9">
-        <v>7.13</v>
+        <v>5.02</v>
       </c>
       <c r="AA9">
         <v>5.03</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>-0.01</v>
       </c>
       <c r="AC9">
-        <v>49.35</v>
+        <v>42.78</v>
       </c>
       <c r="AD9">
-        <v>54.73</v>
+        <v>48.78</v>
       </c>
       <c r="AE9">
-        <v>25.21</v>
+        <v>24.53</v>
       </c>
       <c r="AF9">
-        <v>-85.69</v>
+        <v>-88.23</v>
       </c>
       <c r="AG9">
-        <v>719.48</v>
+        <v>719.62</v>
       </c>
       <c r="AH9">
-        <v>594.37</v>
+        <v>595.1799999999999</v>
       </c>
       <c r="AI9">
-        <v>739.54</v>
+        <v>727</v>
       </c>
       <c r="AJ9" t="s">
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>37.05</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1873,10 +1855,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>363.45</v>
+        <v>367.5</v>
       </c>
       <c r="D10">
-        <v>-1.5</v>
+        <v>1.11</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1885,46 +1867,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-21.3</v>
+        <v>-20.42</v>
       </c>
       <c r="H10">
-        <v>5.27</v>
+        <v>6.44</v>
       </c>
       <c r="I10">
-        <v>-1.5</v>
+        <v>-1.95</v>
       </c>
       <c r="J10">
-        <v>-1.93</v>
+        <v>0.96</v>
       </c>
       <c r="K10">
-        <v>-6.56</v>
+        <v>-4.92</v>
       </c>
       <c r="L10">
-        <v>-8.289999999999999</v>
+        <v>-7.03</v>
       </c>
       <c r="M10">
-        <v>21.85</v>
+        <v>22.21</v>
       </c>
       <c r="N10">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O10">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P10">
-        <v>368.28</v>
+        <v>366.82</v>
       </c>
       <c r="Q10">
-        <v>363.29</v>
+        <v>364.06</v>
       </c>
       <c r="R10">
-        <v>372.14</v>
+        <v>371.95</v>
       </c>
       <c r="S10">
-        <v>387.09</v>
+        <v>387.05</v>
       </c>
       <c r="T10">
-        <v>-6.11</v>
+        <v>-5.05</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1939,34 +1921,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>45.31</v>
+        <v>49.53</v>
       </c>
       <c r="Z10">
-        <v>-1.31</v>
+        <v>-1.14</v>
       </c>
       <c r="AA10">
-        <v>-2.12</v>
+        <v>-1.92</v>
       </c>
       <c r="AB10">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AC10">
-        <v>47.08</v>
+        <v>48.93</v>
       </c>
       <c r="AD10">
-        <v>61.52</v>
+        <v>52.85</v>
       </c>
       <c r="AE10">
-        <v>7.36</v>
+        <v>7.2</v>
       </c>
       <c r="AF10">
-        <v>-46.51</v>
+        <v>-63.67</v>
       </c>
       <c r="AG10">
-        <v>377.95</v>
+        <v>377.82</v>
       </c>
       <c r="AH10">
-        <v>348.63</v>
+        <v>350.31</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -1975,7 +1957,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>42.09</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1986,10 +1968,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>188.02</v>
+        <v>187.97</v>
       </c>
       <c r="D11">
-        <v>-1.47</v>
+        <v>-0.03</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1998,46 +1980,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-13.22</v>
+        <v>-13.24</v>
       </c>
       <c r="H11">
-        <v>19.44</v>
+        <v>19.41</v>
       </c>
       <c r="I11">
-        <v>0.39</v>
+        <v>1.31</v>
       </c>
       <c r="J11">
-        <v>0.58</v>
+        <v>-0.02</v>
       </c>
       <c r="K11">
-        <v>-0.37</v>
+        <v>-0.84</v>
       </c>
       <c r="L11">
-        <v>11.9</v>
+        <v>11.93</v>
       </c>
       <c r="M11">
-        <v>11.38</v>
+        <v>11.42</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P11">
-        <v>186.55</v>
+        <v>187.04</v>
       </c>
       <c r="Q11">
-        <v>185.68</v>
+        <v>185.74</v>
       </c>
       <c r="R11">
-        <v>186.22</v>
+        <v>186.27</v>
       </c>
       <c r="S11">
-        <v>191.36</v>
+        <v>191.5</v>
       </c>
       <c r="T11">
-        <v>-1.75</v>
+        <v>-1.85</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2052,34 +2034,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>53.17</v>
+        <v>53.08</v>
       </c>
       <c r="Z11">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="AA11">
-        <v>-0.34</v>
+        <v>-0.23</v>
       </c>
       <c r="AB11">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="AC11">
-        <v>69.83</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AD11">
-        <v>54.71</v>
+        <v>67.13</v>
       </c>
       <c r="AE11">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="AF11">
-        <v>-48.15</v>
+        <v>-46.63</v>
       </c>
       <c r="AG11">
-        <v>190.11</v>
+        <v>190.26</v>
       </c>
       <c r="AH11">
-        <v>181.25</v>
+        <v>181.21</v>
       </c>
       <c r="AI11">
         <v>180.21</v>
@@ -2088,7 +2070,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>23.53</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2099,10 +2081,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="D12">
-        <v>-0.12</v>
+        <v>-0.24</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2111,46 +2093,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-35.22</v>
+        <v>-35.38</v>
       </c>
       <c r="H12">
-        <v>5.27</v>
+        <v>5.01</v>
       </c>
       <c r="I12">
-        <v>-4.7</v>
+        <v>-1.09</v>
       </c>
       <c r="J12">
-        <v>-9.109999999999999</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K12">
-        <v>-0.37</v>
+        <v>-0.76</v>
       </c>
       <c r="L12">
-        <v>-31.79</v>
+        <v>-29.84</v>
       </c>
       <c r="M12">
-        <v>-9.199999999999999</v>
+        <v>-9.09</v>
       </c>
       <c r="N12">
         <v>50</v>
       </c>
       <c r="O12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P12">
-        <v>2103.06</v>
+        <v>2098.46</v>
       </c>
       <c r="Q12">
-        <v>2230.72</v>
+        <v>2222.4</v>
       </c>
       <c r="R12">
-        <v>2293.23</v>
+        <v>2290.85</v>
       </c>
       <c r="S12">
-        <v>2509.62</v>
+        <v>2504.35</v>
       </c>
       <c r="T12">
-        <v>-16.84</v>
+        <v>-16.86</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2165,43 +2147,43 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>32.65</v>
+        <v>32.24</v>
       </c>
       <c r="Z12">
-        <v>-56.35</v>
+        <v>-58.59</v>
       </c>
       <c r="AA12">
-        <v>-39.19</v>
+        <v>-43.07</v>
       </c>
       <c r="AB12">
-        <v>-17.16</v>
+        <v>-15.52</v>
       </c>
       <c r="AC12">
-        <v>3.59</v>
+        <v>1.06</v>
       </c>
       <c r="AD12">
-        <v>6.44</v>
+        <v>4.29</v>
       </c>
       <c r="AE12">
-        <v>60.73</v>
+        <v>60.12</v>
       </c>
       <c r="AF12">
-        <v>-40.84</v>
+        <v>14.65</v>
       </c>
       <c r="AG12">
-        <v>2424.32</v>
+        <v>2426.8</v>
       </c>
       <c r="AH12">
-        <v>2037.11</v>
+        <v>2017.99</v>
       </c>
       <c r="AI12">
-        <v>2264.2</v>
+        <v>2244.5</v>
       </c>
       <c r="AJ12" t="s">
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>38.29</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2212,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4832.5</v>
+        <v>4884</v>
       </c>
       <c r="D13">
-        <v>-0.97</v>
+        <v>1.07</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2224,46 +2206,46 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-6.51</v>
+        <v>-5.52</v>
       </c>
       <c r="H13">
-        <v>45.24</v>
+        <v>46.79</v>
       </c>
       <c r="I13">
-        <v>-0.18</v>
+        <v>1.78</v>
       </c>
       <c r="J13">
-        <v>-5.7</v>
+        <v>-4.24</v>
       </c>
       <c r="K13">
-        <v>12.61</v>
+        <v>14.19</v>
       </c>
       <c r="L13">
-        <v>39.38</v>
+        <v>41.26</v>
       </c>
       <c r="M13">
-        <v>18.53</v>
+        <v>18.83</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P13">
-        <v>4862.9</v>
+        <v>4880</v>
       </c>
       <c r="Q13">
-        <v>4975.97</v>
+        <v>4963.21</v>
       </c>
       <c r="R13">
-        <v>4944.41</v>
+        <v>4949.57</v>
       </c>
       <c r="S13">
-        <v>4386.79</v>
+        <v>4392.37</v>
       </c>
       <c r="T13">
-        <v>10.16</v>
+        <v>11.19</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2278,34 +2260,34 @@
         <v>3</v>
       </c>
       <c r="Y13">
-        <v>40.75</v>
+        <v>45.57</v>
       </c>
       <c r="Z13">
-        <v>-31.73</v>
+        <v>-31.36</v>
       </c>
       <c r="AA13">
-        <v>-9.5</v>
+        <v>-13.88</v>
       </c>
       <c r="AB13">
-        <v>-22.23</v>
+        <v>-17.48</v>
       </c>
       <c r="AC13">
-        <v>46.75</v>
+        <v>48.46</v>
       </c>
       <c r="AD13">
-        <v>41.25</v>
+        <v>47.41</v>
       </c>
       <c r="AE13">
-        <v>85.90000000000001</v>
+        <v>84.23</v>
       </c>
       <c r="AF13">
-        <v>-14.85</v>
+        <v>-38.49</v>
       </c>
       <c r="AG13">
-        <v>5188.73</v>
+        <v>5165.06</v>
       </c>
       <c r="AH13">
-        <v>4763.21</v>
+        <v>4761.35</v>
       </c>
       <c r="AI13">
         <v>5062.11</v>
@@ -2314,7 +2296,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>41.08</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2325,58 +2307,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2700</v>
+        <v>2669.3</v>
       </c>
       <c r="D14">
-        <v>-2.67</v>
+        <v>-1.14</v>
       </c>
       <c r="E14">
-        <v>5003.11</v>
+        <v>4889.77</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-46.03</v>
+        <v>-45.41</v>
       </c>
       <c r="H14">
-        <v>23.07</v>
+        <v>21.67</v>
       </c>
       <c r="I14">
-        <v>-3.19</v>
+        <v>-5.48</v>
       </c>
       <c r="J14">
-        <v>-7.85</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="K14">
-        <v>-16.05</v>
+        <v>-18.08</v>
       </c>
       <c r="L14">
-        <v>-46.77</v>
+        <v>-46.65</v>
       </c>
       <c r="M14">
-        <v>22.4</v>
+        <v>21.76</v>
       </c>
       <c r="N14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>2779.28</v>
+        <v>2748.34</v>
       </c>
       <c r="Q14">
-        <v>2813.33</v>
+        <v>2802.87</v>
       </c>
       <c r="R14">
-        <v>2903.42</v>
+        <v>2899.6</v>
       </c>
       <c r="S14">
-        <v>2892.46</v>
+        <v>2885.39</v>
       </c>
       <c r="T14">
-        <v>-6.65</v>
+        <v>-7.49</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2391,43 +2373,43 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>32.3</v>
+        <v>29.91</v>
       </c>
       <c r="Z14">
-        <v>-45.59</v>
+        <v>-51.68</v>
       </c>
       <c r="AA14">
-        <v>-42.9</v>
+        <v>-44.66</v>
       </c>
       <c r="AB14">
-        <v>-2.69</v>
+        <v>-7.02</v>
       </c>
       <c r="AC14">
-        <v>49.58</v>
+        <v>26.98</v>
       </c>
       <c r="AD14">
-        <v>70.72</v>
+        <v>50.55</v>
       </c>
       <c r="AE14">
-        <v>59.22</v>
+        <v>60.28</v>
       </c>
       <c r="AF14">
-        <v>-15.54</v>
+        <v>60.82</v>
       </c>
       <c r="AG14">
-        <v>2911.89</v>
+        <v>2915.68</v>
       </c>
       <c r="AH14">
-        <v>2714.77</v>
+        <v>2690.06</v>
       </c>
       <c r="AI14">
-        <v>2911.37</v>
+        <v>2863.84</v>
       </c>
       <c r="AJ14" t="s">
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>44.46</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2438,10 +2420,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>215.13</v>
+        <v>215.65</v>
       </c>
       <c r="D15">
-        <v>-0.55</v>
+        <v>0.24</v>
       </c>
       <c r="E15">
         <v>380.65</v>
@@ -2450,46 +2432,46 @@
         <v>213</v>
       </c>
       <c r="G15">
-        <v>-43.48</v>
+        <v>-43.35</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="I15">
-        <v>-1.99</v>
+        <v>0.19</v>
       </c>
       <c r="J15">
-        <v>-7.15</v>
+        <v>-6.21</v>
       </c>
       <c r="K15">
-        <v>-12.68</v>
+        <v>-9.02</v>
       </c>
       <c r="L15">
-        <v>-40.77</v>
+        <v>-38.61</v>
       </c>
       <c r="M15">
-        <v>11.57</v>
+        <v>11.94</v>
       </c>
       <c r="N15">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P15">
-        <v>215.84</v>
+        <v>215.92</v>
       </c>
       <c r="Q15">
-        <v>222.95</v>
+        <v>222.28</v>
       </c>
       <c r="R15">
-        <v>228.82</v>
+        <v>228.09</v>
       </c>
       <c r="S15">
-        <v>251.42</v>
+        <v>251.09</v>
       </c>
       <c r="T15">
-        <v>-14.43</v>
+        <v>-14.11</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2504,43 +2486,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>37.87</v>
+        <v>38.81</v>
       </c>
       <c r="Z15">
-        <v>-4.2</v>
+        <v>-4.15</v>
       </c>
       <c r="AA15">
-        <v>-3.54</v>
+        <v>-3.66</v>
       </c>
       <c r="AB15">
-        <v>-0.66</v>
+        <v>-0.49</v>
       </c>
       <c r="AC15">
-        <v>28.15</v>
+        <v>28.24</v>
       </c>
       <c r="AD15">
-        <v>28.44</v>
+        <v>28.7</v>
       </c>
       <c r="AE15">
-        <v>7.81</v>
+        <v>7.56</v>
       </c>
       <c r="AF15">
-        <v>4.72</v>
+        <v>-40.04</v>
       </c>
       <c r="AG15">
-        <v>236.93</v>
+        <v>236.29</v>
       </c>
       <c r="AH15">
-        <v>208.97</v>
+        <v>208.26</v>
       </c>
       <c r="AI15">
-        <v>239.07</v>
+        <v>237.02</v>
       </c>
       <c r="AJ15" t="s">
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>29.19</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2551,10 +2533,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>35.02</v>
+        <v>34.44</v>
       </c>
       <c r="D16">
-        <v>-1.71</v>
+        <v>-1.66</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2563,46 +2545,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-40.32</v>
+        <v>-41.31</v>
       </c>
       <c r="H16">
-        <v>11.67</v>
+        <v>9.82</v>
       </c>
       <c r="I16">
-        <v>-4.42</v>
+        <v>-3.61</v>
       </c>
       <c r="J16">
-        <v>-6.74</v>
+        <v>-7.94</v>
       </c>
       <c r="K16">
-        <v>-18.14</v>
+        <v>-18.02</v>
       </c>
       <c r="L16">
-        <v>-39.31</v>
+        <v>-39.83</v>
       </c>
       <c r="M16">
-        <v>-0.05</v>
+        <v>-0.21</v>
       </c>
       <c r="N16">
         <v>19</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>35.47</v>
+        <v>35.21</v>
       </c>
       <c r="Q16">
-        <v>36.67</v>
+        <v>36.57</v>
       </c>
       <c r="R16">
-        <v>38.11</v>
+        <v>37.99</v>
       </c>
       <c r="S16">
-        <v>42.09</v>
+        <v>42.04</v>
       </c>
       <c r="T16">
-        <v>-16.8</v>
+        <v>-18.07</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2617,43 +2599,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>36.29</v>
+        <v>33.4</v>
       </c>
       <c r="Z16">
-        <v>-0.86</v>
+        <v>-0.91</v>
       </c>
       <c r="AA16">
-        <v>-0.82</v>
+        <v>-0.84</v>
       </c>
       <c r="AB16">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="AC16">
-        <v>55</v>
+        <v>40.83</v>
       </c>
       <c r="AD16">
-        <v>50.68</v>
+        <v>49.3</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>-75.41</v>
+        <v>-55.06</v>
       </c>
       <c r="AG16">
-        <v>39.21</v>
+        <v>39.29</v>
       </c>
       <c r="AH16">
-        <v>34.13</v>
+        <v>33.84</v>
       </c>
       <c r="AI16">
-        <v>38.5</v>
+        <v>37.92</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>15.66</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2664,10 +2646,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1113.4</v>
+        <v>1118.2</v>
       </c>
       <c r="D17">
-        <v>-1.47</v>
+        <v>0.43</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2676,46 +2658,46 @@
         <v>1100.8</v>
       </c>
       <c r="G17">
-        <v>-28.46</v>
+        <v>-28.16</v>
       </c>
       <c r="H17">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
       <c r="I17">
-        <v>-1.9</v>
+        <v>0.66</v>
       </c>
       <c r="J17">
-        <v>-10.43</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="K17">
-        <v>-14.51</v>
+        <v>-13.71</v>
       </c>
       <c r="L17">
-        <v>-21.34</v>
+        <v>-18.49</v>
       </c>
       <c r="M17">
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="N17">
         <v>44</v>
       </c>
       <c r="O17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="P17">
-        <v>1119.44</v>
+        <v>1120.9</v>
       </c>
       <c r="Q17">
-        <v>1154.83</v>
+        <v>1149.86</v>
       </c>
       <c r="R17">
-        <v>1238.82</v>
+        <v>1233.71</v>
       </c>
       <c r="S17">
-        <v>1336.35</v>
+        <v>1335.35</v>
       </c>
       <c r="T17">
-        <v>-16.68</v>
+        <v>-16.26</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2730,43 +2712,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>37.49</v>
+        <v>38.72</v>
       </c>
       <c r="Z17">
-        <v>-34.19</v>
+        <v>-33.16</v>
       </c>
       <c r="AA17">
-        <v>-34.63</v>
+        <v>-34.34</v>
       </c>
       <c r="AB17">
-        <v>0.44</v>
+        <v>1.18</v>
       </c>
       <c r="AC17">
-        <v>72.88</v>
+        <v>88.12</v>
       </c>
       <c r="AD17">
-        <v>68.44</v>
+        <v>80.56</v>
       </c>
       <c r="AE17">
-        <v>30.93</v>
+        <v>30.02</v>
       </c>
       <c r="AF17">
-        <v>-27.9</v>
+        <v>-50.54</v>
       </c>
       <c r="AG17">
-        <v>1219.62</v>
+        <v>1209.44</v>
       </c>
       <c r="AH17">
-        <v>1090.03</v>
+        <v>1090.28</v>
       </c>
       <c r="AI17">
-        <v>1205.69</v>
+        <v>1203.06</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>38.48</v>
+        <v>39.63</v>
       </c>
     </row>
   </sheetData>
@@ -2907,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2947,7 +2929,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2965,1741 +2947,1735 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-0.16</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>79</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>7.29</v>
+      </c>
+      <c r="D8" s="6">
+        <v>4.33</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>2.03</v>
+        <v>-5.9</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.16</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.19</v>
+        <v>-6.33</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>11.52</v>
+        <v>4.13</v>
       </c>
       <c r="D10" s="6">
-        <v>7.29</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-4.23</v>
+        <v>0.96</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.12</v>
+        <v>-1.76</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.9</v>
+        <v>1.04</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.78</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>6.85</v>
+        <v>-7</v>
       </c>
       <c r="D12" s="6">
-        <v>4.13</v>
+        <v>-6.1</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.72</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>0.72</v>
+        <v>-13.15</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.76</v>
+        <v>-12.69</v>
       </c>
       <c r="E13" s="7">
-        <v>-2.48</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.42</v>
+        <v>2.17</v>
       </c>
       <c r="D14" s="6">
-        <v>-7</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.58</v>
+        <v>1.11</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-12.56</v>
+        <v>-1.93</v>
       </c>
       <c r="D15" s="6">
-        <v>-13.15</v>
+        <v>0.96</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.59</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>4.39</v>
+        <v>0.58</v>
       </c>
       <c r="D16" s="6">
-        <v>2.17</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.22</v>
+        <v>-0.02</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.2</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.93</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.73</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>2.43</v>
+        <v>-5.7</v>
       </c>
       <c r="D18" s="6">
-        <v>0.58</v>
+        <v>-4.24</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.85</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-8.52</v>
+        <v>-7.85</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.59</v>
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.92</v>
+        <v>-7.15</v>
       </c>
       <c r="D20" s="6">
-        <v>-5.7</v>
+        <v>-6.21</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.78</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.51</v>
+        <v>-6.74</v>
       </c>
       <c r="D21" s="6">
-        <v>-7.85</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.34</v>
+        <v>-7.94</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.95</v>
+        <v>-10.43</v>
       </c>
       <c r="D22" s="6">
-        <v>-7.15</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.2</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.66</v>
+        <v>0.3</v>
       </c>
       <c r="D23" s="6">
-        <v>-6.74</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.08</v>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-9.02</v>
+        <v>2.88</v>
       </c>
       <c r="D24" s="6">
-        <v>-10.43</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.41</v>
+        <v>-3.49</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-6.37</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>4.25</v>
+        <v>-1.85</v>
       </c>
       <c r="D25" s="6">
-        <v>0.3</v>
+        <v>-1.68</v>
       </c>
       <c r="E25" s="7">
-        <v>-3.95</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>8.82</v>
+        <v>-16.31</v>
       </c>
       <c r="D26" s="6">
-        <v>2.88</v>
+        <v>-7.14</v>
       </c>
       <c r="E26" s="7">
-        <v>-5.94</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-0.01</v>
+        <v>-6.79</v>
       </c>
       <c r="D27" s="6">
-        <v>-1.85</v>
+        <v>-6.38</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.84</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-8.460000000000001</v>
+        <v>-2.7</v>
       </c>
       <c r="D28" s="6">
-        <v>-16.31</v>
+        <v>-1.29</v>
       </c>
       <c r="E28" s="7">
-        <v>-7.85</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-5.49</v>
+        <v>-5.85</v>
       </c>
       <c r="D29" s="6">
-        <v>-6.79</v>
+        <v>-2.44</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.3</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-0.58</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.7</v>
+        <v>-7.23</v>
       </c>
       <c r="E30" s="7">
-        <v>-2.12</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-4.77</v>
+        <v>-1.5</v>
       </c>
       <c r="D31" s="6">
-        <v>-5.85</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.08</v>
+        <v>-1.95</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-1.12</v>
+        <v>0.39</v>
       </c>
       <c r="D32" s="6">
-        <v>-8.470000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="E32" s="7">
-        <v>-7.35</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>2.39</v>
+        <v>-4.7</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.5</v>
+        <v>-1.09</v>
       </c>
       <c r="E33" s="7">
-        <v>-3.89</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>4.27</v>
+        <v>-0.18</v>
       </c>
       <c r="D34" s="6">
-        <v>0.39</v>
+        <v>1.78</v>
       </c>
       <c r="E34" s="7">
-        <v>-3.88</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-4.53</v>
+        <v>-3.19</v>
       </c>
       <c r="D35" s="6">
-        <v>-4.7</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.17</v>
+        <v>-5.48</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-0.58</v>
+        <v>-1.99</v>
       </c>
       <c r="D36" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.4</v>
+        <v>0.19</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.18</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>0.16</v>
+        <v>-4.42</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.19</v>
+        <v>-3.61</v>
       </c>
       <c r="E37" s="7">
-        <v>-3.35</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>1.09</v>
+        <v>-1.9</v>
       </c>
       <c r="D38" s="6">
-        <v>-1.99</v>
+        <v>0.66</v>
       </c>
       <c r="E38" s="7">
-        <v>-3.08</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C39" s="6">
-        <v>1.16</v>
+        <v>-6.03</v>
       </c>
       <c r="D39" s="6">
-        <v>-4.42</v>
+        <v>-5.54</v>
       </c>
       <c r="E39" s="7">
-        <v>-5.58</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C40" s="6">
-        <v>-0.09</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D40" s="6">
-        <v>-1.9</v>
+        <v>11.45</v>
       </c>
       <c r="E40" s="7">
-        <v>-1.81</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>-4.9</v>
+        <v>-39.55</v>
       </c>
       <c r="D41" s="6">
-        <v>-6.03</v>
+        <v>-38</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.13</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>12.17</v>
+        <v>-33.35</v>
       </c>
       <c r="D42" s="6">
-        <v>9.220000000000001</v>
+        <v>-32.89</v>
       </c>
       <c r="E42" s="7">
-        <v>-2.95</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-39.6</v>
+        <v>-0.85</v>
       </c>
       <c r="D43" s="6">
-        <v>-39.55</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.05</v>
+        <v>0.82</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.67</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-31.24</v>
+        <v>-11.73</v>
       </c>
       <c r="D44" s="6">
-        <v>-33.35</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.11</v>
+        <v>-12.26</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>1.01</v>
+        <v>-43.37</v>
       </c>
       <c r="D45" s="6">
-        <v>-0.85</v>
+        <v>-42.14</v>
       </c>
       <c r="E45" s="7">
-        <v>-1.86</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-11.21</v>
+        <v>-9.76</v>
       </c>
       <c r="D46" s="6">
-        <v>-11.73</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.52</v>
+        <v>-10.04</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-42.97</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="D47" s="6">
-        <v>-43.37</v>
+        <v>-7.03</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.4</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-9.66</v>
+        <v>11.9</v>
       </c>
       <c r="D48" s="6">
-        <v>-9.76</v>
+        <v>11.93</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-6.13</v>
+        <v>-31.79</v>
       </c>
       <c r="D49" s="6">
-        <v>-8.289999999999999</v>
+        <v>-29.84</v>
       </c>
       <c r="E49" s="7">
-        <v>-2.16</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>13.21</v>
+        <v>39.38</v>
       </c>
       <c r="D50" s="6">
-        <v>11.9</v>
+        <v>41.26</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.31</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-31.86</v>
+        <v>-46.77</v>
       </c>
       <c r="D51" s="6">
-        <v>-31.79</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.07000000000000001</v>
+        <v>-46.65</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>38.98</v>
+        <v>-40.77</v>
       </c>
       <c r="D52" s="6">
-        <v>39.38</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.4</v>
+        <v>-38.61</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.16</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-45.99</v>
+        <v>-39.31</v>
       </c>
       <c r="D53" s="6">
-        <v>-46.77</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-0.78</v>
+        <v>-39.83</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-42.54</v>
+        <v>-21.34</v>
       </c>
       <c r="D54" s="6">
-        <v>-40.77</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1.77</v>
+        <v>-18.49</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2.85</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" s="6">
-        <v>-38.36</v>
+        <v>1.13</v>
       </c>
       <c r="D55" s="6">
-        <v>-39.31</v>
+        <v>2.79</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.95</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="6">
-        <v>-20.52</v>
+        <v>15.06</v>
       </c>
       <c r="D56" s="6">
-        <v>-21.34</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.82</v>
+        <v>9.81</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-5.25</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>2.51</v>
+        <v>-11.94</v>
       </c>
       <c r="D57" s="6">
-        <v>1.13</v>
+        <v>-10.78</v>
       </c>
       <c r="E57" s="7">
-        <v>-1.38</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>18.03</v>
+        <v>-12.6</v>
       </c>
       <c r="D58" s="6">
-        <v>15.06</v>
+        <v>-11.77</v>
       </c>
       <c r="E58" s="7">
-        <v>-2.97</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-12.03</v>
+        <v>-16.16</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.94</v>
+        <v>-16.4</v>
       </c>
       <c r="E59" s="8">
-        <v>0.09</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-8.02</v>
+        <v>-12.82</v>
       </c>
       <c r="D60" s="6">
-        <v>-12.6</v>
+        <v>-11.65</v>
       </c>
       <c r="E60" s="7">
-        <v>-4.58</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-9.449999999999999</v>
+        <v>-20.96</v>
       </c>
       <c r="D61" s="6">
-        <v>-12.82</v>
+        <v>-19.94</v>
       </c>
       <c r="E61" s="7">
-        <v>-3.37</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-20.21</v>
+        <v>-3.02</v>
       </c>
       <c r="D62" s="6">
-        <v>-20.96</v>
+        <v>-2.21</v>
       </c>
       <c r="E62" s="7">
-        <v>-0.75</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>0.61</v>
+        <v>-6.56</v>
       </c>
       <c r="D63" s="6">
-        <v>-3.02</v>
+        <v>-4.92</v>
       </c>
       <c r="E63" s="7">
-        <v>-3.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-6.13</v>
+        <v>-0.37</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.56</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.43</v>
+        <v>-0.84</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="D65" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-0.72</v>
+        <v>-0.76</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-0.92</v>
+        <v>12.61</v>
       </c>
       <c r="D66" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.55</v>
+        <v>14.19</v>
+      </c>
+      <c r="E66" s="7">
+        <v>1.58</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>12.86</v>
+        <v>-16.05</v>
       </c>
       <c r="D67" s="6">
-        <v>12.61</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-0.25</v>
+        <v>-18.08</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-14.57</v>
+        <v>-12.68</v>
       </c>
       <c r="D68" s="6">
-        <v>-16.05</v>
+        <v>-9.02</v>
       </c>
       <c r="E68" s="7">
-        <v>-1.48</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-12.77</v>
+        <v>-18.14</v>
       </c>
       <c r="D69" s="6">
-        <v>-12.68</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.09</v>
+        <v>-18.02</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-17.12</v>
+        <v>-14.51</v>
       </c>
       <c r="D70" s="6">
-        <v>-18.14</v>
+        <v>-13.71</v>
       </c>
       <c r="E70" s="7">
-        <v>-1.02</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6">
-        <v>-13.75</v>
+        <v>-5.28</v>
       </c>
       <c r="D71" s="6">
-        <v>-14.51</v>
+        <v>-3.39</v>
       </c>
       <c r="E71" s="7">
-        <v>-0.76</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-4.11</v>
+        <v>-8.18</v>
       </c>
       <c r="D72" s="6">
-        <v>-5.28</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-1.17</v>
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-5.62</v>
+        <v>-32.01</v>
       </c>
       <c r="D73" s="6">
-        <v>-8.18</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-2.56</v>
+        <v>-32.2</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-38.87</v>
+        <v>-19</v>
       </c>
       <c r="D74" s="6">
-        <v>-38.23</v>
+        <v>-19.17</v>
       </c>
       <c r="E74" s="8">
-        <v>0.64</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-31.54</v>
+        <v>-21.74</v>
       </c>
       <c r="D75" s="6">
-        <v>-32.01</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-0.47</v>
+        <v>-21.99</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-17.51</v>
+        <v>-44.63</v>
       </c>
       <c r="D76" s="6">
-        <v>-19</v>
+        <v>-44.57</v>
       </c>
       <c r="E76" s="7">
-        <v>-1.49</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-21.11</v>
+        <v>-37.45</v>
       </c>
       <c r="D77" s="6">
-        <v>-21.74</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-0.63</v>
+        <v>-38.09</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-44.14</v>
+        <v>-21.3</v>
       </c>
       <c r="D78" s="6">
-        <v>-44.63</v>
+        <v>-20.42</v>
       </c>
       <c r="E78" s="7">
-        <v>-0.49</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-35.94</v>
+        <v>-13.22</v>
       </c>
       <c r="D79" s="6">
-        <v>-37.45</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-1.51</v>
+        <v>-13.24</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-20.1</v>
+        <v>-35.22</v>
       </c>
       <c r="D80" s="6">
-        <v>-21.3</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-1.2</v>
+        <v>-35.38</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-11.93</v>
+        <v>-6.51</v>
       </c>
       <c r="D81" s="6">
-        <v>-13.22</v>
+        <v>-5.52</v>
       </c>
       <c r="E81" s="7">
-        <v>-1.29</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-35.14</v>
+        <v>-46.03</v>
       </c>
       <c r="D82" s="6">
-        <v>-35.22</v>
+        <v>-45.41</v>
       </c>
       <c r="E82" s="7">
-        <v>-0.08</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-5.59</v>
+        <v>-43.48</v>
       </c>
       <c r="D83" s="6">
-        <v>-6.51</v>
+        <v>-43.35</v>
       </c>
       <c r="E83" s="7">
-        <v>-0.92</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-45.31</v>
+        <v>-40.32</v>
       </c>
       <c r="D84" s="6">
-        <v>-46.03</v>
-      </c>
-      <c r="E84" s="7">
-        <v>-0.72</v>
+        <v>-41.31</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-43.17</v>
+        <v>-28.46</v>
       </c>
       <c r="D85" s="6">
-        <v>-43.48</v>
+        <v>-28.16</v>
       </c>
       <c r="E85" s="7">
-        <v>-0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C86" s="6">
-        <v>-39.28</v>
+        <v>728.8</v>
       </c>
       <c r="D86" s="6">
-        <v>-40.32</v>
-      </c>
-      <c r="E86" s="7">
-        <v>-1.04</v>
+        <v>726.8</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-2</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C87" s="6">
-        <v>-27.4</v>
+        <v>993.05</v>
       </c>
       <c r="D87" s="6">
-        <v>-28.46</v>
-      </c>
-      <c r="E87" s="7">
-        <v>-1.06</v>
+        <v>976.5</v>
+      </c>
+      <c r="E87" s="8">
+        <v>-16.55</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>743.7</v>
+        <v>200.36</v>
       </c>
       <c r="D88" s="6">
-        <v>728.8</v>
+        <v>200.38</v>
       </c>
       <c r="E88" s="7">
-        <v>-14.9</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>1020.75</v>
+        <v>652.2</v>
       </c>
       <c r="D89" s="6">
-        <v>993.05</v>
-      </c>
-      <c r="E89" s="7">
-        <v>-27.7</v>
+        <v>643.75</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-8.449999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>202.62</v>
+        <v>1670</v>
       </c>
       <c r="D90" s="6">
-        <v>200.36</v>
-      </c>
-      <c r="E90" s="7">
-        <v>-2.26</v>
+        <v>1666.5</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>669.9</v>
+        <v>986.3</v>
       </c>
       <c r="D91" s="6">
-        <v>652.2</v>
-      </c>
-      <c r="E91" s="7">
-        <v>-17.7</v>
+        <v>983.2</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>1700.6</v>
+        <v>3183.8</v>
       </c>
       <c r="D92" s="6">
-        <v>1670</v>
+        <v>3186.9</v>
       </c>
       <c r="E92" s="7">
-        <v>-30.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>994.3</v>
+        <v>658.35</v>
       </c>
       <c r="D93" s="6">
-        <v>986.3</v>
-      </c>
-      <c r="E93" s="7">
-        <v>-8</v>
+        <v>651.6</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>3212</v>
+        <v>363.45</v>
       </c>
       <c r="D94" s="6">
-        <v>3183.8</v>
+        <v>367.5</v>
       </c>
       <c r="E94" s="7">
-        <v>-28.2</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>674.3</v>
+        <v>188.02</v>
       </c>
       <c r="D95" s="6">
-        <v>658.35</v>
-      </c>
-      <c r="E95" s="7">
-        <v>-15.95</v>
+        <v>187.97</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>369</v>
+        <v>2087</v>
       </c>
       <c r="D96" s="6">
-        <v>363.45</v>
-      </c>
-      <c r="E96" s="7">
-        <v>-5.55</v>
+        <v>2082</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>190.82</v>
+        <v>4832.5</v>
       </c>
       <c r="D97" s="6">
-        <v>188.02</v>
+        <v>4884</v>
       </c>
       <c r="E97" s="7">
-        <v>-2.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>2089.6</v>
+        <v>2700</v>
       </c>
       <c r="D98" s="6">
-        <v>2087</v>
-      </c>
-      <c r="E98" s="7">
-        <v>-2.6</v>
+        <v>2669.3</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-30.7</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>4880</v>
+        <v>215.13</v>
       </c>
       <c r="D99" s="6">
-        <v>4832.5</v>
+        <v>215.65</v>
       </c>
       <c r="E99" s="7">
-        <v>-47.5</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>2774</v>
+        <v>35.02</v>
       </c>
       <c r="D100" s="6">
-        <v>2700</v>
-      </c>
-      <c r="E100" s="7">
-        <v>-74</v>
+        <v>34.44</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>216.31</v>
+        <v>1113.4</v>
       </c>
       <c r="D101" s="6">
-        <v>215.13</v>
+        <v>1118.2</v>
       </c>
       <c r="E101" s="7">
-        <v>-1.18</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C102" s="6">
-        <v>35.63</v>
+        <v>32</v>
       </c>
       <c r="D102" s="6">
-        <v>35.02</v>
-      </c>
-      <c r="E102" s="7">
-        <v>-0.61</v>
+        <v>26</v>
+      </c>
+      <c r="E102" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C103" s="6">
-        <v>1130</v>
+        <v>7</v>
       </c>
       <c r="D103" s="6">
-        <v>1113.4</v>
+        <v>13</v>
       </c>
       <c r="E103" s="7">
-        <v>-16.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C104" s="6">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D104" s="6">
-        <v>38</v>
-      </c>
-      <c r="E104" s="7">
-        <v>-12</v>
+        <v>68</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C105" s="6">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D105" s="6">
-        <v>50</v>
-      </c>
-      <c r="E105" s="8">
+        <v>74</v>
+      </c>
+      <c r="E105" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D106" s="6">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E106" s="8">
-        <v>7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>13</v>
@@ -4708,577 +4684,560 @@
         <v>26</v>
       </c>
       <c r="D107" s="6">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E107" s="7">
-        <v>-7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C108" s="6">
-        <v>38</v>
+        <v>50.83</v>
       </c>
       <c r="D108" s="6">
-        <v>44</v>
+        <v>49.85</v>
       </c>
       <c r="E108" s="8">
-        <v>6</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C109" s="6">
-        <v>58.78</v>
+        <v>55.13</v>
       </c>
       <c r="D109" s="6">
-        <v>50.83</v>
-      </c>
-      <c r="E109" s="7">
-        <v>-7.95</v>
+        <v>52.19</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C110" s="6">
-        <v>60.42</v>
+        <v>31.95</v>
       </c>
       <c r="D110" s="6">
-        <v>55.13</v>
+        <v>32.02</v>
       </c>
       <c r="E110" s="7">
-        <v>-5.29</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C111" s="6">
-        <v>36.21</v>
+        <v>47.27</v>
       </c>
       <c r="D111" s="6">
-        <v>31.95</v>
-      </c>
-      <c r="E111" s="7">
-        <v>-4.26</v>
+        <v>45.71</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>50.64</v>
+        <v>39.11</v>
       </c>
       <c r="D112" s="6">
-        <v>47.27</v>
-      </c>
-      <c r="E112" s="7">
-        <v>-3.37</v>
+        <v>38.66</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>43.16</v>
+        <v>37.15</v>
       </c>
       <c r="D113" s="6">
-        <v>39.11</v>
-      </c>
-      <c r="E113" s="7">
-        <v>-4.05</v>
+        <v>36.29</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>39.39</v>
+        <v>25.99</v>
       </c>
       <c r="D114" s="6">
-        <v>37.15</v>
+        <v>26.4</v>
       </c>
       <c r="E114" s="7">
-        <v>-2.24</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>27.26</v>
+        <v>48.41</v>
       </c>
       <c r="D115" s="6">
-        <v>25.99</v>
-      </c>
-      <c r="E115" s="7">
-        <v>-1.27</v>
+        <v>46.7</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>52.66</v>
+        <v>45.31</v>
       </c>
       <c r="D116" s="6">
-        <v>48.41</v>
+        <v>49.53</v>
       </c>
       <c r="E116" s="7">
-        <v>-4.25</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>50.7</v>
+        <v>53.17</v>
       </c>
       <c r="D117" s="6">
-        <v>45.31</v>
-      </c>
-      <c r="E117" s="7">
-        <v>-5.39</v>
+        <v>53.08</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>58.32</v>
+        <v>32.65</v>
       </c>
       <c r="D118" s="6">
-        <v>53.17</v>
-      </c>
-      <c r="E118" s="7">
-        <v>-5.15</v>
+        <v>32.24</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>32.86</v>
+        <v>40.75</v>
       </c>
       <c r="D119" s="6">
-        <v>32.65</v>
+        <v>45.57</v>
       </c>
       <c r="E119" s="7">
-        <v>-0.21</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>44.1</v>
+        <v>32.3</v>
       </c>
       <c r="D120" s="6">
-        <v>40.75</v>
-      </c>
-      <c r="E120" s="7">
-        <v>-3.35</v>
+        <v>29.91</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>39.32</v>
+        <v>37.87</v>
       </c>
       <c r="D121" s="6">
-        <v>32.3</v>
+        <v>38.81</v>
       </c>
       <c r="E121" s="7">
-        <v>-7.02</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>39.14</v>
+        <v>36.29</v>
       </c>
       <c r="D122" s="6">
-        <v>37.87</v>
-      </c>
-      <c r="E122" s="7">
-        <v>-1.27</v>
+        <v>33.4</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-2.89</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>39.64</v>
+        <v>37.49</v>
       </c>
       <c r="D123" s="6">
-        <v>36.29</v>
+        <v>38.72</v>
       </c>
       <c r="E123" s="7">
-        <v>-3.35</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C124" s="6">
-        <v>40.07</v>
+        <v>-35.84</v>
       </c>
       <c r="D124" s="6">
-        <v>37.49</v>
+        <v>-13.77</v>
       </c>
       <c r="E124" s="7">
-        <v>-2.58</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C125" s="6">
-        <v>-26.52</v>
+        <v>-47.21</v>
       </c>
       <c r="D125" s="6">
-        <v>-35.84</v>
-      </c>
-      <c r="E125" s="7">
-        <v>-9.32</v>
+        <v>-62.82</v>
+      </c>
+      <c r="E125" s="8">
+        <v>-15.61</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C126" s="6">
-        <v>55.75</v>
+        <v>-16.44</v>
       </c>
       <c r="D126" s="6">
-        <v>-47.21</v>
-      </c>
-      <c r="E126" s="7">
-        <v>-102.96</v>
+        <v>-41.09</v>
+      </c>
+      <c r="E126" s="8">
+        <v>-24.65</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C127" s="6">
-        <v>-57.16</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="D127" s="6">
-        <v>-16.44</v>
-      </c>
-      <c r="E127" s="8">
-        <v>40.72</v>
+        <v>-66.17</v>
+      </c>
+      <c r="E127" s="7">
+        <v>10.79</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>-64.14</v>
+        <v>-59.44</v>
       </c>
       <c r="D128" s="6">
-        <v>-76.95999999999999</v>
+        <v>-51.44</v>
       </c>
       <c r="E128" s="7">
-        <v>-12.82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>-43.3</v>
+        <v>-11.71</v>
       </c>
       <c r="D129" s="6">
-        <v>-59.44</v>
-      </c>
-      <c r="E129" s="7">
-        <v>-16.14</v>
+        <v>-22.9</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-11.19</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>-25.8</v>
+        <v>6.62</v>
       </c>
       <c r="D130" s="6">
-        <v>-11.71</v>
+        <v>-15.56</v>
       </c>
       <c r="E130" s="8">
-        <v>14.09</v>
+        <v>-22.18</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>-23.71</v>
+        <v>-85.69</v>
       </c>
       <c r="D131" s="6">
-        <v>6.62</v>
+        <v>-88.23</v>
       </c>
       <c r="E131" s="8">
-        <v>30.33</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>-83.44</v>
+        <v>-46.51</v>
       </c>
       <c r="D132" s="6">
-        <v>-85.69</v>
-      </c>
-      <c r="E132" s="7">
-        <v>-2.25</v>
+        <v>-63.67</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-17.16</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>-72.62</v>
+        <v>-48.15</v>
       </c>
       <c r="D133" s="6">
-        <v>-46.51</v>
-      </c>
-      <c r="E133" s="8">
-        <v>26.11</v>
+        <v>-46.63</v>
+      </c>
+      <c r="E133" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>32.26</v>
+        <v>-40.84</v>
       </c>
       <c r="D134" s="6">
-        <v>-48.15</v>
+        <v>14.65</v>
       </c>
       <c r="E134" s="7">
-        <v>-80.41</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>-24.34</v>
+        <v>-14.85</v>
       </c>
       <c r="D135" s="6">
-        <v>-40.84</v>
-      </c>
-      <c r="E135" s="7">
-        <v>-16.5</v>
+        <v>-38.49</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-23.64</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>35.65</v>
+        <v>-15.54</v>
       </c>
       <c r="D136" s="6">
-        <v>-14.85</v>
+        <v>60.82</v>
       </c>
       <c r="E136" s="7">
-        <v>-50.5</v>
+        <v>76.36</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>30.51</v>
+        <v>4.72</v>
       </c>
       <c r="D137" s="6">
-        <v>-15.54</v>
-      </c>
-      <c r="E137" s="7">
-        <v>-46.05</v>
+        <v>-40.04</v>
+      </c>
+      <c r="E137" s="8">
+        <v>-44.76</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>-10.95</v>
+        <v>-75.41</v>
       </c>
       <c r="D138" s="6">
-        <v>4.72</v>
-      </c>
-      <c r="E138" s="8">
-        <v>15.67</v>
+        <v>-55.06</v>
+      </c>
+      <c r="E138" s="7">
+        <v>20.35</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>-72.76000000000001</v>
+        <v>-27.9</v>
       </c>
       <c r="D139" s="6">
-        <v>-75.41</v>
-      </c>
-      <c r="E139" s="7">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C140" s="6">
-        <v>7.92</v>
-      </c>
-      <c r="D140" s="6">
-        <v>-27.9</v>
-      </c>
-      <c r="E140" s="7">
-        <v>-35.82</v>
+        <v>-50.54</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-22.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5302,28 +5261,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5337,16 +5296,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.3</v>
+        <v>-7</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5460,10 +5419,10 @@
         <v>37</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>48</v>
@@ -5486,34 +5445,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.4048</v>
+        <v>0.401</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3355</v>
+        <v>0.3199</v>
       </c>
       <c r="C2" s="14">
-        <v>0.224</v>
+        <v>0.2221</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2185</v>
+        <v>0.2176</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1853</v>
+        <v>0.1883</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1157</v>
+        <v>0.1194</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1138</v>
+        <v>0.1142</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1114</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I2" s="14">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="J2" s="14">
-        <v>0.042</v>
+        <v>0.04190000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5538,22 +5497,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.0005</v>
+        <v>-0.0021</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.015</v>
+        <v>-0.0124</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.04559999999999999</v>
+        <v>-0.0544</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0583</v>
+        <v>-0.0576</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.092</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1059</v>
+        <v>-0.1013</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="84">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,19 +214,25 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.8 → 49.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>49.9</t>
+    <t>52.2 → 43.2</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>43.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -438,8 +444,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -951,10 +957,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>726.8</v>
+        <v>711</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>-2.17</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -963,46 +969,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-3.39</v>
+        <v>-5.49</v>
       </c>
       <c r="H2">
-        <v>27.3</v>
+        <v>24.53</v>
       </c>
       <c r="I2">
-        <v>-0.8100000000000001</v>
+        <v>-4.56</v>
       </c>
       <c r="J2">
-        <v>0.8</v>
+        <v>-1.04</v>
       </c>
       <c r="K2">
-        <v>2.79</v>
+        <v>-0.41</v>
       </c>
       <c r="L2">
-        <v>-5.54</v>
+        <v>-5.45</v>
       </c>
       <c r="M2">
-        <v>31.99</v>
+        <v>31.65</v>
       </c>
       <c r="N2">
         <v>81</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>736.11</v>
+        <v>729.3099999999999</v>
       </c>
       <c r="Q2">
-        <v>725.1799999999999</v>
+        <v>725.41</v>
       </c>
       <c r="R2">
-        <v>728.28</v>
+        <v>727.9400000000001</v>
       </c>
       <c r="S2">
-        <v>688.34</v>
+        <v>688.26</v>
       </c>
       <c r="T2">
-        <v>5.59</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1017,34 +1023,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.85</v>
+        <v>42.86</v>
       </c>
       <c r="Z2">
-        <v>2.12</v>
+        <v>0.5</v>
       </c>
       <c r="AA2">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="AB2">
-        <v>1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="AC2">
-        <v>52.87</v>
+        <v>23.6</v>
       </c>
       <c r="AD2">
-        <v>67.58</v>
+        <v>47.05</v>
       </c>
       <c r="AE2">
-        <v>14.82</v>
+        <v>14.94</v>
       </c>
       <c r="AF2">
-        <v>-13.77</v>
+        <v>50.37</v>
       </c>
       <c r="AG2">
-        <v>746.05</v>
+        <v>745.49</v>
       </c>
       <c r="AH2">
-        <v>704.3099999999999</v>
+        <v>705.3200000000001</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1053,7 +1059,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>26.25</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1064,10 +1070,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>976.5</v>
+        <v>916.45</v>
       </c>
       <c r="D3">
-        <v>-1.67</v>
+        <v>-6.15</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1076,88 +1082,88 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-9.710000000000001</v>
+        <v>-15.26</v>
       </c>
       <c r="H3">
-        <v>93.23</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="I3">
-        <v>-3.49</v>
+        <v>-7.09</v>
       </c>
       <c r="J3">
-        <v>4.33</v>
+        <v>-4.58</v>
       </c>
       <c r="K3">
-        <v>9.81</v>
+        <v>-1.44</v>
       </c>
       <c r="L3">
-        <v>11.45</v>
+        <v>3.82</v>
       </c>
       <c r="M3">
-        <v>9.710000000000001</v>
+        <v>7.26</v>
       </c>
       <c r="N3">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>997.6799999999999</v>
+        <v>983.7</v>
       </c>
       <c r="Q3">
-        <v>959.45</v>
+        <v>957.21</v>
       </c>
       <c r="R3">
-        <v>958.34</v>
+        <v>959.33</v>
       </c>
       <c r="S3">
-        <v>762.8200000000001</v>
+        <v>763.61</v>
       </c>
       <c r="T3">
-        <v>28.01</v>
+        <v>20.02</v>
       </c>
       <c r="U3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V3" t="s">
         <v>55</v>
       </c>
       <c r="W3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.19</v>
+        <v>43.18</v>
       </c>
       <c r="Z3">
-        <v>13.58</v>
+        <v>7.65</v>
       </c>
       <c r="AA3">
-        <v>8.970000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB3">
-        <v>4.61</v>
+        <v>-1.06</v>
       </c>
       <c r="AC3">
-        <v>68.47</v>
+        <v>35.45</v>
       </c>
       <c r="AD3">
-        <v>80.43000000000001</v>
+        <v>63.22</v>
       </c>
       <c r="AE3">
-        <v>44.17</v>
+        <v>46.09</v>
       </c>
       <c r="AF3">
-        <v>-62.82</v>
+        <v>-11.12</v>
       </c>
       <c r="AG3">
-        <v>1023.99</v>
+        <v>1024.53</v>
       </c>
       <c r="AH3">
-        <v>894.91</v>
+        <v>889.89</v>
       </c>
       <c r="AI3">
         <v>1054.09</v>
@@ -1166,7 +1172,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>26.19</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,58 +1183,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>200.38</v>
+        <v>199.42</v>
       </c>
       <c r="D4">
-        <v>0.01</v>
+        <v>-0.48</v>
       </c>
       <c r="E4">
-        <v>324.39</v>
+        <v>315.16</v>
       </c>
       <c r="F4">
-        <v>200.36</v>
+        <v>199.42</v>
       </c>
       <c r="G4">
-        <v>-38.23</v>
+        <v>-36.72</v>
       </c>
       <c r="H4">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.68</v>
+        <v>-1.35</v>
       </c>
       <c r="J4">
-        <v>-6.33</v>
+        <v>-5.15</v>
       </c>
       <c r="K4">
-        <v>-10.78</v>
+        <v>-10.39</v>
       </c>
       <c r="L4">
-        <v>-38</v>
+        <v>-38.52</v>
       </c>
       <c r="M4">
-        <v>-5.76</v>
+        <v>-5.71</v>
       </c>
       <c r="N4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>201.49</v>
+        <v>200.95</v>
       </c>
       <c r="Q4">
-        <v>204.58</v>
+        <v>204.06</v>
       </c>
       <c r="R4">
-        <v>212.05</v>
+        <v>211.36</v>
       </c>
       <c r="S4">
-        <v>241.32</v>
+        <v>241.05</v>
       </c>
       <c r="T4">
-        <v>-16.96</v>
+        <v>-17.27</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1243,43 +1249,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.02</v>
+        <v>30.27</v>
       </c>
       <c r="Z4">
-        <v>-3.25</v>
+        <v>-3.28</v>
       </c>
       <c r="AA4">
-        <v>-3.36</v>
+        <v>-3.34</v>
       </c>
       <c r="AB4">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AC4">
-        <v>52.59</v>
+        <v>40.66</v>
       </c>
       <c r="AD4">
-        <v>54.27</v>
+        <v>48.9</v>
       </c>
       <c r="AE4">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="AF4">
-        <v>-41.09</v>
+        <v>-26</v>
       </c>
       <c r="AG4">
-        <v>210.93</v>
+        <v>210.35</v>
       </c>
       <c r="AH4">
-        <v>198.22</v>
+        <v>197.78</v>
       </c>
       <c r="AI4">
-        <v>211.77</v>
+        <v>211.26</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>22.11</v>
+        <v>23.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1290,10 +1296,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>643.75</v>
+        <v>641.45</v>
       </c>
       <c r="D5">
-        <v>-1.3</v>
+        <v>-0.36</v>
       </c>
       <c r="E5">
         <v>949.55</v>
@@ -1302,46 +1308,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-32.2</v>
+        <v>-32.45</v>
       </c>
       <c r="H5">
-        <v>12.07</v>
+        <v>11.67</v>
       </c>
       <c r="I5">
-        <v>-7.14</v>
+        <v>-7.67</v>
       </c>
       <c r="J5">
-        <v>0.96</v>
+        <v>-0.42</v>
       </c>
       <c r="K5">
-        <v>-11.77</v>
+        <v>-10.41</v>
       </c>
       <c r="L5">
-        <v>-32.89</v>
+        <v>-32.15</v>
       </c>
       <c r="M5">
-        <v>-5.44</v>
+        <v>-5.33</v>
       </c>
       <c r="N5">
         <v>38</v>
       </c>
       <c r="O5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P5">
-        <v>666.91</v>
+        <v>656.26</v>
       </c>
       <c r="Q5">
-        <v>657.6799999999999</v>
+        <v>656.97</v>
       </c>
       <c r="R5">
-        <v>662.89</v>
+        <v>661.75</v>
       </c>
       <c r="S5">
-        <v>701.21</v>
+        <v>700.73</v>
       </c>
       <c r="T5">
-        <v>-8.19</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1356,34 +1362,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>45.71</v>
+        <v>45.27</v>
       </c>
       <c r="Z5">
-        <v>4.58</v>
+        <v>2.06</v>
       </c>
       <c r="AA5">
-        <v>5.12</v>
+        <v>4.51</v>
       </c>
       <c r="AB5">
-        <v>-0.54</v>
+        <v>-2.44</v>
       </c>
       <c r="AC5">
-        <v>39.6</v>
+        <v>35.9</v>
       </c>
       <c r="AD5">
-        <v>44.11</v>
+        <v>39.68</v>
       </c>
       <c r="AE5">
-        <v>32.66</v>
+        <v>33.25</v>
       </c>
       <c r="AF5">
-        <v>-66.17</v>
+        <v>-32.32</v>
       </c>
       <c r="AG5">
-        <v>753.85</v>
+        <v>753.41</v>
       </c>
       <c r="AH5">
-        <v>561.52</v>
+        <v>560.53</v>
       </c>
       <c r="AI5">
         <v>742.12</v>
@@ -1392,7 +1398,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>31.72</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1409,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1666.5</v>
+        <v>1655.3</v>
       </c>
       <c r="D6">
-        <v>-0.21</v>
+        <v>-0.67</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1415,46 +1421,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-19.17</v>
+        <v>-19.71</v>
       </c>
       <c r="H6">
-        <v>23.64</v>
+        <v>22.81</v>
       </c>
       <c r="I6">
-        <v>-6.38</v>
+        <v>-4.47</v>
       </c>
       <c r="J6">
-        <v>1.04</v>
+        <v>-2.03</v>
       </c>
       <c r="K6">
-        <v>-16.4</v>
+        <v>-16</v>
       </c>
       <c r="L6">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="N6">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>1692.44</v>
+        <v>1676.96</v>
       </c>
       <c r="Q6">
-        <v>1734.3</v>
+        <v>1732.33</v>
       </c>
       <c r="R6">
-        <v>1738.19</v>
+        <v>1734.95</v>
       </c>
       <c r="S6">
-        <v>1708.54</v>
+        <v>1707.78</v>
       </c>
       <c r="T6">
-        <v>-2.46</v>
+        <v>-3.07</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1469,43 +1475,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>38.66</v>
+        <v>37.2</v>
       </c>
       <c r="Z6">
-        <v>-11.4</v>
+        <v>-15.62</v>
       </c>
       <c r="AA6">
-        <v>-2.65</v>
+        <v>-5.24</v>
       </c>
       <c r="AB6">
-        <v>-8.76</v>
+        <v>-10.38</v>
       </c>
       <c r="AC6">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>4.86</v>
+        <v>1.86</v>
       </c>
       <c r="AE6">
-        <v>47.97</v>
+        <v>46.65</v>
       </c>
       <c r="AF6">
-        <v>-51.44</v>
+        <v>-42.27</v>
       </c>
       <c r="AG6">
-        <v>1812.58</v>
+        <v>1816.56</v>
       </c>
       <c r="AH6">
-        <v>1656.01</v>
+        <v>1648.09</v>
       </c>
       <c r="AI6">
-        <v>1809.97</v>
+        <v>1791.46</v>
       </c>
       <c r="AJ6" t="s">
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>31.36</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1516,58 +1522,58 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>983.2</v>
+        <v>960</v>
       </c>
       <c r="D7">
-        <v>-0.31</v>
+        <v>-2.36</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
       </c>
       <c r="F7">
-        <v>983.2</v>
+        <v>960</v>
       </c>
       <c r="G7">
-        <v>-21.99</v>
+        <v>-23.83</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-1.29</v>
+        <v>-4.06</v>
       </c>
       <c r="J7">
-        <v>-6.1</v>
+        <v>-7.87</v>
       </c>
       <c r="K7">
-        <v>-11.65</v>
+        <v>-10.75</v>
       </c>
       <c r="L7">
-        <v>-12.26</v>
+        <v>-14.21</v>
       </c>
       <c r="M7">
-        <v>4.19</v>
+        <v>3.99</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P7">
-        <v>989.7</v>
+        <v>981.58</v>
       </c>
       <c r="Q7">
-        <v>1005.75</v>
+        <v>1001.71</v>
       </c>
       <c r="R7">
-        <v>1050.79</v>
+        <v>1048.21</v>
       </c>
       <c r="S7">
-        <v>1112.38</v>
+        <v>1111.5</v>
       </c>
       <c r="T7">
-        <v>-11.61</v>
+        <v>-13.63</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1582,43 +1588,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>36.29</v>
+        <v>30.57</v>
       </c>
       <c r="Z7">
-        <v>-18.64</v>
+        <v>-20.24</v>
       </c>
       <c r="AA7">
-        <v>-19.3</v>
+        <v>-19.48</v>
       </c>
       <c r="AB7">
-        <v>0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="AC7">
-        <v>66.27</v>
+        <v>45.8</v>
       </c>
       <c r="AD7">
-        <v>65.48999999999999</v>
+        <v>58.24</v>
       </c>
       <c r="AE7">
-        <v>17.53</v>
+        <v>18.29</v>
       </c>
       <c r="AF7">
-        <v>-22.9</v>
+        <v>14.71</v>
       </c>
       <c r="AG7">
-        <v>1040.09</v>
+        <v>1037.69</v>
       </c>
       <c r="AH7">
-        <v>971.41</v>
+        <v>965.74</v>
       </c>
       <c r="AI7">
-        <v>1037.15</v>
+        <v>1024.42</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>46.76</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,10 +1635,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3186.9</v>
+        <v>3191</v>
       </c>
       <c r="D8">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1641,46 +1647,46 @@
         <v>3183.8</v>
       </c>
       <c r="G8">
-        <v>-44.57</v>
+        <v>-44.5</v>
       </c>
       <c r="H8">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="I8">
-        <v>-2.44</v>
+        <v>-2.92</v>
       </c>
       <c r="J8">
-        <v>-12.69</v>
+        <v>-12.17</v>
       </c>
       <c r="K8">
-        <v>-19.94</v>
+        <v>-16.68</v>
       </c>
       <c r="L8">
-        <v>-42.14</v>
+        <v>-41.53</v>
       </c>
       <c r="M8">
-        <v>-10.13</v>
+        <v>-9.92</v>
       </c>
       <c r="N8">
         <v>13</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P8">
-        <v>3217.94</v>
+        <v>3198.74</v>
       </c>
       <c r="Q8">
-        <v>3418.19</v>
+        <v>3393.49</v>
       </c>
       <c r="R8">
-        <v>3560.67</v>
+        <v>3554.43</v>
       </c>
       <c r="S8">
-        <v>4262.71</v>
+        <v>4254.21</v>
       </c>
       <c r="T8">
-        <v>-25.24</v>
+        <v>-24.99</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1695,34 +1701,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>26.4</v>
+        <v>26.97</v>
       </c>
       <c r="Z8">
-        <v>-119.3</v>
+        <v>-119.8</v>
       </c>
       <c r="AA8">
-        <v>-98.15000000000001</v>
+        <v>-102.48</v>
       </c>
       <c r="AB8">
-        <v>-21.15</v>
+        <v>-17.32</v>
       </c>
       <c r="AC8">
-        <v>1.18</v>
+        <v>4.03</v>
       </c>
       <c r="AD8">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AE8">
-        <v>81.72</v>
+        <v>79.52</v>
       </c>
       <c r="AF8">
-        <v>-15.56</v>
+        <v>-23.75</v>
       </c>
       <c r="AG8">
-        <v>3734.69</v>
+        <v>3699.24</v>
       </c>
       <c r="AH8">
-        <v>3101.69</v>
+        <v>3087.74</v>
       </c>
       <c r="AI8">
         <v>3417.66</v>
@@ -1731,7 +1737,7 @@
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>45.76</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1748,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>651.6</v>
+        <v>644.45</v>
       </c>
       <c r="D9">
-        <v>-1.03</v>
+        <v>-1.1</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1754,46 +1760,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-38.09</v>
+        <v>-38.77</v>
       </c>
       <c r="H9">
-        <v>21.03</v>
+        <v>19.7</v>
       </c>
       <c r="I9">
-        <v>-7.23</v>
+        <v>-5.3</v>
       </c>
       <c r="J9">
-        <v>1.11</v>
+        <v>0.37</v>
       </c>
       <c r="K9">
-        <v>-2.21</v>
+        <v>-3.35</v>
       </c>
       <c r="L9">
-        <v>-10.04</v>
+        <v>-20.4</v>
       </c>
       <c r="M9">
-        <v>40.1</v>
+        <v>39.98</v>
       </c>
       <c r="N9">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O9">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P9">
-        <v>669.4</v>
+        <v>662.1900000000001</v>
       </c>
       <c r="Q9">
-        <v>657.4</v>
+        <v>657.6799999999999</v>
       </c>
       <c r="R9">
-        <v>659.72</v>
+        <v>659.37</v>
       </c>
       <c r="S9">
-        <v>662.64</v>
+        <v>662.3</v>
       </c>
       <c r="T9">
-        <v>-1.67</v>
+        <v>-2.69</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1808,34 +1814,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.7</v>
+        <v>44.88</v>
       </c>
       <c r="Z9">
-        <v>5.02</v>
+        <v>2.73</v>
       </c>
       <c r="AA9">
-        <v>5.03</v>
+        <v>4.57</v>
       </c>
       <c r="AB9">
-        <v>-0.01</v>
+        <v>-1.84</v>
       </c>
       <c r="AC9">
-        <v>42.78</v>
+        <v>36.54</v>
       </c>
       <c r="AD9">
-        <v>48.78</v>
+        <v>42.89</v>
       </c>
       <c r="AE9">
-        <v>24.53</v>
+        <v>24.99</v>
       </c>
       <c r="AF9">
-        <v>-88.23</v>
+        <v>-78.17</v>
       </c>
       <c r="AG9">
-        <v>719.62</v>
+        <v>719.6</v>
       </c>
       <c r="AH9">
-        <v>595.1799999999999</v>
+        <v>595.77</v>
       </c>
       <c r="AI9">
         <v>727</v>
@@ -1844,7 +1850,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>33.13</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,10 +1861,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>367.5</v>
+        <v>361.9</v>
       </c>
       <c r="D10">
-        <v>1.11</v>
+        <v>-1.52</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1867,46 +1873,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-20.42</v>
+        <v>-21.63</v>
       </c>
       <c r="H10">
-        <v>6.44</v>
+        <v>4.82</v>
       </c>
       <c r="I10">
-        <v>-1.95</v>
+        <v>-1.43</v>
       </c>
       <c r="J10">
-        <v>0.96</v>
+        <v>2.81</v>
       </c>
       <c r="K10">
-        <v>-4.92</v>
+        <v>-6.12</v>
       </c>
       <c r="L10">
-        <v>-7.03</v>
+        <v>-8.5</v>
       </c>
       <c r="M10">
-        <v>22.21</v>
+        <v>21.59</v>
       </c>
       <c r="N10">
         <v>74</v>
       </c>
       <c r="O10">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P10">
-        <v>366.82</v>
+        <v>365.77</v>
       </c>
       <c r="Q10">
-        <v>364.06</v>
+        <v>364.57</v>
       </c>
       <c r="R10">
-        <v>371.95</v>
+        <v>371.64</v>
       </c>
       <c r="S10">
-        <v>387.05</v>
+        <v>386.98</v>
       </c>
       <c r="T10">
-        <v>-5.05</v>
+        <v>-6.48</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1921,34 +1927,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>49.53</v>
+        <v>44.42</v>
       </c>
       <c r="Z10">
-        <v>-1.14</v>
+        <v>-1.43</v>
       </c>
       <c r="AA10">
-        <v>-1.92</v>
+        <v>-1.82</v>
       </c>
       <c r="AB10">
-        <v>0.78</v>
+        <v>0.39</v>
       </c>
       <c r="AC10">
-        <v>48.93</v>
+        <v>35.64</v>
       </c>
       <c r="AD10">
-        <v>52.85</v>
+        <v>43.89</v>
       </c>
       <c r="AE10">
-        <v>7.2</v>
+        <v>7.22</v>
       </c>
       <c r="AF10">
-        <v>-63.67</v>
+        <v>-35.11</v>
       </c>
       <c r="AG10">
-        <v>377.82</v>
+        <v>377.13</v>
       </c>
       <c r="AH10">
-        <v>350.31</v>
+        <v>352.01</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -1957,7 +1963,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>39.66</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1968,10 +1974,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>187.97</v>
+        <v>186.3</v>
       </c>
       <c r="D11">
-        <v>-0.03</v>
+        <v>-0.89</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1980,46 +1986,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-13.24</v>
+        <v>-14.01</v>
       </c>
       <c r="H11">
-        <v>19.41</v>
+        <v>18.35</v>
       </c>
       <c r="I11">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="J11">
-        <v>-0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="K11">
-        <v>-0.84</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L11">
-        <v>11.93</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M11">
-        <v>11.42</v>
+        <v>11.02</v>
       </c>
       <c r="N11">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="O11">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P11">
-        <v>187.04</v>
+        <v>187.62</v>
       </c>
       <c r="Q11">
-        <v>185.74</v>
+        <v>185.73</v>
       </c>
       <c r="R11">
         <v>186.27</v>
       </c>
       <c r="S11">
-        <v>191.5</v>
+        <v>191.65</v>
       </c>
       <c r="T11">
-        <v>-1.85</v>
+        <v>-2.79</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2034,31 +2040,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>53.08</v>
+        <v>50.03</v>
       </c>
       <c r="Z11">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AA11">
-        <v>-0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="AB11">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="AC11">
-        <v>76.09999999999999</v>
+        <v>57.03</v>
       </c>
       <c r="AD11">
-        <v>67.13</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="AE11">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AF11">
-        <v>-46.63</v>
+        <v>-52.99</v>
       </c>
       <c r="AG11">
-        <v>190.26</v>
+        <v>190.24</v>
       </c>
       <c r="AH11">
         <v>181.21</v>
@@ -2070,7 +2076,7 @@
         <v>56</v>
       </c>
       <c r="AK11">
-        <v>24.68</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2081,10 +2087,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2082</v>
+        <v>2070.7</v>
       </c>
       <c r="D12">
-        <v>-0.24</v>
+        <v>-0.54</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2093,46 +2099,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-35.38</v>
+        <v>-35.73</v>
       </c>
       <c r="H12">
-        <v>5.01</v>
+        <v>4.44</v>
       </c>
       <c r="I12">
-        <v>-1.09</v>
+        <v>-2.72</v>
       </c>
       <c r="J12">
-        <v>-8.279999999999999</v>
+        <v>-7.9</v>
       </c>
       <c r="K12">
-        <v>-0.76</v>
+        <v>1.93</v>
       </c>
       <c r="L12">
-        <v>-29.84</v>
+        <v>-29.96</v>
       </c>
       <c r="M12">
-        <v>-9.09</v>
+        <v>-8.91</v>
       </c>
       <c r="N12">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O12">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P12">
-        <v>2098.46</v>
+        <v>2086.86</v>
       </c>
       <c r="Q12">
-        <v>2222.4</v>
+        <v>2208.83</v>
       </c>
       <c r="R12">
-        <v>2290.85</v>
+        <v>2286.89</v>
       </c>
       <c r="S12">
-        <v>2504.35</v>
+        <v>2499.16</v>
       </c>
       <c r="T12">
-        <v>-16.86</v>
+        <v>-17.14</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2147,34 +2153,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>32.24</v>
+        <v>31.26</v>
       </c>
       <c r="Z12">
-        <v>-58.59</v>
+        <v>-60.58</v>
       </c>
       <c r="AA12">
-        <v>-43.07</v>
+        <v>-46.57</v>
       </c>
       <c r="AB12">
-        <v>-15.52</v>
+        <v>-14.01</v>
       </c>
       <c r="AC12">
-        <v>1.06</v>
+        <v>0.35</v>
       </c>
       <c r="AD12">
-        <v>4.29</v>
+        <v>1.67</v>
       </c>
       <c r="AE12">
-        <v>60.12</v>
+        <v>59.32</v>
       </c>
       <c r="AF12">
-        <v>14.65</v>
+        <v>-17.96</v>
       </c>
       <c r="AG12">
-        <v>2426.8</v>
+        <v>2415.81</v>
       </c>
       <c r="AH12">
-        <v>2017.99</v>
+        <v>2001.85</v>
       </c>
       <c r="AI12">
         <v>2244.5</v>
@@ -2183,7 +2189,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>41.32</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2194,10 +2200,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4884</v>
+        <v>4819.5</v>
       </c>
       <c r="D13">
-        <v>1.07</v>
+        <v>-1.32</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2206,88 +2212,88 @@
         <v>3327.3</v>
       </c>
       <c r="G13">
-        <v>-5.52</v>
+        <v>-6.77</v>
       </c>
       <c r="H13">
-        <v>46.79</v>
+        <v>44.85</v>
       </c>
       <c r="I13">
-        <v>1.78</v>
+        <v>-1.14</v>
       </c>
       <c r="J13">
-        <v>-4.24</v>
+        <v>-6.22</v>
       </c>
       <c r="K13">
-        <v>14.19</v>
+        <v>9.43</v>
       </c>
       <c r="L13">
-        <v>41.26</v>
+        <v>40.13</v>
       </c>
       <c r="M13">
-        <v>18.83</v>
+        <v>18.06</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P13">
-        <v>4880</v>
+        <v>4868.9</v>
       </c>
       <c r="Q13">
-        <v>4963.21</v>
+        <v>4945.72</v>
       </c>
       <c r="R13">
-        <v>4949.57</v>
+        <v>4953.2</v>
       </c>
       <c r="S13">
-        <v>4392.37</v>
+        <v>4397.22</v>
       </c>
       <c r="T13">
-        <v>11.19</v>
+        <v>9.6</v>
       </c>
       <c r="U13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V13" t="s">
         <v>55</v>
       </c>
       <c r="W13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13">
-        <v>45.57</v>
+        <v>41.06</v>
       </c>
       <c r="Z13">
-        <v>-31.36</v>
+        <v>-35.86</v>
       </c>
       <c r="AA13">
-        <v>-13.88</v>
+        <v>-18.27</v>
       </c>
       <c r="AB13">
-        <v>-17.48</v>
+        <v>-17.59</v>
       </c>
       <c r="AC13">
-        <v>48.46</v>
+        <v>43.24</v>
       </c>
       <c r="AD13">
-        <v>47.41</v>
+        <v>46.15</v>
       </c>
       <c r="AE13">
-        <v>84.23</v>
+        <v>83.5</v>
       </c>
       <c r="AF13">
-        <v>-38.49</v>
+        <v>5.68</v>
       </c>
       <c r="AG13">
-        <v>5165.06</v>
+        <v>5132.46</v>
       </c>
       <c r="AH13">
-        <v>4761.35</v>
+        <v>4758.98</v>
       </c>
       <c r="AI13">
         <v>5062.11</v>
@@ -2296,7 +2302,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>38.54</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2307,10 +2313,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2669.3</v>
+        <v>2626</v>
       </c>
       <c r="D14">
-        <v>-1.14</v>
+        <v>-1.62</v>
       </c>
       <c r="E14">
         <v>4889.77</v>
@@ -2319,25 +2325,25 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-45.41</v>
+        <v>-46.3</v>
       </c>
       <c r="H14">
-        <v>21.67</v>
+        <v>19.69</v>
       </c>
       <c r="I14">
-        <v>-5.48</v>
+        <v>-6.73</v>
       </c>
       <c r="J14">
-        <v>-8.210000000000001</v>
+        <v>-8.77</v>
       </c>
       <c r="K14">
-        <v>-18.08</v>
+        <v>-20</v>
       </c>
       <c r="L14">
-        <v>-46.65</v>
+        <v>-46.23</v>
       </c>
       <c r="M14">
-        <v>21.76</v>
+        <v>21.08</v>
       </c>
       <c r="N14">
         <v>7</v>
@@ -2346,19 +2352,19 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>2748.34</v>
+        <v>2710.44</v>
       </c>
       <c r="Q14">
-        <v>2802.87</v>
+        <v>2789.27</v>
       </c>
       <c r="R14">
-        <v>2899.6</v>
+        <v>2895.27</v>
       </c>
       <c r="S14">
-        <v>2885.39</v>
+        <v>2878.12</v>
       </c>
       <c r="T14">
-        <v>-7.49</v>
+        <v>-8.76</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2373,43 +2379,43 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>29.91</v>
+        <v>26.9</v>
       </c>
       <c r="Z14">
-        <v>-51.68</v>
+        <v>-59.32</v>
       </c>
       <c r="AA14">
-        <v>-44.66</v>
+        <v>-47.59</v>
       </c>
       <c r="AB14">
-        <v>-7.02</v>
+        <v>-11.73</v>
       </c>
       <c r="AC14">
-        <v>26.98</v>
+        <v>6.07</v>
       </c>
       <c r="AD14">
-        <v>50.55</v>
+        <v>27.55</v>
       </c>
       <c r="AE14">
-        <v>60.28</v>
+        <v>59.85</v>
       </c>
       <c r="AF14">
-        <v>60.82</v>
+        <v>-6.88</v>
       </c>
       <c r="AG14">
-        <v>2915.68</v>
+        <v>2918.22</v>
       </c>
       <c r="AH14">
-        <v>2690.06</v>
+        <v>2660.32</v>
       </c>
       <c r="AI14">
-        <v>2863.84</v>
+        <v>2818.99</v>
       </c>
       <c r="AJ14" t="s">
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>48.22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2420,58 +2426,58 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>215.65</v>
+        <v>207.55</v>
       </c>
       <c r="D15">
-        <v>0.24</v>
+        <v>-3.76</v>
       </c>
       <c r="E15">
         <v>380.65</v>
       </c>
       <c r="F15">
-        <v>213</v>
+        <v>207.55</v>
       </c>
       <c r="G15">
-        <v>-43.35</v>
+        <v>-45.47</v>
       </c>
       <c r="H15">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0.19</v>
+        <v>-4.1</v>
       </c>
       <c r="J15">
-        <v>-6.21</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="K15">
-        <v>-9.02</v>
+        <v>-13.47</v>
       </c>
       <c r="L15">
-        <v>-38.61</v>
+        <v>-42.27</v>
       </c>
       <c r="M15">
-        <v>11.94</v>
+        <v>11.87</v>
       </c>
       <c r="N15">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="O15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>215.92</v>
+        <v>214.14</v>
       </c>
       <c r="Q15">
-        <v>222.28</v>
+        <v>221.18</v>
       </c>
       <c r="R15">
-        <v>228.09</v>
+        <v>227.41</v>
       </c>
       <c r="S15">
-        <v>251.09</v>
+        <v>250.68</v>
       </c>
       <c r="T15">
-        <v>-14.11</v>
+        <v>-17.2</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2486,34 +2492,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>38.81</v>
+        <v>30.94</v>
       </c>
       <c r="Z15">
-        <v>-4.15</v>
+        <v>-4.71</v>
       </c>
       <c r="AA15">
-        <v>-3.66</v>
+        <v>-3.87</v>
       </c>
       <c r="AB15">
-        <v>-0.49</v>
+        <v>-0.84</v>
       </c>
       <c r="AC15">
-        <v>28.24</v>
+        <v>18.15</v>
       </c>
       <c r="AD15">
-        <v>28.7</v>
+        <v>24.85</v>
       </c>
       <c r="AE15">
-        <v>7.56</v>
+        <v>7.95</v>
       </c>
       <c r="AF15">
-        <v>-40.04</v>
+        <v>206.15</v>
       </c>
       <c r="AG15">
-        <v>236.29</v>
+        <v>236.22</v>
       </c>
       <c r="AH15">
-        <v>208.26</v>
+        <v>206.14</v>
       </c>
       <c r="AI15">
         <v>237.02</v>
@@ -2522,7 +2528,7 @@
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>28.83</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2533,10 +2539,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>34.44</v>
+        <v>36.19</v>
       </c>
       <c r="D16">
-        <v>-1.66</v>
+        <v>5.08</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2545,46 +2551,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-41.31</v>
+        <v>-38.33</v>
       </c>
       <c r="H16">
-        <v>9.82</v>
+        <v>15.4</v>
       </c>
       <c r="I16">
-        <v>-3.61</v>
+        <v>2.35</v>
       </c>
       <c r="J16">
-        <v>-7.94</v>
+        <v>-0.74</v>
       </c>
       <c r="K16">
-        <v>-18.02</v>
+        <v>-15.46</v>
       </c>
       <c r="L16">
-        <v>-39.83</v>
+        <v>-36.39</v>
       </c>
       <c r="M16">
-        <v>-0.21</v>
+        <v>0.87</v>
       </c>
       <c r="N16">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O16">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P16">
-        <v>35.21</v>
+        <v>35.38</v>
       </c>
       <c r="Q16">
-        <v>36.57</v>
+        <v>36.44</v>
       </c>
       <c r="R16">
-        <v>37.99</v>
+        <v>37.91</v>
       </c>
       <c r="S16">
-        <v>42.04</v>
+        <v>41.95</v>
       </c>
       <c r="T16">
-        <v>-18.07</v>
+        <v>-13.73</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2599,34 +2605,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>33.4</v>
+        <v>47.09</v>
       </c>
       <c r="Z16">
-        <v>-0.91</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AA16">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
       <c r="AB16">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="AC16">
-        <v>40.83</v>
+        <v>53.39</v>
       </c>
       <c r="AD16">
-        <v>49.3</v>
+        <v>49.74</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AF16">
-        <v>-55.06</v>
+        <v>1893.81</v>
       </c>
       <c r="AG16">
-        <v>39.29</v>
+        <v>38.95</v>
       </c>
       <c r="AH16">
-        <v>33.84</v>
+        <v>33.93</v>
       </c>
       <c r="AI16">
         <v>37.92</v>
@@ -2635,7 +2641,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>17.18</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2646,10 +2652,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1118.2</v>
+        <v>1135.5</v>
       </c>
       <c r="D17">
-        <v>0.43</v>
+        <v>1.55</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2658,46 +2664,46 @@
         <v>1100.8</v>
       </c>
       <c r="G17">
-        <v>-28.16</v>
+        <v>-27.04</v>
       </c>
       <c r="H17">
-        <v>1.58</v>
+        <v>3.15</v>
       </c>
       <c r="I17">
-        <v>0.66</v>
+        <v>-0.58</v>
       </c>
       <c r="J17">
-        <v>-8.119999999999999</v>
+        <v>-6.74</v>
       </c>
       <c r="K17">
-        <v>-13.71</v>
+        <v>-11.12</v>
       </c>
       <c r="L17">
-        <v>-18.49</v>
+        <v>-17.02</v>
       </c>
       <c r="M17">
-        <v>-1.24</v>
+        <v>-0.79</v>
       </c>
       <c r="N17">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O17">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="P17">
-        <v>1120.9</v>
+        <v>1119.58</v>
       </c>
       <c r="Q17">
-        <v>1149.86</v>
+        <v>1146.64</v>
       </c>
       <c r="R17">
-        <v>1233.71</v>
+        <v>1229.57</v>
       </c>
       <c r="S17">
-        <v>1335.35</v>
+        <v>1334.37</v>
       </c>
       <c r="T17">
-        <v>-16.26</v>
+        <v>-14.9</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2712,34 +2718,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>38.72</v>
+        <v>43.06</v>
       </c>
       <c r="Z17">
-        <v>-33.16</v>
+        <v>-30.59</v>
       </c>
       <c r="AA17">
-        <v>-34.34</v>
+        <v>-33.59</v>
       </c>
       <c r="AB17">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="AC17">
         <v>88.12</v>
       </c>
       <c r="AD17">
-        <v>80.56</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="AE17">
-        <v>30.02</v>
+        <v>29.75</v>
       </c>
       <c r="AF17">
-        <v>-50.54</v>
+        <v>30.82</v>
       </c>
       <c r="AG17">
-        <v>1209.44</v>
+        <v>1201.59</v>
       </c>
       <c r="AH17">
-        <v>1090.28</v>
+        <v>1091.68</v>
       </c>
       <c r="AI17">
         <v>1203.06</v>
@@ -2748,7 +2754,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>39.63</v>
+        <v>35.44</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +2895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2929,2315 +2935,2463 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="F5" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-0.16</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>7.29</v>
-      </c>
-      <c r="D8" s="6">
-        <v>4.33</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-5.9</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.33</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4.13</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.96</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-3.17</v>
+      <c r="D10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.76</v>
+        <v>0.8</v>
       </c>
       <c r="D11" s="6">
-        <v>1.04</v>
+        <v>-1.04</v>
       </c>
       <c r="E11" s="7">
-        <v>2.8</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-7</v>
+        <v>4.33</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.1</v>
+        <v>-4.58</v>
       </c>
       <c r="E12" s="7">
-        <v>0.9</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-13.15</v>
+        <v>-6.33</v>
       </c>
       <c r="D13" s="6">
-        <v>-12.69</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.46</v>
+        <v>-5.15</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>2.17</v>
+        <v>0.96</v>
       </c>
       <c r="D14" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.06</v>
+        <v>-0.42</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-1.93</v>
+        <v>1.04</v>
       </c>
       <c r="D15" s="6">
-        <v>0.96</v>
+        <v>-2.03</v>
       </c>
       <c r="E15" s="7">
-        <v>2.89</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>0.58</v>
+        <v>-6.1</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.6</v>
+        <v>-7.87</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-9.109999999999999</v>
+        <v>-12.69</v>
       </c>
       <c r="D17" s="6">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.83</v>
+        <v>-12.17</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.52</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.7</v>
+        <v>1.11</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.24</v>
+        <v>0.37</v>
       </c>
       <c r="E18" s="7">
-        <v>1.46</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.85</v>
+        <v>0.96</v>
       </c>
       <c r="D19" s="6">
-        <v>-8.210000000000001</v>
+        <v>2.81</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.36</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.15</v>
+        <v>-0.02</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.21</v>
+        <v>-0.27</v>
       </c>
       <c r="E20" s="7">
-        <v>0.9399999999999999</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-6.74</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D21" s="6">
-        <v>-7.94</v>
+        <v>-7.9</v>
       </c>
       <c r="E21" s="8">
-        <v>-1.2</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-10.43</v>
+        <v>-4.24</v>
       </c>
       <c r="D22" s="6">
-        <v>-8.119999999999999</v>
+        <v>-6.22</v>
       </c>
       <c r="E22" s="7">
-        <v>2.31</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>0.3</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.11</v>
+        <v>-8.77</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>2.88</v>
+        <v>-6.21</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-6.37</v>
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-1.85</v>
+        <v>-7.94</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.68</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.17</v>
+        <v>-0.74</v>
+      </c>
+      <c r="E25" s="8">
+        <v>7.2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-16.31</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="D26" s="6">
-        <v>-7.14</v>
-      </c>
-      <c r="E26" s="7">
-        <v>9.17</v>
+        <v>-6.74</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.38</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-6.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D27" s="6">
-        <v>-6.38</v>
+        <v>-4.56</v>
       </c>
       <c r="E27" s="7">
-        <v>0.41</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.7</v>
+        <v>-3.49</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.29</v>
+        <v>-7.09</v>
       </c>
       <c r="E28" s="7">
-        <v>1.41</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-5.85</v>
+        <v>-1.68</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3.41</v>
+        <v>-1.35</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.33</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-8.470000000000001</v>
+        <v>-7.14</v>
       </c>
       <c r="D30" s="6">
-        <v>-7.23</v>
+        <v>-7.67</v>
       </c>
       <c r="E30" s="7">
-        <v>1.24</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-1.5</v>
+        <v>-6.38</v>
       </c>
       <c r="D31" s="6">
-        <v>-1.95</v>
+        <v>-4.47</v>
       </c>
       <c r="E31" s="8">
-        <v>-0.45</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>0.39</v>
+        <v>-1.29</v>
       </c>
       <c r="D32" s="6">
-        <v>1.31</v>
+        <v>-4.06</v>
       </c>
       <c r="E32" s="7">
-        <v>0.92</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-4.7</v>
+        <v>-2.44</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.09</v>
+        <v>-2.92</v>
       </c>
       <c r="E33" s="7">
-        <v>3.61</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-0.18</v>
+        <v>-7.23</v>
       </c>
       <c r="D34" s="6">
-        <v>1.78</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.96</v>
+        <v>-5.3</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.93</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-3.19</v>
+        <v>-1.95</v>
       </c>
       <c r="D35" s="6">
-        <v>-5.48</v>
+        <v>-1.43</v>
       </c>
       <c r="E35" s="8">
-        <v>-2.29</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.99</v>
+        <v>1.31</v>
       </c>
       <c r="D36" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.18</v>
+        <v>1.58</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-4.42</v>
+        <v>-1.09</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.61</v>
+        <v>-2.72</v>
       </c>
       <c r="E37" s="7">
-        <v>0.8100000000000001</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.9</v>
+        <v>1.78</v>
       </c>
       <c r="D38" s="6">
-        <v>0.66</v>
+        <v>-1.14</v>
       </c>
       <c r="E38" s="7">
-        <v>2.56</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-6.03</v>
+        <v>-5.48</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.54</v>
+        <v>-6.73</v>
       </c>
       <c r="E39" s="7">
-        <v>0.49</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>9.220000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="D40" s="6">
-        <v>11.45</v>
+        <v>-4.1</v>
       </c>
       <c r="E40" s="7">
-        <v>2.23</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>-39.55</v>
+        <v>-3.61</v>
       </c>
       <c r="D41" s="6">
-        <v>-38</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.55</v>
+        <v>2.35</v>
+      </c>
+      <c r="E41" s="8">
+        <v>5.96</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>-33.35</v>
+        <v>0.66</v>
       </c>
       <c r="D42" s="6">
-        <v>-32.89</v>
+        <v>-0.58</v>
       </c>
       <c r="E42" s="7">
-        <v>0.46</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.85</v>
+        <v>-5.54</v>
       </c>
       <c r="D43" s="6">
-        <v>0.82</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.67</v>
+        <v>-5.45</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.73</v>
+        <v>11.45</v>
       </c>
       <c r="D44" s="6">
-        <v>-12.26</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.53</v>
+        <v>3.82</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-7.63</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-43.37</v>
+        <v>-38</v>
       </c>
       <c r="D45" s="6">
-        <v>-42.14</v>
+        <v>-38.52</v>
       </c>
       <c r="E45" s="7">
-        <v>1.23</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-9.76</v>
+        <v>-32.89</v>
       </c>
       <c r="D46" s="6">
-        <v>-10.04</v>
+        <v>-32.15</v>
       </c>
       <c r="E46" s="8">
-        <v>-0.28</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-8.289999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D47" s="6">
-        <v>-7.03</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7">
-        <v>1.26</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>11.9</v>
+        <v>-12.26</v>
       </c>
       <c r="D48" s="6">
-        <v>11.93</v>
+        <v>-14.21</v>
       </c>
       <c r="E48" s="7">
-        <v>0.03</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-31.79</v>
+        <v>-42.14</v>
       </c>
       <c r="D49" s="6">
-        <v>-29.84</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.95</v>
+        <v>-41.53</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.61</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>39.38</v>
+        <v>-10.04</v>
       </c>
       <c r="D50" s="6">
-        <v>41.26</v>
+        <v>-20.4</v>
       </c>
       <c r="E50" s="7">
-        <v>1.88</v>
+        <v>-10.36</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-46.77</v>
+        <v>-7.03</v>
       </c>
       <c r="D51" s="6">
-        <v>-46.65</v>
+        <v>-8.5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.12</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-40.77</v>
+        <v>11.93</v>
       </c>
       <c r="D52" s="6">
-        <v>-38.61</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E52" s="7">
-        <v>2.16</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-39.31</v>
+        <v>-29.84</v>
       </c>
       <c r="D53" s="6">
-        <v>-39.83</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.52</v>
+        <v>-29.96</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-21.34</v>
+        <v>41.26</v>
       </c>
       <c r="D54" s="6">
-        <v>-18.49</v>
+        <v>40.13</v>
       </c>
       <c r="E54" s="7">
-        <v>2.85</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>1.13</v>
+        <v>-46.65</v>
       </c>
       <c r="D55" s="6">
-        <v>2.79</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.66</v>
+        <v>-46.23</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>15.06</v>
+        <v>-38.61</v>
       </c>
       <c r="D56" s="6">
-        <v>9.81</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-5.25</v>
+        <v>-42.27</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-3.66</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>-11.94</v>
+        <v>-39.83</v>
       </c>
       <c r="D57" s="6">
-        <v>-10.78</v>
-      </c>
-      <c r="E57" s="7">
-        <v>1.16</v>
+        <v>-36.39</v>
+      </c>
+      <c r="E57" s="8">
+        <v>3.44</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-12.6</v>
+        <v>-18.49</v>
       </c>
       <c r="D58" s="6">
-        <v>-11.77</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.83</v>
+        <v>-17.02</v>
+      </c>
+      <c r="E58" s="8">
+        <v>1.47</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-16.16</v>
+        <v>2.79</v>
       </c>
       <c r="D59" s="6">
-        <v>-16.4</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-0.24</v>
+        <v>-0.41</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-12.82</v>
+        <v>9.81</v>
       </c>
       <c r="D60" s="6">
-        <v>-11.65</v>
+        <v>-1.44</v>
       </c>
       <c r="E60" s="7">
-        <v>1.17</v>
+        <v>-11.25</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-20.96</v>
+        <v>-10.78</v>
       </c>
       <c r="D61" s="6">
-        <v>-19.94</v>
-      </c>
-      <c r="E61" s="7">
-        <v>1.02</v>
+        <v>-10.39</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.39</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-3.02</v>
+        <v>-11.77</v>
       </c>
       <c r="D62" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="E62" s="7">
-        <v>0.8100000000000001</v>
+        <v>-10.41</v>
+      </c>
+      <c r="E62" s="8">
+        <v>1.36</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-6.56</v>
+        <v>-16.4</v>
       </c>
       <c r="D63" s="6">
-        <v>-4.92</v>
-      </c>
-      <c r="E63" s="7">
-        <v>1.64</v>
+        <v>-16</v>
+      </c>
+      <c r="E63" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-0.37</v>
+        <v>-11.65</v>
       </c>
       <c r="D64" s="6">
-        <v>-0.84</v>
+        <v>-10.75</v>
       </c>
       <c r="E64" s="8">
-        <v>-0.47</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-0.37</v>
+        <v>-19.94</v>
       </c>
       <c r="D65" s="6">
-        <v>-0.76</v>
+        <v>-16.68</v>
       </c>
       <c r="E65" s="8">
-        <v>-0.39</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>12.61</v>
+        <v>-2.21</v>
       </c>
       <c r="D66" s="6">
-        <v>14.19</v>
+        <v>-3.35</v>
       </c>
       <c r="E66" s="7">
-        <v>1.58</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-16.05</v>
+        <v>-4.92</v>
       </c>
       <c r="D67" s="6">
-        <v>-18.08</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.03</v>
+        <v>-6.12</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-12.68</v>
+        <v>-0.84</v>
       </c>
       <c r="D68" s="6">
-        <v>-9.02</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E68" s="7">
-        <v>3.66</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-18.14</v>
+        <v>-0.76</v>
       </c>
       <c r="D69" s="6">
-        <v>-18.02</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0.12</v>
+        <v>1.93</v>
+      </c>
+      <c r="E69" s="8">
+        <v>2.69</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-14.51</v>
+        <v>14.19</v>
       </c>
       <c r="D70" s="6">
-        <v>-13.71</v>
+        <v>9.43</v>
       </c>
       <c r="E70" s="7">
-        <v>0.8</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-5.28</v>
+        <v>-18.08</v>
       </c>
       <c r="D71" s="6">
-        <v>-3.39</v>
+        <v>-20</v>
       </c>
       <c r="E71" s="7">
-        <v>1.89</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-8.18</v>
+        <v>-9.02</v>
       </c>
       <c r="D72" s="6">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-1.53</v>
+        <v>-13.47</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4.45</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>-32.01</v>
+        <v>-18.02</v>
       </c>
       <c r="D73" s="6">
-        <v>-32.2</v>
+        <v>-15.46</v>
       </c>
       <c r="E73" s="8">
-        <v>-0.19</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>-19</v>
+        <v>-13.71</v>
       </c>
       <c r="D74" s="6">
-        <v>-19.17</v>
+        <v>-11.12</v>
       </c>
       <c r="E74" s="8">
-        <v>-0.17</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-21.74</v>
+        <v>-3.39</v>
       </c>
       <c r="D75" s="6">
-        <v>-21.99</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-0.25</v>
+        <v>-5.49</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-44.63</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="D76" s="6">
-        <v>-44.57</v>
+        <v>-15.26</v>
       </c>
       <c r="E76" s="7">
-        <v>0.06</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-37.45</v>
+        <v>-38.23</v>
       </c>
       <c r="D77" s="6">
-        <v>-38.09</v>
+        <v>-36.72</v>
       </c>
       <c r="E77" s="8">
-        <v>-0.64</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-21.3</v>
+        <v>-32.2</v>
       </c>
       <c r="D78" s="6">
-        <v>-20.42</v>
+        <v>-32.45</v>
       </c>
       <c r="E78" s="7">
-        <v>0.88</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-13.22</v>
+        <v>-19.17</v>
       </c>
       <c r="D79" s="6">
-        <v>-13.24</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.02</v>
+        <v>-19.71</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-35.22</v>
+        <v>-21.99</v>
       </c>
       <c r="D80" s="6">
-        <v>-35.38</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-0.16</v>
+        <v>-23.83</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-6.51</v>
+        <v>-44.57</v>
       </c>
       <c r="D81" s="6">
-        <v>-5.52</v>
-      </c>
-      <c r="E81" s="7">
-        <v>0.99</v>
+        <v>-44.5</v>
+      </c>
+      <c r="E81" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-46.03</v>
+        <v>-38.09</v>
       </c>
       <c r="D82" s="6">
-        <v>-45.41</v>
+        <v>-38.77</v>
       </c>
       <c r="E82" s="7">
-        <v>0.62</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-43.48</v>
+        <v>-20.42</v>
       </c>
       <c r="D83" s="6">
-        <v>-43.35</v>
+        <v>-21.63</v>
       </c>
       <c r="E83" s="7">
-        <v>0.13</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-40.32</v>
+        <v>-13.24</v>
       </c>
       <c r="D84" s="6">
-        <v>-41.31</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.99</v>
+        <v>-14.01</v>
+      </c>
+      <c r="E84" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-28.46</v>
+        <v>-35.38</v>
       </c>
       <c r="D85" s="6">
-        <v>-28.16</v>
+        <v>-35.73</v>
       </c>
       <c r="E85" s="7">
-        <v>0.3</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>728.8</v>
+        <v>-5.52</v>
       </c>
       <c r="D86" s="6">
-        <v>726.8</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-2</v>
+        <v>-6.77</v>
+      </c>
+      <c r="E86" s="7">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>993.05</v>
+        <v>-45.41</v>
       </c>
       <c r="D87" s="6">
-        <v>976.5</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-16.55</v>
+        <v>-46.3</v>
+      </c>
+      <c r="E87" s="7">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>200.36</v>
+        <v>-43.35</v>
       </c>
       <c r="D88" s="6">
-        <v>200.38</v>
+        <v>-45.47</v>
       </c>
       <c r="E88" s="7">
-        <v>0.02</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>652.2</v>
+        <v>-41.31</v>
       </c>
       <c r="D89" s="6">
-        <v>643.75</v>
+        <v>-38.33</v>
       </c>
       <c r="E89" s="8">
-        <v>-8.449999999999999</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>1670</v>
+        <v>-28.16</v>
       </c>
       <c r="D90" s="6">
-        <v>1666.5</v>
+        <v>-27.04</v>
       </c>
       <c r="E90" s="8">
-        <v>-3.5</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>986.3</v>
+        <v>726.8</v>
       </c>
       <c r="D91" s="6">
-        <v>983.2</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-3.1</v>
+        <v>711</v>
+      </c>
+      <c r="E91" s="7">
+        <v>-15.8</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>3183.8</v>
+        <v>976.5</v>
       </c>
       <c r="D92" s="6">
-        <v>3186.9</v>
+        <v>916.45</v>
       </c>
       <c r="E92" s="7">
-        <v>3.1</v>
+        <v>-60.05</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>658.35</v>
+        <v>200.38</v>
       </c>
       <c r="D93" s="6">
-        <v>651.6</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-6.75</v>
+        <v>199.42</v>
+      </c>
+      <c r="E93" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>363.45</v>
+        <v>643.75</v>
       </c>
       <c r="D94" s="6">
-        <v>367.5</v>
+        <v>641.45</v>
       </c>
       <c r="E94" s="7">
-        <v>4.05</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>188.02</v>
+        <v>1666.5</v>
       </c>
       <c r="D95" s="6">
-        <v>187.97</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-0.05</v>
+        <v>1655.3</v>
+      </c>
+      <c r="E95" s="7">
+        <v>-11.2</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>2087</v>
+        <v>983.2</v>
       </c>
       <c r="D96" s="6">
-        <v>2082</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-5</v>
+        <v>960</v>
+      </c>
+      <c r="E96" s="7">
+        <v>-23.2</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>4832.5</v>
+        <v>3186.9</v>
       </c>
       <c r="D97" s="6">
-        <v>4884</v>
-      </c>
-      <c r="E97" s="7">
-        <v>51.5</v>
+        <v>3191</v>
+      </c>
+      <c r="E97" s="8">
+        <v>4.1</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>2700</v>
+        <v>651.6</v>
       </c>
       <c r="D98" s="6">
-        <v>2669.3</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-30.7</v>
+        <v>644.45</v>
+      </c>
+      <c r="E98" s="7">
+        <v>-7.15</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>215.13</v>
+        <v>367.5</v>
       </c>
       <c r="D99" s="6">
-        <v>215.65</v>
+        <v>361.9</v>
       </c>
       <c r="E99" s="7">
-        <v>0.52</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>35.02</v>
+        <v>187.97</v>
       </c>
       <c r="D100" s="6">
-        <v>34.44</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-0.58</v>
+        <v>186.3</v>
+      </c>
+      <c r="E100" s="7">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>1113.4</v>
+        <v>2082</v>
       </c>
       <c r="D101" s="6">
-        <v>1118.2</v>
+        <v>2070.7</v>
       </c>
       <c r="E101" s="7">
-        <v>4.8</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>32</v>
+        <v>4884</v>
       </c>
       <c r="D102" s="6">
-        <v>26</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-6</v>
+        <v>4819.5</v>
+      </c>
+      <c r="E102" s="7">
+        <v>-64.5</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C103" s="6">
-        <v>7</v>
+        <v>2669.3</v>
       </c>
       <c r="D103" s="6">
-        <v>13</v>
+        <v>2626</v>
       </c>
       <c r="E103" s="7">
-        <v>6</v>
+        <v>-43.3</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C104" s="6">
-        <v>74</v>
+        <v>215.65</v>
       </c>
       <c r="D104" s="6">
-        <v>68</v>
-      </c>
-      <c r="E104" s="8">
-        <v>-6</v>
+        <v>207.55</v>
+      </c>
+      <c r="E104" s="7">
+        <v>-8.1</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C105" s="6">
-        <v>68</v>
+        <v>34.44</v>
       </c>
       <c r="D105" s="6">
-        <v>74</v>
-      </c>
-      <c r="E105" s="7">
-        <v>6</v>
+        <v>36.19</v>
+      </c>
+      <c r="E105" s="8">
+        <v>1.75</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C106" s="6">
-        <v>13</v>
+        <v>1118.2</v>
       </c>
       <c r="D106" s="6">
-        <v>7</v>
+        <v>1135.5</v>
       </c>
       <c r="E106" s="8">
-        <v>-6</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="D107" s="6">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="E107" s="7">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>50.83</v>
+        <v>26</v>
       </c>
       <c r="D108" s="6">
-        <v>49.85</v>
+        <v>32</v>
       </c>
       <c r="E108" s="8">
-        <v>-0.98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C109" s="6">
-        <v>55.13</v>
+        <v>62</v>
       </c>
       <c r="D109" s="6">
-        <v>52.19</v>
+        <v>68</v>
       </c>
       <c r="E109" s="8">
-        <v>-2.94</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C110" s="6">
-        <v>31.95</v>
+        <v>68</v>
       </c>
       <c r="D110" s="6">
-        <v>32.02</v>
+        <v>62</v>
       </c>
       <c r="E110" s="7">
-        <v>0.07000000000000001</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="6">
-        <v>47.27</v>
+        <v>87</v>
       </c>
       <c r="D111" s="6">
-        <v>45.71</v>
+        <v>93</v>
       </c>
       <c r="E111" s="8">
-        <v>-1.56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C112" s="6">
-        <v>39.11</v>
+        <v>50</v>
       </c>
       <c r="D112" s="6">
-        <v>38.66</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-0.45</v>
+        <v>44</v>
+      </c>
+      <c r="E112" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C113" s="6">
-        <v>37.15</v>
+        <v>32</v>
       </c>
       <c r="D113" s="6">
-        <v>36.29</v>
-      </c>
-      <c r="E113" s="8">
-        <v>-0.86</v>
+        <v>19</v>
+      </c>
+      <c r="E113" s="7">
+        <v>-13</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C114" s="6">
-        <v>25.99</v>
+        <v>19</v>
       </c>
       <c r="D114" s="6">
-        <v>26.4</v>
-      </c>
-      <c r="E114" s="7">
-        <v>0.41</v>
+        <v>26</v>
+      </c>
+      <c r="E114" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="6">
         <v>44</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C115" s="6">
-        <v>48.41</v>
-      </c>
       <c r="D115" s="6">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="E115" s="8">
-        <v>-1.71</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>45.31</v>
+        <v>49.85</v>
       </c>
       <c r="D116" s="6">
-        <v>49.53</v>
+        <v>42.86</v>
       </c>
       <c r="E116" s="7">
-        <v>4.22</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>53.17</v>
+        <v>52.19</v>
       </c>
       <c r="D117" s="6">
-        <v>53.08</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-0.09</v>
+        <v>43.18</v>
+      </c>
+      <c r="E117" s="7">
+        <v>-9.01</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>32.65</v>
+        <v>32.02</v>
       </c>
       <c r="D118" s="6">
-        <v>32.24</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-0.41</v>
+        <v>30.27</v>
+      </c>
+      <c r="E118" s="7">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>40.75</v>
+        <v>45.71</v>
       </c>
       <c r="D119" s="6">
-        <v>45.57</v>
+        <v>45.27</v>
       </c>
       <c r="E119" s="7">
-        <v>4.82</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>32.3</v>
+        <v>38.66</v>
       </c>
       <c r="D120" s="6">
-        <v>29.91</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-2.39</v>
+        <v>37.2</v>
+      </c>
+      <c r="E120" s="7">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>37.87</v>
+        <v>36.29</v>
       </c>
       <c r="D121" s="6">
-        <v>38.81</v>
+        <v>30.57</v>
       </c>
       <c r="E121" s="7">
-        <v>0.9399999999999999</v>
+        <v>-5.72</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>36.29</v>
+        <v>26.4</v>
       </c>
       <c r="D122" s="6">
-        <v>33.4</v>
+        <v>26.97</v>
       </c>
       <c r="E122" s="8">
-        <v>-2.89</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>37.49</v>
+        <v>46.7</v>
       </c>
       <c r="D123" s="6">
-        <v>38.72</v>
+        <v>44.88</v>
       </c>
       <c r="E123" s="7">
-        <v>1.23</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>-35.84</v>
+        <v>49.53</v>
       </c>
       <c r="D124" s="6">
-        <v>-13.77</v>
+        <v>44.42</v>
       </c>
       <c r="E124" s="7">
-        <v>22.07</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C125" s="6">
-        <v>-47.21</v>
+        <v>53.08</v>
       </c>
       <c r="D125" s="6">
-        <v>-62.82</v>
-      </c>
-      <c r="E125" s="8">
-        <v>-15.61</v>
+        <v>50.03</v>
+      </c>
+      <c r="E125" s="7">
+        <v>-3.05</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C126" s="6">
-        <v>-16.44</v>
+        <v>32.24</v>
       </c>
       <c r="D126" s="6">
-        <v>-41.09</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-24.65</v>
+        <v>31.26</v>
+      </c>
+      <c r="E126" s="7">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="6">
-        <v>-76.95999999999999</v>
+        <v>45.57</v>
       </c>
       <c r="D127" s="6">
-        <v>-66.17</v>
+        <v>41.06</v>
       </c>
       <c r="E127" s="7">
-        <v>10.79</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C128" s="6">
-        <v>-59.44</v>
+        <v>29.91</v>
       </c>
       <c r="D128" s="6">
-        <v>-51.44</v>
+        <v>26.9</v>
       </c>
       <c r="E128" s="7">
-        <v>8</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C129" s="6">
-        <v>-11.71</v>
+        <v>38.81</v>
       </c>
       <c r="D129" s="6">
-        <v>-22.9</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-11.19</v>
+        <v>30.94</v>
+      </c>
+      <c r="E129" s="7">
+        <v>-7.87</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C130" s="6">
-        <v>6.62</v>
+        <v>33.4</v>
       </c>
       <c r="D130" s="6">
-        <v>-15.56</v>
+        <v>47.09</v>
       </c>
       <c r="E130" s="8">
-        <v>-22.18</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C131" s="6">
-        <v>-85.69</v>
+        <v>38.72</v>
       </c>
       <c r="D131" s="6">
-        <v>-88.23</v>
+        <v>43.06</v>
       </c>
       <c r="E131" s="8">
-        <v>-2.54</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>-46.51</v>
+        <v>-13.77</v>
       </c>
       <c r="D132" s="6">
-        <v>-63.67</v>
+        <v>50.37</v>
       </c>
       <c r="E132" s="8">
-        <v>-17.16</v>
+        <v>64.14</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>-48.15</v>
+        <v>-62.82</v>
       </c>
       <c r="D133" s="6">
-        <v>-46.63</v>
-      </c>
-      <c r="E133" s="7">
-        <v>1.52</v>
+        <v>-11.12</v>
+      </c>
+      <c r="E133" s="8">
+        <v>51.7</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-40.84</v>
+        <v>-41.09</v>
       </c>
       <c r="D134" s="6">
-        <v>14.65</v>
-      </c>
-      <c r="E134" s="7">
-        <v>55.49</v>
+        <v>-26</v>
+      </c>
+      <c r="E134" s="8">
+        <v>15.09</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>-14.85</v>
+        <v>-66.17</v>
       </c>
       <c r="D135" s="6">
-        <v>-38.49</v>
+        <v>-32.32</v>
       </c>
       <c r="E135" s="8">
-        <v>-23.64</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-15.54</v>
+        <v>-51.44</v>
       </c>
       <c r="D136" s="6">
-        <v>60.82</v>
-      </c>
-      <c r="E136" s="7">
-        <v>76.36</v>
+        <v>-42.27</v>
+      </c>
+      <c r="E136" s="8">
+        <v>9.17</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>4.72</v>
+        <v>-22.9</v>
       </c>
       <c r="D137" s="6">
-        <v>-40.04</v>
+        <v>14.71</v>
       </c>
       <c r="E137" s="8">
-        <v>-44.76</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>-75.41</v>
+        <v>-15.56</v>
       </c>
       <c r="D138" s="6">
-        <v>-55.06</v>
+        <v>-23.75</v>
       </c>
       <c r="E138" s="7">
-        <v>20.35</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>-27.9</v>
+        <v>-88.23</v>
       </c>
       <c r="D139" s="6">
+        <v>-78.17</v>
+      </c>
+      <c r="E139" s="8">
+        <v>10.06</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="6">
+        <v>-63.67</v>
+      </c>
+      <c r="D140" s="6">
+        <v>-35.11</v>
+      </c>
+      <c r="E140" s="8">
+        <v>28.56</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="6">
+        <v>-46.63</v>
+      </c>
+      <c r="D141" s="6">
+        <v>-52.99</v>
+      </c>
+      <c r="E141" s="7">
+        <v>-6.36</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="6">
+        <v>14.65</v>
+      </c>
+      <c r="D142" s="6">
+        <v>-17.96</v>
+      </c>
+      <c r="E142" s="7">
+        <v>-32.61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6">
+        <v>-38.49</v>
+      </c>
+      <c r="D143" s="6">
+        <v>5.68</v>
+      </c>
+      <c r="E143" s="8">
+        <v>44.17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="6">
+        <v>60.82</v>
+      </c>
+      <c r="D144" s="6">
+        <v>-6.88</v>
+      </c>
+      <c r="E144" s="7">
+        <v>-67.7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="6">
+        <v>-40.04</v>
+      </c>
+      <c r="D145" s="6">
+        <v>206.15</v>
+      </c>
+      <c r="E145" s="8">
+        <v>246.19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="6">
+        <v>-55.06</v>
+      </c>
+      <c r="D146" s="6">
+        <v>1893.81</v>
+      </c>
+      <c r="E146" s="8">
+        <v>1948.87</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147" s="6">
         <v>-50.54</v>
       </c>
-      <c r="E139" s="8">
-        <v>-22.64</v>
+      <c r="D147" s="6">
+        <v>30.82</v>
+      </c>
+      <c r="E147" s="8">
+        <v>81.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5261,28 +5415,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5296,22 +5450,22 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>40.6</v>
+        <v>38.5</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.7</v>
+        <v>-4.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-7</v>
+        <v>-7.8</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
       </c>
       <c r="I2" s="11">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5445,34 +5599,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.401</v>
+        <v>0.3998</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3199</v>
+        <v>0.3165</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2221</v>
+        <v>0.2159</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2176</v>
+        <v>0.2108</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1883</v>
+        <v>0.1806</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1194</v>
+        <v>0.1187</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1142</v>
+        <v>0.1102</v>
       </c>
       <c r="H2" s="14">
-        <v>0.09710000000000001</v>
+        <v>0.0726</v>
       </c>
       <c r="I2" s="14">
-        <v>0.044</v>
+        <v>0.047</v>
       </c>
       <c r="J2" s="14">
-        <v>0.04190000000000001</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5497,22 +5651,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.0021</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0124</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0544</v>
+        <v>-0.0533</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0576</v>
+        <v>-0.0571</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.09089999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1013</v>
+        <v>-0.0992</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,16 +217,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.5 → 46.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.5</t>
+    <t>46.9 → 50.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>46.9</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.8 → 32.6</t>
+  </si>
+  <si>
+    <t>26.8</t>
+  </si>
+  <si>
+    <t>32.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -312,14 +324,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,13 +364,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -951,10 +963,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="D2">
-        <v>-1.46</v>
+        <v>0.97</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -963,46 +975,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-4.56</v>
+        <v>-3.63</v>
       </c>
       <c r="H2">
-        <v>25.76</v>
+        <v>26.98</v>
       </c>
       <c r="I2">
-        <v>-1.48</v>
+        <v>-0.25</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="K2">
-        <v>-1.45</v>
+        <v>-1.78</v>
       </c>
       <c r="L2">
-        <v>1.16</v>
+        <v>0.1</v>
       </c>
       <c r="M2">
-        <v>32.38</v>
+        <v>31.3</v>
       </c>
       <c r="N2">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O2">
         <v>62</v>
       </c>
       <c r="P2">
-        <v>719.76</v>
+        <v>719.4</v>
       </c>
       <c r="Q2">
-        <v>724.28</v>
+        <v>723.9299999999999</v>
       </c>
       <c r="R2">
-        <v>727.53</v>
+        <v>727.55</v>
       </c>
       <c r="S2">
-        <v>688.15</v>
+        <v>688.12</v>
       </c>
       <c r="T2">
-        <v>4.34</v>
+        <v>5.36</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1017,34 +1029,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>46.86</v>
+        <v>50.07</v>
       </c>
       <c r="Z2">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="AA2">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="AB2">
-        <v>-0.88</v>
+        <v>-0.61</v>
       </c>
       <c r="AC2">
-        <v>26.95</v>
+        <v>37.09</v>
       </c>
       <c r="AD2">
-        <v>20.18</v>
+        <v>27.85</v>
       </c>
       <c r="AE2">
-        <v>16.34</v>
+        <v>16.14</v>
       </c>
       <c r="AF2">
-        <v>37.18</v>
+        <v>20.36</v>
       </c>
       <c r="AG2">
-        <v>744.08</v>
+        <v>743.4</v>
       </c>
       <c r="AH2">
-        <v>704.48</v>
+        <v>704.46</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1053,7 +1065,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>19.24</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1064,10 +1076,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>889.2</v>
+        <v>885.1</v>
       </c>
       <c r="D3">
-        <v>-2.77</v>
+        <v>-0.46</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1076,46 +1088,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-17.78</v>
+        <v>-18.16</v>
       </c>
       <c r="H3">
-        <v>75.95</v>
+        <v>75.14</v>
       </c>
       <c r="I3">
-        <v>-10.46</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="J3">
-        <v>-3.8</v>
+        <v>-4.79</v>
       </c>
       <c r="K3">
-        <v>-4.34</v>
+        <v>-3.93</v>
       </c>
       <c r="L3">
-        <v>3.7</v>
+        <v>4.79</v>
       </c>
       <c r="M3">
-        <v>3.54</v>
+        <v>1.45</v>
       </c>
       <c r="N3">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>923.79</v>
+        <v>905.51</v>
       </c>
       <c r="Q3">
-        <v>953.23</v>
+        <v>950.8</v>
       </c>
       <c r="R3">
-        <v>958.79</v>
+        <v>957.8099999999999</v>
       </c>
       <c r="S3">
-        <v>765.86</v>
+        <v>766.52</v>
       </c>
       <c r="T3">
-        <v>16.1</v>
+        <v>15.47</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1130,43 +1142,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.65</v>
+        <v>39.1</v>
       </c>
       <c r="Z3">
-        <v>-5.79</v>
+        <v>-10.08</v>
       </c>
       <c r="AA3">
-        <v>3.63</v>
+        <v>0.89</v>
       </c>
       <c r="AB3">
-        <v>-9.42</v>
+        <v>-10.97</v>
       </c>
       <c r="AC3">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>6.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
-        <v>44.47</v>
+        <v>43.79</v>
       </c>
       <c r="AF3">
-        <v>-19.5</v>
+        <v>-62.01</v>
       </c>
       <c r="AG3">
-        <v>1028.64</v>
+        <v>1031.79</v>
       </c>
       <c r="AH3">
-        <v>877.83</v>
+        <v>869.8200000000001</v>
       </c>
       <c r="AI3">
-        <v>1039.33</v>
+        <v>1028.89</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>27.25</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,58 +1189,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>199.69</v>
+        <v>197.16</v>
       </c>
       <c r="D4">
-        <v>-0.02</v>
+        <v>-1.27</v>
       </c>
       <c r="E4">
         <v>307.76</v>
       </c>
       <c r="F4">
-        <v>199.42</v>
+        <v>197.16</v>
       </c>
       <c r="G4">
-        <v>-35.12</v>
+        <v>-35.94</v>
       </c>
       <c r="H4">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.33</v>
+        <v>-1.61</v>
       </c>
       <c r="J4">
-        <v>-3.61</v>
+        <v>-5.89</v>
       </c>
       <c r="K4">
-        <v>-12.47</v>
+        <v>-15.04</v>
       </c>
       <c r="L4">
-        <v>-34.39</v>
+        <v>-35.84</v>
       </c>
       <c r="M4">
-        <v>-5.76</v>
+        <v>-6.35</v>
       </c>
       <c r="N4">
         <v>32</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>199.84</v>
+        <v>199.19</v>
       </c>
       <c r="Q4">
-        <v>202.84</v>
+        <v>202.21</v>
       </c>
       <c r="R4">
-        <v>209.42</v>
+        <v>208.93</v>
       </c>
       <c r="S4">
-        <v>240.16</v>
+        <v>239.84</v>
       </c>
       <c r="T4">
-        <v>-16.85</v>
+        <v>-17.79</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1243,34 +1255,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.95</v>
+        <v>26.97</v>
       </c>
       <c r="Z4">
-        <v>-3.09</v>
+        <v>-3.19</v>
       </c>
       <c r="AA4">
-        <v>-3.25</v>
+        <v>-3.24</v>
       </c>
       <c r="AB4">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="AC4">
-        <v>48.85</v>
+        <v>32.16</v>
       </c>
       <c r="AD4">
-        <v>45.46</v>
+        <v>41.6</v>
       </c>
       <c r="AE4">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="AF4">
-        <v>16.37</v>
+        <v>-44.03</v>
       </c>
       <c r="AG4">
-        <v>208.71</v>
+        <v>207.62</v>
       </c>
       <c r="AH4">
-        <v>196.97</v>
+        <v>196.8</v>
       </c>
       <c r="AI4">
         <v>210.35</v>
@@ -1279,7 +1291,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>31.16</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1290,10 +1302,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>607.8</v>
+        <v>617.4</v>
       </c>
       <c r="D5">
-        <v>-0.6</v>
+        <v>1.58</v>
       </c>
       <c r="E5">
         <v>912.72</v>
@@ -1302,25 +1314,25 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-33.41</v>
+        <v>-32.36</v>
       </c>
       <c r="H5">
-        <v>5.81</v>
+        <v>7.48</v>
       </c>
       <c r="I5">
-        <v>-6.81</v>
+        <v>-4.09</v>
       </c>
       <c r="J5">
-        <v>-4.07</v>
+        <v>-2.61</v>
       </c>
       <c r="K5">
-        <v>-12.31</v>
+        <v>-11.31</v>
       </c>
       <c r="L5">
-        <v>-33.7</v>
+        <v>-32.26</v>
       </c>
       <c r="M5">
-        <v>-6.44</v>
+        <v>-6.55</v>
       </c>
       <c r="N5">
         <v>38</v>
@@ -1329,19 +1341,19 @@
         <v>22</v>
       </c>
       <c r="P5">
-        <v>623.66</v>
+        <v>618.39</v>
       </c>
       <c r="Q5">
-        <v>653.09</v>
+        <v>651.9</v>
       </c>
       <c r="R5">
-        <v>656.9</v>
+        <v>655.66</v>
       </c>
       <c r="S5">
-        <v>698.74</v>
+        <v>698.0599999999999</v>
       </c>
       <c r="T5">
-        <v>-13.02</v>
+        <v>-11.55</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1356,34 +1368,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>39.21</v>
+        <v>41.92</v>
       </c>
       <c r="Z5">
-        <v>-8.52</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="AA5">
-        <v>-0.5600000000000001</v>
+        <v>-2.44</v>
       </c>
       <c r="AB5">
-        <v>-7.96</v>
+        <v>-7.51</v>
       </c>
       <c r="AC5">
-        <v>15.78</v>
+        <v>10.21</v>
       </c>
       <c r="AD5">
-        <v>23.61</v>
+        <v>16.66</v>
       </c>
       <c r="AE5">
-        <v>31.14</v>
+        <v>30.81</v>
       </c>
       <c r="AF5">
-        <v>-65.94</v>
+        <v>-73.64</v>
       </c>
       <c r="AG5">
-        <v>754.62</v>
+        <v>754.5599999999999</v>
       </c>
       <c r="AH5">
-        <v>551.5700000000001</v>
+        <v>549.23</v>
       </c>
       <c r="AI5">
         <v>703.01</v>
@@ -1392,7 +1404,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>20.59</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1415,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1683</v>
+        <v>1677.2</v>
       </c>
       <c r="D6">
-        <v>1.62</v>
+        <v>-0.34</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1415,25 +1427,25 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-18.37</v>
+        <v>-18.65</v>
       </c>
       <c r="H6">
-        <v>24.86</v>
+        <v>24.43</v>
       </c>
       <c r="I6">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="J6">
-        <v>-2.93</v>
+        <v>-1.92</v>
       </c>
       <c r="K6">
-        <v>-11.73</v>
+        <v>-11.35</v>
       </c>
       <c r="L6">
-        <v>4.29</v>
+        <v>3.98</v>
       </c>
       <c r="M6">
-        <v>4.83</v>
+        <v>4.16</v>
       </c>
       <c r="N6">
         <v>74</v>
@@ -1442,19 +1454,19 @@
         <v>57</v>
       </c>
       <c r="P6">
-        <v>1663.14</v>
+        <v>1665.28</v>
       </c>
       <c r="Q6">
-        <v>1723.66</v>
+        <v>1722.7</v>
       </c>
       <c r="R6">
-        <v>1726.77</v>
+        <v>1724.3</v>
       </c>
       <c r="S6">
-        <v>1705.9</v>
+        <v>1705.33</v>
       </c>
       <c r="T6">
-        <v>-1.34</v>
+        <v>-1.65</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1469,34 +1481,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>43.8</v>
+        <v>42.79</v>
       </c>
       <c r="Z6">
-        <v>-20.26</v>
+        <v>-19.95</v>
       </c>
       <c r="AA6">
-        <v>-12.49</v>
+        <v>-13.99</v>
       </c>
       <c r="AB6">
-        <v>-7.77</v>
+        <v>-5.97</v>
       </c>
       <c r="AC6">
-        <v>10.46</v>
+        <v>18.87</v>
       </c>
       <c r="AD6">
-        <v>3.67</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AE6">
-        <v>47.67</v>
+        <v>47.83</v>
       </c>
       <c r="AF6">
-        <v>-40.67</v>
+        <v>-62.42</v>
       </c>
       <c r="AG6">
-        <v>1821.93</v>
+        <v>1822.46</v>
       </c>
       <c r="AH6">
-        <v>1625.39</v>
+        <v>1622.94</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1505,7 +1517,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>32.04</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1516,10 +1528,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>957</v>
+        <v>953.75</v>
       </c>
       <c r="D7">
-        <v>0.79</v>
+        <v>-0.34</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1528,46 +1540,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-24.07</v>
+        <v>-24.33</v>
       </c>
       <c r="H7">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="I7">
-        <v>-2.97</v>
+        <v>-3</v>
       </c>
       <c r="J7">
-        <v>-7.13</v>
+        <v>-5.76</v>
       </c>
       <c r="K7">
-        <v>-14.3</v>
+        <v>-14.68</v>
       </c>
       <c r="L7">
-        <v>-13.75</v>
+        <v>-14.36</v>
       </c>
       <c r="M7">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="N7">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O7">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P7">
-        <v>963.48</v>
+        <v>957.59</v>
       </c>
       <c r="Q7">
-        <v>991.42</v>
+        <v>988.15</v>
       </c>
       <c r="R7">
-        <v>1040.33</v>
+        <v>1037.25</v>
       </c>
       <c r="S7">
-        <v>1108.85</v>
+        <v>1107.88</v>
       </c>
       <c r="T7">
-        <v>-13.69</v>
+        <v>-13.91</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1582,43 +1594,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>33.69</v>
+        <v>32.92</v>
       </c>
       <c r="Z7">
-        <v>-22.53</v>
+        <v>-22.8</v>
       </c>
       <c r="AA7">
-        <v>-20.67</v>
+        <v>-21.1</v>
       </c>
       <c r="AB7">
-        <v>-1.85</v>
+        <v>-1.71</v>
       </c>
       <c r="AC7">
-        <v>32.18</v>
+        <v>29.05</v>
       </c>
       <c r="AD7">
-        <v>32.08</v>
+        <v>28.72</v>
       </c>
       <c r="AE7">
-        <v>18.22</v>
+        <v>18.13</v>
       </c>
       <c r="AF7">
-        <v>49.4</v>
+        <v>21.9</v>
       </c>
       <c r="AG7">
-        <v>1031.68</v>
+        <v>1029.53</v>
       </c>
       <c r="AH7">
-        <v>951.17</v>
+        <v>946.77</v>
       </c>
       <c r="AI7">
-        <v>1009.56</v>
+        <v>1007.9</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>59.57</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,10 +1641,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3092.8</v>
+        <v>3105</v>
       </c>
       <c r="D8">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1641,25 +1653,25 @@
         <v>3088.9</v>
       </c>
       <c r="G8">
-        <v>-46.21</v>
+        <v>-46</v>
       </c>
       <c r="H8">
-        <v>0.13</v>
+        <v>0.52</v>
       </c>
       <c r="I8">
-        <v>-2.86</v>
+        <v>-2.57</v>
       </c>
       <c r="J8">
-        <v>-14.99</v>
+        <v>-13.97</v>
       </c>
       <c r="K8">
-        <v>-15.93</v>
+        <v>-15.13</v>
       </c>
       <c r="L8">
-        <v>-40.63</v>
+        <v>-40.38</v>
       </c>
       <c r="M8">
-        <v>-10.85</v>
+        <v>-10.96</v>
       </c>
       <c r="N8">
         <v>19</v>
@@ -1668,19 +1680,19 @@
         <v>11</v>
       </c>
       <c r="P8">
-        <v>3154.26</v>
+        <v>3137.88</v>
       </c>
       <c r="Q8">
-        <v>3321.88</v>
+        <v>3298.13</v>
       </c>
       <c r="R8">
-        <v>3534.2</v>
+        <v>3528.55</v>
       </c>
       <c r="S8">
-        <v>4227.94</v>
+        <v>4218.67</v>
       </c>
       <c r="T8">
-        <v>-26.85</v>
+        <v>-26.4</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1695,34 +1707,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>24.3</v>
+        <v>26.05</v>
       </c>
       <c r="Z8">
-        <v>-126.88</v>
+        <v>-127.04</v>
       </c>
       <c r="AA8">
-        <v>-112.62</v>
+        <v>-115.5</v>
       </c>
       <c r="AB8">
-        <v>-14.26</v>
+        <v>-11.54</v>
       </c>
       <c r="AC8">
-        <v>12.76</v>
+        <v>6.84</v>
       </c>
       <c r="AD8">
-        <v>14.19</v>
+        <v>11.31</v>
       </c>
       <c r="AE8">
-        <v>87.02</v>
+        <v>86.39</v>
       </c>
       <c r="AF8">
-        <v>41.47</v>
+        <v>-2.51</v>
       </c>
       <c r="AG8">
-        <v>3618.25</v>
+        <v>3583.33</v>
       </c>
       <c r="AH8">
-        <v>3025.51</v>
+        <v>3012.93</v>
       </c>
       <c r="AI8">
         <v>3366.35</v>
@@ -1731,7 +1743,7 @@
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>54.86</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1754,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>615.05</v>
+        <v>621.75</v>
       </c>
       <c r="D9">
-        <v>-0.8100000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1754,46 +1766,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-41.57</v>
+        <v>-40.93</v>
       </c>
       <c r="H9">
-        <v>14.24</v>
+        <v>15.49</v>
       </c>
       <c r="I9">
-        <v>-6.58</v>
+        <v>-4.58</v>
       </c>
       <c r="J9">
-        <v>-2.94</v>
+        <v>-1.01</v>
       </c>
       <c r="K9">
-        <v>-7.83</v>
+        <v>-6.4</v>
       </c>
       <c r="L9">
-        <v>-28.66</v>
+        <v>-29.33</v>
       </c>
       <c r="M9">
-        <v>35.66</v>
+        <v>35.56</v>
       </c>
       <c r="N9">
         <v>50</v>
       </c>
       <c r="O9">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P9">
-        <v>631.3200000000001</v>
+        <v>625.35</v>
       </c>
       <c r="Q9">
-        <v>655.51</v>
+        <v>654.7</v>
       </c>
       <c r="R9">
-        <v>657.35</v>
+        <v>657.14</v>
       </c>
       <c r="S9">
-        <v>660.89</v>
+        <v>660.39</v>
       </c>
       <c r="T9">
-        <v>-6.94</v>
+        <v>-5.85</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1808,34 +1820,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>38.06</v>
+        <v>40.53</v>
       </c>
       <c r="Z9">
-        <v>-6.39</v>
+        <v>-7.93</v>
       </c>
       <c r="AA9">
-        <v>0.4</v>
+        <v>-1.27</v>
       </c>
       <c r="AB9">
-        <v>-6.79</v>
+        <v>-6.66</v>
       </c>
       <c r="AC9">
-        <v>7.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD9">
-        <v>18.38</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AE9">
-        <v>23.91</v>
+        <v>23.23</v>
       </c>
       <c r="AF9">
-        <v>-87.76000000000001</v>
+        <v>-88.94</v>
       </c>
       <c r="AG9">
-        <v>721.52</v>
+        <v>722</v>
       </c>
       <c r="AH9">
-        <v>589.51</v>
+        <v>587.41</v>
       </c>
       <c r="AI9">
         <v>682.46</v>
@@ -1844,7 +1856,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>24.28</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,10 +1867,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>350.15</v>
+        <v>351.5</v>
       </c>
       <c r="D10">
-        <v>-2.47</v>
+        <v>0.39</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1867,25 +1879,25 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-24.18</v>
+        <v>-23.88</v>
       </c>
       <c r="H10">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="I10">
-        <v>-3.66</v>
+        <v>-4.35</v>
       </c>
       <c r="J10">
-        <v>-0.11</v>
+        <v>-3.43</v>
       </c>
       <c r="K10">
-        <v>-6.68</v>
+        <v>-6.9</v>
       </c>
       <c r="L10">
-        <v>-8.77</v>
+        <v>-9.42</v>
       </c>
       <c r="M10">
-        <v>17.07</v>
+        <v>15.04</v>
       </c>
       <c r="N10">
         <v>68</v>
@@ -1894,19 +1906,19 @@
         <v>49</v>
       </c>
       <c r="P10">
-        <v>359.51</v>
+        <v>356.31</v>
       </c>
       <c r="Q10">
-        <v>364.9</v>
+        <v>364.19</v>
       </c>
       <c r="R10">
-        <v>370.12</v>
+        <v>369.63</v>
       </c>
       <c r="S10">
-        <v>386.61</v>
+        <v>386.46</v>
       </c>
       <c r="T10">
-        <v>-9.43</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1921,34 +1933,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>35.24</v>
+        <v>36.91</v>
       </c>
       <c r="Z10">
-        <v>-3.15</v>
+        <v>-3.74</v>
       </c>
       <c r="AA10">
-        <v>-2.16</v>
+        <v>-2.47</v>
       </c>
       <c r="AB10">
-        <v>-0.99</v>
+        <v>-1.27</v>
       </c>
       <c r="AC10">
-        <v>5.1</v>
+        <v>5.16</v>
       </c>
       <c r="AD10">
-        <v>15.51</v>
+        <v>7.67</v>
       </c>
       <c r="AE10">
-        <v>7.53</v>
+        <v>7.42</v>
       </c>
       <c r="AF10">
-        <v>-0.32</v>
+        <v>-35.24</v>
       </c>
       <c r="AG10">
-        <v>375.28</v>
+        <v>376.16</v>
       </c>
       <c r="AH10">
-        <v>354.52</v>
+        <v>352.22</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -1957,7 +1969,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>33.13</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1968,10 +1980,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>178</v>
+        <v>178.14</v>
       </c>
       <c r="D11">
-        <v>-3.42</v>
+        <v>0.08</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1980,46 +1992,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-17.84</v>
+        <v>-17.78</v>
       </c>
       <c r="H11">
-        <v>13.07</v>
+        <v>13.16</v>
       </c>
       <c r="I11">
-        <v>-5.33</v>
+        <v>-5.23</v>
       </c>
       <c r="J11">
-        <v>-3.3</v>
+        <v>-3.11</v>
       </c>
       <c r="K11">
-        <v>-6.22</v>
+        <v>-6.67</v>
       </c>
       <c r="L11">
-        <v>8.52</v>
+        <v>7.59</v>
       </c>
       <c r="M11">
-        <v>9.73</v>
+        <v>9.42</v>
       </c>
       <c r="N11">
         <v>93</v>
       </c>
       <c r="O11">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P11">
-        <v>184.91</v>
+        <v>182.95</v>
       </c>
       <c r="Q11">
-        <v>185.63</v>
+        <v>185.32</v>
       </c>
       <c r="R11">
-        <v>186.08</v>
+        <v>185.96</v>
       </c>
       <c r="S11">
-        <v>191.95</v>
+        <v>191.99</v>
       </c>
       <c r="T11">
-        <v>-7.27</v>
+        <v>-7.21</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2034,43 +2046,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>38.02</v>
+        <v>38.29</v>
       </c>
       <c r="Z11">
-        <v>-0.57</v>
+        <v>-1.08</v>
       </c>
       <c r="AA11">
-        <v>-0.13</v>
+        <v>-0.32</v>
       </c>
       <c r="AB11">
-        <v>-0.44</v>
+        <v>-0.76</v>
       </c>
       <c r="AC11">
-        <v>27.28</v>
+        <v>6.65</v>
       </c>
       <c r="AD11">
-        <v>41.82</v>
+        <v>25.16</v>
       </c>
       <c r="AE11">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="AF11">
-        <v>76.84</v>
+        <v>-24.34</v>
       </c>
       <c r="AG11">
-        <v>191.35</v>
+        <v>191.93</v>
       </c>
       <c r="AH11">
-        <v>179.91</v>
+        <v>178.71</v>
       </c>
       <c r="AI11">
-        <v>193.9</v>
+        <v>193.65</v>
       </c>
       <c r="AJ11" t="s">
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>22.45</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2081,10 +2093,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2075</v>
+        <v>2114.4</v>
       </c>
       <c r="D12">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2093,46 +2105,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-35.6</v>
+        <v>-34.37</v>
       </c>
       <c r="H12">
-        <v>4.66</v>
+        <v>6.65</v>
       </c>
       <c r="I12">
-        <v>-0.57</v>
+        <v>1.56</v>
       </c>
       <c r="J12">
-        <v>-12.41</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="K12">
-        <v>-0.88</v>
+        <v>2.76</v>
       </c>
       <c r="L12">
-        <v>-25.86</v>
+        <v>-24.38</v>
       </c>
       <c r="M12">
-        <v>-8.630000000000001</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="N12">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O12">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P12">
-        <v>2062.14</v>
+        <v>2068.62</v>
       </c>
       <c r="Q12">
-        <v>2160.92</v>
+        <v>2150.63</v>
       </c>
       <c r="R12">
-        <v>2276.44</v>
+        <v>2273.87</v>
       </c>
       <c r="S12">
-        <v>2483.43</v>
+        <v>2478.35</v>
       </c>
       <c r="T12">
-        <v>-16.45</v>
+        <v>-14.69</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2147,34 +2159,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>36.09</v>
+        <v>42.59</v>
       </c>
       <c r="Z12">
-        <v>-63.4</v>
+        <v>-57.97</v>
       </c>
       <c r="AA12">
-        <v>-55.24</v>
+        <v>-55.79</v>
       </c>
       <c r="AB12">
-        <v>-8.16</v>
+        <v>-2.18</v>
       </c>
       <c r="AC12">
-        <v>22.1</v>
+        <v>50.08</v>
       </c>
       <c r="AD12">
-        <v>9.609999999999999</v>
+        <v>26.3</v>
       </c>
       <c r="AE12">
-        <v>58.78</v>
+        <v>60.1</v>
       </c>
       <c r="AF12">
-        <v>11.15</v>
+        <v>68.94</v>
       </c>
       <c r="AG12">
-        <v>2338.82</v>
+        <v>2312.89</v>
       </c>
       <c r="AH12">
-        <v>1983.01</v>
+        <v>1988.37</v>
       </c>
       <c r="AI12">
         <v>2235.3</v>
@@ -2183,7 +2195,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>44.56</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2194,10 +2206,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4515.7</v>
+        <v>4580</v>
       </c>
       <c r="D13">
-        <v>-1.55</v>
+        <v>1.42</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2206,25 +2218,25 @@
         <v>3367</v>
       </c>
       <c r="G13">
-        <v>-12.64</v>
+        <v>-11.4</v>
       </c>
       <c r="H13">
-        <v>34.12</v>
+        <v>36.03</v>
       </c>
       <c r="I13">
-        <v>-6.56</v>
+        <v>-6.22</v>
       </c>
       <c r="J13">
-        <v>-10.58</v>
+        <v>-9.74</v>
       </c>
       <c r="K13">
-        <v>1.22</v>
+        <v>2.13</v>
       </c>
       <c r="L13">
-        <v>35.72</v>
+        <v>34.66</v>
       </c>
       <c r="M13">
-        <v>16.16</v>
+        <v>16.18</v>
       </c>
       <c r="N13">
         <v>99</v>
@@ -2233,19 +2245,19 @@
         <v>77</v>
       </c>
       <c r="P13">
-        <v>4696.24</v>
+        <v>4635.44</v>
       </c>
       <c r="Q13">
-        <v>4873.29</v>
+        <v>4850.94</v>
       </c>
       <c r="R13">
-        <v>4947.88</v>
+        <v>4945.54</v>
       </c>
       <c r="S13">
-        <v>4408.26</v>
+        <v>4411.83</v>
       </c>
       <c r="T13">
-        <v>2.44</v>
+        <v>3.81</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2260,34 +2272,34 @@
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>26.8</v>
+        <v>32.64</v>
       </c>
       <c r="Z13">
-        <v>-87.36</v>
+        <v>-96.08</v>
       </c>
       <c r="AA13">
-        <v>-44.24</v>
+        <v>-54.61</v>
       </c>
       <c r="AB13">
-        <v>-43.12</v>
+        <v>-41.47</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AD13">
-        <v>14.61</v>
+        <v>7.03</v>
       </c>
       <c r="AE13">
-        <v>92.45999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AF13">
-        <v>11.72</v>
+        <v>15.81</v>
       </c>
       <c r="AG13">
-        <v>5161.91</v>
+        <v>5158.08</v>
       </c>
       <c r="AH13">
-        <v>4584.66</v>
+        <v>4543.79</v>
       </c>
       <c r="AI13">
         <v>4833.78</v>
@@ -2296,7 +2308,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>47.97</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2310,7 +2322,7 @@
         <v>2580</v>
       </c>
       <c r="D14">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>4824.87</v>
@@ -2325,40 +2337,40 @@
         <v>17.6</v>
       </c>
       <c r="I14">
-        <v>-4.44</v>
+        <v>-3.35</v>
       </c>
       <c r="J14">
-        <v>-9.630000000000001</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="K14">
-        <v>-22.77</v>
+        <v>-22.84</v>
       </c>
       <c r="L14">
-        <v>-44.78</v>
+        <v>-45.38</v>
       </c>
       <c r="M14">
-        <v>19.94</v>
+        <v>19.81</v>
       </c>
       <c r="N14">
         <v>7</v>
       </c>
       <c r="O14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P14">
-        <v>2626.38</v>
+        <v>2608.52</v>
       </c>
       <c r="Q14">
-        <v>2751.74</v>
+        <v>2739.96</v>
       </c>
       <c r="R14">
-        <v>2877.84</v>
+        <v>2871.95</v>
       </c>
       <c r="S14">
-        <v>2856.69</v>
+        <v>2849.07</v>
       </c>
       <c r="T14">
-        <v>-9.69</v>
+        <v>-9.44</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2376,31 +2388,31 @@
         <v>24.71</v>
       </c>
       <c r="Z14">
-        <v>-73.48</v>
+        <v>-77.05</v>
       </c>
       <c r="AA14">
-        <v>-58.1</v>
+        <v>-61.89</v>
       </c>
       <c r="AB14">
-        <v>-15.38</v>
+        <v>-15.16</v>
       </c>
       <c r="AC14">
-        <v>4.14</v>
+        <v>1.18</v>
       </c>
       <c r="AD14">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="AE14">
-        <v>60.78</v>
+        <v>58.97</v>
       </c>
       <c r="AF14">
-        <v>23.11</v>
+        <v>8.41</v>
       </c>
       <c r="AG14">
-        <v>2917.18</v>
+        <v>2919.23</v>
       </c>
       <c r="AH14">
-        <v>2586.3</v>
+        <v>2560.69</v>
       </c>
       <c r="AI14">
         <v>2767.24</v>
@@ -2409,7 +2421,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>57.84</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2420,10 +2432,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>192.33</v>
+        <v>194.02</v>
       </c>
       <c r="D15">
-        <v>-2.78</v>
+        <v>0.88</v>
       </c>
       <c r="E15">
         <v>380.65</v>
@@ -2432,46 +2444,46 @@
         <v>192.33</v>
       </c>
       <c r="G15">
-        <v>-49.47</v>
+        <v>-49.03</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="I15">
-        <v>-10.6</v>
+        <v>-10.03</v>
       </c>
       <c r="J15">
-        <v>-14.21</v>
+        <v>-13.24</v>
       </c>
       <c r="K15">
-        <v>-19.24</v>
+        <v>-17.03</v>
       </c>
       <c r="L15">
-        <v>-44.19</v>
+        <v>-43.19</v>
       </c>
       <c r="M15">
-        <v>7.3</v>
+        <v>5.41</v>
       </c>
       <c r="N15">
         <v>13</v>
       </c>
       <c r="O15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>203.25</v>
+        <v>198.92</v>
       </c>
       <c r="Q15">
-        <v>217.06</v>
+        <v>215.26</v>
       </c>
       <c r="R15">
-        <v>224.84</v>
+        <v>224.07</v>
       </c>
       <c r="S15">
-        <v>249.17</v>
+        <v>248.54</v>
       </c>
       <c r="T15">
-        <v>-22.81</v>
+        <v>-21.94</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2486,43 +2498,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>21.42</v>
+        <v>24.4</v>
       </c>
       <c r="Z15">
-        <v>-7.49</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AA15">
-        <v>-5.2</v>
+        <v>-5.79</v>
       </c>
       <c r="AB15">
-        <v>-2.29</v>
+        <v>-2.34</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="AD15">
-        <v>3.23</v>
+        <v>1.67</v>
       </c>
       <c r="AE15">
-        <v>8.5</v>
+        <v>8.32</v>
       </c>
       <c r="AF15">
-        <v>-49.32</v>
+        <v>7.48</v>
       </c>
       <c r="AG15">
-        <v>239.5</v>
+        <v>239.06</v>
       </c>
       <c r="AH15">
-        <v>194.62</v>
+        <v>191.47</v>
       </c>
       <c r="AI15">
-        <v>222.11</v>
+        <v>220.55</v>
       </c>
       <c r="AJ15" t="s">
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>34.13</v>
+        <v>37.51</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2533,10 +2545,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>34.82</v>
+        <v>34.33</v>
       </c>
       <c r="D16">
-        <v>1.52</v>
+        <v>-1.41</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2545,25 +2557,25 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-40.66</v>
+        <v>-41.5</v>
       </c>
       <c r="H16">
-        <v>11.03</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I16">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="J16">
-        <v>-10.53</v>
+        <v>-9.66</v>
       </c>
       <c r="K16">
-        <v>-18.59</v>
+        <v>-18.75</v>
       </c>
       <c r="L16">
-        <v>-37.34</v>
+        <v>-37.53</v>
       </c>
       <c r="M16">
-        <v>-1.26</v>
+        <v>-3.42</v>
       </c>
       <c r="N16">
         <v>26</v>
@@ -2572,19 +2584,19 @@
         <v>13</v>
       </c>
       <c r="P16">
-        <v>34.99</v>
+        <v>34.96</v>
       </c>
       <c r="Q16">
-        <v>35.88</v>
+        <v>35.69</v>
       </c>
       <c r="R16">
-        <v>37.57</v>
+        <v>37.47</v>
       </c>
       <c r="S16">
-        <v>41.71</v>
+        <v>41.64</v>
       </c>
       <c r="T16">
-        <v>-16.53</v>
+        <v>-17.56</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2599,34 +2611,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>41.33</v>
+        <v>39.05</v>
       </c>
       <c r="Z16">
+        <v>-0.86</v>
+      </c>
+      <c r="AA16">
         <v>-0.84</v>
       </c>
-      <c r="AA16">
-        <v>-0.83</v>
-      </c>
       <c r="AB16">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AC16">
-        <v>58.08</v>
+        <v>51.49</v>
       </c>
       <c r="AD16">
-        <v>63.37</v>
+        <v>59.82</v>
       </c>
       <c r="AE16">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AF16">
-        <v>46.69</v>
+        <v>-63.47</v>
       </c>
       <c r="AG16">
-        <v>37.89</v>
+        <v>37.55</v>
       </c>
       <c r="AH16">
-        <v>33.87</v>
+        <v>33.84</v>
       </c>
       <c r="AI16">
         <v>37.92</v>
@@ -2635,7 +2647,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>17.32</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2646,10 +2658,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1053.2</v>
+        <v>1061.3</v>
       </c>
       <c r="D17">
-        <v>-1.57</v>
+        <v>0.77</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2658,46 +2670,46 @@
         <v>1053.2</v>
       </c>
       <c r="G17">
-        <v>-32.33</v>
+        <v>-31.81</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="I17">
-        <v>-5.41</v>
+        <v>-5.09</v>
       </c>
       <c r="J17">
-        <v>-12.6</v>
+        <v>-7.88</v>
       </c>
       <c r="K17">
-        <v>-17.73</v>
+        <v>-17.38</v>
       </c>
       <c r="L17">
-        <v>-21.17</v>
+        <v>-22.54</v>
       </c>
       <c r="M17">
-        <v>-2.37</v>
+        <v>-2.77</v>
       </c>
       <c r="N17">
         <v>44</v>
       </c>
       <c r="O17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P17">
-        <v>1093.38</v>
+        <v>1082</v>
       </c>
       <c r="Q17">
-        <v>1129.72</v>
+        <v>1123.89</v>
       </c>
       <c r="R17">
-        <v>1213.34</v>
+        <v>1208.36</v>
       </c>
       <c r="S17">
-        <v>1330.14</v>
+        <v>1328.53</v>
       </c>
       <c r="T17">
-        <v>-20.82</v>
+        <v>-20.11</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2712,34 +2724,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>31.17</v>
+        <v>33.32</v>
       </c>
       <c r="Z17">
-        <v>-36.78</v>
+        <v>-37.83</v>
       </c>
       <c r="AA17">
-        <v>-34.09</v>
+        <v>-34.83</v>
       </c>
       <c r="AB17">
-        <v>-2.69</v>
+        <v>-2.99</v>
       </c>
       <c r="AC17">
-        <v>31.23</v>
+        <v>25.19</v>
       </c>
       <c r="AD17">
-        <v>56.52</v>
+        <v>38.65</v>
       </c>
       <c r="AE17">
-        <v>31.6</v>
+        <v>30.71</v>
       </c>
       <c r="AF17">
-        <v>-12.67</v>
+        <v>-41.69</v>
       </c>
       <c r="AG17">
-        <v>1195.76</v>
+        <v>1192.53</v>
       </c>
       <c r="AH17">
-        <v>1063.68</v>
+        <v>1055.24</v>
       </c>
       <c r="AI17">
         <v>1154.39</v>
@@ -2748,7 +2760,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>40.09</v>
+        <v>42.64</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2947,1339 +2959,1342 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1.25</v>
+      <c r="B7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.89</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>-3.8</v>
+        <v>-0.37</v>
       </c>
       <c r="E8" s="7">
-        <v>0.09</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.6</v>
+        <v>-3.8</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.61</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.01</v>
+        <v>-4.79</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.91</v>
+        <v>-3.61</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.07</v>
+        <v>-5.89</v>
       </c>
       <c r="E10" s="7">
-        <v>0.84</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.9</v>
+        <v>-4.07</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.97</v>
+        <v>-2.61</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-8.48</v>
+        <v>-2.93</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.13</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.35</v>
+        <v>-1.92</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-13.68</v>
+        <v>-7.13</v>
       </c>
       <c r="D13" s="6">
-        <v>-14.99</v>
+        <v>-5.76</v>
       </c>
       <c r="E13" s="8">
-        <v>-1.31</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.45</v>
+        <v>-14.99</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.51</v>
+        <v>-13.97</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.02</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>3.46</v>
+        <v>-2.94</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.11</v>
+        <v>-1.01</v>
       </c>
       <c r="E15" s="8">
-        <v>-3.57</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-3.27</v>
+        <v>-3.43</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-14.53</v>
+        <v>-3.3</v>
       </c>
       <c r="D17" s="6">
-        <v>-12.41</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.12</v>
+        <v>-3.11</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.19</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-10.1</v>
+        <v>-12.41</v>
       </c>
       <c r="D18" s="6">
-        <v>-10.58</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="E18" s="8">
-        <v>-0.48</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-8.970000000000001</v>
+        <v>-10.58</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.630000000000001</v>
+        <v>-9.74</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.66</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-13.07</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="D20" s="6">
-        <v>-14.21</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="E20" s="8">
-        <v>-1.14</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-11.09</v>
+        <v>-14.21</v>
       </c>
       <c r="D21" s="6">
-        <v>-10.53</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.5600000000000001</v>
+        <v>-13.24</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.97</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-10.42</v>
+        <v>-10.53</v>
       </c>
       <c r="D22" s="6">
-        <v>-12.6</v>
+        <v>-9.66</v>
       </c>
       <c r="E22" s="8">
-        <v>-2.18</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-2.02</v>
+        <v>-12.6</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.54</v>
+        <v>-7.88</v>
+      </c>
+      <c r="E23" s="8">
+        <v>4.72</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-10.41</v>
+        <v>-1.48</v>
       </c>
       <c r="D24" s="6">
-        <v>-10.46</v>
+        <v>-0.25</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.05</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-1.43</v>
+        <v>-10.46</v>
       </c>
       <c r="D25" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="E25" s="7">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="E25" s="8">
         <v>1.1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-8.73</v>
+        <v>-0.33</v>
       </c>
       <c r="D26" s="6">
-        <v>-6.81</v>
+        <v>-1.61</v>
       </c>
       <c r="E26" s="7">
-        <v>1.92</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-2.61</v>
+        <v>-6.81</v>
       </c>
       <c r="D27" s="6">
-        <v>0.78</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.39</v>
+        <v>-4.09</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2.72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-4.51</v>
+        <v>0.78</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.97</v>
+        <v>0.64</v>
       </c>
       <c r="E28" s="7">
-        <v>1.54</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-3.83</v>
+        <v>-2.97</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.86</v>
+        <v>-3</v>
       </c>
       <c r="E29" s="7">
-        <v>0.97</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-8.050000000000001</v>
+        <v>-2.86</v>
       </c>
       <c r="D30" s="6">
-        <v>-6.58</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.47</v>
+        <v>-2.57</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.71</v>
+        <v>-6.58</v>
       </c>
       <c r="D31" s="6">
-        <v>-3.66</v>
+        <v>-4.58</v>
       </c>
       <c r="E31" s="8">
-        <v>-0.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-3.42</v>
+        <v>-3.66</v>
       </c>
       <c r="D32" s="6">
-        <v>-5.33</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.91</v>
+        <v>-4.35</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.87</v>
+        <v>-5.33</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.57</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.3</v>
+        <v>-5.23</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-6</v>
+        <v>-0.57</v>
       </c>
       <c r="D34" s="6">
-        <v>-6.56</v>
+        <v>1.56</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.5600000000000001</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-5.49</v>
+        <v>-6.56</v>
       </c>
       <c r="D35" s="6">
-        <v>-4.44</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.05</v>
+        <v>-6.22</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.34</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-8.550000000000001</v>
+        <v>-4.44</v>
       </c>
       <c r="D36" s="6">
-        <v>-10.6</v>
+        <v>-3.35</v>
       </c>
       <c r="E36" s="8">
-        <v>-2.05</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-3.73</v>
+        <v>-10.6</v>
       </c>
       <c r="D37" s="6">
-        <v>-0.57</v>
-      </c>
-      <c r="E37" s="7">
-        <v>3.16</v>
+        <v>-10.03</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.57</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-5.31</v>
+        <v>-0.57</v>
       </c>
       <c r="D38" s="6">
-        <v>-5.41</v>
+        <v>-0.32</v>
       </c>
       <c r="E38" s="8">
-        <v>-0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.48</v>
+        <v>-5.41</v>
       </c>
       <c r="D39" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.64</v>
+        <v>-5.09</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.32</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="6">
-        <v>3.01</v>
+        <v>1.16</v>
       </c>
       <c r="D40" s="6">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="E40" s="7">
-        <v>0.6899999999999999</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>-36.59</v>
+        <v>3.7</v>
       </c>
       <c r="D41" s="6">
-        <v>-34.39</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.2</v>
+        <v>4.79</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>-34.8</v>
+        <v>-34.39</v>
       </c>
       <c r="D42" s="6">
-        <v>-33.7</v>
+        <v>-35.84</v>
       </c>
       <c r="E42" s="7">
-        <v>1.1</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.16</v>
+        <v>-33.7</v>
       </c>
       <c r="D43" s="6">
-        <v>4.29</v>
-      </c>
-      <c r="E43" s="7">
-        <v>4.45</v>
+        <v>-32.26</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1.44</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-15.58</v>
+        <v>4.29</v>
       </c>
       <c r="D44" s="6">
-        <v>-13.75</v>
+        <v>3.98</v>
       </c>
       <c r="E44" s="7">
-        <v>1.83</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-42.43</v>
+        <v>-13.75</v>
       </c>
       <c r="D45" s="6">
-        <v>-40.63</v>
+        <v>-14.36</v>
       </c>
       <c r="E45" s="7">
-        <v>1.8</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-25.56</v>
+        <v>-40.63</v>
       </c>
       <c r="D46" s="6">
-        <v>-28.66</v>
+        <v>-40.38</v>
       </c>
       <c r="E46" s="8">
-        <v>-3.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-6.99</v>
+        <v>-28.66</v>
       </c>
       <c r="D47" s="6">
-        <v>-8.77</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-1.78</v>
+        <v>-29.33</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>9.119999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="D48" s="6">
-        <v>8.52</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.6</v>
+        <v>-9.42</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-28.18</v>
+        <v>8.52</v>
       </c>
       <c r="D49" s="6">
-        <v>-25.86</v>
+        <v>7.59</v>
       </c>
       <c r="E49" s="7">
-        <v>2.32</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>35.77</v>
+        <v>-25.86</v>
       </c>
       <c r="D50" s="6">
-        <v>35.72</v>
+        <v>-24.38</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.05</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-44.64</v>
+        <v>35.72</v>
       </c>
       <c r="D51" s="6">
-        <v>-44.78</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.14</v>
+        <v>34.66</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-45.87</v>
+        <v>-44.78</v>
       </c>
       <c r="D52" s="6">
-        <v>-44.19</v>
+        <v>-45.38</v>
       </c>
       <c r="E52" s="7">
-        <v>1.68</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-38.55</v>
+        <v>-44.19</v>
       </c>
       <c r="D53" s="6">
-        <v>-37.34</v>
-      </c>
-      <c r="E53" s="7">
-        <v>1.21</v>
+        <v>-43.19</v>
+      </c>
+      <c r="E53" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-21.79</v>
+        <v>-37.34</v>
       </c>
       <c r="D54" s="6">
-        <v>-21.17</v>
+        <v>-37.53</v>
       </c>
       <c r="E54" s="7">
-        <v>0.62</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>1.1</v>
+        <v>-21.17</v>
       </c>
       <c r="D55" s="6">
-        <v>-1.45</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-2.55</v>
+        <v>-22.54</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="6">
-        <v>-1.42</v>
+        <v>-1.45</v>
       </c>
       <c r="D56" s="6">
-        <v>-4.34</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-2.92</v>
+        <v>-1.78</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>-12.12</v>
+        <v>-4.34</v>
       </c>
       <c r="D57" s="6">
-        <v>-12.47</v>
+        <v>-3.93</v>
       </c>
       <c r="E57" s="8">
-        <v>-0.35</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-11.22</v>
+        <v>-12.47</v>
       </c>
       <c r="D58" s="6">
-        <v>-12.31</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-1.09</v>
+        <v>-15.04</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-2.57</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-14.54</v>
+        <v>-12.31</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.73</v>
-      </c>
-      <c r="E59" s="7">
-        <v>2.81</v>
+        <v>-11.31</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-14.24</v>
+        <v>-11.73</v>
       </c>
       <c r="D60" s="6">
-        <v>-14.3</v>
+        <v>-11.35</v>
       </c>
       <c r="E60" s="8">
-        <v>-0.06</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-15.86</v>
+        <v>-14.3</v>
       </c>
       <c r="D61" s="6">
-        <v>-15.93</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-14.68</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-7.12</v>
+        <v>-15.93</v>
       </c>
       <c r="D62" s="6">
-        <v>-7.83</v>
+        <v>-15.13</v>
       </c>
       <c r="E62" s="8">
-        <v>-0.71</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-4.62</v>
+        <v>-7.83</v>
       </c>
       <c r="D63" s="6">
-        <v>-6.68</v>
+        <v>-6.4</v>
       </c>
       <c r="E63" s="8">
-        <v>-2.06</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-1.8</v>
+        <v>-6.68</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.22</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-4.42</v>
+        <v>-6.9</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-0.85</v>
+        <v>-6.22</v>
       </c>
       <c r="D65" s="6">
-        <v>-0.88</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.03</v>
+        <v>-6.67</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>2.36</v>
+        <v>-0.88</v>
       </c>
       <c r="D66" s="6">
-        <v>1.22</v>
+        <v>2.76</v>
       </c>
       <c r="E66" s="8">
-        <v>-1.14</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-20.98</v>
+        <v>1.22</v>
       </c>
       <c r="D67" s="6">
-        <v>-22.77</v>
+        <v>2.13</v>
       </c>
       <c r="E67" s="8">
-        <v>-1.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-16.43</v>
+        <v>-22.77</v>
       </c>
       <c r="D68" s="6">
-        <v>-19.24</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-2.81</v>
+        <v>-22.84</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-20.36</v>
+        <v>-19.24</v>
       </c>
       <c r="D69" s="6">
-        <v>-18.59</v>
-      </c>
-      <c r="E69" s="7">
-        <v>1.77</v>
+        <v>-17.03</v>
+      </c>
+      <c r="E69" s="8">
+        <v>2.21</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-17.09</v>
+        <v>-18.59</v>
       </c>
       <c r="D70" s="6">
-        <v>-17.73</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-0.64</v>
+        <v>-18.75</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-3.14</v>
+        <v>-17.73</v>
       </c>
       <c r="D71" s="6">
-        <v>-4.56</v>
+        <v>-17.38</v>
       </c>
       <c r="E71" s="8">
-        <v>-1.42</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-15.44</v>
+        <v>-4.56</v>
       </c>
       <c r="D72" s="6">
-        <v>-17.78</v>
+        <v>-3.63</v>
       </c>
       <c r="E72" s="8">
-        <v>-2.34</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-35.1</v>
+        <v>-17.78</v>
       </c>
       <c r="D73" s="6">
-        <v>-35.12</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-0.02</v>
+        <v>-18.16</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-33.3</v>
+        <v>-35.12</v>
       </c>
       <c r="D74" s="6">
-        <v>-33.41</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-0.11</v>
+        <v>-35.94</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-19.67</v>
+        <v>-33.41</v>
       </c>
       <c r="D75" s="6">
-        <v>-18.37</v>
-      </c>
-      <c r="E75" s="7">
-        <v>1.3</v>
+        <v>-32.36</v>
+      </c>
+      <c r="E75" s="8">
+        <v>1.05</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-24.66</v>
+        <v>-18.37</v>
       </c>
       <c r="D76" s="6">
-        <v>-24.07</v>
+        <v>-18.65</v>
       </c>
       <c r="E76" s="7">
-        <v>0.59</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-46.28</v>
+        <v>-24.07</v>
       </c>
       <c r="D77" s="6">
-        <v>-46.21</v>
+        <v>-24.33</v>
       </c>
       <c r="E77" s="7">
-        <v>0.07000000000000001</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-41.09</v>
+        <v>-46.21</v>
       </c>
       <c r="D78" s="6">
-        <v>-41.57</v>
+        <v>-46</v>
       </c>
       <c r="E78" s="8">
-        <v>-0.48</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-22.26</v>
+        <v>-41.57</v>
       </c>
       <c r="D79" s="6">
-        <v>-24.18</v>
+        <v>-40.93</v>
       </c>
       <c r="E79" s="8">
-        <v>-1.92</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-14.94</v>
+        <v>-24.18</v>
       </c>
       <c r="D80" s="6">
-        <v>-17.84</v>
+        <v>-23.88</v>
       </c>
       <c r="E80" s="8">
-        <v>-2.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-36.35</v>
+        <v>-17.84</v>
       </c>
       <c r="D81" s="6">
-        <v>-35.6</v>
-      </c>
-      <c r="E81" s="7">
-        <v>0.75</v>
+        <v>-17.78</v>
+      </c>
+      <c r="E81" s="8">
+        <v>0.06</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-11.26</v>
+        <v>-35.6</v>
       </c>
       <c r="D82" s="6">
-        <v>-12.64</v>
+        <v>-34.37</v>
       </c>
       <c r="E82" s="8">
-        <v>-1.38</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-45.66</v>
+        <v>-12.64</v>
       </c>
       <c r="D83" s="6">
-        <v>-46.53</v>
+        <v>-11.4</v>
       </c>
       <c r="E83" s="8">
-        <v>-0.87</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4290,13 +4305,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-48.03</v>
+        <v>-49.47</v>
       </c>
       <c r="D84" s="6">
-        <v>-49.47</v>
+        <v>-49.03</v>
       </c>
       <c r="E84" s="8">
-        <v>-1.44</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4307,13 +4322,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-41.55</v>
+        <v>-40.66</v>
       </c>
       <c r="D85" s="6">
-        <v>-40.66</v>
+        <v>-41.5</v>
       </c>
       <c r="E85" s="7">
-        <v>0.89</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4324,13 +4339,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-31.25</v>
+        <v>-32.33</v>
       </c>
       <c r="D86" s="6">
-        <v>-32.33</v>
+        <v>-31.81</v>
       </c>
       <c r="E86" s="8">
-        <v>-1.08</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4341,13 +4356,13 @@
         <v>2</v>
       </c>
       <c r="C87" s="6">
-        <v>728.65</v>
+        <v>718</v>
       </c>
       <c r="D87" s="6">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="E87" s="8">
-        <v>-10.65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4358,13 +4373,13 @@
         <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>914.5</v>
+        <v>889.2</v>
       </c>
       <c r="D88" s="6">
-        <v>889.2</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-25.3</v>
+        <v>885.1</v>
+      </c>
+      <c r="E88" s="7">
+        <v>-4.1</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4375,13 +4390,13 @@
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>199.73</v>
+        <v>199.69</v>
       </c>
       <c r="D89" s="6">
-        <v>199.69</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.04</v>
+        <v>197.16</v>
+      </c>
+      <c r="E89" s="7">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4392,13 +4407,13 @@
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>611.45</v>
+        <v>607.8</v>
       </c>
       <c r="D90" s="6">
-        <v>607.8</v>
+        <v>617.4</v>
       </c>
       <c r="E90" s="8">
-        <v>-3.65</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4409,13 +4424,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>1656.2</v>
+        <v>1683</v>
       </c>
       <c r="D91" s="6">
-        <v>1683</v>
+        <v>1677.2</v>
       </c>
       <c r="E91" s="7">
-        <v>26.8</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4426,13 +4441,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>949.5</v>
+        <v>957</v>
       </c>
       <c r="D92" s="6">
-        <v>957</v>
+        <v>953.75</v>
       </c>
       <c r="E92" s="7">
-        <v>7.5</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4443,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>3088.9</v>
+        <v>3092.8</v>
       </c>
       <c r="D93" s="6">
-        <v>3092.8</v>
-      </c>
-      <c r="E93" s="7">
-        <v>3.9</v>
+        <v>3105</v>
+      </c>
+      <c r="E93" s="8">
+        <v>12.2</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4460,13 +4475,13 @@
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>620.05</v>
+        <v>615.05</v>
       </c>
       <c r="D94" s="6">
-        <v>615.05</v>
+        <v>621.75</v>
       </c>
       <c r="E94" s="8">
-        <v>-5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4477,13 +4492,13 @@
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>359</v>
+        <v>350.15</v>
       </c>
       <c r="D95" s="6">
-        <v>350.15</v>
+        <v>351.5</v>
       </c>
       <c r="E95" s="8">
-        <v>-8.85</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4494,13 +4509,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>184.3</v>
+        <v>178</v>
       </c>
       <c r="D96" s="6">
-        <v>178</v>
+        <v>178.14</v>
       </c>
       <c r="E96" s="8">
-        <v>-6.3</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4511,13 +4526,13 @@
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>2050.6</v>
+        <v>2075</v>
       </c>
       <c r="D97" s="6">
-        <v>2075</v>
-      </c>
-      <c r="E97" s="7">
-        <v>24.4</v>
+        <v>2114.4</v>
+      </c>
+      <c r="E97" s="8">
+        <v>39.4</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4528,699 +4543,665 @@
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>4587</v>
+        <v>4515.7</v>
       </c>
       <c r="D98" s="6">
-        <v>4515.7</v>
+        <v>4580</v>
       </c>
       <c r="E98" s="8">
-        <v>-71.3</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>2621.6</v>
+        <v>192.33</v>
       </c>
       <c r="D99" s="6">
-        <v>2580</v>
+        <v>194.02</v>
       </c>
       <c r="E99" s="8">
-        <v>-41.6</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>197.82</v>
+        <v>34.82</v>
       </c>
       <c r="D100" s="6">
-        <v>192.33</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-5.49</v>
+        <v>34.33</v>
+      </c>
+      <c r="E100" s="7">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>34.3</v>
+        <v>1053.2</v>
       </c>
       <c r="D101" s="6">
-        <v>34.82</v>
-      </c>
-      <c r="E101" s="7">
-        <v>0.52</v>
+        <v>1061.3</v>
+      </c>
+      <c r="E101" s="8">
+        <v>8.1</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C102" s="6">
-        <v>1070</v>
+        <v>87</v>
       </c>
       <c r="D102" s="6">
-        <v>1053.2</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-16.8</v>
+        <v>81</v>
+      </c>
+      <c r="E102" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C103" s="6">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D103" s="6">
-        <v>74</v>
-      </c>
-      <c r="E103" s="7">
+        <v>87</v>
+      </c>
+      <c r="E103" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C104" s="6">
+        <v>62</v>
+      </c>
+      <c r="D104" s="6">
         <v>56</v>
       </c>
-      <c r="D104" s="6">
-        <v>50</v>
-      </c>
-      <c r="E104" s="8">
+      <c r="E104" s="7">
         <v>-6</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C105" s="6">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D105" s="6">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E105" s="8">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C106" s="6">
-        <v>50</v>
+        <v>46.86</v>
       </c>
       <c r="D106" s="6">
-        <v>56</v>
-      </c>
-      <c r="E106" s="7">
-        <v>6</v>
+        <v>50.07</v>
+      </c>
+      <c r="E106" s="8">
+        <v>3.21</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C107" s="6">
-        <v>51.55</v>
+        <v>39.65</v>
       </c>
       <c r="D107" s="6">
-        <v>46.86</v>
-      </c>
-      <c r="E107" s="8">
-        <v>-4.69</v>
+        <v>39.1</v>
+      </c>
+      <c r="E107" s="7">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C108" s="6">
-        <v>43.09</v>
+        <v>31.95</v>
       </c>
       <c r="D108" s="6">
-        <v>39.65</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-3.44</v>
+        <v>26.97</v>
+      </c>
+      <c r="E108" s="7">
+        <v>-4.98</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C109" s="6">
-        <v>32.04</v>
+        <v>39.21</v>
       </c>
       <c r="D109" s="6">
-        <v>31.95</v>
+        <v>41.92</v>
       </c>
       <c r="E109" s="8">
-        <v>-0.09</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C110" s="6">
-        <v>39.87</v>
+        <v>43.8</v>
       </c>
       <c r="D110" s="6">
-        <v>39.21</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-0.66</v>
+        <v>42.79</v>
+      </c>
+      <c r="E110" s="7">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C111" s="6">
-        <v>37.48</v>
+        <v>33.69</v>
       </c>
       <c r="D111" s="6">
-        <v>43.8</v>
+        <v>32.92</v>
       </c>
       <c r="E111" s="7">
-        <v>6.32</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>30.17</v>
+        <v>24.3</v>
       </c>
       <c r="D112" s="6">
-        <v>33.69</v>
-      </c>
-      <c r="E112" s="7">
-        <v>3.52</v>
+        <v>26.05</v>
+      </c>
+      <c r="E112" s="8">
+        <v>1.75</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>23.77</v>
+        <v>38.06</v>
       </c>
       <c r="D113" s="6">
-        <v>24.3</v>
-      </c>
-      <c r="E113" s="7">
-        <v>0.53</v>
+        <v>40.53</v>
+      </c>
+      <c r="E113" s="8">
+        <v>2.47</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>39.19</v>
+        <v>35.24</v>
       </c>
       <c r="D114" s="6">
-        <v>38.06</v>
+        <v>36.91</v>
       </c>
       <c r="E114" s="8">
-        <v>-1.13</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>42.01</v>
+        <v>38.02</v>
       </c>
       <c r="D115" s="6">
-        <v>35.24</v>
+        <v>38.29</v>
       </c>
       <c r="E115" s="8">
-        <v>-6.77</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>46.53</v>
+        <v>36.09</v>
       </c>
       <c r="D116" s="6">
-        <v>38.02</v>
+        <v>42.59</v>
       </c>
       <c r="E116" s="8">
-        <v>-8.51</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>31.63</v>
+        <v>26.8</v>
       </c>
       <c r="D117" s="6">
-        <v>36.09</v>
-      </c>
-      <c r="E117" s="7">
-        <v>4.46</v>
+        <v>32.64</v>
+      </c>
+      <c r="E117" s="8">
+        <v>5.84</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>29.43</v>
+        <v>21.42</v>
       </c>
       <c r="D118" s="6">
-        <v>26.8</v>
+        <v>24.4</v>
       </c>
       <c r="E118" s="8">
-        <v>-2.63</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>27.53</v>
+        <v>41.33</v>
       </c>
       <c r="D119" s="6">
-        <v>24.71</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-2.82</v>
+        <v>39.05</v>
+      </c>
+      <c r="E119" s="7">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>24.31</v>
+        <v>31.17</v>
       </c>
       <c r="D120" s="6">
-        <v>21.42</v>
+        <v>33.32</v>
       </c>
       <c r="E120" s="8">
-        <v>-2.89</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C121" s="6">
-        <v>37.75</v>
+        <v>37.18</v>
       </c>
       <c r="D121" s="6">
-        <v>41.33</v>
+        <v>20.36</v>
       </c>
       <c r="E121" s="7">
-        <v>3.58</v>
+        <v>-16.82</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C122" s="6">
-        <v>33.24</v>
+        <v>-19.5</v>
       </c>
       <c r="D122" s="6">
-        <v>31.17</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-2.07</v>
+        <v>-62.01</v>
+      </c>
+      <c r="E122" s="7">
+        <v>-42.51</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C123" s="6">
-        <v>24.38</v>
+        <v>16.37</v>
       </c>
       <c r="D123" s="6">
-        <v>37.18</v>
+        <v>-44.03</v>
       </c>
       <c r="E123" s="7">
-        <v>12.8</v>
+        <v>-60.4</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C124" s="6">
-        <v>-66.63</v>
+        <v>-65.94</v>
       </c>
       <c r="D124" s="6">
-        <v>-19.5</v>
+        <v>-73.64</v>
       </c>
       <c r="E124" s="7">
-        <v>47.13</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C125" s="6">
-        <v>-22.38</v>
+        <v>-40.67</v>
       </c>
       <c r="D125" s="6">
-        <v>16.37</v>
+        <v>-62.42</v>
       </c>
       <c r="E125" s="7">
-        <v>38.75</v>
+        <v>-21.75</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C126" s="6">
-        <v>-68.62</v>
+        <v>49.4</v>
       </c>
       <c r="D126" s="6">
-        <v>-65.94</v>
+        <v>21.9</v>
       </c>
       <c r="E126" s="7">
-        <v>2.68</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C127" s="6">
-        <v>-44.13</v>
+        <v>41.47</v>
       </c>
       <c r="D127" s="6">
-        <v>-40.67</v>
+        <v>-2.51</v>
       </c>
       <c r="E127" s="7">
-        <v>3.46</v>
+        <v>-43.98</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>39.64</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="D128" s="6">
-        <v>49.4</v>
+        <v>-88.94</v>
       </c>
       <c r="E128" s="7">
-        <v>9.76</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>57.27</v>
+        <v>-0.32</v>
       </c>
       <c r="D129" s="6">
-        <v>41.47</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-15.8</v>
+        <v>-35.24</v>
+      </c>
+      <c r="E129" s="7">
+        <v>-34.92</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>-86.48</v>
+        <v>76.84</v>
       </c>
       <c r="D130" s="6">
-        <v>-87.76000000000001</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-1.28</v>
+        <v>-24.34</v>
+      </c>
+      <c r="E130" s="7">
+        <v>-101.18</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>26.64</v>
+        <v>11.15</v>
       </c>
       <c r="D131" s="6">
-        <v>-0.32</v>
+        <v>68.94</v>
       </c>
       <c r="E131" s="8">
-        <v>-26.96</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>19.2</v>
+        <v>11.72</v>
       </c>
       <c r="D132" s="6">
-        <v>76.84</v>
-      </c>
-      <c r="E132" s="7">
-        <v>57.64</v>
+        <v>15.81</v>
+      </c>
+      <c r="E132" s="8">
+        <v>4.09</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>19.96</v>
+        <v>23.11</v>
       </c>
       <c r="D133" s="6">
-        <v>11.15</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-8.81</v>
+        <v>8.41</v>
+      </c>
+      <c r="E133" s="7">
+        <v>-14.7</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>52.69</v>
+        <v>-49.32</v>
       </c>
       <c r="D134" s="6">
-        <v>11.72</v>
+        <v>7.48</v>
       </c>
       <c r="E134" s="8">
-        <v>-40.97</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>6.49</v>
+        <v>46.69</v>
       </c>
       <c r="D135" s="6">
-        <v>23.11</v>
+        <v>-63.47</v>
       </c>
       <c r="E135" s="7">
-        <v>16.62</v>
+        <v>-110.16</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>37.43</v>
+        <v>-12.67</v>
       </c>
       <c r="D136" s="6">
-        <v>-49.32</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-86.75</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C137" s="6">
-        <v>-41.31</v>
-      </c>
-      <c r="D137" s="6">
-        <v>46.69</v>
-      </c>
-      <c r="E137" s="7">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C138" s="6">
-        <v>37.79</v>
-      </c>
-      <c r="D138" s="6">
-        <v>-12.67</v>
-      </c>
-      <c r="E138" s="8">
-        <v>-50.46</v>
+        <v>-41.69</v>
+      </c>
+      <c r="E136" s="7">
+        <v>-29.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5244,28 +5225,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5279,16 +5260,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>34.5</v>
+        <v>35.8</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-7.1</v>
+        <v>-6.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-10.7</v>
+        <v>-10.3</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5405,10 +5386,10 @@
         <v>49</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>46</v>
@@ -5417,10 +5398,10 @@
         <v>50</v>
       </c>
       <c r="H1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>38</v>
@@ -5428,42 +5409,42 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3566</v>
+        <v>0.3556</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3238</v>
+        <v>0.313</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1994</v>
+        <v>0.1981</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1707</v>
+        <v>0.1618</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1616</v>
+        <v>0.1504</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0973</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G2" s="14">
-        <v>0.073</v>
+        <v>0.0541</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0483</v>
+        <v>0.044</v>
       </c>
       <c r="I2" s="14">
-        <v>0.04480000000000001</v>
+        <v>0.0416</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0354</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>52</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
@@ -5480,22 +5461,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.0126</v>
+        <v>-0.0277</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0237</v>
+        <v>-0.0342</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0576</v>
+        <v>-0.0635</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0644</v>
+        <v>-0.0655</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.0863</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1085</v>
+        <v>-0.1096</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,31 +214,31 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.0 → 39.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>39.6</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.9 → 50.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.9</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.8 → 32.6</t>
-  </si>
-  <si>
-    <t>26.8</t>
-  </si>
-  <si>
-    <t>32.6</t>
+    <t>24.7 → 61.0</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>61.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -450,8 +450,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -963,10 +963,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="D2">
-        <v>0.97</v>
+        <v>1.52</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -975,46 +975,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-3.63</v>
+        <v>-2.17</v>
       </c>
       <c r="H2">
-        <v>26.98</v>
+        <v>28.91</v>
       </c>
       <c r="I2">
-        <v>-0.25</v>
+        <v>3.52</v>
       </c>
       <c r="J2">
-        <v>-0.37</v>
+        <v>0.55</v>
       </c>
       <c r="K2">
-        <v>-1.78</v>
+        <v>-1.33</v>
       </c>
       <c r="L2">
-        <v>0.1</v>
+        <v>2.18</v>
       </c>
       <c r="M2">
-        <v>31.3</v>
+        <v>32.87</v>
       </c>
       <c r="N2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>719.4</v>
+        <v>724.4</v>
       </c>
       <c r="Q2">
-        <v>723.9299999999999</v>
+        <v>724.73</v>
       </c>
       <c r="R2">
-        <v>727.55</v>
+        <v>727.72</v>
       </c>
       <c r="S2">
-        <v>688.12</v>
+        <v>688.17</v>
       </c>
       <c r="T2">
-        <v>5.36</v>
+        <v>6.95</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1029,34 +1029,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>50.07</v>
+        <v>54.71</v>
       </c>
       <c r="Z2">
-        <v>-0.59</v>
+        <v>0.39</v>
       </c>
       <c r="AA2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="AB2">
-        <v>-0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AC2">
-        <v>37.09</v>
+        <v>42.99</v>
       </c>
       <c r="AD2">
-        <v>27.85</v>
+        <v>35.67</v>
       </c>
       <c r="AE2">
-        <v>16.14</v>
+        <v>16.11</v>
       </c>
       <c r="AF2">
-        <v>20.36</v>
+        <v>-22.34</v>
       </c>
       <c r="AG2">
-        <v>743.4</v>
+        <v>744.8200000000001</v>
       </c>
       <c r="AH2">
-        <v>704.46</v>
+        <v>704.63</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1065,7 +1065,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>17.01</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1076,10 +1076,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>885.1</v>
+        <v>924.15</v>
       </c>
       <c r="D3">
-        <v>-0.46</v>
+        <v>4.41</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1088,46 +1088,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-18.16</v>
+        <v>-14.55</v>
       </c>
       <c r="H3">
-        <v>75.14</v>
+        <v>82.87</v>
       </c>
       <c r="I3">
-        <v>-9.359999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="J3">
-        <v>-4.79</v>
+        <v>-1.03</v>
       </c>
       <c r="K3">
-        <v>-3.93</v>
+        <v>1.1</v>
       </c>
       <c r="L3">
-        <v>4.79</v>
+        <v>9.9</v>
       </c>
       <c r="M3">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="N3">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>905.51</v>
+        <v>907.05</v>
       </c>
       <c r="Q3">
-        <v>950.8</v>
+        <v>951.45</v>
       </c>
       <c r="R3">
-        <v>957.8099999999999</v>
+        <v>957.64</v>
       </c>
       <c r="S3">
-        <v>766.52</v>
+        <v>767.41</v>
       </c>
       <c r="T3">
-        <v>15.47</v>
+        <v>20.43</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1142,34 +1142,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.1</v>
+        <v>46.64</v>
       </c>
       <c r="Z3">
-        <v>-10.08</v>
+        <v>-10.22</v>
       </c>
       <c r="AA3">
-        <v>0.89</v>
+        <v>-1.33</v>
       </c>
       <c r="AB3">
-        <v>-10.97</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>4.54</v>
       </c>
       <c r="AE3">
-        <v>43.79</v>
+        <v>43.89</v>
       </c>
       <c r="AF3">
-        <v>-62.01</v>
+        <v>-44.31</v>
       </c>
       <c r="AG3">
-        <v>1031.79</v>
+        <v>1031.31</v>
       </c>
       <c r="AH3">
-        <v>869.8200000000001</v>
+        <v>871.59</v>
       </c>
       <c r="AI3">
         <v>1028.89</v>
@@ -1178,7 +1178,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>28.54</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1189,10 +1189,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>197.16</v>
+        <v>200.3</v>
       </c>
       <c r="D4">
-        <v>-1.27</v>
+        <v>1.59</v>
       </c>
       <c r="E4">
         <v>307.76</v>
@@ -1201,46 +1201,46 @@
         <v>197.16</v>
       </c>
       <c r="G4">
-        <v>-35.94</v>
+        <v>-34.92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="I4">
-        <v>-1.61</v>
+        <v>0.44</v>
       </c>
       <c r="J4">
-        <v>-5.89</v>
+        <v>-4.54</v>
       </c>
       <c r="K4">
-        <v>-15.04</v>
+        <v>-13.25</v>
       </c>
       <c r="L4">
-        <v>-35.84</v>
+        <v>-33.45</v>
       </c>
       <c r="M4">
-        <v>-6.35</v>
+        <v>-6.17</v>
       </c>
       <c r="N4">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>199.19</v>
+        <v>199.37</v>
       </c>
       <c r="Q4">
-        <v>202.21</v>
+        <v>201.78</v>
       </c>
       <c r="R4">
-        <v>208.93</v>
+        <v>208.56</v>
       </c>
       <c r="S4">
-        <v>239.84</v>
+        <v>239.51</v>
       </c>
       <c r="T4">
-        <v>-17.79</v>
+        <v>-16.37</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1255,34 +1255,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.97</v>
+        <v>39.56</v>
       </c>
       <c r="Z4">
+        <v>-2.98</v>
+      </c>
+      <c r="AA4">
         <v>-3.19</v>
       </c>
-      <c r="AA4">
-        <v>-3.24</v>
-      </c>
       <c r="AB4">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="AC4">
-        <v>32.16</v>
+        <v>49.6</v>
       </c>
       <c r="AD4">
-        <v>41.6</v>
+        <v>43.54</v>
       </c>
       <c r="AE4">
         <v>3.84</v>
       </c>
       <c r="AF4">
-        <v>-44.03</v>
+        <v>-31.31</v>
       </c>
       <c r="AG4">
-        <v>207.62</v>
+        <v>206.26</v>
       </c>
       <c r="AH4">
-        <v>196.8</v>
+        <v>197.3</v>
       </c>
       <c r="AI4">
         <v>210.35</v>
@@ -1291,7 +1291,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>31.89</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1302,10 +1302,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>617.4</v>
+        <v>616.55</v>
       </c>
       <c r="D5">
-        <v>1.58</v>
+        <v>-0.14</v>
       </c>
       <c r="E5">
         <v>912.72</v>
@@ -1314,46 +1314,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-32.36</v>
+        <v>-32.45</v>
       </c>
       <c r="H5">
-        <v>7.48</v>
+        <v>7.33</v>
       </c>
       <c r="I5">
-        <v>-4.09</v>
+        <v>-3.88</v>
       </c>
       <c r="J5">
-        <v>-2.61</v>
+        <v>-3.87</v>
       </c>
       <c r="K5">
-        <v>-11.31</v>
+        <v>-14.2</v>
       </c>
       <c r="L5">
-        <v>-32.26</v>
+        <v>-31.94</v>
       </c>
       <c r="M5">
-        <v>-6.55</v>
+        <v>-7.2</v>
       </c>
       <c r="N5">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O5">
         <v>22</v>
       </c>
       <c r="P5">
-        <v>618.39</v>
+        <v>613.41</v>
       </c>
       <c r="Q5">
-        <v>651.9</v>
+        <v>651.47</v>
       </c>
       <c r="R5">
-        <v>655.66</v>
+        <v>654.28</v>
       </c>
       <c r="S5">
-        <v>698.0599999999999</v>
+        <v>697.42</v>
       </c>
       <c r="T5">
-        <v>-11.55</v>
+        <v>-11.6</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1368,34 +1368,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41.92</v>
+        <v>41.74</v>
       </c>
       <c r="Z5">
-        <v>-9.960000000000001</v>
+        <v>-11.04</v>
       </c>
       <c r="AA5">
-        <v>-2.44</v>
+        <v>-4.16</v>
       </c>
       <c r="AB5">
-        <v>-7.51</v>
+        <v>-6.87</v>
       </c>
       <c r="AC5">
-        <v>10.21</v>
+        <v>7.82</v>
       </c>
       <c r="AD5">
-        <v>16.66</v>
+        <v>11.27</v>
       </c>
       <c r="AE5">
-        <v>30.81</v>
+        <v>29.27</v>
       </c>
       <c r="AF5">
-        <v>-73.64</v>
+        <v>-80.95999999999999</v>
       </c>
       <c r="AG5">
-        <v>754.5599999999999</v>
+        <v>754.67</v>
       </c>
       <c r="AH5">
-        <v>549.23</v>
+        <v>548.27</v>
       </c>
       <c r="AI5">
         <v>703.01</v>
@@ -1404,7 +1404,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>18.09</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1415,10 +1415,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1677.2</v>
+        <v>1681.8</v>
       </c>
       <c r="D6">
-        <v>-0.34</v>
+        <v>0.27</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1427,46 +1427,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-18.65</v>
+        <v>-18.43</v>
       </c>
       <c r="H6">
-        <v>24.43</v>
+        <v>24.77</v>
       </c>
       <c r="I6">
-        <v>0.64</v>
+        <v>1.6</v>
       </c>
       <c r="J6">
-        <v>-1.92</v>
+        <v>-0.86</v>
       </c>
       <c r="K6">
-        <v>-11.35</v>
+        <v>-11.8</v>
       </c>
       <c r="L6">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="M6">
-        <v>4.16</v>
+        <v>3.85</v>
       </c>
       <c r="N6">
         <v>74</v>
       </c>
       <c r="O6">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P6">
-        <v>1665.28</v>
+        <v>1670.58</v>
       </c>
       <c r="Q6">
-        <v>1722.7</v>
+        <v>1718.98</v>
       </c>
       <c r="R6">
-        <v>1724.3</v>
+        <v>1722.43</v>
       </c>
       <c r="S6">
-        <v>1705.33</v>
+        <v>1704.61</v>
       </c>
       <c r="T6">
-        <v>-1.65</v>
+        <v>-1.34</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1481,34 +1481,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.79</v>
+        <v>43.9</v>
       </c>
       <c r="Z6">
-        <v>-19.95</v>
+        <v>-19.12</v>
       </c>
       <c r="AA6">
-        <v>-13.99</v>
+        <v>-15.01</v>
       </c>
       <c r="AB6">
-        <v>-5.97</v>
+        <v>-4.11</v>
       </c>
       <c r="AC6">
-        <v>18.87</v>
+        <v>28.38</v>
       </c>
       <c r="AD6">
-        <v>9.960000000000001</v>
+        <v>19.23</v>
       </c>
       <c r="AE6">
-        <v>47.83</v>
+        <v>46.59</v>
       </c>
       <c r="AF6">
-        <v>-62.42</v>
+        <v>-38.37</v>
       </c>
       <c r="AG6">
-        <v>1822.46</v>
+        <v>1819.04</v>
       </c>
       <c r="AH6">
-        <v>1622.94</v>
+        <v>1618.93</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1517,7 +1517,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>28.48</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1528,10 +1528,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>953.75</v>
+        <v>976</v>
       </c>
       <c r="D7">
-        <v>-0.34</v>
+        <v>2.33</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1540,46 +1540,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-24.33</v>
+        <v>-22.56</v>
       </c>
       <c r="H7">
-        <v>0.45</v>
+        <v>2.79</v>
       </c>
       <c r="I7">
-        <v>-3</v>
+        <v>1.67</v>
       </c>
       <c r="J7">
-        <v>-5.76</v>
+        <v>-4.24</v>
       </c>
       <c r="K7">
-        <v>-14.68</v>
+        <v>-13.24</v>
       </c>
       <c r="L7">
-        <v>-14.36</v>
+        <v>-12.84</v>
       </c>
       <c r="M7">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="N7">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O7">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>957.59</v>
+        <v>960.79</v>
       </c>
       <c r="Q7">
-        <v>988.15</v>
+        <v>986.45</v>
       </c>
       <c r="R7">
-        <v>1037.25</v>
+        <v>1035.01</v>
       </c>
       <c r="S7">
-        <v>1107.88</v>
+        <v>1106.96</v>
       </c>
       <c r="T7">
-        <v>-13.91</v>
+        <v>-11.83</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1594,34 +1594,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>32.92</v>
+        <v>42.63</v>
       </c>
       <c r="Z7">
-        <v>-22.8</v>
+        <v>-20.99</v>
       </c>
       <c r="AA7">
-        <v>-21.1</v>
+        <v>-21.08</v>
       </c>
       <c r="AB7">
-        <v>-1.71</v>
+        <v>0.09</v>
       </c>
       <c r="AC7">
-        <v>29.05</v>
+        <v>57.54</v>
       </c>
       <c r="AD7">
-        <v>28.72</v>
+        <v>39.59</v>
       </c>
       <c r="AE7">
-        <v>18.13</v>
+        <v>18.96</v>
       </c>
       <c r="AF7">
-        <v>21.9</v>
+        <v>-29.72</v>
       </c>
       <c r="AG7">
-        <v>1029.53</v>
+        <v>1026.83</v>
       </c>
       <c r="AH7">
-        <v>946.77</v>
+        <v>946.0700000000001</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1630,7 +1630,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>62.17</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1641,10 +1641,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3105</v>
+        <v>3093</v>
       </c>
       <c r="D8">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1653,46 +1653,46 @@
         <v>3088.9</v>
       </c>
       <c r="G8">
-        <v>-46</v>
+        <v>-46.21</v>
       </c>
       <c r="H8">
-        <v>0.52</v>
+        <v>0.13</v>
       </c>
       <c r="I8">
-        <v>-2.57</v>
+        <v>-3.07</v>
       </c>
       <c r="J8">
-        <v>-13.97</v>
+        <v>-13.6</v>
       </c>
       <c r="K8">
-        <v>-15.13</v>
+        <v>-16.57</v>
       </c>
       <c r="L8">
-        <v>-40.38</v>
+        <v>-39.77</v>
       </c>
       <c r="M8">
-        <v>-10.96</v>
+        <v>-11.98</v>
       </c>
       <c r="N8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O8">
         <v>11</v>
       </c>
       <c r="P8">
-        <v>3137.88</v>
+        <v>3118.28</v>
       </c>
       <c r="Q8">
-        <v>3298.13</v>
+        <v>3274.88</v>
       </c>
       <c r="R8">
-        <v>3528.55</v>
+        <v>3519.65</v>
       </c>
       <c r="S8">
-        <v>4218.67</v>
+        <v>4209.58</v>
       </c>
       <c r="T8">
-        <v>-26.4</v>
+        <v>-26.52</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1707,43 +1707,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>26.05</v>
+        <v>25.43</v>
       </c>
       <c r="Z8">
-        <v>-127.04</v>
+        <v>-126.68</v>
       </c>
       <c r="AA8">
-        <v>-115.5</v>
+        <v>-117.74</v>
       </c>
       <c r="AB8">
-        <v>-11.54</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="AC8">
-        <v>6.84</v>
+        <v>12.01</v>
       </c>
       <c r="AD8">
-        <v>11.31</v>
+        <v>10.54</v>
       </c>
       <c r="AE8">
-        <v>86.39</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="AF8">
-        <v>-2.51</v>
+        <v>-20.07</v>
       </c>
       <c r="AG8">
-        <v>3583.33</v>
+        <v>3546.37</v>
       </c>
       <c r="AH8">
-        <v>3012.93</v>
+        <v>3003.39</v>
       </c>
       <c r="AI8">
-        <v>3366.35</v>
+        <v>3348.63</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>57.27</v>
+        <v>59.37</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1754,10 +1754,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>621.75</v>
+        <v>624.15</v>
       </c>
       <c r="D9">
-        <v>1.09</v>
+        <v>0.39</v>
       </c>
       <c r="E9">
         <v>1052.57</v>
@@ -1766,46 +1766,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-40.93</v>
+        <v>-40.7</v>
       </c>
       <c r="H9">
-        <v>15.49</v>
+        <v>15.93</v>
       </c>
       <c r="I9">
-        <v>-4.58</v>
+        <v>-3.15</v>
       </c>
       <c r="J9">
-        <v>-1.01</v>
+        <v>-2.16</v>
       </c>
       <c r="K9">
-        <v>-6.4</v>
+        <v>-6.54</v>
       </c>
       <c r="L9">
-        <v>-29.33</v>
+        <v>-39.27</v>
       </c>
       <c r="M9">
-        <v>35.56</v>
+        <v>36.06</v>
       </c>
       <c r="N9">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P9">
-        <v>625.35</v>
+        <v>621.29</v>
       </c>
       <c r="Q9">
-        <v>654.7</v>
+        <v>654.23</v>
       </c>
       <c r="R9">
-        <v>657.14</v>
+        <v>657.01</v>
       </c>
       <c r="S9">
-        <v>660.39</v>
+        <v>659.97</v>
       </c>
       <c r="T9">
-        <v>-5.85</v>
+        <v>-5.43</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1820,34 +1820,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>40.53</v>
+        <v>41.43</v>
       </c>
       <c r="Z9">
-        <v>-7.93</v>
+        <v>-8.85</v>
       </c>
       <c r="AA9">
-        <v>-1.27</v>
+        <v>-2.78</v>
       </c>
       <c r="AB9">
-        <v>-6.66</v>
+        <v>-6.07</v>
       </c>
       <c r="AC9">
-        <v>2.35</v>
+        <v>6.38</v>
       </c>
       <c r="AD9">
-        <v>9.130000000000001</v>
+        <v>5.29</v>
       </c>
       <c r="AE9">
-        <v>23.23</v>
+        <v>22.73</v>
       </c>
       <c r="AF9">
-        <v>-88.94</v>
+        <v>-85.61</v>
       </c>
       <c r="AG9">
-        <v>722</v>
+        <v>722.29</v>
       </c>
       <c r="AH9">
-        <v>587.41</v>
+        <v>586.17</v>
       </c>
       <c r="AI9">
         <v>682.46</v>
@@ -1856,7 +1856,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>21.91</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1867,10 +1867,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>351.5</v>
+        <v>351.65</v>
       </c>
       <c r="D10">
-        <v>0.39</v>
+        <v>0.04</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1879,46 +1879,46 @@
         <v>345.25</v>
       </c>
       <c r="G10">
-        <v>-23.88</v>
+        <v>-23.85</v>
       </c>
       <c r="H10">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="I10">
-        <v>-4.35</v>
+        <v>-2.83</v>
       </c>
       <c r="J10">
-        <v>-3.43</v>
+        <v>-3.84</v>
       </c>
       <c r="K10">
-        <v>-6.9</v>
+        <v>-6.77</v>
       </c>
       <c r="L10">
-        <v>-9.42</v>
+        <v>-9.52</v>
       </c>
       <c r="M10">
-        <v>15.04</v>
+        <v>15.49</v>
       </c>
       <c r="N10">
         <v>68</v>
       </c>
       <c r="O10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P10">
-        <v>356.31</v>
+        <v>354.26</v>
       </c>
       <c r="Q10">
-        <v>364.19</v>
+        <v>363.37</v>
       </c>
       <c r="R10">
-        <v>369.63</v>
+        <v>369.17</v>
       </c>
       <c r="S10">
-        <v>386.46</v>
+        <v>386.32</v>
       </c>
       <c r="T10">
-        <v>-9.050000000000001</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1933,34 +1933,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>36.91</v>
+        <v>37.1</v>
       </c>
       <c r="Z10">
-        <v>-3.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AA10">
-        <v>-2.47</v>
+        <v>-2.81</v>
       </c>
       <c r="AB10">
-        <v>-1.27</v>
+        <v>-1.34</v>
       </c>
       <c r="AC10">
-        <v>5.16</v>
+        <v>5.53</v>
       </c>
       <c r="AD10">
-        <v>7.67</v>
+        <v>5.26</v>
       </c>
       <c r="AE10">
-        <v>7.42</v>
+        <v>7.38</v>
       </c>
       <c r="AF10">
-        <v>-35.24</v>
+        <v>50.5</v>
       </c>
       <c r="AG10">
-        <v>376.16</v>
+        <v>376.43</v>
       </c>
       <c r="AH10">
-        <v>352.22</v>
+        <v>350.31</v>
       </c>
       <c r="AI10">
         <v>347.84</v>
@@ -1969,7 +1969,7 @@
         <v>56</v>
       </c>
       <c r="AK10">
-        <v>34.84</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1980,10 +1980,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>178.14</v>
+        <v>178.69</v>
       </c>
       <c r="D11">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1992,46 +1992,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-17.78</v>
+        <v>-17.53</v>
       </c>
       <c r="H11">
-        <v>13.16</v>
+        <v>13.51</v>
       </c>
       <c r="I11">
-        <v>-5.23</v>
+        <v>-4.08</v>
       </c>
       <c r="J11">
-        <v>-3.11</v>
+        <v>-2.99</v>
       </c>
       <c r="K11">
-        <v>-6.67</v>
+        <v>-5.85</v>
       </c>
       <c r="L11">
-        <v>7.59</v>
+        <v>8.06</v>
       </c>
       <c r="M11">
-        <v>9.42</v>
+        <v>10.12</v>
       </c>
       <c r="N11">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="O11">
         <v>63</v>
       </c>
       <c r="P11">
-        <v>182.95</v>
+        <v>181.43</v>
       </c>
       <c r="Q11">
-        <v>185.32</v>
+        <v>184.82</v>
       </c>
       <c r="R11">
-        <v>185.96</v>
+        <v>185.88</v>
       </c>
       <c r="S11">
-        <v>191.99</v>
+        <v>192.05</v>
       </c>
       <c r="T11">
-        <v>-7.21</v>
+        <v>-6.96</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2046,43 +2046,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>38.29</v>
+        <v>39.41</v>
       </c>
       <c r="Z11">
-        <v>-1.08</v>
+        <v>-1.42</v>
       </c>
       <c r="AA11">
-        <v>-0.32</v>
+        <v>-0.54</v>
       </c>
       <c r="AB11">
-        <v>-0.76</v>
+        <v>-0.88</v>
       </c>
       <c r="AC11">
-        <v>6.65</v>
+        <v>2.72</v>
       </c>
       <c r="AD11">
-        <v>25.16</v>
+        <v>12.22</v>
       </c>
       <c r="AE11">
-        <v>4.83</v>
+        <v>4.73</v>
       </c>
       <c r="AF11">
-        <v>-24.34</v>
+        <v>-36.22</v>
       </c>
       <c r="AG11">
-        <v>191.93</v>
+        <v>191.84</v>
       </c>
       <c r="AH11">
-        <v>178.71</v>
+        <v>177.79</v>
       </c>
       <c r="AI11">
-        <v>193.65</v>
+        <v>192.88</v>
       </c>
       <c r="AJ11" t="s">
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>24.66</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2093,10 +2093,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2114.4</v>
+        <v>2100</v>
       </c>
       <c r="D12">
-        <v>1.9</v>
+        <v>-0.68</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2105,46 +2105,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-34.37</v>
+        <v>-34.82</v>
       </c>
       <c r="H12">
-        <v>6.65</v>
+        <v>5.92</v>
       </c>
       <c r="I12">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="J12">
-        <v>-9.949999999999999</v>
+        <v>-9.49</v>
       </c>
       <c r="K12">
-        <v>2.76</v>
+        <v>0.19</v>
       </c>
       <c r="L12">
-        <v>-24.38</v>
+        <v>-24.69</v>
       </c>
       <c r="M12">
-        <v>-8.779999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="N12">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O12">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P12">
-        <v>2068.62</v>
+        <v>2074.48</v>
       </c>
       <c r="Q12">
-        <v>2150.63</v>
+        <v>2140.43</v>
       </c>
       <c r="R12">
-        <v>2273.87</v>
+        <v>2270.78</v>
       </c>
       <c r="S12">
-        <v>2478.35</v>
+        <v>2473.32</v>
       </c>
       <c r="T12">
-        <v>-14.69</v>
+        <v>-15.09</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2159,34 +2159,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>42.59</v>
+        <v>40.95</v>
       </c>
       <c r="Z12">
-        <v>-57.97</v>
+        <v>-54.21</v>
       </c>
       <c r="AA12">
-        <v>-55.79</v>
+        <v>-55.47</v>
       </c>
       <c r="AB12">
-        <v>-2.18</v>
+        <v>1.27</v>
       </c>
       <c r="AC12">
-        <v>50.08</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AD12">
-        <v>26.3</v>
+        <v>48.36</v>
       </c>
       <c r="AE12">
-        <v>60.1</v>
+        <v>58.12</v>
       </c>
       <c r="AF12">
-        <v>68.94</v>
+        <v>-26.73</v>
       </c>
       <c r="AG12">
-        <v>2312.89</v>
+        <v>2286.98</v>
       </c>
       <c r="AH12">
-        <v>1988.37</v>
+        <v>1993.88</v>
       </c>
       <c r="AI12">
         <v>2235.3</v>
@@ -2195,7 +2195,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>39.59</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2206,58 +2206,58 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4580</v>
+        <v>4550</v>
       </c>
       <c r="D13">
-        <v>1.42</v>
+        <v>-0.66</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
       </c>
       <c r="F13">
-        <v>3367</v>
+        <v>3408.3</v>
       </c>
       <c r="G13">
-        <v>-11.4</v>
+        <v>-11.98</v>
       </c>
       <c r="H13">
-        <v>36.03</v>
+        <v>33.5</v>
       </c>
       <c r="I13">
-        <v>-6.22</v>
+        <v>-5.59</v>
       </c>
       <c r="J13">
-        <v>-9.74</v>
+        <v>-9.49</v>
       </c>
       <c r="K13">
-        <v>2.13</v>
+        <v>-1.18</v>
       </c>
       <c r="L13">
-        <v>34.66</v>
+        <v>35.14</v>
       </c>
       <c r="M13">
-        <v>16.18</v>
+        <v>16.51</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P13">
-        <v>4635.44</v>
+        <v>4581.54</v>
       </c>
       <c r="Q13">
-        <v>4850.94</v>
+        <v>4827.44</v>
       </c>
       <c r="R13">
-        <v>4945.54</v>
+        <v>4943</v>
       </c>
       <c r="S13">
-        <v>4411.83</v>
+        <v>4414.93</v>
       </c>
       <c r="T13">
-        <v>3.81</v>
+        <v>3.06</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2272,34 +2272,34 @@
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>32.64</v>
+        <v>31.38</v>
       </c>
       <c r="Z13">
-        <v>-96.08</v>
+        <v>-104.21</v>
       </c>
       <c r="AA13">
-        <v>-54.61</v>
+        <v>-64.53</v>
       </c>
       <c r="AB13">
-        <v>-41.47</v>
+        <v>-39.68</v>
       </c>
       <c r="AC13">
-        <v>9.25</v>
+        <v>16.51</v>
       </c>
       <c r="AD13">
-        <v>7.03</v>
+        <v>8.59</v>
       </c>
       <c r="AE13">
-        <v>93.3</v>
+        <v>91.61</v>
       </c>
       <c r="AF13">
-        <v>15.81</v>
+        <v>27.36</v>
       </c>
       <c r="AG13">
-        <v>5158.08</v>
+        <v>5151.57</v>
       </c>
       <c r="AH13">
-        <v>4543.79</v>
+        <v>4503.3</v>
       </c>
       <c r="AI13">
         <v>4833.78</v>
@@ -2308,7 +2308,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>51.72</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2319,10 +2319,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2580</v>
+        <v>2906</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>12.64</v>
       </c>
       <c r="E14">
         <v>4824.87</v>
@@ -2331,46 +2331,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-46.53</v>
+        <v>-39.77</v>
       </c>
       <c r="H14">
-        <v>17.6</v>
+        <v>32.45</v>
       </c>
       <c r="I14">
-        <v>-3.35</v>
+        <v>10.66</v>
       </c>
       <c r="J14">
-        <v>-9.550000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="K14">
-        <v>-22.84</v>
+        <v>-0.74</v>
       </c>
       <c r="L14">
-        <v>-45.38</v>
+        <v>-37.78</v>
       </c>
       <c r="M14">
-        <v>19.81</v>
+        <v>22.82</v>
       </c>
       <c r="N14">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="O14">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="P14">
-        <v>2608.52</v>
+        <v>2664.52</v>
       </c>
       <c r="Q14">
-        <v>2739.96</v>
+        <v>2742.61</v>
       </c>
       <c r="R14">
-        <v>2871.95</v>
+        <v>2872.26</v>
       </c>
       <c r="S14">
-        <v>2849.07</v>
+        <v>2843.09</v>
       </c>
       <c r="T14">
-        <v>-9.44</v>
+        <v>2.21</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2382,46 +2382,46 @@
         <v>54</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14">
-        <v>24.71</v>
+        <v>61.04</v>
       </c>
       <c r="Z14">
-        <v>-77.05</v>
+        <v>-52.97</v>
       </c>
       <c r="AA14">
-        <v>-61.89</v>
+        <v>-60.1</v>
       </c>
       <c r="AB14">
-        <v>-15.16</v>
+        <v>7.14</v>
       </c>
       <c r="AC14">
-        <v>1.18</v>
+        <v>33.33</v>
       </c>
       <c r="AD14">
-        <v>3.15</v>
+        <v>12.88</v>
       </c>
       <c r="AE14">
-        <v>58.97</v>
+        <v>78.62</v>
       </c>
       <c r="AF14">
-        <v>8.41</v>
+        <v>808.73</v>
       </c>
       <c r="AG14">
-        <v>2919.23</v>
+        <v>2930.29</v>
       </c>
       <c r="AH14">
-        <v>2560.69</v>
+        <v>2554.93</v>
       </c>
       <c r="AI14">
-        <v>2767.24</v>
+        <v>2612.29</v>
       </c>
       <c r="AJ14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AK14">
-        <v>59.39</v>
+        <v>55.95</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2432,10 +2432,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>194.02</v>
+        <v>196.3</v>
       </c>
       <c r="D15">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="E15">
         <v>380.65</v>
@@ -2444,46 +2444,46 @@
         <v>192.33</v>
       </c>
       <c r="G15">
-        <v>-49.03</v>
+        <v>-48.43</v>
       </c>
       <c r="H15">
-        <v>0.88</v>
+        <v>2.06</v>
       </c>
       <c r="I15">
-        <v>-10.03</v>
+        <v>-5.42</v>
       </c>
       <c r="J15">
-        <v>-13.24</v>
+        <v>-14.66</v>
       </c>
       <c r="K15">
-        <v>-17.03</v>
+        <v>-16.13</v>
       </c>
       <c r="L15">
-        <v>-43.19</v>
+        <v>-42.2</v>
       </c>
       <c r="M15">
-        <v>5.41</v>
+        <v>4.7</v>
       </c>
       <c r="N15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>7</v>
       </c>
       <c r="P15">
-        <v>198.92</v>
+        <v>196.67</v>
       </c>
       <c r="Q15">
-        <v>215.26</v>
+        <v>213.5</v>
       </c>
       <c r="R15">
-        <v>224.07</v>
+        <v>223.33</v>
       </c>
       <c r="S15">
-        <v>248.54</v>
+        <v>247.96</v>
       </c>
       <c r="T15">
-        <v>-21.94</v>
+        <v>-20.83</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2498,43 +2498,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>24.4</v>
+        <v>28.35</v>
       </c>
       <c r="Z15">
-        <v>-8.130000000000001</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="AA15">
-        <v>-5.79</v>
+        <v>-6.3</v>
       </c>
       <c r="AB15">
-        <v>-2.34</v>
+        <v>-2.06</v>
       </c>
       <c r="AC15">
-        <v>5.01</v>
+        <v>16.65</v>
       </c>
       <c r="AD15">
-        <v>1.67</v>
+        <v>7.22</v>
       </c>
       <c r="AE15">
-        <v>8.32</v>
+        <v>7.97</v>
       </c>
       <c r="AF15">
-        <v>7.48</v>
+        <v>-57.01</v>
       </c>
       <c r="AG15">
-        <v>239.06</v>
+        <v>237.43</v>
       </c>
       <c r="AH15">
-        <v>191.47</v>
+        <v>189.57</v>
       </c>
       <c r="AI15">
-        <v>220.55</v>
+        <v>219.64</v>
       </c>
       <c r="AJ15" t="s">
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>37.51</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2545,10 +2545,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>34.33</v>
+        <v>34.18</v>
       </c>
       <c r="D16">
-        <v>-1.41</v>
+        <v>-0.44</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2557,46 +2557,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-41.5</v>
+        <v>-41.75</v>
       </c>
       <c r="H16">
-        <v>9.470000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="I16">
-        <v>-0.32</v>
+        <v>-5.55</v>
       </c>
       <c r="J16">
-        <v>-9.66</v>
+        <v>-10.08</v>
       </c>
       <c r="K16">
-        <v>-18.75</v>
+        <v>-17.86</v>
       </c>
       <c r="L16">
-        <v>-37.53</v>
+        <v>-37.88</v>
       </c>
       <c r="M16">
-        <v>-3.42</v>
+        <v>-2.95</v>
       </c>
       <c r="N16">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P16">
-        <v>34.96</v>
+        <v>34.56</v>
       </c>
       <c r="Q16">
-        <v>35.69</v>
+        <v>35.51</v>
       </c>
       <c r="R16">
-        <v>37.47</v>
+        <v>37.37</v>
       </c>
       <c r="S16">
-        <v>41.64</v>
+        <v>41.56</v>
       </c>
       <c r="T16">
-        <v>-17.56</v>
+        <v>-17.75</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2611,34 +2611,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>39.05</v>
+        <v>38.35</v>
       </c>
       <c r="Z16">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
       <c r="AA16">
         <v>-0.84</v>
       </c>
       <c r="AB16">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AC16">
-        <v>51.49</v>
+        <v>51.6</v>
       </c>
       <c r="AD16">
-        <v>59.82</v>
+        <v>53.72</v>
       </c>
       <c r="AE16">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AF16">
-        <v>-63.47</v>
+        <v>-79.73999999999999</v>
       </c>
       <c r="AG16">
-        <v>37.55</v>
+        <v>37.22</v>
       </c>
       <c r="AH16">
-        <v>33.84</v>
+        <v>33.81</v>
       </c>
       <c r="AI16">
         <v>37.92</v>
@@ -2647,7 +2647,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>16.22</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2658,10 +2658,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1061.3</v>
+        <v>1067.9</v>
       </c>
       <c r="D17">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2670,46 +2670,46 @@
         <v>1053.2</v>
       </c>
       <c r="G17">
-        <v>-31.81</v>
+        <v>-31.39</v>
       </c>
       <c r="H17">
-        <v>0.77</v>
+        <v>1.4</v>
       </c>
       <c r="I17">
-        <v>-5.09</v>
+        <v>-5.95</v>
       </c>
       <c r="J17">
-        <v>-7.88</v>
+        <v>-9.35</v>
       </c>
       <c r="K17">
-        <v>-17.38</v>
+        <v>-17.09</v>
       </c>
       <c r="L17">
-        <v>-22.54</v>
+        <v>-20.85</v>
       </c>
       <c r="M17">
-        <v>-2.77</v>
+        <v>-2.33</v>
       </c>
       <c r="N17">
         <v>44</v>
       </c>
       <c r="O17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P17">
-        <v>1082</v>
+        <v>1068.48</v>
       </c>
       <c r="Q17">
-        <v>1123.89</v>
+        <v>1118.78</v>
       </c>
       <c r="R17">
-        <v>1208.36</v>
+        <v>1203.17</v>
       </c>
       <c r="S17">
-        <v>1328.53</v>
+        <v>1326.92</v>
       </c>
       <c r="T17">
-        <v>-20.11</v>
+        <v>-19.52</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2724,43 +2724,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>33.32</v>
+        <v>35.1</v>
       </c>
       <c r="Z17">
-        <v>-37.83</v>
+        <v>-37.69</v>
       </c>
       <c r="AA17">
-        <v>-34.83</v>
+        <v>-35.4</v>
       </c>
       <c r="AB17">
-        <v>-2.99</v>
+        <v>-2.28</v>
       </c>
       <c r="AC17">
-        <v>25.19</v>
+        <v>29.63</v>
       </c>
       <c r="AD17">
-        <v>38.65</v>
+        <v>28.68</v>
       </c>
       <c r="AE17">
-        <v>30.71</v>
+        <v>30.29</v>
       </c>
       <c r="AF17">
-        <v>-41.69</v>
+        <v>300.91</v>
       </c>
       <c r="AG17">
-        <v>1192.53</v>
+        <v>1188.17</v>
       </c>
       <c r="AH17">
-        <v>1055.24</v>
+        <v>1049.39</v>
       </c>
       <c r="AI17">
-        <v>1154.39</v>
+        <v>1151.87</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>42.64</v>
+        <v>45.08</v>
       </c>
     </row>
   </sheetData>
@@ -2901,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>69</v>
@@ -2979,2229 +2979,2436 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.8</v>
+        <v>-0.37</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.79</v>
+        <v>0.55</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.99</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-3.61</v>
+        <v>-4.79</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.89</v>
+        <v>-1.03</v>
       </c>
       <c r="E10" s="7">
-        <v>-2.28</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.07</v>
+        <v>-5.89</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.46</v>
+        <v>-4.54</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.93</v>
+        <v>-2.61</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.92</v>
+        <v>-3.87</v>
       </c>
       <c r="E12" s="8">
-        <v>1.01</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.13</v>
+        <v>-1.92</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.76</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.37</v>
+        <v>-0.86</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-14.99</v>
+        <v>-5.76</v>
       </c>
       <c r="D14" s="6">
-        <v>-13.97</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.02</v>
+        <v>-4.24</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.94</v>
+        <v>-13.97</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.01</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.93</v>
+        <v>-13.6</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.11</v>
+        <v>-1.01</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.43</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.32</v>
+        <v>-2.16</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.3</v>
+        <v>-3.43</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.11</v>
+        <v>-3.84</v>
       </c>
       <c r="E17" s="8">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-12.41</v>
+        <v>-3.11</v>
       </c>
       <c r="D18" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.46</v>
+        <v>-2.99</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-10.58</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.74</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.84</v>
+        <v>-9.49</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-9.630000000000001</v>
+        <v>-9.74</v>
       </c>
       <c r="D20" s="6">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.08</v>
+        <v>-9.49</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-14.21</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="D21" s="6">
-        <v>-13.24</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.97</v>
+        <v>3.21</v>
+      </c>
+      <c r="E21" s="7">
+        <v>12.76</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-10.53</v>
+        <v>-13.24</v>
       </c>
       <c r="D22" s="6">
-        <v>-9.66</v>
+        <v>-14.66</v>
       </c>
       <c r="E22" s="8">
-        <v>0.87</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-12.6</v>
+        <v>-9.66</v>
       </c>
       <c r="D23" s="6">
-        <v>-7.88</v>
+        <v>-10.08</v>
       </c>
       <c r="E23" s="8">
-        <v>4.72</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.48</v>
+        <v>-7.88</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.25</v>
+        <v>-9.35</v>
       </c>
       <c r="E24" s="8">
-        <v>1.23</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-10.46</v>
+        <v>-0.25</v>
       </c>
       <c r="D25" s="6">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.1</v>
+        <v>3.52</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.77</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-0.33</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="D26" s="6">
-        <v>-1.61</v>
+        <v>0.84</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.28</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-6.81</v>
+        <v>-1.61</v>
       </c>
       <c r="D27" s="6">
-        <v>-4.09</v>
-      </c>
-      <c r="E27" s="8">
-        <v>2.72</v>
+        <v>0.44</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>0.78</v>
+        <v>-4.09</v>
       </c>
       <c r="D28" s="6">
-        <v>0.64</v>
+        <v>-3.88</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.14</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-2.97</v>
+        <v>0.64</v>
       </c>
       <c r="D29" s="6">
-        <v>-3</v>
+        <v>1.6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.03</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.86</v>
+        <v>-3</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.57</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.29</v>
+        <v>1.67</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.67</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-6.58</v>
+        <v>-2.57</v>
       </c>
       <c r="D31" s="6">
-        <v>-4.58</v>
+        <v>-3.07</v>
       </c>
       <c r="E31" s="8">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-3.66</v>
+        <v>-4.58</v>
       </c>
       <c r="D32" s="6">
-        <v>-4.35</v>
+        <v>-3.15</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.6899999999999999</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-5.33</v>
+        <v>-4.35</v>
       </c>
       <c r="D33" s="6">
-        <v>-5.23</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.1</v>
+        <v>-2.83</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-0.57</v>
+        <v>-5.23</v>
       </c>
       <c r="D34" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.13</v>
+        <v>-4.08</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.15</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-6.56</v>
+        <v>1.56</v>
       </c>
       <c r="D35" s="6">
-        <v>-6.22</v>
+        <v>1.41</v>
       </c>
       <c r="E35" s="8">
-        <v>0.34</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-4.44</v>
+        <v>-6.22</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.35</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.09</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.63</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-10.6</v>
+        <v>-3.35</v>
       </c>
       <c r="D37" s="6">
-        <v>-10.03</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.57</v>
+        <v>10.66</v>
+      </c>
+      <c r="E37" s="7">
+        <v>14.01</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-0.57</v>
+        <v>-10.03</v>
       </c>
       <c r="D38" s="6">
-        <v>-0.32</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.25</v>
+        <v>-5.42</v>
+      </c>
+      <c r="E38" s="7">
+        <v>4.61</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-5.41</v>
+        <v>-0.32</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.09</v>
+        <v>-5.55</v>
       </c>
       <c r="E39" s="8">
-        <v>0.32</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>1.16</v>
+        <v>-5.09</v>
       </c>
       <c r="D40" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.06</v>
+        <v>-5.95</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="6">
-        <v>4.79</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.09</v>
+        <v>2.18</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.08</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>-34.39</v>
+        <v>4.79</v>
       </c>
       <c r="D42" s="6">
-        <v>-35.84</v>
+        <v>9.9</v>
       </c>
       <c r="E42" s="7">
-        <v>-1.45</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-33.7</v>
+        <v>-35.84</v>
       </c>
       <c r="D43" s="6">
-        <v>-32.26</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.44</v>
+        <v>-33.45</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.39</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>4.29</v>
+        <v>-32.26</v>
       </c>
       <c r="D44" s="6">
-        <v>3.98</v>
+        <v>-31.94</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-13.75</v>
+        <v>3.98</v>
       </c>
       <c r="D45" s="6">
-        <v>-14.36</v>
+        <v>4.25</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.61</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-40.63</v>
+        <v>-14.36</v>
       </c>
       <c r="D46" s="6">
-        <v>-40.38</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.25</v>
+        <v>-12.84</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-28.66</v>
+        <v>-40.38</v>
       </c>
       <c r="D47" s="6">
-        <v>-29.33</v>
+        <v>-39.77</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.67</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-8.77</v>
+        <v>-29.33</v>
       </c>
       <c r="D48" s="6">
-        <v>-9.42</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.65</v>
+        <v>-39.27</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-9.94</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>8.52</v>
+        <v>-9.42</v>
       </c>
       <c r="D49" s="6">
-        <v>7.59</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.93</v>
+        <v>-9.52</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-25.86</v>
+        <v>7.59</v>
       </c>
       <c r="D50" s="6">
-        <v>-24.38</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.48</v>
+        <v>8.06</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>35.72</v>
+        <v>-24.38</v>
       </c>
       <c r="D51" s="6">
-        <v>34.66</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.06</v>
+        <v>-24.69</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-44.78</v>
+        <v>34.66</v>
       </c>
       <c r="D52" s="6">
-        <v>-45.38</v>
+        <v>35.14</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.6</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-44.19</v>
+        <v>-45.38</v>
       </c>
       <c r="D53" s="6">
-        <v>-43.19</v>
-      </c>
-      <c r="E53" s="8">
-        <v>1</v>
+        <v>-37.78</v>
+      </c>
+      <c r="E53" s="7">
+        <v>7.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-37.34</v>
+        <v>-43.19</v>
       </c>
       <c r="D54" s="6">
-        <v>-37.53</v>
+        <v>-42.2</v>
       </c>
       <c r="E54" s="7">
-        <v>-0.19</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-21.17</v>
+        <v>-37.53</v>
       </c>
       <c r="D55" s="6">
-        <v>-22.54</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.37</v>
+        <v>-37.88</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-1.45</v>
+        <v>-22.54</v>
       </c>
       <c r="D56" s="6">
-        <v>-1.78</v>
+        <v>-20.85</v>
       </c>
       <c r="E56" s="7">
-        <v>-0.33</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>-4.34</v>
+        <v>-1.78</v>
       </c>
       <c r="D57" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.41</v>
+        <v>-1.33</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-12.47</v>
+        <v>-3.93</v>
       </c>
       <c r="D58" s="6">
-        <v>-15.04</v>
+        <v>1.1</v>
       </c>
       <c r="E58" s="7">
-        <v>-2.57</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-12.31</v>
+        <v>-15.04</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.31</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1</v>
+        <v>-13.25</v>
+      </c>
+      <c r="E59" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-11.73</v>
+        <v>-11.31</v>
       </c>
       <c r="D60" s="6">
-        <v>-11.35</v>
+        <v>-14.2</v>
       </c>
       <c r="E60" s="8">
-        <v>0.38</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-14.3</v>
+        <v>-11.35</v>
       </c>
       <c r="D61" s="6">
-        <v>-14.68</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.38</v>
+        <v>-11.8</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-15.93</v>
+        <v>-14.68</v>
       </c>
       <c r="D62" s="6">
-        <v>-15.13</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.8</v>
+        <v>-13.24</v>
+      </c>
+      <c r="E62" s="7">
+        <v>1.44</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-7.83</v>
+        <v>-15.13</v>
       </c>
       <c r="D63" s="6">
-        <v>-6.4</v>
+        <v>-16.57</v>
       </c>
       <c r="E63" s="8">
-        <v>1.43</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-6.68</v>
+        <v>-6.4</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.9</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.22</v>
+        <v>-6.54</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-6.22</v>
+        <v>-6.9</v>
       </c>
       <c r="D65" s="6">
-        <v>-6.67</v>
+        <v>-6.77</v>
       </c>
       <c r="E65" s="7">
-        <v>-0.45</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-0.88</v>
+        <v>-6.67</v>
       </c>
       <c r="D66" s="6">
-        <v>2.76</v>
-      </c>
-      <c r="E66" s="8">
-        <v>3.64</v>
+        <v>-5.85</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0.82</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>1.22</v>
+        <v>2.76</v>
       </c>
       <c r="D67" s="6">
-        <v>2.13</v>
+        <v>0.19</v>
       </c>
       <c r="E67" s="8">
-        <v>0.91</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-22.77</v>
+        <v>2.13</v>
       </c>
       <c r="D68" s="6">
-        <v>-22.84</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-1.18</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-19.24</v>
+        <v>-22.84</v>
       </c>
       <c r="D69" s="6">
-        <v>-17.03</v>
-      </c>
-      <c r="E69" s="8">
-        <v>2.21</v>
+        <v>-0.74</v>
+      </c>
+      <c r="E69" s="7">
+        <v>22.1</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-18.59</v>
+        <v>-17.03</v>
       </c>
       <c r="D70" s="6">
-        <v>-18.75</v>
+        <v>-16.13</v>
       </c>
       <c r="E70" s="7">
-        <v>-0.16</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-17.73</v>
+        <v>-18.75</v>
       </c>
       <c r="D71" s="6">
-        <v>-17.38</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.35</v>
+        <v>-17.86</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.89</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-4.56</v>
+        <v>-17.38</v>
       </c>
       <c r="D72" s="6">
-        <v>-3.63</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.93</v>
+        <v>-17.09</v>
+      </c>
+      <c r="E72" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-17.78</v>
+        <v>-3.63</v>
       </c>
       <c r="D73" s="6">
-        <v>-18.16</v>
+        <v>-2.17</v>
       </c>
       <c r="E73" s="7">
-        <v>-0.38</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-35.12</v>
+        <v>-18.16</v>
       </c>
       <c r="D74" s="6">
-        <v>-35.94</v>
+        <v>-14.55</v>
       </c>
       <c r="E74" s="7">
-        <v>-0.82</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-33.41</v>
+        <v>-35.94</v>
       </c>
       <c r="D75" s="6">
-        <v>-32.36</v>
-      </c>
-      <c r="E75" s="8">
-        <v>1.05</v>
+        <v>-34.92</v>
+      </c>
+      <c r="E75" s="7">
+        <v>1.02</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-18.37</v>
+        <v>-32.36</v>
       </c>
       <c r="D76" s="6">
-        <v>-18.65</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-0.28</v>
+        <v>-32.45</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-24.07</v>
+        <v>-18.65</v>
       </c>
       <c r="D77" s="6">
-        <v>-24.33</v>
+        <v>-18.43</v>
       </c>
       <c r="E77" s="7">
-        <v>-0.26</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-46.21</v>
+        <v>-24.33</v>
       </c>
       <c r="D78" s="6">
-        <v>-46</v>
-      </c>
-      <c r="E78" s="8">
-        <v>0.21</v>
+        <v>-22.56</v>
+      </c>
+      <c r="E78" s="7">
+        <v>1.77</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-41.57</v>
+        <v>-46</v>
       </c>
       <c r="D79" s="6">
-        <v>-40.93</v>
+        <v>-46.21</v>
       </c>
       <c r="E79" s="8">
-        <v>0.64</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-24.18</v>
+        <v>-40.93</v>
       </c>
       <c r="D80" s="6">
-        <v>-23.88</v>
-      </c>
-      <c r="E80" s="8">
-        <v>0.3</v>
+        <v>-40.7</v>
+      </c>
+      <c r="E80" s="7">
+        <v>0.23</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-17.84</v>
+        <v>-23.88</v>
       </c>
       <c r="D81" s="6">
-        <v>-17.78</v>
-      </c>
-      <c r="E81" s="8">
-        <v>0.06</v>
+        <v>-23.85</v>
+      </c>
+      <c r="E81" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-35.6</v>
+        <v>-17.78</v>
       </c>
       <c r="D82" s="6">
-        <v>-34.37</v>
-      </c>
-      <c r="E82" s="8">
-        <v>1.23</v>
+        <v>-17.53</v>
+      </c>
+      <c r="E82" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-12.64</v>
+        <v>-34.37</v>
       </c>
       <c r="D83" s="6">
-        <v>-11.4</v>
+        <v>-34.82</v>
       </c>
       <c r="E83" s="8">
-        <v>1.24</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-49.47</v>
+        <v>-11.4</v>
       </c>
       <c r="D84" s="6">
-        <v>-49.03</v>
+        <v>-11.98</v>
       </c>
       <c r="E84" s="8">
-        <v>0.44</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-40.66</v>
+        <v>-46.53</v>
       </c>
       <c r="D85" s="6">
-        <v>-41.5</v>
+        <v>-39.77</v>
       </c>
       <c r="E85" s="7">
-        <v>-0.84</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-32.33</v>
+        <v>-49.03</v>
       </c>
       <c r="D86" s="6">
-        <v>-31.81</v>
-      </c>
-      <c r="E86" s="8">
-        <v>0.52</v>
+        <v>-48.43</v>
+      </c>
+      <c r="E86" s="7">
+        <v>0.6</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>718</v>
+        <v>-41.5</v>
       </c>
       <c r="D87" s="6">
-        <v>725</v>
+        <v>-41.75</v>
       </c>
       <c r="E87" s="8">
-        <v>7</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>889.2</v>
+        <v>-31.81</v>
       </c>
       <c r="D88" s="6">
-        <v>885.1</v>
+        <v>-31.39</v>
       </c>
       <c r="E88" s="7">
-        <v>-4.1</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>199.69</v>
+        <v>725</v>
       </c>
       <c r="D89" s="6">
-        <v>197.16</v>
+        <v>736</v>
       </c>
       <c r="E89" s="7">
-        <v>-2.53</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>607.8</v>
+        <v>885.1</v>
       </c>
       <c r="D90" s="6">
-        <v>617.4</v>
-      </c>
-      <c r="E90" s="8">
-        <v>9.6</v>
+        <v>924.15</v>
+      </c>
+      <c r="E90" s="7">
+        <v>39.05</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>1683</v>
+        <v>197.16</v>
       </c>
       <c r="D91" s="6">
-        <v>1677.2</v>
+        <v>200.3</v>
       </c>
       <c r="E91" s="7">
-        <v>-5.8</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>957</v>
+        <v>617.4</v>
       </c>
       <c r="D92" s="6">
-        <v>953.75</v>
-      </c>
-      <c r="E92" s="7">
-        <v>-3.25</v>
+        <v>616.55</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>3092.8</v>
+        <v>1677.2</v>
       </c>
       <c r="D93" s="6">
-        <v>3105</v>
-      </c>
-      <c r="E93" s="8">
-        <v>12.2</v>
+        <v>1681.8</v>
+      </c>
+      <c r="E93" s="7">
+        <v>4.6</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>615.05</v>
+        <v>953.75</v>
       </c>
       <c r="D94" s="6">
-        <v>621.75</v>
-      </c>
-      <c r="E94" s="8">
-        <v>6.7</v>
+        <v>976</v>
+      </c>
+      <c r="E94" s="7">
+        <v>22.25</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>350.15</v>
+        <v>3105</v>
       </c>
       <c r="D95" s="6">
-        <v>351.5</v>
+        <v>3093</v>
       </c>
       <c r="E95" s="8">
-        <v>1.35</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>178</v>
+        <v>621.75</v>
       </c>
       <c r="D96" s="6">
-        <v>178.14</v>
-      </c>
-      <c r="E96" s="8">
-        <v>0.14</v>
+        <v>624.15</v>
+      </c>
+      <c r="E96" s="7">
+        <v>2.4</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>2075</v>
+        <v>351.5</v>
       </c>
       <c r="D97" s="6">
-        <v>2114.4</v>
-      </c>
-      <c r="E97" s="8">
-        <v>39.4</v>
+        <v>351.65</v>
+      </c>
+      <c r="E97" s="7">
+        <v>0.15</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>4515.7</v>
+        <v>178.14</v>
       </c>
       <c r="D98" s="6">
-        <v>4580</v>
-      </c>
-      <c r="E98" s="8">
-        <v>64.3</v>
+        <v>178.69</v>
+      </c>
+      <c r="E98" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>192.33</v>
+        <v>2114.4</v>
       </c>
       <c r="D99" s="6">
-        <v>194.02</v>
+        <v>2100</v>
       </c>
       <c r="E99" s="8">
-        <v>1.69</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>34.82</v>
+        <v>4580</v>
       </c>
       <c r="D100" s="6">
-        <v>34.33</v>
-      </c>
-      <c r="E100" s="7">
-        <v>-0.49</v>
+        <v>4550</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-30</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>1053.2</v>
+        <v>2580</v>
       </c>
       <c r="D101" s="6">
-        <v>1061.3</v>
-      </c>
-      <c r="E101" s="8">
-        <v>8.1</v>
+        <v>2906</v>
+      </c>
+      <c r="E101" s="7">
+        <v>326</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>87</v>
+        <v>194.02</v>
       </c>
       <c r="D102" s="6">
-        <v>81</v>
+        <v>196.3</v>
       </c>
       <c r="E102" s="7">
-        <v>-6</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C103" s="6">
-        <v>81</v>
+        <v>34.33</v>
       </c>
       <c r="D103" s="6">
-        <v>87</v>
+        <v>34.18</v>
       </c>
       <c r="E103" s="8">
-        <v>6</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C104" s="6">
-        <v>62</v>
+        <v>1061.3</v>
       </c>
       <c r="D104" s="6">
-        <v>56</v>
+        <v>1067.9</v>
       </c>
       <c r="E104" s="7">
-        <v>-6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C105" s="6">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D105" s="6">
-        <v>62</v>
-      </c>
-      <c r="E105" s="8">
+        <v>87</v>
+      </c>
+      <c r="E105" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>46.86</v>
+        <v>87</v>
       </c>
       <c r="D106" s="6">
-        <v>50.07</v>
-      </c>
-      <c r="E106" s="8">
-        <v>3.21</v>
+        <v>93</v>
+      </c>
+      <c r="E106" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>39.65</v>
+        <v>32</v>
       </c>
       <c r="D107" s="6">
-        <v>39.1</v>
-      </c>
-      <c r="E107" s="7">
-        <v>-0.55</v>
+        <v>26</v>
+      </c>
+      <c r="E107" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>31.95</v>
+        <v>38</v>
       </c>
       <c r="D108" s="6">
-        <v>26.97</v>
-      </c>
-      <c r="E108" s="7">
-        <v>-4.98</v>
+        <v>32</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C109" s="6">
-        <v>39.21</v>
+        <v>56</v>
       </c>
       <c r="D109" s="6">
-        <v>41.92</v>
-      </c>
-      <c r="E109" s="8">
-        <v>2.71</v>
+        <v>62</v>
+      </c>
+      <c r="E109" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C110" s="6">
-        <v>43.8</v>
+        <v>19</v>
       </c>
       <c r="D110" s="6">
-        <v>42.79</v>
-      </c>
-      <c r="E110" s="7">
-        <v>-1.01</v>
+        <v>13</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="6">
-        <v>33.69</v>
+        <v>50</v>
       </c>
       <c r="D111" s="6">
-        <v>32.92</v>
-      </c>
-      <c r="E111" s="7">
-        <v>-0.77</v>
+        <v>38</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-12</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C112" s="6">
-        <v>24.3</v>
+        <v>93</v>
       </c>
       <c r="D112" s="6">
-        <v>26.05</v>
+        <v>81</v>
       </c>
       <c r="E112" s="8">
-        <v>1.75</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C113" s="6">
-        <v>38.06</v>
+        <v>62</v>
       </c>
       <c r="D113" s="6">
-        <v>40.53</v>
+        <v>56</v>
       </c>
       <c r="E113" s="8">
-        <v>2.47</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C114" s="6">
-        <v>35.24</v>
+        <v>7</v>
       </c>
       <c r="D114" s="6">
-        <v>36.91</v>
-      </c>
-      <c r="E114" s="8">
-        <v>1.67</v>
+        <v>50</v>
+      </c>
+      <c r="E114" s="7">
+        <v>43</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C115" s="6">
-        <v>38.02</v>
+        <v>13</v>
       </c>
       <c r="D115" s="6">
-        <v>38.29</v>
+        <v>7</v>
       </c>
       <c r="E115" s="8">
-        <v>0.27</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C116" s="6">
-        <v>36.09</v>
+        <v>26</v>
       </c>
       <c r="D116" s="6">
-        <v>42.59</v>
+        <v>19</v>
       </c>
       <c r="E116" s="8">
-        <v>6.5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>26.8</v>
+        <v>50.07</v>
       </c>
       <c r="D117" s="6">
-        <v>32.64</v>
-      </c>
-      <c r="E117" s="8">
-        <v>5.84</v>
+        <v>54.71</v>
+      </c>
+      <c r="E117" s="7">
+        <v>4.64</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>21.42</v>
+        <v>39.1</v>
       </c>
       <c r="D118" s="6">
-        <v>24.4</v>
-      </c>
-      <c r="E118" s="8">
-        <v>2.98</v>
+        <v>46.64</v>
+      </c>
+      <c r="E118" s="7">
+        <v>7.54</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>41.33</v>
+        <v>26.97</v>
       </c>
       <c r="D119" s="6">
-        <v>39.05</v>
+        <v>39.56</v>
       </c>
       <c r="E119" s="7">
-        <v>-2.28</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>31.17</v>
+        <v>41.92</v>
       </c>
       <c r="D120" s="6">
-        <v>33.32</v>
+        <v>41.74</v>
       </c>
       <c r="E120" s="8">
-        <v>2.15</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>37.18</v>
+        <v>42.79</v>
       </c>
       <c r="D121" s="6">
-        <v>20.36</v>
+        <v>43.9</v>
       </c>
       <c r="E121" s="7">
-        <v>-16.82</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>-19.5</v>
+        <v>32.92</v>
       </c>
       <c r="D122" s="6">
-        <v>-62.01</v>
+        <v>42.63</v>
       </c>
       <c r="E122" s="7">
-        <v>-42.51</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>16.37</v>
+        <v>26.05</v>
       </c>
       <c r="D123" s="6">
-        <v>-44.03</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-60.4</v>
+        <v>25.43</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>-65.94</v>
+        <v>40.53</v>
       </c>
       <c r="D124" s="6">
-        <v>-73.64</v>
+        <v>41.43</v>
       </c>
       <c r="E124" s="7">
-        <v>-7.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C125" s="6">
-        <v>-40.67</v>
+        <v>36.91</v>
       </c>
       <c r="D125" s="6">
-        <v>-62.42</v>
+        <v>37.1</v>
       </c>
       <c r="E125" s="7">
-        <v>-21.75</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C126" s="6">
-        <v>49.4</v>
+        <v>38.29</v>
       </c>
       <c r="D126" s="6">
-        <v>21.9</v>
+        <v>39.41</v>
       </c>
       <c r="E126" s="7">
-        <v>-27.5</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="6">
-        <v>41.47</v>
+        <v>42.59</v>
       </c>
       <c r="D127" s="6">
-        <v>-2.51</v>
-      </c>
-      <c r="E127" s="7">
-        <v>-43.98</v>
+        <v>40.95</v>
+      </c>
+      <c r="E127" s="8">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C128" s="6">
-        <v>-87.76000000000001</v>
+        <v>32.64</v>
       </c>
       <c r="D128" s="6">
-        <v>-88.94</v>
-      </c>
-      <c r="E128" s="7">
-        <v>-1.18</v>
+        <v>31.38</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C129" s="6">
-        <v>-0.32</v>
+        <v>24.71</v>
       </c>
       <c r="D129" s="6">
-        <v>-35.24</v>
+        <v>61.04</v>
       </c>
       <c r="E129" s="7">
-        <v>-34.92</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C130" s="6">
-        <v>76.84</v>
+        <v>24.4</v>
       </c>
       <c r="D130" s="6">
-        <v>-24.34</v>
+        <v>28.35</v>
       </c>
       <c r="E130" s="7">
-        <v>-101.18</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C131" s="6">
-        <v>11.15</v>
+        <v>39.05</v>
       </c>
       <c r="D131" s="6">
-        <v>68.94</v>
+        <v>38.35</v>
       </c>
       <c r="E131" s="8">
-        <v>57.79</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C132" s="6">
-        <v>11.72</v>
+        <v>33.32</v>
       </c>
       <c r="D132" s="6">
-        <v>15.81</v>
-      </c>
-      <c r="E132" s="8">
-        <v>4.09</v>
+        <v>35.1</v>
+      </c>
+      <c r="E132" s="7">
+        <v>1.78</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>23.11</v>
+        <v>20.36</v>
       </c>
       <c r="D133" s="6">
-        <v>8.41</v>
-      </c>
-      <c r="E133" s="7">
-        <v>-14.7</v>
+        <v>-22.34</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-42.7</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-49.32</v>
+        <v>-62.01</v>
       </c>
       <c r="D134" s="6">
-        <v>7.48</v>
-      </c>
-      <c r="E134" s="8">
-        <v>56.8</v>
+        <v>-44.31</v>
+      </c>
+      <c r="E134" s="7">
+        <v>17.7</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>46.69</v>
+        <v>-44.03</v>
       </c>
       <c r="D135" s="6">
-        <v>-63.47</v>
+        <v>-31.31</v>
       </c>
       <c r="E135" s="7">
-        <v>-110.16</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-12.67</v>
+        <v>-73.64</v>
       </c>
       <c r="D136" s="6">
+        <v>-80.95999999999999</v>
+      </c>
+      <c r="E136" s="8">
+        <v>-7.32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" s="6">
+        <v>-62.42</v>
+      </c>
+      <c r="D137" s="6">
+        <v>-38.37</v>
+      </c>
+      <c r="E137" s="7">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" s="6">
+        <v>21.9</v>
+      </c>
+      <c r="D138" s="6">
+        <v>-29.72</v>
+      </c>
+      <c r="E138" s="8">
+        <v>-51.62</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" s="6">
+        <v>-2.51</v>
+      </c>
+      <c r="D139" s="6">
+        <v>-20.07</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-17.56</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="6">
+        <v>-88.94</v>
+      </c>
+      <c r="D140" s="6">
+        <v>-85.61</v>
+      </c>
+      <c r="E140" s="7">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="6">
+        <v>-35.24</v>
+      </c>
+      <c r="D141" s="6">
+        <v>50.5</v>
+      </c>
+      <c r="E141" s="7">
+        <v>85.73999999999999</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="6">
+        <v>-24.34</v>
+      </c>
+      <c r="D142" s="6">
+        <v>-36.22</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-11.88</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6">
+        <v>68.94</v>
+      </c>
+      <c r="D143" s="6">
+        <v>-26.73</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-95.67</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="6">
+        <v>15.81</v>
+      </c>
+      <c r="D144" s="6">
+        <v>27.36</v>
+      </c>
+      <c r="E144" s="7">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="6">
+        <v>8.41</v>
+      </c>
+      <c r="D145" s="6">
+        <v>808.73</v>
+      </c>
+      <c r="E145" s="7">
+        <v>800.3200000000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="6">
+        <v>7.48</v>
+      </c>
+      <c r="D146" s="6">
+        <v>-57.01</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-64.48999999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147" s="6">
+        <v>-63.47</v>
+      </c>
+      <c r="D147" s="6">
+        <v>-79.73999999999999</v>
+      </c>
+      <c r="E147" s="8">
+        <v>-16.27</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C148" s="6">
         <v>-41.69</v>
       </c>
-      <c r="E136" s="7">
-        <v>-29.02</v>
+      <c r="D148" s="6">
+        <v>300.91</v>
+      </c>
+      <c r="E148" s="7">
+        <v>342.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5260,16 +5467,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>35.8</v>
+        <v>40.5</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.4</v>
+        <v>-5.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-10.3</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5409,34 +5616,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3556</v>
+        <v>0.3606</v>
       </c>
       <c r="B2" s="14">
-        <v>0.313</v>
+        <v>0.3287</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1981</v>
+        <v>0.2282</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1618</v>
+        <v>0.1651</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1504</v>
+        <v>0.1549</v>
       </c>
       <c r="F2" s="14">
-        <v>0.09420000000000001</v>
+        <v>0.1012</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0541</v>
+        <v>0.047</v>
       </c>
       <c r="H2" s="14">
-        <v>0.044</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0416</v>
+        <v>0.0385</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0145</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5461,22 +5668,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.0277</v>
+        <v>-0.0233</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0342</v>
+        <v>-0.0295</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0635</v>
+        <v>-0.0617</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0655</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.08779999999999999</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1096</v>
+        <v>-0.1198</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,28 +217,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>27.0 → 39.6</t>
+    <t>28.4 → 31.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>39.6</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>24.7 → 61.0</t>
-  </si>
-  <si>
-    <t>24.7</t>
-  </si>
-  <si>
-    <t>61.0</t>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>31.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -963,10 +951,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>736</v>
+        <v>731.3</v>
       </c>
       <c r="D2">
-        <v>1.52</v>
+        <v>-0.64</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -975,46 +963,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-2.17</v>
+        <v>-2.79</v>
       </c>
       <c r="H2">
-        <v>28.91</v>
+        <v>28.08</v>
       </c>
       <c r="I2">
-        <v>3.52</v>
+        <v>2.37</v>
       </c>
       <c r="J2">
-        <v>0.55</v>
+        <v>1.57</v>
       </c>
       <c r="K2">
-        <v>-1.33</v>
+        <v>1.16</v>
       </c>
       <c r="L2">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="M2">
-        <v>32.87</v>
+        <v>31.19</v>
       </c>
       <c r="N2">
         <v>87</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>724.4</v>
+        <v>727.79</v>
       </c>
       <c r="Q2">
-        <v>724.73</v>
+        <v>725.48</v>
       </c>
       <c r="R2">
-        <v>727.72</v>
+        <v>727.67</v>
       </c>
       <c r="S2">
-        <v>688.17</v>
+        <v>688.26</v>
       </c>
       <c r="T2">
-        <v>6.95</v>
+        <v>6.25</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1029,34 +1017,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.71</v>
+        <v>52.47</v>
       </c>
       <c r="Z2">
-        <v>0.39</v>
+        <v>0.78</v>
       </c>
       <c r="AA2">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="AB2">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AC2">
-        <v>42.99</v>
+        <v>53.45</v>
       </c>
       <c r="AD2">
-        <v>35.67</v>
+        <v>44.51</v>
       </c>
       <c r="AE2">
-        <v>16.11</v>
+        <v>15.99</v>
       </c>
       <c r="AF2">
-        <v>-22.34</v>
+        <v>0.17</v>
       </c>
       <c r="AG2">
-        <v>744.8200000000001</v>
+        <v>745.36</v>
       </c>
       <c r="AH2">
-        <v>704.63</v>
+        <v>705.6</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1065,7 +1053,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>17.13</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1076,10 +1064,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>924.15</v>
+        <v>915.8</v>
       </c>
       <c r="D3">
-        <v>4.41</v>
+        <v>-0.9</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1088,25 +1076,25 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-14.55</v>
+        <v>-15.32</v>
       </c>
       <c r="H3">
-        <v>82.87</v>
+        <v>81.22</v>
       </c>
       <c r="I3">
-        <v>0.84</v>
+        <v>-0.7</v>
       </c>
       <c r="J3">
-        <v>-1.03</v>
+        <v>0.5</v>
       </c>
       <c r="K3">
-        <v>1.1</v>
+        <v>3.33</v>
       </c>
       <c r="L3">
-        <v>9.9</v>
+        <v>6.81</v>
       </c>
       <c r="M3">
-        <v>1.33</v>
+        <v>2.19</v>
       </c>
       <c r="N3">
         <v>93</v>
@@ -1115,19 +1103,19 @@
         <v>68</v>
       </c>
       <c r="P3">
-        <v>907.05</v>
+        <v>905.75</v>
       </c>
       <c r="Q3">
-        <v>951.45</v>
+        <v>950.58</v>
       </c>
       <c r="R3">
-        <v>957.64</v>
+        <v>957.28</v>
       </c>
       <c r="S3">
-        <v>767.41</v>
+        <v>768.3200000000001</v>
       </c>
       <c r="T3">
-        <v>20.43</v>
+        <v>19.2</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1142,34 +1130,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.64</v>
+        <v>45.35</v>
       </c>
       <c r="Z3">
-        <v>-10.22</v>
+        <v>-10.88</v>
       </c>
       <c r="AA3">
-        <v>-1.33</v>
+        <v>-3.24</v>
       </c>
       <c r="AB3">
-        <v>-8.890000000000001</v>
+        <v>-7.63</v>
       </c>
       <c r="AC3">
-        <v>11.7</v>
+        <v>21.39</v>
       </c>
       <c r="AD3">
-        <v>4.54</v>
+        <v>11.03</v>
       </c>
       <c r="AE3">
-        <v>43.89</v>
+        <v>42.6</v>
       </c>
       <c r="AF3">
-        <v>-44.31</v>
+        <v>-60.35</v>
       </c>
       <c r="AG3">
-        <v>1031.31</v>
+        <v>1031.64</v>
       </c>
       <c r="AH3">
-        <v>871.59</v>
+        <v>869.51</v>
       </c>
       <c r="AI3">
         <v>1028.89</v>
@@ -1178,7 +1166,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>27.75</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1189,10 +1177,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>200.3</v>
+        <v>200.03</v>
       </c>
       <c r="D4">
-        <v>1.59</v>
+        <v>-0.13</v>
       </c>
       <c r="E4">
         <v>307.76</v>
@@ -1201,46 +1189,46 @@
         <v>197.16</v>
       </c>
       <c r="G4">
-        <v>-34.92</v>
+        <v>-35</v>
       </c>
       <c r="H4">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="I4">
-        <v>0.44</v>
+        <v>0.04</v>
       </c>
       <c r="J4">
-        <v>-4.54</v>
+        <v>-4.21</v>
       </c>
       <c r="K4">
-        <v>-13.25</v>
+        <v>-10.34</v>
       </c>
       <c r="L4">
-        <v>-33.45</v>
+        <v>-34.48</v>
       </c>
       <c r="M4">
-        <v>-6.17</v>
+        <v>-6.25</v>
       </c>
       <c r="N4">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>199.37</v>
+        <v>199.38</v>
       </c>
       <c r="Q4">
-        <v>201.78</v>
+        <v>201.48</v>
       </c>
       <c r="R4">
-        <v>208.56</v>
+        <v>208.13</v>
       </c>
       <c r="S4">
-        <v>239.51</v>
+        <v>239.2</v>
       </c>
       <c r="T4">
-        <v>-16.37</v>
+        <v>-16.38</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1255,34 +1243,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.56</v>
+        <v>38.94</v>
       </c>
       <c r="Z4">
-        <v>-2.98</v>
+        <v>-2.81</v>
       </c>
       <c r="AA4">
-        <v>-3.19</v>
+        <v>-3.11</v>
       </c>
       <c r="AB4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AC4">
-        <v>49.6</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="AD4">
-        <v>43.54</v>
+        <v>49.14</v>
       </c>
       <c r="AE4">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="AF4">
-        <v>-31.31</v>
+        <v>-36.72</v>
       </c>
       <c r="AG4">
-        <v>206.26</v>
+        <v>205.51</v>
       </c>
       <c r="AH4">
-        <v>197.3</v>
+        <v>197.44</v>
       </c>
       <c r="AI4">
         <v>210.35</v>
@@ -1291,7 +1279,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>32.4</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1302,10 +1290,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>616.55</v>
+        <v>609.8</v>
       </c>
       <c r="D5">
-        <v>-0.14</v>
+        <v>-1.09</v>
       </c>
       <c r="E5">
         <v>912.72</v>
@@ -1314,46 +1302,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-32.45</v>
+        <v>-33.19</v>
       </c>
       <c r="H5">
-        <v>7.33</v>
+        <v>6.16</v>
       </c>
       <c r="I5">
-        <v>-3.88</v>
+        <v>-0.66</v>
       </c>
       <c r="J5">
-        <v>-3.87</v>
+        <v>-2.45</v>
       </c>
       <c r="K5">
-        <v>-14.2</v>
+        <v>-14.16</v>
       </c>
       <c r="L5">
-        <v>-31.94</v>
+        <v>-32.52</v>
       </c>
       <c r="M5">
-        <v>-7.2</v>
+        <v>-7.34</v>
       </c>
       <c r="N5">
         <v>32</v>
       </c>
       <c r="O5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5">
-        <v>613.41</v>
+        <v>612.6</v>
       </c>
       <c r="Q5">
-        <v>651.47</v>
+        <v>651.29</v>
       </c>
       <c r="R5">
-        <v>654.28</v>
+        <v>652.5</v>
       </c>
       <c r="S5">
-        <v>697.42</v>
+        <v>696.77</v>
       </c>
       <c r="T5">
-        <v>-11.6</v>
+        <v>-12.48</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1368,43 +1356,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41.74</v>
+        <v>40.28</v>
       </c>
       <c r="Z5">
-        <v>-11.04</v>
+        <v>-12.29</v>
       </c>
       <c r="AA5">
-        <v>-4.16</v>
+        <v>-5.79</v>
       </c>
       <c r="AB5">
-        <v>-6.87</v>
+        <v>-6.51</v>
       </c>
       <c r="AC5">
-        <v>7.82</v>
+        <v>5.56</v>
       </c>
       <c r="AD5">
-        <v>11.27</v>
+        <v>7.86</v>
       </c>
       <c r="AE5">
-        <v>29.27</v>
+        <v>27.9</v>
       </c>
       <c r="AF5">
-        <v>-80.95999999999999</v>
+        <v>-87.65000000000001</v>
       </c>
       <c r="AG5">
-        <v>754.67</v>
+        <v>754.78</v>
       </c>
       <c r="AH5">
-        <v>548.27</v>
+        <v>547.8</v>
       </c>
       <c r="AI5">
-        <v>703.01</v>
+        <v>697.49</v>
       </c>
       <c r="AJ5" t="s">
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>15.93</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1415,10 +1403,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1681.8</v>
+        <v>1659.6</v>
       </c>
       <c r="D6">
-        <v>0.27</v>
+        <v>-1.32</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1427,46 +1415,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-18.43</v>
+        <v>-19.5</v>
       </c>
       <c r="H6">
-        <v>24.77</v>
+        <v>23.12</v>
       </c>
       <c r="I6">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J6">
-        <v>-0.86</v>
+        <v>-5.5</v>
       </c>
       <c r="K6">
-        <v>-11.8</v>
+        <v>-12.01</v>
       </c>
       <c r="L6">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="M6">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N6">
         <v>74</v>
       </c>
       <c r="O6">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P6">
-        <v>1670.58</v>
+        <v>1671.56</v>
       </c>
       <c r="Q6">
-        <v>1718.98</v>
+        <v>1715.04</v>
       </c>
       <c r="R6">
-        <v>1722.43</v>
+        <v>1720.92</v>
       </c>
       <c r="S6">
-        <v>1704.61</v>
+        <v>1703.77</v>
       </c>
       <c r="T6">
-        <v>-1.34</v>
+        <v>-2.59</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1481,34 +1469,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>43.9</v>
+        <v>39.9</v>
       </c>
       <c r="Z6">
-        <v>-19.12</v>
+        <v>-20.02</v>
       </c>
       <c r="AA6">
-        <v>-15.01</v>
+        <v>-16.01</v>
       </c>
       <c r="AB6">
-        <v>-4.11</v>
+        <v>-4</v>
       </c>
       <c r="AC6">
-        <v>28.38</v>
+        <v>22.9</v>
       </c>
       <c r="AD6">
-        <v>19.23</v>
+        <v>23.38</v>
       </c>
       <c r="AE6">
-        <v>46.59</v>
+        <v>47.98</v>
       </c>
       <c r="AF6">
-        <v>-38.37</v>
+        <v>191.51</v>
       </c>
       <c r="AG6">
-        <v>1819.04</v>
+        <v>1818.03</v>
       </c>
       <c r="AH6">
-        <v>1618.93</v>
+        <v>1612.05</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1517,7 +1505,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>25.4</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1528,10 +1516,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>976</v>
+        <v>968.5</v>
       </c>
       <c r="D7">
-        <v>2.33</v>
+        <v>-0.77</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1540,46 +1528,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-22.56</v>
+        <v>-23.16</v>
       </c>
       <c r="H7">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>1.67</v>
+        <v>0.08</v>
       </c>
       <c r="J7">
-        <v>-4.24</v>
+        <v>-4.11</v>
       </c>
       <c r="K7">
-        <v>-13.24</v>
+        <v>-11.13</v>
       </c>
       <c r="L7">
-        <v>-12.84</v>
+        <v>-14.68</v>
       </c>
       <c r="M7">
-        <v>4.39</v>
+        <v>4.13</v>
       </c>
       <c r="N7">
         <v>62</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P7">
-        <v>960.79</v>
+        <v>960.95</v>
       </c>
       <c r="Q7">
-        <v>986.45</v>
+        <v>984.13</v>
       </c>
       <c r="R7">
-        <v>1035.01</v>
+        <v>1032.23</v>
       </c>
       <c r="S7">
-        <v>1106.96</v>
+        <v>1105.96</v>
       </c>
       <c r="T7">
-        <v>-11.83</v>
+        <v>-12.43</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1594,34 +1582,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.63</v>
+        <v>40.5</v>
       </c>
       <c r="Z7">
-        <v>-20.99</v>
+        <v>-19.92</v>
       </c>
       <c r="AA7">
-        <v>-21.08</v>
+        <v>-20.84</v>
       </c>
       <c r="AB7">
-        <v>0.09</v>
+        <v>0.92</v>
       </c>
       <c r="AC7">
-        <v>57.54</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AD7">
-        <v>39.59</v>
+        <v>52.92</v>
       </c>
       <c r="AE7">
-        <v>18.96</v>
+        <v>18.56</v>
       </c>
       <c r="AF7">
-        <v>-29.72</v>
+        <v>-58.61</v>
       </c>
       <c r="AG7">
-        <v>1026.83</v>
+        <v>1022.91</v>
       </c>
       <c r="AH7">
-        <v>946.0700000000001</v>
+        <v>945.34</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1630,7 +1618,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>57.33</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1641,37 +1629,37 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3093</v>
+        <v>3082.5</v>
       </c>
       <c r="D8">
-        <v>-0.39</v>
+        <v>-0.34</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
       </c>
       <c r="F8">
-        <v>3088.9</v>
+        <v>3082.5</v>
       </c>
       <c r="G8">
-        <v>-46.21</v>
+        <v>-46.39</v>
       </c>
       <c r="H8">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-3.07</v>
+        <v>-4.02</v>
       </c>
       <c r="J8">
-        <v>-13.6</v>
+        <v>-13.36</v>
       </c>
       <c r="K8">
-        <v>-16.57</v>
+        <v>-14.93</v>
       </c>
       <c r="L8">
-        <v>-39.77</v>
+        <v>-39.96</v>
       </c>
       <c r="M8">
-        <v>-11.98</v>
+        <v>-12.56</v>
       </c>
       <c r="N8">
         <v>13</v>
@@ -1680,19 +1668,19 @@
         <v>11</v>
       </c>
       <c r="P8">
-        <v>3118.28</v>
+        <v>3092.44</v>
       </c>
       <c r="Q8">
-        <v>3274.88</v>
+        <v>3254.15</v>
       </c>
       <c r="R8">
-        <v>3519.65</v>
+        <v>3510.21</v>
       </c>
       <c r="S8">
-        <v>4209.58</v>
+        <v>4200.59</v>
       </c>
       <c r="T8">
-        <v>-26.52</v>
+        <v>-26.62</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1707,34 +1695,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>25.43</v>
+        <v>24.87</v>
       </c>
       <c r="Z8">
-        <v>-126.68</v>
+        <v>-125.79</v>
       </c>
       <c r="AA8">
-        <v>-117.74</v>
+        <v>-119.35</v>
       </c>
       <c r="AB8">
-        <v>-8.949999999999999</v>
+        <v>-6.45</v>
       </c>
       <c r="AC8">
-        <v>12.01</v>
+        <v>14.14</v>
       </c>
       <c r="AD8">
-        <v>10.54</v>
+        <v>11</v>
       </c>
       <c r="AE8">
-        <v>83.20999999999999</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="AF8">
-        <v>-20.07</v>
+        <v>-29.08</v>
       </c>
       <c r="AG8">
-        <v>3546.37</v>
+        <v>3517.4</v>
       </c>
       <c r="AH8">
-        <v>3003.39</v>
+        <v>2990.91</v>
       </c>
       <c r="AI8">
         <v>3348.63</v>
@@ -1743,7 +1731,7 @@
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>59.37</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1754,58 +1742,58 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>624.15</v>
+        <v>615.3</v>
       </c>
       <c r="D9">
-        <v>0.39</v>
+        <v>-1.42</v>
       </c>
       <c r="E9">
-        <v>1052.57</v>
+        <v>1029.69</v>
       </c>
       <c r="F9">
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-40.7</v>
+        <v>-40.24</v>
       </c>
       <c r="H9">
-        <v>15.93</v>
+        <v>14.29</v>
       </c>
       <c r="I9">
-        <v>-3.15</v>
+        <v>-1.62</v>
       </c>
       <c r="J9">
-        <v>-2.16</v>
+        <v>-2.9</v>
       </c>
       <c r="K9">
-        <v>-6.54</v>
+        <v>-7.22</v>
       </c>
       <c r="L9">
-        <v>-39.27</v>
+        <v>-41.54</v>
       </c>
       <c r="M9">
-        <v>36.06</v>
+        <v>35.21</v>
       </c>
       <c r="N9">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P9">
-        <v>621.29</v>
+        <v>619.26</v>
       </c>
       <c r="Q9">
-        <v>654.23</v>
+        <v>653.6</v>
       </c>
       <c r="R9">
-        <v>657.01</v>
+        <v>656.3099999999999</v>
       </c>
       <c r="S9">
-        <v>659.97</v>
+        <v>659.52</v>
       </c>
       <c r="T9">
-        <v>-5.43</v>
+        <v>-6.7</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1820,34 +1808,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.43</v>
+        <v>39.08</v>
       </c>
       <c r="Z9">
-        <v>-8.85</v>
+        <v>-10.18</v>
       </c>
       <c r="AA9">
-        <v>-2.78</v>
+        <v>-4.26</v>
       </c>
       <c r="AB9">
-        <v>-6.07</v>
+        <v>-5.92</v>
       </c>
       <c r="AC9">
-        <v>6.38</v>
+        <v>7.6</v>
       </c>
       <c r="AD9">
-        <v>5.29</v>
+        <v>5.44</v>
       </c>
       <c r="AE9">
-        <v>22.73</v>
+        <v>21.98</v>
       </c>
       <c r="AF9">
-        <v>-85.61</v>
+        <v>-90.52</v>
       </c>
       <c r="AG9">
-        <v>722.29</v>
+        <v>722.9</v>
       </c>
       <c r="AH9">
-        <v>586.17</v>
+        <v>584.3</v>
       </c>
       <c r="AI9">
         <v>682.46</v>
@@ -1856,7 +1844,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>19.58</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1867,58 +1855,58 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>351.65</v>
+        <v>345.15</v>
       </c>
       <c r="D10">
-        <v>0.04</v>
+        <v>-1.85</v>
       </c>
       <c r="E10">
         <v>461.8</v>
       </c>
       <c r="F10">
-        <v>345.25</v>
+        <v>345.15</v>
       </c>
       <c r="G10">
-        <v>-23.85</v>
+        <v>-25.26</v>
       </c>
       <c r="H10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>-2.83</v>
+        <v>-3.86</v>
       </c>
       <c r="J10">
-        <v>-3.84</v>
+        <v>-6.21</v>
       </c>
       <c r="K10">
-        <v>-6.77</v>
+        <v>-7.24</v>
       </c>
       <c r="L10">
-        <v>-9.52</v>
+        <v>-11.76</v>
       </c>
       <c r="M10">
-        <v>15.49</v>
+        <v>14.83</v>
       </c>
       <c r="N10">
         <v>68</v>
       </c>
       <c r="O10">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P10">
-        <v>354.26</v>
+        <v>351.49</v>
       </c>
       <c r="Q10">
-        <v>363.37</v>
+        <v>362.34</v>
       </c>
       <c r="R10">
-        <v>369.17</v>
+        <v>368.53</v>
       </c>
       <c r="S10">
-        <v>386.32</v>
+        <v>386.15</v>
       </c>
       <c r="T10">
-        <v>-8.970000000000001</v>
+        <v>-10.62</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1933,43 +1921,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>37.1</v>
+        <v>32.44</v>
       </c>
       <c r="Z10">
-        <v>-4.15</v>
+        <v>-4.94</v>
       </c>
       <c r="AA10">
-        <v>-2.81</v>
+        <v>-3.24</v>
       </c>
       <c r="AB10">
-        <v>-1.34</v>
+        <v>-1.71</v>
       </c>
       <c r="AC10">
         <v>5.53</v>
       </c>
       <c r="AD10">
-        <v>5.26</v>
+        <v>5.41</v>
       </c>
       <c r="AE10">
-        <v>7.38</v>
+        <v>7.62</v>
       </c>
       <c r="AF10">
-        <v>50.5</v>
+        <v>37.04</v>
       </c>
       <c r="AG10">
-        <v>376.43</v>
+        <v>377.67</v>
       </c>
       <c r="AH10">
-        <v>350.31</v>
+        <v>347.02</v>
       </c>
       <c r="AI10">
-        <v>347.84</v>
+        <v>368.8</v>
       </c>
       <c r="AJ10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK10">
-        <v>34.02</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1980,10 +1968,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>178.69</v>
+        <v>175.64</v>
       </c>
       <c r="D11">
-        <v>0.31</v>
+        <v>-1.71</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1992,46 +1980,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-17.53</v>
+        <v>-18.93</v>
       </c>
       <c r="H11">
-        <v>13.51</v>
+        <v>11.57</v>
       </c>
       <c r="I11">
-        <v>-4.08</v>
+        <v>-6.57</v>
       </c>
       <c r="J11">
-        <v>-2.99</v>
+        <v>-6.97</v>
       </c>
       <c r="K11">
-        <v>-5.85</v>
+        <v>-6.67</v>
       </c>
       <c r="L11">
-        <v>8.06</v>
+        <v>7.01</v>
       </c>
       <c r="M11">
-        <v>10.12</v>
+        <v>9.58</v>
       </c>
       <c r="N11">
         <v>81</v>
       </c>
       <c r="O11">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="P11">
-        <v>181.43</v>
+        <v>178.95</v>
       </c>
       <c r="Q11">
-        <v>184.82</v>
+        <v>184.32</v>
       </c>
       <c r="R11">
-        <v>185.88</v>
+        <v>185.7</v>
       </c>
       <c r="S11">
-        <v>192.05</v>
+        <v>192.1</v>
       </c>
       <c r="T11">
-        <v>-6.96</v>
+        <v>-8.57</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2046,43 +2034,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>39.41</v>
+        <v>35.56</v>
       </c>
       <c r="Z11">
-        <v>-1.42</v>
+        <v>-1.92</v>
       </c>
       <c r="AA11">
-        <v>-0.54</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AB11">
-        <v>-0.88</v>
+        <v>-1.1</v>
       </c>
       <c r="AC11">
         <v>2.72</v>
       </c>
       <c r="AD11">
-        <v>12.22</v>
+        <v>4.03</v>
       </c>
       <c r="AE11">
-        <v>4.73</v>
+        <v>4.68</v>
       </c>
       <c r="AF11">
-        <v>-36.22</v>
+        <v>-29.73</v>
       </c>
       <c r="AG11">
-        <v>191.84</v>
+        <v>192.44</v>
       </c>
       <c r="AH11">
-        <v>177.79</v>
+        <v>176.2</v>
       </c>
       <c r="AI11">
-        <v>192.88</v>
+        <v>190.47</v>
       </c>
       <c r="AJ11" t="s">
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>26.58</v>
+        <v>29.57</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2093,10 +2081,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2100</v>
+        <v>2080.3</v>
       </c>
       <c r="D12">
-        <v>-0.68</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2105,46 +2093,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-34.82</v>
+        <v>-35.43</v>
       </c>
       <c r="H12">
-        <v>5.92</v>
+        <v>4.93</v>
       </c>
       <c r="I12">
-        <v>1.41</v>
+        <v>2.36</v>
       </c>
       <c r="J12">
-        <v>-9.49</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K12">
-        <v>0.19</v>
+        <v>1.11</v>
       </c>
       <c r="L12">
-        <v>-24.69</v>
+        <v>-26.06</v>
       </c>
       <c r="M12">
-        <v>-8.800000000000001</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="N12">
         <v>56</v>
       </c>
       <c r="O12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P12">
-        <v>2074.48</v>
+        <v>2084.06</v>
       </c>
       <c r="Q12">
-        <v>2140.43</v>
+        <v>2130.95</v>
       </c>
       <c r="R12">
-        <v>2270.78</v>
+        <v>2266.47</v>
       </c>
       <c r="S12">
-        <v>2473.32</v>
+        <v>2468.13</v>
       </c>
       <c r="T12">
-        <v>-15.09</v>
+        <v>-15.71</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2159,34 +2147,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>40.95</v>
+        <v>38.75</v>
       </c>
       <c r="Z12">
-        <v>-54.21</v>
+        <v>-52.21</v>
       </c>
       <c r="AA12">
-        <v>-55.47</v>
+        <v>-54.82</v>
       </c>
       <c r="AB12">
-        <v>1.27</v>
+        <v>2.61</v>
       </c>
       <c r="AC12">
-        <v>72.90000000000001</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="AD12">
-        <v>48.36</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="AE12">
-        <v>58.12</v>
+        <v>56.04</v>
       </c>
       <c r="AF12">
-        <v>-26.73</v>
+        <v>-58.8</v>
       </c>
       <c r="AG12">
-        <v>2286.98</v>
+        <v>2266.31</v>
       </c>
       <c r="AH12">
-        <v>1993.88</v>
+        <v>1995.58</v>
       </c>
       <c r="AI12">
         <v>2235.3</v>
@@ -2195,7 +2183,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>35.28</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2206,58 +2194,58 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4550</v>
+        <v>4377</v>
       </c>
       <c r="D13">
-        <v>-0.66</v>
+        <v>-3.8</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
       </c>
       <c r="F13">
-        <v>3408.3</v>
+        <v>3418.2</v>
       </c>
       <c r="G13">
-        <v>-11.98</v>
+        <v>-15.33</v>
       </c>
       <c r="H13">
-        <v>33.5</v>
+        <v>28.05</v>
       </c>
       <c r="I13">
-        <v>-5.59</v>
+        <v>-6.37</v>
       </c>
       <c r="J13">
-        <v>-9.49</v>
+        <v>-12.81</v>
       </c>
       <c r="K13">
-        <v>-1.18</v>
+        <v>-4.57</v>
       </c>
       <c r="L13">
-        <v>35.14</v>
+        <v>28.42</v>
       </c>
       <c r="M13">
-        <v>16.51</v>
+        <v>13.3</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P13">
-        <v>4581.54</v>
+        <v>4521.94</v>
       </c>
       <c r="Q13">
-        <v>4827.44</v>
+        <v>4796.54</v>
       </c>
       <c r="R13">
-        <v>4943</v>
+        <v>4935.73</v>
       </c>
       <c r="S13">
-        <v>4414.93</v>
+        <v>4417.27</v>
       </c>
       <c r="T13">
-        <v>3.06</v>
+        <v>-0.91</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2269,46 +2257,46 @@
         <v>54</v>
       </c>
       <c r="X13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>31.38</v>
+        <v>25.32</v>
       </c>
       <c r="Z13">
-        <v>-104.21</v>
+        <v>-123.19</v>
       </c>
       <c r="AA13">
-        <v>-64.53</v>
+        <v>-76.26000000000001</v>
       </c>
       <c r="AB13">
-        <v>-39.68</v>
+        <v>-46.93</v>
       </c>
       <c r="AC13">
         <v>16.51</v>
       </c>
       <c r="AD13">
-        <v>8.59</v>
+        <v>14.09</v>
       </c>
       <c r="AE13">
-        <v>91.61</v>
+        <v>100.38</v>
       </c>
       <c r="AF13">
-        <v>27.36</v>
+        <v>361.77</v>
       </c>
       <c r="AG13">
-        <v>5151.57</v>
+        <v>5167.81</v>
       </c>
       <c r="AH13">
-        <v>4503.3</v>
+        <v>4425.26</v>
       </c>
       <c r="AI13">
-        <v>4833.78</v>
+        <v>4688.95</v>
       </c>
       <c r="AJ13" t="s">
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>54.97</v>
+        <v>59.14</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2319,58 +2307,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2906</v>
+        <v>2890.3</v>
       </c>
       <c r="D14">
-        <v>12.64</v>
+        <v>-0.54</v>
       </c>
       <c r="E14">
-        <v>4824.87</v>
+        <v>4808.59</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-39.77</v>
+        <v>-39.89</v>
       </c>
       <c r="H14">
-        <v>32.45</v>
+        <v>31.74</v>
       </c>
       <c r="I14">
-        <v>10.66</v>
+        <v>9.69</v>
       </c>
       <c r="J14">
-        <v>3.21</v>
+        <v>1.31</v>
       </c>
       <c r="K14">
-        <v>-0.74</v>
+        <v>-1.15</v>
       </c>
       <c r="L14">
-        <v>-37.78</v>
+        <v>-40.1</v>
       </c>
       <c r="M14">
-        <v>22.82</v>
+        <v>21.23</v>
       </c>
       <c r="N14">
         <v>50</v>
       </c>
       <c r="O14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P14">
-        <v>2664.52</v>
+        <v>2715.58</v>
       </c>
       <c r="Q14">
-        <v>2742.61</v>
+        <v>2746.4</v>
       </c>
       <c r="R14">
-        <v>2872.26</v>
+        <v>2871.3</v>
       </c>
       <c r="S14">
-        <v>2843.09</v>
+        <v>2837.35</v>
       </c>
       <c r="T14">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2385,43 +2373,43 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>61.04</v>
+        <v>59.55</v>
       </c>
       <c r="Z14">
-        <v>-52.97</v>
+        <v>-34.75</v>
       </c>
       <c r="AA14">
-        <v>-60.1</v>
+        <v>-55.03</v>
       </c>
       <c r="AB14">
-        <v>7.14</v>
+        <v>20.28</v>
       </c>
       <c r="AC14">
-        <v>33.33</v>
+        <v>65.3</v>
       </c>
       <c r="AD14">
-        <v>12.88</v>
+        <v>33.27</v>
       </c>
       <c r="AE14">
-        <v>78.62</v>
+        <v>75.3</v>
       </c>
       <c r="AF14">
-        <v>808.73</v>
+        <v>27.88</v>
       </c>
       <c r="AG14">
-        <v>2930.29</v>
+        <v>2943.04</v>
       </c>
       <c r="AH14">
-        <v>2554.93</v>
+        <v>2549.76</v>
       </c>
       <c r="AI14">
-        <v>2612.29</v>
+        <v>2666.99</v>
       </c>
       <c r="AJ14" t="s">
         <v>56</v>
       </c>
       <c r="AK14">
-        <v>55.95</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2432,10 +2420,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>196.3</v>
+        <v>198.02</v>
       </c>
       <c r="D15">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="E15">
         <v>380.65</v>
@@ -2444,25 +2432,25 @@
         <v>192.33</v>
       </c>
       <c r="G15">
-        <v>-48.43</v>
+        <v>-47.98</v>
       </c>
       <c r="H15">
-        <v>2.06</v>
+        <v>2.96</v>
       </c>
       <c r="I15">
-        <v>-5.42</v>
+        <v>-2.41</v>
       </c>
       <c r="J15">
-        <v>-14.66</v>
+        <v>-14.5</v>
       </c>
       <c r="K15">
-        <v>-16.13</v>
+        <v>-12.41</v>
       </c>
       <c r="L15">
-        <v>-42.2</v>
+        <v>-43.01</v>
       </c>
       <c r="M15">
-        <v>4.7</v>
+        <v>3.89</v>
       </c>
       <c r="N15">
         <v>7</v>
@@ -2471,19 +2459,19 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>196.67</v>
+        <v>195.7</v>
       </c>
       <c r="Q15">
-        <v>213.5</v>
+        <v>211.64</v>
       </c>
       <c r="R15">
-        <v>223.33</v>
+        <v>222.64</v>
       </c>
       <c r="S15">
-        <v>247.96</v>
+        <v>247.43</v>
       </c>
       <c r="T15">
-        <v>-20.83</v>
+        <v>-19.97</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2498,43 +2486,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>28.35</v>
+        <v>31.26</v>
       </c>
       <c r="Z15">
-        <v>-8.359999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AA15">
-        <v>-6.3</v>
+        <v>-6.7</v>
       </c>
       <c r="AB15">
-        <v>-2.06</v>
+        <v>-1.6</v>
       </c>
       <c r="AC15">
-        <v>16.65</v>
+        <v>33.2</v>
       </c>
       <c r="AD15">
-        <v>7.22</v>
+        <v>18.29</v>
       </c>
       <c r="AE15">
-        <v>7.97</v>
+        <v>7.82</v>
       </c>
       <c r="AF15">
-        <v>-57.01</v>
+        <v>-60.73</v>
       </c>
       <c r="AG15">
-        <v>237.43</v>
+        <v>234.23</v>
       </c>
       <c r="AH15">
-        <v>189.57</v>
+        <v>189.06</v>
       </c>
       <c r="AI15">
-        <v>219.64</v>
+        <v>219.48</v>
       </c>
       <c r="AJ15" t="s">
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>40.44</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2545,10 +2533,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>34.18</v>
+        <v>34.01</v>
       </c>
       <c r="D16">
-        <v>-0.44</v>
+        <v>-0.5</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2557,46 +2545,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-41.75</v>
+        <v>-42.04</v>
       </c>
       <c r="H16">
-        <v>8.99</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I16">
-        <v>-5.55</v>
+        <v>-3.33</v>
       </c>
       <c r="J16">
-        <v>-10.08</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="K16">
-        <v>-17.86</v>
+        <v>-15.67</v>
       </c>
       <c r="L16">
-        <v>-37.88</v>
+        <v>-38.32</v>
       </c>
       <c r="M16">
-        <v>-2.95</v>
+        <v>-3.97</v>
       </c>
       <c r="N16">
         <v>19</v>
       </c>
       <c r="O16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P16">
-        <v>34.56</v>
+        <v>34.33</v>
       </c>
       <c r="Q16">
-        <v>35.51</v>
+        <v>35.35</v>
       </c>
       <c r="R16">
-        <v>37.37</v>
+        <v>37.26</v>
       </c>
       <c r="S16">
-        <v>41.56</v>
+        <v>41.47</v>
       </c>
       <c r="T16">
-        <v>-17.75</v>
+        <v>-17.99</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2611,43 +2599,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>38.35</v>
+        <v>37.53</v>
       </c>
       <c r="Z16">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="AA16">
-        <v>-0.84</v>
+        <v>-0.86</v>
       </c>
       <c r="AB16">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AC16">
-        <v>51.6</v>
+        <v>40.13</v>
       </c>
       <c r="AD16">
-        <v>53.72</v>
+        <v>47.74</v>
       </c>
       <c r="AE16">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF16">
-        <v>-79.73999999999999</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="AG16">
-        <v>37.22</v>
+        <v>36.95</v>
       </c>
       <c r="AH16">
-        <v>33.81</v>
+        <v>33.75</v>
       </c>
       <c r="AI16">
-        <v>37.92</v>
+        <v>37.7</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>15.27</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2658,10 +2646,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1067.9</v>
+        <v>1056.8</v>
       </c>
       <c r="D17">
-        <v>0.62</v>
+        <v>-1.04</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2670,46 +2658,46 @@
         <v>1053.2</v>
       </c>
       <c r="G17">
-        <v>-31.39</v>
+        <v>-32.1</v>
       </c>
       <c r="H17">
-        <v>1.4</v>
+        <v>0.34</v>
       </c>
       <c r="I17">
-        <v>-5.95</v>
+        <v>-3.05</v>
       </c>
       <c r="J17">
-        <v>-9.35</v>
+        <v>-9.68</v>
       </c>
       <c r="K17">
-        <v>-17.09</v>
+        <v>-15.7</v>
       </c>
       <c r="L17">
-        <v>-20.85</v>
+        <v>-21.68</v>
       </c>
       <c r="M17">
-        <v>-2.33</v>
+        <v>-3.36</v>
       </c>
       <c r="N17">
         <v>44</v>
       </c>
       <c r="O17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P17">
-        <v>1068.48</v>
+        <v>1061.84</v>
       </c>
       <c r="Q17">
-        <v>1118.78</v>
+        <v>1113.26</v>
       </c>
       <c r="R17">
-        <v>1203.17</v>
+        <v>1197.92</v>
       </c>
       <c r="S17">
-        <v>1326.92</v>
+        <v>1325.32</v>
       </c>
       <c r="T17">
-        <v>-19.52</v>
+        <v>-20.26</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2724,43 +2712,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>35.1</v>
+        <v>33.48</v>
       </c>
       <c r="Z17">
-        <v>-37.69</v>
+        <v>-38.04</v>
       </c>
       <c r="AA17">
-        <v>-35.4</v>
+        <v>-35.93</v>
       </c>
       <c r="AB17">
-        <v>-2.28</v>
+        <v>-2.11</v>
       </c>
       <c r="AC17">
-        <v>29.63</v>
+        <v>35.13</v>
       </c>
       <c r="AD17">
-        <v>28.68</v>
+        <v>29.98</v>
       </c>
       <c r="AE17">
-        <v>30.29</v>
+        <v>29.58</v>
       </c>
       <c r="AF17">
-        <v>300.91</v>
+        <v>-58.62</v>
       </c>
       <c r="AG17">
-        <v>1188.17</v>
+        <v>1183.98</v>
       </c>
       <c r="AH17">
-        <v>1049.39</v>
+        <v>1042.54</v>
       </c>
       <c r="AI17">
-        <v>1151.87</v>
+        <v>1151.25</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>45.08</v>
+        <v>47.21</v>
       </c>
     </row>
   </sheetData>
@@ -2901,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2941,7 +2929,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2959,1702 +2947,1696 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>72</v>
+      <c r="E6" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.55</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.02</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>77</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-1.03</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.37</v>
+        <v>-4.54</v>
       </c>
       <c r="D9" s="6">
-        <v>0.55</v>
+        <v>-4.21</v>
       </c>
       <c r="E9" s="7">
-        <v>0.92</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.79</v>
+        <v>-3.87</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.03</v>
+        <v>-2.45</v>
       </c>
       <c r="E10" s="7">
-        <v>3.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.89</v>
+        <v>-0.86</v>
       </c>
       <c r="D11" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.35</v>
+        <v>-5.5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-4.64</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.61</v>
+        <v>-4.24</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.87</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.26</v>
+        <v>-4.11</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.92</v>
+        <v>-13.6</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.86</v>
+        <v>-13.36</v>
       </c>
       <c r="E13" s="7">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.76</v>
+        <v>-2.16</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.24</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.52</v>
+        <v>-2.9</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-13.97</v>
+        <v>-3.84</v>
       </c>
       <c r="D15" s="6">
-        <v>-13.6</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.37</v>
+        <v>-6.21</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.01</v>
+        <v>-2.99</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.16</v>
+        <v>-6.97</v>
       </c>
       <c r="E16" s="8">
-        <v>-1.15</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.43</v>
+        <v>-9.49</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.84</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="E17" s="8">
-        <v>-0.41</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.11</v>
+        <v>-9.49</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.12</v>
+        <v>-12.81</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-9.949999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.49</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.46</v>
+        <v>1.31</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-9.74</v>
+        <v>-14.66</v>
       </c>
       <c r="D20" s="6">
-        <v>-9.49</v>
+        <v>-14.5</v>
       </c>
       <c r="E20" s="7">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-9.550000000000001</v>
+        <v>-10.08</v>
       </c>
       <c r="D21" s="6">
-        <v>3.21</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="E21" s="7">
-        <v>12.76</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-13.24</v>
+        <v>-9.35</v>
       </c>
       <c r="D22" s="6">
-        <v>-14.66</v>
+        <v>-9.68</v>
       </c>
       <c r="E22" s="8">
-        <v>-1.42</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-9.66</v>
+        <v>3.52</v>
       </c>
       <c r="D23" s="6">
-        <v>-10.08</v>
+        <v>2.37</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.42</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-7.88</v>
+        <v>0.84</v>
       </c>
       <c r="D24" s="6">
-        <v>-9.35</v>
+        <v>-0.7</v>
       </c>
       <c r="E24" s="8">
-        <v>-1.47</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-0.25</v>
+        <v>0.44</v>
       </c>
       <c r="D25" s="6">
-        <v>3.52</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.77</v>
+        <v>0.04</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-9.359999999999999</v>
+        <v>-3.88</v>
       </c>
       <c r="D26" s="6">
-        <v>0.84</v>
+        <v>-0.66</v>
       </c>
       <c r="E26" s="7">
-        <v>10.2</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-1.61</v>
+        <v>1.6</v>
       </c>
       <c r="D27" s="6">
-        <v>0.44</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.05</v>
+        <v>0.3</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-4.09</v>
+        <v>1.67</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.88</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.21</v>
+        <v>0.08</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>0.64</v>
+        <v>-3.07</v>
       </c>
       <c r="D29" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.96</v>
+        <v>-4.02</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-3</v>
+        <v>-3.15</v>
       </c>
       <c r="D30" s="6">
-        <v>1.67</v>
+        <v>-1.62</v>
       </c>
       <c r="E30" s="7">
-        <v>4.67</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.57</v>
+        <v>-2.83</v>
       </c>
       <c r="D31" s="6">
-        <v>-3.07</v>
+        <v>-3.86</v>
       </c>
       <c r="E31" s="8">
-        <v>-0.5</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-4.58</v>
+        <v>-4.08</v>
       </c>
       <c r="D32" s="6">
-        <v>-3.15</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.43</v>
+        <v>-6.57</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-4.35</v>
+        <v>1.41</v>
       </c>
       <c r="D33" s="6">
-        <v>-2.83</v>
+        <v>2.36</v>
       </c>
       <c r="E33" s="7">
-        <v>1.52</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-5.23</v>
+        <v>-5.59</v>
       </c>
       <c r="D34" s="6">
-        <v>-4.08</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.15</v>
+        <v>-6.37</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>1.56</v>
+        <v>10.66</v>
       </c>
       <c r="D35" s="6">
-        <v>1.41</v>
+        <v>9.69</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.15</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-6.22</v>
+        <v>-5.42</v>
       </c>
       <c r="D36" s="6">
-        <v>-5.59</v>
+        <v>-2.41</v>
       </c>
       <c r="E36" s="7">
-        <v>0.63</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-3.35</v>
+        <v>-5.55</v>
       </c>
       <c r="D37" s="6">
-        <v>10.66</v>
+        <v>-3.33</v>
       </c>
       <c r="E37" s="7">
-        <v>14.01</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-10.03</v>
+        <v>-5.95</v>
       </c>
       <c r="D38" s="6">
-        <v>-5.42</v>
+        <v>-3.05</v>
       </c>
       <c r="E38" s="7">
-        <v>4.61</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.32</v>
+        <v>2.18</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.55</v>
+        <v>1.11</v>
       </c>
       <c r="E39" s="8">
-        <v>-5.23</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C40" s="6">
-        <v>-5.09</v>
+        <v>9.9</v>
       </c>
       <c r="D40" s="6">
-        <v>-5.95</v>
+        <v>6.81</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.86</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>0.1</v>
+        <v>-33.45</v>
       </c>
       <c r="D41" s="6">
-        <v>2.18</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.08</v>
+        <v>-34.48</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>4.79</v>
+        <v>-31.94</v>
       </c>
       <c r="D42" s="6">
-        <v>9.9</v>
-      </c>
-      <c r="E42" s="7">
-        <v>5.11</v>
+        <v>-32.52</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-35.84</v>
+        <v>4.25</v>
       </c>
       <c r="D43" s="6">
-        <v>-33.45</v>
-      </c>
-      <c r="E43" s="7">
-        <v>2.39</v>
+        <v>2.88</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-32.26</v>
+        <v>-12.84</v>
       </c>
       <c r="D44" s="6">
-        <v>-31.94</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.32</v>
+        <v>-14.68</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>3.98</v>
+        <v>-39.77</v>
       </c>
       <c r="D45" s="6">
-        <v>4.25</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.27</v>
+        <v>-39.96</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-14.36</v>
+        <v>-39.27</v>
       </c>
       <c r="D46" s="6">
-        <v>-12.84</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.52</v>
+        <v>-41.54</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-40.38</v>
+        <v>-9.52</v>
       </c>
       <c r="D47" s="6">
-        <v>-39.77</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.61</v>
+        <v>-11.76</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-29.33</v>
+        <v>8.06</v>
       </c>
       <c r="D48" s="6">
-        <v>-39.27</v>
+        <v>7.01</v>
       </c>
       <c r="E48" s="8">
-        <v>-9.94</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-9.42</v>
+        <v>-24.69</v>
       </c>
       <c r="D49" s="6">
-        <v>-9.52</v>
+        <v>-26.06</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.1</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>7.59</v>
+        <v>35.14</v>
       </c>
       <c r="D50" s="6">
-        <v>8.06</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.47</v>
+        <v>28.42</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-6.72</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-24.38</v>
+        <v>-37.78</v>
       </c>
       <c r="D51" s="6">
-        <v>-24.69</v>
+        <v>-40.1</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.31</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>34.66</v>
+        <v>-42.2</v>
       </c>
       <c r="D52" s="6">
-        <v>35.14</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.48</v>
+        <v>-43.01</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-45.38</v>
+        <v>-37.88</v>
       </c>
       <c r="D53" s="6">
-        <v>-37.78</v>
-      </c>
-      <c r="E53" s="7">
-        <v>7.6</v>
+        <v>-38.32</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-43.19</v>
+        <v>-20.85</v>
       </c>
       <c r="D54" s="6">
-        <v>-42.2</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.99</v>
+        <v>-21.68</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" s="6">
-        <v>-37.53</v>
+        <v>-1.33</v>
       </c>
       <c r="D55" s="6">
-        <v>-37.88</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.35</v>
+        <v>1.16</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.49</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="6">
-        <v>-22.54</v>
+        <v>1.1</v>
       </c>
       <c r="D56" s="6">
-        <v>-20.85</v>
+        <v>3.33</v>
       </c>
       <c r="E56" s="7">
-        <v>1.69</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>-1.78</v>
+        <v>-13.25</v>
       </c>
       <c r="D57" s="6">
-        <v>-1.33</v>
+        <v>-10.34</v>
       </c>
       <c r="E57" s="7">
-        <v>0.45</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-3.93</v>
+        <v>-14.2</v>
       </c>
       <c r="D58" s="6">
-        <v>1.1</v>
+        <v>-14.16</v>
       </c>
       <c r="E58" s="7">
-        <v>5.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-15.04</v>
+        <v>-11.8</v>
       </c>
       <c r="D59" s="6">
-        <v>-13.25</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.79</v>
+        <v>-12.01</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-11.31</v>
+        <v>-13.24</v>
       </c>
       <c r="D60" s="6">
-        <v>-14.2</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-2.89</v>
+        <v>-11.13</v>
+      </c>
+      <c r="E60" s="7">
+        <v>2.11</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-11.35</v>
+        <v>-16.57</v>
       </c>
       <c r="D61" s="6">
-        <v>-11.8</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.45</v>
+        <v>-14.93</v>
+      </c>
+      <c r="E61" s="7">
+        <v>1.64</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-14.68</v>
+        <v>-6.54</v>
       </c>
       <c r="D62" s="6">
-        <v>-13.24</v>
-      </c>
-      <c r="E62" s="7">
-        <v>1.44</v>
+        <v>-7.22</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-15.13</v>
+        <v>-6.77</v>
       </c>
       <c r="D63" s="6">
-        <v>-16.57</v>
+        <v>-7.24</v>
       </c>
       <c r="E63" s="8">
-        <v>-1.44</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-6.4</v>
+        <v>-5.85</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.54</v>
+        <v>-6.67</v>
       </c>
       <c r="E64" s="8">
-        <v>-0.14</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-6.9</v>
+        <v>0.19</v>
       </c>
       <c r="D65" s="6">
-        <v>-6.77</v>
+        <v>1.11</v>
       </c>
       <c r="E65" s="7">
-        <v>0.13</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-6.67</v>
+        <v>-1.18</v>
       </c>
       <c r="D66" s="6">
-        <v>-5.85</v>
-      </c>
-      <c r="E66" s="7">
-        <v>0.82</v>
+        <v>-4.57</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>2.76</v>
+        <v>-0.74</v>
       </c>
       <c r="D67" s="6">
-        <v>0.19</v>
+        <v>-1.15</v>
       </c>
       <c r="E67" s="8">
-        <v>-2.57</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>2.13</v>
+        <v>-16.13</v>
       </c>
       <c r="D68" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-3.31</v>
+        <v>-12.41</v>
+      </c>
+      <c r="E68" s="7">
+        <v>3.72</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-22.84</v>
+        <v>-17.86</v>
       </c>
       <c r="D69" s="6">
-        <v>-0.74</v>
+        <v>-15.67</v>
       </c>
       <c r="E69" s="7">
-        <v>22.1</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-17.03</v>
+        <v>-17.09</v>
       </c>
       <c r="D70" s="6">
-        <v>-16.13</v>
+        <v>-15.7</v>
       </c>
       <c r="E70" s="7">
-        <v>0.9</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6">
-        <v>-18.75</v>
+        <v>-2.17</v>
       </c>
       <c r="D71" s="6">
-        <v>-17.86</v>
-      </c>
-      <c r="E71" s="7">
-        <v>0.89</v>
+        <v>-2.79</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-17.38</v>
+        <v>-14.55</v>
       </c>
       <c r="D72" s="6">
-        <v>-17.09</v>
-      </c>
-      <c r="E72" s="7">
-        <v>0.29</v>
+        <v>-15.32</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-3.63</v>
+        <v>-34.92</v>
       </c>
       <c r="D73" s="6">
-        <v>-2.17</v>
-      </c>
-      <c r="E73" s="7">
-        <v>1.46</v>
+        <v>-35</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-18.16</v>
+        <v>-32.45</v>
       </c>
       <c r="D74" s="6">
-        <v>-14.55</v>
-      </c>
-      <c r="E74" s="7">
-        <v>3.61</v>
+        <v>-33.19</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-35.94</v>
+        <v>-18.43</v>
       </c>
       <c r="D75" s="6">
-        <v>-34.92</v>
-      </c>
-      <c r="E75" s="7">
-        <v>1.02</v>
+        <v>-19.5</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-32.36</v>
+        <v>-22.56</v>
       </c>
       <c r="D76" s="6">
-        <v>-32.45</v>
+        <v>-23.16</v>
       </c>
       <c r="E76" s="8">
-        <v>-0.09</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-18.65</v>
+        <v>-46.21</v>
       </c>
       <c r="D77" s="6">
-        <v>-18.43</v>
-      </c>
-      <c r="E77" s="7">
-        <v>0.22</v>
+        <v>-46.39</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-24.33</v>
+        <v>-40.7</v>
       </c>
       <c r="D78" s="6">
-        <v>-22.56</v>
+        <v>-40.24</v>
       </c>
       <c r="E78" s="7">
-        <v>1.77</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-46</v>
+        <v>-23.85</v>
       </c>
       <c r="D79" s="6">
-        <v>-46.21</v>
+        <v>-25.26</v>
       </c>
       <c r="E79" s="8">
-        <v>-0.21</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-40.93</v>
+        <v>-17.53</v>
       </c>
       <c r="D80" s="6">
-        <v>-40.7</v>
-      </c>
-      <c r="E80" s="7">
-        <v>0.23</v>
+        <v>-18.93</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-23.88</v>
+        <v>-34.82</v>
       </c>
       <c r="D81" s="6">
-        <v>-23.85</v>
-      </c>
-      <c r="E81" s="7">
-        <v>0.03</v>
+        <v>-35.43</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-17.78</v>
+        <v>-11.98</v>
       </c>
       <c r="D82" s="6">
-        <v>-17.53</v>
-      </c>
-      <c r="E82" s="7">
-        <v>0.25</v>
+        <v>-15.33</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-34.37</v>
+        <v>-39.77</v>
       </c>
       <c r="D83" s="6">
-        <v>-34.82</v>
+        <v>-39.89</v>
       </c>
       <c r="E83" s="8">
-        <v>-0.45</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-11.4</v>
+        <v>-48.43</v>
       </c>
       <c r="D84" s="6">
-        <v>-11.98</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.58</v>
+        <v>-47.98</v>
+      </c>
+      <c r="E84" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-46.53</v>
+        <v>-41.75</v>
       </c>
       <c r="D85" s="6">
-        <v>-39.77</v>
-      </c>
-      <c r="E85" s="7">
-        <v>6.76</v>
+        <v>-42.04</v>
+      </c>
+      <c r="E85" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-49.03</v>
+        <v>-31.39</v>
       </c>
       <c r="D86" s="6">
-        <v>-48.43</v>
-      </c>
-      <c r="E86" s="7">
-        <v>0.6</v>
+        <v>-32.1</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C87" s="6">
-        <v>-41.5</v>
+        <v>736</v>
       </c>
       <c r="D87" s="6">
-        <v>-41.75</v>
+        <v>731.3</v>
       </c>
       <c r="E87" s="8">
-        <v>-0.25</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>-31.81</v>
+        <v>924.15</v>
       </c>
       <c r="D88" s="6">
-        <v>-31.39</v>
-      </c>
-      <c r="E88" s="7">
-        <v>0.42</v>
+        <v>915.8</v>
+      </c>
+      <c r="E88" s="8">
+        <v>-8.35</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>725</v>
+        <v>200.3</v>
       </c>
       <c r="D89" s="6">
-        <v>736</v>
-      </c>
-      <c r="E89" s="7">
-        <v>11</v>
+        <v>200.03</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>885.1</v>
+        <v>616.55</v>
       </c>
       <c r="D90" s="6">
-        <v>924.15</v>
-      </c>
-      <c r="E90" s="7">
-        <v>39.05</v>
+        <v>609.8</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>197.16</v>
+        <v>1681.8</v>
       </c>
       <c r="D91" s="6">
-        <v>200.3</v>
-      </c>
-      <c r="E91" s="7">
-        <v>3.14</v>
+        <v>1659.6</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-22.2</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>617.4</v>
+        <v>976</v>
       </c>
       <c r="D92" s="6">
-        <v>616.55</v>
+        <v>968.5</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.85</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>1677.2</v>
+        <v>3093</v>
       </c>
       <c r="D93" s="6">
-        <v>1681.8</v>
-      </c>
-      <c r="E93" s="7">
-        <v>4.6</v>
+        <v>3082.5</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>953.75</v>
+        <v>624.15</v>
       </c>
       <c r="D94" s="6">
-        <v>976</v>
-      </c>
-      <c r="E94" s="7">
-        <v>22.25</v>
+        <v>615.3</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-8.85</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>3105</v>
+        <v>351.65</v>
       </c>
       <c r="D95" s="6">
-        <v>3093</v>
+        <v>345.15</v>
       </c>
       <c r="E95" s="8">
-        <v>-12</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>621.75</v>
+        <v>178.69</v>
       </c>
       <c r="D96" s="6">
-        <v>624.15</v>
-      </c>
-      <c r="E96" s="7">
-        <v>2.4</v>
+        <v>175.64</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-3.05</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>351.5</v>
+        <v>2100</v>
       </c>
       <c r="D97" s="6">
-        <v>351.65</v>
-      </c>
-      <c r="E97" s="7">
-        <v>0.15</v>
+        <v>2080.3</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-19.7</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>178.14</v>
+        <v>4550</v>
       </c>
       <c r="D98" s="6">
-        <v>178.69</v>
-      </c>
-      <c r="E98" s="7">
-        <v>0.55</v>
+        <v>4377</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-173</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>2114.4</v>
+        <v>2906</v>
       </c>
       <c r="D99" s="6">
-        <v>2100</v>
+        <v>2890.3</v>
       </c>
       <c r="E99" s="8">
-        <v>-14.4</v>
+        <v>-15.7</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>4580</v>
+        <v>196.3</v>
       </c>
       <c r="D100" s="6">
-        <v>4550</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-30</v>
+        <v>198.02</v>
+      </c>
+      <c r="E100" s="7">
+        <v>1.72</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>2580</v>
+        <v>34.18</v>
       </c>
       <c r="D101" s="6">
-        <v>2906</v>
-      </c>
-      <c r="E101" s="7">
-        <v>326</v>
+        <v>34.01</v>
+      </c>
+      <c r="E101" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>194.02</v>
+        <v>1067.9</v>
       </c>
       <c r="D102" s="6">
-        <v>196.3</v>
-      </c>
-      <c r="E102" s="7">
-        <v>2.28</v>
+        <v>1056.8</v>
+      </c>
+      <c r="E102" s="8">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C103" s="6">
-        <v>34.33</v>
+        <v>26</v>
       </c>
       <c r="D103" s="6">
-        <v>34.18</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-0.15</v>
+        <v>38</v>
+      </c>
+      <c r="E103" s="7">
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C104" s="6">
-        <v>1061.3</v>
+        <v>38</v>
       </c>
       <c r="D104" s="6">
-        <v>1067.9</v>
-      </c>
-      <c r="E104" s="7">
-        <v>6.6</v>
+        <v>26</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-12</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4662,16 +4644,16 @@
         <v>37</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C105" s="6">
-        <v>81</v>
+        <v>54.71</v>
       </c>
       <c r="D105" s="6">
-        <v>87</v>
-      </c>
-      <c r="E105" s="7">
-        <v>6</v>
+        <v>52.47</v>
+      </c>
+      <c r="E105" s="8">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4679,16 +4661,16 @@
         <v>38</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C106" s="6">
-        <v>87</v>
+        <v>46.64</v>
       </c>
       <c r="D106" s="6">
-        <v>93</v>
-      </c>
-      <c r="E106" s="7">
-        <v>6</v>
+        <v>45.35</v>
+      </c>
+      <c r="E106" s="8">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -4696,16 +4678,16 @@
         <v>39</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C107" s="6">
-        <v>32</v>
+        <v>39.56</v>
       </c>
       <c r="D107" s="6">
-        <v>26</v>
+        <v>38.94</v>
       </c>
       <c r="E107" s="8">
-        <v>-6</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -4713,702 +4695,498 @@
         <v>40</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C108" s="6">
-        <v>38</v>
+        <v>41.74</v>
       </c>
       <c r="D108" s="6">
-        <v>32</v>
+        <v>40.28</v>
       </c>
       <c r="E108" s="8">
-        <v>-6</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C109" s="6">
-        <v>56</v>
+        <v>43.9</v>
       </c>
       <c r="D109" s="6">
-        <v>62</v>
-      </c>
-      <c r="E109" s="7">
-        <v>6</v>
+        <v>39.9</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-4</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C110" s="6">
-        <v>19</v>
+        <v>42.63</v>
       </c>
       <c r="D110" s="6">
-        <v>13</v>
+        <v>40.5</v>
       </c>
       <c r="E110" s="8">
-        <v>-6</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C111" s="6">
-        <v>50</v>
+        <v>25.43</v>
       </c>
       <c r="D111" s="6">
-        <v>38</v>
+        <v>24.87</v>
       </c>
       <c r="E111" s="8">
-        <v>-12</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>93</v>
+        <v>41.43</v>
       </c>
       <c r="D112" s="6">
-        <v>81</v>
+        <v>39.08</v>
       </c>
       <c r="E112" s="8">
-        <v>-12</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>62</v>
+        <v>37.1</v>
       </c>
       <c r="D113" s="6">
-        <v>56</v>
+        <v>32.44</v>
       </c>
       <c r="E113" s="8">
-        <v>-6</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>7</v>
+        <v>39.41</v>
       </c>
       <c r="D114" s="6">
-        <v>50</v>
-      </c>
-      <c r="E114" s="7">
-        <v>43</v>
+        <v>35.56</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>13</v>
+        <v>40.95</v>
       </c>
       <c r="D115" s="6">
-        <v>7</v>
+        <v>38.75</v>
       </c>
       <c r="E115" s="8">
-        <v>-6</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>26</v>
+        <v>31.38</v>
       </c>
       <c r="D116" s="6">
-        <v>19</v>
+        <v>25.32</v>
       </c>
       <c r="E116" s="8">
-        <v>-7</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>50.07</v>
+        <v>61.04</v>
       </c>
       <c r="D117" s="6">
-        <v>54.71</v>
-      </c>
-      <c r="E117" s="7">
-        <v>4.64</v>
+        <v>59.55</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>39.1</v>
+        <v>28.35</v>
       </c>
       <c r="D118" s="6">
-        <v>46.64</v>
+        <v>31.26</v>
       </c>
       <c r="E118" s="7">
-        <v>7.54</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>26.97</v>
+        <v>38.35</v>
       </c>
       <c r="D119" s="6">
-        <v>39.56</v>
-      </c>
-      <c r="E119" s="7">
-        <v>12.59</v>
+        <v>37.53</v>
+      </c>
+      <c r="E119" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>41.92</v>
+        <v>35.1</v>
       </c>
       <c r="D120" s="6">
-        <v>41.74</v>
+        <v>33.48</v>
       </c>
       <c r="E120" s="8">
-        <v>-0.18</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C121" s="6">
-        <v>42.79</v>
+        <v>-22.34</v>
       </c>
       <c r="D121" s="6">
-        <v>43.9</v>
+        <v>0.17</v>
       </c>
       <c r="E121" s="7">
-        <v>1.11</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C122" s="6">
-        <v>32.92</v>
+        <v>-44.31</v>
       </c>
       <c r="D122" s="6">
-        <v>42.63</v>
-      </c>
-      <c r="E122" s="7">
-        <v>9.710000000000001</v>
+        <v>-60.35</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-16.04</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C123" s="6">
-        <v>26.05</v>
+        <v>-31.31</v>
       </c>
       <c r="D123" s="6">
-        <v>25.43</v>
+        <v>-36.72</v>
       </c>
       <c r="E123" s="8">
-        <v>-0.62</v>
+        <v>-5.41</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C124" s="6">
-        <v>40.53</v>
+        <v>-80.95999999999999</v>
       </c>
       <c r="D124" s="6">
-        <v>41.43</v>
-      </c>
-      <c r="E124" s="7">
-        <v>0.9</v>
+        <v>-87.65000000000001</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-6.69</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C125" s="6">
-        <v>36.91</v>
+        <v>-38.37</v>
       </c>
       <c r="D125" s="6">
-        <v>37.1</v>
+        <v>191.51</v>
       </c>
       <c r="E125" s="7">
-        <v>0.19</v>
+        <v>229.88</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C126" s="6">
-        <v>38.29</v>
+        <v>-29.72</v>
       </c>
       <c r="D126" s="6">
-        <v>39.41</v>
-      </c>
-      <c r="E126" s="7">
-        <v>1.12</v>
+        <v>-58.61</v>
+      </c>
+      <c r="E126" s="8">
+        <v>-28.89</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C127" s="6">
-        <v>42.59</v>
+        <v>-20.07</v>
       </c>
       <c r="D127" s="6">
-        <v>40.95</v>
+        <v>-29.08</v>
       </c>
       <c r="E127" s="8">
-        <v>-1.64</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>32.64</v>
+        <v>-85.61</v>
       </c>
       <c r="D128" s="6">
-        <v>31.38</v>
+        <v>-90.52</v>
       </c>
       <c r="E128" s="8">
-        <v>-1.26</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>24.71</v>
+        <v>50.5</v>
       </c>
       <c r="D129" s="6">
-        <v>61.04</v>
-      </c>
-      <c r="E129" s="7">
-        <v>36.33</v>
+        <v>37.04</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-13.46</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>24.4</v>
+        <v>-36.22</v>
       </c>
       <c r="D130" s="6">
-        <v>28.35</v>
+        <v>-29.73</v>
       </c>
       <c r="E130" s="7">
-        <v>3.95</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>39.05</v>
+        <v>-26.73</v>
       </c>
       <c r="D131" s="6">
-        <v>38.35</v>
+        <v>-58.8</v>
       </c>
       <c r="E131" s="8">
-        <v>-0.7</v>
+        <v>-32.07</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>33.32</v>
+        <v>27.36</v>
       </c>
       <c r="D132" s="6">
-        <v>35.1</v>
+        <v>361.77</v>
       </c>
       <c r="E132" s="7">
-        <v>1.78</v>
+        <v>334.41</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>20.36</v>
+        <v>808.73</v>
       </c>
       <c r="D133" s="6">
-        <v>-22.34</v>
+        <v>27.88</v>
       </c>
       <c r="E133" s="8">
-        <v>-42.7</v>
+        <v>-780.85</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-62.01</v>
+        <v>-57.01</v>
       </c>
       <c r="D134" s="6">
-        <v>-44.31</v>
-      </c>
-      <c r="E134" s="7">
-        <v>17.7</v>
+        <v>-60.73</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-3.72</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>-44.03</v>
+        <v>-79.73999999999999</v>
       </c>
       <c r="D135" s="6">
-        <v>-31.31</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="E135" s="7">
-        <v>12.72</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-73.64</v>
+        <v>300.91</v>
       </c>
       <c r="D136" s="6">
-        <v>-80.95999999999999</v>
+        <v>-58.62</v>
       </c>
       <c r="E136" s="8">
-        <v>-7.32</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C137" s="6">
-        <v>-62.42</v>
-      </c>
-      <c r="D137" s="6">
-        <v>-38.37</v>
-      </c>
-      <c r="E137" s="7">
-        <v>24.05</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C138" s="6">
-        <v>21.9</v>
-      </c>
-      <c r="D138" s="6">
-        <v>-29.72</v>
-      </c>
-      <c r="E138" s="8">
-        <v>-51.62</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C139" s="6">
-        <v>-2.51</v>
-      </c>
-      <c r="D139" s="6">
-        <v>-20.07</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-17.56</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C140" s="6">
-        <v>-88.94</v>
-      </c>
-      <c r="D140" s="6">
-        <v>-85.61</v>
-      </c>
-      <c r="E140" s="7">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C141" s="6">
-        <v>-35.24</v>
-      </c>
-      <c r="D141" s="6">
-        <v>50.5</v>
-      </c>
-      <c r="E141" s="7">
-        <v>85.73999999999999</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C142" s="6">
-        <v>-24.34</v>
-      </c>
-      <c r="D142" s="6">
-        <v>-36.22</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-11.88</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C143" s="6">
-        <v>68.94</v>
-      </c>
-      <c r="D143" s="6">
-        <v>-26.73</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-95.67</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C144" s="6">
-        <v>15.81</v>
-      </c>
-      <c r="D144" s="6">
-        <v>27.36</v>
-      </c>
-      <c r="E144" s="7">
-        <v>11.55</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C145" s="6">
-        <v>8.41</v>
-      </c>
-      <c r="D145" s="6">
-        <v>808.73</v>
-      </c>
-      <c r="E145" s="7">
-        <v>800.3200000000001</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C146" s="6">
-        <v>7.48</v>
-      </c>
-      <c r="D146" s="6">
-        <v>-57.01</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-64.48999999999999</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C147" s="6">
-        <v>-63.47</v>
-      </c>
-      <c r="D147" s="6">
-        <v>-79.73999999999999</v>
-      </c>
-      <c r="E147" s="8">
-        <v>-16.27</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C148" s="6">
-        <v>-41.69</v>
-      </c>
-      <c r="D148" s="6">
-        <v>300.91</v>
-      </c>
-      <c r="E148" s="7">
-        <v>342.6</v>
+        <v>-359.53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5432,28 +5210,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5467,16 +5245,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.800000000000001</v>
+        <v>-8</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5593,19 +5371,19 @@
         <v>49</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>46</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>41</v>
@@ -5616,34 +5394,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3606</v>
+        <v>0.3521</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3287</v>
+        <v>0.3119</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2282</v>
+        <v>0.2123</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1651</v>
+        <v>0.1483</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1549</v>
+        <v>0.133</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1012</v>
+        <v>0.0958</v>
       </c>
       <c r="G2" s="14">
-        <v>0.047</v>
+        <v>0.0413</v>
       </c>
       <c r="H2" s="14">
-        <v>0.04389999999999999</v>
+        <v>0.0389</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0385</v>
+        <v>0.0367</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0133</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5668,22 +5446,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.0233</v>
+        <v>-0.0336</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0295</v>
+        <v>-0.0397</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0617</v>
+        <v>-0.0625</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.07200000000000001</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.08800000000000001</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1198</v>
+        <v>-0.1256</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,19 +214,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.4 → 31.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.4</t>
-  </si>
-  <si>
-    <t>31.3</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.5 → 44.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.5</t>
+  </si>
+  <si>
+    <t>44.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -312,14 +312,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,13 +352,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -951,10 +951,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>731.3</v>
+        <v>711.65</v>
       </c>
       <c r="D2">
-        <v>-0.64</v>
+        <v>-2.69</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -963,46 +963,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-2.79</v>
+        <v>-5.4</v>
       </c>
       <c r="H2">
-        <v>28.08</v>
+        <v>24.64</v>
       </c>
       <c r="I2">
-        <v>2.37</v>
+        <v>-2.33</v>
       </c>
       <c r="J2">
-        <v>1.57</v>
+        <v>-0.64</v>
       </c>
       <c r="K2">
-        <v>1.16</v>
+        <v>-2.71</v>
       </c>
       <c r="L2">
-        <v>1.11</v>
+        <v>-1.77</v>
       </c>
       <c r="M2">
-        <v>31.19</v>
+        <v>29.63</v>
       </c>
       <c r="N2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="O2">
         <v>64</v>
       </c>
       <c r="P2">
-        <v>727.79</v>
+        <v>724.39</v>
       </c>
       <c r="Q2">
-        <v>725.48</v>
+        <v>725.0700000000001</v>
       </c>
       <c r="R2">
-        <v>727.67</v>
+        <v>727.21</v>
       </c>
       <c r="S2">
-        <v>688.26</v>
+        <v>688.21</v>
       </c>
       <c r="T2">
-        <v>6.25</v>
+        <v>3.41</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1017,34 +1017,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>52.47</v>
+        <v>44.29</v>
       </c>
       <c r="Z2">
-        <v>0.78</v>
+        <v>-0.49</v>
       </c>
       <c r="AA2">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="AB2">
-        <v>0.55</v>
+        <v>-0.58</v>
       </c>
       <c r="AC2">
-        <v>53.45</v>
+        <v>42.67</v>
       </c>
       <c r="AD2">
-        <v>44.51</v>
+        <v>46.37</v>
       </c>
       <c r="AE2">
-        <v>15.99</v>
+        <v>16.42</v>
       </c>
       <c r="AF2">
-        <v>0.17</v>
+        <v>-28.91</v>
       </c>
       <c r="AG2">
-        <v>745.36</v>
+        <v>745.76</v>
       </c>
       <c r="AH2">
-        <v>705.6</v>
+        <v>704.37</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1053,7 +1053,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>18.84</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1064,10 +1064,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>915.8</v>
+        <v>865</v>
       </c>
       <c r="D3">
-        <v>-0.9</v>
+        <v>-5.55</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1076,46 +1076,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-15.32</v>
+        <v>-20.02</v>
       </c>
       <c r="H3">
-        <v>81.22</v>
+        <v>71.17</v>
       </c>
       <c r="I3">
-        <v>-0.7</v>
+        <v>-5.41</v>
       </c>
       <c r="J3">
-        <v>0.5</v>
+        <v>-7.31</v>
       </c>
       <c r="K3">
-        <v>3.33</v>
+        <v>-3.48</v>
       </c>
       <c r="L3">
-        <v>6.81</v>
+        <v>-4.43</v>
       </c>
       <c r="M3">
-        <v>2.19</v>
+        <v>0.05</v>
       </c>
       <c r="N3">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P3">
-        <v>905.75</v>
+        <v>895.85</v>
       </c>
       <c r="Q3">
-        <v>950.58</v>
+        <v>945.17</v>
       </c>
       <c r="R3">
-        <v>957.28</v>
+        <v>955.33</v>
       </c>
       <c r="S3">
-        <v>768.3200000000001</v>
+        <v>769.0599999999999</v>
       </c>
       <c r="T3">
-        <v>19.2</v>
+        <v>12.47</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1130,43 +1130,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.35</v>
+        <v>38.38</v>
       </c>
       <c r="Z3">
-        <v>-10.88</v>
+        <v>-15.32</v>
       </c>
       <c r="AA3">
-        <v>-3.24</v>
+        <v>-5.66</v>
       </c>
       <c r="AB3">
-        <v>-7.63</v>
+        <v>-9.66</v>
       </c>
       <c r="AC3">
         <v>21.39</v>
       </c>
       <c r="AD3">
-        <v>11.03</v>
+        <v>18.16</v>
       </c>
       <c r="AE3">
-        <v>42.6</v>
+        <v>43.54</v>
       </c>
       <c r="AF3">
-        <v>-60.35</v>
+        <v>-35.54</v>
       </c>
       <c r="AG3">
-        <v>1031.64</v>
+        <v>1033.96</v>
       </c>
       <c r="AH3">
-        <v>869.51</v>
+        <v>856.38</v>
       </c>
       <c r="AI3">
-        <v>1028.89</v>
+        <v>1018.42</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>27.07</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,58 +1177,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>200.03</v>
+        <v>195.76</v>
       </c>
       <c r="D4">
-        <v>-0.13</v>
+        <v>-2.13</v>
       </c>
       <c r="E4">
-        <v>307.76</v>
+        <v>304.6</v>
       </c>
       <c r="F4">
-        <v>197.16</v>
+        <v>195.76</v>
       </c>
       <c r="G4">
-        <v>-35</v>
+        <v>-35.73</v>
       </c>
       <c r="H4">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.04</v>
+        <v>-1.99</v>
       </c>
       <c r="J4">
-        <v>-4.21</v>
+        <v>-5.04</v>
       </c>
       <c r="K4">
-        <v>-10.34</v>
+        <v>-12.38</v>
       </c>
       <c r="L4">
-        <v>-34.48</v>
+        <v>-36.39</v>
       </c>
       <c r="M4">
-        <v>-6.25</v>
+        <v>-7.67</v>
       </c>
       <c r="N4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>199.38</v>
+        <v>198.59</v>
       </c>
       <c r="Q4">
-        <v>201.48</v>
+        <v>201</v>
       </c>
       <c r="R4">
-        <v>208.13</v>
+        <v>207.73</v>
       </c>
       <c r="S4">
-        <v>239.2</v>
+        <v>238.87</v>
       </c>
       <c r="T4">
-        <v>-16.38</v>
+        <v>-18.05</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1243,43 +1243,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.94</v>
+        <v>30.72</v>
       </c>
       <c r="Z4">
-        <v>-2.81</v>
+        <v>-2.98</v>
       </c>
       <c r="AA4">
-        <v>-3.11</v>
+        <v>-3.08</v>
       </c>
       <c r="AB4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AC4">
-        <v>65.65000000000001</v>
+        <v>74.94</v>
       </c>
       <c r="AD4">
-        <v>49.14</v>
+        <v>63.4</v>
       </c>
       <c r="AE4">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="AF4">
-        <v>-36.72</v>
+        <v>6.04</v>
       </c>
       <c r="AG4">
-        <v>205.51</v>
+        <v>205.37</v>
       </c>
       <c r="AH4">
-        <v>197.44</v>
+        <v>196.62</v>
       </c>
       <c r="AI4">
-        <v>210.35</v>
+        <v>208.92</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>32.84</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1290,10 +1290,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>609.8</v>
+        <v>592.95</v>
       </c>
       <c r="D5">
-        <v>-1.09</v>
+        <v>-2.76</v>
       </c>
       <c r="E5">
         <v>912.72</v>
@@ -1302,46 +1302,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-33.19</v>
+        <v>-35.03</v>
       </c>
       <c r="H5">
-        <v>6.16</v>
+        <v>3.23</v>
       </c>
       <c r="I5">
-        <v>-0.66</v>
+        <v>-3.03</v>
       </c>
       <c r="J5">
-        <v>-2.45</v>
+        <v>-3.33</v>
       </c>
       <c r="K5">
-        <v>-14.16</v>
+        <v>-16.92</v>
       </c>
       <c r="L5">
-        <v>-32.52</v>
+        <v>-34.95</v>
       </c>
       <c r="M5">
-        <v>-7.34</v>
+        <v>-7.98</v>
       </c>
       <c r="N5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P5">
-        <v>612.6</v>
+        <v>608.9</v>
       </c>
       <c r="Q5">
-        <v>651.29</v>
+        <v>650.5599999999999</v>
       </c>
       <c r="R5">
-        <v>652.5</v>
+        <v>650.87</v>
       </c>
       <c r="S5">
-        <v>696.77</v>
+        <v>696.04</v>
       </c>
       <c r="T5">
-        <v>-12.48</v>
+        <v>-14.81</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
@@ -1356,43 +1356,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.28</v>
+        <v>36.83</v>
       </c>
       <c r="Z5">
-        <v>-12.29</v>
+        <v>-14.48</v>
       </c>
       <c r="AA5">
-        <v>-5.79</v>
+        <v>-7.53</v>
       </c>
       <c r="AB5">
-        <v>-6.51</v>
+        <v>-6.96</v>
       </c>
       <c r="AC5">
-        <v>5.56</v>
+        <v>3.17</v>
       </c>
       <c r="AD5">
-        <v>7.86</v>
+        <v>5.52</v>
       </c>
       <c r="AE5">
-        <v>27.9</v>
+        <v>27.54</v>
       </c>
       <c r="AF5">
-        <v>-87.65000000000001</v>
+        <v>-79.47</v>
       </c>
       <c r="AG5">
-        <v>754.78</v>
+        <v>755.55</v>
       </c>
       <c r="AH5">
-        <v>547.8</v>
+        <v>545.5599999999999</v>
       </c>
       <c r="AI5">
-        <v>697.49</v>
+        <v>685.0700000000001</v>
       </c>
       <c r="AJ5" t="s">
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>14.45</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1403,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1659.6</v>
+        <v>1677.4</v>
       </c>
       <c r="D6">
-        <v>-1.32</v>
+        <v>1.07</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1415,46 +1415,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-19.5</v>
+        <v>-18.64</v>
       </c>
       <c r="H6">
-        <v>23.12</v>
+        <v>24.45</v>
       </c>
       <c r="I6">
-        <v>0.3</v>
+        <v>1.28</v>
       </c>
       <c r="J6">
-        <v>-5.5</v>
+        <v>-3.51</v>
       </c>
       <c r="K6">
-        <v>-12.01</v>
+        <v>-10.32</v>
       </c>
       <c r="L6">
-        <v>2.88</v>
+        <v>3.94</v>
       </c>
       <c r="M6">
-        <v>3.67</v>
+        <v>4.07</v>
       </c>
       <c r="N6">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="O6">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="P6">
-        <v>1671.56</v>
+        <v>1675.8</v>
       </c>
       <c r="Q6">
-        <v>1715.04</v>
+        <v>1711.27</v>
       </c>
       <c r="R6">
-        <v>1720.92</v>
+        <v>1719.18</v>
       </c>
       <c r="S6">
-        <v>1703.77</v>
+        <v>1703.2</v>
       </c>
       <c r="T6">
-        <v>-2.59</v>
+        <v>-1.51</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1469,34 +1469,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39.9</v>
+        <v>44.28</v>
       </c>
       <c r="Z6">
-        <v>-20.02</v>
+        <v>-19.07</v>
       </c>
       <c r="AA6">
-        <v>-16.01</v>
+        <v>-16.63</v>
       </c>
       <c r="AB6">
-        <v>-4</v>
+        <v>-2.45</v>
       </c>
       <c r="AC6">
-        <v>22.9</v>
+        <v>27.29</v>
       </c>
       <c r="AD6">
-        <v>23.38</v>
+        <v>26.19</v>
       </c>
       <c r="AE6">
-        <v>47.98</v>
+        <v>49.31</v>
       </c>
       <c r="AF6">
-        <v>191.51</v>
+        <v>127.64</v>
       </c>
       <c r="AG6">
-        <v>1818.03</v>
+        <v>1813.96</v>
       </c>
       <c r="AH6">
-        <v>1612.05</v>
+        <v>1608.58</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1505,7 +1505,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>27.26</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1516,10 +1516,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>968.5</v>
+        <v>951.9</v>
       </c>
       <c r="D7">
-        <v>-0.77</v>
+        <v>-1.71</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1528,46 +1528,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-23.16</v>
+        <v>-24.47</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="I7">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="J7">
-        <v>-4.11</v>
+        <v>-6.22</v>
       </c>
       <c r="K7">
-        <v>-11.13</v>
+        <v>-13.99</v>
       </c>
       <c r="L7">
-        <v>-14.68</v>
+        <v>-15.61</v>
       </c>
       <c r="M7">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="N7">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P7">
-        <v>960.95</v>
+        <v>961.4299999999999</v>
       </c>
       <c r="Q7">
-        <v>984.13</v>
+        <v>981.02</v>
       </c>
       <c r="R7">
-        <v>1032.23</v>
+        <v>1029.63</v>
       </c>
       <c r="S7">
-        <v>1105.96</v>
+        <v>1104.91</v>
       </c>
       <c r="T7">
-        <v>-12.43</v>
+        <v>-13.85</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1582,34 +1582,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>40.5</v>
+        <v>36.19</v>
       </c>
       <c r="Z7">
-        <v>-19.92</v>
+        <v>-20.18</v>
       </c>
       <c r="AA7">
-        <v>-20.84</v>
+        <v>-20.71</v>
       </c>
       <c r="AB7">
-        <v>0.92</v>
+        <v>0.53</v>
       </c>
       <c r="AC7">
-        <v>72.18000000000001</v>
+        <v>77.08</v>
       </c>
       <c r="AD7">
-        <v>52.92</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="AE7">
-        <v>18.56</v>
+        <v>19.14</v>
       </c>
       <c r="AF7">
-        <v>-58.61</v>
+        <v>-30.77</v>
       </c>
       <c r="AG7">
-        <v>1022.91</v>
+        <v>1019.66</v>
       </c>
       <c r="AH7">
-        <v>945.34</v>
+        <v>942.38</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1618,7 +1618,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>53.13</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,58 +1629,58 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3082.5</v>
+        <v>2996</v>
       </c>
       <c r="D8">
-        <v>-0.34</v>
+        <v>-2.81</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
       </c>
       <c r="F8">
-        <v>3082.5</v>
+        <v>2996</v>
       </c>
       <c r="G8">
-        <v>-46.39</v>
+        <v>-47.89</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.02</v>
+        <v>-3.01</v>
       </c>
       <c r="J8">
-        <v>-13.36</v>
+        <v>-14.33</v>
       </c>
       <c r="K8">
-        <v>-14.93</v>
+        <v>-17.27</v>
       </c>
       <c r="L8">
-        <v>-39.96</v>
+        <v>-43.05</v>
       </c>
       <c r="M8">
-        <v>-12.56</v>
+        <v>-12.73</v>
       </c>
       <c r="N8">
         <v>13</v>
       </c>
       <c r="O8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>3092.44</v>
+        <v>3073.86</v>
       </c>
       <c r="Q8">
-        <v>3254.15</v>
+        <v>3229.35</v>
       </c>
       <c r="R8">
-        <v>3510.21</v>
+        <v>3498.49</v>
       </c>
       <c r="S8">
-        <v>4200.59</v>
+        <v>4190.94</v>
       </c>
       <c r="T8">
-        <v>-26.62</v>
+        <v>-28.51</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1695,43 +1695,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>24.87</v>
+        <v>20.82</v>
       </c>
       <c r="Z8">
-        <v>-125.79</v>
+        <v>-130.57</v>
       </c>
       <c r="AA8">
-        <v>-119.35</v>
+        <v>-121.59</v>
       </c>
       <c r="AB8">
-        <v>-6.45</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AC8">
-        <v>14.14</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>11</v>
+        <v>11.58</v>
       </c>
       <c r="AE8">
-        <v>81.31999999999999</v>
+        <v>85.89</v>
       </c>
       <c r="AF8">
-        <v>-29.08</v>
+        <v>-2.53</v>
       </c>
       <c r="AG8">
-        <v>3517.4</v>
+        <v>3491.71</v>
       </c>
       <c r="AH8">
-        <v>2990.91</v>
+        <v>2967</v>
       </c>
       <c r="AI8">
-        <v>3348.63</v>
+        <v>3326.38</v>
       </c>
       <c r="AJ8" t="s">
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>59.4</v>
+        <v>61.26</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1742,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>615.3</v>
+        <v>609.3</v>
       </c>
       <c r="D9">
-        <v>-1.42</v>
+        <v>-0.98</v>
       </c>
       <c r="E9">
         <v>1029.69</v>
@@ -1754,46 +1754,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-40.24</v>
+        <v>-40.83</v>
       </c>
       <c r="H9">
-        <v>14.29</v>
+        <v>13.17</v>
       </c>
       <c r="I9">
-        <v>-1.62</v>
+        <v>-1.73</v>
       </c>
       <c r="J9">
-        <v>-2.9</v>
+        <v>-2.95</v>
       </c>
       <c r="K9">
-        <v>-7.22</v>
+        <v>-11.03</v>
       </c>
       <c r="L9">
-        <v>-41.54</v>
+        <v>-38.77</v>
       </c>
       <c r="M9">
-        <v>35.21</v>
+        <v>34.9</v>
       </c>
       <c r="N9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P9">
-        <v>619.26</v>
+        <v>617.11</v>
       </c>
       <c r="Q9">
-        <v>653.6</v>
+        <v>652.96</v>
       </c>
       <c r="R9">
-        <v>656.3099999999999</v>
+        <v>655.41</v>
       </c>
       <c r="S9">
-        <v>659.52</v>
+        <v>659.0700000000001</v>
       </c>
       <c r="T9">
-        <v>-6.7</v>
+        <v>-7.55</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1808,43 +1808,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.08</v>
+        <v>37.53</v>
       </c>
       <c r="Z9">
-        <v>-10.18</v>
+        <v>-11.58</v>
       </c>
       <c r="AA9">
-        <v>-4.26</v>
+        <v>-5.73</v>
       </c>
       <c r="AB9">
-        <v>-5.92</v>
+        <v>-5.86</v>
       </c>
       <c r="AC9">
-        <v>7.6</v>
+        <v>5.24</v>
       </c>
       <c r="AD9">
-        <v>5.44</v>
+        <v>6.41</v>
       </c>
       <c r="AE9">
-        <v>21.98</v>
+        <v>21.23</v>
       </c>
       <c r="AF9">
-        <v>-90.52</v>
+        <v>-77.59</v>
       </c>
       <c r="AG9">
-        <v>722.9</v>
+        <v>723.7</v>
       </c>
       <c r="AH9">
-        <v>584.3</v>
+        <v>582.23</v>
       </c>
       <c r="AI9">
-        <v>682.46</v>
+        <v>675.8</v>
       </c>
       <c r="AJ9" t="s">
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>17.65</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,58 +1855,58 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>345.15</v>
+        <v>335.65</v>
       </c>
       <c r="D10">
-        <v>-1.85</v>
+        <v>-2.75</v>
       </c>
       <c r="E10">
         <v>461.8</v>
       </c>
       <c r="F10">
-        <v>345.15</v>
+        <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-25.26</v>
+        <v>-27.32</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>-3.86</v>
+        <v>-6.5</v>
       </c>
       <c r="J10">
-        <v>-6.21</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K10">
-        <v>-7.24</v>
+        <v>-10.61</v>
       </c>
       <c r="L10">
-        <v>-11.76</v>
+        <v>-15</v>
       </c>
       <c r="M10">
-        <v>14.83</v>
+        <v>14.31</v>
       </c>
       <c r="N10">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P10">
-        <v>351.49</v>
+        <v>346.82</v>
       </c>
       <c r="Q10">
-        <v>362.34</v>
+        <v>360.85</v>
       </c>
       <c r="R10">
-        <v>368.53</v>
+        <v>367.81</v>
       </c>
       <c r="S10">
-        <v>386.15</v>
+        <v>385.96</v>
       </c>
       <c r="T10">
-        <v>-10.62</v>
+        <v>-13.03</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1921,43 +1921,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>32.44</v>
+        <v>27.08</v>
       </c>
       <c r="Z10">
-        <v>-4.94</v>
+        <v>-6.26</v>
       </c>
       <c r="AA10">
-        <v>-3.24</v>
+        <v>-3.84</v>
       </c>
       <c r="AB10">
-        <v>-1.71</v>
+        <v>-2.42</v>
       </c>
       <c r="AC10">
-        <v>5.53</v>
+        <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>5.41</v>
+        <v>4.66</v>
       </c>
       <c r="AE10">
-        <v>7.62</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AF10">
-        <v>37.04</v>
+        <v>62.18</v>
       </c>
       <c r="AG10">
-        <v>377.67</v>
+        <v>380.17</v>
       </c>
       <c r="AH10">
-        <v>347.02</v>
+        <v>341.53</v>
       </c>
       <c r="AI10">
-        <v>368.8</v>
+        <v>365.04</v>
       </c>
       <c r="AJ10" t="s">
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>36.18</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1968,10 +1968,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>175.64</v>
+        <v>171.96</v>
       </c>
       <c r="D11">
-        <v>-1.71</v>
+        <v>-2.1</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1980,46 +1980,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-18.93</v>
+        <v>-20.63</v>
       </c>
       <c r="H11">
-        <v>11.57</v>
+        <v>9.24</v>
       </c>
       <c r="I11">
-        <v>-6.57</v>
+        <v>-6.7</v>
       </c>
       <c r="J11">
-        <v>-6.97</v>
+        <v>-7.35</v>
       </c>
       <c r="K11">
-        <v>-6.67</v>
+        <v>-8.49</v>
       </c>
       <c r="L11">
-        <v>7.01</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
-        <v>9.58</v>
+        <v>8.91</v>
       </c>
       <c r="N11">
         <v>81</v>
       </c>
       <c r="O11">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P11">
-        <v>178.95</v>
+        <v>176.49</v>
       </c>
       <c r="Q11">
-        <v>184.32</v>
+        <v>183.71</v>
       </c>
       <c r="R11">
-        <v>185.7</v>
+        <v>185.49</v>
       </c>
       <c r="S11">
-        <v>192.1</v>
+        <v>192.13</v>
       </c>
       <c r="T11">
-        <v>-8.57</v>
+        <v>-10.5</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2034,43 +2034,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>35.56</v>
+        <v>31.57</v>
       </c>
       <c r="Z11">
-        <v>-1.92</v>
+        <v>-2.58</v>
       </c>
       <c r="AA11">
-        <v>-0.8100000000000001</v>
+        <v>-1.17</v>
       </c>
       <c r="AB11">
-        <v>-1.1</v>
+        <v>-1.41</v>
       </c>
       <c r="AC11">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="AD11">
-        <v>4.03</v>
+        <v>2.57</v>
       </c>
       <c r="AE11">
-        <v>4.68</v>
+        <v>4.77</v>
       </c>
       <c r="AF11">
-        <v>-29.73</v>
+        <v>18.14</v>
       </c>
       <c r="AG11">
-        <v>192.44</v>
+        <v>193.54</v>
       </c>
       <c r="AH11">
-        <v>176.2</v>
+        <v>173.89</v>
       </c>
       <c r="AI11">
-        <v>190.47</v>
+        <v>187.77</v>
       </c>
       <c r="AJ11" t="s">
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>29.57</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2081,10 +2081,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2080.3</v>
+        <v>2076</v>
       </c>
       <c r="D12">
-        <v>-0.9399999999999999</v>
+        <v>-0.21</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2093,46 +2093,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-35.43</v>
+        <v>-35.56</v>
       </c>
       <c r="H12">
-        <v>4.93</v>
+        <v>4.71</v>
       </c>
       <c r="I12">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="J12">
-        <v>-9.710000000000001</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="K12">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="L12">
-        <v>-26.06</v>
+        <v>-25.9</v>
       </c>
       <c r="M12">
-        <v>-9.359999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="N12">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="O12">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P12">
-        <v>2084.06</v>
+        <v>2089.14</v>
       </c>
       <c r="Q12">
-        <v>2130.95</v>
+        <v>2121.97</v>
       </c>
       <c r="R12">
-        <v>2266.47</v>
+        <v>2260.03</v>
       </c>
       <c r="S12">
-        <v>2468.13</v>
+        <v>2462.61</v>
       </c>
       <c r="T12">
-        <v>-15.71</v>
+        <v>-15.7</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2147,34 +2147,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>38.75</v>
+        <v>38.27</v>
       </c>
       <c r="Z12">
-        <v>-52.21</v>
+        <v>-50.39</v>
       </c>
       <c r="AA12">
-        <v>-54.82</v>
+        <v>-53.94</v>
       </c>
       <c r="AB12">
-        <v>2.61</v>
+        <v>3.54</v>
       </c>
       <c r="AC12">
-        <v>81.98999999999999</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="AD12">
-        <v>68.31999999999999</v>
+        <v>77.41</v>
       </c>
       <c r="AE12">
-        <v>56.04</v>
+        <v>57.86</v>
       </c>
       <c r="AF12">
-        <v>-58.8</v>
+        <v>33.34</v>
       </c>
       <c r="AG12">
-        <v>2266.31</v>
+        <v>2245.88</v>
       </c>
       <c r="AH12">
-        <v>1995.58</v>
+        <v>1998.06</v>
       </c>
       <c r="AI12">
         <v>2235.3</v>
@@ -2183,7 +2183,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>32.13</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2194,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4377</v>
+        <v>4359.5</v>
       </c>
       <c r="D13">
-        <v>-3.8</v>
+        <v>-0.4</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2206,46 +2206,46 @@
         <v>3418.2</v>
       </c>
       <c r="G13">
-        <v>-15.33</v>
+        <v>-15.66</v>
       </c>
       <c r="H13">
-        <v>28.05</v>
+        <v>27.54</v>
       </c>
       <c r="I13">
-        <v>-6.37</v>
+        <v>-4.96</v>
       </c>
       <c r="J13">
-        <v>-12.81</v>
+        <v>-12.72</v>
       </c>
       <c r="K13">
-        <v>-4.57</v>
+        <v>-4.31</v>
       </c>
       <c r="L13">
-        <v>28.42</v>
+        <v>26.24</v>
       </c>
       <c r="M13">
-        <v>13.3</v>
+        <v>13.37</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P13">
-        <v>4521.94</v>
+        <v>4476.44</v>
       </c>
       <c r="Q13">
-        <v>4796.54</v>
+        <v>4765.16</v>
       </c>
       <c r="R13">
-        <v>4935.73</v>
+        <v>4925.93</v>
       </c>
       <c r="S13">
-        <v>4417.27</v>
+        <v>4419.48</v>
       </c>
       <c r="T13">
-        <v>-0.91</v>
+        <v>-1.36</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2260,34 +2260,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>25.32</v>
+        <v>24.8</v>
       </c>
       <c r="Z13">
-        <v>-123.19</v>
+        <v>-138.05</v>
       </c>
       <c r="AA13">
-        <v>-76.26000000000001</v>
+        <v>-88.62</v>
       </c>
       <c r="AB13">
-        <v>-46.93</v>
+        <v>-49.44</v>
       </c>
       <c r="AC13">
-        <v>16.51</v>
+        <v>7.26</v>
       </c>
       <c r="AD13">
-        <v>14.09</v>
+        <v>13.43</v>
       </c>
       <c r="AE13">
-        <v>100.38</v>
+        <v>100.89</v>
       </c>
       <c r="AF13">
-        <v>361.77</v>
+        <v>94.87</v>
       </c>
       <c r="AG13">
-        <v>5167.81</v>
+        <v>5172.92</v>
       </c>
       <c r="AH13">
-        <v>4425.26</v>
+        <v>4357.4</v>
       </c>
       <c r="AI13">
         <v>4688.95</v>
@@ -2296,7 +2296,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>59.14</v>
+        <v>61.17</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2307,58 +2307,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2890.3</v>
+        <v>2876.3</v>
       </c>
       <c r="D14">
-        <v>-0.54</v>
+        <v>-0.48</v>
       </c>
       <c r="E14">
-        <v>4808.59</v>
+        <v>4807.3</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-39.89</v>
+        <v>-40.17</v>
       </c>
       <c r="H14">
-        <v>31.74</v>
+        <v>31.1</v>
       </c>
       <c r="I14">
-        <v>9.69</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J14">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="K14">
-        <v>-1.15</v>
+        <v>-0.96</v>
       </c>
       <c r="L14">
-        <v>-40.1</v>
+        <v>-40.18</v>
       </c>
       <c r="M14">
-        <v>21.23</v>
+        <v>21.24</v>
       </c>
       <c r="N14">
         <v>50</v>
       </c>
       <c r="O14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="P14">
-        <v>2715.58</v>
+        <v>2766.52</v>
       </c>
       <c r="Q14">
-        <v>2746.4</v>
+        <v>2750.53</v>
       </c>
       <c r="R14">
-        <v>2871.3</v>
+        <v>2870.21</v>
       </c>
       <c r="S14">
-        <v>2837.35</v>
+        <v>2831.61</v>
       </c>
       <c r="T14">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2373,43 +2373,43 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>59.55</v>
+        <v>58.18</v>
       </c>
       <c r="Z14">
-        <v>-34.75</v>
+        <v>-21.19</v>
       </c>
       <c r="AA14">
-        <v>-55.03</v>
+        <v>-48.26</v>
       </c>
       <c r="AB14">
-        <v>20.28</v>
+        <v>27.07</v>
       </c>
       <c r="AC14">
-        <v>65.3</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="AD14">
-        <v>33.27</v>
+        <v>64.88</v>
       </c>
       <c r="AE14">
-        <v>75.3</v>
+        <v>74.77</v>
       </c>
       <c r="AF14">
-        <v>27.88</v>
+        <v>26.51</v>
       </c>
       <c r="AG14">
-        <v>2943.04</v>
+        <v>2954.68</v>
       </c>
       <c r="AH14">
-        <v>2549.76</v>
+        <v>2546.39</v>
       </c>
       <c r="AI14">
-        <v>2666.99</v>
+        <v>2677.8</v>
       </c>
       <c r="AJ14" t="s">
         <v>56</v>
       </c>
       <c r="AK14">
-        <v>52.97</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2420,37 +2420,37 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>198.02</v>
+        <v>191.78</v>
       </c>
       <c r="D15">
-        <v>0.88</v>
+        <v>-3.15</v>
       </c>
       <c r="E15">
-        <v>380.65</v>
+        <v>367.5</v>
       </c>
       <c r="F15">
-        <v>192.33</v>
+        <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-47.98</v>
+        <v>-47.81</v>
       </c>
       <c r="H15">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>-2.41</v>
+        <v>-3.05</v>
       </c>
       <c r="J15">
-        <v>-14.5</v>
+        <v>-18.44</v>
       </c>
       <c r="K15">
-        <v>-12.41</v>
+        <v>-17.76</v>
       </c>
       <c r="L15">
-        <v>-43.01</v>
+        <v>-49.62</v>
       </c>
       <c r="M15">
-        <v>3.89</v>
+        <v>2.78</v>
       </c>
       <c r="N15">
         <v>7</v>
@@ -2459,19 +2459,19 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>195.7</v>
+        <v>194.49</v>
       </c>
       <c r="Q15">
-        <v>211.64</v>
+        <v>209.68</v>
       </c>
       <c r="R15">
-        <v>222.64</v>
+        <v>221.92</v>
       </c>
       <c r="S15">
-        <v>247.43</v>
+        <v>246.87</v>
       </c>
       <c r="T15">
-        <v>-19.97</v>
+        <v>-22.32</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2486,43 +2486,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>31.26</v>
+        <v>26.97</v>
       </c>
       <c r="Z15">
-        <v>-8.300000000000001</v>
+        <v>-8.66</v>
       </c>
       <c r="AA15">
-        <v>-6.7</v>
+        <v>-7.09</v>
       </c>
       <c r="AB15">
-        <v>-1.6</v>
+        <v>-1.57</v>
       </c>
       <c r="AC15">
-        <v>33.2</v>
+        <v>38.63</v>
       </c>
       <c r="AD15">
-        <v>18.29</v>
+        <v>29.49</v>
       </c>
       <c r="AE15">
-        <v>7.82</v>
+        <v>7.87</v>
       </c>
       <c r="AF15">
-        <v>-60.73</v>
+        <v>-2.64</v>
       </c>
       <c r="AG15">
-        <v>234.23</v>
+        <v>232.01</v>
       </c>
       <c r="AH15">
-        <v>189.06</v>
+        <v>187.36</v>
       </c>
       <c r="AI15">
-        <v>219.48</v>
+        <v>218.86</v>
       </c>
       <c r="AJ15" t="s">
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>41.22</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2533,10 +2533,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>34.01</v>
+        <v>32.95</v>
       </c>
       <c r="D16">
-        <v>-0.5</v>
+        <v>-3.12</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2545,46 +2545,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-42.04</v>
+        <v>-43.85</v>
       </c>
       <c r="H16">
-        <v>8.449999999999999</v>
+        <v>5.07</v>
       </c>
       <c r="I16">
-        <v>-3.33</v>
+        <v>-3.94</v>
       </c>
       <c r="J16">
-        <v>-9.880000000000001</v>
+        <v>-11.78</v>
       </c>
       <c r="K16">
-        <v>-15.67</v>
+        <v>-18.62</v>
       </c>
       <c r="L16">
-        <v>-38.32</v>
+        <v>-41.71</v>
       </c>
       <c r="M16">
-        <v>-3.97</v>
+        <v>-5.49</v>
       </c>
       <c r="N16">
         <v>19</v>
       </c>
       <c r="O16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>34.33</v>
+        <v>34.06</v>
       </c>
       <c r="Q16">
-        <v>35.35</v>
+        <v>35.17</v>
       </c>
       <c r="R16">
-        <v>37.26</v>
+        <v>37.14</v>
       </c>
       <c r="S16">
-        <v>41.47</v>
+        <v>41.39</v>
       </c>
       <c r="T16">
-        <v>-17.99</v>
+        <v>-20.39</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2599,43 +2599,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>37.53</v>
+        <v>32.82</v>
       </c>
       <c r="Z16">
-        <v>-0.9</v>
+        <v>-0.99</v>
       </c>
       <c r="AA16">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
       <c r="AB16">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="AC16">
-        <v>40.13</v>
+        <v>24.33</v>
       </c>
       <c r="AD16">
-        <v>47.74</v>
+        <v>38.69</v>
       </c>
       <c r="AE16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF16">
-        <v>-77.09999999999999</v>
+        <v>-66.27</v>
       </c>
       <c r="AG16">
-        <v>36.95</v>
+        <v>37</v>
       </c>
       <c r="AH16">
-        <v>33.75</v>
+        <v>33.34</v>
       </c>
       <c r="AI16">
-        <v>37.7</v>
+        <v>37.14</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>14.09</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2646,58 +2646,58 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1056.8</v>
+        <v>1032</v>
       </c>
       <c r="D17">
-        <v>-1.04</v>
+        <v>-2.35</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
       </c>
       <c r="F17">
-        <v>1053.2</v>
+        <v>1032</v>
       </c>
       <c r="G17">
-        <v>-32.1</v>
+        <v>-33.69</v>
       </c>
       <c r="H17">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>-3.05</v>
+        <v>-3.55</v>
       </c>
       <c r="J17">
-        <v>-9.68</v>
+        <v>-11.58</v>
       </c>
       <c r="K17">
-        <v>-15.7</v>
+        <v>-18.7</v>
       </c>
       <c r="L17">
-        <v>-21.68</v>
+        <v>-23.9</v>
       </c>
       <c r="M17">
-        <v>-3.36</v>
+        <v>-3.79</v>
       </c>
       <c r="N17">
         <v>44</v>
       </c>
       <c r="O17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P17">
-        <v>1061.84</v>
+        <v>1054.24</v>
       </c>
       <c r="Q17">
-        <v>1113.26</v>
+        <v>1107.62</v>
       </c>
       <c r="R17">
-        <v>1197.92</v>
+        <v>1192.34</v>
       </c>
       <c r="S17">
-        <v>1325.32</v>
+        <v>1323.49</v>
       </c>
       <c r="T17">
-        <v>-20.26</v>
+        <v>-22.02</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2712,43 +2712,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>33.48</v>
+        <v>30.14</v>
       </c>
       <c r="Z17">
-        <v>-38.04</v>
+        <v>-39.86</v>
       </c>
       <c r="AA17">
-        <v>-35.93</v>
+        <v>-36.72</v>
       </c>
       <c r="AB17">
-        <v>-2.11</v>
+        <v>-3.14</v>
       </c>
       <c r="AC17">
-        <v>35.13</v>
+        <v>27.55</v>
       </c>
       <c r="AD17">
-        <v>29.98</v>
+        <v>30.77</v>
       </c>
       <c r="AE17">
-        <v>29.58</v>
+        <v>29.9</v>
       </c>
       <c r="AF17">
-        <v>-58.62</v>
+        <v>-35.14</v>
       </c>
       <c r="AG17">
-        <v>1183.98</v>
+        <v>1185.39</v>
       </c>
       <c r="AH17">
-        <v>1042.54</v>
+        <v>1029.85</v>
       </c>
       <c r="AI17">
-        <v>1151.25</v>
+        <v>1130.86</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>47.21</v>
+        <v>50.49</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2981,13 +2981,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>0.55</v>
+        <v>1.57</v>
       </c>
       <c r="D7" s="6">
-        <v>1.57</v>
+        <v>-0.64</v>
       </c>
       <c r="E7" s="7">
-        <v>1.02</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2998,13 +2998,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.03</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="6">
-        <v>0.5</v>
+        <v>-7.31</v>
       </c>
       <c r="E8" s="7">
-        <v>1.53</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3015,13 +3015,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.54</v>
+        <v>-4.21</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.21</v>
+        <v>-5.04</v>
       </c>
       <c r="E9" s="7">
-        <v>0.33</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3032,13 +3032,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-3.87</v>
+        <v>-2.45</v>
       </c>
       <c r="D10" s="6">
-        <v>-2.45</v>
+        <v>-3.33</v>
       </c>
       <c r="E10" s="7">
-        <v>1.42</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3049,13 +3049,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.86</v>
+        <v>-5.5</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.5</v>
+        <v>-3.51</v>
       </c>
       <c r="E11" s="8">
-        <v>-4.64</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3066,13 +3066,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.24</v>
+        <v>-4.11</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.11</v>
+        <v>-6.22</v>
       </c>
       <c r="E12" s="7">
-        <v>0.13</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-13.6</v>
+        <v>-13.36</v>
       </c>
       <c r="D13" s="6">
-        <v>-13.36</v>
+        <v>-14.33</v>
       </c>
       <c r="E13" s="7">
-        <v>0.24</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3100,13 +3100,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.16</v>
+        <v>-2.9</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.9</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.74</v>
+        <v>-2.95</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3117,13 +3117,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.84</v>
+        <v>-6.21</v>
       </c>
       <c r="D15" s="6">
-        <v>-6.21</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-2.37</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3134,13 +3134,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.99</v>
+        <v>-6.97</v>
       </c>
       <c r="D16" s="6">
-        <v>-6.97</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-3.98</v>
+        <v>-7.35</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3151,13 +3151,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-9.49</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="D17" s="6">
-        <v>-9.710000000000001</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="E17" s="8">
-        <v>-0.22</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3168,13 +3168,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-9.49</v>
+        <v>-12.81</v>
       </c>
       <c r="D18" s="6">
-        <v>-12.81</v>
+        <v>-12.72</v>
       </c>
       <c r="E18" s="8">
-        <v>-3.32</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3185,13 +3185,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>3.21</v>
+        <v>1.31</v>
       </c>
       <c r="D19" s="6">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.9</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3202,13 +3202,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-14.66</v>
+        <v>-14.5</v>
       </c>
       <c r="D20" s="6">
-        <v>-14.5</v>
+        <v>-18.44</v>
       </c>
       <c r="E20" s="7">
-        <v>0.16</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3219,13 +3219,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-10.08</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D21" s="6">
-        <v>-9.880000000000001</v>
+        <v>-11.78</v>
       </c>
       <c r="E21" s="7">
-        <v>0.2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3236,13 +3236,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-9.35</v>
+        <v>-9.68</v>
       </c>
       <c r="D22" s="6">
-        <v>-9.68</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.33</v>
+        <v>-11.58</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3253,13 +3253,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>3.52</v>
+        <v>2.37</v>
       </c>
       <c r="D23" s="6">
-        <v>2.37</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.15</v>
+        <v>-2.33</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-4.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3270,13 +3270,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>0.84</v>
+        <v>-0.7</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.7</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.54</v>
+        <v>-5.41</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3287,13 +3287,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>0.44</v>
+        <v>0.04</v>
       </c>
       <c r="D25" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.4</v>
+        <v>-1.99</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3304,13 +3304,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-3.88</v>
+        <v>-0.66</v>
       </c>
       <c r="D26" s="6">
-        <v>-0.66</v>
+        <v>-3.03</v>
       </c>
       <c r="E26" s="7">
-        <v>3.22</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3321,13 +3321,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="D27" s="6">
-        <v>0.3</v>
+        <v>1.28</v>
       </c>
       <c r="E27" s="8">
-        <v>-1.3</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3338,13 +3338,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>1.67</v>
+        <v>0.08</v>
       </c>
       <c r="D28" s="6">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="E28" s="8">
-        <v>-1.59</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3355,13 +3355,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-3.07</v>
+        <v>-4.02</v>
       </c>
       <c r="D29" s="6">
-        <v>-4.02</v>
+        <v>-3.01</v>
       </c>
       <c r="E29" s="8">
-        <v>-0.95</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3372,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-3.15</v>
+        <v>-1.62</v>
       </c>
       <c r="D30" s="6">
-        <v>-1.62</v>
+        <v>-1.73</v>
       </c>
       <c r="E30" s="7">
-        <v>1.53</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3389,13 +3389,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.83</v>
+        <v>-3.86</v>
       </c>
       <c r="D31" s="6">
-        <v>-3.86</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.03</v>
+        <v>-6.5</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3406,13 +3406,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-4.08</v>
+        <v>-6.57</v>
       </c>
       <c r="D32" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.49</v>
+        <v>-6.7</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3423,13 +3423,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>1.41</v>
+        <v>2.36</v>
       </c>
       <c r="D33" s="6">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="E33" s="7">
-        <v>0.95</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3440,13 +3440,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-5.59</v>
+        <v>-6.37</v>
       </c>
       <c r="D34" s="6">
-        <v>-6.37</v>
+        <v>-4.96</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.78</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3457,13 +3457,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>10.66</v>
+        <v>9.69</v>
       </c>
       <c r="D35" s="6">
-        <v>9.69</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.97</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3474,13 +3474,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-5.42</v>
+        <v>-2.41</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.41</v>
+        <v>-3.05</v>
       </c>
       <c r="E36" s="7">
-        <v>3.01</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3491,13 +3491,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-5.55</v>
+        <v>-3.33</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.33</v>
+        <v>-3.94</v>
       </c>
       <c r="E37" s="7">
-        <v>2.22</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3508,13 +3508,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-5.95</v>
+        <v>-3.05</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.05</v>
+        <v>-3.55</v>
       </c>
       <c r="E38" s="7">
-        <v>2.9</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3525,13 +3525,13 @@
         <v>11</v>
       </c>
       <c r="C39" s="6">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="D39" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.07</v>
+        <v>-1.77</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3542,13 +3542,13 @@
         <v>11</v>
       </c>
       <c r="C40" s="6">
-        <v>9.9</v>
+        <v>6.81</v>
       </c>
       <c r="D40" s="6">
-        <v>6.81</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-3.09</v>
+        <v>-4.43</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-11.24</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3559,13 +3559,13 @@
         <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>-33.45</v>
+        <v>-34.48</v>
       </c>
       <c r="D41" s="6">
-        <v>-34.48</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.03</v>
+        <v>-36.39</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3576,13 +3576,13 @@
         <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>-31.94</v>
+        <v>-32.52</v>
       </c>
       <c r="D42" s="6">
-        <v>-32.52</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.58</v>
+        <v>-34.95</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3593,13 +3593,13 @@
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="D43" s="6">
-        <v>2.88</v>
+        <v>3.94</v>
       </c>
       <c r="E43" s="8">
-        <v>-1.37</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3610,13 +3610,13 @@
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-12.84</v>
+        <v>-14.68</v>
       </c>
       <c r="D44" s="6">
-        <v>-14.68</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.84</v>
+        <v>-15.61</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3627,13 +3627,13 @@
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-39.77</v>
+        <v>-39.96</v>
       </c>
       <c r="D45" s="6">
-        <v>-39.96</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.19</v>
+        <v>-43.05</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-3.09</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3644,13 +3644,13 @@
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-39.27</v>
+        <v>-41.54</v>
       </c>
       <c r="D46" s="6">
-        <v>-41.54</v>
+        <v>-38.77</v>
       </c>
       <c r="E46" s="8">
-        <v>-2.27</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3661,13 +3661,13 @@
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-9.52</v>
+        <v>-11.76</v>
       </c>
       <c r="D47" s="6">
-        <v>-11.76</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.24</v>
+        <v>-15</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -3678,13 +3678,13 @@
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>8.06</v>
+        <v>7.01</v>
       </c>
       <c r="D48" s="6">
-        <v>7.01</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.05</v>
+        <v>1.33</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-5.68</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3695,13 +3695,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-24.69</v>
+        <v>-26.06</v>
       </c>
       <c r="D49" s="6">
-        <v>-26.06</v>
+        <v>-25.9</v>
       </c>
       <c r="E49" s="8">
-        <v>-1.37</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3712,13 +3712,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>35.14</v>
+        <v>28.42</v>
       </c>
       <c r="D50" s="6">
-        <v>28.42</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-6.72</v>
+        <v>26.24</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -3729,13 +3729,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-37.78</v>
+        <v>-40.1</v>
       </c>
       <c r="D51" s="6">
-        <v>-40.1</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-2.32</v>
+        <v>-40.18</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -3746,13 +3746,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-42.2</v>
+        <v>-43.01</v>
       </c>
       <c r="D52" s="6">
-        <v>-43.01</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-49.62</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-6.61</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3763,13 +3763,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-37.88</v>
+        <v>-38.32</v>
       </c>
       <c r="D53" s="6">
-        <v>-38.32</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.44</v>
+        <v>-41.71</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -3780,13 +3780,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-20.85</v>
+        <v>-21.68</v>
       </c>
       <c r="D54" s="6">
-        <v>-21.68</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.83</v>
+        <v>-23.9</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3797,13 +3797,13 @@
         <v>10</v>
       </c>
       <c r="C55" s="6">
-        <v>-1.33</v>
+        <v>1.16</v>
       </c>
       <c r="D55" s="6">
-        <v>1.16</v>
+        <v>-2.71</v>
       </c>
       <c r="E55" s="7">
-        <v>2.49</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3814,13 +3814,13 @@
         <v>10</v>
       </c>
       <c r="C56" s="6">
-        <v>1.1</v>
+        <v>3.33</v>
       </c>
       <c r="D56" s="6">
-        <v>3.33</v>
+        <v>-3.48</v>
       </c>
       <c r="E56" s="7">
-        <v>2.23</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3831,13 +3831,13 @@
         <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>-13.25</v>
+        <v>-10.34</v>
       </c>
       <c r="D57" s="6">
-        <v>-10.34</v>
+        <v>-12.38</v>
       </c>
       <c r="E57" s="7">
-        <v>2.91</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3848,13 +3848,13 @@
         <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-14.2</v>
+        <v>-14.16</v>
       </c>
       <c r="D58" s="6">
-        <v>-14.16</v>
+        <v>-16.92</v>
       </c>
       <c r="E58" s="7">
-        <v>0.04</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3865,13 +3865,13 @@
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-11.8</v>
+        <v>-12.01</v>
       </c>
       <c r="D59" s="6">
-        <v>-12.01</v>
+        <v>-10.32</v>
       </c>
       <c r="E59" s="8">
-        <v>-0.21</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3882,13 +3882,13 @@
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-13.24</v>
+        <v>-11.13</v>
       </c>
       <c r="D60" s="6">
-        <v>-11.13</v>
+        <v>-13.99</v>
       </c>
       <c r="E60" s="7">
-        <v>2.11</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3899,13 +3899,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-16.57</v>
+        <v>-14.93</v>
       </c>
       <c r="D61" s="6">
-        <v>-14.93</v>
+        <v>-17.27</v>
       </c>
       <c r="E61" s="7">
-        <v>1.64</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3916,13 +3916,13 @@
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-6.54</v>
+        <v>-7.22</v>
       </c>
       <c r="D62" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.68</v>
+        <v>-11.03</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-3.81</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3933,13 +3933,13 @@
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-6.77</v>
+        <v>-7.24</v>
       </c>
       <c r="D63" s="6">
-        <v>-7.24</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-0.47</v>
+        <v>-10.61</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3950,13 +3950,13 @@
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-5.85</v>
+        <v>-6.67</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.67</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.82</v>
+        <v>-8.49</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3967,13 +3967,13 @@
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>0.19</v>
+        <v>1.11</v>
       </c>
       <c r="D65" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.92</v>
+        <v>1.29</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.18</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3984,13 +3984,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-1.18</v>
+        <v>-4.57</v>
       </c>
       <c r="D66" s="6">
-        <v>-4.57</v>
+        <v>-4.31</v>
       </c>
       <c r="E66" s="8">
-        <v>-3.39</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4001,13 +4001,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-0.74</v>
+        <v>-1.15</v>
       </c>
       <c r="D67" s="6">
-        <v>-1.15</v>
+        <v>-0.96</v>
       </c>
       <c r="E67" s="8">
-        <v>-0.41</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4018,13 +4018,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-16.13</v>
+        <v>-12.41</v>
       </c>
       <c r="D68" s="6">
-        <v>-12.41</v>
+        <v>-17.76</v>
       </c>
       <c r="E68" s="7">
-        <v>3.72</v>
+        <v>-5.35</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4035,13 +4035,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-17.86</v>
+        <v>-15.67</v>
       </c>
       <c r="D69" s="6">
-        <v>-15.67</v>
+        <v>-18.62</v>
       </c>
       <c r="E69" s="7">
-        <v>2.19</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4052,13 +4052,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-17.09</v>
+        <v>-15.7</v>
       </c>
       <c r="D70" s="6">
-        <v>-15.7</v>
+        <v>-18.7</v>
       </c>
       <c r="E70" s="7">
-        <v>1.39</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4069,13 +4069,13 @@
         <v>6</v>
       </c>
       <c r="C71" s="6">
-        <v>-2.17</v>
+        <v>-2.79</v>
       </c>
       <c r="D71" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-0.62</v>
+        <v>-5.4</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4086,13 +4086,13 @@
         <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-14.55</v>
+        <v>-15.32</v>
       </c>
       <c r="D72" s="6">
-        <v>-15.32</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.77</v>
+        <v>-20.02</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4.7</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4103,13 +4103,13 @@
         <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-34.92</v>
+        <v>-35</v>
       </c>
       <c r="D73" s="6">
-        <v>-35</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-0.08</v>
+        <v>-35.73</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4120,13 +4120,13 @@
         <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-32.45</v>
+        <v>-33.19</v>
       </c>
       <c r="D74" s="6">
-        <v>-33.19</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-0.74</v>
+        <v>-35.03</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4137,13 +4137,13 @@
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-18.43</v>
+        <v>-19.5</v>
       </c>
       <c r="D75" s="6">
-        <v>-19.5</v>
+        <v>-18.64</v>
       </c>
       <c r="E75" s="8">
-        <v>-1.07</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4154,13 +4154,13 @@
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-22.56</v>
+        <v>-23.16</v>
       </c>
       <c r="D76" s="6">
-        <v>-23.16</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.6</v>
+        <v>-24.47</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4171,13 +4171,13 @@
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-46.21</v>
+        <v>-46.39</v>
       </c>
       <c r="D77" s="6">
-        <v>-46.39</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-0.18</v>
+        <v>-47.89</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4188,13 +4188,13 @@
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-40.7</v>
+        <v>-40.24</v>
       </c>
       <c r="D78" s="6">
-        <v>-40.24</v>
+        <v>-40.83</v>
       </c>
       <c r="E78" s="7">
-        <v>0.46</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4205,13 +4205,13 @@
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-23.85</v>
+        <v>-25.26</v>
       </c>
       <c r="D79" s="6">
-        <v>-25.26</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-1.41</v>
+        <v>-27.32</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4222,13 +4222,13 @@
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-17.53</v>
+        <v>-18.93</v>
       </c>
       <c r="D80" s="6">
-        <v>-18.93</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-1.4</v>
+        <v>-20.63</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4239,13 +4239,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-34.82</v>
+        <v>-35.43</v>
       </c>
       <c r="D81" s="6">
-        <v>-35.43</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-0.61</v>
+        <v>-35.56</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4256,13 +4256,13 @@
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-11.98</v>
+        <v>-15.33</v>
       </c>
       <c r="D82" s="6">
-        <v>-15.33</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-3.35</v>
+        <v>-15.66</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4273,13 +4273,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-39.77</v>
+        <v>-39.89</v>
       </c>
       <c r="D83" s="6">
-        <v>-39.89</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.12</v>
+        <v>-40.17</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4290,13 +4290,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-48.43</v>
+        <v>-47.98</v>
       </c>
       <c r="D84" s="6">
-        <v>-47.98</v>
-      </c>
-      <c r="E84" s="7">
-        <v>0.45</v>
+        <v>-47.81</v>
+      </c>
+      <c r="E84" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4307,13 +4307,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-41.75</v>
+        <v>-42.04</v>
       </c>
       <c r="D85" s="6">
-        <v>-42.04</v>
-      </c>
-      <c r="E85" s="8">
-        <v>-0.29</v>
+        <v>-43.85</v>
+      </c>
+      <c r="E85" s="7">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4324,13 +4324,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-31.39</v>
+        <v>-32.1</v>
       </c>
       <c r="D86" s="6">
-        <v>-32.1</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-0.71</v>
+        <v>-33.69</v>
+      </c>
+      <c r="E86" s="7">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4341,13 +4341,13 @@
         <v>2</v>
       </c>
       <c r="C87" s="6">
-        <v>736</v>
+        <v>731.3</v>
       </c>
       <c r="D87" s="6">
-        <v>731.3</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-4.7</v>
+        <v>711.65</v>
+      </c>
+      <c r="E87" s="7">
+        <v>-19.65</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4358,13 +4358,13 @@
         <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>924.15</v>
+        <v>915.8</v>
       </c>
       <c r="D88" s="6">
-        <v>915.8</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-8.35</v>
+        <v>865</v>
+      </c>
+      <c r="E88" s="7">
+        <v>-50.8</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4375,13 +4375,13 @@
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>200.3</v>
+        <v>200.03</v>
       </c>
       <c r="D89" s="6">
-        <v>200.03</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.27</v>
+        <v>195.76</v>
+      </c>
+      <c r="E89" s="7">
+        <v>-4.27</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4392,13 +4392,13 @@
         <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>616.55</v>
+        <v>609.8</v>
       </c>
       <c r="D90" s="6">
-        <v>609.8</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-6.75</v>
+        <v>592.95</v>
+      </c>
+      <c r="E90" s="7">
+        <v>-16.85</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4409,13 +4409,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>1681.8</v>
+        <v>1659.6</v>
       </c>
       <c r="D91" s="6">
-        <v>1659.6</v>
+        <v>1677.4</v>
       </c>
       <c r="E91" s="8">
-        <v>-22.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4426,13 +4426,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>976</v>
+        <v>968.5</v>
       </c>
       <c r="D92" s="6">
-        <v>968.5</v>
-      </c>
-      <c r="E92" s="8">
-        <v>-7.5</v>
+        <v>951.9</v>
+      </c>
+      <c r="E92" s="7">
+        <v>-16.6</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4443,13 +4443,13 @@
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>3093</v>
+        <v>3082.5</v>
       </c>
       <c r="D93" s="6">
-        <v>3082.5</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-10.5</v>
+        <v>2996</v>
+      </c>
+      <c r="E93" s="7">
+        <v>-86.5</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4460,13 +4460,13 @@
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>624.15</v>
+        <v>615.3</v>
       </c>
       <c r="D94" s="6">
-        <v>615.3</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-8.85</v>
+        <v>609.3</v>
+      </c>
+      <c r="E94" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4477,13 +4477,13 @@
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>351.65</v>
+        <v>345.15</v>
       </c>
       <c r="D95" s="6">
-        <v>345.15</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-6.5</v>
+        <v>335.65</v>
+      </c>
+      <c r="E95" s="7">
+        <v>-9.5</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4494,13 +4494,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>178.69</v>
+        <v>175.64</v>
       </c>
       <c r="D96" s="6">
-        <v>175.64</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-3.05</v>
+        <v>171.96</v>
+      </c>
+      <c r="E96" s="7">
+        <v>-3.68</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4511,13 +4511,13 @@
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>2100</v>
+        <v>2080.3</v>
       </c>
       <c r="D97" s="6">
-        <v>2080.3</v>
-      </c>
-      <c r="E97" s="8">
-        <v>-19.7</v>
+        <v>2076</v>
+      </c>
+      <c r="E97" s="7">
+        <v>-4.3</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4528,13 +4528,13 @@
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>4550</v>
+        <v>4377</v>
       </c>
       <c r="D98" s="6">
-        <v>4377</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-173</v>
+        <v>4359.5</v>
+      </c>
+      <c r="E98" s="7">
+        <v>-17.5</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4545,13 +4545,13 @@
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>2906</v>
+        <v>2890.3</v>
       </c>
       <c r="D99" s="6">
-        <v>2890.3</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-15.7</v>
+        <v>2876.3</v>
+      </c>
+      <c r="E99" s="7">
+        <v>-14</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4562,13 +4562,13 @@
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>196.3</v>
+        <v>198.02</v>
       </c>
       <c r="D100" s="6">
-        <v>198.02</v>
+        <v>191.78</v>
       </c>
       <c r="E100" s="7">
-        <v>1.72</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4579,13 +4579,13 @@
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>34.18</v>
+        <v>34.01</v>
       </c>
       <c r="D101" s="6">
-        <v>34.01</v>
-      </c>
-      <c r="E101" s="8">
-        <v>-0.17</v>
+        <v>32.95</v>
+      </c>
+      <c r="E101" s="7">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4596,591 +4596,710 @@
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>1067.9</v>
+        <v>1056.8</v>
       </c>
       <c r="D102" s="6">
-        <v>1056.8</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-11.1</v>
+        <v>1032</v>
+      </c>
+      <c r="E102" s="7">
+        <v>-24.8</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C103" s="6">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="D103" s="6">
-        <v>38</v>
-      </c>
-      <c r="E103" s="7">
-        <v>12</v>
+        <v>93</v>
+      </c>
+      <c r="E103" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C104" s="6">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D104" s="6">
-        <v>26</v>
-      </c>
-      <c r="E104" s="8">
-        <v>-12</v>
+        <v>74</v>
+      </c>
+      <c r="E104" s="7">
+        <v>-19</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C105" s="6">
-        <v>54.71</v>
+        <v>38</v>
       </c>
       <c r="D105" s="6">
-        <v>52.47</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-2.24</v>
+        <v>32</v>
+      </c>
+      <c r="E105" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>46.64</v>
+        <v>32</v>
       </c>
       <c r="D106" s="6">
-        <v>45.35</v>
-      </c>
-      <c r="E106" s="8">
-        <v>-1.29</v>
+        <v>26</v>
+      </c>
+      <c r="E106" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>39.56</v>
+        <v>74</v>
       </c>
       <c r="D107" s="6">
-        <v>38.94</v>
+        <v>87</v>
       </c>
       <c r="E107" s="8">
-        <v>-0.62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>41.74</v>
+        <v>62</v>
       </c>
       <c r="D108" s="6">
-        <v>40.28</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-1.46</v>
+        <v>56</v>
+      </c>
+      <c r="E108" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C109" s="6">
-        <v>43.9</v>
+        <v>26</v>
       </c>
       <c r="D109" s="6">
-        <v>39.9</v>
+        <v>38</v>
       </c>
       <c r="E109" s="8">
-        <v>-4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C110" s="6">
-        <v>42.63</v>
+        <v>68</v>
       </c>
       <c r="D110" s="6">
-        <v>40.5</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-2.13</v>
+        <v>62</v>
+      </c>
+      <c r="E110" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="6">
-        <v>25.43</v>
+        <v>56</v>
       </c>
       <c r="D111" s="6">
-        <v>24.87</v>
+        <v>68</v>
       </c>
       <c r="E111" s="8">
-        <v>-0.5600000000000001</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>41.43</v>
+        <v>52.47</v>
       </c>
       <c r="D112" s="6">
-        <v>39.08</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-2.35</v>
+        <v>44.29</v>
+      </c>
+      <c r="E112" s="7">
+        <v>-8.18</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>37.1</v>
+        <v>45.35</v>
       </c>
       <c r="D113" s="6">
-        <v>32.44</v>
-      </c>
-      <c r="E113" s="8">
-        <v>-4.66</v>
+        <v>38.38</v>
+      </c>
+      <c r="E113" s="7">
+        <v>-6.97</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>39.41</v>
+        <v>38.94</v>
       </c>
       <c r="D114" s="6">
-        <v>35.56</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-3.85</v>
+        <v>30.72</v>
+      </c>
+      <c r="E114" s="7">
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>40.95</v>
+        <v>40.28</v>
       </c>
       <c r="D115" s="6">
-        <v>38.75</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-2.2</v>
+        <v>36.83</v>
+      </c>
+      <c r="E115" s="7">
+        <v>-3.45</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>31.38</v>
+        <v>39.9</v>
       </c>
       <c r="D116" s="6">
-        <v>25.32</v>
+        <v>44.28</v>
       </c>
       <c r="E116" s="8">
-        <v>-6.06</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>61.04</v>
+        <v>40.5</v>
       </c>
       <c r="D117" s="6">
-        <v>59.55</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-1.49</v>
+        <v>36.19</v>
+      </c>
+      <c r="E117" s="7">
+        <v>-4.31</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>28.35</v>
+        <v>24.87</v>
       </c>
       <c r="D118" s="6">
-        <v>31.26</v>
+        <v>20.82</v>
       </c>
       <c r="E118" s="7">
-        <v>2.91</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>38.35</v>
+        <v>39.08</v>
       </c>
       <c r="D119" s="6">
         <v>37.53</v>
       </c>
-      <c r="E119" s="8">
-        <v>-0.82</v>
+      <c r="E119" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>35.1</v>
+        <v>32.44</v>
       </c>
       <c r="D120" s="6">
-        <v>33.48</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-1.62</v>
+        <v>27.08</v>
+      </c>
+      <c r="E120" s="7">
+        <v>-5.36</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>-22.34</v>
+        <v>35.56</v>
       </c>
       <c r="D121" s="6">
-        <v>0.17</v>
+        <v>31.57</v>
       </c>
       <c r="E121" s="7">
-        <v>22.51</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>-44.31</v>
+        <v>38.75</v>
       </c>
       <c r="D122" s="6">
-        <v>-60.35</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-16.04</v>
+        <v>38.27</v>
+      </c>
+      <c r="E122" s="7">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>-31.31</v>
+        <v>25.32</v>
       </c>
       <c r="D123" s="6">
-        <v>-36.72</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-5.41</v>
+        <v>24.8</v>
+      </c>
+      <c r="E123" s="7">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>-80.95999999999999</v>
+        <v>59.55</v>
       </c>
       <c r="D124" s="6">
-        <v>-87.65000000000001</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-6.69</v>
+        <v>58.18</v>
+      </c>
+      <c r="E124" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C125" s="6">
-        <v>-38.37</v>
+        <v>31.26</v>
       </c>
       <c r="D125" s="6">
-        <v>191.51</v>
+        <v>26.97</v>
       </c>
       <c r="E125" s="7">
-        <v>229.88</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C126" s="6">
-        <v>-29.72</v>
+        <v>37.53</v>
       </c>
       <c r="D126" s="6">
-        <v>-58.61</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-28.89</v>
+        <v>32.82</v>
+      </c>
+      <c r="E126" s="7">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="6">
-        <v>-20.07</v>
+        <v>33.48</v>
       </c>
       <c r="D127" s="6">
-        <v>-29.08</v>
-      </c>
-      <c r="E127" s="8">
-        <v>-9.01</v>
+        <v>30.14</v>
+      </c>
+      <c r="E127" s="7">
+        <v>-3.34</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>-85.61</v>
+        <v>0.17</v>
       </c>
       <c r="D128" s="6">
-        <v>-90.52</v>
-      </c>
-      <c r="E128" s="8">
-        <v>-4.91</v>
+        <v>-28.91</v>
+      </c>
+      <c r="E128" s="7">
+        <v>-29.08</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>50.5</v>
+        <v>-60.35</v>
       </c>
       <c r="D129" s="6">
-        <v>37.04</v>
+        <v>-35.54</v>
       </c>
       <c r="E129" s="8">
-        <v>-13.46</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>-36.22</v>
+        <v>-36.72</v>
       </c>
       <c r="D130" s="6">
-        <v>-29.73</v>
-      </c>
-      <c r="E130" s="7">
-        <v>6.49</v>
+        <v>6.04</v>
+      </c>
+      <c r="E130" s="8">
+        <v>42.76</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>-26.73</v>
+        <v>-87.65000000000001</v>
       </c>
       <c r="D131" s="6">
-        <v>-58.8</v>
+        <v>-79.47</v>
       </c>
       <c r="E131" s="8">
-        <v>-32.07</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>27.36</v>
+        <v>191.51</v>
       </c>
       <c r="D132" s="6">
-        <v>361.77</v>
+        <v>127.64</v>
       </c>
       <c r="E132" s="7">
-        <v>334.41</v>
+        <v>-63.87</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>808.73</v>
+        <v>-58.61</v>
       </c>
       <c r="D133" s="6">
-        <v>27.88</v>
+        <v>-30.77</v>
       </c>
       <c r="E133" s="8">
-        <v>-780.85</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-57.01</v>
+        <v>-29.08</v>
       </c>
       <c r="D134" s="6">
-        <v>-60.73</v>
+        <v>-2.53</v>
       </c>
       <c r="E134" s="8">
-        <v>-3.72</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>-79.73999999999999</v>
+        <v>-90.52</v>
       </c>
       <c r="D135" s="6">
-        <v>-77.09999999999999</v>
-      </c>
-      <c r="E135" s="7">
-        <v>2.64</v>
+        <v>-77.59</v>
+      </c>
+      <c r="E135" s="8">
+        <v>12.93</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>300.91</v>
+        <v>37.04</v>
       </c>
       <c r="D136" s="6">
+        <v>62.18</v>
+      </c>
+      <c r="E136" s="8">
+        <v>25.14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" s="6">
+        <v>-29.73</v>
+      </c>
+      <c r="D137" s="6">
+        <v>18.14</v>
+      </c>
+      <c r="E137" s="8">
+        <v>47.87</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" s="6">
+        <v>-58.8</v>
+      </c>
+      <c r="D138" s="6">
+        <v>33.34</v>
+      </c>
+      <c r="E138" s="8">
+        <v>92.14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" s="6">
+        <v>361.77</v>
+      </c>
+      <c r="D139" s="6">
+        <v>94.87</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-266.9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="6">
+        <v>27.88</v>
+      </c>
+      <c r="D140" s="6">
+        <v>26.51</v>
+      </c>
+      <c r="E140" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="6">
+        <v>-60.73</v>
+      </c>
+      <c r="D141" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="E141" s="8">
+        <v>58.09</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="6">
+        <v>-77.09999999999999</v>
+      </c>
+      <c r="D142" s="6">
+        <v>-66.27</v>
+      </c>
+      <c r="E142" s="8">
+        <v>10.83</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6">
         <v>-58.62</v>
       </c>
-      <c r="E136" s="8">
-        <v>-359.53</v>
+      <c r="D143" s="6">
+        <v>-35.14</v>
+      </c>
+      <c r="E143" s="8">
+        <v>23.48</v>
       </c>
     </row>
   </sheetData>
@@ -5245,16 +5364,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>38.5</v>
+        <v>34.9</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.2</v>
+        <v>-7.5</v>
       </c>
       <c r="G2" s="11">
-        <v>-8</v>
+        <v>-10.4</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5380,13 +5499,13 @@
         <v>46</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>38</v>
@@ -5394,34 +5513,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3521</v>
+        <v>0.349</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3119</v>
+        <v>0.2963</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2123</v>
+        <v>0.2124</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1483</v>
+        <v>0.1431</v>
       </c>
       <c r="E2" s="14">
-        <v>0.133</v>
+        <v>0.1337</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0958</v>
+        <v>0.0891</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0413</v>
+        <v>0.0407</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0389</v>
+        <v>0.0392</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0367</v>
+        <v>0.0278</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0219</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5446,22 +5565,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.0336</v>
+        <v>-0.0379</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0397</v>
+        <v>-0.0549</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0625</v>
+        <v>-0.0767</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.07339999999999999</v>
+        <v>-0.07980000000000001</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.09359999999999999</v>
+        <v>-0.096</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1256</v>
+        <v>-0.1273</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -199,49 +199,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.5 → 44.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.5</t>
-  </si>
-  <si>
-    <t>44.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -272,13 +236,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,22 +272,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,24 +289,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,34 +358,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2889,7 +2812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2909,47 +2832,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2958,2348 +2846,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1.57</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-0.64</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-7.31</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-7.81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-4.21</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-2.45</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-3.33</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-5.5</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.51</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.11</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-6.22</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-13.36</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-14.33</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.9</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-6.21</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.97</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-7.35</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-8.550000000000001</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-12.81</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-12.72</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.31</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-14.5</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-18.44</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-11.78</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-9.68</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-11.58</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2.37</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-2.33</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-0.7</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.99</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-0.66</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-3.03</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1.28</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-4.02</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-3.01</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-1.62</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-3.86</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-6.5</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="D33" s="6">
-        <v>1.24</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-4.96</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="6">
-        <v>9.69</v>
-      </c>
-      <c r="D35" s="6">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-2.41</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-3.05</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-3.33</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-3.94</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-3.05</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-3.55</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-1.77</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="6">
-        <v>6.81</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-4.43</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-11.24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-34.48</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-36.39</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-32.52</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-34.95</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="D43" s="6">
-        <v>3.94</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-14.68</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-15.61</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-39.96</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-43.05</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-41.54</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-38.77</v>
-      </c>
-      <c r="E46" s="8">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-11.76</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-15</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="6">
-        <v>7.01</v>
-      </c>
-      <c r="D48" s="6">
-        <v>1.33</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-5.68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-26.06</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-25.9</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="6">
-        <v>28.42</v>
-      </c>
-      <c r="D50" s="6">
-        <v>26.24</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-40.1</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-40.18</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-43.01</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-49.62</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-6.61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-38.32</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-41.71</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-21.68</v>
-      </c>
-      <c r="D54" s="6">
-        <v>-23.9</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="D55" s="6">
-        <v>-2.71</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-3.87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="6">
-        <v>3.33</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-3.48</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-6.81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="6">
-        <v>-10.34</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-12.38</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-14.16</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-16.92</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-10.32</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-11.13</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-13.99</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-14.93</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-17.27</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-11.03</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-3.81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-7.24</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-10.61</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-6.67</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-8.49</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="D65" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-4.57</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-4.31</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-0.96</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-12.41</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-17.76</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-5.35</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-15.67</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-18.62</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-15.7</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-18.7</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-5.4</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-15.32</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-20.02</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-35</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-35.73</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-33.19</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-35.03</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-19.5</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-18.64</v>
-      </c>
-      <c r="E75" s="8">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-23.16</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-24.47</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-46.39</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-47.89</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-40.24</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-40.83</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-25.26</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-27.32</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-18.93</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-20.63</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-35.43</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-35.56</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-15.33</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-15.66</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="6">
-        <v>-39.89</v>
-      </c>
-      <c r="D83" s="6">
-        <v>-40.17</v>
-      </c>
-      <c r="E83" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="6">
-        <v>-47.98</v>
-      </c>
-      <c r="D84" s="6">
-        <v>-47.81</v>
-      </c>
-      <c r="E84" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="6">
-        <v>-42.04</v>
-      </c>
-      <c r="D85" s="6">
-        <v>-43.85</v>
-      </c>
-      <c r="E85" s="7">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="6">
-        <v>-32.1</v>
-      </c>
-      <c r="D86" s="6">
-        <v>-33.69</v>
-      </c>
-      <c r="E86" s="7">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C87" s="6">
-        <v>731.3</v>
-      </c>
-      <c r="D87" s="6">
-        <v>711.65</v>
-      </c>
-      <c r="E87" s="7">
-        <v>-19.65</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C88" s="6">
-        <v>915.8</v>
-      </c>
-      <c r="D88" s="6">
-        <v>865</v>
-      </c>
-      <c r="E88" s="7">
-        <v>-50.8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C89" s="6">
-        <v>200.03</v>
-      </c>
-      <c r="D89" s="6">
-        <v>195.76</v>
-      </c>
-      <c r="E89" s="7">
-        <v>-4.27</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C90" s="6">
-        <v>609.8</v>
-      </c>
-      <c r="D90" s="6">
-        <v>592.95</v>
-      </c>
-      <c r="E90" s="7">
-        <v>-16.85</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C91" s="6">
-        <v>1659.6</v>
-      </c>
-      <c r="D91" s="6">
-        <v>1677.4</v>
-      </c>
-      <c r="E91" s="8">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C92" s="6">
-        <v>968.5</v>
-      </c>
-      <c r="D92" s="6">
-        <v>951.9</v>
-      </c>
-      <c r="E92" s="7">
-        <v>-16.6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C93" s="6">
-        <v>3082.5</v>
-      </c>
-      <c r="D93" s="6">
-        <v>2996</v>
-      </c>
-      <c r="E93" s="7">
-        <v>-86.5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C94" s="6">
-        <v>615.3</v>
-      </c>
-      <c r="D94" s="6">
-        <v>609.3</v>
-      </c>
-      <c r="E94" s="7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C95" s="6">
-        <v>345.15</v>
-      </c>
-      <c r="D95" s="6">
-        <v>335.65</v>
-      </c>
-      <c r="E95" s="7">
-        <v>-9.5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C96" s="6">
-        <v>175.64</v>
-      </c>
-      <c r="D96" s="6">
-        <v>171.96</v>
-      </c>
-      <c r="E96" s="7">
-        <v>-3.68</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C97" s="6">
-        <v>2080.3</v>
-      </c>
-      <c r="D97" s="6">
-        <v>2076</v>
-      </c>
-      <c r="E97" s="7">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C98" s="6">
-        <v>4377</v>
-      </c>
-      <c r="D98" s="6">
-        <v>4359.5</v>
-      </c>
-      <c r="E98" s="7">
-        <v>-17.5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C99" s="6">
-        <v>2890.3</v>
-      </c>
-      <c r="D99" s="6">
-        <v>2876.3</v>
-      </c>
-      <c r="E99" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C100" s="6">
-        <v>198.02</v>
-      </c>
-      <c r="D100" s="6">
-        <v>191.78</v>
-      </c>
-      <c r="E100" s="7">
-        <v>-6.24</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C101" s="6">
-        <v>34.01</v>
-      </c>
-      <c r="D101" s="6">
-        <v>32.95</v>
-      </c>
-      <c r="E101" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C102" s="6">
-        <v>1056.8</v>
-      </c>
-      <c r="D102" s="6">
-        <v>1032</v>
-      </c>
-      <c r="E102" s="7">
-        <v>-24.8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C103" s="6">
-        <v>87</v>
-      </c>
-      <c r="D103" s="6">
-        <v>93</v>
-      </c>
-      <c r="E103" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C104" s="6">
-        <v>93</v>
-      </c>
-      <c r="D104" s="6">
-        <v>74</v>
-      </c>
-      <c r="E104" s="7">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C105" s="6">
-        <v>38</v>
-      </c>
-      <c r="D105" s="6">
-        <v>32</v>
-      </c>
-      <c r="E105" s="7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C106" s="6">
-        <v>32</v>
-      </c>
-      <c r="D106" s="6">
-        <v>26</v>
-      </c>
-      <c r="E106" s="7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C107" s="6">
-        <v>74</v>
-      </c>
-      <c r="D107" s="6">
-        <v>87</v>
-      </c>
-      <c r="E107" s="8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C108" s="6">
-        <v>62</v>
-      </c>
-      <c r="D108" s="6">
-        <v>56</v>
-      </c>
-      <c r="E108" s="7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" s="6">
-        <v>26</v>
-      </c>
-      <c r="D109" s="6">
-        <v>38</v>
-      </c>
-      <c r="E109" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C110" s="6">
-        <v>68</v>
-      </c>
-      <c r="D110" s="6">
-        <v>62</v>
-      </c>
-      <c r="E110" s="7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" s="6">
-        <v>56</v>
-      </c>
-      <c r="D111" s="6">
-        <v>68</v>
-      </c>
-      <c r="E111" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C112" s="6">
-        <v>52.47</v>
-      </c>
-      <c r="D112" s="6">
-        <v>44.29</v>
-      </c>
-      <c r="E112" s="7">
-        <v>-8.18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C113" s="6">
-        <v>45.35</v>
-      </c>
-      <c r="D113" s="6">
-        <v>38.38</v>
-      </c>
-      <c r="E113" s="7">
-        <v>-6.97</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C114" s="6">
-        <v>38.94</v>
-      </c>
-      <c r="D114" s="6">
-        <v>30.72</v>
-      </c>
-      <c r="E114" s="7">
-        <v>-8.220000000000001</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C115" s="6">
-        <v>40.28</v>
-      </c>
-      <c r="D115" s="6">
-        <v>36.83</v>
-      </c>
-      <c r="E115" s="7">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C116" s="6">
-        <v>39.9</v>
-      </c>
-      <c r="D116" s="6">
-        <v>44.28</v>
-      </c>
-      <c r="E116" s="8">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C117" s="6">
-        <v>40.5</v>
-      </c>
-      <c r="D117" s="6">
-        <v>36.19</v>
-      </c>
-      <c r="E117" s="7">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C118" s="6">
-        <v>24.87</v>
-      </c>
-      <c r="D118" s="6">
-        <v>20.82</v>
-      </c>
-      <c r="E118" s="7">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C119" s="6">
-        <v>39.08</v>
-      </c>
-      <c r="D119" s="6">
-        <v>37.53</v>
-      </c>
-      <c r="E119" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C120" s="6">
-        <v>32.44</v>
-      </c>
-      <c r="D120" s="6">
-        <v>27.08</v>
-      </c>
-      <c r="E120" s="7">
-        <v>-5.36</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C121" s="6">
-        <v>35.56</v>
-      </c>
-      <c r="D121" s="6">
-        <v>31.57</v>
-      </c>
-      <c r="E121" s="7">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C122" s="6">
-        <v>38.75</v>
-      </c>
-      <c r="D122" s="6">
-        <v>38.27</v>
-      </c>
-      <c r="E122" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C123" s="6">
-        <v>25.32</v>
-      </c>
-      <c r="D123" s="6">
-        <v>24.8</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C124" s="6">
-        <v>59.55</v>
-      </c>
-      <c r="D124" s="6">
-        <v>58.18</v>
-      </c>
-      <c r="E124" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C125" s="6">
-        <v>31.26</v>
-      </c>
-      <c r="D125" s="6">
-        <v>26.97</v>
-      </c>
-      <c r="E125" s="7">
-        <v>-4.29</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C126" s="6">
-        <v>37.53</v>
-      </c>
-      <c r="D126" s="6">
-        <v>32.82</v>
-      </c>
-      <c r="E126" s="7">
-        <v>-4.71</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C127" s="6">
-        <v>33.48</v>
-      </c>
-      <c r="D127" s="6">
-        <v>30.14</v>
-      </c>
-      <c r="E127" s="7">
-        <v>-3.34</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C128" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="D128" s="6">
-        <v>-28.91</v>
-      </c>
-      <c r="E128" s="7">
-        <v>-29.08</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C129" s="6">
-        <v>-60.35</v>
-      </c>
-      <c r="D129" s="6">
-        <v>-35.54</v>
-      </c>
-      <c r="E129" s="8">
-        <v>24.81</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C130" s="6">
-        <v>-36.72</v>
-      </c>
-      <c r="D130" s="6">
-        <v>6.04</v>
-      </c>
-      <c r="E130" s="8">
-        <v>42.76</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C131" s="6">
-        <v>-87.65000000000001</v>
-      </c>
-      <c r="D131" s="6">
-        <v>-79.47</v>
-      </c>
-      <c r="E131" s="8">
-        <v>8.18</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C132" s="6">
-        <v>191.51</v>
-      </c>
-      <c r="D132" s="6">
-        <v>127.64</v>
-      </c>
-      <c r="E132" s="7">
-        <v>-63.87</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C133" s="6">
-        <v>-58.61</v>
-      </c>
-      <c r="D133" s="6">
-        <v>-30.77</v>
-      </c>
-      <c r="E133" s="8">
-        <v>27.84</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C134" s="6">
-        <v>-29.08</v>
-      </c>
-      <c r="D134" s="6">
-        <v>-2.53</v>
-      </c>
-      <c r="E134" s="8">
-        <v>26.55</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C135" s="6">
-        <v>-90.52</v>
-      </c>
-      <c r="D135" s="6">
-        <v>-77.59</v>
-      </c>
-      <c r="E135" s="8">
-        <v>12.93</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C136" s="6">
-        <v>37.04</v>
-      </c>
-      <c r="D136" s="6">
-        <v>62.18</v>
-      </c>
-      <c r="E136" s="8">
-        <v>25.14</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C137" s="6">
-        <v>-29.73</v>
-      </c>
-      <c r="D137" s="6">
-        <v>18.14</v>
-      </c>
-      <c r="E137" s="8">
-        <v>47.87</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C138" s="6">
-        <v>-58.8</v>
-      </c>
-      <c r="D138" s="6">
-        <v>33.34</v>
-      </c>
-      <c r="E138" s="8">
-        <v>92.14</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C139" s="6">
-        <v>361.77</v>
-      </c>
-      <c r="D139" s="6">
-        <v>94.87</v>
-      </c>
-      <c r="E139" s="7">
-        <v>-266.9</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C140" s="6">
-        <v>27.88</v>
-      </c>
-      <c r="D140" s="6">
-        <v>26.51</v>
-      </c>
-      <c r="E140" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C141" s="6">
-        <v>-60.73</v>
-      </c>
-      <c r="D141" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="E141" s="8">
-        <v>58.09</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C142" s="6">
-        <v>-77.09999999999999</v>
-      </c>
-      <c r="D142" s="6">
-        <v>-66.27</v>
-      </c>
-      <c r="E142" s="8">
-        <v>10.83</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C143" s="6">
-        <v>-58.62</v>
-      </c>
-      <c r="D143" s="6">
-        <v>-35.14</v>
-      </c>
-      <c r="E143" s="8">
-        <v>23.48</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5325,60 +2872,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>81</v>
+      <c r="B1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>39.24</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>16</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>34.9</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-7.5</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>-10.4</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>53.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -5480,106 +3027,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.349</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.2963</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>0.2124</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.1431</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>0.1337</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>0.0891</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>0.0407</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="9">
         <v>0.0392</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="9">
         <v>0.0278</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="9">
         <v>0.0005</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="14">
+      <c r="A4" s="9">
         <v>-0.0379</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>-0.0549</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="9">
         <v>-0.0767</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>-0.07980000000000001</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="9">
         <v>-0.096</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="9">
         <v>-0.1273</v>
       </c>
     </row>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="94">
   <si>
     <t>Symbol</t>
   </si>
@@ -199,13 +199,85 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>20.8 → 37.7</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>37.7</t>
+  </si>
+  <si>
+    <t>27.1 → 35.0</t>
+  </si>
+  <si>
+    <t>27.1</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>38.3 → 50.6</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>27.0 → 54.2</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>54.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -236,11 +308,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,8 +346,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,6 +377,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -358,27 +464,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -874,10 +987,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>711.65</v>
+        <v>715.65</v>
       </c>
       <c r="D2">
-        <v>-2.69</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -886,25 +999,25 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-5.4</v>
+        <v>-4.87</v>
       </c>
       <c r="H2">
-        <v>24.64</v>
+        <v>25.34</v>
       </c>
       <c r="I2">
-        <v>-2.33</v>
+        <v>-0.33</v>
       </c>
       <c r="J2">
-        <v>-0.64</v>
+        <v>-0.6</v>
       </c>
       <c r="K2">
-        <v>-2.71</v>
+        <v>-4.87</v>
       </c>
       <c r="L2">
-        <v>-1.77</v>
+        <v>-1.09</v>
       </c>
       <c r="M2">
-        <v>29.63</v>
+        <v>29.28</v>
       </c>
       <c r="N2">
         <v>93</v>
@@ -913,19 +1026,19 @@
         <v>64</v>
       </c>
       <c r="P2">
-        <v>724.39</v>
+        <v>723.92</v>
       </c>
       <c r="Q2">
-        <v>725.0700000000001</v>
+        <v>724.71</v>
       </c>
       <c r="R2">
-        <v>727.21</v>
+        <v>726.76</v>
       </c>
       <c r="S2">
-        <v>688.21</v>
+        <v>688.13</v>
       </c>
       <c r="T2">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -940,34 +1053,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.29</v>
+        <v>46.13</v>
       </c>
       <c r="Z2">
-        <v>-0.49</v>
+        <v>-1.16</v>
       </c>
       <c r="AA2">
-        <v>0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="AB2">
-        <v>-0.58</v>
+        <v>-1</v>
       </c>
       <c r="AC2">
-        <v>42.67</v>
+        <v>26.68</v>
       </c>
       <c r="AD2">
-        <v>46.37</v>
+        <v>40.93</v>
       </c>
       <c r="AE2">
-        <v>16.42</v>
+        <v>16.23</v>
       </c>
       <c r="AF2">
-        <v>-28.91</v>
+        <v>-68.11</v>
       </c>
       <c r="AG2">
-        <v>745.76</v>
+        <v>745.8099999999999</v>
       </c>
       <c r="AH2">
-        <v>704.37</v>
+        <v>703.61</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -976,7 +1089,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>17.62</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -987,10 +1100,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>865</v>
+        <v>853.35</v>
       </c>
       <c r="D3">
-        <v>-5.55</v>
+        <v>-1.35</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -999,25 +1112,25 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-20.02</v>
+        <v>-21.1</v>
       </c>
       <c r="H3">
-        <v>71.17</v>
+        <v>68.86</v>
       </c>
       <c r="I3">
-        <v>-5.41</v>
+        <v>-4.03</v>
       </c>
       <c r="J3">
-        <v>-7.31</v>
+        <v>-12.31</v>
       </c>
       <c r="K3">
-        <v>-3.48</v>
+        <v>-4.16</v>
       </c>
       <c r="L3">
-        <v>-4.43</v>
+        <v>-5.25</v>
       </c>
       <c r="M3">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="N3">
         <v>74</v>
@@ -1026,19 +1139,19 @@
         <v>59</v>
       </c>
       <c r="P3">
-        <v>895.85</v>
+        <v>888.6799999999999</v>
       </c>
       <c r="Q3">
-        <v>945.17</v>
+        <v>939.92</v>
       </c>
       <c r="R3">
-        <v>955.33</v>
+        <v>953.72</v>
       </c>
       <c r="S3">
-        <v>769.0599999999999</v>
+        <v>769.66</v>
       </c>
       <c r="T3">
-        <v>12.47</v>
+        <v>10.87</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1053,43 +1166,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>38.38</v>
+        <v>36.97</v>
       </c>
       <c r="Z3">
-        <v>-15.32</v>
+        <v>-19.55</v>
       </c>
       <c r="AA3">
-        <v>-5.66</v>
+        <v>-8.44</v>
       </c>
       <c r="AB3">
-        <v>-9.66</v>
+        <v>-11.12</v>
       </c>
       <c r="AC3">
-        <v>21.39</v>
+        <v>9.69</v>
       </c>
       <c r="AD3">
-        <v>18.16</v>
+        <v>17.49</v>
       </c>
       <c r="AE3">
-        <v>43.54</v>
+        <v>43.02</v>
       </c>
       <c r="AF3">
-        <v>-35.54</v>
+        <v>-39.35</v>
       </c>
       <c r="AG3">
-        <v>1033.96</v>
+        <v>1037.43</v>
       </c>
       <c r="AH3">
-        <v>856.38</v>
+        <v>842.42</v>
       </c>
       <c r="AI3">
-        <v>1018.42</v>
+        <v>988.8099999999999</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>29.24</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1100,58 +1213,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>195.76</v>
+        <v>198.06</v>
       </c>
       <c r="D4">
-        <v>-2.13</v>
+        <v>1.17</v>
       </c>
       <c r="E4">
-        <v>304.6</v>
+        <v>301.78</v>
       </c>
       <c r="F4">
         <v>195.76</v>
       </c>
       <c r="G4">
-        <v>-35.73</v>
+        <v>-34.37</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="I4">
-        <v>-1.99</v>
+        <v>-0.82</v>
       </c>
       <c r="J4">
-        <v>-5.04</v>
+        <v>-3.52</v>
       </c>
       <c r="K4">
-        <v>-12.38</v>
+        <v>-13.54</v>
       </c>
       <c r="L4">
-        <v>-36.39</v>
+        <v>-34.98</v>
       </c>
       <c r="M4">
-        <v>-7.67</v>
+        <v>-7.37</v>
       </c>
       <c r="N4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O4">
         <v>23</v>
       </c>
       <c r="P4">
-        <v>198.59</v>
+        <v>198.26</v>
       </c>
       <c r="Q4">
-        <v>201</v>
+        <v>200.7</v>
       </c>
       <c r="R4">
-        <v>207.73</v>
+        <v>207.32</v>
       </c>
       <c r="S4">
-        <v>238.87</v>
+        <v>238.55</v>
       </c>
       <c r="T4">
-        <v>-18.05</v>
+        <v>-16.97</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1166,43 +1279,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>30.72</v>
+        <v>38.28</v>
       </c>
       <c r="Z4">
-        <v>-2.98</v>
+        <v>-2.9</v>
       </c>
       <c r="AA4">
-        <v>-3.08</v>
+        <v>-3.05</v>
       </c>
       <c r="AB4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AC4">
-        <v>74.94</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="AD4">
-        <v>63.4</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="AE4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AF4">
-        <v>6.04</v>
+        <v>-30.33</v>
       </c>
       <c r="AG4">
-        <v>205.37</v>
+        <v>205.02</v>
       </c>
       <c r="AH4">
-        <v>196.62</v>
+        <v>196.38</v>
       </c>
       <c r="AI4">
-        <v>208.92</v>
+        <v>207.87</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>36.16</v>
+        <v>40.13</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1213,61 +1326,61 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>592.95</v>
+        <v>589.75</v>
       </c>
       <c r="D5">
-        <v>-2.76</v>
+        <v>-0.54</v>
       </c>
       <c r="E5">
-        <v>912.72</v>
+        <v>908.04</v>
       </c>
       <c r="F5">
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-35.03</v>
+        <v>-35.05</v>
       </c>
       <c r="H5">
-        <v>3.23</v>
+        <v>2.67</v>
       </c>
       <c r="I5">
-        <v>-3.03</v>
+        <v>-2.97</v>
       </c>
       <c r="J5">
-        <v>-3.33</v>
+        <v>-2.95</v>
       </c>
       <c r="K5">
-        <v>-16.92</v>
+        <v>-18.21</v>
       </c>
       <c r="L5">
-        <v>-34.95</v>
+        <v>-35.39</v>
       </c>
       <c r="M5">
-        <v>-7.98</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="N5">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O5">
         <v>20</v>
       </c>
       <c r="P5">
-        <v>608.9</v>
+        <v>605.29</v>
       </c>
       <c r="Q5">
-        <v>650.5599999999999</v>
+        <v>649.89</v>
       </c>
       <c r="R5">
-        <v>650.87</v>
+        <v>649.09</v>
       </c>
       <c r="S5">
-        <v>696.04</v>
+        <v>695.24</v>
       </c>
       <c r="T5">
-        <v>-14.81</v>
+        <v>-15.17</v>
       </c>
       <c r="U5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V5" t="s">
         <v>54</v>
@@ -1276,46 +1389,46 @@
         <v>54</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>36.83</v>
+        <v>36.19</v>
       </c>
       <c r="Z5">
-        <v>-14.48</v>
+        <v>-16.29</v>
       </c>
       <c r="AA5">
-        <v>-7.53</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AB5">
-        <v>-6.96</v>
+        <v>-7.01</v>
       </c>
       <c r="AC5">
-        <v>3.17</v>
+        <v>0.95</v>
       </c>
       <c r="AD5">
-        <v>5.52</v>
+        <v>3.23</v>
       </c>
       <c r="AE5">
-        <v>27.54</v>
+        <v>26.92</v>
       </c>
       <c r="AF5">
-        <v>-79.47</v>
+        <v>-73.45999999999999</v>
       </c>
       <c r="AG5">
-        <v>755.55</v>
+        <v>756.3099999999999</v>
       </c>
       <c r="AH5">
-        <v>545.5599999999999</v>
+        <v>543.47</v>
       </c>
       <c r="AI5">
-        <v>685.0700000000001</v>
+        <v>676.63</v>
       </c>
       <c r="AJ5" t="s">
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>15.32</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1326,10 +1439,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1677.4</v>
+        <v>1656.7</v>
       </c>
       <c r="D6">
-        <v>1.07</v>
+        <v>-1.23</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1338,46 +1451,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-18.64</v>
+        <v>-19.64</v>
       </c>
       <c r="H6">
-        <v>24.45</v>
+        <v>22.91</v>
       </c>
       <c r="I6">
-        <v>1.28</v>
+        <v>-1.56</v>
       </c>
       <c r="J6">
-        <v>-3.51</v>
+        <v>-5.48</v>
       </c>
       <c r="K6">
-        <v>-10.32</v>
+        <v>-10.75</v>
       </c>
       <c r="L6">
-        <v>3.94</v>
+        <v>-0.11</v>
       </c>
       <c r="M6">
-        <v>4.07</v>
+        <v>4.17</v>
       </c>
       <c r="N6">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O6">
         <v>60</v>
       </c>
       <c r="P6">
-        <v>1675.8</v>
+        <v>1670.54</v>
       </c>
       <c r="Q6">
-        <v>1711.27</v>
+        <v>1705.46</v>
       </c>
       <c r="R6">
-        <v>1719.18</v>
+        <v>1716.7</v>
       </c>
       <c r="S6">
-        <v>1703.2</v>
+        <v>1702.36</v>
       </c>
       <c r="T6">
-        <v>-1.51</v>
+        <v>-2.68</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1392,34 +1505,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>44.28</v>
+        <v>40.58</v>
       </c>
       <c r="Z6">
-        <v>-19.07</v>
+        <v>-19.77</v>
       </c>
       <c r="AA6">
-        <v>-16.63</v>
+        <v>-17.25</v>
       </c>
       <c r="AB6">
-        <v>-2.45</v>
+        <v>-2.51</v>
       </c>
       <c r="AC6">
-        <v>27.29</v>
+        <v>28.47</v>
       </c>
       <c r="AD6">
-        <v>26.19</v>
+        <v>26.22</v>
       </c>
       <c r="AE6">
-        <v>49.31</v>
+        <v>49.81</v>
       </c>
       <c r="AF6">
-        <v>127.64</v>
+        <v>27.2</v>
       </c>
       <c r="AG6">
-        <v>1813.96</v>
+        <v>1806.63</v>
       </c>
       <c r="AH6">
-        <v>1608.58</v>
+        <v>1604.3</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1428,7 +1541,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>27.08</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1439,10 +1552,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>951.9</v>
+        <v>955</v>
       </c>
       <c r="D7">
-        <v>-1.71</v>
+        <v>0.33</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1451,25 +1564,25 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-24.47</v>
+        <v>-24.23</v>
       </c>
       <c r="H7">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="I7">
-        <v>0.25</v>
+        <v>-0.21</v>
       </c>
       <c r="J7">
-        <v>-6.22</v>
+        <v>-5.83</v>
       </c>
       <c r="K7">
-        <v>-13.99</v>
+        <v>-14.11</v>
       </c>
       <c r="L7">
-        <v>-15.61</v>
+        <v>-15.67</v>
       </c>
       <c r="M7">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="N7">
         <v>56</v>
@@ -1478,19 +1591,19 @@
         <v>40</v>
       </c>
       <c r="P7">
-        <v>961.4299999999999</v>
+        <v>961.03</v>
       </c>
       <c r="Q7">
-        <v>981.02</v>
+        <v>978.72</v>
       </c>
       <c r="R7">
-        <v>1029.63</v>
+        <v>1026.81</v>
       </c>
       <c r="S7">
-        <v>1104.91</v>
+        <v>1103.81</v>
       </c>
       <c r="T7">
-        <v>-13.85</v>
+        <v>-13.48</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1505,34 +1618,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>36.19</v>
+        <v>37.53</v>
       </c>
       <c r="Z7">
-        <v>-20.18</v>
+        <v>-19.91</v>
       </c>
       <c r="AA7">
-        <v>-20.71</v>
+        <v>-20.55</v>
       </c>
       <c r="AB7">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="AC7">
-        <v>77.08</v>
+        <v>63.43</v>
       </c>
       <c r="AD7">
-        <v>68.93000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="AE7">
-        <v>19.14</v>
+        <v>18.53</v>
       </c>
       <c r="AF7">
-        <v>-30.77</v>
+        <v>-23.48</v>
       </c>
       <c r="AG7">
-        <v>1019.66</v>
+        <v>1017.82</v>
       </c>
       <c r="AH7">
-        <v>942.38</v>
+        <v>939.61</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1541,7 +1654,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>52.5</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1552,10 +1665,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>2996</v>
+        <v>3130</v>
       </c>
       <c r="D8">
-        <v>-2.81</v>
+        <v>4.47</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1564,25 +1677,25 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-47.89</v>
+        <v>-45.56</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="I8">
-        <v>-3.01</v>
+        <v>1.2</v>
       </c>
       <c r="J8">
-        <v>-14.33</v>
+        <v>-10.37</v>
       </c>
       <c r="K8">
-        <v>-17.27</v>
+        <v>-15.18</v>
       </c>
       <c r="L8">
-        <v>-43.05</v>
+        <v>-40.93</v>
       </c>
       <c r="M8">
-        <v>-12.73</v>
+        <v>-11.98</v>
       </c>
       <c r="N8">
         <v>13</v>
@@ -1591,19 +1704,19 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>3073.86</v>
+        <v>3081.3</v>
       </c>
       <c r="Q8">
-        <v>3229.35</v>
+        <v>3216.7</v>
       </c>
       <c r="R8">
-        <v>3498.49</v>
+        <v>3487.62</v>
       </c>
       <c r="S8">
-        <v>4190.94</v>
+        <v>4180</v>
       </c>
       <c r="T8">
-        <v>-28.51</v>
+        <v>-25.12</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1618,34 +1731,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>20.82</v>
+        <v>37.74</v>
       </c>
       <c r="Z8">
-        <v>-130.57</v>
+        <v>-122.13</v>
       </c>
       <c r="AA8">
-        <v>-121.59</v>
+        <v>-121.7</v>
       </c>
       <c r="AB8">
-        <v>-8.970000000000001</v>
+        <v>-0.43</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>36.76</v>
       </c>
       <c r="AD8">
-        <v>11.58</v>
+        <v>19.83</v>
       </c>
       <c r="AE8">
-        <v>85.89</v>
+        <v>91.83</v>
       </c>
       <c r="AF8">
-        <v>-2.53</v>
+        <v>146.94</v>
       </c>
       <c r="AG8">
-        <v>3491.71</v>
+        <v>3472.18</v>
       </c>
       <c r="AH8">
-        <v>2967</v>
+        <v>2961.23</v>
       </c>
       <c r="AI8">
         <v>3326.38</v>
@@ -1654,7 +1767,7 @@
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>61.26</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1665,10 +1778,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>609.3</v>
+        <v>599.25</v>
       </c>
       <c r="D9">
-        <v>-0.98</v>
+        <v>-1.65</v>
       </c>
       <c r="E9">
         <v>1029.69</v>
@@ -1677,46 +1790,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-40.83</v>
+        <v>-41.8</v>
       </c>
       <c r="H9">
-        <v>13.17</v>
+        <v>11.31</v>
       </c>
       <c r="I9">
-        <v>-1.73</v>
+        <v>-2.57</v>
       </c>
       <c r="J9">
-        <v>-2.95</v>
+        <v>-3.67</v>
       </c>
       <c r="K9">
-        <v>-11.03</v>
+        <v>-13.62</v>
       </c>
       <c r="L9">
-        <v>-38.77</v>
+        <v>-39.45</v>
       </c>
       <c r="M9">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="N9">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O9">
         <v>22</v>
       </c>
       <c r="P9">
-        <v>617.11</v>
+        <v>613.95</v>
       </c>
       <c r="Q9">
-        <v>652.96</v>
+        <v>651.99</v>
       </c>
       <c r="R9">
-        <v>655.41</v>
+        <v>653.88</v>
       </c>
       <c r="S9">
-        <v>659.0700000000001</v>
+        <v>658.54</v>
       </c>
       <c r="T9">
-        <v>-7.55</v>
+        <v>-9</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1731,43 +1844,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>37.53</v>
+        <v>35.01</v>
       </c>
       <c r="Z9">
-        <v>-11.58</v>
+        <v>-13.35</v>
       </c>
       <c r="AA9">
-        <v>-5.73</v>
+        <v>-7.25</v>
       </c>
       <c r="AB9">
-        <v>-5.86</v>
+        <v>-6.1</v>
       </c>
       <c r="AC9">
-        <v>5.24</v>
+        <v>1.22</v>
       </c>
       <c r="AD9">
-        <v>6.41</v>
+        <v>4.69</v>
       </c>
       <c r="AE9">
-        <v>21.23</v>
+        <v>20.7</v>
       </c>
       <c r="AF9">
-        <v>-77.59</v>
+        <v>-87.64</v>
       </c>
       <c r="AG9">
-        <v>723.7</v>
+        <v>725.21</v>
       </c>
       <c r="AH9">
-        <v>582.23</v>
+        <v>578.76</v>
       </c>
       <c r="AI9">
-        <v>675.8</v>
+        <v>665.02</v>
       </c>
       <c r="AJ9" t="s">
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>17.08</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1778,10 +1891,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>335.65</v>
+        <v>342.15</v>
       </c>
       <c r="D10">
-        <v>-2.75</v>
+        <v>1.94</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1790,25 +1903,25 @@
         <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-27.32</v>
+        <v>-25.91</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="I10">
-        <v>-6.5</v>
+        <v>-2.28</v>
       </c>
       <c r="J10">
-        <v>-8.220000000000001</v>
+        <v>-6.4</v>
       </c>
       <c r="K10">
-        <v>-10.61</v>
+        <v>-10.27</v>
       </c>
       <c r="L10">
-        <v>-15</v>
+        <v>-13.5</v>
       </c>
       <c r="M10">
-        <v>14.31</v>
+        <v>12.95</v>
       </c>
       <c r="N10">
         <v>62</v>
@@ -1817,19 +1930,19 @@
         <v>42</v>
       </c>
       <c r="P10">
-        <v>346.82</v>
+        <v>345.22</v>
       </c>
       <c r="Q10">
-        <v>360.85</v>
+        <v>359.45</v>
       </c>
       <c r="R10">
-        <v>367.81</v>
+        <v>367.11</v>
       </c>
       <c r="S10">
-        <v>385.96</v>
+        <v>385.76</v>
       </c>
       <c r="T10">
-        <v>-13.03</v>
+        <v>-11.31</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1844,43 +1957,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>27.08</v>
+        <v>34.99</v>
       </c>
       <c r="Z10">
-        <v>-6.26</v>
+        <v>-6.71</v>
       </c>
       <c r="AA10">
-        <v>-3.84</v>
+        <v>-4.41</v>
       </c>
       <c r="AB10">
-        <v>-2.42</v>
+        <v>-2.29</v>
       </c>
       <c r="AC10">
-        <v>2.92</v>
+        <v>11.16</v>
       </c>
       <c r="AD10">
-        <v>4.66</v>
+        <v>6.54</v>
       </c>
       <c r="AE10">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AF10">
-        <v>62.18</v>
+        <v>10.83</v>
       </c>
       <c r="AG10">
-        <v>380.17</v>
+        <v>379.97</v>
       </c>
       <c r="AH10">
-        <v>341.53</v>
+        <v>338.94</v>
       </c>
       <c r="AI10">
-        <v>365.04</v>
+        <v>362.14</v>
       </c>
       <c r="AJ10" t="s">
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>39.48</v>
+        <v>42.41</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1891,10 +2004,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>171.96</v>
+        <v>173.8</v>
       </c>
       <c r="D11">
-        <v>-2.1</v>
+        <v>1.07</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1903,46 +2016,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-20.63</v>
+        <v>-19.78</v>
       </c>
       <c r="H11">
-        <v>9.24</v>
+        <v>10.41</v>
       </c>
       <c r="I11">
-        <v>-6.7</v>
+        <v>-2.36</v>
       </c>
       <c r="J11">
-        <v>-7.35</v>
+        <v>-5.62</v>
       </c>
       <c r="K11">
-        <v>-8.49</v>
+        <v>-9.1</v>
       </c>
       <c r="L11">
-        <v>1.33</v>
+        <v>4.31</v>
       </c>
       <c r="M11">
-        <v>8.91</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N11">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="O11">
         <v>60</v>
       </c>
       <c r="P11">
-        <v>176.49</v>
+        <v>175.65</v>
       </c>
       <c r="Q11">
-        <v>183.71</v>
+        <v>182.96</v>
       </c>
       <c r="R11">
-        <v>185.49</v>
+        <v>185.22</v>
       </c>
       <c r="S11">
-        <v>192.13</v>
+        <v>192.18</v>
       </c>
       <c r="T11">
-        <v>-10.5</v>
+        <v>-9.56</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -1957,43 +2070,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>31.57</v>
+        <v>35.47</v>
       </c>
       <c r="Z11">
-        <v>-2.58</v>
+        <v>-2.92</v>
       </c>
       <c r="AA11">
-        <v>-1.17</v>
+        <v>-1.52</v>
       </c>
       <c r="AB11">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="AC11">
-        <v>2.28</v>
+        <v>4.87</v>
       </c>
       <c r="AD11">
-        <v>2.57</v>
+        <v>3.29</v>
       </c>
       <c r="AE11">
-        <v>4.77</v>
+        <v>4.73</v>
       </c>
       <c r="AF11">
-        <v>18.14</v>
+        <v>-50.38</v>
       </c>
       <c r="AG11">
-        <v>193.54</v>
+        <v>193.43</v>
       </c>
       <c r="AH11">
-        <v>173.89</v>
+        <v>172.5</v>
       </c>
       <c r="AI11">
-        <v>187.77</v>
+        <v>186.52</v>
       </c>
       <c r="AJ11" t="s">
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>33.8</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2004,10 +2117,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2076</v>
+        <v>2156</v>
       </c>
       <c r="D12">
-        <v>-0.21</v>
+        <v>3.85</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2016,25 +2129,25 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-35.56</v>
+        <v>-33.08</v>
       </c>
       <c r="H12">
-        <v>4.71</v>
+        <v>8.75</v>
       </c>
       <c r="I12">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="J12">
-        <v>-8.550000000000001</v>
+        <v>-4.41</v>
       </c>
       <c r="K12">
-        <v>1.29</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
-        <v>-25.9</v>
+        <v>-25.27</v>
       </c>
       <c r="M12">
-        <v>-9.6</v>
+        <v>-7.71</v>
       </c>
       <c r="N12">
         <v>68</v>
@@ -2043,19 +2156,19 @@
         <v>41</v>
       </c>
       <c r="P12">
-        <v>2089.14</v>
+        <v>2105.34</v>
       </c>
       <c r="Q12">
-        <v>2121.97</v>
+        <v>2119.37</v>
       </c>
       <c r="R12">
-        <v>2260.03</v>
+        <v>2254.22</v>
       </c>
       <c r="S12">
-        <v>2462.61</v>
+        <v>2457.49</v>
       </c>
       <c r="T12">
-        <v>-15.7</v>
+        <v>-12.27</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2070,34 +2183,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>38.27</v>
+        <v>50.61</v>
       </c>
       <c r="Z12">
-        <v>-50.39</v>
+        <v>-42.01</v>
       </c>
       <c r="AA12">
-        <v>-53.94</v>
+        <v>-51.55</v>
       </c>
       <c r="AB12">
-        <v>3.54</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AC12">
-        <v>77.34999999999999</v>
+        <v>81.14</v>
       </c>
       <c r="AD12">
-        <v>77.41</v>
+        <v>80.16</v>
       </c>
       <c r="AE12">
-        <v>57.86</v>
+        <v>62.87</v>
       </c>
       <c r="AF12">
-        <v>33.34</v>
+        <v>253.23</v>
       </c>
       <c r="AG12">
-        <v>2245.88</v>
+        <v>2237.74</v>
       </c>
       <c r="AH12">
-        <v>1998.06</v>
+        <v>2001</v>
       </c>
       <c r="AI12">
         <v>2235.3</v>
@@ -2106,7 +2219,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>29.69</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2117,10 +2230,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4359.5</v>
+        <v>4410</v>
       </c>
       <c r="D13">
-        <v>-0.4</v>
+        <v>1.16</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2129,25 +2242,25 @@
         <v>3418.2</v>
       </c>
       <c r="G13">
-        <v>-15.66</v>
+        <v>-14.69</v>
       </c>
       <c r="H13">
-        <v>27.54</v>
+        <v>29.02</v>
       </c>
       <c r="I13">
-        <v>-4.96</v>
+        <v>-2.34</v>
       </c>
       <c r="J13">
-        <v>-12.72</v>
+        <v>-11.57</v>
       </c>
       <c r="K13">
-        <v>-4.31</v>
+        <v>-3.8</v>
       </c>
       <c r="L13">
-        <v>26.24</v>
+        <v>28.74</v>
       </c>
       <c r="M13">
-        <v>13.37</v>
+        <v>13.61</v>
       </c>
       <c r="N13">
         <v>99</v>
@@ -2156,19 +2269,19 @@
         <v>75</v>
       </c>
       <c r="P13">
-        <v>4476.44</v>
+        <v>4455.3</v>
       </c>
       <c r="Q13">
-        <v>4765.16</v>
+        <v>4735.41</v>
       </c>
       <c r="R13">
-        <v>4925.93</v>
+        <v>4917.13</v>
       </c>
       <c r="S13">
-        <v>4419.48</v>
+        <v>4421.88</v>
       </c>
       <c r="T13">
-        <v>-1.36</v>
+        <v>-0.27</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2183,34 +2296,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>24.8</v>
+        <v>29.33</v>
       </c>
       <c r="Z13">
-        <v>-138.05</v>
+        <v>-144.1</v>
       </c>
       <c r="AA13">
-        <v>-88.62</v>
+        <v>-99.70999999999999</v>
       </c>
       <c r="AB13">
-        <v>-49.44</v>
+        <v>-44.38</v>
       </c>
       <c r="AC13">
-        <v>7.26</v>
+        <v>6.55</v>
       </c>
       <c r="AD13">
-        <v>13.43</v>
+        <v>10.11</v>
       </c>
       <c r="AE13">
-        <v>100.89</v>
+        <v>98.77</v>
       </c>
       <c r="AF13">
-        <v>94.87</v>
+        <v>-27.22</v>
       </c>
       <c r="AG13">
-        <v>5172.92</v>
+        <v>5156.11</v>
       </c>
       <c r="AH13">
-        <v>4357.4</v>
+        <v>4314.71</v>
       </c>
       <c r="AI13">
         <v>4688.95</v>
@@ -2219,7 +2332,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>61.17</v>
+        <v>62.94</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2230,10 +2343,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2876.3</v>
+        <v>2918.2</v>
       </c>
       <c r="D14">
-        <v>-0.48</v>
+        <v>1.46</v>
       </c>
       <c r="E14">
         <v>4807.3</v>
@@ -2242,25 +2355,25 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-40.17</v>
+        <v>-39.3</v>
       </c>
       <c r="H14">
-        <v>31.1</v>
+        <v>33.01</v>
       </c>
       <c r="I14">
-        <v>9.720000000000001</v>
+        <v>13.11</v>
       </c>
       <c r="J14">
-        <v>2.2</v>
+        <v>4.46</v>
       </c>
       <c r="K14">
-        <v>-0.96</v>
+        <v>0.53</v>
       </c>
       <c r="L14">
-        <v>-40.18</v>
+        <v>-38.83</v>
       </c>
       <c r="M14">
-        <v>21.24</v>
+        <v>21.62</v>
       </c>
       <c r="N14">
         <v>50</v>
@@ -2269,19 +2382,19 @@
         <v>36</v>
       </c>
       <c r="P14">
-        <v>2766.52</v>
+        <v>2834.16</v>
       </c>
       <c r="Q14">
-        <v>2750.53</v>
+        <v>2755.44</v>
       </c>
       <c r="R14">
-        <v>2870.21</v>
+        <v>2868.47</v>
       </c>
       <c r="S14">
-        <v>2831.61</v>
+        <v>2825.92</v>
       </c>
       <c r="T14">
-        <v>1.58</v>
+        <v>3.27</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2296,34 +2409,34 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>58.18</v>
+        <v>61.06</v>
       </c>
       <c r="Z14">
-        <v>-21.19</v>
+        <v>-6.99</v>
       </c>
       <c r="AA14">
-        <v>-48.26</v>
+        <v>-40.01</v>
       </c>
       <c r="AB14">
-        <v>27.07</v>
+        <v>33.02</v>
       </c>
       <c r="AC14">
         <v>96.01000000000001</v>
       </c>
       <c r="AD14">
-        <v>64.88</v>
+        <v>85.78</v>
       </c>
       <c r="AE14">
-        <v>74.77</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="AF14">
-        <v>26.51</v>
+        <v>-30.32</v>
       </c>
       <c r="AG14">
-        <v>2954.68</v>
+        <v>2971.03</v>
       </c>
       <c r="AH14">
-        <v>2546.39</v>
+        <v>2539.86</v>
       </c>
       <c r="AI14">
         <v>2677.8</v>
@@ -2332,7 +2445,7 @@
         <v>56</v>
       </c>
       <c r="AK14">
-        <v>50.98</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2343,58 +2456,58 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>191.78</v>
+        <v>216.94</v>
       </c>
       <c r="D15">
-        <v>-3.15</v>
+        <v>13.12</v>
       </c>
       <c r="E15">
-        <v>367.5</v>
+        <v>365.95</v>
       </c>
       <c r="F15">
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-47.81</v>
+        <v>-40.72</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>13.12</v>
       </c>
       <c r="I15">
-        <v>-3.05</v>
+        <v>12.8</v>
       </c>
       <c r="J15">
-        <v>-18.44</v>
+        <v>-6.08</v>
       </c>
       <c r="K15">
-        <v>-17.76</v>
+        <v>-7.68</v>
       </c>
       <c r="L15">
-        <v>-49.62</v>
+        <v>-40.97</v>
       </c>
       <c r="M15">
-        <v>2.78</v>
+        <v>5.63</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="O15">
         <v>7</v>
       </c>
       <c r="P15">
-        <v>194.49</v>
+        <v>199.41</v>
       </c>
       <c r="Q15">
-        <v>209.68</v>
+        <v>209.09</v>
       </c>
       <c r="R15">
-        <v>221.92</v>
+        <v>221.65</v>
       </c>
       <c r="S15">
-        <v>246.87</v>
+        <v>246.43</v>
       </c>
       <c r="T15">
-        <v>-22.32</v>
+        <v>-11.97</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2409,34 +2522,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>26.97</v>
+        <v>54.23</v>
       </c>
       <c r="Z15">
-        <v>-8.66</v>
+        <v>-6.84</v>
       </c>
       <c r="AA15">
-        <v>-7.09</v>
+        <v>-7.04</v>
       </c>
       <c r="AB15">
-        <v>-1.57</v>
+        <v>0.2</v>
       </c>
       <c r="AC15">
-        <v>38.63</v>
+        <v>60.32</v>
       </c>
       <c r="AD15">
-        <v>29.49</v>
+        <v>44.05</v>
       </c>
       <c r="AE15">
-        <v>7.87</v>
+        <v>9.74</v>
       </c>
       <c r="AF15">
-        <v>-2.64</v>
+        <v>297.67</v>
       </c>
       <c r="AG15">
-        <v>232.01</v>
+        <v>229.85</v>
       </c>
       <c r="AH15">
-        <v>187.36</v>
+        <v>188.33</v>
       </c>
       <c r="AI15">
         <v>218.86</v>
@@ -2445,7 +2558,7 @@
         <v>57</v>
       </c>
       <c r="AK15">
-        <v>42.74</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2456,10 +2569,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>32.95</v>
+        <v>32.89</v>
       </c>
       <c r="D16">
-        <v>-3.12</v>
+        <v>-0.18</v>
       </c>
       <c r="E16">
         <v>58.68</v>
@@ -2468,46 +2581,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-43.85</v>
+        <v>-43.95</v>
       </c>
       <c r="H16">
-        <v>5.07</v>
+        <v>4.88</v>
       </c>
       <c r="I16">
-        <v>-3.94</v>
+        <v>-5.54</v>
       </c>
       <c r="J16">
-        <v>-11.78</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="K16">
-        <v>-18.62</v>
+        <v>-20.32</v>
       </c>
       <c r="L16">
-        <v>-41.71</v>
+        <v>-42.52</v>
       </c>
       <c r="M16">
-        <v>-5.49</v>
+        <v>-6.44</v>
       </c>
       <c r="N16">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="P16">
-        <v>34.06</v>
+        <v>33.67</v>
       </c>
       <c r="Q16">
-        <v>35.17</v>
+        <v>35.01</v>
       </c>
       <c r="R16">
-        <v>37.14</v>
+        <v>37</v>
       </c>
       <c r="S16">
-        <v>41.39</v>
+        <v>41.3</v>
       </c>
       <c r="T16">
-        <v>-20.39</v>
+        <v>-20.37</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2522,43 +2635,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>32.82</v>
+        <v>32.57</v>
       </c>
       <c r="Z16">
-        <v>-0.99</v>
+        <v>-1.05</v>
       </c>
       <c r="AA16">
-        <v>-0.88</v>
+        <v>-0.91</v>
       </c>
       <c r="AB16">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="AC16">
-        <v>24.33</v>
+        <v>10.05</v>
       </c>
       <c r="AD16">
-        <v>38.69</v>
+        <v>24.84</v>
       </c>
       <c r="AE16">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>-66.27</v>
+        <v>-75.8</v>
       </c>
       <c r="AG16">
-        <v>37</v>
+        <v>37.05</v>
       </c>
       <c r="AH16">
-        <v>33.34</v>
+        <v>32.97</v>
       </c>
       <c r="AI16">
-        <v>37.14</v>
+        <v>36.59</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>15.46</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2569,10 +2682,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1032</v>
+        <v>1033.7</v>
       </c>
       <c r="D17">
-        <v>-2.35</v>
+        <v>0.16</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2581,25 +2694,25 @@
         <v>1032</v>
       </c>
       <c r="G17">
-        <v>-33.69</v>
+        <v>-33.58</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I17">
-        <v>-3.55</v>
+        <v>-1.85</v>
       </c>
       <c r="J17">
-        <v>-11.58</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="K17">
-        <v>-18.7</v>
+        <v>-19.66</v>
       </c>
       <c r="L17">
-        <v>-23.9</v>
+        <v>-24.13</v>
       </c>
       <c r="M17">
-        <v>-3.79</v>
+        <v>-4.1</v>
       </c>
       <c r="N17">
         <v>44</v>
@@ -2608,19 +2721,19 @@
         <v>25</v>
       </c>
       <c r="P17">
-        <v>1054.24</v>
+        <v>1050.34</v>
       </c>
       <c r="Q17">
-        <v>1107.62</v>
+        <v>1102.12</v>
       </c>
       <c r="R17">
-        <v>1192.34</v>
+        <v>1186.75</v>
       </c>
       <c r="S17">
-        <v>1323.49</v>
+        <v>1321.81</v>
       </c>
       <c r="T17">
-        <v>-22.02</v>
+        <v>-21.8</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2635,43 +2748,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>30.14</v>
+        <v>30.65</v>
       </c>
       <c r="Z17">
-        <v>-39.86</v>
+        <v>-40.69</v>
       </c>
       <c r="AA17">
-        <v>-36.72</v>
+        <v>-37.51</v>
       </c>
       <c r="AB17">
-        <v>-3.14</v>
+        <v>-3.18</v>
       </c>
       <c r="AC17">
-        <v>27.55</v>
+        <v>14.47</v>
       </c>
       <c r="AD17">
-        <v>30.77</v>
+        <v>25.72</v>
       </c>
       <c r="AE17">
-        <v>29.9</v>
+        <v>29.19</v>
       </c>
       <c r="AF17">
-        <v>-35.14</v>
+        <v>-68.88</v>
       </c>
       <c r="AG17">
-        <v>1185.39</v>
+        <v>1184.55</v>
       </c>
       <c r="AH17">
-        <v>1029.85</v>
+        <v>1019.68</v>
       </c>
       <c r="AI17">
-        <v>1130.86</v>
+        <v>1126.12</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>50.49</v>
+        <v>53.34</v>
       </c>
     </row>
   </sheetData>
@@ -2812,7 +2925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2832,27 +2945,2469 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>61</v>
+      <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.64</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-7.31</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-12.31</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.33</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-5.48</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-6.22</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-5.83</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-14.33</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-10.37</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-6.4</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-7.35</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-5.62</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-4.41</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-12.72</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-11.57</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2.2</v>
+      </c>
+      <c r="D24" s="6">
+        <v>4.46</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-18.44</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-6.08</v>
+      </c>
+      <c r="E25" s="7">
+        <v>12.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-11.78</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-11.58</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-2.33</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-4.03</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-1.99</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-0.82</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-3.03</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1.28</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-1.56</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-0.21</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-3.01</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="E34" s="7">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-1.73</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-2.57</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-6.5</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-2.28</v>
+      </c>
+      <c r="E36" s="7">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-2.36</v>
+      </c>
+      <c r="E37" s="7">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1.24</v>
+      </c>
+      <c r="D38" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-4.96</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-2.34</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="6">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D40" s="6">
+        <v>13.11</v>
+      </c>
+      <c r="E40" s="7">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-3.05</v>
+      </c>
+      <c r="D41" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="E41" s="7">
+        <v>15.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-3.94</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-5.54</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-3.55</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-1.77</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-1.09</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-4.43</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-5.25</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-36.39</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-34.98</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-34.95</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-35.39</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="6">
+        <v>3.94</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-0.11</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-4.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-15.61</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-15.67</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-43.05</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-40.93</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-38.77</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-39.45</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-15</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-13.5</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="D53" s="6">
+        <v>4.31</v>
+      </c>
+      <c r="E53" s="7">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-25.9</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-25.27</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="6">
+        <v>26.24</v>
+      </c>
+      <c r="D55" s="6">
+        <v>28.74</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-40.18</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-38.83</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-49.62</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-40.97</v>
+      </c>
+      <c r="E57" s="7">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-41.71</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-42.52</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-23.9</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-24.13</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-2.71</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-3.48</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-4.16</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-12.38</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-13.54</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-16.92</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-18.21</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-10.32</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-10.75</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-13.99</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-14.11</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-17.27</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-15.18</v>
+      </c>
+      <c r="E66" s="7">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-11.03</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-13.62</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-10.61</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-10.27</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-8.49</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-9.1</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="D70" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="E70" s="7">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-4.31</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-3.8</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-0.96</v>
+      </c>
+      <c r="D72" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="E72" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-17.76</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-7.68</v>
+      </c>
+      <c r="E73" s="7">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-18.62</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-20.32</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-18.7</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-19.66</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-5.4</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="E76" s="7">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-20.02</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-21.1</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-35.73</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-34.37</v>
+      </c>
+      <c r="E78" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-35.03</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-35.05</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-18.64</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-19.64</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-24.47</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-24.23</v>
+      </c>
+      <c r="E81" s="7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-47.89</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-45.56</v>
+      </c>
+      <c r="E82" s="7">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6">
+        <v>-40.83</v>
+      </c>
+      <c r="D83" s="6">
+        <v>-41.8</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6">
+        <v>-27.32</v>
+      </c>
+      <c r="D84" s="6">
+        <v>-25.91</v>
+      </c>
+      <c r="E84" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6">
+        <v>-20.63</v>
+      </c>
+      <c r="D85" s="6">
+        <v>-19.78</v>
+      </c>
+      <c r="E85" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="6">
+        <v>-35.56</v>
+      </c>
+      <c r="D86" s="6">
+        <v>-33.08</v>
+      </c>
+      <c r="E86" s="7">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="6">
+        <v>-15.66</v>
+      </c>
+      <c r="D87" s="6">
+        <v>-14.69</v>
+      </c>
+      <c r="E87" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="6">
+        <v>-40.17</v>
+      </c>
+      <c r="D88" s="6">
+        <v>-39.3</v>
+      </c>
+      <c r="E88" s="7">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6">
+        <v>-47.81</v>
+      </c>
+      <c r="D89" s="6">
+        <v>-40.72</v>
+      </c>
+      <c r="E89" s="7">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="6">
+        <v>-43.85</v>
+      </c>
+      <c r="D90" s="6">
+        <v>-43.95</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="6">
+        <v>-33.69</v>
+      </c>
+      <c r="D91" s="6">
+        <v>-33.58</v>
+      </c>
+      <c r="E91" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="6">
+        <v>711.65</v>
+      </c>
+      <c r="D92" s="6">
+        <v>715.65</v>
+      </c>
+      <c r="E92" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C93" s="6">
+        <v>865</v>
+      </c>
+      <c r="D93" s="6">
+        <v>853.35</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-11.65</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="6">
+        <v>195.76</v>
+      </c>
+      <c r="D94" s="6">
+        <v>198.06</v>
+      </c>
+      <c r="E94" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" s="6">
+        <v>592.95</v>
+      </c>
+      <c r="D95" s="6">
+        <v>589.75</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C96" s="6">
+        <v>1677.4</v>
+      </c>
+      <c r="D96" s="6">
+        <v>1656.7</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-20.7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="6">
+        <v>951.9</v>
+      </c>
+      <c r="D97" s="6">
+        <v>955</v>
+      </c>
+      <c r="E97" s="7">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C98" s="6">
+        <v>2996</v>
+      </c>
+      <c r="D98" s="6">
+        <v>3130</v>
+      </c>
+      <c r="E98" s="7">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C99" s="6">
+        <v>609.3</v>
+      </c>
+      <c r="D99" s="6">
+        <v>599.25</v>
+      </c>
+      <c r="E99" s="8">
+        <v>-10.05</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100" s="6">
+        <v>335.65</v>
+      </c>
+      <c r="D100" s="6">
+        <v>342.15</v>
+      </c>
+      <c r="E100" s="7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="6">
+        <v>171.96</v>
+      </c>
+      <c r="D101" s="6">
+        <v>173.8</v>
+      </c>
+      <c r="E101" s="7">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C102" s="6">
+        <v>2076</v>
+      </c>
+      <c r="D102" s="6">
+        <v>2156</v>
+      </c>
+      <c r="E102" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="6">
+        <v>4359.5</v>
+      </c>
+      <c r="D103" s="6">
+        <v>4410</v>
+      </c>
+      <c r="E103" s="7">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" s="6">
+        <v>2876.3</v>
+      </c>
+      <c r="D104" s="6">
+        <v>2918.2</v>
+      </c>
+      <c r="E104" s="7">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" s="6">
+        <v>191.78</v>
+      </c>
+      <c r="D105" s="6">
+        <v>216.94</v>
+      </c>
+      <c r="E105" s="7">
+        <v>25.16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="6">
+        <v>32.95</v>
+      </c>
+      <c r="D106" s="6">
+        <v>32.89</v>
+      </c>
+      <c r="E106" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" s="6">
+        <v>1032</v>
+      </c>
+      <c r="D107" s="6">
+        <v>1033.7</v>
+      </c>
+      <c r="E107" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="6">
+        <v>32</v>
+      </c>
+      <c r="D108" s="6">
+        <v>38</v>
+      </c>
+      <c r="E108" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="6">
+        <v>26</v>
+      </c>
+      <c r="D109" s="6">
+        <v>19</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="6">
+        <v>87</v>
+      </c>
+      <c r="D110" s="6">
+        <v>81</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="6">
+        <v>38</v>
+      </c>
+      <c r="D111" s="6">
+        <v>26</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="6">
+        <v>81</v>
+      </c>
+      <c r="D112" s="6">
+        <v>87</v>
+      </c>
+      <c r="E112" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="6">
+        <v>7</v>
+      </c>
+      <c r="D113" s="6">
+        <v>32</v>
+      </c>
+      <c r="E113" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="6">
+        <v>19</v>
+      </c>
+      <c r="D114" s="6">
+        <v>7</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" s="6">
+        <v>44.29</v>
+      </c>
+      <c r="D115" s="6">
+        <v>46.13</v>
+      </c>
+      <c r="E115" s="7">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" s="6">
+        <v>38.38</v>
+      </c>
+      <c r="D116" s="6">
+        <v>36.97</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" s="6">
+        <v>30.72</v>
+      </c>
+      <c r="D117" s="6">
+        <v>38.28</v>
+      </c>
+      <c r="E117" s="7">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" s="6">
+        <v>36.83</v>
+      </c>
+      <c r="D118" s="6">
+        <v>36.19</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" s="6">
+        <v>44.28</v>
+      </c>
+      <c r="D119" s="6">
+        <v>40.58</v>
+      </c>
+      <c r="E119" s="8">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" s="6">
+        <v>36.19</v>
+      </c>
+      <c r="D120" s="6">
+        <v>37.53</v>
+      </c>
+      <c r="E120" s="7">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" s="6">
+        <v>20.82</v>
+      </c>
+      <c r="D121" s="6">
+        <v>37.74</v>
+      </c>
+      <c r="E121" s="7">
+        <v>16.92</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" s="6">
+        <v>37.53</v>
+      </c>
+      <c r="D122" s="6">
+        <v>35.01</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" s="6">
+        <v>27.08</v>
+      </c>
+      <c r="D123" s="6">
+        <v>34.99</v>
+      </c>
+      <c r="E123" s="7">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" s="6">
+        <v>31.57</v>
+      </c>
+      <c r="D124" s="6">
+        <v>35.47</v>
+      </c>
+      <c r="E124" s="7">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" s="6">
+        <v>38.27</v>
+      </c>
+      <c r="D125" s="6">
+        <v>50.61</v>
+      </c>
+      <c r="E125" s="7">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" s="6">
+        <v>24.8</v>
+      </c>
+      <c r="D126" s="6">
+        <v>29.33</v>
+      </c>
+      <c r="E126" s="7">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" s="6">
+        <v>58.18</v>
+      </c>
+      <c r="D127" s="6">
+        <v>61.06</v>
+      </c>
+      <c r="E127" s="7">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" s="6">
+        <v>26.97</v>
+      </c>
+      <c r="D128" s="6">
+        <v>54.23</v>
+      </c>
+      <c r="E128" s="7">
+        <v>27.26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" s="6">
+        <v>32.82</v>
+      </c>
+      <c r="D129" s="6">
+        <v>32.57</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" s="6">
+        <v>30.14</v>
+      </c>
+      <c r="D130" s="6">
+        <v>30.65</v>
+      </c>
+      <c r="E130" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C131" s="6">
+        <v>-28.91</v>
+      </c>
+      <c r="D131" s="6">
+        <v>-68.11</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-39.2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" s="6">
+        <v>-35.54</v>
+      </c>
+      <c r="D132" s="6">
+        <v>-39.35</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-3.81</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C133" s="6">
+        <v>6.04</v>
+      </c>
+      <c r="D133" s="6">
+        <v>-30.33</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-36.37</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C134" s="6">
+        <v>-79.47</v>
+      </c>
+      <c r="D134" s="6">
+        <v>-73.45999999999999</v>
+      </c>
+      <c r="E134" s="7">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C135" s="6">
+        <v>127.64</v>
+      </c>
+      <c r="D135" s="6">
+        <v>27.2</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-100.44</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="6">
+        <v>-30.77</v>
+      </c>
+      <c r="D136" s="6">
+        <v>-23.48</v>
+      </c>
+      <c r="E136" s="7">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" s="6">
+        <v>-2.53</v>
+      </c>
+      <c r="D137" s="6">
+        <v>146.94</v>
+      </c>
+      <c r="E137" s="7">
+        <v>149.47</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" s="6">
+        <v>-77.59</v>
+      </c>
+      <c r="D138" s="6">
+        <v>-87.64</v>
+      </c>
+      <c r="E138" s="8">
+        <v>-10.05</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" s="6">
+        <v>62.18</v>
+      </c>
+      <c r="D139" s="6">
+        <v>10.83</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-51.35</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="6">
+        <v>18.14</v>
+      </c>
+      <c r="D140" s="6">
+        <v>-50.38</v>
+      </c>
+      <c r="E140" s="8">
+        <v>-68.52</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="6">
+        <v>33.34</v>
+      </c>
+      <c r="D141" s="6">
+        <v>253.23</v>
+      </c>
+      <c r="E141" s="7">
+        <v>219.89</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="6">
+        <v>94.87</v>
+      </c>
+      <c r="D142" s="6">
+        <v>-27.22</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-122.09</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6">
+        <v>26.51</v>
+      </c>
+      <c r="D143" s="6">
+        <v>-30.32</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-56.83</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="D144" s="6">
+        <v>297.67</v>
+      </c>
+      <c r="E144" s="7">
+        <v>300.31</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="6">
+        <v>-66.27</v>
+      </c>
+      <c r="D145" s="6">
+        <v>-75.8</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-9.529999999999999</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="6">
+        <v>-35.14</v>
+      </c>
+      <c r="D146" s="6">
+        <v>-68.88</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-33.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2872,60 +5427,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>69</v>
+      <c r="B1" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>39.24</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="12">
         <v>16</v>
       </c>
-      <c r="D2" s="6">
-        <v>34.9</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="11">
+        <v>39.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="6">
-        <v>-7.5</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-10.4</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="11">
+        <v>-5.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-10</v>
+      </c>
+      <c r="H2" s="11">
         <v>53.1</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3027,107 +5582,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="9">
-        <v>0.349</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.2963</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.2124</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.1431</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.1337</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.0891</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.0407</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0.0392</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0.0278</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0.0005</v>
+      <c r="A2" s="14">
+        <v>0.346</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2928</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2162</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1361</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1295</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.08960000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0563</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.0417</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0.0405</v>
+      </c>
+      <c r="J2" s="14">
+        <v>0.002</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="9">
-        <v>-0.0379</v>
-      </c>
-      <c r="B4" s="9">
-        <v>-0.0549</v>
-      </c>
-      <c r="C4" s="9">
-        <v>-0.0767</v>
-      </c>
-      <c r="D4" s="9">
-        <v>-0.07980000000000001</v>
-      </c>
-      <c r="E4" s="9">
-        <v>-0.096</v>
-      </c>
-      <c r="F4" s="9">
-        <v>-0.1273</v>
+      <c r="A4" s="14">
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="B4" s="14">
+        <v>-0.0644</v>
+      </c>
+      <c r="C4" s="14">
+        <v>-0.0737</v>
+      </c>
+      <c r="D4" s="14">
+        <v>-0.0771</v>
+      </c>
+      <c r="E4" s="14">
+        <v>-0.0814</v>
+      </c>
+      <c r="F4" s="14">
+        <v>-0.1198</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -1023,7 +1023,7 @@
         <v>93</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P2">
         <v>723.92</v>
@@ -1136,7 +1136,7 @@
         <v>74</v>
       </c>
       <c r="O3">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P3">
         <v>888.6799999999999</v>
@@ -1475,7 +1475,7 @@
         <v>81</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P6">
         <v>1670.54</v>
@@ -1588,7 +1588,7 @@
         <v>56</v>
       </c>
       <c r="O7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P7">
         <v>961.03</v>
@@ -1701,7 +1701,7 @@
         <v>13</v>
       </c>
       <c r="O8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P8">
         <v>3081.3</v>
@@ -1814,7 +1814,7 @@
         <v>26</v>
       </c>
       <c r="O9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P9">
         <v>613.95</v>
@@ -1927,7 +1927,7 @@
         <v>62</v>
       </c>
       <c r="O10">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P10">
         <v>345.22</v>
@@ -2040,7 +2040,7 @@
         <v>87</v>
       </c>
       <c r="O11">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P11">
         <v>175.65</v>
@@ -2153,7 +2153,7 @@
         <v>68</v>
       </c>
       <c r="O12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P12">
         <v>2105.34</v>
@@ -2266,7 +2266,7 @@
         <v>99</v>
       </c>
       <c r="O13">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P13">
         <v>4455.3</v>
@@ -2379,7 +2379,7 @@
         <v>50</v>
       </c>
       <c r="O14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P14">
         <v>2834.16</v>
@@ -2492,7 +2492,7 @@
         <v>32</v>
       </c>
       <c r="O15">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="P15">
         <v>199.41</v>
@@ -2718,7 +2718,7 @@
         <v>44</v>
       </c>
       <c r="O17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P17">
         <v>1050.34</v>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,55 +214,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>20.8 → 37.7</t>
-  </si>
-  <si>
-    <t>20.8</t>
-  </si>
-  <si>
-    <t>37.7</t>
-  </si>
-  <si>
-    <t>27.1 → 35.0</t>
-  </si>
-  <si>
-    <t>27.1</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>38.3 → 50.6</t>
-  </si>
-  <si>
-    <t>38.3</t>
+    <t>50.6 → 46.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.6</t>
   </si>
   <si>
-    <t>27.0 → 54.2</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>54.2</t>
+    <t>46.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -348,14 +312,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -388,13 +352,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -987,10 +951,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>715.65</v>
+        <v>711.5</v>
       </c>
       <c r="D2">
-        <v>0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -999,46 +963,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-4.87</v>
+        <v>-5.42</v>
       </c>
       <c r="H2">
-        <v>25.34</v>
+        <v>24.62</v>
       </c>
       <c r="I2">
-        <v>-0.33</v>
+        <v>-1.86</v>
       </c>
       <c r="J2">
-        <v>-0.6</v>
+        <v>-1.56</v>
       </c>
       <c r="K2">
-        <v>-4.87</v>
+        <v>-3.66</v>
       </c>
       <c r="L2">
-        <v>-1.09</v>
+        <v>-2.97</v>
       </c>
       <c r="M2">
-        <v>29.28</v>
+        <v>28.25</v>
       </c>
       <c r="N2">
         <v>93</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>723.92</v>
+        <v>721.22</v>
       </c>
       <c r="Q2">
-        <v>724.71</v>
+        <v>724.5</v>
       </c>
       <c r="R2">
-        <v>726.76</v>
+        <v>726.01</v>
       </c>
       <c r="S2">
-        <v>688.13</v>
+        <v>687.99</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1053,34 +1017,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>46.13</v>
+        <v>44.49</v>
       </c>
       <c r="Z2">
-        <v>-1.16</v>
+        <v>-2.01</v>
       </c>
       <c r="AA2">
-        <v>-0.16</v>
+        <v>-0.53</v>
       </c>
       <c r="AB2">
-        <v>-1</v>
+        <v>-1.48</v>
       </c>
       <c r="AC2">
-        <v>26.68</v>
+        <v>12.17</v>
       </c>
       <c r="AD2">
-        <v>40.93</v>
+        <v>27.17</v>
       </c>
       <c r="AE2">
-        <v>16.23</v>
+        <v>16.07</v>
       </c>
       <c r="AF2">
-        <v>-68.11</v>
+        <v>-34.09</v>
       </c>
       <c r="AG2">
-        <v>745.8099999999999</v>
+        <v>746.0599999999999</v>
       </c>
       <c r="AH2">
-        <v>703.61</v>
+        <v>702.9299999999999</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1089,7 +1053,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>16.69</v>
+        <v>16.31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1100,10 +1064,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>853.35</v>
+        <v>852.6</v>
       </c>
       <c r="D3">
-        <v>-1.35</v>
+        <v>-0.09</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1112,46 +1076,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-21.1</v>
+        <v>-21.17</v>
       </c>
       <c r="H3">
-        <v>68.86</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="I3">
-        <v>-4.03</v>
+        <v>-3.67</v>
       </c>
       <c r="J3">
-        <v>-12.31</v>
+        <v>-11.03</v>
       </c>
       <c r="K3">
-        <v>-4.16</v>
+        <v>-5.41</v>
       </c>
       <c r="L3">
-        <v>-5.25</v>
+        <v>-2.46</v>
       </c>
       <c r="M3">
-        <v>0.2</v>
+        <v>1.22</v>
       </c>
       <c r="N3">
         <v>74</v>
       </c>
       <c r="O3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P3">
-        <v>888.6799999999999</v>
+        <v>882.1799999999999</v>
       </c>
       <c r="Q3">
-        <v>939.92</v>
+        <v>935.6799999999999</v>
       </c>
       <c r="R3">
-        <v>953.72</v>
+        <v>952.17</v>
       </c>
       <c r="S3">
-        <v>769.66</v>
+        <v>770.23</v>
       </c>
       <c r="T3">
-        <v>10.87</v>
+        <v>10.69</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1166,34 +1130,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>36.97</v>
+        <v>36.88</v>
       </c>
       <c r="Z3">
-        <v>-19.55</v>
+        <v>-22.71</v>
       </c>
       <c r="AA3">
-        <v>-8.44</v>
+        <v>-11.29</v>
       </c>
       <c r="AB3">
-        <v>-11.12</v>
+        <v>-11.42</v>
       </c>
       <c r="AC3">
-        <v>9.69</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>17.49</v>
+        <v>10.36</v>
       </c>
       <c r="AE3">
-        <v>43.02</v>
+        <v>42.41</v>
       </c>
       <c r="AF3">
-        <v>-39.35</v>
+        <v>-65.17</v>
       </c>
       <c r="AG3">
-        <v>1037.43</v>
+        <v>1040.72</v>
       </c>
       <c r="AH3">
-        <v>842.42</v>
+        <v>830.63</v>
       </c>
       <c r="AI3">
         <v>988.8099999999999</v>
@@ -1202,7 +1166,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>32.05</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1213,58 +1177,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>198.06</v>
+        <v>200.11</v>
       </c>
       <c r="D4">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="E4">
-        <v>301.78</v>
+        <v>299.61</v>
       </c>
       <c r="F4">
         <v>195.76</v>
       </c>
       <c r="G4">
-        <v>-34.37</v>
+        <v>-33.21</v>
       </c>
       <c r="H4">
-        <v>1.17</v>
+        <v>2.22</v>
       </c>
       <c r="I4">
-        <v>-0.82</v>
+        <v>1.5</v>
       </c>
       <c r="J4">
-        <v>-3.52</v>
+        <v>-1.91</v>
       </c>
       <c r="K4">
-        <v>-13.54</v>
+        <v>-13.24</v>
       </c>
       <c r="L4">
-        <v>-34.98</v>
+        <v>-33.69</v>
       </c>
       <c r="M4">
-        <v>-7.37</v>
+        <v>-7</v>
       </c>
       <c r="N4">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>198.26</v>
+        <v>198.85</v>
       </c>
       <c r="Q4">
-        <v>200.7</v>
+        <v>200.55</v>
       </c>
       <c r="R4">
-        <v>207.32</v>
+        <v>206.98</v>
       </c>
       <c r="S4">
-        <v>238.55</v>
+        <v>238.19</v>
       </c>
       <c r="T4">
-        <v>-16.97</v>
+        <v>-15.99</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1279,34 +1243,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.28</v>
+        <v>44.13</v>
       </c>
       <c r="Z4">
-        <v>-2.9</v>
+        <v>-2.64</v>
       </c>
       <c r="AA4">
-        <v>-3.05</v>
+        <v>-2.97</v>
       </c>
       <c r="AB4">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="AC4">
-        <v>71.54000000000001</v>
+        <v>73.19</v>
       </c>
       <c r="AD4">
-        <v>70.70999999999999</v>
+        <v>73.22</v>
       </c>
       <c r="AE4">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="AF4">
-        <v>-30.33</v>
+        <v>-45.51</v>
       </c>
       <c r="AG4">
-        <v>205.02</v>
+        <v>204.74</v>
       </c>
       <c r="AH4">
-        <v>196.38</v>
+        <v>196.37</v>
       </c>
       <c r="AI4">
         <v>207.87</v>
@@ -1315,7 +1279,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>40.13</v>
+        <v>38.47</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1326,58 +1290,58 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>589.75</v>
+        <v>636.95</v>
       </c>
       <c r="D5">
-        <v>-0.54</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>908.04</v>
+        <v>907</v>
       </c>
       <c r="F5">
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-35.05</v>
+        <v>-29.77</v>
       </c>
       <c r="H5">
-        <v>2.67</v>
+        <v>10.89</v>
       </c>
       <c r="I5">
-        <v>-2.97</v>
+        <v>3.17</v>
       </c>
       <c r="J5">
-        <v>-2.95</v>
+        <v>5.62</v>
       </c>
       <c r="K5">
-        <v>-18.21</v>
+        <v>-10.84</v>
       </c>
       <c r="L5">
-        <v>-35.39</v>
+        <v>-29.85</v>
       </c>
       <c r="M5">
-        <v>-8.140000000000001</v>
+        <v>-6.75</v>
       </c>
       <c r="N5">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="O5">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="P5">
-        <v>605.29</v>
+        <v>609.2</v>
       </c>
       <c r="Q5">
-        <v>649.89</v>
+        <v>651.21</v>
       </c>
       <c r="R5">
-        <v>649.09</v>
+        <v>648.42</v>
       </c>
       <c r="S5">
-        <v>695.24</v>
+        <v>694.64</v>
       </c>
       <c r="T5">
-        <v>-15.17</v>
+        <v>-8.31</v>
       </c>
       <c r="U5" t="s">
         <v>55</v>
@@ -1392,34 +1356,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>36.19</v>
+        <v>49.92</v>
       </c>
       <c r="Z5">
-        <v>-16.29</v>
+        <v>-13.75</v>
       </c>
       <c r="AA5">
-        <v>-9.279999999999999</v>
+        <v>-10.18</v>
       </c>
       <c r="AB5">
-        <v>-7.01</v>
+        <v>-3.58</v>
       </c>
       <c r="AC5">
-        <v>0.95</v>
+        <v>30.03</v>
       </c>
       <c r="AD5">
-        <v>3.23</v>
+        <v>11.38</v>
       </c>
       <c r="AE5">
-        <v>26.92</v>
+        <v>28.78</v>
       </c>
       <c r="AF5">
-        <v>-73.45999999999999</v>
+        <v>166.49</v>
       </c>
       <c r="AG5">
-        <v>756.3099999999999</v>
+        <v>756.22</v>
       </c>
       <c r="AH5">
-        <v>543.47</v>
+        <v>546.2</v>
       </c>
       <c r="AI5">
         <v>676.63</v>
@@ -1428,7 +1392,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>16.58</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1439,10 +1403,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1656.7</v>
+        <v>1662.7</v>
       </c>
       <c r="D6">
-        <v>-1.23</v>
+        <v>0.36</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1451,46 +1415,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-19.64</v>
+        <v>-19.35</v>
       </c>
       <c r="H6">
-        <v>22.91</v>
+        <v>23.35</v>
       </c>
       <c r="I6">
-        <v>-1.56</v>
+        <v>-0.86</v>
       </c>
       <c r="J6">
-        <v>-5.48</v>
+        <v>-6.21</v>
       </c>
       <c r="K6">
-        <v>-10.75</v>
+        <v>-9.41</v>
       </c>
       <c r="L6">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="M6">
-        <v>4.17</v>
+        <v>4.83</v>
       </c>
       <c r="N6">
         <v>81</v>
       </c>
       <c r="O6">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P6">
-        <v>1670.54</v>
+        <v>1667.64</v>
       </c>
       <c r="Q6">
-        <v>1705.46</v>
+        <v>1700.38</v>
       </c>
       <c r="R6">
-        <v>1716.7</v>
+        <v>1714.48</v>
       </c>
       <c r="S6">
-        <v>1702.36</v>
+        <v>1701.68</v>
       </c>
       <c r="T6">
-        <v>-2.68</v>
+        <v>-2.29</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1505,34 +1469,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>40.58</v>
+        <v>42.09</v>
       </c>
       <c r="Z6">
-        <v>-19.77</v>
+        <v>-19.61</v>
       </c>
       <c r="AA6">
-        <v>-17.25</v>
+        <v>-17.72</v>
       </c>
       <c r="AB6">
-        <v>-2.51</v>
+        <v>-1.88</v>
       </c>
       <c r="AC6">
-        <v>28.47</v>
+        <v>47.18</v>
       </c>
       <c r="AD6">
-        <v>26.22</v>
+        <v>34.31</v>
       </c>
       <c r="AE6">
-        <v>49.81</v>
+        <v>49.53</v>
       </c>
       <c r="AF6">
-        <v>27.2</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="AG6">
-        <v>1806.63</v>
+        <v>1799.27</v>
       </c>
       <c r="AH6">
-        <v>1604.3</v>
+        <v>1601.49</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1541,7 +1505,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>27.94</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1552,10 +1516,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>955</v>
+        <v>958.8</v>
       </c>
       <c r="D7">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1564,46 +1528,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-24.23</v>
+        <v>-23.93</v>
       </c>
       <c r="H7">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
       <c r="I7">
-        <v>-0.21</v>
+        <v>0.53</v>
       </c>
       <c r="J7">
-        <v>-5.83</v>
+        <v>-4.22</v>
       </c>
       <c r="K7">
-        <v>-14.11</v>
+        <v>-12.73</v>
       </c>
       <c r="L7">
-        <v>-15.67</v>
+        <v>-13.67</v>
       </c>
       <c r="M7">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
       <c r="N7">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O7">
         <v>43</v>
       </c>
       <c r="P7">
-        <v>961.03</v>
+        <v>962.04</v>
       </c>
       <c r="Q7">
-        <v>978.72</v>
+        <v>976.6799999999999</v>
       </c>
       <c r="R7">
-        <v>1026.81</v>
+        <v>1024.1</v>
       </c>
       <c r="S7">
-        <v>1103.81</v>
+        <v>1102.76</v>
       </c>
       <c r="T7">
-        <v>-13.48</v>
+        <v>-13.05</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1618,34 +1582,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.53</v>
+        <v>39.21</v>
       </c>
       <c r="Z7">
-        <v>-19.91</v>
+        <v>-19.17</v>
       </c>
       <c r="AA7">
-        <v>-20.55</v>
+        <v>-20.28</v>
       </c>
       <c r="AB7">
-        <v>0.64</v>
+        <v>1.11</v>
       </c>
       <c r="AC7">
-        <v>63.43</v>
+        <v>59.97</v>
       </c>
       <c r="AD7">
-        <v>70.89</v>
+        <v>66.83</v>
       </c>
       <c r="AE7">
-        <v>18.53</v>
+        <v>17.97</v>
       </c>
       <c r="AF7">
-        <v>-23.48</v>
+        <v>-42.62</v>
       </c>
       <c r="AG7">
-        <v>1017.82</v>
+        <v>1015.45</v>
       </c>
       <c r="AH7">
-        <v>939.61</v>
+        <v>937.91</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1654,7 +1618,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>51.95</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1665,10 +1629,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3130</v>
+        <v>3257</v>
       </c>
       <c r="D8">
-        <v>4.47</v>
+        <v>4.06</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1677,46 +1641,46 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-45.56</v>
+        <v>-43.36</v>
       </c>
       <c r="H8">
-        <v>4.47</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I8">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J8">
-        <v>-10.37</v>
+        <v>-3.72</v>
       </c>
       <c r="K8">
-        <v>-15.18</v>
+        <v>-14.82</v>
       </c>
       <c r="L8">
-        <v>-40.93</v>
+        <v>-38.48</v>
       </c>
       <c r="M8">
-        <v>-11.98</v>
+        <v>-10.8</v>
       </c>
       <c r="N8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O8">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="P8">
-        <v>3081.3</v>
+        <v>3111.7</v>
       </c>
       <c r="Q8">
-        <v>3216.7</v>
+        <v>3209.1</v>
       </c>
       <c r="R8">
-        <v>3487.62</v>
+        <v>3479.6</v>
       </c>
       <c r="S8">
-        <v>4180</v>
+        <v>4169.48</v>
       </c>
       <c r="T8">
-        <v>-25.12</v>
+        <v>-21.88</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1731,34 +1695,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>37.74</v>
+        <v>48.88</v>
       </c>
       <c r="Z8">
-        <v>-122.13</v>
+        <v>-103.99</v>
       </c>
       <c r="AA8">
-        <v>-121.7</v>
+        <v>-118.16</v>
       </c>
       <c r="AB8">
-        <v>-0.43</v>
+        <v>14.17</v>
       </c>
       <c r="AC8">
-        <v>36.76</v>
+        <v>66.67</v>
       </c>
       <c r="AD8">
-        <v>19.83</v>
+        <v>37.34</v>
       </c>
       <c r="AE8">
-        <v>91.83</v>
+        <v>96.7</v>
       </c>
       <c r="AF8">
-        <v>146.94</v>
+        <v>183.92</v>
       </c>
       <c r="AG8">
-        <v>3472.18</v>
+        <v>3449.06</v>
       </c>
       <c r="AH8">
-        <v>2961.23</v>
+        <v>2969.15</v>
       </c>
       <c r="AI8">
         <v>3326.38</v>
@@ -1767,7 +1731,7 @@
         <v>57</v>
       </c>
       <c r="AK8">
-        <v>60.51</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1778,10 +1742,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>599.25</v>
+        <v>619.6</v>
       </c>
       <c r="D9">
-        <v>-1.65</v>
+        <v>3.4</v>
       </c>
       <c r="E9">
         <v>1029.69</v>
@@ -1790,46 +1754,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-41.8</v>
+        <v>-39.83</v>
       </c>
       <c r="H9">
-        <v>11.31</v>
+        <v>15.09</v>
       </c>
       <c r="I9">
-        <v>-2.57</v>
+        <v>-0.35</v>
       </c>
       <c r="J9">
-        <v>-3.67</v>
+        <v>0.13</v>
       </c>
       <c r="K9">
-        <v>-13.62</v>
+        <v>-9.75</v>
       </c>
       <c r="L9">
-        <v>-39.45</v>
+        <v>-32.34</v>
       </c>
       <c r="M9">
-        <v>34.6</v>
+        <v>35.36</v>
       </c>
       <c r="N9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O9">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P9">
-        <v>613.95</v>
+        <v>613.52</v>
       </c>
       <c r="Q9">
-        <v>651.99</v>
+        <v>650.71</v>
       </c>
       <c r="R9">
-        <v>653.88</v>
+        <v>652.7</v>
       </c>
       <c r="S9">
-        <v>658.54</v>
+        <v>658.0599999999999</v>
       </c>
       <c r="T9">
-        <v>-9</v>
+        <v>-5.84</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1844,34 +1808,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>35.01</v>
+        <v>43.29</v>
       </c>
       <c r="Z9">
-        <v>-13.35</v>
+        <v>-12.96</v>
       </c>
       <c r="AA9">
-        <v>-7.25</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="AB9">
-        <v>-6.1</v>
+        <v>-4.57</v>
       </c>
       <c r="AC9">
-        <v>1.22</v>
+        <v>13.89</v>
       </c>
       <c r="AD9">
-        <v>4.69</v>
+        <v>6.78</v>
       </c>
       <c r="AE9">
-        <v>20.7</v>
+        <v>21.36</v>
       </c>
       <c r="AF9">
-        <v>-87.64</v>
+        <v>-69.78</v>
       </c>
       <c r="AG9">
-        <v>725.21</v>
+        <v>725.3099999999999</v>
       </c>
       <c r="AH9">
-        <v>578.76</v>
+        <v>576.11</v>
       </c>
       <c r="AI9">
         <v>665.02</v>
@@ -1880,7 +1844,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>18.05</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1891,10 +1855,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>342.15</v>
+        <v>343.7</v>
       </c>
       <c r="D10">
-        <v>1.94</v>
+        <v>0.45</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1903,46 +1867,46 @@
         <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-25.91</v>
+        <v>-25.57</v>
       </c>
       <c r="H10">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="I10">
-        <v>-2.28</v>
+        <v>-2.22</v>
       </c>
       <c r="J10">
-        <v>-6.4</v>
+        <v>-7.11</v>
       </c>
       <c r="K10">
-        <v>-10.27</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L10">
-        <v>-13.5</v>
+        <v>-12.43</v>
       </c>
       <c r="M10">
-        <v>12.95</v>
+        <v>12.54</v>
       </c>
       <c r="N10">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P10">
-        <v>345.22</v>
+        <v>343.66</v>
       </c>
       <c r="Q10">
-        <v>359.45</v>
+        <v>358.29</v>
       </c>
       <c r="R10">
-        <v>367.11</v>
+        <v>366.47</v>
       </c>
       <c r="S10">
-        <v>385.76</v>
+        <v>385.58</v>
       </c>
       <c r="T10">
-        <v>-11.31</v>
+        <v>-10.86</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1957,34 +1921,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>34.99</v>
+        <v>36.75</v>
       </c>
       <c r="Z10">
-        <v>-6.71</v>
+        <v>-6.86</v>
       </c>
       <c r="AA10">
-        <v>-4.41</v>
+        <v>-4.9</v>
       </c>
       <c r="AB10">
-        <v>-2.29</v>
+        <v>-1.95</v>
       </c>
       <c r="AC10">
-        <v>11.16</v>
+        <v>24.81</v>
       </c>
       <c r="AD10">
-        <v>6.54</v>
+        <v>12.96</v>
       </c>
       <c r="AE10">
-        <v>8.09</v>
+        <v>7.85</v>
       </c>
       <c r="AF10">
-        <v>10.83</v>
+        <v>-15.22</v>
       </c>
       <c r="AG10">
-        <v>379.97</v>
+        <v>379.63</v>
       </c>
       <c r="AH10">
-        <v>338.94</v>
+        <v>336.95</v>
       </c>
       <c r="AI10">
         <v>362.14</v>
@@ -1993,7 +1957,7 @@
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>42.41</v>
+        <v>42.38</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2004,10 +1968,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>173.8</v>
+        <v>172.24</v>
       </c>
       <c r="D11">
-        <v>1.07</v>
+        <v>-0.9</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2016,46 +1980,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-19.78</v>
+        <v>-20.5</v>
       </c>
       <c r="H11">
-        <v>10.41</v>
+        <v>9.41</v>
       </c>
       <c r="I11">
-        <v>-2.36</v>
+        <v>-3.31</v>
       </c>
       <c r="J11">
-        <v>-5.62</v>
+        <v>-8.75</v>
       </c>
       <c r="K11">
-        <v>-9.1</v>
+        <v>-7.95</v>
       </c>
       <c r="L11">
-        <v>4.31</v>
+        <v>2.54</v>
       </c>
       <c r="M11">
-        <v>8.960000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="P11">
-        <v>175.65</v>
+        <v>174.47</v>
       </c>
       <c r="Q11">
-        <v>182.96</v>
+        <v>182.24</v>
       </c>
       <c r="R11">
-        <v>185.22</v>
+        <v>184.93</v>
       </c>
       <c r="S11">
-        <v>192.18</v>
+        <v>192.21</v>
       </c>
       <c r="T11">
-        <v>-9.56</v>
+        <v>-10.39</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2070,34 +2034,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>35.47</v>
+        <v>33.72</v>
       </c>
       <c r="Z11">
-        <v>-2.92</v>
+        <v>-3.28</v>
       </c>
       <c r="AA11">
-        <v>-1.52</v>
+        <v>-1.87</v>
       </c>
       <c r="AB11">
-        <v>-1.4</v>
+        <v>-1.41</v>
       </c>
       <c r="AC11">
-        <v>4.87</v>
+        <v>7.55</v>
       </c>
       <c r="AD11">
-        <v>3.29</v>
+        <v>4.9</v>
       </c>
       <c r="AE11">
-        <v>4.73</v>
+        <v>4.76</v>
       </c>
       <c r="AF11">
-        <v>-50.38</v>
+        <v>5.06</v>
       </c>
       <c r="AG11">
-        <v>193.43</v>
+        <v>193.57</v>
       </c>
       <c r="AH11">
-        <v>172.5</v>
+        <v>170.9</v>
       </c>
       <c r="AI11">
         <v>186.52</v>
@@ -2106,7 +2070,7 @@
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>37.57</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2117,10 +2081,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2156</v>
+        <v>2125</v>
       </c>
       <c r="D12">
-        <v>3.85</v>
+        <v>-1.44</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2129,46 +2093,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-33.08</v>
+        <v>-34.04</v>
       </c>
       <c r="H12">
-        <v>8.75</v>
+        <v>7.18</v>
       </c>
       <c r="I12">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J12">
-        <v>-4.41</v>
+        <v>-3.76</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>-2.59</v>
       </c>
       <c r="L12">
-        <v>-25.27</v>
+        <v>-25.98</v>
       </c>
       <c r="M12">
-        <v>-7.71</v>
+        <v>-7.81</v>
       </c>
       <c r="N12">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="O12">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P12">
-        <v>2105.34</v>
+        <v>2107.46</v>
       </c>
       <c r="Q12">
-        <v>2119.37</v>
+        <v>2115.42</v>
       </c>
       <c r="R12">
-        <v>2254.22</v>
+        <v>2248.09</v>
       </c>
       <c r="S12">
-        <v>2457.49</v>
+        <v>2452.01</v>
       </c>
       <c r="T12">
-        <v>-12.27</v>
+        <v>-13.34</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2183,34 +2147,34 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>50.61</v>
+        <v>46.71</v>
       </c>
       <c r="Z12">
-        <v>-42.01</v>
+        <v>-37.44</v>
       </c>
       <c r="AA12">
-        <v>-51.55</v>
+        <v>-48.73</v>
       </c>
       <c r="AB12">
-        <v>9.539999999999999</v>
+        <v>11.29</v>
       </c>
       <c r="AC12">
-        <v>81.14</v>
+        <v>84.23</v>
       </c>
       <c r="AD12">
-        <v>80.16</v>
+        <v>80.91</v>
       </c>
       <c r="AE12">
-        <v>62.87</v>
+        <v>63.68</v>
       </c>
       <c r="AF12">
-        <v>253.23</v>
+        <v>-6.02</v>
       </c>
       <c r="AG12">
-        <v>2237.74</v>
+        <v>2226.95</v>
       </c>
       <c r="AH12">
-        <v>2001</v>
+        <v>2003.88</v>
       </c>
       <c r="AI12">
         <v>2235.3</v>
@@ -2219,7 +2183,7 @@
         <v>57</v>
       </c>
       <c r="AK12">
-        <v>31.14</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2230,58 +2194,58 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4410</v>
+        <v>4400</v>
       </c>
       <c r="D13">
-        <v>1.16</v>
+        <v>-0.23</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
       </c>
       <c r="F13">
-        <v>3418.2</v>
+        <v>3531.9</v>
       </c>
       <c r="G13">
-        <v>-14.69</v>
+        <v>-14.88</v>
       </c>
       <c r="H13">
-        <v>29.02</v>
+        <v>24.58</v>
       </c>
       <c r="I13">
-        <v>-2.34</v>
+        <v>-3.93</v>
       </c>
       <c r="J13">
-        <v>-11.57</v>
+        <v>-12.09</v>
       </c>
       <c r="K13">
-        <v>-3.8</v>
+        <v>-4.38</v>
       </c>
       <c r="L13">
-        <v>28.74</v>
+        <v>28.72</v>
       </c>
       <c r="M13">
-        <v>13.61</v>
+        <v>12.33</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P13">
-        <v>4455.3</v>
+        <v>4419.3</v>
       </c>
       <c r="Q13">
-        <v>4735.41</v>
+        <v>4704.36</v>
       </c>
       <c r="R13">
-        <v>4917.13</v>
+        <v>4908.13</v>
       </c>
       <c r="S13">
-        <v>4421.88</v>
+        <v>4424.21</v>
       </c>
       <c r="T13">
-        <v>-0.27</v>
+        <v>-0.55</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2296,43 +2260,43 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>29.33</v>
+        <v>28.95</v>
       </c>
       <c r="Z13">
-        <v>-144.1</v>
+        <v>-147.99</v>
       </c>
       <c r="AA13">
-        <v>-99.70999999999999</v>
+        <v>-109.37</v>
       </c>
       <c r="AB13">
-        <v>-44.38</v>
+        <v>-38.62</v>
       </c>
       <c r="AC13">
-        <v>6.55</v>
+        <v>12.56</v>
       </c>
       <c r="AD13">
-        <v>10.11</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AE13">
-        <v>98.77</v>
+        <v>96.56</v>
       </c>
       <c r="AF13">
-        <v>-27.22</v>
+        <v>-11.72</v>
       </c>
       <c r="AG13">
-        <v>5156.11</v>
+        <v>5127.97</v>
       </c>
       <c r="AH13">
-        <v>4314.71</v>
+        <v>4280.75</v>
       </c>
       <c r="AI13">
-        <v>4688.95</v>
+        <v>4684.57</v>
       </c>
       <c r="AJ13" t="s">
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>62.94</v>
+        <v>64.47</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2343,10 +2307,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2918.2</v>
+        <v>2913</v>
       </c>
       <c r="D14">
-        <v>1.46</v>
+        <v>-0.18</v>
       </c>
       <c r="E14">
         <v>4807.3</v>
@@ -2355,25 +2319,25 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-39.3</v>
+        <v>-39.4</v>
       </c>
       <c r="H14">
-        <v>33.01</v>
+        <v>32.77</v>
       </c>
       <c r="I14">
-        <v>13.11</v>
+        <v>12.91</v>
       </c>
       <c r="J14">
-        <v>4.46</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="L14">
-        <v>-38.83</v>
+        <v>-37.74</v>
       </c>
       <c r="M14">
-        <v>21.62</v>
+        <v>20.89</v>
       </c>
       <c r="N14">
         <v>50</v>
@@ -2382,19 +2346,19 @@
         <v>38</v>
       </c>
       <c r="P14">
-        <v>2834.16</v>
+        <v>2900.76</v>
       </c>
       <c r="Q14">
-        <v>2755.44</v>
+        <v>2760.16</v>
       </c>
       <c r="R14">
-        <v>2868.47</v>
+        <v>2866.75</v>
       </c>
       <c r="S14">
-        <v>2825.92</v>
+        <v>2819.48</v>
       </c>
       <c r="T14">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2409,43 +2373,43 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>61.06</v>
+        <v>60.5</v>
       </c>
       <c r="Z14">
-        <v>-6.99</v>
+        <v>3.8</v>
       </c>
       <c r="AA14">
-        <v>-40.01</v>
+        <v>-31.25</v>
       </c>
       <c r="AB14">
-        <v>33.02</v>
+        <v>35.05</v>
       </c>
       <c r="AC14">
-        <v>96.01000000000001</v>
+        <v>96.87</v>
       </c>
       <c r="AD14">
-        <v>85.78</v>
+        <v>96.3</v>
       </c>
       <c r="AE14">
-        <v>74.81999999999999</v>
+        <v>74.08</v>
       </c>
       <c r="AF14">
-        <v>-30.32</v>
+        <v>-41.64</v>
       </c>
       <c r="AG14">
-        <v>2971.03</v>
+        <v>2985.48</v>
       </c>
       <c r="AH14">
-        <v>2539.86</v>
+        <v>2534.84</v>
       </c>
       <c r="AI14">
-        <v>2677.8</v>
+        <v>2711.5</v>
       </c>
       <c r="AJ14" t="s">
         <v>56</v>
       </c>
       <c r="AK14">
-        <v>48.58</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2456,58 +2420,58 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>216.94</v>
+        <v>227.89</v>
       </c>
       <c r="D15">
-        <v>13.12</v>
+        <v>5.05</v>
       </c>
       <c r="E15">
-        <v>365.95</v>
+        <v>356.55</v>
       </c>
       <c r="F15">
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-40.72</v>
+        <v>-36.08</v>
       </c>
       <c r="H15">
-        <v>13.12</v>
+        <v>18.83</v>
       </c>
       <c r="I15">
-        <v>12.8</v>
+        <v>17.46</v>
       </c>
       <c r="J15">
-        <v>-6.08</v>
+        <v>-0.39</v>
       </c>
       <c r="K15">
-        <v>-7.68</v>
+        <v>-5.29</v>
       </c>
       <c r="L15">
-        <v>-40.97</v>
+        <v>-37.73</v>
       </c>
       <c r="M15">
-        <v>5.63</v>
+        <v>6.97</v>
       </c>
       <c r="N15">
         <v>32</v>
       </c>
       <c r="O15">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P15">
-        <v>199.41</v>
+        <v>206.19</v>
       </c>
       <c r="Q15">
-        <v>209.09</v>
+        <v>209.44</v>
       </c>
       <c r="R15">
-        <v>221.65</v>
+        <v>221.7</v>
       </c>
       <c r="S15">
-        <v>246.43</v>
+        <v>246.04</v>
       </c>
       <c r="T15">
-        <v>-11.97</v>
+        <v>-7.38</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2522,43 +2486,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>54.23</v>
+        <v>61.04</v>
       </c>
       <c r="Z15">
-        <v>-6.84</v>
+        <v>-4.46</v>
       </c>
       <c r="AA15">
-        <v>-7.04</v>
+        <v>-6.53</v>
       </c>
       <c r="AB15">
-        <v>0.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
-        <v>60.32</v>
+        <v>77.11</v>
       </c>
       <c r="AD15">
-        <v>44.05</v>
+        <v>58.69</v>
       </c>
       <c r="AE15">
-        <v>9.74</v>
+        <v>10.47</v>
       </c>
       <c r="AF15">
-        <v>297.67</v>
+        <v>354.72</v>
       </c>
       <c r="AG15">
-        <v>229.85</v>
+        <v>231.26</v>
       </c>
       <c r="AH15">
-        <v>188.33</v>
+        <v>187.63</v>
       </c>
       <c r="AI15">
-        <v>218.86</v>
+        <v>193.57</v>
       </c>
       <c r="AJ15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AK15">
-        <v>42.56</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2569,58 +2533,58 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>32.89</v>
+        <v>33.02</v>
       </c>
       <c r="D16">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="E16">
-        <v>58.68</v>
+        <v>57.7</v>
       </c>
       <c r="F16">
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-43.95</v>
+        <v>-42.77</v>
       </c>
       <c r="H16">
-        <v>4.88</v>
+        <v>5.29</v>
       </c>
       <c r="I16">
-        <v>-5.54</v>
+        <v>-3.82</v>
       </c>
       <c r="J16">
-        <v>-9.869999999999999</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K16">
-        <v>-20.32</v>
+        <v>-19.7</v>
       </c>
       <c r="L16">
-        <v>-42.52</v>
+        <v>-43.73</v>
       </c>
       <c r="M16">
-        <v>-6.44</v>
+        <v>-7.25</v>
       </c>
       <c r="N16">
         <v>7</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P16">
-        <v>33.67</v>
+        <v>33.41</v>
       </c>
       <c r="Q16">
-        <v>35.01</v>
+        <v>34.86</v>
       </c>
       <c r="R16">
-        <v>37</v>
+        <v>36.87</v>
       </c>
       <c r="S16">
-        <v>41.3</v>
+        <v>41.22</v>
       </c>
       <c r="T16">
-        <v>-20.37</v>
+        <v>-19.89</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2635,34 +2599,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>32.57</v>
+        <v>33.75</v>
       </c>
       <c r="Z16">
-        <v>-1.05</v>
+        <v>-1.08</v>
       </c>
       <c r="AA16">
-        <v>-0.91</v>
+        <v>-0.95</v>
       </c>
       <c r="AB16">
         <v>-0.13</v>
       </c>
       <c r="AC16">
-        <v>10.05</v>
+        <v>2.69</v>
       </c>
       <c r="AD16">
-        <v>24.84</v>
+        <v>12.36</v>
       </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF16">
-        <v>-75.8</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="AG16">
-        <v>37.05</v>
+        <v>37.04</v>
       </c>
       <c r="AH16">
-        <v>32.97</v>
+        <v>32.69</v>
       </c>
       <c r="AI16">
         <v>36.59</v>
@@ -2671,7 +2635,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>16.86</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2682,58 +2646,58 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1033.7</v>
+        <v>1020</v>
       </c>
       <c r="D17">
-        <v>0.16</v>
+        <v>-1.33</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
       </c>
       <c r="F17">
-        <v>1032</v>
+        <v>1020</v>
       </c>
       <c r="G17">
-        <v>-33.58</v>
+        <v>-34.46</v>
       </c>
       <c r="H17">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>-1.85</v>
+        <v>-3.89</v>
       </c>
       <c r="J17">
-        <v>-9.699999999999999</v>
+        <v>-10.82</v>
       </c>
       <c r="K17">
-        <v>-19.66</v>
+        <v>-24.42</v>
       </c>
       <c r="L17">
-        <v>-24.13</v>
+        <v>-25.43</v>
       </c>
       <c r="M17">
-        <v>-4.1</v>
+        <v>-4.27</v>
       </c>
       <c r="N17">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="O17">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P17">
-        <v>1050.34</v>
+        <v>1042.08</v>
       </c>
       <c r="Q17">
-        <v>1102.12</v>
+        <v>1095.19</v>
       </c>
       <c r="R17">
-        <v>1186.75</v>
+        <v>1180.49</v>
       </c>
       <c r="S17">
-        <v>1321.81</v>
+        <v>1319.99</v>
       </c>
       <c r="T17">
-        <v>-21.8</v>
+        <v>-22.73</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2748,43 +2712,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>30.65</v>
+        <v>28.82</v>
       </c>
       <c r="Z17">
-        <v>-40.69</v>
+        <v>-41.97</v>
       </c>
       <c r="AA17">
-        <v>-37.51</v>
+        <v>-38.4</v>
       </c>
       <c r="AB17">
-        <v>-3.18</v>
+        <v>-3.57</v>
       </c>
       <c r="AC17">
-        <v>14.47</v>
+        <v>3.91</v>
       </c>
       <c r="AD17">
-        <v>25.72</v>
+        <v>15.31</v>
       </c>
       <c r="AE17">
-        <v>29.19</v>
+        <v>29.08</v>
       </c>
       <c r="AF17">
-        <v>-68.88</v>
+        <v>-61.52</v>
       </c>
       <c r="AG17">
-        <v>1184.55</v>
+        <v>1180.89</v>
       </c>
       <c r="AH17">
-        <v>1019.68</v>
+        <v>1009.49</v>
       </c>
       <c r="AI17">
-        <v>1126.12</v>
+        <v>1119.4</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>53.34</v>
+        <v>56.25</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2965,7 +2929,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2977,2437 +2941,2354 @@
         <v>66</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>80</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-1.56</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>80</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-12.31</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-11.03</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-1.91</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="D10" s="6">
+        <v>5.62</v>
+      </c>
+      <c r="E10" s="8">
+        <v>8.57</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>85</v>
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-5.48</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-6.21</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.64</v>
+        <v>-5.83</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.04</v>
+        <v>-4.22</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.31</v>
+        <v>-10.37</v>
       </c>
       <c r="D13" s="6">
-        <v>-12.31</v>
+        <v>-3.72</v>
       </c>
       <c r="E13" s="8">
-        <v>-5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.04</v>
+        <v>-3.67</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.52</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.52</v>
+        <v>0.13</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3.8</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.33</v>
+        <v>-6.4</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.95</v>
+        <v>-7.11</v>
       </c>
       <c r="E15" s="7">
-        <v>0.38</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.51</v>
+        <v>-5.62</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.48</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.97</v>
+        <v>-8.75</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.22</v>
+        <v>-4.41</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.83</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.39</v>
+        <v>-3.76</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.65</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-14.33</v>
+        <v>-11.57</v>
       </c>
       <c r="D18" s="6">
-        <v>-10.37</v>
+        <v>-12.09</v>
       </c>
       <c r="E18" s="7">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.95</v>
+        <v>4.46</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.72</v>
+        <v>3.3</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-8.220000000000001</v>
+        <v>-6.08</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.4</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.82</v>
+        <v>-0.39</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5.69</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-7.35</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.73</v>
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-8.550000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.41</v>
+        <v>-10.82</v>
       </c>
       <c r="E22" s="7">
-        <v>4.14</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-12.72</v>
+        <v>-0.33</v>
       </c>
       <c r="D23" s="6">
-        <v>-11.57</v>
+        <v>-1.86</v>
       </c>
       <c r="E23" s="7">
-        <v>1.15</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>2.2</v>
+        <v>-4.03</v>
       </c>
       <c r="D24" s="6">
-        <v>4.46</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.26</v>
+        <v>-3.67</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-18.44</v>
+        <v>-0.82</v>
       </c>
       <c r="D25" s="6">
-        <v>-6.08</v>
-      </c>
-      <c r="E25" s="7">
-        <v>12.36</v>
+        <v>1.5</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-11.78</v>
+        <v>-2.97</v>
       </c>
       <c r="D26" s="6">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.91</v>
+        <v>3.17</v>
+      </c>
+      <c r="E26" s="8">
+        <v>6.14</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-11.58</v>
+        <v>-1.56</v>
       </c>
       <c r="D27" s="6">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.88</v>
+        <v>-0.86</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.33</v>
+        <v>-0.21</v>
       </c>
       <c r="D28" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2</v>
+        <v>0.53</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-5.41</v>
+        <v>1.2</v>
       </c>
       <c r="D29" s="6">
-        <v>-4.03</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.38</v>
+        <v>4.9</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.7</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-1.99</v>
+        <v>-2.57</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.82</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.17</v>
+        <v>-0.35</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.22</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-3.03</v>
+        <v>-2.28</v>
       </c>
       <c r="D31" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="E31" s="7">
+        <v>-2.22</v>
+      </c>
+      <c r="E31" s="8">
         <v>0.06</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>1.28</v>
+        <v>-2.36</v>
       </c>
       <c r="D32" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.84</v>
+        <v>-3.31</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>0.25</v>
+        <v>3.9</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.21</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.46</v>
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-3.01</v>
+        <v>-2.34</v>
       </c>
       <c r="D34" s="6">
-        <v>1.2</v>
+        <v>-3.93</v>
       </c>
       <c r="E34" s="7">
-        <v>4.21</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.73</v>
+        <v>13.11</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.57</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.84</v>
+        <v>12.91</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-6.5</v>
+        <v>12.8</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.28</v>
-      </c>
-      <c r="E36" s="7">
-        <v>4.22</v>
+        <v>17.46</v>
+      </c>
+      <c r="E36" s="8">
+        <v>4.66</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-6.7</v>
+        <v>-5.54</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.36</v>
-      </c>
-      <c r="E37" s="7">
-        <v>4.34</v>
+        <v>-3.82</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.72</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>1.24</v>
+        <v>-1.85</v>
       </c>
       <c r="D38" s="6">
-        <v>3.9</v>
+        <v>-3.89</v>
       </c>
       <c r="E38" s="7">
-        <v>2.66</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C39" s="6">
-        <v>-4.96</v>
+        <v>-1.09</v>
       </c>
       <c r="D39" s="6">
-        <v>-2.34</v>
+        <v>-2.97</v>
       </c>
       <c r="E39" s="7">
-        <v>2.62</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C40" s="6">
-        <v>9.720000000000001</v>
+        <v>-5.25</v>
       </c>
       <c r="D40" s="6">
-        <v>13.11</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.39</v>
+        <v>-2.46</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.79</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C41" s="6">
-        <v>-3.05</v>
+        <v>-34.98</v>
       </c>
       <c r="D41" s="6">
-        <v>12.8</v>
-      </c>
-      <c r="E41" s="7">
-        <v>15.85</v>
+        <v>-33.69</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>-3.94</v>
+        <v>-35.39</v>
       </c>
       <c r="D42" s="6">
-        <v>-5.54</v>
+        <v>-29.85</v>
       </c>
       <c r="E42" s="8">
-        <v>-1.6</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-3.55</v>
+        <v>-0.11</v>
       </c>
       <c r="D43" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.7</v>
+        <v>0.01</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.12</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-1.77</v>
+        <v>-15.67</v>
       </c>
       <c r="D44" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.68</v>
+        <v>-13.67</v>
+      </c>
+      <c r="E44" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-4.43</v>
+        <v>-40.93</v>
       </c>
       <c r="D45" s="6">
-        <v>-5.25</v>
+        <v>-38.48</v>
       </c>
       <c r="E45" s="8">
-        <v>-0.82</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-36.39</v>
+        <v>-39.45</v>
       </c>
       <c r="D46" s="6">
-        <v>-34.98</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.41</v>
+        <v>-32.34</v>
+      </c>
+      <c r="E46" s="8">
+        <v>7.11</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-34.95</v>
+        <v>-13.5</v>
       </c>
       <c r="D47" s="6">
-        <v>-35.39</v>
+        <v>-12.43</v>
       </c>
       <c r="E47" s="8">
-        <v>-0.44</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>3.94</v>
+        <v>4.31</v>
       </c>
       <c r="D48" s="6">
-        <v>-0.11</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-4.05</v>
+        <v>2.54</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-15.61</v>
+        <v>-25.27</v>
       </c>
       <c r="D49" s="6">
-        <v>-15.67</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.06</v>
+        <v>-25.98</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-43.05</v>
+        <v>28.74</v>
       </c>
       <c r="D50" s="6">
-        <v>-40.93</v>
+        <v>28.72</v>
       </c>
       <c r="E50" s="7">
-        <v>2.12</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-38.77</v>
+        <v>-38.83</v>
       </c>
       <c r="D51" s="6">
-        <v>-39.45</v>
+        <v>-37.74</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.68</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-15</v>
+        <v>-40.97</v>
       </c>
       <c r="D52" s="6">
-        <v>-13.5</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.5</v>
+        <v>-37.73</v>
+      </c>
+      <c r="E52" s="8">
+        <v>3.24</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>1.33</v>
+        <v>-42.52</v>
       </c>
       <c r="D53" s="6">
-        <v>4.31</v>
+        <v>-43.73</v>
       </c>
       <c r="E53" s="7">
-        <v>2.98</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-25.9</v>
+        <v>-24.13</v>
       </c>
       <c r="D54" s="6">
-        <v>-25.27</v>
+        <v>-25.43</v>
       </c>
       <c r="E54" s="7">
-        <v>0.63</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" s="6">
-        <v>26.24</v>
+        <v>-4.87</v>
       </c>
       <c r="D55" s="6">
-        <v>28.74</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.5</v>
+        <v>-3.66</v>
+      </c>
+      <c r="E55" s="8">
+        <v>1.21</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="6">
-        <v>-40.18</v>
+        <v>-4.16</v>
       </c>
       <c r="D56" s="6">
-        <v>-38.83</v>
+        <v>-5.41</v>
       </c>
       <c r="E56" s="7">
-        <v>1.35</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" s="6">
-        <v>-49.62</v>
+        <v>-13.54</v>
       </c>
       <c r="D57" s="6">
-        <v>-40.97</v>
-      </c>
-      <c r="E57" s="7">
-        <v>8.65</v>
+        <v>-13.24</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.3</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-41.71</v>
+        <v>-18.21</v>
       </c>
       <c r="D58" s="6">
-        <v>-42.52</v>
+        <v>-10.84</v>
       </c>
       <c r="E58" s="8">
-        <v>-0.8100000000000001</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-23.9</v>
+        <v>-10.75</v>
       </c>
       <c r="D59" s="6">
-        <v>-24.13</v>
+        <v>-9.41</v>
       </c>
       <c r="E59" s="8">
-        <v>-0.23</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-2.71</v>
+        <v>-14.11</v>
       </c>
       <c r="D60" s="6">
-        <v>-4.87</v>
+        <v>-12.73</v>
       </c>
       <c r="E60" s="8">
-        <v>-2.16</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-3.48</v>
+        <v>-15.18</v>
       </c>
       <c r="D61" s="6">
-        <v>-4.16</v>
+        <v>-14.82</v>
       </c>
       <c r="E61" s="8">
-        <v>-0.68</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-12.38</v>
+        <v>-13.62</v>
       </c>
       <c r="D62" s="6">
-        <v>-13.54</v>
+        <v>-9.75</v>
       </c>
       <c r="E62" s="8">
-        <v>-1.16</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-16.92</v>
+        <v>-10.27</v>
       </c>
       <c r="D63" s="6">
-        <v>-18.21</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="E63" s="8">
-        <v>-1.29</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-10.32</v>
+        <v>-9.1</v>
       </c>
       <c r="D64" s="6">
-        <v>-10.75</v>
+        <v>-7.95</v>
       </c>
       <c r="E64" s="8">
-        <v>-0.43</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-13.99</v>
+        <v>4.2</v>
       </c>
       <c r="D65" s="6">
-        <v>-14.11</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.12</v>
+        <v>-2.59</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-6.79</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-17.27</v>
+        <v>-3.8</v>
       </c>
       <c r="D66" s="6">
-        <v>-15.18</v>
+        <v>-4.38</v>
       </c>
       <c r="E66" s="7">
-        <v>2.09</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-11.03</v>
+        <v>0.53</v>
       </c>
       <c r="D67" s="6">
-        <v>-13.62</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.59</v>
+        <v>0.44</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-10.61</v>
+        <v>-7.68</v>
       </c>
       <c r="D68" s="6">
-        <v>-10.27</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.34</v>
+        <v>-5.29</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.39</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-8.49</v>
+        <v>-20.32</v>
       </c>
       <c r="D69" s="6">
-        <v>-9.1</v>
+        <v>-19.7</v>
       </c>
       <c r="E69" s="8">
-        <v>-0.61</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>1.29</v>
+        <v>-19.66</v>
       </c>
       <c r="D70" s="6">
-        <v>4.2</v>
+        <v>-24.42</v>
       </c>
       <c r="E70" s="7">
-        <v>2.91</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6">
-        <v>-4.31</v>
+        <v>-4.87</v>
       </c>
       <c r="D71" s="6">
-        <v>-3.8</v>
+        <v>-5.42</v>
       </c>
       <c r="E71" s="7">
-        <v>0.51</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6">
-        <v>-0.96</v>
+        <v>-21.1</v>
       </c>
       <c r="D72" s="6">
-        <v>0.53</v>
+        <v>-21.17</v>
       </c>
       <c r="E72" s="7">
-        <v>1.49</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6">
-        <v>-17.76</v>
+        <v>-34.37</v>
       </c>
       <c r="D73" s="6">
-        <v>-7.68</v>
-      </c>
-      <c r="E73" s="7">
-        <v>10.08</v>
+        <v>-33.21</v>
+      </c>
+      <c r="E73" s="8">
+        <v>1.16</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-18.62</v>
+        <v>-35.05</v>
       </c>
       <c r="D74" s="6">
-        <v>-20.32</v>
+        <v>-29.77</v>
       </c>
       <c r="E74" s="8">
-        <v>-1.7</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-18.7</v>
+        <v>-19.64</v>
       </c>
       <c r="D75" s="6">
-        <v>-19.66</v>
+        <v>-19.35</v>
       </c>
       <c r="E75" s="8">
-        <v>-0.96</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-5.4</v>
+        <v>-24.23</v>
       </c>
       <c r="D76" s="6">
-        <v>-4.87</v>
-      </c>
-      <c r="E76" s="7">
-        <v>0.53</v>
+        <v>-23.93</v>
+      </c>
+      <c r="E76" s="8">
+        <v>0.3</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-20.02</v>
+        <v>-45.56</v>
       </c>
       <c r="D77" s="6">
-        <v>-21.1</v>
+        <v>-43.36</v>
       </c>
       <c r="E77" s="8">
-        <v>-1.08</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-35.73</v>
+        <v>-41.8</v>
       </c>
       <c r="D78" s="6">
-        <v>-34.37</v>
-      </c>
-      <c r="E78" s="7">
-        <v>1.36</v>
+        <v>-39.83</v>
+      </c>
+      <c r="E78" s="8">
+        <v>1.97</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-35.03</v>
+        <v>-25.91</v>
       </c>
       <c r="D79" s="6">
-        <v>-35.05</v>
+        <v>-25.57</v>
       </c>
       <c r="E79" s="8">
-        <v>-0.02</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-18.64</v>
+        <v>-19.78</v>
       </c>
       <c r="D80" s="6">
-        <v>-19.64</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-1</v>
+        <v>-20.5</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-24.47</v>
+        <v>-33.08</v>
       </c>
       <c r="D81" s="6">
-        <v>-24.23</v>
+        <v>-34.04</v>
       </c>
       <c r="E81" s="7">
-        <v>0.24</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-47.89</v>
+        <v>-14.69</v>
       </c>
       <c r="D82" s="6">
-        <v>-45.56</v>
+        <v>-14.88</v>
       </c>
       <c r="E82" s="7">
-        <v>2.33</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-40.83</v>
+        <v>-39.3</v>
       </c>
       <c r="D83" s="6">
-        <v>-41.8</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.97</v>
+        <v>-39.4</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-27.32</v>
+        <v>-40.72</v>
       </c>
       <c r="D84" s="6">
-        <v>-25.91</v>
-      </c>
-      <c r="E84" s="7">
-        <v>1.41</v>
+        <v>-36.08</v>
+      </c>
+      <c r="E84" s="8">
+        <v>4.64</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-20.63</v>
+        <v>-43.95</v>
       </c>
       <c r="D85" s="6">
-        <v>-19.78</v>
-      </c>
-      <c r="E85" s="7">
-        <v>0.85</v>
+        <v>-42.77</v>
+      </c>
+      <c r="E85" s="8">
+        <v>1.18</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-35.56</v>
+        <v>-33.58</v>
       </c>
       <c r="D86" s="6">
-        <v>-33.08</v>
+        <v>-34.46</v>
       </c>
       <c r="E86" s="7">
-        <v>2.48</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C87" s="6">
-        <v>-15.66</v>
+        <v>715.65</v>
       </c>
       <c r="D87" s="6">
-        <v>-14.69</v>
+        <v>711.5</v>
       </c>
       <c r="E87" s="7">
-        <v>0.97</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>-40.17</v>
+        <v>853.35</v>
       </c>
       <c r="D88" s="6">
-        <v>-39.3</v>
+        <v>852.6</v>
       </c>
       <c r="E88" s="7">
-        <v>0.87</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>-47.81</v>
+        <v>198.06</v>
       </c>
       <c r="D89" s="6">
-        <v>-40.72</v>
-      </c>
-      <c r="E89" s="7">
-        <v>7.09</v>
+        <v>200.11</v>
+      </c>
+      <c r="E89" s="8">
+        <v>2.05</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>-43.85</v>
+        <v>589.75</v>
       </c>
       <c r="D90" s="6">
-        <v>-43.95</v>
+        <v>636.95</v>
       </c>
       <c r="E90" s="8">
-        <v>-0.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="6">
+        <v>1656.7</v>
+      </c>
+      <c r="D91" s="6">
+        <v>1662.7</v>
+      </c>
+      <c r="E91" s="8">
         <v>6</v>
-      </c>
-      <c r="C91" s="6">
-        <v>-33.69</v>
-      </c>
-      <c r="D91" s="6">
-        <v>-33.58</v>
-      </c>
-      <c r="E91" s="7">
-        <v>0.11</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>711.65</v>
+        <v>955</v>
       </c>
       <c r="D92" s="6">
-        <v>715.65</v>
-      </c>
-      <c r="E92" s="7">
-        <v>4</v>
+        <v>958.8</v>
+      </c>
+      <c r="E92" s="8">
+        <v>3.8</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>865</v>
+        <v>3130</v>
       </c>
       <c r="D93" s="6">
-        <v>853.35</v>
+        <v>3257</v>
       </c>
       <c r="E93" s="8">
-        <v>-11.65</v>
+        <v>127</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>195.76</v>
+        <v>599.25</v>
       </c>
       <c r="D94" s="6">
-        <v>198.06</v>
-      </c>
-      <c r="E94" s="7">
-        <v>2.3</v>
+        <v>619.6</v>
+      </c>
+      <c r="E94" s="8">
+        <v>20.35</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>592.95</v>
+        <v>342.15</v>
       </c>
       <c r="D95" s="6">
-        <v>589.75</v>
+        <v>343.7</v>
       </c>
       <c r="E95" s="8">
-        <v>-3.2</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>1677.4</v>
+        <v>173.8</v>
       </c>
       <c r="D96" s="6">
-        <v>1656.7</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-20.7</v>
+        <v>172.24</v>
+      </c>
+      <c r="E96" s="7">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>951.9</v>
+        <v>2156</v>
       </c>
       <c r="D97" s="6">
-        <v>955</v>
+        <v>2125</v>
       </c>
       <c r="E97" s="7">
-        <v>3.1</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>2996</v>
+        <v>4410</v>
       </c>
       <c r="D98" s="6">
-        <v>3130</v>
+        <v>4400</v>
       </c>
       <c r="E98" s="7">
-        <v>134</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>609.3</v>
+        <v>2918.2</v>
       </c>
       <c r="D99" s="6">
-        <v>599.25</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-10.05</v>
+        <v>2913</v>
+      </c>
+      <c r="E99" s="7">
+        <v>-5.2</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>335.65</v>
+        <v>216.94</v>
       </c>
       <c r="D100" s="6">
-        <v>342.15</v>
-      </c>
-      <c r="E100" s="7">
-        <v>6.5</v>
+        <v>227.89</v>
+      </c>
+      <c r="E100" s="8">
+        <v>10.95</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>171.96</v>
+        <v>32.89</v>
       </c>
       <c r="D101" s="6">
-        <v>173.8</v>
-      </c>
-      <c r="E101" s="7">
-        <v>1.84</v>
+        <v>33.02</v>
+      </c>
+      <c r="E101" s="8">
+        <v>0.13</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>2076</v>
+        <v>1033.7</v>
       </c>
       <c r="D102" s="6">
-        <v>2156</v>
+        <v>1020</v>
       </c>
       <c r="E102" s="7">
-        <v>80</v>
+        <v>-13.7</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C103" s="6">
-        <v>4359.5</v>
+        <v>38</v>
       </c>
       <c r="D103" s="6">
-        <v>4410</v>
+        <v>26</v>
       </c>
       <c r="E103" s="7">
-        <v>50.5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C104" s="6">
-        <v>2876.3</v>
+        <v>19</v>
       </c>
       <c r="D104" s="6">
-        <v>2918.2</v>
-      </c>
-      <c r="E104" s="7">
-        <v>41.9</v>
+        <v>44</v>
+      </c>
+      <c r="E104" s="8">
+        <v>25</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C105" s="6">
-        <v>191.78</v>
+        <v>56</v>
       </c>
       <c r="D105" s="6">
-        <v>216.94</v>
-      </c>
-      <c r="E105" s="7">
-        <v>25.16</v>
+        <v>62</v>
+      </c>
+      <c r="E105" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>32.95</v>
+        <v>13</v>
       </c>
       <c r="D106" s="6">
-        <v>32.89</v>
+        <v>19</v>
       </c>
       <c r="E106" s="8">
-        <v>-0.06</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>1032</v>
+        <v>26</v>
       </c>
       <c r="D107" s="6">
-        <v>1033.7</v>
-      </c>
-      <c r="E107" s="7">
-        <v>1.7</v>
+        <v>38</v>
+      </c>
+      <c r="E107" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="D108" s="6">
-        <v>38</v>
-      </c>
-      <c r="E108" s="7">
+        <v>68</v>
+      </c>
+      <c r="E108" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="6">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D109" s="6">
-        <v>19</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-7</v>
+        <v>56</v>
+      </c>
+      <c r="E109" s="7">
+        <v>-12</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C110" s="6">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="D110" s="6">
-        <v>81</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-6</v>
+        <v>13</v>
+      </c>
+      <c r="E110" s="7">
+        <v>-31</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C111" s="6">
-        <v>38</v>
+        <v>46.13</v>
       </c>
       <c r="D111" s="6">
-        <v>26</v>
-      </c>
-      <c r="E111" s="8">
-        <v>-12</v>
+        <v>44.49</v>
+      </c>
+      <c r="E111" s="7">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C112" s="6">
-        <v>81</v>
+        <v>36.97</v>
       </c>
       <c r="D112" s="6">
-        <v>87</v>
+        <v>36.88</v>
       </c>
       <c r="E112" s="7">
-        <v>6</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C113" s="6">
-        <v>7</v>
+        <v>38.28</v>
       </c>
       <c r="D113" s="6">
-        <v>32</v>
-      </c>
-      <c r="E113" s="7">
-        <v>25</v>
+        <v>44.13</v>
+      </c>
+      <c r="E113" s="8">
+        <v>5.85</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C114" s="6">
-        <v>19</v>
+        <v>36.19</v>
       </c>
       <c r="D114" s="6">
-        <v>7</v>
+        <v>49.92</v>
       </c>
       <c r="E114" s="8">
-        <v>-12</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="6">
-        <v>44.29</v>
+        <v>40.58</v>
       </c>
       <c r="D115" s="6">
-        <v>46.13</v>
-      </c>
-      <c r="E115" s="7">
-        <v>1.84</v>
+        <v>42.09</v>
+      </c>
+      <c r="E115" s="8">
+        <v>1.51</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>38.38</v>
+        <v>37.53</v>
       </c>
       <c r="D116" s="6">
-        <v>36.97</v>
+        <v>39.21</v>
       </c>
       <c r="E116" s="8">
-        <v>-1.41</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>30.72</v>
+        <v>37.74</v>
       </c>
       <c r="D117" s="6">
-        <v>38.28</v>
-      </c>
-      <c r="E117" s="7">
-        <v>7.56</v>
+        <v>48.88</v>
+      </c>
+      <c r="E117" s="8">
+        <v>11.14</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>36.83</v>
+        <v>35.01</v>
       </c>
       <c r="D118" s="6">
-        <v>36.19</v>
+        <v>43.29</v>
       </c>
       <c r="E118" s="8">
-        <v>-0.64</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>44.28</v>
+        <v>34.99</v>
       </c>
       <c r="D119" s="6">
-        <v>40.58</v>
+        <v>36.75</v>
       </c>
       <c r="E119" s="8">
-        <v>-3.7</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>36.19</v>
+        <v>35.47</v>
       </c>
       <c r="D120" s="6">
-        <v>37.53</v>
+        <v>33.72</v>
       </c>
       <c r="E120" s="7">
-        <v>1.34</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>20.82</v>
+        <v>50.61</v>
       </c>
       <c r="D121" s="6">
-        <v>37.74</v>
+        <v>46.71</v>
       </c>
       <c r="E121" s="7">
-        <v>16.92</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>37.53</v>
+        <v>29.33</v>
       </c>
       <c r="D122" s="6">
-        <v>35.01</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-2.52</v>
+        <v>28.95</v>
+      </c>
+      <c r="E122" s="7">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>27.08</v>
+        <v>61.06</v>
       </c>
       <c r="D123" s="6">
-        <v>34.99</v>
+        <v>60.5</v>
       </c>
       <c r="E123" s="7">
-        <v>7.91</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>31.57</v>
+        <v>54.23</v>
       </c>
       <c r="D124" s="6">
-        <v>35.47</v>
-      </c>
-      <c r="E124" s="7">
-        <v>3.9</v>
+        <v>61.04</v>
+      </c>
+      <c r="E124" s="8">
+        <v>6.81</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="6">
-        <v>38.27</v>
+        <v>32.57</v>
       </c>
       <c r="D125" s="6">
-        <v>50.61</v>
-      </c>
-      <c r="E125" s="7">
-        <v>12.34</v>
+        <v>33.75</v>
+      </c>
+      <c r="E125" s="8">
+        <v>1.18</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C126" s="6">
-        <v>24.8</v>
+        <v>30.65</v>
       </c>
       <c r="D126" s="6">
-        <v>29.33</v>
+        <v>28.82</v>
       </c>
       <c r="E126" s="7">
-        <v>4.53</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C127" s="6">
-        <v>58.18</v>
+        <v>-68.11</v>
       </c>
       <c r="D127" s="6">
-        <v>61.06</v>
-      </c>
-      <c r="E127" s="7">
-        <v>2.88</v>
+        <v>-34.09</v>
+      </c>
+      <c r="E127" s="8">
+        <v>34.02</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C128" s="6">
-        <v>26.97</v>
+        <v>-39.35</v>
       </c>
       <c r="D128" s="6">
-        <v>54.23</v>
+        <v>-65.17</v>
       </c>
       <c r="E128" s="7">
-        <v>27.26</v>
+        <v>-25.82</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C129" s="6">
-        <v>32.82</v>
+        <v>-30.33</v>
       </c>
       <c r="D129" s="6">
-        <v>32.57</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-0.25</v>
+        <v>-45.51</v>
+      </c>
+      <c r="E129" s="7">
+        <v>-15.18</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C130" s="6">
-        <v>30.14</v>
+        <v>-73.45999999999999</v>
       </c>
       <c r="D130" s="6">
-        <v>30.65</v>
-      </c>
-      <c r="E130" s="7">
-        <v>0.51</v>
+        <v>166.49</v>
+      </c>
+      <c r="E130" s="8">
+        <v>239.95</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="6">
-        <v>-28.91</v>
+        <v>27.2</v>
       </c>
       <c r="D131" s="6">
-        <v>-68.11</v>
-      </c>
-      <c r="E131" s="8">
-        <v>-39.2</v>
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E131" s="7">
+        <v>-36.23</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>-35.54</v>
+        <v>-23.48</v>
       </c>
       <c r="D132" s="6">
-        <v>-39.35</v>
-      </c>
-      <c r="E132" s="8">
-        <v>-3.81</v>
+        <v>-42.62</v>
+      </c>
+      <c r="E132" s="7">
+        <v>-19.14</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>6.04</v>
+        <v>146.94</v>
       </c>
       <c r="D133" s="6">
-        <v>-30.33</v>
+        <v>183.92</v>
       </c>
       <c r="E133" s="8">
-        <v>-36.37</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-79.47</v>
+        <v>-87.64</v>
       </c>
       <c r="D134" s="6">
-        <v>-73.45999999999999</v>
-      </c>
-      <c r="E134" s="7">
-        <v>6.01</v>
+        <v>-69.78</v>
+      </c>
+      <c r="E134" s="8">
+        <v>17.86</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>127.64</v>
+        <v>10.83</v>
       </c>
       <c r="D135" s="6">
-        <v>27.2</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-100.44</v>
+        <v>-15.22</v>
+      </c>
+      <c r="E135" s="7">
+        <v>-26.05</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-30.77</v>
+        <v>-50.38</v>
       </c>
       <c r="D136" s="6">
-        <v>-23.48</v>
-      </c>
-      <c r="E136" s="7">
-        <v>7.29</v>
+        <v>5.06</v>
+      </c>
+      <c r="E136" s="8">
+        <v>55.44</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>-2.53</v>
+        <v>253.23</v>
       </c>
       <c r="D137" s="6">
-        <v>146.94</v>
+        <v>-6.02</v>
       </c>
       <c r="E137" s="7">
-        <v>149.47</v>
+        <v>-259.25</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>-77.59</v>
+        <v>-27.22</v>
       </c>
       <c r="D138" s="6">
-        <v>-87.64</v>
+        <v>-11.72</v>
       </c>
       <c r="E138" s="8">
-        <v>-10.05</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>62.18</v>
+        <v>-30.32</v>
       </c>
       <c r="D139" s="6">
-        <v>10.83</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-51.35</v>
+        <v>-41.64</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-11.32</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="6">
-        <v>18.14</v>
+        <v>297.67</v>
       </c>
       <c r="D140" s="6">
-        <v>-50.38</v>
+        <v>354.72</v>
       </c>
       <c r="E140" s="8">
-        <v>-68.52</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="6">
-        <v>33.34</v>
+        <v>-75.8</v>
       </c>
       <c r="D141" s="6">
-        <v>253.23</v>
-      </c>
-      <c r="E141" s="7">
-        <v>219.89</v>
+        <v>-70.31999999999999</v>
+      </c>
+      <c r="E141" s="8">
+        <v>5.48</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C142" s="6">
-        <v>94.87</v>
+        <v>-68.88</v>
       </c>
       <c r="D142" s="6">
-        <v>-27.22</v>
+        <v>-61.52</v>
       </c>
       <c r="E142" s="8">
-        <v>-122.09</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C143" s="6">
-        <v>26.51</v>
-      </c>
-      <c r="D143" s="6">
-        <v>-30.32</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-56.83</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C144" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="D144" s="6">
-        <v>297.67</v>
-      </c>
-      <c r="E144" s="7">
-        <v>300.31</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C145" s="6">
-        <v>-66.27</v>
-      </c>
-      <c r="D145" s="6">
-        <v>-75.8</v>
-      </c>
-      <c r="E145" s="8">
-        <v>-9.529999999999999</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C146" s="6">
-        <v>-35.14</v>
-      </c>
-      <c r="D146" s="6">
-        <v>-68.88</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-33.74</v>
+        <v>7.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5431,28 +5312,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5466,16 +5347,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>39.8</v>
+        <v>42.4</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.9</v>
+        <v>-4.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5592,10 +5473,10 @@
         <v>49</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>46</v>
@@ -5615,34 +5496,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.346</v>
+        <v>0.3536</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2928</v>
+        <v>0.2825</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2162</v>
+        <v>0.2089</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1361</v>
+        <v>0.1254</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1295</v>
+        <v>0.1233</v>
       </c>
       <c r="F2" s="14">
-        <v>0.08960000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0563</v>
+        <v>0.0697</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0417</v>
+        <v>0.0483</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0405</v>
+        <v>0.0413</v>
       </c>
       <c r="J2" s="14">
-        <v>0.002</v>
+        <v>0.0122</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5650,16 +5531,16 @@
         <v>52</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>43</v>
@@ -5667,22 +5548,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.04099999999999999</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0644</v>
+        <v>-0.0675</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0737</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0771</v>
+        <v>-0.0725</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.0814</v>
+        <v>-0.0781</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1198</v>
+        <v>-0.108</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="95">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,16 +217,55 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.6 → 46.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.6</t>
+    <t>44.5 → 50.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>48.9 → 59.4</t>
+  </si>
+  <si>
+    <t>48.9</t>
+  </si>
+  <si>
+    <t>59.4</t>
+  </si>
+  <si>
+    <t>46.7 → 61.5</t>
   </si>
   <si>
     <t>46.7</t>
+  </si>
+  <si>
+    <t>61.5</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.9 → 36.5</t>
+  </si>
+  <si>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>36.5</t>
+  </si>
+  <si>
+    <t>28.8 → 35.2</t>
+  </si>
+  <si>
+    <t>28.8</t>
+  </si>
+  <si>
+    <t>35.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -312,14 +351,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,13 +391,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -951,10 +990,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>711.5</v>
+        <v>724.15</v>
       </c>
       <c r="D2">
-        <v>-0.58</v>
+        <v>1.78</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -963,46 +1002,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-5.42</v>
+        <v>-3.74</v>
       </c>
       <c r="H2">
-        <v>24.62</v>
+        <v>26.83</v>
       </c>
       <c r="I2">
-        <v>-1.86</v>
+        <v>-1.61</v>
       </c>
       <c r="J2">
-        <v>-1.56</v>
+        <v>1.17</v>
       </c>
       <c r="K2">
-        <v>-3.66</v>
+        <v>-1.25</v>
       </c>
       <c r="L2">
-        <v>-2.97</v>
+        <v>-0.8</v>
       </c>
       <c r="M2">
-        <v>28.25</v>
+        <v>26.73</v>
       </c>
       <c r="N2">
         <v>93</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>721.22</v>
+        <v>718.85</v>
       </c>
       <c r="Q2">
-        <v>724.5</v>
+        <v>724.78</v>
       </c>
       <c r="R2">
-        <v>726.01</v>
+        <v>725.72</v>
       </c>
       <c r="S2">
-        <v>687.99</v>
+        <v>687.92</v>
       </c>
       <c r="T2">
-        <v>3.42</v>
+        <v>5.27</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1017,34 +1056,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.49</v>
+        <v>50.3</v>
       </c>
       <c r="Z2">
-        <v>-2.01</v>
+        <v>-1.64</v>
       </c>
       <c r="AA2">
-        <v>-0.53</v>
+        <v>-0.75</v>
       </c>
       <c r="AB2">
-        <v>-1.48</v>
+        <v>-0.88</v>
       </c>
       <c r="AC2">
-        <v>12.17</v>
+        <v>25.08</v>
       </c>
       <c r="AD2">
-        <v>27.17</v>
+        <v>21.31</v>
       </c>
       <c r="AE2">
-        <v>16.07</v>
+        <v>15.96</v>
       </c>
       <c r="AF2">
-        <v>-34.09</v>
+        <v>-47.54</v>
       </c>
       <c r="AG2">
-        <v>746.0599999999999</v>
+        <v>746.16</v>
       </c>
       <c r="AH2">
-        <v>702.9299999999999</v>
+        <v>703.4</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1053,7 +1092,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>16.31</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1064,10 +1103,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>852.6</v>
+        <v>852.3</v>
       </c>
       <c r="D3">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1076,46 +1115,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-21.17</v>
+        <v>-21.19</v>
       </c>
       <c r="H3">
-        <v>68.70999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I3">
-        <v>-3.67</v>
+        <v>-7.77</v>
       </c>
       <c r="J3">
-        <v>-11.03</v>
+        <v>-9.09</v>
       </c>
       <c r="K3">
-        <v>-5.41</v>
+        <v>-4.69</v>
       </c>
       <c r="L3">
-        <v>-2.46</v>
+        <v>-1.51</v>
       </c>
       <c r="M3">
-        <v>1.22</v>
+        <v>0.23</v>
       </c>
       <c r="N3">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>882.1799999999999</v>
+        <v>867.8099999999999</v>
       </c>
       <c r="Q3">
-        <v>935.6799999999999</v>
+        <v>930.9299999999999</v>
       </c>
       <c r="R3">
-        <v>952.17</v>
+        <v>948.91</v>
       </c>
       <c r="S3">
-        <v>770.23</v>
+        <v>770.72</v>
       </c>
       <c r="T3">
-        <v>10.69</v>
+        <v>10.58</v>
       </c>
       <c r="U3" t="s">
         <v>54</v>
@@ -1130,43 +1169,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>36.88</v>
+        <v>36.84</v>
       </c>
       <c r="Z3">
-        <v>-22.71</v>
+        <v>-24.95</v>
       </c>
       <c r="AA3">
-        <v>-11.29</v>
+        <v>-14.02</v>
       </c>
       <c r="AB3">
-        <v>-11.42</v>
+        <v>-10.92</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>10.36</v>
+        <v>3.23</v>
       </c>
       <c r="AE3">
-        <v>42.41</v>
+        <v>41.08</v>
       </c>
       <c r="AF3">
-        <v>-65.17</v>
+        <v>-69.2</v>
       </c>
       <c r="AG3">
-        <v>1040.72</v>
+        <v>1042.17</v>
       </c>
       <c r="AH3">
-        <v>830.63</v>
+        <v>819.6900000000001</v>
       </c>
       <c r="AI3">
-        <v>988.8099999999999</v>
+        <v>968.6799999999999</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>33.64</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,10 +1216,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>200.11</v>
+        <v>200.05</v>
       </c>
       <c r="D4">
-        <v>1.04</v>
+        <v>-0.03</v>
       </c>
       <c r="E4">
         <v>299.61</v>
@@ -1189,46 +1228,46 @@
         <v>195.76</v>
       </c>
       <c r="G4">
-        <v>-33.21</v>
+        <v>-33.23</v>
       </c>
       <c r="H4">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="I4">
-        <v>1.5</v>
+        <v>-0.12</v>
       </c>
       <c r="J4">
-        <v>-1.91</v>
+        <v>-1.48</v>
       </c>
       <c r="K4">
-        <v>-13.24</v>
+        <v>-13.33</v>
       </c>
       <c r="L4">
-        <v>-33.69</v>
+        <v>-32.37</v>
       </c>
       <c r="M4">
-        <v>-7</v>
+        <v>-7.59</v>
       </c>
       <c r="N4">
         <v>26</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>198.85</v>
+        <v>198.8</v>
       </c>
       <c r="Q4">
-        <v>200.55</v>
+        <v>200.46</v>
       </c>
       <c r="R4">
-        <v>206.98</v>
+        <v>206.64</v>
       </c>
       <c r="S4">
-        <v>238.19</v>
+        <v>237.83</v>
       </c>
       <c r="T4">
-        <v>-15.99</v>
+        <v>-15.89</v>
       </c>
       <c r="U4" t="s">
         <v>54</v>
@@ -1243,34 +1282,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.13</v>
+        <v>44</v>
       </c>
       <c r="Z4">
-        <v>-2.64</v>
+        <v>-2.41</v>
       </c>
       <c r="AA4">
-        <v>-2.97</v>
+        <v>-2.85</v>
       </c>
       <c r="AB4">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="AC4">
-        <v>73.19</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="AD4">
-        <v>73.22</v>
+        <v>80.36</v>
       </c>
       <c r="AE4">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="AF4">
-        <v>-45.51</v>
+        <v>-41.34</v>
       </c>
       <c r="AG4">
-        <v>204.74</v>
+        <v>204.59</v>
       </c>
       <c r="AH4">
-        <v>196.37</v>
+        <v>196.33</v>
       </c>
       <c r="AI4">
         <v>207.87</v>
@@ -1279,7 +1318,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>38.47</v>
+        <v>35.24</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1290,10 +1329,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>636.95</v>
+        <v>629.85</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>-1.11</v>
       </c>
       <c r="E5">
         <v>907</v>
@@ -1302,46 +1341,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-29.77</v>
+        <v>-30.56</v>
       </c>
       <c r="H5">
-        <v>10.89</v>
+        <v>9.65</v>
       </c>
       <c r="I5">
-        <v>3.17</v>
+        <v>2.16</v>
       </c>
       <c r="J5">
-        <v>5.62</v>
+        <v>3.16</v>
       </c>
       <c r="K5">
-        <v>-10.84</v>
+        <v>-10.31</v>
       </c>
       <c r="L5">
-        <v>-29.85</v>
+        <v>-29.56</v>
       </c>
       <c r="M5">
-        <v>-6.75</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="N5">
         <v>44</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P5">
-        <v>609.2</v>
+        <v>611.86</v>
       </c>
       <c r="Q5">
-        <v>651.21</v>
+        <v>652.08</v>
       </c>
       <c r="R5">
-        <v>648.42</v>
+        <v>647.54</v>
       </c>
       <c r="S5">
-        <v>694.64</v>
+        <v>693.97</v>
       </c>
       <c r="T5">
-        <v>-8.31</v>
+        <v>-9.24</v>
       </c>
       <c r="U5" t="s">
         <v>55</v>
@@ -1356,34 +1395,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>49.92</v>
+        <v>48.23</v>
       </c>
       <c r="Z5">
-        <v>-13.75</v>
+        <v>-12.18</v>
       </c>
       <c r="AA5">
-        <v>-10.18</v>
+        <v>-10.58</v>
       </c>
       <c r="AB5">
-        <v>-3.58</v>
+        <v>-1.6</v>
       </c>
       <c r="AC5">
-        <v>30.03</v>
+        <v>57.82</v>
       </c>
       <c r="AD5">
-        <v>11.38</v>
+        <v>29.6</v>
       </c>
       <c r="AE5">
-        <v>28.78</v>
+        <v>27.96</v>
       </c>
       <c r="AF5">
-        <v>166.49</v>
+        <v>-48.99</v>
       </c>
       <c r="AG5">
-        <v>756.22</v>
+        <v>756.02</v>
       </c>
       <c r="AH5">
-        <v>546.2</v>
+        <v>548.14</v>
       </c>
       <c r="AI5">
         <v>676.63</v>
@@ -1392,7 +1431,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>16.16</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1442,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1662.7</v>
+        <v>1672.4</v>
       </c>
       <c r="D6">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1415,46 +1454,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-19.35</v>
+        <v>-18.88</v>
       </c>
       <c r="H6">
-        <v>23.35</v>
+        <v>24.07</v>
       </c>
       <c r="I6">
-        <v>-0.86</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J6">
-        <v>-6.21</v>
+        <v>-5.21</v>
       </c>
       <c r="K6">
-        <v>-9.41</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L6">
-        <v>0.01</v>
+        <v>-0.99</v>
       </c>
       <c r="M6">
-        <v>4.83</v>
+        <v>4.04</v>
       </c>
       <c r="N6">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O6">
         <v>55</v>
       </c>
       <c r="P6">
-        <v>1667.64</v>
+        <v>1665.76</v>
       </c>
       <c r="Q6">
-        <v>1700.38</v>
+        <v>1695.92</v>
       </c>
       <c r="R6">
-        <v>1714.48</v>
+        <v>1712.8</v>
       </c>
       <c r="S6">
-        <v>1701.68</v>
+        <v>1701.08</v>
       </c>
       <c r="T6">
-        <v>-2.29</v>
+        <v>-1.69</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -1469,34 +1508,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.09</v>
+        <v>44.55</v>
       </c>
       <c r="Z6">
-        <v>-19.61</v>
+        <v>-18.48</v>
       </c>
       <c r="AA6">
-        <v>-17.72</v>
+        <v>-17.88</v>
       </c>
       <c r="AB6">
-        <v>-1.88</v>
+        <v>-0.61</v>
       </c>
       <c r="AC6">
-        <v>47.18</v>
+        <v>67.7</v>
       </c>
       <c r="AD6">
-        <v>34.31</v>
+        <v>47.78</v>
       </c>
       <c r="AE6">
-        <v>49.53</v>
+        <v>48.45</v>
       </c>
       <c r="AF6">
-        <v>-9.029999999999999</v>
+        <v>-60.23</v>
       </c>
       <c r="AG6">
-        <v>1799.27</v>
+        <v>1791.16</v>
       </c>
       <c r="AH6">
-        <v>1601.49</v>
+        <v>1600.68</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1505,7 +1544,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>27.85</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1516,10 +1555,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>958.8</v>
+        <v>960</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1528,46 +1567,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-23.93</v>
+        <v>-23.83</v>
       </c>
       <c r="H7">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="I7">
-        <v>0.53</v>
+        <v>-1.64</v>
       </c>
       <c r="J7">
-        <v>-4.22</v>
+        <v>-3.96</v>
       </c>
       <c r="K7">
-        <v>-12.73</v>
+        <v>-12.54</v>
       </c>
       <c r="L7">
-        <v>-13.67</v>
+        <v>-13.58</v>
       </c>
       <c r="M7">
-        <v>4.13</v>
+        <v>3.36</v>
       </c>
       <c r="N7">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P7">
-        <v>962.04</v>
+        <v>958.84</v>
       </c>
       <c r="Q7">
-        <v>976.6799999999999</v>
+        <v>975.13</v>
       </c>
       <c r="R7">
-        <v>1024.1</v>
+        <v>1021.64</v>
       </c>
       <c r="S7">
-        <v>1102.76</v>
+        <v>1101.68</v>
       </c>
       <c r="T7">
-        <v>-13.05</v>
+        <v>-12.86</v>
       </c>
       <c r="U7" t="s">
         <v>54</v>
@@ -1582,34 +1621,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>39.21</v>
+        <v>39.76</v>
       </c>
       <c r="Z7">
-        <v>-19.17</v>
+        <v>-18.27</v>
       </c>
       <c r="AA7">
-        <v>-20.28</v>
+        <v>-19.88</v>
       </c>
       <c r="AB7">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AC7">
-        <v>59.97</v>
+        <v>69.52</v>
       </c>
       <c r="AD7">
-        <v>66.83</v>
+        <v>64.31</v>
       </c>
       <c r="AE7">
-        <v>17.97</v>
+        <v>17.91</v>
       </c>
       <c r="AF7">
-        <v>-42.62</v>
+        <v>54.03</v>
       </c>
       <c r="AG7">
-        <v>1015.45</v>
+        <v>1013.97</v>
       </c>
       <c r="AH7">
-        <v>937.91</v>
+        <v>936.29</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1618,7 +1657,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>49.28</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,10 +1668,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3257</v>
+        <v>3426.7</v>
       </c>
       <c r="D8">
-        <v>4.06</v>
+        <v>5.21</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1641,46 +1680,46 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-43.36</v>
+        <v>-40.4</v>
       </c>
       <c r="H8">
-        <v>8.710000000000001</v>
+        <v>14.38</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>10.79</v>
       </c>
       <c r="J8">
-        <v>-3.72</v>
+        <v>0.52</v>
       </c>
       <c r="K8">
-        <v>-14.82</v>
+        <v>-7.32</v>
       </c>
       <c r="L8">
-        <v>-38.48</v>
+        <v>-36.11</v>
       </c>
       <c r="M8">
-        <v>-10.8</v>
+        <v>-10.03</v>
       </c>
       <c r="N8">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P8">
-        <v>3111.7</v>
+        <v>3178.44</v>
       </c>
       <c r="Q8">
-        <v>3209.1</v>
+        <v>3211.29</v>
       </c>
       <c r="R8">
-        <v>3479.6</v>
+        <v>3474.67</v>
       </c>
       <c r="S8">
-        <v>4169.48</v>
+        <v>4159.94</v>
       </c>
       <c r="T8">
-        <v>-21.88</v>
+        <v>-17.63</v>
       </c>
       <c r="U8" t="s">
         <v>54</v>
@@ -1695,43 +1734,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>48.88</v>
+        <v>59.36</v>
       </c>
       <c r="Z8">
-        <v>-103.99</v>
+        <v>-75.06</v>
       </c>
       <c r="AA8">
-        <v>-118.16</v>
+        <v>-109.54</v>
       </c>
       <c r="AB8">
-        <v>14.17</v>
+        <v>34.48</v>
       </c>
       <c r="AC8">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="AD8">
-        <v>37.34</v>
+        <v>67.81</v>
       </c>
       <c r="AE8">
-        <v>96.7</v>
+        <v>102.93</v>
       </c>
       <c r="AF8">
-        <v>183.92</v>
+        <v>239.24</v>
       </c>
       <c r="AG8">
-        <v>3449.06</v>
+        <v>3458.6</v>
       </c>
       <c r="AH8">
-        <v>2969.15</v>
+        <v>2963.98</v>
       </c>
       <c r="AI8">
-        <v>3326.38</v>
+        <v>3028.27</v>
       </c>
       <c r="AJ8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AK8">
-        <v>52.98</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1781,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>619.6</v>
+        <v>621.55</v>
       </c>
       <c r="D9">
-        <v>3.4</v>
+        <v>0.31</v>
       </c>
       <c r="E9">
         <v>1029.69</v>
@@ -1754,46 +1793,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-39.83</v>
+        <v>-39.64</v>
       </c>
       <c r="H9">
-        <v>15.09</v>
+        <v>15.45</v>
       </c>
       <c r="I9">
-        <v>-0.35</v>
+        <v>-0.42</v>
       </c>
       <c r="J9">
-        <v>0.13</v>
+        <v>-3.66</v>
       </c>
       <c r="K9">
-        <v>-9.75</v>
+        <v>-7.03</v>
       </c>
       <c r="L9">
-        <v>-32.34</v>
+        <v>-32.43</v>
       </c>
       <c r="M9">
-        <v>35.36</v>
+        <v>32.02</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P9">
-        <v>613.52</v>
+        <v>613</v>
       </c>
       <c r="Q9">
-        <v>650.71</v>
+        <v>649.24</v>
       </c>
       <c r="R9">
-        <v>652.7</v>
+        <v>651.54</v>
       </c>
       <c r="S9">
-        <v>658.0599999999999</v>
+        <v>657.61</v>
       </c>
       <c r="T9">
-        <v>-5.84</v>
+        <v>-5.48</v>
       </c>
       <c r="U9" t="s">
         <v>54</v>
@@ -1808,34 +1847,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>43.29</v>
+        <v>44.03</v>
       </c>
       <c r="Z9">
-        <v>-12.96</v>
+        <v>-12.36</v>
       </c>
       <c r="AA9">
-        <v>-8.390000000000001</v>
+        <v>-9.19</v>
       </c>
       <c r="AB9">
-        <v>-4.57</v>
+        <v>-3.17</v>
       </c>
       <c r="AC9">
-        <v>13.89</v>
+        <v>30.92</v>
       </c>
       <c r="AD9">
-        <v>6.78</v>
+        <v>15.34</v>
       </c>
       <c r="AE9">
-        <v>21.36</v>
+        <v>20.93</v>
       </c>
       <c r="AF9">
-        <v>-69.78</v>
+        <v>-91.48</v>
       </c>
       <c r="AG9">
-        <v>725.3099999999999</v>
+        <v>724.98</v>
       </c>
       <c r="AH9">
-        <v>576.11</v>
+        <v>573.51</v>
       </c>
       <c r="AI9">
         <v>665.02</v>
@@ -1844,7 +1883,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>15.99</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,10 +1894,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>343.7</v>
+        <v>345</v>
       </c>
       <c r="D10">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1867,46 +1906,46 @@
         <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-25.57</v>
+        <v>-25.29</v>
       </c>
       <c r="H10">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="I10">
-        <v>-2.22</v>
+        <v>-1.89</v>
       </c>
       <c r="J10">
-        <v>-7.11</v>
+        <v>-5.99</v>
       </c>
       <c r="K10">
-        <v>-9.039999999999999</v>
+        <v>-8.66</v>
       </c>
       <c r="L10">
-        <v>-12.43</v>
+        <v>-10.49</v>
       </c>
       <c r="M10">
-        <v>12.54</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N10">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O10">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P10">
-        <v>343.66</v>
+        <v>342.33</v>
       </c>
       <c r="Q10">
-        <v>358.29</v>
+        <v>357.31</v>
       </c>
       <c r="R10">
-        <v>366.47</v>
+        <v>365.75</v>
       </c>
       <c r="S10">
-        <v>385.58</v>
+        <v>385.39</v>
       </c>
       <c r="T10">
-        <v>-10.86</v>
+        <v>-10.48</v>
       </c>
       <c r="U10" t="s">
         <v>54</v>
@@ -1921,34 +1960,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>36.75</v>
+        <v>38.26</v>
       </c>
       <c r="Z10">
-        <v>-6.86</v>
+        <v>-6.79</v>
       </c>
       <c r="AA10">
-        <v>-4.9</v>
+        <v>-5.28</v>
       </c>
       <c r="AB10">
-        <v>-1.95</v>
+        <v>-1.51</v>
       </c>
       <c r="AC10">
-        <v>24.81</v>
+        <v>40.59</v>
       </c>
       <c r="AD10">
-        <v>12.96</v>
+        <v>25.52</v>
       </c>
       <c r="AE10">
-        <v>7.85</v>
+        <v>7.6</v>
       </c>
       <c r="AF10">
-        <v>-15.22</v>
+        <v>-39.38</v>
       </c>
       <c r="AG10">
-        <v>379.63</v>
+        <v>379.22</v>
       </c>
       <c r="AH10">
-        <v>336.95</v>
+        <v>335.39</v>
       </c>
       <c r="AI10">
         <v>362.14</v>
@@ -1957,7 +1996,7 @@
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>42.38</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1968,10 +2007,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>172.24</v>
+        <v>175</v>
       </c>
       <c r="D11">
-        <v>-0.9</v>
+        <v>1.6</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1980,46 +2019,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-20.5</v>
+        <v>-19.23</v>
       </c>
       <c r="H11">
-        <v>9.41</v>
+        <v>11.17</v>
       </c>
       <c r="I11">
-        <v>-3.31</v>
+        <v>-2.07</v>
       </c>
       <c r="J11">
-        <v>-8.75</v>
+        <v>-6.31</v>
       </c>
       <c r="K11">
-        <v>-7.95</v>
+        <v>-7.05</v>
       </c>
       <c r="L11">
-        <v>2.54</v>
+        <v>3.88</v>
       </c>
       <c r="M11">
-        <v>8.49</v>
+        <v>8.43</v>
       </c>
       <c r="N11">
         <v>87</v>
       </c>
       <c r="O11">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P11">
-        <v>174.47</v>
+        <v>173.73</v>
       </c>
       <c r="Q11">
-        <v>182.24</v>
+        <v>181.84</v>
       </c>
       <c r="R11">
-        <v>184.93</v>
+        <v>184.63</v>
       </c>
       <c r="S11">
-        <v>192.21</v>
+        <v>192.25</v>
       </c>
       <c r="T11">
-        <v>-10.39</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="U11" t="s">
         <v>54</v>
@@ -2034,34 +2073,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>33.72</v>
+        <v>39.43</v>
       </c>
       <c r="Z11">
-        <v>-3.28</v>
+        <v>-3.3</v>
       </c>
       <c r="AA11">
-        <v>-1.87</v>
+        <v>-2.16</v>
       </c>
       <c r="AB11">
-        <v>-1.41</v>
+        <v>-1.15</v>
       </c>
       <c r="AC11">
-        <v>7.55</v>
+        <v>17.35</v>
       </c>
       <c r="AD11">
-        <v>4.9</v>
+        <v>9.92</v>
       </c>
       <c r="AE11">
-        <v>4.76</v>
+        <v>4.66</v>
       </c>
       <c r="AF11">
-        <v>5.06</v>
+        <v>-17.17</v>
       </c>
       <c r="AG11">
-        <v>193.57</v>
+        <v>193.61</v>
       </c>
       <c r="AH11">
-        <v>170.9</v>
+        <v>170.06</v>
       </c>
       <c r="AI11">
         <v>186.52</v>
@@ -2070,7 +2109,7 @@
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>36.98</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2081,10 +2120,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2125</v>
+        <v>2269.3</v>
       </c>
       <c r="D12">
-        <v>-1.44</v>
+        <v>6.79</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2093,46 +2132,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-34.04</v>
+        <v>-29.57</v>
       </c>
       <c r="H12">
-        <v>7.18</v>
+        <v>14.46</v>
       </c>
       <c r="I12">
-        <v>0.5</v>
+        <v>8.06</v>
       </c>
       <c r="J12">
-        <v>-3.76</v>
+        <v>2.96</v>
       </c>
       <c r="K12">
-        <v>-2.59</v>
+        <v>3.12</v>
       </c>
       <c r="L12">
-        <v>-25.98</v>
+        <v>-22.35</v>
       </c>
       <c r="M12">
-        <v>-7.81</v>
+        <v>-6.6</v>
       </c>
       <c r="N12">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="O12">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="P12">
-        <v>2107.46</v>
+        <v>2141.32</v>
       </c>
       <c r="Q12">
-        <v>2115.42</v>
+        <v>2118.84</v>
       </c>
       <c r="R12">
-        <v>2248.09</v>
+        <v>2246.16</v>
       </c>
       <c r="S12">
-        <v>2452.01</v>
+        <v>2447.32</v>
       </c>
       <c r="T12">
-        <v>-13.34</v>
+        <v>-7.27</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2147,43 +2186,43 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>46.71</v>
+        <v>61.55</v>
       </c>
       <c r="Z12">
-        <v>-37.44</v>
+        <v>-21.93</v>
       </c>
       <c r="AA12">
-        <v>-48.73</v>
+        <v>-43.37</v>
       </c>
       <c r="AB12">
-        <v>11.29</v>
+        <v>21.44</v>
       </c>
       <c r="AC12">
-        <v>84.23</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="AD12">
-        <v>80.91</v>
+        <v>86.53</v>
       </c>
       <c r="AE12">
-        <v>63.68</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="AF12">
-        <v>-6.02</v>
+        <v>192.78</v>
       </c>
       <c r="AG12">
-        <v>2226.95</v>
+        <v>2244.71</v>
       </c>
       <c r="AH12">
-        <v>2003.88</v>
+        <v>1992.97</v>
       </c>
       <c r="AI12">
-        <v>2235.3</v>
+        <v>2003.85</v>
       </c>
       <c r="AJ12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AK12">
-        <v>32.4</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2194,10 +2233,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4400</v>
+        <v>4487</v>
       </c>
       <c r="D13">
-        <v>-0.23</v>
+        <v>1.98</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2206,46 +2245,46 @@
         <v>3531.9</v>
       </c>
       <c r="G13">
-        <v>-14.88</v>
+        <v>-13.2</v>
       </c>
       <c r="H13">
-        <v>24.58</v>
+        <v>27.04</v>
       </c>
       <c r="I13">
-        <v>-3.93</v>
+        <v>-1.38</v>
       </c>
       <c r="J13">
-        <v>-12.09</v>
+        <v>-10.64</v>
       </c>
       <c r="K13">
-        <v>-4.38</v>
+        <v>-1.9</v>
       </c>
       <c r="L13">
-        <v>28.72</v>
+        <v>25.84</v>
       </c>
       <c r="M13">
-        <v>12.33</v>
+        <v>12.37</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P13">
-        <v>4419.3</v>
+        <v>4406.7</v>
       </c>
       <c r="Q13">
-        <v>4704.36</v>
+        <v>4678.24</v>
       </c>
       <c r="R13">
-        <v>4908.13</v>
+        <v>4900.36</v>
       </c>
       <c r="S13">
-        <v>4424.21</v>
+        <v>4427.01</v>
       </c>
       <c r="T13">
-        <v>-0.55</v>
+        <v>1.36</v>
       </c>
       <c r="U13" t="s">
         <v>54</v>
@@ -2257,37 +2296,37 @@
         <v>54</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13">
-        <v>28.95</v>
+        <v>36.49</v>
       </c>
       <c r="Z13">
-        <v>-147.99</v>
+        <v>-142.41</v>
       </c>
       <c r="AA13">
-        <v>-109.37</v>
+        <v>-115.98</v>
       </c>
       <c r="AB13">
-        <v>-38.62</v>
+        <v>-26.43</v>
       </c>
       <c r="AC13">
-        <v>12.56</v>
+        <v>31.32</v>
       </c>
       <c r="AD13">
-        <v>8.789999999999999</v>
+        <v>16.81</v>
       </c>
       <c r="AE13">
-        <v>96.56</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="AF13">
-        <v>-11.72</v>
+        <v>-33.78</v>
       </c>
       <c r="AG13">
-        <v>5127.97</v>
+        <v>5086.79</v>
       </c>
       <c r="AH13">
-        <v>4280.75</v>
+        <v>4269.68</v>
       </c>
       <c r="AI13">
         <v>4684.57</v>
@@ -2296,7 +2335,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>64.47</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2307,10 +2346,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2913</v>
+        <v>2987.8</v>
       </c>
       <c r="D14">
-        <v>-0.18</v>
+        <v>2.57</v>
       </c>
       <c r="E14">
         <v>4807.3</v>
@@ -2319,46 +2358,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-39.4</v>
+        <v>-37.85</v>
       </c>
       <c r="H14">
-        <v>32.77</v>
+        <v>36.18</v>
       </c>
       <c r="I14">
-        <v>12.91</v>
+        <v>2.81</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>0.44</v>
+        <v>4.14</v>
       </c>
       <c r="L14">
-        <v>-37.74</v>
+        <v>-35.19</v>
       </c>
       <c r="M14">
-        <v>20.89</v>
+        <v>20.65</v>
       </c>
       <c r="N14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P14">
-        <v>2900.76</v>
+        <v>2917.12</v>
       </c>
       <c r="Q14">
-        <v>2760.16</v>
+        <v>2769.43</v>
       </c>
       <c r="R14">
-        <v>2866.75</v>
+        <v>2866.38</v>
       </c>
       <c r="S14">
-        <v>2819.48</v>
+        <v>2813.5</v>
       </c>
       <c r="T14">
-        <v>3.32</v>
+        <v>6.2</v>
       </c>
       <c r="U14" t="s">
         <v>54</v>
@@ -2373,43 +2412,43 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>60.5</v>
+        <v>65.39</v>
       </c>
       <c r="Z14">
-        <v>3.8</v>
+        <v>18.18</v>
       </c>
       <c r="AA14">
-        <v>-31.25</v>
+        <v>-21.36</v>
       </c>
       <c r="AB14">
-        <v>35.05</v>
+        <v>39.54</v>
       </c>
       <c r="AC14">
-        <v>96.87</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="AD14">
-        <v>96.3</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="AE14">
-        <v>74.08</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AF14">
-        <v>-41.64</v>
+        <v>-18.2</v>
       </c>
       <c r="AG14">
-        <v>2985.48</v>
+        <v>3016.29</v>
       </c>
       <c r="AH14">
-        <v>2534.84</v>
+        <v>2522.57</v>
       </c>
       <c r="AI14">
-        <v>2711.5</v>
+        <v>2722.95</v>
       </c>
       <c r="AJ14" t="s">
         <v>56</v>
       </c>
       <c r="AK14">
-        <v>47.41</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2420,58 +2459,58 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>227.89</v>
+        <v>214.83</v>
       </c>
       <c r="D15">
-        <v>5.05</v>
+        <v>-5.73</v>
       </c>
       <c r="E15">
-        <v>356.55</v>
+        <v>353.1</v>
       </c>
       <c r="F15">
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-36.08</v>
+        <v>-39.16</v>
       </c>
       <c r="H15">
-        <v>18.83</v>
+        <v>12.02</v>
       </c>
       <c r="I15">
-        <v>17.46</v>
+        <v>9.44</v>
       </c>
       <c r="J15">
-        <v>-0.39</v>
+        <v>-2.7</v>
       </c>
       <c r="K15">
-        <v>-5.29</v>
+        <v>-14.9</v>
       </c>
       <c r="L15">
-        <v>-37.73</v>
+        <v>-39.75</v>
       </c>
       <c r="M15">
-        <v>6.97</v>
+        <v>5.48</v>
       </c>
       <c r="N15">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="O15">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="P15">
-        <v>206.19</v>
+        <v>209.89</v>
       </c>
       <c r="Q15">
-        <v>209.44</v>
+        <v>209.08</v>
       </c>
       <c r="R15">
-        <v>221.7</v>
+        <v>221.48</v>
       </c>
       <c r="S15">
-        <v>246.04</v>
+        <v>245.58</v>
       </c>
       <c r="T15">
-        <v>-7.38</v>
+        <v>-12.52</v>
       </c>
       <c r="U15" t="s">
         <v>54</v>
@@ -2486,34 +2525,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>61.04</v>
+        <v>51.24</v>
       </c>
       <c r="Z15">
-        <v>-4.46</v>
+        <v>-3.58</v>
       </c>
       <c r="AA15">
-        <v>-6.53</v>
+        <v>-5.94</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="AC15">
-        <v>77.11</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="AD15">
-        <v>58.69</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AE15">
-        <v>10.47</v>
+        <v>11.29</v>
       </c>
       <c r="AF15">
-        <v>354.72</v>
+        <v>394.92</v>
       </c>
       <c r="AG15">
-        <v>231.26</v>
+        <v>230.25</v>
       </c>
       <c r="AH15">
-        <v>187.63</v>
+        <v>187.91</v>
       </c>
       <c r="AI15">
         <v>193.57</v>
@@ -2522,7 +2561,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>44.29</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2533,10 +2572,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>33.02</v>
+        <v>33.76</v>
       </c>
       <c r="D16">
-        <v>0.4</v>
+        <v>2.24</v>
       </c>
       <c r="E16">
         <v>57.7</v>
@@ -2545,25 +2584,25 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-42.77</v>
+        <v>-41.49</v>
       </c>
       <c r="H16">
-        <v>5.29</v>
+        <v>7.65</v>
       </c>
       <c r="I16">
-        <v>-3.82</v>
+        <v>-1.23</v>
       </c>
       <c r="J16">
-        <v>-8.609999999999999</v>
+        <v>-5.99</v>
       </c>
       <c r="K16">
-        <v>-19.7</v>
+        <v>-16.87</v>
       </c>
       <c r="L16">
-        <v>-43.73</v>
+        <v>-41.27</v>
       </c>
       <c r="M16">
-        <v>-7.25</v>
+        <v>-7.74</v>
       </c>
       <c r="N16">
         <v>7</v>
@@ -2572,19 +2611,19 @@
         <v>12</v>
       </c>
       <c r="P16">
-        <v>33.41</v>
+        <v>33.33</v>
       </c>
       <c r="Q16">
-        <v>34.86</v>
+        <v>34.77</v>
       </c>
       <c r="R16">
-        <v>36.87</v>
+        <v>36.75</v>
       </c>
       <c r="S16">
-        <v>41.22</v>
+        <v>41.14</v>
       </c>
       <c r="T16">
-        <v>-19.89</v>
+        <v>-17.94</v>
       </c>
       <c r="U16" t="s">
         <v>54</v>
@@ -2599,34 +2638,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>33.75</v>
+        <v>40.13</v>
       </c>
       <c r="Z16">
-        <v>-1.08</v>
+        <v>-1.03</v>
       </c>
       <c r="AA16">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="AB16">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="AC16">
-        <v>2.69</v>
+        <v>20.05</v>
       </c>
       <c r="AD16">
-        <v>12.36</v>
+        <v>10.93</v>
       </c>
       <c r="AE16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>-70.31999999999999</v>
+        <v>-73.58</v>
       </c>
       <c r="AG16">
-        <v>37.04</v>
+        <v>36.97</v>
       </c>
       <c r="AH16">
-        <v>32.69</v>
+        <v>32.57</v>
       </c>
       <c r="AI16">
         <v>36.59</v>
@@ -2635,7 +2674,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>15.56</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2646,10 +2685,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1020</v>
+        <v>1041</v>
       </c>
       <c r="D17">
-        <v>-1.33</v>
+        <v>2.06</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2658,46 +2697,46 @@
         <v>1020</v>
       </c>
       <c r="G17">
-        <v>-34.46</v>
+        <v>-33.12</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="I17">
-        <v>-3.89</v>
+        <v>-2.52</v>
       </c>
       <c r="J17">
-        <v>-10.82</v>
+        <v>-10.14</v>
       </c>
       <c r="K17">
-        <v>-24.42</v>
+        <v>-23.39</v>
       </c>
       <c r="L17">
-        <v>-25.43</v>
+        <v>-23.63</v>
       </c>
       <c r="M17">
-        <v>-4.27</v>
+        <v>-4.06</v>
       </c>
       <c r="N17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P17">
-        <v>1042.08</v>
+        <v>1036.7</v>
       </c>
       <c r="Q17">
-        <v>1095.19</v>
+        <v>1088.99</v>
       </c>
       <c r="R17">
-        <v>1180.49</v>
+        <v>1174.73</v>
       </c>
       <c r="S17">
-        <v>1319.99</v>
+        <v>1318.29</v>
       </c>
       <c r="T17">
-        <v>-22.73</v>
+        <v>-21.03</v>
       </c>
       <c r="U17" t="s">
         <v>54</v>
@@ -2712,43 +2751,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>28.82</v>
+        <v>35.21</v>
       </c>
       <c r="Z17">
-        <v>-41.97</v>
+        <v>-40.82</v>
       </c>
       <c r="AA17">
-        <v>-38.4</v>
+        <v>-38.89</v>
       </c>
       <c r="AB17">
-        <v>-3.57</v>
+        <v>-1.94</v>
       </c>
       <c r="AC17">
-        <v>3.91</v>
+        <v>16.28</v>
       </c>
       <c r="AD17">
-        <v>15.31</v>
+        <v>11.55</v>
       </c>
       <c r="AE17">
-        <v>29.08</v>
+        <v>29.04</v>
       </c>
       <c r="AF17">
-        <v>-61.52</v>
+        <v>-35.2</v>
       </c>
       <c r="AG17">
-        <v>1180.89</v>
+        <v>1171.3</v>
       </c>
       <c r="AH17">
-        <v>1009.49</v>
+        <v>1006.68</v>
       </c>
       <c r="AI17">
-        <v>1119.4</v>
+        <v>1113.88</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>56.25</v>
+        <v>59.02</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +2928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2929,7 +2968,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2947,2348 +2986,2445 @@
         <v>68</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-12.31</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-11.03</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.52</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-1.91</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="D10" s="6">
-        <v>5.62</v>
-      </c>
-      <c r="E10" s="8">
-        <v>8.57</v>
+      <c r="B10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.48</v>
+        <v>-1.56</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.21</v>
+        <v>1.17</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.73</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.83</v>
+        <v>-11.03</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.22</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.61</v>
+        <v>-9.09</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.94</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.37</v>
+        <v>-1.91</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.72</v>
-      </c>
-      <c r="E13" s="8">
-        <v>6.65</v>
+        <v>-1.48</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.67</v>
+        <v>5.62</v>
       </c>
       <c r="D14" s="6">
-        <v>0.13</v>
+        <v>3.16</v>
       </c>
       <c r="E14" s="8">
-        <v>3.8</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.4</v>
+        <v>-6.21</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.11</v>
+        <v>-5.21</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.62</v>
+        <v>-4.22</v>
       </c>
       <c r="D16" s="6">
-        <v>-8.75</v>
+        <v>-3.96</v>
       </c>
       <c r="E16" s="7">
-        <v>-3.13</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.41</v>
+        <v>-3.72</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.76</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.65</v>
+        <v>0.52</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.24</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-11.57</v>
+        <v>0.13</v>
       </c>
       <c r="D18" s="6">
-        <v>-12.09</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.52</v>
+        <v>-3.66</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-3.79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>4.46</v>
+        <v>-7.11</v>
       </c>
       <c r="D19" s="6">
-        <v>3.3</v>
+        <v>-5.99</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.16</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-6.08</v>
+        <v>-8.75</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="E20" s="8">
-        <v>5.69</v>
+        <v>-6.31</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-9.869999999999999</v>
+        <v>-3.76</v>
       </c>
       <c r="D21" s="6">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.26</v>
+        <v>2.96</v>
+      </c>
+      <c r="E21" s="7">
+        <v>6.72</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-9.699999999999999</v>
+        <v>-12.09</v>
       </c>
       <c r="D22" s="6">
-        <v>-10.82</v>
+        <v>-10.64</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.12</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.33</v>
+        <v>3.3</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.86</v>
+        <v>6</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.53</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.03</v>
+        <v>-0.39</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.67</v>
+        <v>-2.7</v>
       </c>
       <c r="E24" s="8">
-        <v>0.36</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-0.82</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="D25" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.32</v>
+        <v>-5.99</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.62</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-2.97</v>
+        <v>-10.82</v>
       </c>
       <c r="D26" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="E26" s="8">
-        <v>6.14</v>
+        <v>-10.14</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.68</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-1.56</v>
+        <v>-1.86</v>
       </c>
       <c r="D27" s="6">
-        <v>-0.86</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.7</v>
+        <v>-1.61</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.21</v>
+        <v>-3.67</v>
       </c>
       <c r="D28" s="6">
-        <v>0.53</v>
+        <v>-7.77</v>
       </c>
       <c r="E28" s="8">
-        <v>0.74</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D29" s="6">
-        <v>4.9</v>
+        <v>-0.12</v>
       </c>
       <c r="E29" s="8">
-        <v>3.7</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.57</v>
+        <v>3.17</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.35</v>
+        <v>2.16</v>
       </c>
       <c r="E30" s="8">
-        <v>2.22</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.28</v>
+        <v>-0.86</v>
       </c>
       <c r="D31" s="6">
-        <v>-2.22</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.06</v>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.3</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-2.36</v>
+        <v>0.53</v>
       </c>
       <c r="D32" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.95</v>
+        <v>-1.64</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="D33" s="6">
-        <v>0.5</v>
+        <v>10.79</v>
       </c>
       <c r="E33" s="7">
-        <v>-3.4</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.34</v>
+        <v>-0.35</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.59</v>
+        <v>-0.42</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>13.11</v>
+        <v>-2.22</v>
       </c>
       <c r="D35" s="6">
-        <v>12.91</v>
+        <v>-1.89</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.2</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>12.8</v>
+        <v>-3.31</v>
       </c>
       <c r="D36" s="6">
-        <v>17.46</v>
-      </c>
-      <c r="E36" s="8">
-        <v>4.66</v>
+        <v>-2.07</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.24</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-5.54</v>
+        <v>0.5</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.82</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.72</v>
+        <v>8.06</v>
+      </c>
+      <c r="E37" s="7">
+        <v>7.56</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.85</v>
+        <v>-3.93</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.89</v>
+        <v>-1.38</v>
       </c>
       <c r="E38" s="7">
-        <v>-2.04</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-1.09</v>
+        <v>12.91</v>
       </c>
       <c r="D39" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.88</v>
+        <v>2.81</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-10.1</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>-5.25</v>
+        <v>17.46</v>
       </c>
       <c r="D40" s="6">
-        <v>-2.46</v>
+        <v>9.44</v>
       </c>
       <c r="E40" s="8">
-        <v>2.79</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>-34.98</v>
+        <v>-3.82</v>
       </c>
       <c r="D41" s="6">
-        <v>-33.69</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.29</v>
+        <v>-1.23</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.59</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>-35.39</v>
+        <v>-3.89</v>
       </c>
       <c r="D42" s="6">
-        <v>-29.85</v>
-      </c>
-      <c r="E42" s="8">
-        <v>5.54</v>
+        <v>-2.52</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.37</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.11</v>
+        <v>-2.97</v>
       </c>
       <c r="D43" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.12</v>
+        <v>-0.8</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.17</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-15.67</v>
+        <v>-2.46</v>
       </c>
       <c r="D44" s="6">
-        <v>-13.67</v>
-      </c>
-      <c r="E44" s="8">
-        <v>2</v>
+        <v>-1.51</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-40.93</v>
+        <v>-33.69</v>
       </c>
       <c r="D45" s="6">
-        <v>-38.48</v>
-      </c>
-      <c r="E45" s="8">
-        <v>2.45</v>
+        <v>-32.37</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.32</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-39.45</v>
+        <v>-29.85</v>
       </c>
       <c r="D46" s="6">
-        <v>-32.34</v>
-      </c>
-      <c r="E46" s="8">
-        <v>7.11</v>
+        <v>-29.56</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-13.5</v>
+        <v>0.01</v>
       </c>
       <c r="D47" s="6">
-        <v>-12.43</v>
+        <v>-0.99</v>
       </c>
       <c r="E47" s="8">
-        <v>1.07</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>4.31</v>
+        <v>-13.67</v>
       </c>
       <c r="D48" s="6">
-        <v>2.54</v>
+        <v>-13.58</v>
       </c>
       <c r="E48" s="7">
-        <v>-1.77</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-25.27</v>
+        <v>-38.48</v>
       </c>
       <c r="D49" s="6">
-        <v>-25.98</v>
+        <v>-36.11</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.71</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>28.74</v>
+        <v>-32.34</v>
       </c>
       <c r="D50" s="6">
-        <v>28.72</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.02</v>
+        <v>-32.43</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-38.83</v>
+        <v>-12.43</v>
       </c>
       <c r="D51" s="6">
-        <v>-37.74</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.09</v>
+        <v>-10.49</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1.94</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-40.97</v>
+        <v>2.54</v>
       </c>
       <c r="D52" s="6">
-        <v>-37.73</v>
-      </c>
-      <c r="E52" s="8">
-        <v>3.24</v>
+        <v>3.88</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.34</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-42.52</v>
+        <v>-25.98</v>
       </c>
       <c r="D53" s="6">
-        <v>-43.73</v>
+        <v>-22.35</v>
       </c>
       <c r="E53" s="7">
-        <v>-1.21</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-24.13</v>
+        <v>28.72</v>
       </c>
       <c r="D54" s="6">
-        <v>-25.43</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.3</v>
+        <v>25.84</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-4.87</v>
+        <v>-37.74</v>
       </c>
       <c r="D55" s="6">
-        <v>-3.66</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.21</v>
+        <v>-35.19</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.55</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-4.16</v>
+        <v>-37.73</v>
       </c>
       <c r="D56" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.25</v>
+        <v>-39.75</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>-13.54</v>
+        <v>-43.73</v>
       </c>
       <c r="D57" s="6">
-        <v>-13.24</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.3</v>
+        <v>-41.27</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2.46</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-18.21</v>
+        <v>-25.43</v>
       </c>
       <c r="D58" s="6">
-        <v>-10.84</v>
-      </c>
-      <c r="E58" s="8">
-        <v>7.37</v>
+        <v>-23.63</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1.8</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-10.75</v>
+        <v>-3.66</v>
       </c>
       <c r="D59" s="6">
-        <v>-9.41</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.34</v>
+        <v>-1.25</v>
+      </c>
+      <c r="E59" s="7">
+        <v>2.41</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-14.11</v>
+        <v>-5.41</v>
       </c>
       <c r="D60" s="6">
-        <v>-12.73</v>
-      </c>
-      <c r="E60" s="8">
-        <v>1.38</v>
+        <v>-4.69</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.72</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-15.18</v>
+        <v>-13.24</v>
       </c>
       <c r="D61" s="6">
-        <v>-14.82</v>
+        <v>-13.33</v>
       </c>
       <c r="E61" s="8">
-        <v>0.36</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-13.62</v>
+        <v>-10.84</v>
       </c>
       <c r="D62" s="6">
-        <v>-9.75</v>
-      </c>
-      <c r="E62" s="8">
-        <v>3.87</v>
+        <v>-10.31</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-10.27</v>
+        <v>-9.41</v>
       </c>
       <c r="D63" s="6">
-        <v>-9.039999999999999</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="E63" s="8">
-        <v>1.23</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-9.1</v>
+        <v>-12.73</v>
       </c>
       <c r="D64" s="6">
-        <v>-7.95</v>
-      </c>
-      <c r="E64" s="8">
-        <v>1.15</v>
+        <v>-12.54</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0.19</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>4.2</v>
+        <v>-14.82</v>
       </c>
       <c r="D65" s="6">
-        <v>-2.59</v>
+        <v>-7.32</v>
       </c>
       <c r="E65" s="7">
-        <v>-6.79</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-3.8</v>
+        <v>-9.75</v>
       </c>
       <c r="D66" s="6">
-        <v>-4.38</v>
+        <v>-7.03</v>
       </c>
       <c r="E66" s="7">
-        <v>-0.58</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>0.53</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="D67" s="6">
-        <v>0.44</v>
+        <v>-8.66</v>
       </c>
       <c r="E67" s="7">
-        <v>-0.09</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-7.68</v>
+        <v>-7.95</v>
       </c>
       <c r="D68" s="6">
-        <v>-5.29</v>
-      </c>
-      <c r="E68" s="8">
-        <v>2.39</v>
+        <v>-7.05</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-20.32</v>
+        <v>-2.59</v>
       </c>
       <c r="D69" s="6">
-        <v>-19.7</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.62</v>
+        <v>3.12</v>
+      </c>
+      <c r="E69" s="7">
+        <v>5.71</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-19.66</v>
+        <v>-4.38</v>
       </c>
       <c r="D70" s="6">
-        <v>-24.42</v>
+        <v>-1.9</v>
       </c>
       <c r="E70" s="7">
-        <v>-4.76</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-4.87</v>
+        <v>0.44</v>
       </c>
       <c r="D71" s="6">
-        <v>-5.42</v>
+        <v>4.14</v>
       </c>
       <c r="E71" s="7">
-        <v>-0.55</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-21.1</v>
+        <v>-5.29</v>
       </c>
       <c r="D72" s="6">
-        <v>-21.17</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-14.9</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-9.609999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>-34.37</v>
+        <v>-19.7</v>
       </c>
       <c r="D73" s="6">
-        <v>-33.21</v>
-      </c>
-      <c r="E73" s="8">
-        <v>1.16</v>
+        <v>-16.87</v>
+      </c>
+      <c r="E73" s="7">
+        <v>2.83</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>-35.05</v>
+        <v>-24.42</v>
       </c>
       <c r="D74" s="6">
-        <v>-29.77</v>
-      </c>
-      <c r="E74" s="8">
-        <v>5.28</v>
+        <v>-23.39</v>
+      </c>
+      <c r="E74" s="7">
+        <v>1.03</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-19.64</v>
+        <v>-5.42</v>
       </c>
       <c r="D75" s="6">
-        <v>-19.35</v>
-      </c>
-      <c r="E75" s="8">
-        <v>0.29</v>
+        <v>-3.74</v>
+      </c>
+      <c r="E75" s="7">
+        <v>1.68</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-24.23</v>
+        <v>-21.17</v>
       </c>
       <c r="D76" s="6">
-        <v>-23.93</v>
+        <v>-21.19</v>
       </c>
       <c r="E76" s="8">
-        <v>0.3</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-45.56</v>
+        <v>-33.21</v>
       </c>
       <c r="D77" s="6">
-        <v>-43.36</v>
+        <v>-33.23</v>
       </c>
       <c r="E77" s="8">
-        <v>2.2</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-41.8</v>
+        <v>-29.77</v>
       </c>
       <c r="D78" s="6">
-        <v>-39.83</v>
+        <v>-30.56</v>
       </c>
       <c r="E78" s="8">
-        <v>1.97</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-25.91</v>
+        <v>-19.35</v>
       </c>
       <c r="D79" s="6">
-        <v>-25.57</v>
-      </c>
-      <c r="E79" s="8">
-        <v>0.34</v>
+        <v>-18.88</v>
+      </c>
+      <c r="E79" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-19.78</v>
+        <v>-23.93</v>
       </c>
       <c r="D80" s="6">
-        <v>-20.5</v>
+        <v>-23.83</v>
       </c>
       <c r="E80" s="7">
-        <v>-0.72</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-33.08</v>
+        <v>-43.36</v>
       </c>
       <c r="D81" s="6">
-        <v>-34.04</v>
+        <v>-40.4</v>
       </c>
       <c r="E81" s="7">
-        <v>-0.96</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-14.69</v>
+        <v>-39.83</v>
       </c>
       <c r="D82" s="6">
-        <v>-14.88</v>
+        <v>-39.64</v>
       </c>
       <c r="E82" s="7">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-39.3</v>
+        <v>-25.57</v>
       </c>
       <c r="D83" s="6">
-        <v>-39.4</v>
+        <v>-25.29</v>
       </c>
       <c r="E83" s="7">
-        <v>-0.1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-40.72</v>
+        <v>-20.5</v>
       </c>
       <c r="D84" s="6">
-        <v>-36.08</v>
-      </c>
-      <c r="E84" s="8">
-        <v>4.64</v>
+        <v>-19.23</v>
+      </c>
+      <c r="E84" s="7">
+        <v>1.27</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-43.95</v>
+        <v>-34.04</v>
       </c>
       <c r="D85" s="6">
-        <v>-42.77</v>
-      </c>
-      <c r="E85" s="8">
-        <v>1.18</v>
+        <v>-29.57</v>
+      </c>
+      <c r="E85" s="7">
+        <v>4.47</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-33.58</v>
+        <v>-14.88</v>
       </c>
       <c r="D86" s="6">
-        <v>-34.46</v>
+        <v>-13.2</v>
       </c>
       <c r="E86" s="7">
-        <v>-0.88</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>715.65</v>
+        <v>-39.4</v>
       </c>
       <c r="D87" s="6">
-        <v>711.5</v>
+        <v>-37.85</v>
       </c>
       <c r="E87" s="7">
-        <v>-4.15</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>853.35</v>
+        <v>-36.08</v>
       </c>
       <c r="D88" s="6">
-        <v>852.6</v>
-      </c>
-      <c r="E88" s="7">
-        <v>-0.75</v>
+        <v>-39.16</v>
+      </c>
+      <c r="E88" s="8">
+        <v>-3.08</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>198.06</v>
+        <v>-42.77</v>
       </c>
       <c r="D89" s="6">
-        <v>200.11</v>
-      </c>
-      <c r="E89" s="8">
-        <v>2.05</v>
+        <v>-41.49</v>
+      </c>
+      <c r="E89" s="7">
+        <v>1.28</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>589.75</v>
+        <v>-34.46</v>
       </c>
       <c r="D90" s="6">
-        <v>636.95</v>
-      </c>
-      <c r="E90" s="8">
-        <v>47.2</v>
+        <v>-33.12</v>
+      </c>
+      <c r="E90" s="7">
+        <v>1.34</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>1656.7</v>
+        <v>711.5</v>
       </c>
       <c r="D91" s="6">
-        <v>1662.7</v>
-      </c>
-      <c r="E91" s="8">
-        <v>6</v>
+        <v>724.15</v>
+      </c>
+      <c r="E91" s="7">
+        <v>12.65</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>955</v>
+        <v>852.6</v>
       </c>
       <c r="D92" s="6">
-        <v>958.8</v>
+        <v>852.3</v>
       </c>
       <c r="E92" s="8">
-        <v>3.8</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>3130</v>
+        <v>200.11</v>
       </c>
       <c r="D93" s="6">
-        <v>3257</v>
+        <v>200.05</v>
       </c>
       <c r="E93" s="8">
-        <v>127</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>599.25</v>
+        <v>636.95</v>
       </c>
       <c r="D94" s="6">
-        <v>619.6</v>
+        <v>629.85</v>
       </c>
       <c r="E94" s="8">
-        <v>20.35</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>342.15</v>
+        <v>1662.7</v>
       </c>
       <c r="D95" s="6">
-        <v>343.7</v>
-      </c>
-      <c r="E95" s="8">
-        <v>1.55</v>
+        <v>1672.4</v>
+      </c>
+      <c r="E95" s="7">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>173.8</v>
+        <v>958.8</v>
       </c>
       <c r="D96" s="6">
-        <v>172.24</v>
+        <v>960</v>
       </c>
       <c r="E96" s="7">
-        <v>-1.56</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>2156</v>
+        <v>3257</v>
       </c>
       <c r="D97" s="6">
-        <v>2125</v>
+        <v>3426.7</v>
       </c>
       <c r="E97" s="7">
-        <v>-31</v>
+        <v>169.7</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>4410</v>
+        <v>619.6</v>
       </c>
       <c r="D98" s="6">
-        <v>4400</v>
+        <v>621.55</v>
       </c>
       <c r="E98" s="7">
-        <v>-10</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>2918.2</v>
+        <v>343.7</v>
       </c>
       <c r="D99" s="6">
-        <v>2913</v>
+        <v>345</v>
       </c>
       <c r="E99" s="7">
-        <v>-5.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>216.94</v>
+        <v>172.24</v>
       </c>
       <c r="D100" s="6">
-        <v>227.89</v>
-      </c>
-      <c r="E100" s="8">
-        <v>10.95</v>
+        <v>175</v>
+      </c>
+      <c r="E100" s="7">
+        <v>2.76</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>32.89</v>
+        <v>2125</v>
       </c>
       <c r="D101" s="6">
-        <v>33.02</v>
-      </c>
-      <c r="E101" s="8">
-        <v>0.13</v>
+        <v>2269.3</v>
+      </c>
+      <c r="E101" s="7">
+        <v>144.3</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>1033.7</v>
+        <v>4400</v>
       </c>
       <c r="D102" s="6">
-        <v>1020</v>
+        <v>4487</v>
       </c>
       <c r="E102" s="7">
-        <v>-13.7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C103" s="6">
-        <v>38</v>
+        <v>2913</v>
       </c>
       <c r="D103" s="6">
-        <v>26</v>
+        <v>2987.8</v>
       </c>
       <c r="E103" s="7">
-        <v>-12</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C104" s="6">
-        <v>19</v>
+        <v>227.89</v>
       </c>
       <c r="D104" s="6">
-        <v>44</v>
+        <v>214.83</v>
       </c>
       <c r="E104" s="8">
-        <v>25</v>
+        <v>-13.06</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C105" s="6">
-        <v>56</v>
+        <v>33.02</v>
       </c>
       <c r="D105" s="6">
-        <v>62</v>
-      </c>
-      <c r="E105" s="8">
-        <v>6</v>
+        <v>33.76</v>
+      </c>
+      <c r="E105" s="7">
+        <v>0.74</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C106" s="6">
-        <v>13</v>
+        <v>1020</v>
       </c>
       <c r="D106" s="6">
-        <v>19</v>
-      </c>
-      <c r="E106" s="8">
-        <v>6</v>
+        <v>1041</v>
+      </c>
+      <c r="E106" s="7">
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D107" s="6">
-        <v>38</v>
-      </c>
-      <c r="E107" s="8">
-        <v>12</v>
+        <v>81</v>
+      </c>
+      <c r="E107" s="7">
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D108" s="6">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E108" s="8">
-        <v>6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="6">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D109" s="6">
-        <v>56</v>
-      </c>
-      <c r="E109" s="7">
+        <v>50</v>
+      </c>
+      <c r="E109" s="8">
         <v>-12</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C110" s="6">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D110" s="6">
+        <v>32</v>
+      </c>
+      <c r="E110" s="7">
         <v>13</v>
-      </c>
-      <c r="E110" s="7">
-        <v>-31</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="6">
-        <v>46.13</v>
+        <v>68</v>
       </c>
       <c r="D111" s="6">
-        <v>44.49</v>
-      </c>
-      <c r="E111" s="7">
-        <v>-1.64</v>
+        <v>62</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C112" s="6">
-        <v>36.97</v>
+        <v>56</v>
       </c>
       <c r="D112" s="6">
-        <v>36.88</v>
+        <v>68</v>
       </c>
       <c r="E112" s="7">
-        <v>-0.09</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C113" s="6">
-        <v>38.28</v>
+        <v>50</v>
       </c>
       <c r="D113" s="6">
-        <v>44.13</v>
-      </c>
-      <c r="E113" s="8">
-        <v>5.85</v>
+        <v>56</v>
+      </c>
+      <c r="E113" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C114" s="6">
-        <v>36.19</v>
+        <v>32</v>
       </c>
       <c r="D114" s="6">
-        <v>49.92</v>
+        <v>13</v>
       </c>
       <c r="E114" s="8">
-        <v>13.73</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C115" s="6">
-        <v>40.58</v>
+        <v>13</v>
       </c>
       <c r="D115" s="6">
-        <v>42.09</v>
-      </c>
-      <c r="E115" s="8">
-        <v>1.51</v>
+        <v>19</v>
+      </c>
+      <c r="E115" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>37.53</v>
+        <v>44.49</v>
       </c>
       <c r="D116" s="6">
-        <v>39.21</v>
-      </c>
-      <c r="E116" s="8">
-        <v>1.68</v>
+        <v>50.3</v>
+      </c>
+      <c r="E116" s="7">
+        <v>5.81</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>37.74</v>
+        <v>36.88</v>
       </c>
       <c r="D117" s="6">
-        <v>48.88</v>
+        <v>36.84</v>
       </c>
       <c r="E117" s="8">
-        <v>11.14</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>35.01</v>
+        <v>44.13</v>
       </c>
       <c r="D118" s="6">
-        <v>43.29</v>
+        <v>44</v>
       </c>
       <c r="E118" s="8">
-        <v>8.279999999999999</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>34.99</v>
+        <v>49.92</v>
       </c>
       <c r="D119" s="6">
-        <v>36.75</v>
+        <v>48.23</v>
       </c>
       <c r="E119" s="8">
-        <v>1.76</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>35.47</v>
+        <v>42.09</v>
       </c>
       <c r="D120" s="6">
-        <v>33.72</v>
+        <v>44.55</v>
       </c>
       <c r="E120" s="7">
-        <v>-1.75</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>50.61</v>
+        <v>39.21</v>
       </c>
       <c r="D121" s="6">
-        <v>46.71</v>
+        <v>39.76</v>
       </c>
       <c r="E121" s="7">
-        <v>-3.9</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>29.33</v>
+        <v>48.88</v>
       </c>
       <c r="D122" s="6">
-        <v>28.95</v>
+        <v>59.36</v>
       </c>
       <c r="E122" s="7">
-        <v>-0.38</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>61.06</v>
+        <v>43.29</v>
       </c>
       <c r="D123" s="6">
-        <v>60.5</v>
+        <v>44.03</v>
       </c>
       <c r="E123" s="7">
-        <v>-0.5600000000000001</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>54.23</v>
+        <v>36.75</v>
       </c>
       <c r="D124" s="6">
-        <v>61.04</v>
-      </c>
-      <c r="E124" s="8">
-        <v>6.81</v>
+        <v>38.26</v>
+      </c>
+      <c r="E124" s="7">
+        <v>1.51</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="6">
-        <v>32.57</v>
+        <v>33.72</v>
       </c>
       <c r="D125" s="6">
-        <v>33.75</v>
-      </c>
-      <c r="E125" s="8">
-        <v>1.18</v>
+        <v>39.43</v>
+      </c>
+      <c r="E125" s="7">
+        <v>5.71</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C126" s="6">
-        <v>30.65</v>
+        <v>46.71</v>
       </c>
       <c r="D126" s="6">
-        <v>28.82</v>
+        <v>61.55</v>
       </c>
       <c r="E126" s="7">
-        <v>-1.83</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="6">
-        <v>-68.11</v>
+        <v>28.95</v>
       </c>
       <c r="D127" s="6">
-        <v>-34.09</v>
-      </c>
-      <c r="E127" s="8">
-        <v>34.02</v>
+        <v>36.49</v>
+      </c>
+      <c r="E127" s="7">
+        <v>7.54</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C128" s="6">
-        <v>-39.35</v>
+        <v>60.5</v>
       </c>
       <c r="D128" s="6">
-        <v>-65.17</v>
+        <v>65.39</v>
       </c>
       <c r="E128" s="7">
-        <v>-25.82</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C129" s="6">
-        <v>-30.33</v>
+        <v>61.04</v>
       </c>
       <c r="D129" s="6">
-        <v>-45.51</v>
-      </c>
-      <c r="E129" s="7">
-        <v>-15.18</v>
+        <v>51.24</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C130" s="6">
-        <v>-73.45999999999999</v>
+        <v>33.75</v>
       </c>
       <c r="D130" s="6">
-        <v>166.49</v>
-      </c>
-      <c r="E130" s="8">
-        <v>239.95</v>
+        <v>40.13</v>
+      </c>
+      <c r="E130" s="7">
+        <v>6.38</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C131" s="6">
-        <v>27.2</v>
+        <v>28.82</v>
       </c>
       <c r="D131" s="6">
-        <v>-9.029999999999999</v>
+        <v>35.21</v>
       </c>
       <c r="E131" s="7">
-        <v>-36.23</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>-23.48</v>
+        <v>-34.09</v>
       </c>
       <c r="D132" s="6">
-        <v>-42.62</v>
-      </c>
-      <c r="E132" s="7">
-        <v>-19.14</v>
+        <v>-47.54</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-13.45</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>146.94</v>
+        <v>-65.17</v>
       </c>
       <c r="D133" s="6">
-        <v>183.92</v>
+        <v>-69.2</v>
       </c>
       <c r="E133" s="8">
-        <v>36.98</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-87.64</v>
+        <v>-45.51</v>
       </c>
       <c r="D134" s="6">
-        <v>-69.78</v>
-      </c>
-      <c r="E134" s="8">
-        <v>17.86</v>
+        <v>-41.34</v>
+      </c>
+      <c r="E134" s="7">
+        <v>4.17</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>10.83</v>
+        <v>166.49</v>
       </c>
       <c r="D135" s="6">
-        <v>-15.22</v>
-      </c>
-      <c r="E135" s="7">
-        <v>-26.05</v>
+        <v>-48.99</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-215.48</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-50.38</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="D136" s="6">
-        <v>5.06</v>
+        <v>-60.23</v>
       </c>
       <c r="E136" s="8">
-        <v>55.44</v>
+        <v>-51.2</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>253.23</v>
+        <v>-42.62</v>
       </c>
       <c r="D137" s="6">
-        <v>-6.02</v>
+        <v>54.03</v>
       </c>
       <c r="E137" s="7">
-        <v>-259.25</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>-27.22</v>
+        <v>183.92</v>
       </c>
       <c r="D138" s="6">
-        <v>-11.72</v>
-      </c>
-      <c r="E138" s="8">
-        <v>15.5</v>
+        <v>239.24</v>
+      </c>
+      <c r="E138" s="7">
+        <v>55.32</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>-30.32</v>
+        <v>-69.78</v>
       </c>
       <c r="D139" s="6">
-        <v>-41.64</v>
-      </c>
-      <c r="E139" s="7">
-        <v>-11.32</v>
+        <v>-91.48</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-21.7</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="6">
-        <v>297.67</v>
+        <v>-15.22</v>
       </c>
       <c r="D140" s="6">
-        <v>354.72</v>
+        <v>-39.38</v>
       </c>
       <c r="E140" s="8">
-        <v>57.05</v>
+        <v>-24.16</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="6">
-        <v>-75.8</v>
+        <v>5.06</v>
       </c>
       <c r="D141" s="6">
-        <v>-70.31999999999999</v>
+        <v>-17.17</v>
       </c>
       <c r="E141" s="8">
-        <v>5.48</v>
+        <v>-22.23</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C142" s="6">
-        <v>-68.88</v>
+        <v>-6.02</v>
       </c>
       <c r="D142" s="6">
+        <v>192.78</v>
+      </c>
+      <c r="E142" s="7">
+        <v>198.8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6">
+        <v>-11.72</v>
+      </c>
+      <c r="D143" s="6">
+        <v>-33.78</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-22.06</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="6">
+        <v>-41.64</v>
+      </c>
+      <c r="D144" s="6">
+        <v>-18.2</v>
+      </c>
+      <c r="E144" s="7">
+        <v>23.44</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="6">
+        <v>354.72</v>
+      </c>
+      <c r="D145" s="6">
+        <v>394.92</v>
+      </c>
+      <c r="E145" s="7">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="6">
+        <v>-70.31999999999999</v>
+      </c>
+      <c r="D146" s="6">
+        <v>-73.58</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147" s="6">
         <v>-61.52</v>
       </c>
-      <c r="E142" s="8">
-        <v>7.36</v>
+      <c r="D147" s="6">
+        <v>-35.2</v>
+      </c>
+      <c r="E147" s="7">
+        <v>26.32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5312,28 +5448,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5347,16 +5483,16 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>42.4</v>
+        <v>45.9</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.4</v>
+        <v>-3.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-9.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -5473,10 +5609,10 @@
         <v>49</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>46</v>
@@ -5496,34 +5632,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3536</v>
+        <v>0.3202</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2825</v>
+        <v>0.2673</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2089</v>
+        <v>0.2065</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1254</v>
+        <v>0.1237</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1233</v>
+        <v>0.09609999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0849</v>
+        <v>0.0843</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0697</v>
+        <v>0.0548</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0483</v>
+        <v>0.0404</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0413</v>
+        <v>0.0336</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0122</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5531,7 +5667,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
@@ -5540,7 +5676,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>43</v>
@@ -5548,22 +5684,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.04269999999999999</v>
+        <v>-0.0406</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.0675</v>
+        <v>-0.066</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.07000000000000001</v>
+        <v>-0.0759</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0725</v>
+        <v>-0.0774</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.0781</v>
+        <v>-0.09380000000000001</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.108</v>
+        <v>-0.1003</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="87">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,12 +184,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -214,58 +214,34 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>44.5 → 50.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>44.5</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>48.9 → 59.4</t>
-  </si>
-  <si>
-    <t>48.9</t>
-  </si>
-  <si>
-    <t>59.4</t>
-  </si>
-  <si>
-    <t>46.7 → 61.5</t>
-  </si>
-  <si>
-    <t>46.7</t>
-  </si>
-  <si>
-    <t>61.5</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.9 → 36.5</t>
-  </si>
-  <si>
-    <t>28.9</t>
-  </si>
-  <si>
-    <t>36.5</t>
-  </si>
-  <si>
-    <t>28.8 → 35.2</t>
-  </si>
-  <si>
-    <t>28.8</t>
-  </si>
-  <si>
-    <t>35.2</t>
+    <t>44.0 → 51.1</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>39.8 → 50.9</t>
+  </si>
+  <si>
+    <t>39.8</t>
+  </si>
+  <si>
+    <t>50.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -477,8 +453,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -990,10 +966,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>724.15</v>
+        <v>725.4</v>
       </c>
       <c r="D2">
-        <v>1.78</v>
+        <v>0.17</v>
       </c>
       <c r="E2">
         <v>752.3</v>
@@ -1002,88 +978,88 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-3.74</v>
+        <v>-3.58</v>
       </c>
       <c r="H2">
-        <v>26.83</v>
+        <v>27.05</v>
       </c>
       <c r="I2">
-        <v>-1.61</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J2">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="K2">
-        <v>-1.25</v>
+        <v>-2.4</v>
       </c>
       <c r="L2">
-        <v>-0.8</v>
+        <v>-0.92</v>
       </c>
       <c r="M2">
-        <v>26.73</v>
+        <v>26.92</v>
       </c>
       <c r="N2">
         <v>93</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>718.85</v>
+        <v>717.67</v>
       </c>
       <c r="Q2">
-        <v>724.78</v>
+        <v>725.3</v>
       </c>
       <c r="R2">
-        <v>725.72</v>
+        <v>725.1900000000001</v>
       </c>
       <c r="S2">
-        <v>687.92</v>
+        <v>687.85</v>
       </c>
       <c r="T2">
-        <v>5.27</v>
+        <v>5.46</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
       </c>
       <c r="V2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W2" t="s">
         <v>54</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.3</v>
+        <v>50.84</v>
       </c>
       <c r="Z2">
-        <v>-1.64</v>
+        <v>-1.23</v>
       </c>
       <c r="AA2">
-        <v>-0.75</v>
+        <v>-0.85</v>
       </c>
       <c r="AB2">
-        <v>-0.88</v>
+        <v>-0.38</v>
       </c>
       <c r="AC2">
-        <v>25.08</v>
+        <v>41.44</v>
       </c>
       <c r="AD2">
-        <v>21.31</v>
+        <v>26.23</v>
       </c>
       <c r="AE2">
-        <v>15.96</v>
+        <v>15.76</v>
       </c>
       <c r="AF2">
-        <v>-47.54</v>
+        <v>-50.18</v>
       </c>
       <c r="AG2">
-        <v>746.16</v>
+        <v>746.1799999999999</v>
       </c>
       <c r="AH2">
-        <v>703.4</v>
+        <v>704.42</v>
       </c>
       <c r="AI2">
         <v>700.95</v>
@@ -1092,7 +1068,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>15.25</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1103,10 +1079,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>852.3</v>
+        <v>844.4</v>
       </c>
       <c r="D3">
-        <v>-0.04</v>
+        <v>-0.93</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1115,97 +1091,97 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-21.19</v>
+        <v>-21.92</v>
       </c>
       <c r="H3">
-        <v>68.65000000000001</v>
+        <v>67.09</v>
       </c>
       <c r="I3">
-        <v>-7.77</v>
+        <v>-7.8</v>
       </c>
       <c r="J3">
-        <v>-9.09</v>
+        <v>-10.86</v>
       </c>
       <c r="K3">
-        <v>-4.69</v>
+        <v>-2.1</v>
       </c>
       <c r="L3">
-        <v>-1.51</v>
+        <v>-3.73</v>
       </c>
       <c r="M3">
-        <v>0.23</v>
+        <v>-0.63</v>
       </c>
       <c r="N3">
         <v>81</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P3">
-        <v>867.8099999999999</v>
+        <v>853.53</v>
       </c>
       <c r="Q3">
-        <v>930.9299999999999</v>
+        <v>926.9299999999999</v>
       </c>
       <c r="R3">
-        <v>948.91</v>
+        <v>945.78</v>
       </c>
       <c r="S3">
-        <v>770.72</v>
+        <v>771.23</v>
       </c>
       <c r="T3">
-        <v>10.58</v>
+        <v>9.49</v>
       </c>
       <c r="U3" t="s">
+        <v>55</v>
+      </c>
+      <c r="V3" t="s">
         <v>54</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>55</v>
-      </c>
-      <c r="W3" t="s">
-        <v>54</v>
       </c>
       <c r="X3">
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>36.84</v>
+        <v>35.74</v>
       </c>
       <c r="Z3">
-        <v>-24.95</v>
+        <v>-27.05</v>
       </c>
       <c r="AA3">
-        <v>-14.02</v>
+        <v>-16.63</v>
       </c>
       <c r="AB3">
-        <v>-10.92</v>
+        <v>-10.42</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>41.08</v>
+        <v>39.65</v>
       </c>
       <c r="AF3">
-        <v>-69.2</v>
+        <v>-73.23999999999999</v>
       </c>
       <c r="AG3">
-        <v>1042.17</v>
+        <v>1044.73</v>
       </c>
       <c r="AH3">
-        <v>819.6900000000001</v>
+        <v>809.14</v>
       </c>
       <c r="AI3">
-        <v>968.6799999999999</v>
+        <v>968.46</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>35.9</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1216,100 +1192,100 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>200.05</v>
+        <v>202.77</v>
       </c>
       <c r="D4">
-        <v>-0.03</v>
+        <v>1.36</v>
       </c>
       <c r="E4">
-        <v>299.61</v>
+        <v>298.72</v>
       </c>
       <c r="F4">
         <v>195.76</v>
       </c>
       <c r="G4">
-        <v>-33.23</v>
+        <v>-32.12</v>
       </c>
       <c r="H4">
-        <v>2.19</v>
+        <v>3.58</v>
       </c>
       <c r="I4">
-        <v>-0.12</v>
+        <v>1.37</v>
       </c>
       <c r="J4">
-        <v>-1.48</v>
+        <v>0.39</v>
       </c>
       <c r="K4">
-        <v>-13.33</v>
+        <v>-14.91</v>
       </c>
       <c r="L4">
-        <v>-32.37</v>
+        <v>-32.32</v>
       </c>
       <c r="M4">
-        <v>-7.59</v>
+        <v>-7.28</v>
       </c>
       <c r="N4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>198.8</v>
+        <v>199.35</v>
       </c>
       <c r="Q4">
-        <v>200.46</v>
+        <v>200.55</v>
       </c>
       <c r="R4">
-        <v>206.64</v>
+        <v>206.34</v>
       </c>
       <c r="S4">
-        <v>237.83</v>
+        <v>237.51</v>
       </c>
       <c r="T4">
-        <v>-15.89</v>
+        <v>-14.63</v>
       </c>
       <c r="U4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44</v>
+        <v>51.11</v>
       </c>
       <c r="Z4">
-        <v>-2.41</v>
+        <v>-1.98</v>
       </c>
       <c r="AA4">
-        <v>-2.85</v>
+        <v>-2.68</v>
       </c>
       <c r="AB4">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="AC4">
-        <v>96.34999999999999</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="AD4">
-        <v>80.36</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="AE4">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="AF4">
-        <v>-41.34</v>
+        <v>-24.06</v>
       </c>
       <c r="AG4">
-        <v>204.59</v>
+        <v>204.81</v>
       </c>
       <c r="AH4">
-        <v>196.33</v>
+        <v>196.3</v>
       </c>
       <c r="AI4">
         <v>207.87</v>
@@ -1318,7 +1294,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>35.24</v>
+        <v>32.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1329,10 +1305,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>629.85</v>
+        <v>629.55</v>
       </c>
       <c r="D5">
-        <v>-1.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E5">
         <v>907</v>
@@ -1341,88 +1317,88 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-30.56</v>
+        <v>-30.59</v>
       </c>
       <c r="H5">
-        <v>9.65</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
-        <v>2.16</v>
+        <v>3.24</v>
       </c>
       <c r="J5">
-        <v>3.16</v>
+        <v>2.79</v>
       </c>
       <c r="K5">
-        <v>-10.31</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L5">
-        <v>-29.56</v>
+        <v>-29.45</v>
       </c>
       <c r="M5">
-        <v>-9.380000000000001</v>
+        <v>-9</v>
       </c>
       <c r="N5">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="O5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P5">
-        <v>611.86</v>
+        <v>615.8099999999999</v>
       </c>
       <c r="Q5">
-        <v>652.08</v>
+        <v>646.8099999999999</v>
       </c>
       <c r="R5">
-        <v>647.54</v>
+        <v>646.64</v>
       </c>
       <c r="S5">
-        <v>693.97</v>
+        <v>693.35</v>
       </c>
       <c r="T5">
-        <v>-9.24</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="U5" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" t="s">
         <v>55</v>
       </c>
-      <c r="V5" t="s">
-        <v>54</v>
-      </c>
       <c r="W5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>48.23</v>
+        <v>48.16</v>
       </c>
       <c r="Z5">
-        <v>-12.18</v>
+        <v>-10.83</v>
       </c>
       <c r="AA5">
-        <v>-10.58</v>
+        <v>-10.63</v>
       </c>
       <c r="AB5">
-        <v>-1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AC5">
-        <v>57.82</v>
+        <v>86.89</v>
       </c>
       <c r="AD5">
-        <v>29.6</v>
+        <v>58.25</v>
       </c>
       <c r="AE5">
-        <v>27.96</v>
+        <v>27.29</v>
       </c>
       <c r="AF5">
-        <v>-48.99</v>
+        <v>-68.75</v>
       </c>
       <c r="AG5">
-        <v>756.02</v>
+        <v>743.51</v>
       </c>
       <c r="AH5">
-        <v>548.14</v>
+        <v>550.11</v>
       </c>
       <c r="AI5">
         <v>676.63</v>
@@ -1431,7 +1407,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>15.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1442,10 +1418,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1672.4</v>
+        <v>1658.9</v>
       </c>
       <c r="D6">
-        <v>0.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1454,88 +1430,88 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-18.88</v>
+        <v>-19.54</v>
       </c>
       <c r="H6">
-        <v>24.07</v>
+        <v>23.07</v>
       </c>
       <c r="I6">
-        <v>-0.5600000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="J6">
-        <v>-5.21</v>
+        <v>-5.83</v>
       </c>
       <c r="K6">
-        <v>-9.529999999999999</v>
+        <v>-10.61</v>
       </c>
       <c r="L6">
-        <v>-0.99</v>
+        <v>-2.23</v>
       </c>
       <c r="M6">
-        <v>4.04</v>
+        <v>4.1</v>
       </c>
       <c r="N6">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O6">
+        <v>44</v>
+      </c>
+      <c r="P6">
+        <v>1665.62</v>
+      </c>
+      <c r="Q6">
+        <v>1691.45</v>
+      </c>
+      <c r="R6">
+        <v>1710.37</v>
+      </c>
+      <c r="S6">
+        <v>1700.51</v>
+      </c>
+      <c r="T6">
+        <v>-2.45</v>
+      </c>
+      <c r="U6" t="s">
         <v>55</v>
       </c>
-      <c r="P6">
-        <v>1665.76</v>
-      </c>
-      <c r="Q6">
-        <v>1695.92</v>
-      </c>
-      <c r="R6">
-        <v>1712.8</v>
-      </c>
-      <c r="S6">
-        <v>1701.08</v>
-      </c>
-      <c r="T6">
-        <v>-1.69</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>54</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>55</v>
-      </c>
-      <c r="W6" t="s">
-        <v>54</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>44.55</v>
+        <v>41.88</v>
       </c>
       <c r="Z6">
-        <v>-18.48</v>
+        <v>-18.47</v>
       </c>
       <c r="AA6">
-        <v>-17.88</v>
+        <v>-18</v>
       </c>
       <c r="AB6">
-        <v>-0.61</v>
+        <v>-0.48</v>
       </c>
       <c r="AC6">
-        <v>67.7</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="AD6">
-        <v>47.78</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AE6">
-        <v>48.45</v>
+        <v>48.46</v>
       </c>
       <c r="AF6">
-        <v>-60.23</v>
+        <v>-42.33</v>
       </c>
       <c r="AG6">
-        <v>1791.16</v>
+        <v>1784.73</v>
       </c>
       <c r="AH6">
-        <v>1600.68</v>
+        <v>1598.18</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1544,7 +1520,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>27.19</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1555,10 +1531,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>960</v>
+        <v>987.9</v>
       </c>
       <c r="D7">
-        <v>0.13</v>
+        <v>2.91</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1567,88 +1543,88 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-23.83</v>
+        <v>-21.62</v>
       </c>
       <c r="H7">
-        <v>1.11</v>
+        <v>4.04</v>
       </c>
       <c r="I7">
-        <v>-1.64</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>-3.96</v>
+        <v>-0.31</v>
       </c>
       <c r="K7">
-        <v>-12.54</v>
+        <v>-8.99</v>
       </c>
       <c r="L7">
-        <v>-13.58</v>
+        <v>-10.89</v>
       </c>
       <c r="M7">
-        <v>3.36</v>
+        <v>3.92</v>
       </c>
       <c r="N7">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>958.84</v>
+        <v>962.72</v>
       </c>
       <c r="Q7">
-        <v>975.13</v>
+        <v>975.22</v>
       </c>
       <c r="R7">
-        <v>1021.64</v>
+        <v>1019.2</v>
       </c>
       <c r="S7">
-        <v>1101.68</v>
+        <v>1100.78</v>
       </c>
       <c r="T7">
-        <v>-12.86</v>
+        <v>-10.25</v>
       </c>
       <c r="U7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>39.76</v>
+        <v>50.91</v>
       </c>
       <c r="Z7">
-        <v>-18.27</v>
+        <v>-15.14</v>
       </c>
       <c r="AA7">
-        <v>-19.88</v>
+        <v>-18.93</v>
       </c>
       <c r="AB7">
-        <v>1.6</v>
+        <v>3.79</v>
       </c>
       <c r="AC7">
-        <v>69.52</v>
+        <v>83.17</v>
       </c>
       <c r="AD7">
-        <v>64.31</v>
+        <v>70.89</v>
       </c>
       <c r="AE7">
-        <v>17.91</v>
+        <v>18.62</v>
       </c>
       <c r="AF7">
-        <v>54.03</v>
+        <v>138.52</v>
       </c>
       <c r="AG7">
-        <v>1013.97</v>
+        <v>1014.17</v>
       </c>
       <c r="AH7">
-        <v>936.29</v>
+        <v>936.26</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1657,7 +1633,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>42.84</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1668,10 +1644,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3426.7</v>
+        <v>3623.1</v>
       </c>
       <c r="D8">
-        <v>5.21</v>
+        <v>5.73</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1680,97 +1656,97 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-40.4</v>
+        <v>-36.99</v>
       </c>
       <c r="H8">
-        <v>14.38</v>
+        <v>20.93</v>
       </c>
       <c r="I8">
-        <v>10.79</v>
+        <v>17.54</v>
       </c>
       <c r="J8">
-        <v>0.52</v>
+        <v>7.1</v>
       </c>
       <c r="K8">
-        <v>-7.32</v>
+        <v>2.92</v>
       </c>
       <c r="L8">
-        <v>-36.11</v>
+        <v>-33.82</v>
       </c>
       <c r="M8">
-        <v>-10.03</v>
+        <v>-9.43</v>
       </c>
       <c r="N8">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="O8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="P8">
-        <v>3178.44</v>
+        <v>3286.56</v>
       </c>
       <c r="Q8">
-        <v>3211.29</v>
+        <v>3220.44</v>
       </c>
       <c r="R8">
-        <v>3474.67</v>
+        <v>3471.9</v>
       </c>
       <c r="S8">
-        <v>4159.94</v>
+        <v>4151.6</v>
       </c>
       <c r="T8">
-        <v>-17.63</v>
+        <v>-12.73</v>
       </c>
       <c r="U8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X8">
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>59.36</v>
+        <v>67.62</v>
       </c>
       <c r="Z8">
-        <v>-75.06</v>
+        <v>-35.87</v>
       </c>
       <c r="AA8">
-        <v>-109.54</v>
+        <v>-94.8</v>
       </c>
       <c r="AB8">
-        <v>34.48</v>
+        <v>58.93</v>
       </c>
       <c r="AC8">
         <v>100</v>
       </c>
       <c r="AD8">
-        <v>67.81</v>
+        <v>88.89</v>
       </c>
       <c r="AE8">
-        <v>102.93</v>
+        <v>115.81</v>
       </c>
       <c r="AF8">
-        <v>239.24</v>
+        <v>1052.77</v>
       </c>
       <c r="AG8">
-        <v>3458.6</v>
+        <v>3512.85</v>
       </c>
       <c r="AH8">
-        <v>2963.98</v>
+        <v>2928.04</v>
       </c>
       <c r="AI8">
-        <v>3028.27</v>
+        <v>3241.12</v>
       </c>
       <c r="AJ8" t="s">
         <v>56</v>
       </c>
       <c r="AK8">
-        <v>50.68</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1781,10 +1757,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>621.55</v>
+        <v>616.35</v>
       </c>
       <c r="D9">
-        <v>0.31</v>
+        <v>-0.84</v>
       </c>
       <c r="E9">
         <v>1029.69</v>
@@ -1793,88 +1769,88 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-39.64</v>
+        <v>-40.14</v>
       </c>
       <c r="H9">
-        <v>15.45</v>
+        <v>14.48</v>
       </c>
       <c r="I9">
-        <v>-0.42</v>
+        <v>0.17</v>
       </c>
       <c r="J9">
-        <v>-3.66</v>
+        <v>-5.31</v>
       </c>
       <c r="K9">
-        <v>-7.03</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L9">
-        <v>-32.43</v>
+        <v>-31.32</v>
       </c>
       <c r="M9">
-        <v>32.02</v>
+        <v>31.71</v>
       </c>
       <c r="N9">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P9">
-        <v>613</v>
+        <v>613.21</v>
       </c>
       <c r="Q9">
-        <v>649.24</v>
+        <v>644.14</v>
       </c>
       <c r="R9">
-        <v>651.54</v>
+        <v>650.34</v>
       </c>
       <c r="S9">
-        <v>657.61</v>
+        <v>657.15</v>
       </c>
       <c r="T9">
-        <v>-5.48</v>
+        <v>-6.21</v>
       </c>
       <c r="U9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.03</v>
+        <v>42.45</v>
       </c>
       <c r="Z9">
-        <v>-12.36</v>
+        <v>-12.15</v>
       </c>
       <c r="AA9">
-        <v>-9.19</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AB9">
-        <v>-3.17</v>
+        <v>-2.37</v>
       </c>
       <c r="AC9">
-        <v>30.92</v>
+        <v>49.42</v>
       </c>
       <c r="AD9">
-        <v>15.34</v>
+        <v>31.41</v>
       </c>
       <c r="AE9">
-        <v>20.93</v>
+        <v>20.28</v>
       </c>
       <c r="AF9">
-        <v>-91.48</v>
+        <v>-88.91</v>
       </c>
       <c r="AG9">
-        <v>724.98</v>
+        <v>713.77</v>
       </c>
       <c r="AH9">
-        <v>573.51</v>
+        <v>574.51</v>
       </c>
       <c r="AI9">
         <v>665.02</v>
@@ -1883,7 +1859,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>14</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1894,10 +1870,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D10">
-        <v>0.38</v>
+        <v>2.32</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1906,88 +1882,88 @@
         <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-25.29</v>
+        <v>-23.56</v>
       </c>
       <c r="H10">
-        <v>2.79</v>
+        <v>5.17</v>
       </c>
       <c r="I10">
-        <v>-1.89</v>
+        <v>2.27</v>
       </c>
       <c r="J10">
-        <v>-5.99</v>
+        <v>-3.19</v>
       </c>
       <c r="K10">
-        <v>-8.66</v>
+        <v>-7.32</v>
       </c>
       <c r="L10">
-        <v>-10.49</v>
+        <v>-9.07</v>
       </c>
       <c r="M10">
-        <v>9.609999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="N10">
         <v>62</v>
       </c>
       <c r="O10">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P10">
-        <v>342.33</v>
+        <v>343.9</v>
       </c>
       <c r="Q10">
-        <v>357.31</v>
+        <v>356.81</v>
       </c>
       <c r="R10">
-        <v>365.75</v>
+        <v>365.17</v>
       </c>
       <c r="S10">
-        <v>385.39</v>
+        <v>385.26</v>
       </c>
       <c r="T10">
-        <v>-10.48</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="U10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X10">
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>38.26</v>
+        <v>46.7</v>
       </c>
       <c r="Z10">
-        <v>-6.79</v>
+        <v>-6.03</v>
       </c>
       <c r="AA10">
-        <v>-5.28</v>
+        <v>-5.43</v>
       </c>
       <c r="AB10">
-        <v>-1.51</v>
+        <v>-0.6</v>
       </c>
       <c r="AC10">
-        <v>40.59</v>
+        <v>58.57</v>
       </c>
       <c r="AD10">
-        <v>25.52</v>
+        <v>41.32</v>
       </c>
       <c r="AE10">
-        <v>7.6</v>
+        <v>7.77</v>
       </c>
       <c r="AF10">
-        <v>-39.38</v>
+        <v>27.62</v>
       </c>
       <c r="AG10">
-        <v>379.22</v>
+        <v>378.63</v>
       </c>
       <c r="AH10">
-        <v>335.39</v>
+        <v>334.99</v>
       </c>
       <c r="AI10">
         <v>362.14</v>
@@ -1996,7 +1972,7 @@
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>42.36</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2007,10 +1983,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>175</v>
+        <v>174.49</v>
       </c>
       <c r="D11">
-        <v>1.6</v>
+        <v>-0.29</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2019,25 +1995,25 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-19.23</v>
+        <v>-19.46</v>
       </c>
       <c r="H11">
-        <v>11.17</v>
+        <v>10.84</v>
       </c>
       <c r="I11">
-        <v>-2.07</v>
+        <v>-0.65</v>
       </c>
       <c r="J11">
-        <v>-6.31</v>
+        <v>-4.65</v>
       </c>
       <c r="K11">
-        <v>-7.05</v>
+        <v>-5.81</v>
       </c>
       <c r="L11">
-        <v>3.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M11">
-        <v>8.43</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N11">
         <v>87</v>
@@ -2046,61 +2022,61 @@
         <v>60</v>
       </c>
       <c r="P11">
-        <v>173.73</v>
+        <v>173.5</v>
       </c>
       <c r="Q11">
-        <v>181.84</v>
+        <v>181.38</v>
       </c>
       <c r="R11">
-        <v>184.63</v>
+        <v>184.3</v>
       </c>
       <c r="S11">
-        <v>192.25</v>
+        <v>192.28</v>
       </c>
       <c r="T11">
-        <v>-8.970000000000001</v>
+        <v>-9.25</v>
       </c>
       <c r="U11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X11">
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>39.43</v>
+        <v>38.77</v>
       </c>
       <c r="Z11">
-        <v>-3.3</v>
+        <v>-3.32</v>
       </c>
       <c r="AA11">
-        <v>-2.16</v>
+        <v>-2.39</v>
       </c>
       <c r="AB11">
-        <v>-1.15</v>
+        <v>-0.93</v>
       </c>
       <c r="AC11">
-        <v>17.35</v>
+        <v>23.6</v>
       </c>
       <c r="AD11">
-        <v>9.92</v>
+        <v>16.16</v>
       </c>
       <c r="AE11">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="AF11">
-        <v>-17.17</v>
+        <v>-17.74</v>
       </c>
       <c r="AG11">
-        <v>193.61</v>
+        <v>193.56</v>
       </c>
       <c r="AH11">
-        <v>170.06</v>
+        <v>169.2</v>
       </c>
       <c r="AI11">
         <v>186.52</v>
@@ -2109,7 +2085,7 @@
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>36.68</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2120,10 +2096,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2269.3</v>
+        <v>2304.9</v>
       </c>
       <c r="D12">
-        <v>6.79</v>
+        <v>1.57</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2132,97 +2108,97 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-29.57</v>
+        <v>-28.46</v>
       </c>
       <c r="H12">
-        <v>14.46</v>
+        <v>16.26</v>
       </c>
       <c r="I12">
-        <v>8.06</v>
+        <v>10.8</v>
       </c>
       <c r="J12">
-        <v>2.96</v>
+        <v>4.73</v>
       </c>
       <c r="K12">
-        <v>3.12</v>
+        <v>5.29</v>
       </c>
       <c r="L12">
-        <v>-22.35</v>
+        <v>-22.02</v>
       </c>
       <c r="M12">
-        <v>-6.6</v>
+        <v>-6.12</v>
       </c>
       <c r="N12">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O12">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P12">
-        <v>2141.32</v>
+        <v>2186.24</v>
       </c>
       <c r="Q12">
-        <v>2118.84</v>
+        <v>2121.54</v>
       </c>
       <c r="R12">
-        <v>2246.16</v>
+        <v>2242.78</v>
       </c>
       <c r="S12">
-        <v>2447.32</v>
+        <v>2442.76</v>
       </c>
       <c r="T12">
-        <v>-7.27</v>
+        <v>-5.64</v>
       </c>
       <c r="U12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>61.55</v>
+        <v>64.2</v>
       </c>
       <c r="Z12">
-        <v>-21.93</v>
+        <v>-6.68</v>
       </c>
       <c r="AA12">
-        <v>-43.37</v>
+        <v>-36.03</v>
       </c>
       <c r="AB12">
-        <v>21.44</v>
+        <v>29.35</v>
       </c>
       <c r="AC12">
         <v>94.20999999999999</v>
       </c>
       <c r="AD12">
-        <v>86.53</v>
+        <v>90.88</v>
       </c>
       <c r="AE12">
-        <v>69.43000000000001</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AF12">
-        <v>192.78</v>
+        <v>190.56</v>
       </c>
       <c r="AG12">
-        <v>2244.71</v>
+        <v>2260.9</v>
       </c>
       <c r="AH12">
-        <v>1992.97</v>
+        <v>1982.17</v>
       </c>
       <c r="AI12">
-        <v>2003.85</v>
+        <v>2092.23</v>
       </c>
       <c r="AJ12" t="s">
         <v>56</v>
       </c>
       <c r="AK12">
-        <v>36.09</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2233,10 +2209,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4487</v>
+        <v>4444</v>
       </c>
       <c r="D13">
-        <v>1.98</v>
+        <v>-0.96</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2245,88 +2221,88 @@
         <v>3531.9</v>
       </c>
       <c r="G13">
-        <v>-13.2</v>
+        <v>-14.03</v>
       </c>
       <c r="H13">
-        <v>27.04</v>
+        <v>25.82</v>
       </c>
       <c r="I13">
-        <v>-1.38</v>
+        <v>1.53</v>
       </c>
       <c r="J13">
-        <v>-10.64</v>
+        <v>-11.29</v>
       </c>
       <c r="K13">
-        <v>-1.9</v>
+        <v>-2.96</v>
       </c>
       <c r="L13">
-        <v>25.84</v>
+        <v>25.16</v>
       </c>
       <c r="M13">
-        <v>12.37</v>
+        <v>11.92</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P13">
-        <v>4406.7</v>
+        <v>4420.1</v>
       </c>
       <c r="Q13">
-        <v>4678.24</v>
+        <v>4657.64</v>
       </c>
       <c r="R13">
-        <v>4900.36</v>
+        <v>4889.24</v>
       </c>
       <c r="S13">
-        <v>4427.01</v>
+        <v>4429.69</v>
       </c>
       <c r="T13">
-        <v>1.36</v>
+        <v>0.32</v>
       </c>
       <c r="U13" t="s">
+        <v>55</v>
+      </c>
+      <c r="V13" t="s">
         <v>54</v>
       </c>
-      <c r="V13" t="s">
+      <c r="W13" t="s">
         <v>55</v>
-      </c>
-      <c r="W13" t="s">
-        <v>54</v>
       </c>
       <c r="X13">
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>36.49</v>
+        <v>34.54</v>
       </c>
       <c r="Z13">
-        <v>-142.41</v>
+        <v>-139.85</v>
       </c>
       <c r="AA13">
-        <v>-115.98</v>
+        <v>-120.75</v>
       </c>
       <c r="AB13">
-        <v>-26.43</v>
+        <v>-19.1</v>
       </c>
       <c r="AC13">
-        <v>31.32</v>
+        <v>40.39</v>
       </c>
       <c r="AD13">
-        <v>16.81</v>
+        <v>28.09</v>
       </c>
       <c r="AE13">
-        <v>98.18000000000001</v>
+        <v>96.36</v>
       </c>
       <c r="AF13">
-        <v>-33.78</v>
+        <v>-34.36</v>
       </c>
       <c r="AG13">
-        <v>5086.79</v>
+        <v>5069.98</v>
       </c>
       <c r="AH13">
-        <v>4269.68</v>
+        <v>4245.29</v>
       </c>
       <c r="AI13">
         <v>4684.57</v>
@@ -2335,7 +2311,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>61.74</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2346,10 +2322,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2987.8</v>
+        <v>2971</v>
       </c>
       <c r="D14">
-        <v>2.57</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E14">
         <v>4807.3</v>
@@ -2358,91 +2334,91 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-37.85</v>
+        <v>-38.2</v>
       </c>
       <c r="H14">
-        <v>36.18</v>
+        <v>35.42</v>
       </c>
       <c r="I14">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="K14">
-        <v>4.14</v>
+        <v>3.6</v>
       </c>
       <c r="L14">
-        <v>-35.19</v>
+        <v>-36.16</v>
       </c>
       <c r="M14">
-        <v>20.65</v>
+        <v>20.92</v>
       </c>
       <c r="N14">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="O14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P14">
-        <v>2917.12</v>
+        <v>2933.26</v>
       </c>
       <c r="Q14">
-        <v>2769.43</v>
+        <v>2781.48</v>
       </c>
       <c r="R14">
-        <v>2866.38</v>
+        <v>2864.8</v>
       </c>
       <c r="S14">
-        <v>2813.5</v>
+        <v>2806.94</v>
       </c>
       <c r="T14">
-        <v>6.2</v>
+        <v>5.84</v>
       </c>
       <c r="U14" t="s">
+        <v>55</v>
+      </c>
+      <c r="V14" t="s">
         <v>54</v>
       </c>
-      <c r="V14" t="s">
+      <c r="W14" t="s">
         <v>55</v>
-      </c>
-      <c r="W14" t="s">
-        <v>54</v>
       </c>
       <c r="X14">
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>65.39</v>
+        <v>63.49</v>
       </c>
       <c r="Z14">
-        <v>18.18</v>
+        <v>27.9</v>
       </c>
       <c r="AA14">
-        <v>-21.36</v>
+        <v>-11.51</v>
       </c>
       <c r="AB14">
-        <v>39.54</v>
+        <v>39.41</v>
       </c>
       <c r="AC14">
-        <v>99.48999999999999</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="AD14">
-        <v>97.45999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AE14">
-        <v>74.84999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="AF14">
-        <v>-18.2</v>
+        <v>-38.54</v>
       </c>
       <c r="AG14">
-        <v>3016.29</v>
+        <v>3043.31</v>
       </c>
       <c r="AH14">
-        <v>2522.57</v>
+        <v>2519.65</v>
       </c>
       <c r="AI14">
-        <v>2722.95</v>
+        <v>2752.34</v>
       </c>
       <c r="AJ14" t="s">
         <v>56</v>
@@ -2459,109 +2435,109 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>214.83</v>
+        <v>230.22</v>
       </c>
       <c r="D15">
-        <v>-5.73</v>
+        <v>7.16</v>
       </c>
       <c r="E15">
-        <v>353.1</v>
+        <v>349.6</v>
       </c>
       <c r="F15">
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-39.16</v>
+        <v>-34.15</v>
       </c>
       <c r="H15">
-        <v>12.02</v>
+        <v>20.04</v>
       </c>
       <c r="I15">
-        <v>9.44</v>
+        <v>16.26</v>
       </c>
       <c r="J15">
-        <v>-2.7</v>
+        <v>3.68</v>
       </c>
       <c r="K15">
-        <v>-14.9</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L15">
-        <v>-39.75</v>
+        <v>-34.8</v>
       </c>
       <c r="M15">
-        <v>5.48</v>
+        <v>7.71</v>
       </c>
       <c r="N15">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="O15">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="P15">
-        <v>209.89</v>
+        <v>216.33</v>
       </c>
       <c r="Q15">
-        <v>209.08</v>
+        <v>209.94</v>
       </c>
       <c r="R15">
-        <v>221.48</v>
+        <v>221.51</v>
       </c>
       <c r="S15">
-        <v>245.58</v>
+        <v>245.21</v>
       </c>
       <c r="T15">
-        <v>-12.52</v>
+        <v>-6.11</v>
       </c>
       <c r="U15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>51.24</v>
+        <v>59.49</v>
       </c>
       <c r="Z15">
-        <v>-3.58</v>
+        <v>-1.63</v>
       </c>
       <c r="AA15">
-        <v>-5.94</v>
+        <v>-5.08</v>
       </c>
       <c r="AB15">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="AC15">
-        <v>91.76000000000001</v>
+        <v>90.45</v>
       </c>
       <c r="AD15">
-        <v>76.40000000000001</v>
+        <v>86.44</v>
       </c>
       <c r="AE15">
-        <v>11.29</v>
+        <v>12.85</v>
       </c>
       <c r="AF15">
-        <v>394.92</v>
+        <v>1347.09</v>
       </c>
       <c r="AG15">
-        <v>230.25</v>
+        <v>233.09</v>
       </c>
       <c r="AH15">
-        <v>187.91</v>
+        <v>186.8</v>
       </c>
       <c r="AI15">
-        <v>193.57</v>
+        <v>197.45</v>
       </c>
       <c r="AJ15" t="s">
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>44.31</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2572,10 +2548,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>33.76</v>
+        <v>33.92</v>
       </c>
       <c r="D16">
-        <v>2.24</v>
+        <v>0.47</v>
       </c>
       <c r="E16">
         <v>57.7</v>
@@ -2584,25 +2560,25 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-41.49</v>
+        <v>-41.21</v>
       </c>
       <c r="H16">
-        <v>7.65</v>
+        <v>8.16</v>
       </c>
       <c r="I16">
-        <v>-1.23</v>
+        <v>-0.26</v>
       </c>
       <c r="J16">
-        <v>-5.99</v>
+        <v>-4.72</v>
       </c>
       <c r="K16">
-        <v>-16.87</v>
+        <v>-16.6</v>
       </c>
       <c r="L16">
-        <v>-41.27</v>
+        <v>-39.93</v>
       </c>
       <c r="M16">
-        <v>-7.74</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="N16">
         <v>7</v>
@@ -2611,61 +2587,61 @@
         <v>12</v>
       </c>
       <c r="P16">
-        <v>33.33</v>
+        <v>33.31</v>
       </c>
       <c r="Q16">
-        <v>34.77</v>
+        <v>34.66</v>
       </c>
       <c r="R16">
-        <v>36.75</v>
+        <v>36.62</v>
       </c>
       <c r="S16">
-        <v>41.14</v>
+        <v>41.05</v>
       </c>
       <c r="T16">
-        <v>-17.94</v>
+        <v>-17.38</v>
       </c>
       <c r="U16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>40.13</v>
+        <v>41.45</v>
       </c>
       <c r="Z16">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="AA16">
         <v>-0.96</v>
       </c>
       <c r="AB16">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>20.05</v>
+        <v>40.42</v>
       </c>
       <c r="AD16">
-        <v>10.93</v>
+        <v>21.06</v>
       </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>-73.58</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="AG16">
-        <v>36.97</v>
+        <v>36.79</v>
       </c>
       <c r="AH16">
-        <v>32.57</v>
+        <v>32.53</v>
       </c>
       <c r="AI16">
         <v>36.59</v>
@@ -2674,7 +2650,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>14.25</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2685,10 +2661,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1041</v>
+        <v>1039.8</v>
       </c>
       <c r="D17">
-        <v>2.06</v>
+        <v>-0.12</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2697,88 +2673,88 @@
         <v>1020</v>
       </c>
       <c r="G17">
-        <v>-33.12</v>
+        <v>-33.19</v>
       </c>
       <c r="H17">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="I17">
-        <v>-2.52</v>
+        <v>-1.61</v>
       </c>
       <c r="J17">
-        <v>-10.14</v>
+        <v>-10.75</v>
       </c>
       <c r="K17">
-        <v>-23.39</v>
+        <v>-24.51</v>
       </c>
       <c r="L17">
-        <v>-23.63</v>
+        <v>-24.52</v>
       </c>
       <c r="M17">
-        <v>-4.06</v>
+        <v>-4.29</v>
       </c>
       <c r="N17">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P17">
-        <v>1036.7</v>
+        <v>1033.3</v>
       </c>
       <c r="Q17">
-        <v>1088.99</v>
+        <v>1084.13</v>
       </c>
       <c r="R17">
-        <v>1174.73</v>
+        <v>1169.03</v>
       </c>
       <c r="S17">
-        <v>1318.29</v>
+        <v>1316.53</v>
       </c>
       <c r="T17">
-        <v>-21.03</v>
+        <v>-21.02</v>
       </c>
       <c r="U17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>35.21</v>
+        <v>35.02</v>
       </c>
       <c r="Z17">
-        <v>-40.82</v>
+        <v>-39.55</v>
       </c>
       <c r="AA17">
-        <v>-38.89</v>
+        <v>-39.02</v>
       </c>
       <c r="AB17">
-        <v>-1.94</v>
+        <v>-0.53</v>
       </c>
       <c r="AC17">
-        <v>16.28</v>
+        <v>29.47</v>
       </c>
       <c r="AD17">
-        <v>11.55</v>
+        <v>16.55</v>
       </c>
       <c r="AE17">
-        <v>29.04</v>
+        <v>29.12</v>
       </c>
       <c r="AF17">
-        <v>-35.2</v>
+        <v>-6.98</v>
       </c>
       <c r="AG17">
-        <v>1171.3</v>
+        <v>1165.98</v>
       </c>
       <c r="AH17">
-        <v>1006.68</v>
+        <v>1002.28</v>
       </c>
       <c r="AI17">
         <v>1113.88</v>
@@ -2787,7 +2763,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>59.02</v>
+        <v>58.38</v>
       </c>
     </row>
   </sheetData>
@@ -2971,1774 +2947,1771 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>86</v>
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.56</v>
+        <v>-9.09</v>
       </c>
       <c r="D11" s="6">
-        <v>1.17</v>
+        <v>-10.86</v>
       </c>
       <c r="E11" s="7">
-        <v>2.73</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-11.03</v>
+        <v>-1.48</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.09</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.94</v>
+        <v>0.39</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.87</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.91</v>
+        <v>3.16</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.48</v>
+        <v>2.79</v>
       </c>
       <c r="E13" s="7">
-        <v>0.43</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>5.62</v>
+        <v>-5.21</v>
       </c>
       <c r="D14" s="6">
-        <v>3.16</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-2.46</v>
+        <v>-5.83</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.21</v>
+        <v>-3.96</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.21</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1</v>
+        <v>-0.31</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3.65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.22</v>
+        <v>0.52</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.96</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.26</v>
+        <v>7.1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>6.58</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.72</v>
+        <v>-3.66</v>
       </c>
       <c r="D17" s="6">
-        <v>0.52</v>
+        <v>-5.31</v>
       </c>
       <c r="E17" s="7">
-        <v>4.24</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>0.13</v>
+        <v>-5.99</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.66</v>
+        <v>-3.19</v>
       </c>
       <c r="E18" s="8">
-        <v>-3.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.11</v>
+        <v>-6.31</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.99</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.12</v>
+        <v>-4.65</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-8.75</v>
+        <v>2.96</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.31</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.44</v>
+        <v>4.73</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.77</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.76</v>
+        <v>-10.64</v>
       </c>
       <c r="D21" s="6">
-        <v>2.96</v>
+        <v>-11.29</v>
       </c>
       <c r="E21" s="7">
-        <v>6.72</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-12.09</v>
+        <v>6</v>
       </c>
       <c r="D22" s="6">
-        <v>-10.64</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.45</v>
+        <v>6.02</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.02</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>3.3</v>
+        <v>-2.7</v>
       </c>
       <c r="D23" s="6">
-        <v>6</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.7</v>
+        <v>3.68</v>
+      </c>
+      <c r="E23" s="8">
+        <v>6.38</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.39</v>
+        <v>-5.99</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.7</v>
+        <v>-4.72</v>
       </c>
       <c r="E24" s="8">
-        <v>-2.31</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-8.609999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="D25" s="6">
-        <v>-5.99</v>
+        <v>-10.75</v>
       </c>
       <c r="E25" s="7">
-        <v>2.62</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-10.82</v>
+        <v>-1.61</v>
       </c>
       <c r="D26" s="6">
-        <v>-10.14</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.68</v>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-1.86</v>
+        <v>-7.77</v>
       </c>
       <c r="D27" s="6">
-        <v>-1.61</v>
+        <v>-7.8</v>
       </c>
       <c r="E27" s="7">
-        <v>0.25</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-3.67</v>
+        <v>-0.12</v>
       </c>
       <c r="D28" s="6">
-        <v>-7.77</v>
+        <v>1.37</v>
       </c>
       <c r="E28" s="8">
-        <v>-4.1</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="D29" s="6">
-        <v>-0.12</v>
+        <v>3.24</v>
       </c>
       <c r="E29" s="8">
-        <v>-1.62</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>3.17</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D30" s="6">
-        <v>2.16</v>
+        <v>-0.04</v>
       </c>
       <c r="E30" s="8">
-        <v>-1.01</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-0.86</v>
+        <v>-1.64</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.3</v>
+        <v>2</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.64</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>0.53</v>
+        <v>10.79</v>
       </c>
       <c r="D32" s="6">
-        <v>-1.64</v>
+        <v>17.54</v>
       </c>
       <c r="E32" s="8">
-        <v>-2.17</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>4.9</v>
+        <v>-0.42</v>
       </c>
       <c r="D33" s="6">
-        <v>10.79</v>
-      </c>
-      <c r="E33" s="7">
-        <v>5.89</v>
+        <v>0.17</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-0.35</v>
+        <v>-1.89</v>
       </c>
       <c r="D34" s="6">
-        <v>-0.42</v>
+        <v>2.27</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.07000000000000001</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-2.22</v>
+        <v>-2.07</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.33</v>
+        <v>-0.65</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.42</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-3.31</v>
+        <v>8.06</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.24</v>
+        <v>10.8</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.74</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>0.5</v>
+        <v>-1.38</v>
       </c>
       <c r="D37" s="6">
-        <v>8.06</v>
-      </c>
-      <c r="E37" s="7">
-        <v>7.56</v>
+        <v>1.53</v>
+      </c>
+      <c r="E37" s="8">
+        <v>2.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-3.93</v>
+        <v>2.81</v>
       </c>
       <c r="D38" s="6">
-        <v>-1.38</v>
+        <v>2.79</v>
       </c>
       <c r="E38" s="7">
-        <v>2.55</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>12.91</v>
+        <v>9.44</v>
       </c>
       <c r="D39" s="6">
-        <v>2.81</v>
+        <v>16.26</v>
       </c>
       <c r="E39" s="8">
-        <v>-10.1</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>17.46</v>
+        <v>-1.23</v>
       </c>
       <c r="D40" s="6">
-        <v>9.44</v>
+        <v>-0.26</v>
       </c>
       <c r="E40" s="8">
-        <v>-8.02</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>-3.82</v>
+        <v>-2.52</v>
       </c>
       <c r="D41" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.59</v>
+        <v>-1.61</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.91</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C42" s="6">
-        <v>-3.89</v>
+        <v>-0.8</v>
       </c>
       <c r="D42" s="6">
-        <v>-2.52</v>
+        <v>-0.92</v>
       </c>
       <c r="E42" s="7">
-        <v>1.37</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6">
-        <v>-2.97</v>
+        <v>-1.51</v>
       </c>
       <c r="D43" s="6">
-        <v>-0.8</v>
+        <v>-3.73</v>
       </c>
       <c r="E43" s="7">
-        <v>2.17</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="6">
-        <v>-2.46</v>
+        <v>-32.37</v>
       </c>
       <c r="D44" s="6">
-        <v>-1.51</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.95</v>
+        <v>-32.32</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="6">
-        <v>-33.69</v>
+        <v>-29.56</v>
       </c>
       <c r="D45" s="6">
-        <v>-32.37</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.32</v>
+        <v>-29.45</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.11</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="6">
-        <v>-29.85</v>
+        <v>-0.99</v>
       </c>
       <c r="D46" s="6">
-        <v>-29.56</v>
+        <v>-2.23</v>
       </c>
       <c r="E46" s="7">
-        <v>0.29</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>0.01</v>
+        <v>-13.58</v>
       </c>
       <c r="D47" s="6">
-        <v>-0.99</v>
+        <v>-10.89</v>
       </c>
       <c r="E47" s="8">
-        <v>-1</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-13.67</v>
+        <v>-36.11</v>
       </c>
       <c r="D48" s="6">
-        <v>-13.58</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.09</v>
+        <v>-33.82</v>
+      </c>
+      <c r="E48" s="8">
+        <v>2.29</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-38.48</v>
+        <v>-32.43</v>
       </c>
       <c r="D49" s="6">
-        <v>-36.11</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2.37</v>
+        <v>-31.32</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.11</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-32.34</v>
+        <v>-10.49</v>
       </c>
       <c r="D50" s="6">
-        <v>-32.43</v>
+        <v>-9.07</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.09</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-12.43</v>
+        <v>3.88</v>
       </c>
       <c r="D51" s="6">
-        <v>-10.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E51" s="7">
-        <v>1.94</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>2.54</v>
+        <v>-22.35</v>
       </c>
       <c r="D52" s="6">
-        <v>3.88</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.34</v>
+        <v>-22.02</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.33</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-25.98</v>
+        <v>25.84</v>
       </c>
       <c r="D53" s="6">
-        <v>-22.35</v>
+        <v>25.16</v>
       </c>
       <c r="E53" s="7">
-        <v>3.63</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>28.72</v>
+        <v>-35.19</v>
       </c>
       <c r="D54" s="6">
-        <v>25.84</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.88</v>
+        <v>-36.16</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-37.74</v>
+        <v>-39.75</v>
       </c>
       <c r="D55" s="6">
-        <v>-35.19</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.55</v>
+        <v>-34.8</v>
+      </c>
+      <c r="E55" s="8">
+        <v>4.95</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-37.73</v>
+        <v>-41.27</v>
       </c>
       <c r="D56" s="6">
-        <v>-39.75</v>
+        <v>-39.93</v>
       </c>
       <c r="E56" s="8">
-        <v>-2.02</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>-43.73</v>
+        <v>-23.63</v>
       </c>
       <c r="D57" s="6">
-        <v>-41.27</v>
+        <v>-24.52</v>
       </c>
       <c r="E57" s="7">
-        <v>2.46</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58" s="6">
-        <v>-25.43</v>
+        <v>-1.25</v>
       </c>
       <c r="D58" s="6">
-        <v>-23.63</v>
+        <v>-2.4</v>
       </c>
       <c r="E58" s="7">
-        <v>1.8</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="6">
-        <v>-3.66</v>
+        <v>-4.69</v>
       </c>
       <c r="D59" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="E59" s="7">
-        <v>2.41</v>
+        <v>-2.1</v>
+      </c>
+      <c r="E59" s="8">
+        <v>2.59</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6">
-        <v>-5.41</v>
+        <v>-13.33</v>
       </c>
       <c r="D60" s="6">
-        <v>-4.69</v>
+        <v>-14.91</v>
       </c>
       <c r="E60" s="7">
-        <v>0.72</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6">
-        <v>-13.24</v>
+        <v>-10.31</v>
       </c>
       <c r="D61" s="6">
-        <v>-13.33</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="E61" s="8">
-        <v>-0.09</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6">
-        <v>-10.84</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="D62" s="6">
-        <v>-10.31</v>
+        <v>-10.61</v>
       </c>
       <c r="E62" s="7">
-        <v>0.53</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="6">
-        <v>-9.41</v>
+        <v>-12.54</v>
       </c>
       <c r="D63" s="6">
-        <v>-9.529999999999999</v>
+        <v>-8.99</v>
       </c>
       <c r="E63" s="8">
-        <v>-0.12</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6">
-        <v>-12.73</v>
+        <v>-7.32</v>
       </c>
       <c r="D64" s="6">
-        <v>-12.54</v>
-      </c>
-      <c r="E64" s="7">
-        <v>0.19</v>
+        <v>2.92</v>
+      </c>
+      <c r="E64" s="8">
+        <v>10.24</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="6">
-        <v>-14.82</v>
+        <v>-7.03</v>
       </c>
       <c r="D65" s="6">
-        <v>-7.32</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="E65" s="7">
-        <v>7.5</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-9.75</v>
+        <v>-8.66</v>
       </c>
       <c r="D66" s="6">
-        <v>-7.03</v>
-      </c>
-      <c r="E66" s="7">
-        <v>2.72</v>
+        <v>-7.32</v>
+      </c>
+      <c r="E66" s="8">
+        <v>1.34</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-9.039999999999999</v>
+        <v>-7.05</v>
       </c>
       <c r="D67" s="6">
-        <v>-8.66</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.38</v>
+        <v>-5.81</v>
+      </c>
+      <c r="E67" s="8">
+        <v>1.24</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-7.95</v>
+        <v>3.12</v>
       </c>
       <c r="D68" s="6">
-        <v>-7.05</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.9</v>
+        <v>5.29</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.17</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-2.59</v>
+        <v>-1.9</v>
       </c>
       <c r="D69" s="6">
-        <v>3.12</v>
+        <v>-2.96</v>
       </c>
       <c r="E69" s="7">
-        <v>5.71</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-4.38</v>
+        <v>4.14</v>
       </c>
       <c r="D70" s="6">
-        <v>-1.9</v>
+        <v>3.6</v>
       </c>
       <c r="E70" s="7">
-        <v>2.48</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>0.44</v>
+        <v>-14.9</v>
       </c>
       <c r="D71" s="6">
-        <v>4.14</v>
-      </c>
-      <c r="E71" s="7">
-        <v>3.7</v>
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="E71" s="8">
+        <v>5.04</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-5.29</v>
+        <v>-16.87</v>
       </c>
       <c r="D72" s="6">
-        <v>-14.9</v>
+        <v>-16.6</v>
       </c>
       <c r="E72" s="8">
-        <v>-9.609999999999999</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>-19.7</v>
+        <v>-23.39</v>
       </c>
       <c r="D73" s="6">
-        <v>-16.87</v>
+        <v>-24.51</v>
       </c>
       <c r="E73" s="7">
-        <v>2.83</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>-24.42</v>
+        <v>-3.74</v>
       </c>
       <c r="D74" s="6">
-        <v>-23.39</v>
-      </c>
-      <c r="E74" s="7">
-        <v>1.03</v>
+        <v>-3.58</v>
+      </c>
+      <c r="E74" s="8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="6">
-        <v>-5.42</v>
+        <v>-21.19</v>
       </c>
       <c r="D75" s="6">
-        <v>-3.74</v>
+        <v>-21.92</v>
       </c>
       <c r="E75" s="7">
-        <v>1.68</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6">
-        <v>-21.17</v>
+        <v>-33.23</v>
       </c>
       <c r="D76" s="6">
-        <v>-21.19</v>
+        <v>-32.12</v>
       </c>
       <c r="E76" s="8">
-        <v>-0.02</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="6">
-        <v>-33.21</v>
+        <v>-30.56</v>
       </c>
       <c r="D77" s="6">
-        <v>-33.23</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-0.02</v>
+        <v>-30.59</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="6">
-        <v>-29.77</v>
+        <v>-18.88</v>
       </c>
       <c r="D78" s="6">
-        <v>-30.56</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-0.79</v>
+        <v>-19.54</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="6">
-        <v>-19.35</v>
+        <v>-23.83</v>
       </c>
       <c r="D79" s="6">
-        <v>-18.88</v>
-      </c>
-      <c r="E79" s="7">
-        <v>0.47</v>
+        <v>-21.62</v>
+      </c>
+      <c r="E79" s="8">
+        <v>2.21</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="6">
-        <v>-23.93</v>
+        <v>-40.4</v>
       </c>
       <c r="D80" s="6">
-        <v>-23.83</v>
-      </c>
-      <c r="E80" s="7">
-        <v>0.1</v>
+        <v>-36.99</v>
+      </c>
+      <c r="E80" s="8">
+        <v>3.41</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="6">
-        <v>-43.36</v>
+        <v>-39.64</v>
       </c>
       <c r="D81" s="6">
-        <v>-40.4</v>
+        <v>-40.14</v>
       </c>
       <c r="E81" s="7">
-        <v>2.96</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="6">
-        <v>-39.83</v>
+        <v>-25.29</v>
       </c>
       <c r="D82" s="6">
-        <v>-39.64</v>
-      </c>
-      <c r="E82" s="7">
-        <v>0.19</v>
+        <v>-23.56</v>
+      </c>
+      <c r="E82" s="8">
+        <v>1.73</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="6">
-        <v>-25.57</v>
+        <v>-19.23</v>
       </c>
       <c r="D83" s="6">
-        <v>-25.29</v>
+        <v>-19.46</v>
       </c>
       <c r="E83" s="7">
-        <v>0.28</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="6">
-        <v>-20.5</v>
+        <v>-29.57</v>
       </c>
       <c r="D84" s="6">
-        <v>-19.23</v>
-      </c>
-      <c r="E84" s="7">
-        <v>1.27</v>
+        <v>-28.46</v>
+      </c>
+      <c r="E84" s="8">
+        <v>1.11</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="6">
-        <v>-34.04</v>
+        <v>-13.2</v>
       </c>
       <c r="D85" s="6">
-        <v>-29.57</v>
+        <v>-14.03</v>
       </c>
       <c r="E85" s="7">
-        <v>4.47</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-14.88</v>
+        <v>-37.85</v>
       </c>
       <c r="D86" s="6">
-        <v>-13.2</v>
+        <v>-38.2</v>
       </c>
       <c r="E86" s="7">
-        <v>1.68</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-39.4</v>
+        <v>-39.16</v>
       </c>
       <c r="D87" s="6">
-        <v>-37.85</v>
-      </c>
-      <c r="E87" s="7">
-        <v>1.55</v>
+        <v>-34.15</v>
+      </c>
+      <c r="E87" s="8">
+        <v>5.01</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>-36.08</v>
+        <v>-41.49</v>
       </c>
       <c r="D88" s="6">
-        <v>-39.16</v>
+        <v>-41.21</v>
       </c>
       <c r="E88" s="8">
-        <v>-3.08</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>-42.77</v>
+        <v>-33.12</v>
       </c>
       <c r="D89" s="6">
-        <v>-41.49</v>
+        <v>-33.19</v>
       </c>
       <c r="E89" s="7">
-        <v>1.28</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C90" s="6">
-        <v>-34.46</v>
+        <v>724.15</v>
       </c>
       <c r="D90" s="6">
-        <v>-33.12</v>
-      </c>
-      <c r="E90" s="7">
-        <v>1.34</v>
+        <v>725.4</v>
+      </c>
+      <c r="E90" s="8">
+        <v>1.25</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>711.5</v>
+        <v>852.3</v>
       </c>
       <c r="D91" s="6">
-        <v>724.15</v>
+        <v>844.4</v>
       </c>
       <c r="E91" s="7">
-        <v>12.65</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="6">
-        <v>852.6</v>
+        <v>200.05</v>
       </c>
       <c r="D92" s="6">
-        <v>852.3</v>
+        <v>202.77</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.3</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="6">
-        <v>200.11</v>
+        <v>629.85</v>
       </c>
       <c r="D93" s="6">
-        <v>200.05</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-0.06</v>
+        <v>629.55</v>
+      </c>
+      <c r="E93" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="6">
-        <v>636.95</v>
+        <v>1672.4</v>
       </c>
       <c r="D94" s="6">
-        <v>629.85</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-7.1</v>
+        <v>1658.9</v>
+      </c>
+      <c r="E94" s="7">
+        <v>-13.5</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="6">
-        <v>1662.7</v>
+        <v>960</v>
       </c>
       <c r="D95" s="6">
-        <v>1672.4</v>
-      </c>
-      <c r="E95" s="7">
-        <v>9.699999999999999</v>
+        <v>987.9</v>
+      </c>
+      <c r="E95" s="8">
+        <v>27.9</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="6">
-        <v>958.8</v>
+        <v>3426.7</v>
       </c>
       <c r="D96" s="6">
-        <v>960</v>
-      </c>
-      <c r="E96" s="7">
-        <v>1.2</v>
+        <v>3623.1</v>
+      </c>
+      <c r="E96" s="8">
+        <v>196.4</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6">
-        <v>3257</v>
+        <v>621.55</v>
       </c>
       <c r="D97" s="6">
-        <v>3426.7</v>
+        <v>616.35</v>
       </c>
       <c r="E97" s="7">
-        <v>169.7</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="6">
-        <v>619.6</v>
+        <v>345</v>
       </c>
       <c r="D98" s="6">
-        <v>621.55</v>
-      </c>
-      <c r="E98" s="7">
-        <v>1.95</v>
+        <v>353</v>
+      </c>
+      <c r="E98" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="6">
-        <v>343.7</v>
+        <v>175</v>
       </c>
       <c r="D99" s="6">
-        <v>345</v>
+        <v>174.49</v>
       </c>
       <c r="E99" s="7">
-        <v>1.3</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="6">
-        <v>172.24</v>
+        <v>2269.3</v>
       </c>
       <c r="D100" s="6">
-        <v>175</v>
-      </c>
-      <c r="E100" s="7">
-        <v>2.76</v>
+        <v>2304.9</v>
+      </c>
+      <c r="E100" s="8">
+        <v>35.6</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="6">
-        <v>2125</v>
+        <v>4487</v>
       </c>
       <c r="D101" s="6">
-        <v>2269.3</v>
+        <v>4444</v>
       </c>
       <c r="E101" s="7">
-        <v>144.3</v>
+        <v>-43</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="6">
-        <v>4400</v>
+        <v>2987.8</v>
       </c>
       <c r="D102" s="6">
-        <v>4487</v>
+        <v>2971</v>
       </c>
       <c r="E102" s="7">
-        <v>87</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="6">
-        <v>2913</v>
+        <v>214.83</v>
       </c>
       <c r="D103" s="6">
-        <v>2987.8</v>
-      </c>
-      <c r="E103" s="7">
-        <v>74.8</v>
+        <v>230.22</v>
+      </c>
+      <c r="E103" s="8">
+        <v>15.39</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C104" s="6">
-        <v>227.89</v>
+        <v>33.76</v>
       </c>
       <c r="D104" s="6">
-        <v>214.83</v>
+        <v>33.92</v>
       </c>
       <c r="E104" s="8">
-        <v>-13.06</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C105" s="6">
-        <v>33.02</v>
+        <v>1041</v>
       </c>
       <c r="D105" s="6">
-        <v>33.76</v>
+        <v>1039.8</v>
       </c>
       <c r="E105" s="7">
-        <v>0.74</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C106" s="6">
-        <v>1020</v>
+        <v>26</v>
       </c>
       <c r="D106" s="6">
-        <v>1041</v>
+        <v>19</v>
       </c>
       <c r="E106" s="7">
-        <v>21</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="6">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D107" s="6">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E107" s="7">
-        <v>7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -4749,13 +4722,13 @@
         <v>13</v>
       </c>
       <c r="C108" s="6">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D108" s="6">
-        <v>74</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-7</v>
+        <v>68</v>
+      </c>
+      <c r="E108" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -4766,13 +4739,13 @@
         <v>13</v>
       </c>
       <c r="C109" s="6">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D109" s="6">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E109" s="8">
-        <v>-12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -4783,29 +4756,29 @@
         <v>13</v>
       </c>
       <c r="C110" s="6">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D110" s="6">
-        <v>32</v>
-      </c>
-      <c r="E110" s="7">
-        <v>13</v>
+        <v>50</v>
+      </c>
+      <c r="E110" s="8">
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C111" s="6">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D111" s="6">
-        <v>62</v>
-      </c>
-      <c r="E111" s="8">
+        <v>32</v>
+      </c>
+      <c r="E111" s="7">
         <v>-6</v>
       </c>
     </row>
@@ -4817,13 +4790,13 @@
         <v>13</v>
       </c>
       <c r="C112" s="6">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D112" s="6">
-        <v>68</v>
-      </c>
-      <c r="E112" s="7">
-        <v>12</v>
+        <v>74</v>
+      </c>
+      <c r="E112" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -4834,13 +4807,13 @@
         <v>13</v>
       </c>
       <c r="C113" s="6">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D113" s="6">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E113" s="7">
-        <v>6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4851,13 +4824,13 @@
         <v>13</v>
       </c>
       <c r="C114" s="6">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D114" s="6">
+        <v>26</v>
+      </c>
+      <c r="E114" s="8">
         <v>13</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-19</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4868,13 +4841,13 @@
         <v>13</v>
       </c>
       <c r="C115" s="6">
+        <v>19</v>
+      </c>
+      <c r="D115" s="6">
         <v>13</v>
       </c>
-      <c r="D115" s="6">
-        <v>19</v>
-      </c>
       <c r="E115" s="7">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -4885,13 +4858,13 @@
         <v>24</v>
       </c>
       <c r="C116" s="6">
-        <v>44.49</v>
+        <v>50.3</v>
       </c>
       <c r="D116" s="6">
-        <v>50.3</v>
-      </c>
-      <c r="E116" s="7">
-        <v>5.81</v>
+        <v>50.84</v>
+      </c>
+      <c r="E116" s="8">
+        <v>0.54</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4902,13 +4875,13 @@
         <v>24</v>
       </c>
       <c r="C117" s="6">
-        <v>36.88</v>
+        <v>36.84</v>
       </c>
       <c r="D117" s="6">
-        <v>36.84</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-0.04</v>
+        <v>35.74</v>
+      </c>
+      <c r="E117" s="7">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4919,13 +4892,13 @@
         <v>24</v>
       </c>
       <c r="C118" s="6">
-        <v>44.13</v>
+        <v>44</v>
       </c>
       <c r="D118" s="6">
-        <v>44</v>
+        <v>51.11</v>
       </c>
       <c r="E118" s="8">
-        <v>-0.13</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4936,13 +4909,13 @@
         <v>24</v>
       </c>
       <c r="C119" s="6">
-        <v>49.92</v>
+        <v>48.23</v>
       </c>
       <c r="D119" s="6">
-        <v>48.23</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-1.69</v>
+        <v>48.16</v>
+      </c>
+      <c r="E119" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4953,13 +4926,13 @@
         <v>24</v>
       </c>
       <c r="C120" s="6">
-        <v>42.09</v>
+        <v>44.55</v>
       </c>
       <c r="D120" s="6">
-        <v>44.55</v>
+        <v>41.88</v>
       </c>
       <c r="E120" s="7">
-        <v>2.46</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4970,13 +4943,13 @@
         <v>24</v>
       </c>
       <c r="C121" s="6">
-        <v>39.21</v>
+        <v>39.76</v>
       </c>
       <c r="D121" s="6">
-        <v>39.76</v>
-      </c>
-      <c r="E121" s="7">
-        <v>0.55</v>
+        <v>50.91</v>
+      </c>
+      <c r="E121" s="8">
+        <v>11.15</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4987,13 +4960,13 @@
         <v>24</v>
       </c>
       <c r="C122" s="6">
-        <v>48.88</v>
+        <v>59.36</v>
       </c>
       <c r="D122" s="6">
-        <v>59.36</v>
-      </c>
-      <c r="E122" s="7">
-        <v>10.48</v>
+        <v>67.62</v>
+      </c>
+      <c r="E122" s="8">
+        <v>8.26</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5004,13 +4977,13 @@
         <v>24</v>
       </c>
       <c r="C123" s="6">
-        <v>43.29</v>
+        <v>44.03</v>
       </c>
       <c r="D123" s="6">
-        <v>44.03</v>
+        <v>42.45</v>
       </c>
       <c r="E123" s="7">
-        <v>0.74</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5021,13 +4994,13 @@
         <v>24</v>
       </c>
       <c r="C124" s="6">
-        <v>36.75</v>
+        <v>38.26</v>
       </c>
       <c r="D124" s="6">
-        <v>38.26</v>
-      </c>
-      <c r="E124" s="7">
-        <v>1.51</v>
+        <v>46.7</v>
+      </c>
+      <c r="E124" s="8">
+        <v>8.44</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -5038,13 +5011,13 @@
         <v>24</v>
       </c>
       <c r="C125" s="6">
-        <v>33.72</v>
+        <v>39.43</v>
       </c>
       <c r="D125" s="6">
-        <v>39.43</v>
+        <v>38.77</v>
       </c>
       <c r="E125" s="7">
-        <v>5.71</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -5055,13 +5028,13 @@
         <v>24</v>
       </c>
       <c r="C126" s="6">
-        <v>46.71</v>
+        <v>61.55</v>
       </c>
       <c r="D126" s="6">
-        <v>61.55</v>
-      </c>
-      <c r="E126" s="7">
-        <v>14.84</v>
+        <v>64.2</v>
+      </c>
+      <c r="E126" s="8">
+        <v>2.65</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -5072,13 +5045,13 @@
         <v>24</v>
       </c>
       <c r="C127" s="6">
-        <v>28.95</v>
+        <v>36.49</v>
       </c>
       <c r="D127" s="6">
-        <v>36.49</v>
+        <v>34.54</v>
       </c>
       <c r="E127" s="7">
-        <v>7.54</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -5089,13 +5062,13 @@
         <v>24</v>
       </c>
       <c r="C128" s="6">
-        <v>60.5</v>
+        <v>65.39</v>
       </c>
       <c r="D128" s="6">
-        <v>65.39</v>
+        <v>63.49</v>
       </c>
       <c r="E128" s="7">
-        <v>4.89</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5106,13 +5079,13 @@
         <v>24</v>
       </c>
       <c r="C129" s="6">
-        <v>61.04</v>
+        <v>51.24</v>
       </c>
       <c r="D129" s="6">
-        <v>51.24</v>
+        <v>59.49</v>
       </c>
       <c r="E129" s="8">
-        <v>-9.800000000000001</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5123,13 +5096,13 @@
         <v>24</v>
       </c>
       <c r="C130" s="6">
-        <v>33.75</v>
+        <v>40.13</v>
       </c>
       <c r="D130" s="6">
-        <v>40.13</v>
-      </c>
-      <c r="E130" s="7">
-        <v>6.38</v>
+        <v>41.45</v>
+      </c>
+      <c r="E130" s="8">
+        <v>1.32</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5140,13 +5113,13 @@
         <v>24</v>
       </c>
       <c r="C131" s="6">
-        <v>28.82</v>
+        <v>35.21</v>
       </c>
       <c r="D131" s="6">
-        <v>35.21</v>
+        <v>35.02</v>
       </c>
       <c r="E131" s="7">
-        <v>6.39</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5157,13 +5130,13 @@
         <v>31</v>
       </c>
       <c r="C132" s="6">
-        <v>-34.09</v>
+        <v>-47.54</v>
       </c>
       <c r="D132" s="6">
-        <v>-47.54</v>
-      </c>
-      <c r="E132" s="8">
-        <v>-13.45</v>
+        <v>-50.18</v>
+      </c>
+      <c r="E132" s="7">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -5174,13 +5147,13 @@
         <v>31</v>
       </c>
       <c r="C133" s="6">
-        <v>-65.17</v>
+        <v>-69.2</v>
       </c>
       <c r="D133" s="6">
-        <v>-69.2</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-4.03</v>
+        <v>-73.23999999999999</v>
+      </c>
+      <c r="E133" s="7">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -5191,13 +5164,13 @@
         <v>31</v>
       </c>
       <c r="C134" s="6">
-        <v>-45.51</v>
+        <v>-41.34</v>
       </c>
       <c r="D134" s="6">
-        <v>-41.34</v>
-      </c>
-      <c r="E134" s="7">
-        <v>4.17</v>
+        <v>-24.06</v>
+      </c>
+      <c r="E134" s="8">
+        <v>17.28</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -5208,13 +5181,13 @@
         <v>31</v>
       </c>
       <c r="C135" s="6">
-        <v>166.49</v>
+        <v>-48.99</v>
       </c>
       <c r="D135" s="6">
-        <v>-48.99</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-215.48</v>
+        <v>-68.75</v>
+      </c>
+      <c r="E135" s="7">
+        <v>-19.76</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -5225,13 +5198,13 @@
         <v>31</v>
       </c>
       <c r="C136" s="6">
-        <v>-9.029999999999999</v>
+        <v>-60.23</v>
       </c>
       <c r="D136" s="6">
-        <v>-60.23</v>
+        <v>-42.33</v>
       </c>
       <c r="E136" s="8">
-        <v>-51.2</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -5242,13 +5215,13 @@
         <v>31</v>
       </c>
       <c r="C137" s="6">
-        <v>-42.62</v>
+        <v>54.03</v>
       </c>
       <c r="D137" s="6">
-        <v>54.03</v>
-      </c>
-      <c r="E137" s="7">
-        <v>96.65000000000001</v>
+        <v>138.52</v>
+      </c>
+      <c r="E137" s="8">
+        <v>84.48999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -5259,13 +5232,13 @@
         <v>31</v>
       </c>
       <c r="C138" s="6">
-        <v>183.92</v>
+        <v>239.24</v>
       </c>
       <c r="D138" s="6">
-        <v>239.24</v>
-      </c>
-      <c r="E138" s="7">
-        <v>55.32</v>
+        <v>1052.77</v>
+      </c>
+      <c r="E138" s="8">
+        <v>813.53</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -5276,13 +5249,13 @@
         <v>31</v>
       </c>
       <c r="C139" s="6">
-        <v>-69.78</v>
+        <v>-91.48</v>
       </c>
       <c r="D139" s="6">
-        <v>-91.48</v>
+        <v>-88.91</v>
       </c>
       <c r="E139" s="8">
-        <v>-21.7</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -5293,13 +5266,13 @@
         <v>31</v>
       </c>
       <c r="C140" s="6">
-        <v>-15.22</v>
+        <v>-39.38</v>
       </c>
       <c r="D140" s="6">
-        <v>-39.38</v>
+        <v>27.62</v>
       </c>
       <c r="E140" s="8">
-        <v>-24.16</v>
+        <v>67</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -5310,13 +5283,13 @@
         <v>31</v>
       </c>
       <c r="C141" s="6">
-        <v>5.06</v>
+        <v>-17.17</v>
       </c>
       <c r="D141" s="6">
-        <v>-17.17</v>
-      </c>
-      <c r="E141" s="8">
-        <v>-22.23</v>
+        <v>-17.74</v>
+      </c>
+      <c r="E141" s="7">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -5327,13 +5300,13 @@
         <v>31</v>
       </c>
       <c r="C142" s="6">
-        <v>-6.02</v>
+        <v>192.78</v>
       </c>
       <c r="D142" s="6">
-        <v>192.78</v>
+        <v>190.56</v>
       </c>
       <c r="E142" s="7">
-        <v>198.8</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -5344,13 +5317,13 @@
         <v>31</v>
       </c>
       <c r="C143" s="6">
-        <v>-11.72</v>
+        <v>-33.78</v>
       </c>
       <c r="D143" s="6">
-        <v>-33.78</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-22.06</v>
+        <v>-34.36</v>
+      </c>
+      <c r="E143" s="7">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -5361,13 +5334,13 @@
         <v>31</v>
       </c>
       <c r="C144" s="6">
-        <v>-41.64</v>
+        <v>-18.2</v>
       </c>
       <c r="D144" s="6">
-        <v>-18.2</v>
+        <v>-38.54</v>
       </c>
       <c r="E144" s="7">
-        <v>23.44</v>
+        <v>-20.34</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -5378,13 +5351,13 @@
         <v>31</v>
       </c>
       <c r="C145" s="6">
-        <v>354.72</v>
+        <v>394.92</v>
       </c>
       <c r="D145" s="6">
-        <v>394.92</v>
-      </c>
-      <c r="E145" s="7">
-        <v>40.2</v>
+        <v>1347.09</v>
+      </c>
+      <c r="E145" s="8">
+        <v>952.17</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -5395,13 +5368,13 @@
         <v>31</v>
       </c>
       <c r="C146" s="6">
-        <v>-70.31999999999999</v>
+        <v>-73.58</v>
       </c>
       <c r="D146" s="6">
-        <v>-73.58</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-3.26</v>
+        <v>-84.43000000000001</v>
+      </c>
+      <c r="E146" s="7">
+        <v>-10.85</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -5412,19 +5385,19 @@
         <v>31</v>
       </c>
       <c r="C147" s="6">
-        <v>-61.52</v>
+        <v>-35.2</v>
       </c>
       <c r="D147" s="6">
-        <v>-35.2</v>
-      </c>
-      <c r="E147" s="7">
-        <v>26.32</v>
+        <v>-6.98</v>
+      </c>
+      <c r="E147" s="8">
+        <v>28.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5448,28 +5421,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5483,22 +5456,22 @@
         <v>16</v>
       </c>
       <c r="D2" s="11">
-        <v>45.9</v>
+        <v>48.3</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.2</v>
+        <v>-2</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.199999999999999</v>
+        <v>-7</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
       </c>
       <c r="I2" s="11">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5632,34 +5605,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3202</v>
+        <v>0.3171</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2673</v>
+        <v>0.2692</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2065</v>
+        <v>0.2092</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1237</v>
+        <v>0.1192</v>
       </c>
       <c r="E2" s="14">
-        <v>0.09609999999999999</v>
+        <v>0.1027</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0843</v>
+        <v>0.0803</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0548</v>
+        <v>0.0771</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0404</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0336</v>
+        <v>0.0392</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0023</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5684,22 +5657,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>-0.0406</v>
+        <v>-0.0429</v>
       </c>
       <c r="B4" s="14">
-        <v>-0.066</v>
+        <v>-0.0612</v>
       </c>
       <c r="C4" s="14">
-        <v>-0.0759</v>
+        <v>-0.0728</v>
       </c>
       <c r="D4" s="14">
-        <v>-0.0774</v>
+        <v>-0.08539999999999999</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.09380000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.1003</v>
+        <v>-0.09429999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="91">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,67 +214,46 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-3.6% → -1.4%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-3.6%</t>
-  </si>
-  <si>
-    <t>-1.4%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>41.9 → 61.2</t>
+    <t>47.0 → 55.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>41.9</t>
-  </si>
-  <si>
-    <t>61.2</t>
+    <t>47.0</t>
+  </si>
+  <si>
+    <t>55.6</t>
   </si>
   <si>
     <t>RSI Overbought Entry</t>
   </si>
   <si>
-    <t>67.6 → 70.2</t>
+    <t>67.3 → 73.5</t>
   </si>
   <si>
     <t>⚠️ CAUTION</t>
   </si>
   <si>
-    <t>67.6</t>
-  </si>
-  <si>
-    <t>70.2</t>
-  </si>
-  <si>
-    <t>51.1 → 47.0</t>
+    <t>67.3</t>
+  </si>
+  <si>
+    <t>73.5</t>
+  </si>
+  <si>
+    <t>52.1 → 47.6</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>47.0</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>47.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -881,7 +860,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -1014,58 +993,58 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>741.45</v>
+        <v>772.1</v>
       </c>
       <c r="D2">
-        <v>2.21</v>
+        <v>4.13</v>
       </c>
       <c r="E2">
-        <v>752.3</v>
+        <v>772.1</v>
       </c>
       <c r="F2">
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-1.44</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>29.86</v>
+        <v>35.23</v>
       </c>
       <c r="I2">
-        <v>4.19</v>
+        <v>7.89</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>8.23</v>
       </c>
       <c r="K2">
-        <v>1.37</v>
+        <v>6.07</v>
       </c>
       <c r="L2">
-        <v>0.8</v>
+        <v>6.34</v>
       </c>
       <c r="M2">
-        <v>27.99</v>
+        <v>29.01</v>
       </c>
       <c r="N2">
         <v>93</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>723.63</v>
+        <v>734.92</v>
       </c>
       <c r="Q2">
-        <v>726.7</v>
+        <v>728.98</v>
       </c>
       <c r="R2">
-        <v>725.02</v>
+        <v>725.64</v>
       </c>
       <c r="S2">
-        <v>687.86</v>
+        <v>688.01</v>
       </c>
       <c r="T2">
-        <v>7.79</v>
+        <v>12.22</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1080,43 +1059,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>57.34</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="Z2">
-        <v>0.39</v>
+        <v>4.09</v>
       </c>
       <c r="AA2">
-        <v>-0.6</v>
+        <v>0.34</v>
       </c>
       <c r="AB2">
-        <v>0.99</v>
+        <v>3.75</v>
       </c>
       <c r="AC2">
-        <v>71.36</v>
+        <v>89.12</v>
       </c>
       <c r="AD2">
-        <v>45.96</v>
+        <v>67.31</v>
       </c>
       <c r="AE2">
-        <v>16.58</v>
+        <v>17.87</v>
       </c>
       <c r="AF2">
-        <v>47.13</v>
+        <v>164.5</v>
       </c>
       <c r="AG2">
-        <v>747.98</v>
+        <v>758.38</v>
       </c>
       <c r="AH2">
-        <v>705.42</v>
+        <v>699.5700000000001</v>
       </c>
       <c r="AI2">
-        <v>700.95</v>
+        <v>706.63</v>
       </c>
       <c r="AJ2" t="s">
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>17.76</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1127,10 +1106,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>831.4</v>
+        <v>824.55</v>
       </c>
       <c r="D3">
-        <v>-1.54</v>
+        <v>-0.82</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1139,46 +1118,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-23.13</v>
+        <v>-23.76</v>
       </c>
       <c r="H3">
-        <v>64.52</v>
+        <v>63.16</v>
       </c>
       <c r="I3">
-        <v>-3.88</v>
+        <v>-3.37</v>
       </c>
       <c r="J3">
-        <v>-10.05</v>
+        <v>-12.1</v>
       </c>
       <c r="K3">
-        <v>-3.98</v>
+        <v>-4.91</v>
       </c>
       <c r="L3">
-        <v>-5.16</v>
+        <v>-5.28</v>
       </c>
       <c r="M3">
-        <v>-1.9</v>
+        <v>-2.06</v>
       </c>
       <c r="N3">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P3">
-        <v>846.8099999999999</v>
+        <v>841.05</v>
       </c>
       <c r="Q3">
-        <v>921.6</v>
+        <v>914.5700000000001</v>
       </c>
       <c r="R3">
-        <v>942.77</v>
+        <v>939.36</v>
       </c>
       <c r="S3">
-        <v>771.6799999999999</v>
+        <v>772.16</v>
       </c>
       <c r="T3">
-        <v>7.74</v>
+        <v>6.79</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1193,16 +1172,16 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>33.94</v>
+        <v>33</v>
       </c>
       <c r="Z3">
-        <v>-29.42</v>
+        <v>-31.49</v>
       </c>
       <c r="AA3">
-        <v>-19.19</v>
+        <v>-21.65</v>
       </c>
       <c r="AB3">
-        <v>-10.23</v>
+        <v>-9.84</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1211,25 +1190,25 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>38.63</v>
+        <v>37.08</v>
       </c>
       <c r="AF3">
-        <v>-56.62</v>
+        <v>-56.86</v>
       </c>
       <c r="AG3">
-        <v>1046.7</v>
+        <v>1045.04</v>
       </c>
       <c r="AH3">
-        <v>796.5</v>
+        <v>784.09</v>
       </c>
       <c r="AI3">
-        <v>957.62</v>
+        <v>940.6900000000001</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>39.34</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1240,10 +1219,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>201.01</v>
+        <v>204.93</v>
       </c>
       <c r="D4">
-        <v>-0.87</v>
+        <v>1.95</v>
       </c>
       <c r="E4">
         <v>291.61</v>
@@ -1252,46 +1231,46 @@
         <v>195.76</v>
       </c>
       <c r="G4">
-        <v>-31.07</v>
+        <v>-29.72</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>4.68</v>
       </c>
       <c r="I4">
-        <v>2.68</v>
+        <v>3.47</v>
       </c>
       <c r="J4">
-        <v>0.09</v>
+        <v>1.13</v>
       </c>
       <c r="K4">
-        <v>-14.8</v>
+        <v>-12.4</v>
       </c>
       <c r="L4">
-        <v>-32.71</v>
+        <v>-29.58</v>
       </c>
       <c r="M4">
-        <v>-7.77</v>
+        <v>-7.41</v>
       </c>
       <c r="N4">
         <v>32</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>200.4</v>
+        <v>201.77</v>
       </c>
       <c r="Q4">
-        <v>200.47</v>
+        <v>200.51</v>
       </c>
       <c r="R4">
-        <v>206</v>
+        <v>205.78</v>
       </c>
       <c r="S4">
-        <v>237.15</v>
+        <v>236.79</v>
       </c>
       <c r="T4">
-        <v>-15.24</v>
+        <v>-13.46</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
@@ -1306,34 +1285,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.95</v>
+        <v>55.61</v>
       </c>
       <c r="Z4">
-        <v>-1.77</v>
+        <v>-1.27</v>
       </c>
       <c r="AA4">
-        <v>-2.5</v>
+        <v>-2.25</v>
       </c>
       <c r="AB4">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="AC4">
-        <v>94.01000000000001</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="AD4">
-        <v>96.7</v>
+        <v>96</v>
       </c>
       <c r="AE4">
-        <v>4.52</v>
+        <v>4.72</v>
       </c>
       <c r="AF4">
-        <v>-47.86</v>
+        <v>-18.98</v>
       </c>
       <c r="AG4">
-        <v>204.62</v>
+        <v>204.82</v>
       </c>
       <c r="AH4">
-        <v>196.32</v>
+        <v>196.2</v>
       </c>
       <c r="AI4">
         <v>207.87</v>
@@ -1342,7 +1321,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>32.55</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1353,10 +1332,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>628.35</v>
+        <v>633.15</v>
       </c>
       <c r="D5">
-        <v>-0.19</v>
+        <v>0.76</v>
       </c>
       <c r="E5">
         <v>907</v>
@@ -1365,46 +1344,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-30.72</v>
+        <v>-30.19</v>
       </c>
       <c r="H5">
-        <v>9.390000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="I5">
-        <v>5.97</v>
+        <v>7.36</v>
       </c>
       <c r="J5">
-        <v>-14.5</v>
+        <v>-13.48</v>
       </c>
       <c r="K5">
-        <v>-9.56</v>
+        <v>-9.35</v>
       </c>
       <c r="L5">
-        <v>-29.35</v>
+        <v>-29.4</v>
       </c>
       <c r="M5">
-        <v>-9.220000000000001</v>
+        <v>-9.08</v>
       </c>
       <c r="N5">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P5">
-        <v>622.89</v>
+        <v>631.5700000000001</v>
       </c>
       <c r="Q5">
-        <v>641.64</v>
+        <v>634.33</v>
       </c>
       <c r="R5">
-        <v>645.84</v>
+        <v>645.1799999999999</v>
       </c>
       <c r="S5">
-        <v>692.73</v>
+        <v>692.15</v>
       </c>
       <c r="T5">
-        <v>-9.289999999999999</v>
+        <v>-8.52</v>
       </c>
       <c r="U5" t="s">
         <v>55</v>
@@ -1419,34 +1398,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>47.85</v>
+        <v>49.28</v>
       </c>
       <c r="Z5">
-        <v>-9.74</v>
+        <v>-8.4</v>
       </c>
       <c r="AA5">
-        <v>-10.45</v>
+        <v>-10.04</v>
       </c>
       <c r="AB5">
-        <v>0.71</v>
+        <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>85.17</v>
+        <v>89.16</v>
       </c>
       <c r="AD5">
-        <v>76.63</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="AE5">
-        <v>26.36</v>
+        <v>25.39</v>
       </c>
       <c r="AF5">
-        <v>-77.69</v>
+        <v>-71.86</v>
       </c>
       <c r="AG5">
-        <v>729.9</v>
+        <v>694.25</v>
       </c>
       <c r="AH5">
-        <v>553.38</v>
+        <v>574.42</v>
       </c>
       <c r="AI5">
         <v>676.63</v>
@@ -1455,7 +1434,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>16.17</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1466,10 +1445,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1763.7</v>
+        <v>1742.8</v>
       </c>
       <c r="D6">
-        <v>6.32</v>
+        <v>-1.19</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1478,46 +1457,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-14.45</v>
+        <v>-15.47</v>
       </c>
       <c r="H6">
-        <v>30.85</v>
+        <v>29.3</v>
       </c>
       <c r="I6">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="J6">
-        <v>0.89</v>
+        <v>-3.14</v>
       </c>
       <c r="K6">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="L6">
-        <v>-5.69</v>
+        <v>-3.08</v>
       </c>
       <c r="M6">
-        <v>5.1</v>
+        <v>4.84</v>
       </c>
       <c r="N6">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>1682.88</v>
+        <v>1700.1</v>
       </c>
       <c r="Q6">
-        <v>1689.67</v>
+        <v>1687.23</v>
       </c>
       <c r="R6">
-        <v>1710.08</v>
+        <v>1709.98</v>
       </c>
       <c r="S6">
-        <v>1700.44</v>
+        <v>1700.16</v>
       </c>
       <c r="T6">
-        <v>3.72</v>
+        <v>2.51</v>
       </c>
       <c r="U6" t="s">
         <v>55</v>
@@ -1532,34 +1511,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>61.25</v>
+        <v>57.16</v>
       </c>
       <c r="Z6">
-        <v>-9.890000000000001</v>
+        <v>-4.72</v>
       </c>
       <c r="AA6">
-        <v>-16.37</v>
+        <v>-14.04</v>
       </c>
       <c r="AB6">
-        <v>6.48</v>
+        <v>9.32</v>
       </c>
       <c r="AC6">
-        <v>88.05</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AD6">
-        <v>77.87</v>
+        <v>82.77</v>
       </c>
       <c r="AE6">
-        <v>60.92</v>
+        <v>61</v>
       </c>
       <c r="AF6">
-        <v>2027.45</v>
+        <v>146.06</v>
       </c>
       <c r="AG6">
-        <v>1775.33</v>
+        <v>1762.86</v>
       </c>
       <c r="AH6">
-        <v>1604.02</v>
+        <v>1611.61</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1568,7 +1547,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>29.81</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1579,10 +1558,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>991.45</v>
+        <v>978.9</v>
       </c>
       <c r="D7">
-        <v>0.36</v>
+        <v>-1.27</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1591,46 +1570,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-21.33</v>
+        <v>-22.33</v>
       </c>
       <c r="H7">
-        <v>4.42</v>
+        <v>3.1</v>
       </c>
       <c r="I7">
-        <v>4.15</v>
+        <v>2.5</v>
       </c>
       <c r="J7">
-        <v>0.54</v>
+        <v>-2.12</v>
       </c>
       <c r="K7">
-        <v>-8.92</v>
+        <v>-10.08</v>
       </c>
       <c r="L7">
-        <v>-11.24</v>
+        <v>-11.62</v>
       </c>
       <c r="M7">
-        <v>4.14</v>
+        <v>3.87</v>
       </c>
       <c r="N7">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O7">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>970.63</v>
+        <v>975.41</v>
       </c>
       <c r="Q7">
-        <v>974.79</v>
+        <v>973.05</v>
       </c>
       <c r="R7">
-        <v>1017.19</v>
+        <v>1014.84</v>
       </c>
       <c r="S7">
-        <v>1099.9</v>
+        <v>1098.87</v>
       </c>
       <c r="T7">
-        <v>-9.859999999999999</v>
+        <v>-10.92</v>
       </c>
       <c r="U7" t="s">
         <v>55</v>
@@ -1645,34 +1624,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>52.12</v>
+        <v>47.64</v>
       </c>
       <c r="Z7">
-        <v>-12.22</v>
+        <v>-10.8</v>
       </c>
       <c r="AA7">
-        <v>-17.59</v>
+        <v>-16.23</v>
       </c>
       <c r="AB7">
-        <v>5.36</v>
+        <v>5.43</v>
       </c>
       <c r="AC7">
-        <v>92.31999999999999</v>
+        <v>93.19</v>
       </c>
       <c r="AD7">
-        <v>81.67</v>
+        <v>89.56</v>
       </c>
       <c r="AE7">
-        <v>19.2</v>
+        <v>19.41</v>
       </c>
       <c r="AF7">
-        <v>68.81999999999999</v>
+        <v>7.18</v>
       </c>
       <c r="AG7">
-        <v>1012.76</v>
+        <v>1006.42</v>
       </c>
       <c r="AH7">
-        <v>936.8099999999999</v>
+        <v>939.67</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1681,7 +1660,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>41.14</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1692,10 +1671,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3700</v>
+        <v>3850.1</v>
       </c>
       <c r="D8">
-        <v>2.12</v>
+        <v>4.06</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1704,46 +1683,46 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-35.65</v>
+        <v>-33.04</v>
       </c>
       <c r="H8">
-        <v>23.5</v>
+        <v>28.51</v>
       </c>
       <c r="I8">
-        <v>23.5</v>
+        <v>23.01</v>
       </c>
       <c r="J8">
-        <v>7.56</v>
+        <v>14.14</v>
       </c>
       <c r="K8">
-        <v>4.58</v>
+        <v>9.9</v>
       </c>
       <c r="L8">
-        <v>-30.35</v>
+        <v>-26.77</v>
       </c>
       <c r="M8">
-        <v>-9.23</v>
+        <v>-8.5</v>
       </c>
       <c r="N8">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O8">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="P8">
-        <v>3427.36</v>
+        <v>3571.38</v>
       </c>
       <c r="Q8">
-        <v>3236.79</v>
+        <v>3260.21</v>
       </c>
       <c r="R8">
-        <v>3471.16</v>
+        <v>3473.16</v>
       </c>
       <c r="S8">
-        <v>4143.83</v>
+        <v>4136.97</v>
       </c>
       <c r="T8">
-        <v>-10.71</v>
+        <v>-6.93</v>
       </c>
       <c r="U8" t="s">
         <v>55</v>
@@ -1758,16 +1737,16 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>70.18000000000001</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="Z8">
-        <v>1.38</v>
+        <v>42.52</v>
       </c>
       <c r="AA8">
-        <v>-75.56999999999999</v>
+        <v>-51.95</v>
       </c>
       <c r="AB8">
-        <v>76.95</v>
+        <v>94.47</v>
       </c>
       <c r="AC8">
         <v>100</v>
@@ -1776,25 +1755,25 @@
         <v>100</v>
       </c>
       <c r="AE8">
-        <v>114.25</v>
+        <v>118.42</v>
       </c>
       <c r="AF8">
-        <v>110.46</v>
+        <v>135.41</v>
       </c>
       <c r="AG8">
-        <v>3594.41</v>
+        <v>3707.81</v>
       </c>
       <c r="AH8">
-        <v>2879.18</v>
+        <v>2812.61</v>
       </c>
       <c r="AI8">
-        <v>3332.71</v>
+        <v>3413.19</v>
       </c>
       <c r="AJ8" t="s">
         <v>56</v>
       </c>
       <c r="AK8">
-        <v>53.96</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1805,10 +1784,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>610.95</v>
+        <v>613.55</v>
       </c>
       <c r="D9">
-        <v>-0.88</v>
+        <v>0.43</v>
       </c>
       <c r="E9">
         <v>1029.69</v>
@@ -1817,46 +1796,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-40.67</v>
+        <v>-40.41</v>
       </c>
       <c r="H9">
-        <v>13.48</v>
+        <v>13.96</v>
       </c>
       <c r="I9">
-        <v>0.27</v>
+        <v>2.39</v>
       </c>
       <c r="J9">
-        <v>-14.95</v>
+        <v>-10.03</v>
       </c>
       <c r="K9">
-        <v>-8.24</v>
+        <v>-7.36</v>
       </c>
       <c r="L9">
-        <v>-33.93</v>
+        <v>-37.84</v>
       </c>
       <c r="M9">
-        <v>31.58</v>
+        <v>31.67</v>
       </c>
       <c r="N9">
         <v>19</v>
       </c>
       <c r="O9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P9">
-        <v>613.54</v>
+        <v>616.4</v>
       </c>
       <c r="Q9">
-        <v>640.59</v>
+        <v>635.3</v>
       </c>
       <c r="R9">
-        <v>649</v>
+        <v>647.87</v>
       </c>
       <c r="S9">
-        <v>656.6799999999999</v>
+        <v>656.27</v>
       </c>
       <c r="T9">
-        <v>-6.96</v>
+        <v>-6.51</v>
       </c>
       <c r="U9" t="s">
         <v>55</v>
@@ -1871,34 +1850,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>40.81</v>
+        <v>41.97</v>
       </c>
       <c r="Z9">
-        <v>-12.29</v>
+        <v>-12.04</v>
       </c>
       <c r="AA9">
-        <v>-10.28</v>
+        <v>-10.63</v>
       </c>
       <c r="AB9">
-        <v>-2.01</v>
+        <v>-1.41</v>
       </c>
       <c r="AC9">
-        <v>52.06</v>
+        <v>58.53</v>
       </c>
       <c r="AD9">
-        <v>44.13</v>
+        <v>53.34</v>
       </c>
       <c r="AE9">
-        <v>19.59</v>
+        <v>19.13</v>
       </c>
       <c r="AF9">
-        <v>-91.70999999999999</v>
+        <v>-75.52</v>
       </c>
       <c r="AG9">
-        <v>709.34</v>
+        <v>694.12</v>
       </c>
       <c r="AH9">
-        <v>571.84</v>
+        <v>576.49</v>
       </c>
       <c r="AI9">
         <v>665.02</v>
@@ -1907,7 +1886,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>11.68</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1918,10 +1897,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>349.8</v>
+        <v>353.85</v>
       </c>
       <c r="D10">
-        <v>-0.91</v>
+        <v>1.16</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1930,46 +1909,46 @@
         <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-24.25</v>
+        <v>-23.38</v>
       </c>
       <c r="H10">
-        <v>4.22</v>
+        <v>5.42</v>
       </c>
       <c r="I10">
-        <v>4.22</v>
+        <v>3.42</v>
       </c>
       <c r="J10">
-        <v>-3.64</v>
+        <v>-1.82</v>
       </c>
       <c r="K10">
-        <v>-7.24</v>
+        <v>-6.2</v>
       </c>
       <c r="L10">
-        <v>-10.33</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M10">
-        <v>6.94</v>
+        <v>7.18</v>
       </c>
       <c r="N10">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P10">
-        <v>346.73</v>
+        <v>349.07</v>
       </c>
       <c r="Q10">
-        <v>356.28</v>
+        <v>355.52</v>
       </c>
       <c r="R10">
-        <v>364.57</v>
+        <v>363.99</v>
       </c>
       <c r="S10">
-        <v>385.11</v>
+        <v>385</v>
       </c>
       <c r="T10">
-        <v>-9.17</v>
+        <v>-8.09</v>
       </c>
       <c r="U10" t="s">
         <v>55</v>
@@ -1984,34 +1963,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>44.11</v>
+        <v>48.04</v>
       </c>
       <c r="Z10">
-        <v>-5.61</v>
+        <v>-4.9</v>
       </c>
       <c r="AA10">
-        <v>-5.47</v>
+        <v>-5.35</v>
       </c>
       <c r="AB10">
-        <v>-0.15</v>
+        <v>0.45</v>
       </c>
       <c r="AC10">
-        <v>70.2</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="AD10">
-        <v>56.46</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AE10">
-        <v>7.54</v>
+        <v>7.46</v>
       </c>
       <c r="AF10">
-        <v>-8.31</v>
+        <v>-13.57</v>
       </c>
       <c r="AG10">
-        <v>378.25</v>
+        <v>376.67</v>
       </c>
       <c r="AH10">
-        <v>334.31</v>
+        <v>334.37</v>
       </c>
       <c r="AI10">
         <v>362.14</v>
@@ -2020,7 +1999,7 @@
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>32.59</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2031,10 +2010,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>176.4</v>
+        <v>175.5</v>
       </c>
       <c r="D11">
-        <v>1.09</v>
+        <v>-0.51</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2043,46 +2022,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-18.58</v>
+        <v>-19</v>
       </c>
       <c r="H11">
-        <v>12.06</v>
+        <v>11.49</v>
       </c>
       <c r="I11">
-        <v>2.58</v>
+        <v>0.98</v>
       </c>
       <c r="J11">
-        <v>-3.95</v>
+        <v>-4.1</v>
       </c>
       <c r="K11">
-        <v>-4.9</v>
+        <v>-5.59</v>
       </c>
       <c r="L11">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="M11">
-        <v>7.72</v>
+        <v>7.61</v>
       </c>
       <c r="N11">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O11">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P11">
-        <v>174.39</v>
+        <v>174.73</v>
       </c>
       <c r="Q11">
-        <v>181.05</v>
+        <v>180.46</v>
       </c>
       <c r="R11">
-        <v>184.01</v>
+        <v>183.66</v>
       </c>
       <c r="S11">
-        <v>192.34</v>
+        <v>192.37</v>
       </c>
       <c r="T11">
-        <v>-8.289999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="U11" t="s">
         <v>55</v>
@@ -2097,34 +2076,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>42.67</v>
+        <v>41.33</v>
       </c>
       <c r="Z11">
-        <v>-3.15</v>
+        <v>-3.05</v>
       </c>
       <c r="AA11">
-        <v>-2.54</v>
+        <v>-2.64</v>
       </c>
       <c r="AB11">
-        <v>-0.61</v>
+        <v>-0.41</v>
       </c>
       <c r="AC11">
-        <v>38.12</v>
+        <v>43.52</v>
       </c>
       <c r="AD11">
-        <v>26.36</v>
+        <v>35.08</v>
       </c>
       <c r="AE11">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="AF11">
-        <v>-26.22</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="AG11">
-        <v>193.4</v>
+        <v>192.68</v>
       </c>
       <c r="AH11">
-        <v>168.69</v>
+        <v>168.23</v>
       </c>
       <c r="AI11">
         <v>186.52</v>
@@ -2133,7 +2112,7 @@
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>32.64</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2144,10 +2123,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2350</v>
+        <v>2465</v>
       </c>
       <c r="D12">
-        <v>1.96</v>
+        <v>4.89</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2156,46 +2135,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-27.06</v>
+        <v>-23.49</v>
       </c>
       <c r="H12">
-        <v>18.53</v>
+        <v>24.33</v>
       </c>
       <c r="I12">
-        <v>13.2</v>
+        <v>14.33</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>12.62</v>
       </c>
       <c r="K12">
-        <v>6.77</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L12">
-        <v>-19.62</v>
+        <v>-15.09</v>
       </c>
       <c r="M12">
-        <v>-5.95</v>
+        <v>-5.04</v>
       </c>
       <c r="N12">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="O12">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P12">
-        <v>2241.04</v>
+        <v>2302.84</v>
       </c>
       <c r="Q12">
-        <v>2129.6</v>
+        <v>2143.35</v>
       </c>
       <c r="R12">
-        <v>2240.58</v>
+        <v>2241.62</v>
       </c>
       <c r="S12">
-        <v>2438.62</v>
+        <v>2435.19</v>
       </c>
       <c r="T12">
-        <v>-3.63</v>
+        <v>1.22</v>
       </c>
       <c r="U12" t="s">
         <v>55</v>
@@ -2207,46 +2186,46 @@
         <v>55</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>67.27</v>
+        <v>73.52</v>
       </c>
       <c r="Z12">
-        <v>8.94</v>
+        <v>30.25</v>
       </c>
       <c r="AA12">
-        <v>-27.04</v>
+        <v>-15.58</v>
       </c>
       <c r="AB12">
-        <v>35.98</v>
+        <v>45.83</v>
       </c>
       <c r="AC12">
         <v>100</v>
       </c>
       <c r="AD12">
-        <v>96.14</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="AE12">
-        <v>70.37</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AF12">
-        <v>97.45999999999999</v>
+        <v>152.82</v>
       </c>
       <c r="AG12">
-        <v>2300.43</v>
+        <v>2369.85</v>
       </c>
       <c r="AH12">
-        <v>1958.76</v>
+        <v>1916.84</v>
       </c>
       <c r="AI12">
-        <v>2149.75</v>
+        <v>2205.31</v>
       </c>
       <c r="AJ12" t="s">
         <v>56</v>
       </c>
       <c r="AK12">
-        <v>45.32</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2257,58 +2236,58 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4455.8</v>
+        <v>4444.8</v>
       </c>
       <c r="D13">
-        <v>0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
       </c>
       <c r="F13">
-        <v>3533.6</v>
+        <v>3537.4</v>
       </c>
       <c r="G13">
-        <v>-13.8</v>
+        <v>-14.01</v>
       </c>
       <c r="H13">
-        <v>26.1</v>
+        <v>25.65</v>
       </c>
       <c r="I13">
-        <v>2.21</v>
+        <v>0.79</v>
       </c>
       <c r="J13">
-        <v>-8.24</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="K13">
-        <v>-3.68</v>
+        <v>-4.17</v>
       </c>
       <c r="L13">
-        <v>26.16</v>
+        <v>25.79</v>
       </c>
       <c r="M13">
-        <v>11.79</v>
+        <v>11.72</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P13">
-        <v>4439.36</v>
+        <v>4446.32</v>
       </c>
       <c r="Q13">
-        <v>4635</v>
+        <v>4615.19</v>
       </c>
       <c r="R13">
-        <v>4879.66</v>
+        <v>4870.31</v>
       </c>
       <c r="S13">
-        <v>4432</v>
+        <v>4434.31</v>
       </c>
       <c r="T13">
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2323,34 +2302,34 @@
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>35.56</v>
+        <v>35.01</v>
       </c>
       <c r="Z13">
-        <v>-135.3</v>
+        <v>-131.08</v>
       </c>
       <c r="AA13">
-        <v>-123.66</v>
+        <v>-125.15</v>
       </c>
       <c r="AB13">
-        <v>-11.64</v>
+        <v>-5.93</v>
       </c>
       <c r="AC13">
-        <v>51.64</v>
+        <v>53.81</v>
       </c>
       <c r="AD13">
-        <v>41.12</v>
+        <v>48.61</v>
       </c>
       <c r="AE13">
-        <v>93.19</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="AF13">
-        <v>-37.3</v>
+        <v>-32.03</v>
       </c>
       <c r="AG13">
-        <v>5038.98</v>
+        <v>5015.47</v>
       </c>
       <c r="AH13">
-        <v>4231.02</v>
+        <v>4214.91</v>
       </c>
       <c r="AI13">
         <v>4684.57</v>
@@ -2359,7 +2338,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>56.58</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2370,10 +2349,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2949.7</v>
+        <v>2958.7</v>
       </c>
       <c r="D14">
-        <v>-0.72</v>
+        <v>0.31</v>
       </c>
       <c r="E14">
         <v>4807.3</v>
@@ -2382,46 +2361,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-38.64</v>
+        <v>-38.45</v>
       </c>
       <c r="H14">
-        <v>34.45</v>
+        <v>34.86</v>
       </c>
       <c r="I14">
-        <v>2.55</v>
+        <v>1.39</v>
       </c>
       <c r="J14">
-        <v>8.050000000000001</v>
+        <v>6.82</v>
       </c>
       <c r="K14">
-        <v>3.13</v>
+        <v>4.09</v>
       </c>
       <c r="L14">
-        <v>-37.03</v>
+        <v>-36.71</v>
       </c>
       <c r="M14">
-        <v>20.79</v>
+        <v>20.85</v>
       </c>
       <c r="N14">
         <v>44</v>
       </c>
       <c r="O14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="P14">
-        <v>2947.94</v>
+        <v>2956.04</v>
       </c>
       <c r="Q14">
-        <v>2790.48</v>
+        <v>2798.97</v>
       </c>
       <c r="R14">
-        <v>2861.64</v>
+        <v>2858.24</v>
       </c>
       <c r="S14">
-        <v>2800.29</v>
+        <v>2793.99</v>
       </c>
       <c r="T14">
-        <v>5.34</v>
+        <v>5.9</v>
       </c>
       <c r="U14" t="s">
         <v>55</v>
@@ -2436,34 +2415,34 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>61.07</v>
+        <v>61.73</v>
       </c>
       <c r="Z14">
-        <v>33.5</v>
+        <v>38.22</v>
       </c>
       <c r="AA14">
-        <v>-2.51</v>
+        <v>5.64</v>
       </c>
       <c r="AB14">
-        <v>36.01</v>
+        <v>32.58</v>
       </c>
       <c r="AC14">
-        <v>94.90000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="AD14">
-        <v>97.44</v>
+        <v>94.92</v>
       </c>
       <c r="AE14">
-        <v>72.59</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="AF14">
-        <v>-25.21</v>
+        <v>-53.65</v>
       </c>
       <c r="AG14">
-        <v>3062.77</v>
+        <v>3081.45</v>
       </c>
       <c r="AH14">
-        <v>2518.19</v>
+        <v>2516.48</v>
       </c>
       <c r="AI14">
         <v>2752.34</v>
@@ -2472,7 +2451,7 @@
         <v>56</v>
       </c>
       <c r="AK14">
-        <v>45.06</v>
+        <v>43.47</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2483,10 +2462,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>220.43</v>
+        <v>232.4</v>
       </c>
       <c r="D15">
-        <v>-4.25</v>
+        <v>5.43</v>
       </c>
       <c r="E15">
         <v>342.75</v>
@@ -2495,46 +2474,46 @@
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-35.69</v>
+        <v>-32.2</v>
       </c>
       <c r="H15">
-        <v>14.94</v>
+        <v>21.18</v>
       </c>
       <c r="I15">
-        <v>14.94</v>
+        <v>7.13</v>
       </c>
       <c r="J15">
-        <v>3.49</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K15">
-        <v>-12.62</v>
+        <v>-3.88</v>
       </c>
       <c r="L15">
-        <v>-36.95</v>
+        <v>-31.26</v>
       </c>
       <c r="M15">
-        <v>7.74</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N15">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O15">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="P15">
-        <v>222.06</v>
+        <v>225.15</v>
       </c>
       <c r="Q15">
-        <v>210.27</v>
+        <v>210.91</v>
       </c>
       <c r="R15">
-        <v>221.35</v>
+        <v>221.41</v>
       </c>
       <c r="S15">
-        <v>244.83</v>
+        <v>244.51</v>
       </c>
       <c r="T15">
-        <v>-9.960000000000001</v>
+        <v>-4.95</v>
       </c>
       <c r="U15" t="s">
         <v>55</v>
@@ -2549,34 +2528,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>53.31</v>
+        <v>58.93</v>
       </c>
       <c r="Z15">
-        <v>-0.86</v>
+        <v>0.7</v>
       </c>
       <c r="AA15">
-        <v>-4.23</v>
+        <v>-3.25</v>
       </c>
       <c r="AB15">
-        <v>3.37</v>
+        <v>3.95</v>
       </c>
       <c r="AC15">
-        <v>83.95</v>
+        <v>90.42</v>
       </c>
       <c r="AD15">
-        <v>88.72</v>
+        <v>88.28</v>
       </c>
       <c r="AE15">
-        <v>12.93</v>
+        <v>13.25</v>
       </c>
       <c r="AF15">
-        <v>-32.58</v>
+        <v>111.71</v>
       </c>
       <c r="AG15">
-        <v>233.83</v>
+        <v>236.18</v>
       </c>
       <c r="AH15">
-        <v>186.71</v>
+        <v>185.64</v>
       </c>
       <c r="AI15">
         <v>197.45</v>
@@ -2585,7 +2564,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>46.4</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2596,37 +2575,37 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>33.46</v>
+        <v>33.55</v>
       </c>
       <c r="D16">
-        <v>-1.36</v>
+        <v>0.27</v>
       </c>
       <c r="E16">
-        <v>57.12</v>
+        <v>56.19</v>
       </c>
       <c r="F16">
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-41.42</v>
+        <v>-40.29</v>
       </c>
       <c r="H16">
-        <v>6.7</v>
+        <v>6.98</v>
       </c>
       <c r="I16">
-        <v>1.55</v>
+        <v>2.01</v>
       </c>
       <c r="J16">
-        <v>-7.44</v>
+        <v>-4.74</v>
       </c>
       <c r="K16">
-        <v>-17.77</v>
+        <v>-16.71</v>
       </c>
       <c r="L16">
-        <v>-42.01</v>
+        <v>-41.26</v>
       </c>
       <c r="M16">
-        <v>-9.69</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="N16">
         <v>7</v>
@@ -2635,19 +2614,19 @@
         <v>12</v>
       </c>
       <c r="P16">
-        <v>33.41</v>
+        <v>33.54</v>
       </c>
       <c r="Q16">
-        <v>34.57</v>
+        <v>34.42</v>
       </c>
       <c r="R16">
-        <v>36.49</v>
+        <v>36.37</v>
       </c>
       <c r="S16">
-        <v>40.97</v>
+        <v>40.89</v>
       </c>
       <c r="T16">
-        <v>-18.33</v>
+        <v>-17.95</v>
       </c>
       <c r="U16" t="s">
         <v>55</v>
@@ -2662,34 +2641,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>38.81</v>
+        <v>39.62</v>
       </c>
       <c r="Z16">
-        <v>-0.9399999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="AA16">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="AB16">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AC16">
-        <v>52.05</v>
+        <v>50.87</v>
       </c>
       <c r="AD16">
-        <v>37.51</v>
+        <v>47.78</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>-86.72</v>
+        <v>-85.48</v>
       </c>
       <c r="AG16">
-        <v>36.75</v>
+        <v>36.41</v>
       </c>
       <c r="AH16">
-        <v>32.4</v>
+        <v>32.43</v>
       </c>
       <c r="AI16">
         <v>36.59</v>
@@ -2698,7 +2677,7 @@
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>11.6</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2709,10 +2688,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1052</v>
+        <v>1029.1</v>
       </c>
       <c r="D17">
-        <v>1.17</v>
+        <v>-2.18</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2721,46 +2700,46 @@
         <v>1020</v>
       </c>
       <c r="G17">
-        <v>-32.41</v>
+        <v>-33.88</v>
       </c>
       <c r="H17">
-        <v>3.14</v>
+        <v>0.89</v>
       </c>
       <c r="I17">
-        <v>1.94</v>
+        <v>-0.45</v>
       </c>
       <c r="J17">
-        <v>-7.48</v>
+        <v>-9.01</v>
       </c>
       <c r="K17">
-        <v>-23.43</v>
+        <v>-23.34</v>
       </c>
       <c r="L17">
-        <v>-25.54</v>
+        <v>-25.11</v>
       </c>
       <c r="M17">
-        <v>-4.26</v>
+        <v>-4.67</v>
       </c>
       <c r="N17">
         <v>13</v>
       </c>
       <c r="O17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P17">
-        <v>1037.3</v>
+        <v>1036.38</v>
       </c>
       <c r="Q17">
-        <v>1080.18</v>
+        <v>1074.89</v>
       </c>
       <c r="R17">
-        <v>1163.51</v>
+        <v>1158.09</v>
       </c>
       <c r="S17">
-        <v>1314.91</v>
+        <v>1313.18</v>
       </c>
       <c r="T17">
-        <v>-19.99</v>
+        <v>-21.63</v>
       </c>
       <c r="U17" t="s">
         <v>55</v>
@@ -2775,34 +2754,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>38.7</v>
+        <v>34.72</v>
       </c>
       <c r="Z17">
-        <v>-37.14</v>
+        <v>-36.64</v>
       </c>
       <c r="AA17">
-        <v>-38.64</v>
+        <v>-38.24</v>
       </c>
       <c r="AB17">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AC17">
-        <v>52.61</v>
+        <v>51.46</v>
       </c>
       <c r="AD17">
-        <v>32.78</v>
+        <v>44.51</v>
       </c>
       <c r="AE17">
-        <v>28.92</v>
+        <v>28.89</v>
       </c>
       <c r="AF17">
-        <v>40.48</v>
+        <v>-26.83</v>
       </c>
       <c r="AG17">
-        <v>1160.11</v>
+        <v>1153.54</v>
       </c>
       <c r="AH17">
-        <v>1000.25</v>
+        <v>996.23</v>
       </c>
       <c r="AI17">
         <v>1113.88</v>
@@ -2811,7 +2790,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>55.43</v>
+        <v>54.01</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +2931,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2992,7 +2971,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -3011,1746 +2990,1740 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="D9" s="8">
+        <v>8.23</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4.53</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>89</v>
+      <c r="A10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>-10.05</v>
+      </c>
+      <c r="D10" s="8">
+        <v>-12.1</v>
+      </c>
+      <c r="E10" s="10">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="8">
-        <v>0.96</v>
+        <v>0.09</v>
       </c>
       <c r="D11" s="8">
-        <v>3.7</v>
+        <v>1.13</v>
       </c>
       <c r="E11" s="9">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="8">
-        <v>-10.86</v>
+        <v>-14.5</v>
       </c>
       <c r="D12" s="8">
-        <v>-10.05</v>
+        <v>-13.48</v>
       </c>
       <c r="E12" s="9">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="8">
-        <v>0.39</v>
+        <v>0.89</v>
       </c>
       <c r="D13" s="8">
-        <v>0.09</v>
+        <v>-3.14</v>
       </c>
       <c r="E13" s="10">
-        <v>-0.3</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="8">
-        <v>2.79</v>
+        <v>0.54</v>
       </c>
       <c r="D14" s="8">
-        <v>-14.5</v>
+        <v>-2.12</v>
       </c>
       <c r="E14" s="10">
-        <v>-17.29</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="8">
-        <v>-5.83</v>
+        <v>7.56</v>
       </c>
       <c r="D15" s="8">
-        <v>0.89</v>
+        <v>14.14</v>
       </c>
       <c r="E15" s="9">
-        <v>6.72</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="8">
-        <v>-0.31</v>
+        <v>-14.95</v>
       </c>
       <c r="D16" s="8">
-        <v>0.54</v>
+        <v>-10.03</v>
       </c>
       <c r="E16" s="9">
-        <v>0.85</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="8">
-        <v>7.1</v>
+        <v>-3.64</v>
       </c>
       <c r="D17" s="8">
-        <v>7.56</v>
+        <v>-1.82</v>
       </c>
       <c r="E17" s="9">
-        <v>0.46</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="8">
-        <v>-5.31</v>
+        <v>-3.95</v>
       </c>
       <c r="D18" s="8">
-        <v>-14.95</v>
+        <v>-4.1</v>
       </c>
       <c r="E18" s="10">
-        <v>-9.640000000000001</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="8">
-        <v>-3.19</v>
+        <v>4.4</v>
       </c>
       <c r="D19" s="8">
-        <v>-3.64</v>
-      </c>
-      <c r="E19" s="10">
-        <v>-0.45</v>
+        <v>12.62</v>
+      </c>
+      <c r="E19" s="9">
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="8">
-        <v>-4.65</v>
+        <v>-8.24</v>
       </c>
       <c r="D20" s="8">
-        <v>-3.95</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.7</v>
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E20" s="10">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="8">
-        <v>4.73</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="D21" s="8">
-        <v>4.4</v>
+        <v>6.82</v>
       </c>
       <c r="E21" s="10">
-        <v>-0.33</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="8">
-        <v>-11.29</v>
+        <v>3.49</v>
       </c>
       <c r="D22" s="8">
-        <v>-8.24</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E22" s="9">
-        <v>3.05</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="8">
-        <v>6.02</v>
+        <v>-7.44</v>
       </c>
       <c r="D23" s="8">
-        <v>8.050000000000001</v>
+        <v>-4.74</v>
       </c>
       <c r="E23" s="9">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="8">
-        <v>3.68</v>
+        <v>-7.48</v>
       </c>
       <c r="D24" s="8">
-        <v>3.49</v>
+        <v>-9.01</v>
       </c>
       <c r="E24" s="10">
-        <v>-0.19</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="8">
-        <v>-4.72</v>
+        <v>4.19</v>
       </c>
       <c r="D25" s="8">
-        <v>-7.44</v>
-      </c>
-      <c r="E25" s="10">
-        <v>-2.72</v>
+        <v>7.89</v>
+      </c>
+      <c r="E25" s="9">
+        <v>3.7</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="8">
-        <v>-10.75</v>
+        <v>-3.88</v>
       </c>
       <c r="D26" s="8">
-        <v>-7.48</v>
+        <v>-3.37</v>
       </c>
       <c r="E26" s="9">
-        <v>3.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="8">
-        <v>-0.8100000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="D27" s="8">
-        <v>4.19</v>
+        <v>3.47</v>
       </c>
       <c r="E27" s="9">
-        <v>5</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="8">
-        <v>-7.8</v>
+        <v>5.97</v>
       </c>
       <c r="D28" s="8">
-        <v>-3.88</v>
+        <v>7.36</v>
       </c>
       <c r="E28" s="9">
-        <v>3.92</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="8">
-        <v>1.37</v>
+        <v>5.14</v>
       </c>
       <c r="D29" s="8">
-        <v>2.68</v>
+        <v>5.2</v>
       </c>
       <c r="E29" s="9">
-        <v>1.31</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="8">
-        <v>3.24</v>
+        <v>4.15</v>
       </c>
       <c r="D30" s="8">
-        <v>5.97</v>
-      </c>
-      <c r="E30" s="9">
-        <v>2.73</v>
+        <v>2.5</v>
+      </c>
+      <c r="E30" s="10">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="8">
-        <v>-0.04</v>
+        <v>23.5</v>
       </c>
       <c r="D31" s="8">
-        <v>5.14</v>
-      </c>
-      <c r="E31" s="9">
-        <v>5.18</v>
+        <v>23.01</v>
+      </c>
+      <c r="E31" s="10">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="8">
-        <v>2</v>
+        <v>0.27</v>
       </c>
       <c r="D32" s="8">
-        <v>4.15</v>
+        <v>2.39</v>
       </c>
       <c r="E32" s="9">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="8">
-        <v>17.54</v>
+        <v>4.22</v>
       </c>
       <c r="D33" s="8">
-        <v>23.5</v>
-      </c>
-      <c r="E33" s="9">
-        <v>5.96</v>
+        <v>3.42</v>
+      </c>
+      <c r="E33" s="10">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="8">
-        <v>0.17</v>
+        <v>2.58</v>
       </c>
       <c r="D34" s="8">
-        <v>0.27</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.1</v>
+        <v>0.98</v>
+      </c>
+      <c r="E34" s="10">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="8">
-        <v>2.27</v>
+        <v>13.2</v>
       </c>
       <c r="D35" s="8">
-        <v>4.22</v>
+        <v>14.33</v>
       </c>
       <c r="E35" s="9">
-        <v>1.95</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="8">
-        <v>-0.65</v>
+        <v>2.21</v>
       </c>
       <c r="D36" s="8">
-        <v>2.58</v>
-      </c>
-      <c r="E36" s="9">
-        <v>3.23</v>
+        <v>0.79</v>
+      </c>
+      <c r="E36" s="10">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="8">
-        <v>10.8</v>
+        <v>2.55</v>
       </c>
       <c r="D37" s="8">
-        <v>13.2</v>
-      </c>
-      <c r="E37" s="9">
-        <v>2.4</v>
+        <v>1.39</v>
+      </c>
+      <c r="E37" s="10">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="8">
-        <v>1.53</v>
+        <v>14.94</v>
       </c>
       <c r="D38" s="8">
-        <v>2.21</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.68</v>
+        <v>7.13</v>
+      </c>
+      <c r="E38" s="10">
+        <v>-7.81</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="8">
-        <v>2.79</v>
+        <v>1.55</v>
       </c>
       <c r="D39" s="8">
-        <v>2.55</v>
-      </c>
-      <c r="E39" s="10">
-        <v>-0.24</v>
+        <v>2.01</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.46</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="8">
-        <v>16.26</v>
+        <v>1.94</v>
       </c>
       <c r="D40" s="8">
-        <v>14.94</v>
+        <v>-0.45</v>
       </c>
       <c r="E40" s="10">
-        <v>-1.32</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C41" s="8">
-        <v>-0.26</v>
+        <v>0.8</v>
       </c>
       <c r="D41" s="8">
-        <v>1.55</v>
+        <v>6.34</v>
       </c>
       <c r="E41" s="9">
-        <v>1.81</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C42" s="8">
-        <v>-1.61</v>
+        <v>-5.16</v>
       </c>
       <c r="D42" s="8">
-        <v>1.94</v>
-      </c>
-      <c r="E42" s="9">
-        <v>3.55</v>
+        <v>-5.28</v>
+      </c>
+      <c r="E42" s="10">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="8">
-        <v>-0.92</v>
+        <v>-32.71</v>
       </c>
       <c r="D43" s="8">
-        <v>0.8</v>
+        <v>-29.58</v>
       </c>
       <c r="E43" s="9">
-        <v>1.72</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="8">
-        <v>-3.73</v>
+        <v>-29.35</v>
       </c>
       <c r="D44" s="8">
-        <v>-5.16</v>
+        <v>-29.4</v>
       </c>
       <c r="E44" s="10">
-        <v>-1.43</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="8">
-        <v>-32.32</v>
+        <v>-5.69</v>
       </c>
       <c r="D45" s="8">
-        <v>-32.71</v>
-      </c>
-      <c r="E45" s="10">
-        <v>-0.39</v>
+        <v>-3.08</v>
+      </c>
+      <c r="E45" s="9">
+        <v>2.61</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="8">
-        <v>-29.45</v>
+        <v>-11.24</v>
       </c>
       <c r="D46" s="8">
-        <v>-29.35</v>
-      </c>
-      <c r="E46" s="9">
-        <v>0.1</v>
+        <v>-11.62</v>
+      </c>
+      <c r="E46" s="10">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="8">
-        <v>-2.23</v>
+        <v>-30.35</v>
       </c>
       <c r="D47" s="8">
-        <v>-5.69</v>
-      </c>
-      <c r="E47" s="10">
-        <v>-3.46</v>
+        <v>-26.77</v>
+      </c>
+      <c r="E47" s="9">
+        <v>3.58</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="8">
-        <v>-10.89</v>
+        <v>-33.93</v>
       </c>
       <c r="D48" s="8">
-        <v>-11.24</v>
+        <v>-37.84</v>
       </c>
       <c r="E48" s="10">
-        <v>-0.35</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="8">
-        <v>-33.82</v>
+        <v>-10.33</v>
       </c>
       <c r="D49" s="8">
-        <v>-30.35</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="E49" s="9">
-        <v>3.47</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="8">
-        <v>-31.32</v>
+        <v>3.55</v>
       </c>
       <c r="D50" s="8">
-        <v>-33.93</v>
+        <v>3.52</v>
       </c>
       <c r="E50" s="10">
-        <v>-2.61</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="8">
-        <v>-9.07</v>
+        <v>-19.62</v>
       </c>
       <c r="D51" s="8">
-        <v>-10.33</v>
-      </c>
-      <c r="E51" s="10">
-        <v>-1.26</v>
+        <v>-15.09</v>
+      </c>
+      <c r="E51" s="9">
+        <v>4.53</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="8">
-        <v>0.9399999999999999</v>
+        <v>26.16</v>
       </c>
       <c r="D52" s="8">
-        <v>3.55</v>
-      </c>
-      <c r="E52" s="9">
-        <v>2.61</v>
+        <v>25.79</v>
+      </c>
+      <c r="E52" s="10">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="8">
-        <v>-22.02</v>
+        <v>-37.03</v>
       </c>
       <c r="D53" s="8">
-        <v>-19.62</v>
+        <v>-36.71</v>
       </c>
       <c r="E53" s="9">
-        <v>2.4</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="8">
-        <v>25.16</v>
+        <v>-36.95</v>
       </c>
       <c r="D54" s="8">
-        <v>26.16</v>
+        <v>-31.26</v>
       </c>
       <c r="E54" s="9">
-        <v>1</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="8">
-        <v>-36.16</v>
+        <v>-42.01</v>
       </c>
       <c r="D55" s="8">
-        <v>-37.03</v>
-      </c>
-      <c r="E55" s="10">
-        <v>-0.87</v>
+        <v>-41.26</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.75</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="8">
-        <v>-34.8</v>
+        <v>-25.54</v>
       </c>
       <c r="D56" s="8">
-        <v>-36.95</v>
-      </c>
-      <c r="E56" s="10">
-        <v>-2.15</v>
+        <v>-25.11</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.43</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" s="8">
-        <v>-39.93</v>
+        <v>1.37</v>
       </c>
       <c r="D57" s="8">
-        <v>-42.01</v>
-      </c>
-      <c r="E57" s="10">
-        <v>-2.08</v>
+        <v>6.07</v>
+      </c>
+      <c r="E57" s="9">
+        <v>4.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58" s="8">
-        <v>-24.52</v>
+        <v>-3.98</v>
       </c>
       <c r="D58" s="8">
-        <v>-25.54</v>
+        <v>-4.91</v>
       </c>
       <c r="E58" s="10">
-        <v>-1.02</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="8">
-        <v>-2.4</v>
+        <v>-14.8</v>
       </c>
       <c r="D59" s="8">
-        <v>1.37</v>
+        <v>-12.4</v>
       </c>
       <c r="E59" s="9">
-        <v>3.77</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="8">
-        <v>-2.1</v>
+        <v>-9.56</v>
       </c>
       <c r="D60" s="8">
-        <v>-3.98</v>
-      </c>
-      <c r="E60" s="10">
-        <v>-1.88</v>
+        <v>-9.35</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0.21</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="8">
-        <v>-14.91</v>
+        <v>-4.14</v>
       </c>
       <c r="D61" s="8">
-        <v>-14.8</v>
+        <v>-4.09</v>
       </c>
       <c r="E61" s="9">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="8">
-        <v>-9.859999999999999</v>
+        <v>-8.92</v>
       </c>
       <c r="D62" s="8">
-        <v>-9.56</v>
-      </c>
-      <c r="E62" s="9">
-        <v>0.3</v>
+        <v>-10.08</v>
+      </c>
+      <c r="E62" s="10">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="8">
-        <v>-10.61</v>
+        <v>4.58</v>
       </c>
       <c r="D63" s="8">
-        <v>-4.14</v>
+        <v>9.9</v>
       </c>
       <c r="E63" s="9">
-        <v>6.47</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="8">
-        <v>-8.99</v>
+        <v>-8.24</v>
       </c>
       <c r="D64" s="8">
-        <v>-8.92</v>
+        <v>-7.36</v>
       </c>
       <c r="E64" s="9">
-        <v>0.07000000000000001</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="8">
-        <v>2.92</v>
+        <v>-7.24</v>
       </c>
       <c r="D65" s="8">
-        <v>4.58</v>
+        <v>-6.2</v>
       </c>
       <c r="E65" s="9">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="8">
-        <v>-8.380000000000001</v>
+        <v>-4.9</v>
       </c>
       <c r="D66" s="8">
-        <v>-8.24</v>
-      </c>
-      <c r="E66" s="9">
-        <v>0.14</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E66" s="10">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="8">
-        <v>-7.32</v>
+        <v>6.77</v>
       </c>
       <c r="D67" s="8">
-        <v>-7.24</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E67" s="9">
-        <v>0.08</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="8">
-        <v>-5.81</v>
+        <v>-3.68</v>
       </c>
       <c r="D68" s="8">
-        <v>-4.9</v>
-      </c>
-      <c r="E68" s="9">
-        <v>0.91</v>
+        <v>-4.17</v>
+      </c>
+      <c r="E68" s="10">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="8">
-        <v>5.29</v>
+        <v>3.13</v>
       </c>
       <c r="D69" s="8">
-        <v>6.77</v>
+        <v>4.09</v>
       </c>
       <c r="E69" s="9">
-        <v>1.48</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="8">
-        <v>-2.96</v>
+        <v>-12.62</v>
       </c>
       <c r="D70" s="8">
-        <v>-3.68</v>
-      </c>
-      <c r="E70" s="10">
-        <v>-0.72</v>
+        <v>-3.88</v>
+      </c>
+      <c r="E70" s="9">
+        <v>8.74</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="8">
-        <v>3.6</v>
+        <v>-17.77</v>
       </c>
       <c r="D71" s="8">
-        <v>3.13</v>
-      </c>
-      <c r="E71" s="10">
-        <v>-0.47</v>
+        <v>-16.71</v>
+      </c>
+      <c r="E71" s="9">
+        <v>1.06</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="8">
-        <v>-9.859999999999999</v>
+        <v>-23.43</v>
       </c>
       <c r="D72" s="8">
-        <v>-12.62</v>
-      </c>
-      <c r="E72" s="10">
-        <v>-2.76</v>
+        <v>-23.34</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C73" s="8">
-        <v>-16.6</v>
+        <v>-1.44</v>
       </c>
       <c r="D73" s="8">
-        <v>-17.77</v>
-      </c>
-      <c r="E73" s="10">
-        <v>-1.17</v>
+        <v>0</v>
+      </c>
+      <c r="E73" s="9">
+        <v>1.44</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C74" s="8">
-        <v>-24.51</v>
+        <v>-23.13</v>
       </c>
       <c r="D74" s="8">
-        <v>-23.43</v>
-      </c>
-      <c r="E74" s="9">
-        <v>1.08</v>
+        <v>-23.76</v>
+      </c>
+      <c r="E74" s="10">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="8">
-        <v>-3.58</v>
+        <v>-31.07</v>
       </c>
       <c r="D75" s="8">
-        <v>-1.44</v>
+        <v>-29.72</v>
       </c>
       <c r="E75" s="9">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="8">
-        <v>-21.92</v>
+        <v>-30.72</v>
       </c>
       <c r="D76" s="8">
-        <v>-23.13</v>
-      </c>
-      <c r="E76" s="10">
-        <v>-1.21</v>
+        <v>-30.19</v>
+      </c>
+      <c r="E76" s="9">
+        <v>0.53</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="8">
-        <v>-32.12</v>
+        <v>-14.45</v>
       </c>
       <c r="D77" s="8">
-        <v>-31.07</v>
-      </c>
-      <c r="E77" s="9">
-        <v>1.05</v>
+        <v>-15.47</v>
+      </c>
+      <c r="E77" s="10">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="8">
-        <v>-30.59</v>
+        <v>-21.33</v>
       </c>
       <c r="D78" s="8">
-        <v>-30.72</v>
+        <v>-22.33</v>
       </c>
       <c r="E78" s="10">
-        <v>-0.13</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="8">
-        <v>-19.54</v>
+        <v>-35.65</v>
       </c>
       <c r="D79" s="8">
-        <v>-14.45</v>
+        <v>-33.04</v>
       </c>
       <c r="E79" s="9">
-        <v>5.09</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="8">
-        <v>-21.62</v>
+        <v>-40.67</v>
       </c>
       <c r="D80" s="8">
-        <v>-21.33</v>
+        <v>-40.41</v>
       </c>
       <c r="E80" s="9">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="8">
-        <v>-36.99</v>
+        <v>-24.25</v>
       </c>
       <c r="D81" s="8">
-        <v>-35.65</v>
+        <v>-23.38</v>
       </c>
       <c r="E81" s="9">
-        <v>1.34</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="8">
-        <v>-40.14</v>
+        <v>-18.58</v>
       </c>
       <c r="D82" s="8">
-        <v>-40.67</v>
+        <v>-19</v>
       </c>
       <c r="E82" s="10">
-        <v>-0.53</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="8">
-        <v>-23.56</v>
+        <v>-27.06</v>
       </c>
       <c r="D83" s="8">
-        <v>-24.25</v>
-      </c>
-      <c r="E83" s="10">
-        <v>-0.6899999999999999</v>
+        <v>-23.49</v>
+      </c>
+      <c r="E83" s="9">
+        <v>3.57</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="8">
-        <v>-19.46</v>
+        <v>-13.8</v>
       </c>
       <c r="D84" s="8">
-        <v>-18.58</v>
-      </c>
-      <c r="E84" s="9">
-        <v>0.88</v>
+        <v>-14.01</v>
+      </c>
+      <c r="E84" s="10">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="8">
-        <v>-28.46</v>
+        <v>-38.64</v>
       </c>
       <c r="D85" s="8">
-        <v>-27.06</v>
+        <v>-38.45</v>
       </c>
       <c r="E85" s="9">
-        <v>1.4</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="8">
-        <v>-14.03</v>
+        <v>-35.69</v>
       </c>
       <c r="D86" s="8">
-        <v>-13.8</v>
+        <v>-32.2</v>
       </c>
       <c r="E86" s="9">
-        <v>0.23</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="8">
-        <v>-38.2</v>
+        <v>-41.42</v>
       </c>
       <c r="D87" s="8">
-        <v>-38.64</v>
-      </c>
-      <c r="E87" s="10">
-        <v>-0.44</v>
+        <v>-40.29</v>
+      </c>
+      <c r="E87" s="9">
+        <v>1.13</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="8">
-        <v>-34.15</v>
+        <v>-32.41</v>
       </c>
       <c r="D88" s="8">
-        <v>-35.69</v>
+        <v>-33.88</v>
       </c>
       <c r="E88" s="10">
-        <v>-1.54</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C89" s="8">
-        <v>-41.21</v>
+        <v>741.45</v>
       </c>
       <c r="D89" s="8">
-        <v>-41.42</v>
-      </c>
-      <c r="E89" s="10">
-        <v>-0.21</v>
+        <v>772.1</v>
+      </c>
+      <c r="E89" s="9">
+        <v>30.65</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C90" s="8">
-        <v>-33.19</v>
+        <v>831.4</v>
       </c>
       <c r="D90" s="8">
-        <v>-32.41</v>
-      </c>
-      <c r="E90" s="9">
-        <v>0.78</v>
+        <v>824.55</v>
+      </c>
+      <c r="E90" s="10">
+        <v>-6.85</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="8">
-        <v>725.4</v>
+        <v>201.01</v>
       </c>
       <c r="D91" s="8">
-        <v>741.45</v>
+        <v>204.93</v>
       </c>
       <c r="E91" s="9">
-        <v>16.05</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="8">
-        <v>844.4</v>
+        <v>628.35</v>
       </c>
       <c r="D92" s="8">
-        <v>831.4</v>
-      </c>
-      <c r="E92" s="10">
-        <v>-13</v>
+        <v>633.15</v>
+      </c>
+      <c r="E92" s="9">
+        <v>4.8</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="8">
-        <v>202.77</v>
+        <v>1763.7</v>
       </c>
       <c r="D93" s="8">
-        <v>201.01</v>
+        <v>1742.8</v>
       </c>
       <c r="E93" s="10">
-        <v>-1.76</v>
+        <v>-20.9</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="8">
-        <v>629.55</v>
+        <v>991.45</v>
       </c>
       <c r="D94" s="8">
-        <v>628.35</v>
+        <v>978.9</v>
       </c>
       <c r="E94" s="10">
-        <v>-1.2</v>
+        <v>-12.55</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="8">
-        <v>1658.9</v>
+        <v>3700</v>
       </c>
       <c r="D95" s="8">
-        <v>1763.7</v>
+        <v>3850.1</v>
       </c>
       <c r="E95" s="9">
-        <v>104.8</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="8">
-        <v>987.9</v>
+        <v>610.95</v>
       </c>
       <c r="D96" s="8">
-        <v>991.45</v>
+        <v>613.55</v>
       </c>
       <c r="E96" s="9">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="8">
-        <v>3623.1</v>
+        <v>349.8</v>
       </c>
       <c r="D97" s="8">
-        <v>3700</v>
+        <v>353.85</v>
       </c>
       <c r="E97" s="9">
-        <v>76.90000000000001</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="8">
-        <v>616.35</v>
+        <v>176.4</v>
       </c>
       <c r="D98" s="8">
-        <v>610.95</v>
+        <v>175.5</v>
       </c>
       <c r="E98" s="10">
-        <v>-5.4</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="8">
-        <v>353</v>
+        <v>2350</v>
       </c>
       <c r="D99" s="8">
-        <v>349.8</v>
-      </c>
-      <c r="E99" s="10">
-        <v>-3.2</v>
+        <v>2465</v>
+      </c>
+      <c r="E99" s="9">
+        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="8">
-        <v>174.49</v>
+        <v>4455.8</v>
       </c>
       <c r="D100" s="8">
-        <v>176.4</v>
-      </c>
-      <c r="E100" s="9">
-        <v>1.91</v>
+        <v>4444.8</v>
+      </c>
+      <c r="E100" s="10">
+        <v>-11</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="8">
-        <v>2304.9</v>
+        <v>2949.7</v>
       </c>
       <c r="D101" s="8">
-        <v>2350</v>
+        <v>2958.7</v>
       </c>
       <c r="E101" s="9">
-        <v>45.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="8">
-        <v>4444</v>
+        <v>220.43</v>
       </c>
       <c r="D102" s="8">
-        <v>4455.8</v>
+        <v>232.4</v>
       </c>
       <c r="E102" s="9">
-        <v>11.8</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="8">
-        <v>2971</v>
+        <v>33.46</v>
       </c>
       <c r="D103" s="8">
-        <v>2949.7</v>
-      </c>
-      <c r="E103" s="10">
-        <v>-21.3</v>
+        <v>33.55</v>
+      </c>
+      <c r="E103" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C104" s="8">
-        <v>230.22</v>
+        <v>1052</v>
       </c>
       <c r="D104" s="8">
-        <v>220.43</v>
+        <v>1029.1</v>
       </c>
       <c r="E104" s="10">
-        <v>-9.789999999999999</v>
+        <v>-22.9</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C105" s="8">
-        <v>33.92</v>
+        <v>68</v>
       </c>
       <c r="D105" s="8">
-        <v>33.46</v>
+        <v>62</v>
       </c>
       <c r="E105" s="10">
-        <v>-0.46</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C106" s="8">
-        <v>1039.8</v>
+        <v>38</v>
       </c>
       <c r="D106" s="8">
-        <v>1052</v>
-      </c>
-      <c r="E106" s="9">
-        <v>12.2</v>
+        <v>26</v>
+      </c>
+      <c r="E106" s="10">
+        <v>-12</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>13</v>
@@ -4759,611 +4732,662 @@
         <v>81</v>
       </c>
       <c r="D107" s="8">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E107" s="10">
-        <v>-13</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="8">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D108" s="8">
-        <v>32</v>
-      </c>
-      <c r="E108" s="9">
-        <v>13</v>
+        <v>50</v>
+      </c>
+      <c r="E108" s="10">
+        <v>-6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="8">
+        <v>50</v>
+      </c>
+      <c r="D109" s="8">
         <v>68</v>
       </c>
-      <c r="D109" s="8">
-        <v>81</v>
-      </c>
       <c r="E109" s="9">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C110" s="8">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="D110" s="8">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="E110" s="10">
-        <v>-13</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C111" s="8">
-        <v>50.84</v>
+        <v>87</v>
       </c>
       <c r="D111" s="8">
-        <v>57.34</v>
-      </c>
-      <c r="E111" s="9">
-        <v>6.5</v>
+        <v>81</v>
+      </c>
+      <c r="E111" s="10">
+        <v>-6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C112" s="8">
-        <v>35.74</v>
+        <v>74</v>
       </c>
       <c r="D112" s="8">
-        <v>33.94</v>
-      </c>
-      <c r="E112" s="10">
-        <v>-1.8</v>
+        <v>87</v>
+      </c>
+      <c r="E112" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C113" s="8">
-        <v>51.11</v>
+        <v>26</v>
       </c>
       <c r="D113" s="8">
-        <v>46.95</v>
-      </c>
-      <c r="E113" s="10">
-        <v>-4.16</v>
+        <v>38</v>
+      </c>
+      <c r="E113" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="8">
-        <v>48.16</v>
+        <v>57.34</v>
       </c>
       <c r="D114" s="8">
-        <v>47.85</v>
-      </c>
-      <c r="E114" s="10">
-        <v>-0.31</v>
+        <v>66.45999999999999</v>
+      </c>
+      <c r="E114" s="9">
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="8">
-        <v>41.88</v>
+        <v>33.94</v>
       </c>
       <c r="D115" s="8">
-        <v>61.25</v>
-      </c>
-      <c r="E115" s="9">
-        <v>19.37</v>
+        <v>33</v>
+      </c>
+      <c r="E115" s="10">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="8">
-        <v>50.91</v>
+        <v>46.95</v>
       </c>
       <c r="D116" s="8">
-        <v>52.12</v>
+        <v>55.61</v>
       </c>
       <c r="E116" s="9">
-        <v>1.21</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="8">
-        <v>67.62</v>
+        <v>47.85</v>
       </c>
       <c r="D117" s="8">
-        <v>70.18000000000001</v>
+        <v>49.28</v>
       </c>
       <c r="E117" s="9">
-        <v>2.56</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="8">
-        <v>42.45</v>
+        <v>61.25</v>
       </c>
       <c r="D118" s="8">
-        <v>40.81</v>
+        <v>57.16</v>
       </c>
       <c r="E118" s="10">
-        <v>-1.64</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="8">
-        <v>46.7</v>
+        <v>52.12</v>
       </c>
       <c r="D119" s="8">
-        <v>44.11</v>
+        <v>47.64</v>
       </c>
       <c r="E119" s="10">
-        <v>-2.59</v>
+        <v>-4.48</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="8">
-        <v>38.77</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="D120" s="8">
-        <v>42.67</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="E120" s="9">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="8">
-        <v>64.2</v>
+        <v>40.81</v>
       </c>
       <c r="D121" s="8">
-        <v>67.27</v>
+        <v>41.97</v>
       </c>
       <c r="E121" s="9">
-        <v>3.07</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="8">
-        <v>34.54</v>
+        <v>44.11</v>
       </c>
       <c r="D122" s="8">
-        <v>35.56</v>
+        <v>48.04</v>
       </c>
       <c r="E122" s="9">
-        <v>1.02</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="8">
-        <v>63.49</v>
+        <v>42.67</v>
       </c>
       <c r="D123" s="8">
-        <v>61.07</v>
+        <v>41.33</v>
       </c>
       <c r="E123" s="10">
-        <v>-2.42</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="8">
-        <v>59.49</v>
+        <v>67.27</v>
       </c>
       <c r="D124" s="8">
-        <v>53.31</v>
-      </c>
-      <c r="E124" s="10">
-        <v>-6.18</v>
+        <v>73.52</v>
+      </c>
+      <c r="E124" s="9">
+        <v>6.25</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="8">
-        <v>41.45</v>
+        <v>35.56</v>
       </c>
       <c r="D125" s="8">
-        <v>38.81</v>
+        <v>35.01</v>
       </c>
       <c r="E125" s="10">
-        <v>-2.64</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C126" s="8">
-        <v>35.02</v>
+        <v>61.07</v>
       </c>
       <c r="D126" s="8">
-        <v>38.7</v>
+        <v>61.73</v>
       </c>
       <c r="E126" s="9">
-        <v>3.68</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C127" s="8">
-        <v>-50.18</v>
+        <v>53.31</v>
       </c>
       <c r="D127" s="8">
-        <v>47.13</v>
+        <v>58.93</v>
       </c>
       <c r="E127" s="9">
-        <v>97.31</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C128" s="8">
-        <v>-73.23999999999999</v>
+        <v>38.81</v>
       </c>
       <c r="D128" s="8">
-        <v>-56.62</v>
+        <v>39.62</v>
       </c>
       <c r="E128" s="9">
-        <v>16.62</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C129" s="8">
-        <v>-24.06</v>
+        <v>38.7</v>
       </c>
       <c r="D129" s="8">
-        <v>-47.86</v>
+        <v>34.72</v>
       </c>
       <c r="E129" s="10">
-        <v>-23.8</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="8">
-        <v>-68.75</v>
+        <v>47.13</v>
       </c>
       <c r="D130" s="8">
-        <v>-77.69</v>
-      </c>
-      <c r="E130" s="10">
-        <v>-8.94</v>
+        <v>164.5</v>
+      </c>
+      <c r="E130" s="9">
+        <v>117.37</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="8">
-        <v>-42.33</v>
+        <v>-56.62</v>
       </c>
       <c r="D131" s="8">
-        <v>2027.45</v>
-      </c>
-      <c r="E131" s="9">
-        <v>2069.78</v>
+        <v>-56.86</v>
+      </c>
+      <c r="E131" s="10">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="8">
-        <v>138.52</v>
+        <v>-47.86</v>
       </c>
       <c r="D132" s="8">
-        <v>68.81999999999999</v>
-      </c>
-      <c r="E132" s="10">
-        <v>-69.7</v>
+        <v>-18.98</v>
+      </c>
+      <c r="E132" s="9">
+        <v>28.88</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="8">
-        <v>1052.77</v>
+        <v>-77.69</v>
       </c>
       <c r="D133" s="8">
-        <v>110.46</v>
-      </c>
-      <c r="E133" s="10">
-        <v>-942.3099999999999</v>
+        <v>-71.86</v>
+      </c>
+      <c r="E133" s="9">
+        <v>5.83</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="8">
-        <v>-88.91</v>
+        <v>2027.45</v>
       </c>
       <c r="D134" s="8">
-        <v>-91.70999999999999</v>
+        <v>146.06</v>
       </c>
       <c r="E134" s="10">
-        <v>-2.8</v>
+        <v>-1881.39</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="8">
-        <v>27.62</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D135" s="8">
-        <v>-8.31</v>
+        <v>7.18</v>
       </c>
       <c r="E135" s="10">
-        <v>-35.93</v>
+        <v>-61.64</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="8">
-        <v>-17.74</v>
+        <v>110.46</v>
       </c>
       <c r="D136" s="8">
-        <v>-26.22</v>
-      </c>
-      <c r="E136" s="10">
-        <v>-8.48</v>
+        <v>135.41</v>
+      </c>
+      <c r="E136" s="9">
+        <v>24.95</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="8">
-        <v>190.56</v>
+        <v>-91.70999999999999</v>
       </c>
       <c r="D137" s="8">
-        <v>97.45999999999999</v>
-      </c>
-      <c r="E137" s="10">
-        <v>-93.09999999999999</v>
+        <v>-75.52</v>
+      </c>
+      <c r="E137" s="9">
+        <v>16.19</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="8">
-        <v>-34.36</v>
+        <v>-8.31</v>
       </c>
       <c r="D138" s="8">
-        <v>-37.3</v>
+        <v>-13.57</v>
       </c>
       <c r="E138" s="10">
-        <v>-2.94</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="8">
-        <v>-38.54</v>
+        <v>-26.22</v>
       </c>
       <c r="D139" s="8">
-        <v>-25.21</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="E139" s="9">
-        <v>13.33</v>
+        <v>108.29</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="8">
-        <v>1347.09</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="D140" s="8">
-        <v>-32.58</v>
-      </c>
-      <c r="E140" s="10">
-        <v>-1379.67</v>
+        <v>152.82</v>
+      </c>
+      <c r="E140" s="9">
+        <v>55.36</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="8">
-        <v>-84.43000000000001</v>
+        <v>-37.3</v>
       </c>
       <c r="D141" s="8">
-        <v>-86.72</v>
-      </c>
-      <c r="E141" s="10">
-        <v>-2.29</v>
+        <v>-32.03</v>
+      </c>
+      <c r="E141" s="9">
+        <v>5.27</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C142" s="8">
-        <v>-6.98</v>
+        <v>-25.21</v>
       </c>
       <c r="D142" s="8">
+        <v>-53.65</v>
+      </c>
+      <c r="E142" s="10">
+        <v>-28.44</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="8">
+        <v>-32.58</v>
+      </c>
+      <c r="D143" s="8">
+        <v>111.71</v>
+      </c>
+      <c r="E143" s="9">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="8">
+        <v>-86.72</v>
+      </c>
+      <c r="D144" s="8">
+        <v>-85.48</v>
+      </c>
+      <c r="E144" s="9">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="8">
         <v>40.48</v>
       </c>
-      <c r="E142" s="9">
-        <v>47.46</v>
+      <c r="D145" s="8">
+        <v>-26.83</v>
+      </c>
+      <c r="E145" s="10">
+        <v>-67.31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5387,28 +5411,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5416,22 +5440,22 @@
         <v>53</v>
       </c>
       <c r="B2" s="13">
-        <v>43.24</v>
+        <v>47.24</v>
       </c>
       <c r="C2" s="14">
         <v>16</v>
       </c>
       <c r="D2" s="13">
-        <v>49.5</v>
+        <v>51.2</v>
       </c>
       <c r="E2" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F2" s="13">
-        <v>-2.6</v>
+        <v>-1.2</v>
       </c>
       <c r="G2" s="13">
-        <v>-6.5</v>
+        <v>-5</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
@@ -5571,34 +5595,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.3158</v>
+        <v>0.3167</v>
       </c>
       <c r="B2" s="16">
-        <v>0.2799</v>
+        <v>0.2901</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2079</v>
+        <v>0.2085</v>
       </c>
       <c r="D2" s="16">
-        <v>0.1179</v>
+        <v>0.1172</v>
       </c>
       <c r="E2" s="16">
-        <v>0.0774</v>
+        <v>0.0888</v>
       </c>
       <c r="F2" s="16">
-        <v>0.07719999999999999</v>
+        <v>0.0761</v>
       </c>
       <c r="G2" s="16">
-        <v>0.0694</v>
+        <v>0.0718</v>
       </c>
       <c r="H2" s="16">
-        <v>0.051</v>
+        <v>0.0484</v>
       </c>
       <c r="I2" s="16">
-        <v>0.0414</v>
+        <v>0.0387</v>
       </c>
       <c r="J2" s="16">
-        <v>-0.019</v>
+        <v>-0.0206</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5612,10 +5636,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>40</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>51</v>
@@ -5623,22 +5647,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>-0.0426</v>
+        <v>-0.0467</v>
       </c>
       <c r="B4" s="16">
-        <v>-0.0595</v>
+        <v>-0.0504</v>
       </c>
       <c r="C4" s="16">
-        <v>-0.07769999999999999</v>
+        <v>-0.0741</v>
       </c>
       <c r="D4" s="16">
-        <v>-0.0922</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E4" s="16">
-        <v>-0.09230000000000001</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="F4" s="16">
-        <v>-0.0969</v>
+        <v>-0.0964</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="93">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,31 +214,52 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.6% → -2.5%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.6%</t>
+  </si>
+  <si>
+    <t>-2.5%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.3 → 50.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.3</t>
+    <t>50.6 → 42.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.6</t>
   </si>
   <si>
-    <t>58.9 → 49.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>58.9</t>
-  </si>
-  <si>
-    <t>49.6</t>
+    <t>42.0</t>
+  </si>
+  <si>
+    <t>52.8 → 48.3</t>
+  </si>
+  <si>
+    <t>52.8</t>
+  </si>
+  <si>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>54.3 → 47.9</t>
+  </si>
+  <si>
+    <t>54.3</t>
+  </si>
+  <si>
+    <t>47.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -290,7 +311,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,7 +345,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -336,8 +357,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,13 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,11 +486,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -465,7 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -964,10 +998,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="D2">
-        <v>-1.57</v>
+        <v>-0.92</v>
       </c>
       <c r="E2">
         <v>772.1</v>
@@ -976,46 +1010,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-1.57</v>
+        <v>-2.47</v>
       </c>
       <c r="H2">
-        <v>33.11</v>
+        <v>31.89</v>
       </c>
       <c r="I2">
-        <v>6.82</v>
+        <v>3.98</v>
       </c>
       <c r="J2">
-        <v>4.59</v>
+        <v>2.76</v>
       </c>
       <c r="K2">
-        <v>4.82</v>
+        <v>2.93</v>
       </c>
       <c r="L2">
-        <v>5.39</v>
+        <v>3.47</v>
       </c>
       <c r="M2">
-        <v>29.82</v>
+        <v>29.68</v>
       </c>
       <c r="N2">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P2">
-        <v>744.62</v>
+        <v>750.39</v>
       </c>
       <c r="Q2">
-        <v>730.34</v>
+        <v>730.74</v>
       </c>
       <c r="R2">
-        <v>726.12</v>
+        <v>726.5599999999999</v>
       </c>
       <c r="S2">
-        <v>688.16</v>
+        <v>688.23</v>
       </c>
       <c r="T2">
-        <v>10.44</v>
+        <v>9.41</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1030,34 +1064,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>60.92</v>
+        <v>57.92</v>
       </c>
       <c r="Z2">
-        <v>5.98</v>
+        <v>6.84</v>
       </c>
       <c r="AA2">
-        <v>1.47</v>
+        <v>2.54</v>
       </c>
       <c r="AB2">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="AC2">
-        <v>91.68000000000001</v>
+        <v>78.83</v>
       </c>
       <c r="AD2">
-        <v>84.05</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="AE2">
-        <v>17.91</v>
+        <v>18.38</v>
       </c>
       <c r="AF2">
-        <v>-5.38</v>
+        <v>25.16</v>
       </c>
       <c r="AG2">
-        <v>762.84</v>
+        <v>764.1900000000001</v>
       </c>
       <c r="AH2">
-        <v>697.83</v>
+        <v>697.29</v>
       </c>
       <c r="AI2">
         <v>712.03</v>
@@ -1066,7 +1100,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>28.28</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1077,10 +1111,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>788.45</v>
+        <v>751.25</v>
       </c>
       <c r="D3">
-        <v>-4.38</v>
+        <v>-4.72</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1089,46 +1123,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-27.1</v>
+        <v>-30.54</v>
       </c>
       <c r="H3">
-        <v>56.02</v>
+        <v>48.66</v>
       </c>
       <c r="I3">
-        <v>-7.52</v>
+        <v>-11.86</v>
       </c>
       <c r="J3">
-        <v>-18.32</v>
+        <v>-25.75</v>
       </c>
       <c r="K3">
-        <v>-11.37</v>
+        <v>-19.09</v>
       </c>
       <c r="L3">
-        <v>-9.85</v>
+        <v>-13.53</v>
       </c>
       <c r="M3">
-        <v>-3.64</v>
+        <v>-2.58</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O3">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>828.22</v>
+        <v>808.01</v>
       </c>
       <c r="Q3">
-        <v>903.4</v>
+        <v>891.64</v>
       </c>
       <c r="R3">
-        <v>935.45</v>
+        <v>931.3</v>
       </c>
       <c r="S3">
-        <v>772.53</v>
+        <v>772.64</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>-2.77</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1140,19 +1174,19 @@
         <v>55</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.5</v>
+        <v>24.76</v>
       </c>
       <c r="Z3">
-        <v>-35.63</v>
+        <v>-41.44</v>
       </c>
       <c r="AA3">
-        <v>-24.44</v>
+        <v>-27.84</v>
       </c>
       <c r="AB3">
-        <v>-11.19</v>
+        <v>-13.6</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1161,16 +1195,16 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>45.53</v>
+        <v>46.88</v>
       </c>
       <c r="AF3">
-        <v>-41.61</v>
+        <v>-19.26</v>
       </c>
       <c r="AG3">
-        <v>1037.02</v>
+        <v>1035.51</v>
       </c>
       <c r="AH3">
-        <v>769.78</v>
+        <v>747.77</v>
       </c>
       <c r="AI3">
         <v>889.39</v>
@@ -1179,7 +1213,7 @@
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>47.04</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1190,10 +1224,10 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>204.65</v>
+        <v>204.29</v>
       </c>
       <c r="D4">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="E4">
         <v>291.61</v>
@@ -1202,46 +1236,46 @@
         <v>195.76</v>
       </c>
       <c r="G4">
-        <v>-29.82</v>
+        <v>-29.94</v>
       </c>
       <c r="H4">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="I4">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="J4">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="K4">
-        <v>-14.68</v>
+        <v>-10.64</v>
       </c>
       <c r="L4">
-        <v>-28.45</v>
+        <v>-29.52</v>
       </c>
       <c r="M4">
-        <v>-6.53</v>
+        <v>-4.78</v>
       </c>
       <c r="N4">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>202.68</v>
+        <v>203.53</v>
       </c>
       <c r="Q4">
-        <v>200.55</v>
+        <v>200.66</v>
       </c>
       <c r="R4">
-        <v>205.57</v>
+        <v>205.4</v>
       </c>
       <c r="S4">
-        <v>236.45</v>
+        <v>236.09</v>
       </c>
       <c r="T4">
-        <v>-13.45</v>
+        <v>-13.47</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
@@ -1256,34 +1290,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>54.92</v>
+        <v>53.99</v>
       </c>
       <c r="Z4">
-        <v>-0.88</v>
+        <v>-0.6</v>
       </c>
       <c r="AA4">
-        <v>-1.98</v>
+        <v>-1.7</v>
       </c>
       <c r="AB4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC4">
-        <v>93.45999999999999</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="AD4">
-        <v>93.91</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="AE4">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="AF4">
-        <v>-8.52</v>
+        <v>-3.05</v>
       </c>
       <c r="AG4">
-        <v>205.01</v>
+        <v>205.38</v>
       </c>
       <c r="AH4">
-        <v>196.1</v>
+        <v>195.95</v>
       </c>
       <c r="AI4">
         <v>207.87</v>
@@ -1292,7 +1326,7 @@
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>29.24</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1303,10 +1337,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>637.65</v>
+        <v>605.9</v>
       </c>
       <c r="D5">
-        <v>0.71</v>
+        <v>-4.98</v>
       </c>
       <c r="E5">
         <v>907</v>
@@ -1315,46 +1349,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-29.7</v>
+        <v>-33.2</v>
       </c>
       <c r="H5">
-        <v>11.01</v>
+        <v>5.48</v>
       </c>
       <c r="I5">
-        <v>0.11</v>
+        <v>-3.8</v>
       </c>
       <c r="J5">
-        <v>-18.18</v>
+        <v>-12.6</v>
       </c>
       <c r="K5">
-        <v>-8.07</v>
+        <v>-12.27</v>
       </c>
       <c r="L5">
-        <v>-29.14</v>
+        <v>-31.91</v>
       </c>
       <c r="M5">
-        <v>-8.699999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N5">
         <v>31</v>
       </c>
       <c r="O5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5">
-        <v>631.71</v>
+        <v>626.92</v>
       </c>
       <c r="Q5">
-        <v>631.55</v>
+        <v>627.11</v>
       </c>
       <c r="R5">
-        <v>644.67</v>
+        <v>643.3200000000001</v>
       </c>
       <c r="S5">
-        <v>691.65</v>
+        <v>690.91</v>
       </c>
       <c r="T5">
-        <v>-7.81</v>
+        <v>-12.3</v>
       </c>
       <c r="U5" t="s">
         <v>55</v>
@@ -1369,34 +1403,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>50.64</v>
+        <v>42.04</v>
       </c>
       <c r="Z5">
-        <v>-6.89</v>
+        <v>-8.16</v>
       </c>
       <c r="AA5">
-        <v>-9.41</v>
+        <v>-9.16</v>
       </c>
       <c r="AB5">
-        <v>2.52</v>
+        <v>1</v>
       </c>
       <c r="AC5">
-        <v>93.42</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AD5">
-        <v>89.25</v>
+        <v>87.06</v>
       </c>
       <c r="AE5">
-        <v>25.26</v>
+        <v>26.12</v>
       </c>
       <c r="AF5">
-        <v>-25.81</v>
+        <v>-55.93</v>
       </c>
       <c r="AG5">
-        <v>684.74</v>
+        <v>672.33</v>
       </c>
       <c r="AH5">
-        <v>578.37</v>
+        <v>581.89</v>
       </c>
       <c r="AI5">
         <v>676.63</v>
@@ -1405,7 +1439,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>17.87</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1416,10 +1450,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1718.5</v>
+        <v>1691.7</v>
       </c>
       <c r="D6">
-        <v>-1.39</v>
+        <v>-1.56</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1428,46 +1462,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-16.65</v>
+        <v>-17.95</v>
       </c>
       <c r="H6">
-        <v>27.49</v>
+        <v>25.51</v>
       </c>
       <c r="I6">
-        <v>3.36</v>
+        <v>1.15</v>
       </c>
       <c r="J6">
-        <v>-4.08</v>
+        <v>-4.97</v>
       </c>
       <c r="K6">
-        <v>-5.71</v>
+        <v>-6.99</v>
       </c>
       <c r="L6">
-        <v>-8.23</v>
+        <v>-13.47</v>
       </c>
       <c r="M6">
-        <v>4.02</v>
+        <v>4.7</v>
       </c>
       <c r="N6">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="O6">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>1711.26</v>
+        <v>1715.12</v>
       </c>
       <c r="Q6">
-        <v>1684.15</v>
+        <v>1682.1</v>
       </c>
       <c r="R6">
-        <v>1709.64</v>
+        <v>1708.37</v>
       </c>
       <c r="S6">
-        <v>1699.69</v>
+        <v>1699.02</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>-0.43</v>
       </c>
       <c r="U6" t="s">
         <v>55</v>
@@ -1479,37 +1513,37 @@
         <v>55</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>52.75</v>
+        <v>48.32</v>
       </c>
       <c r="Z6">
-        <v>-2.56</v>
+        <v>-2.97</v>
       </c>
       <c r="AA6">
-        <v>-11.75</v>
+        <v>-9.99</v>
       </c>
       <c r="AB6">
-        <v>9.19</v>
+        <v>7.02</v>
       </c>
       <c r="AC6">
-        <v>82.61</v>
+        <v>64.47</v>
       </c>
       <c r="AD6">
-        <v>84.34999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="AE6">
-        <v>61.2</v>
+        <v>62.22</v>
       </c>
       <c r="AF6">
-        <v>-12.03</v>
+        <v>-44.84</v>
       </c>
       <c r="AG6">
-        <v>1747.95</v>
+        <v>1741.83</v>
       </c>
       <c r="AH6">
-        <v>1620.36</v>
+        <v>1622.38</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1518,7 +1552,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>35.35</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1529,10 +1563,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>966.5</v>
+        <v>970.65</v>
       </c>
       <c r="D7">
-        <v>-1.27</v>
+        <v>0.43</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1541,46 +1575,46 @@
         <v>949.5</v>
       </c>
       <c r="G7">
-        <v>-23.31</v>
+        <v>-22.99</v>
       </c>
       <c r="H7">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="I7">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="J7">
-        <v>-4.66</v>
+        <v>-2.55</v>
       </c>
       <c r="K7">
-        <v>-11.48</v>
+        <v>-10.25</v>
       </c>
       <c r="L7">
-        <v>-12.89</v>
+        <v>-12.15</v>
       </c>
       <c r="M7">
-        <v>3.62</v>
+        <v>4.42</v>
       </c>
       <c r="N7">
         <v>56</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P7">
-        <v>976.95</v>
+        <v>979.08</v>
       </c>
       <c r="Q7">
-        <v>971.5700000000001</v>
+        <v>970.0700000000001</v>
       </c>
       <c r="R7">
-        <v>1012.37</v>
+        <v>1010.13</v>
       </c>
       <c r="S7">
-        <v>1097.86</v>
+        <v>1096.8</v>
       </c>
       <c r="T7">
-        <v>-11.97</v>
+        <v>-11.5</v>
       </c>
       <c r="U7" t="s">
         <v>55</v>
@@ -1595,34 +1629,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>43.64</v>
+        <v>45.3</v>
       </c>
       <c r="Z7">
-        <v>-10.56</v>
+        <v>-9.91</v>
       </c>
       <c r="AA7">
-        <v>-15.1</v>
+        <v>-14.06</v>
       </c>
       <c r="AB7">
-        <v>4.54</v>
+        <v>4.15</v>
       </c>
       <c r="AC7">
-        <v>80.31</v>
+        <v>69.94</v>
       </c>
       <c r="AD7">
-        <v>88.61</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="AE7">
-        <v>19.24</v>
+        <v>18.72</v>
       </c>
       <c r="AF7">
-        <v>-61.38</v>
+        <v>-45.76</v>
       </c>
       <c r="AG7">
-        <v>1003.24</v>
+        <v>998.64</v>
       </c>
       <c r="AH7">
-        <v>939.9</v>
+        <v>941.51</v>
       </c>
       <c r="AI7">
         <v>1007.9</v>
@@ -1631,7 +1665,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>34.46</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1642,10 +1676,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3790</v>
+        <v>3848.6</v>
       </c>
       <c r="D8">
-        <v>-1.56</v>
+        <v>1.55</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1654,46 +1688,46 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-34.09</v>
+        <v>-33.07</v>
       </c>
       <c r="H8">
-        <v>26.5</v>
+        <v>28.46</v>
       </c>
       <c r="I8">
-        <v>16.36</v>
+        <v>12.31</v>
       </c>
       <c r="J8">
-        <v>12.07</v>
+        <v>17.81</v>
       </c>
       <c r="K8">
-        <v>7.16</v>
+        <v>11.18</v>
       </c>
       <c r="L8">
-        <v>-27.69</v>
+        <v>-27.01</v>
       </c>
       <c r="M8">
-        <v>-8.699999999999999</v>
+        <v>-7.27</v>
       </c>
       <c r="N8">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O8">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="P8">
-        <v>3677.98</v>
+        <v>3762.36</v>
       </c>
       <c r="Q8">
-        <v>3286.38</v>
+        <v>3314.46</v>
       </c>
       <c r="R8">
-        <v>3474.66</v>
+        <v>3476.02</v>
       </c>
       <c r="S8">
-        <v>4130.41</v>
+        <v>4123.91</v>
       </c>
       <c r="T8">
-        <v>-8.24</v>
+        <v>-6.68</v>
       </c>
       <c r="U8" t="s">
         <v>55</v>
@@ -1708,43 +1742,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>70.12</v>
+        <v>71.83</v>
       </c>
       <c r="Z8">
-        <v>69.47</v>
+        <v>94.47</v>
       </c>
       <c r="AA8">
-        <v>-27.67</v>
+        <v>-3.24</v>
       </c>
       <c r="AB8">
-        <v>97.14</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="AC8">
-        <v>97.31999999999999</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="AD8">
-        <v>99.11</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="AE8">
-        <v>117.24</v>
+        <v>114.8</v>
       </c>
       <c r="AF8">
-        <v>-22.5</v>
+        <v>-39.01</v>
       </c>
       <c r="AG8">
-        <v>3792.87</v>
+        <v>3879.93</v>
       </c>
       <c r="AH8">
-        <v>2779.88</v>
+        <v>2748.98</v>
       </c>
       <c r="AI8">
-        <v>3464.53</v>
+        <v>3489.41</v>
       </c>
       <c r="AJ8" t="s">
         <v>56</v>
       </c>
       <c r="AK8">
-        <v>58.53</v>
+        <v>60.44</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1755,58 +1789,58 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>604.5</v>
+        <v>586.85</v>
       </c>
       <c r="D9">
-        <v>-1.48</v>
+        <v>-2.92</v>
       </c>
       <c r="E9">
-        <v>936.17</v>
+        <v>901.35</v>
       </c>
       <c r="F9">
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-35.43</v>
+        <v>-34.89</v>
       </c>
       <c r="H9">
-        <v>12.28</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-2.44</v>
+        <v>-5.58</v>
       </c>
       <c r="J9">
-        <v>-15.96</v>
+        <v>-16.44</v>
       </c>
       <c r="K9">
-        <v>-8.69</v>
+        <v>-10.67</v>
       </c>
       <c r="L9">
-        <v>-41.29</v>
+        <v>-37.31</v>
       </c>
       <c r="M9">
-        <v>32.06</v>
+        <v>32.41</v>
       </c>
       <c r="N9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O9">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P9">
-        <v>613.38</v>
+        <v>606.4400000000001</v>
       </c>
       <c r="Q9">
-        <v>630.41</v>
+        <v>625.73</v>
       </c>
       <c r="R9">
-        <v>646.61</v>
+        <v>644.48</v>
       </c>
       <c r="S9">
-        <v>655.86</v>
+        <v>655.3200000000001</v>
       </c>
       <c r="T9">
-        <v>-7.83</v>
+        <v>-10.45</v>
       </c>
       <c r="U9" t="s">
         <v>55</v>
@@ -1821,43 +1855,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.09</v>
+        <v>34.17</v>
       </c>
       <c r="Z9">
-        <v>-12.44</v>
+        <v>-14.01</v>
       </c>
       <c r="AA9">
-        <v>-10.99</v>
+        <v>-11.6</v>
       </c>
       <c r="AB9">
-        <v>-1.44</v>
+        <v>-2.42</v>
       </c>
       <c r="AC9">
-        <v>55.11</v>
+        <v>38.58</v>
       </c>
       <c r="AD9">
-        <v>55.24</v>
+        <v>50.74</v>
       </c>
       <c r="AE9">
-        <v>18.99</v>
+        <v>19.37</v>
       </c>
       <c r="AF9">
-        <v>-67.98999999999999</v>
+        <v>-50.66</v>
       </c>
       <c r="AG9">
-        <v>681.51</v>
+        <v>674.62</v>
       </c>
       <c r="AH9">
-        <v>579.3099999999999</v>
+        <v>576.84</v>
       </c>
       <c r="AI9">
-        <v>665.02</v>
+        <v>653.83</v>
       </c>
       <c r="AJ9" t="s">
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>12.97</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1868,10 +1902,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>352.25</v>
+        <v>352</v>
       </c>
       <c r="D10">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1880,46 +1914,46 @@
         <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-23.72</v>
+        <v>-23.78</v>
       </c>
       <c r="H10">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="I10">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
       <c r="J10">
-        <v>-4.54</v>
+        <v>-6.08</v>
       </c>
       <c r="K10">
-        <v>-8.34</v>
+        <v>-7.72</v>
       </c>
       <c r="L10">
-        <v>-10.04</v>
+        <v>-11.22</v>
       </c>
       <c r="M10">
-        <v>9.529999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N10">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="O10">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P10">
-        <v>350.78</v>
+        <v>352.18</v>
       </c>
       <c r="Q10">
-        <v>354.39</v>
+        <v>353.63</v>
       </c>
       <c r="R10">
-        <v>363.46</v>
+        <v>362.89</v>
       </c>
       <c r="S10">
-        <v>384.89</v>
+        <v>384.75</v>
       </c>
       <c r="T10">
-        <v>-8.48</v>
+        <v>-8.51</v>
       </c>
       <c r="U10" t="s">
         <v>55</v>
@@ -1934,34 +1968,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>46.65</v>
+        <v>46.42</v>
       </c>
       <c r="Z10">
-        <v>-4.41</v>
+        <v>-4</v>
       </c>
       <c r="AA10">
-        <v>-5.16</v>
+        <v>-4.93</v>
       </c>
       <c r="AB10">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="AC10">
-        <v>89.73</v>
+        <v>95.19</v>
       </c>
       <c r="AD10">
-        <v>82.56</v>
+        <v>90.89</v>
       </c>
       <c r="AE10">
-        <v>7.3</v>
+        <v>7.23</v>
       </c>
       <c r="AF10">
-        <v>-19.51</v>
+        <v>-6.82</v>
       </c>
       <c r="AG10">
-        <v>373.52</v>
+        <v>371.82</v>
       </c>
       <c r="AH10">
-        <v>335.26</v>
+        <v>335.45</v>
       </c>
       <c r="AI10">
         <v>362.14</v>
@@ -1970,7 +2004,7 @@
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>26.26</v>
+        <v>23.47</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1981,10 +2015,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>174.04</v>
+        <v>172.45</v>
       </c>
       <c r="D11">
-        <v>-0.83</v>
+        <v>-0.91</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -1993,46 +2027,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-19.67</v>
+        <v>-20.41</v>
       </c>
       <c r="H11">
-        <v>10.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="I11">
-        <v>1.05</v>
+        <v>-1.46</v>
       </c>
       <c r="J11">
-        <v>-7.07</v>
+        <v>-7.06</v>
       </c>
       <c r="K11">
-        <v>-6.64</v>
+        <v>-7.9</v>
       </c>
       <c r="L11">
-        <v>4.18</v>
+        <v>1.6</v>
       </c>
       <c r="M11">
-        <v>8.109999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="N11">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="O11">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P11">
-        <v>175.09</v>
+        <v>174.58</v>
       </c>
       <c r="Q11">
-        <v>179.88</v>
+        <v>179.34</v>
       </c>
       <c r="R11">
-        <v>183.36</v>
+        <v>183.06</v>
       </c>
       <c r="S11">
-        <v>192.38</v>
+        <v>192.36</v>
       </c>
       <c r="T11">
-        <v>-9.529999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="U11" t="s">
         <v>55</v>
@@ -2047,43 +2081,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>39.19</v>
+        <v>36.94</v>
       </c>
       <c r="Z11">
-        <v>-3.05</v>
+        <v>-3.15</v>
       </c>
       <c r="AA11">
-        <v>-2.73</v>
+        <v>-2.81</v>
       </c>
       <c r="AB11">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="AC11">
-        <v>44.26</v>
+        <v>39.04</v>
       </c>
       <c r="AD11">
-        <v>41.97</v>
+        <v>42.27</v>
       </c>
       <c r="AE11">
-        <v>4.26</v>
+        <v>4.36</v>
       </c>
       <c r="AF11">
-        <v>-47.74</v>
+        <v>-7.76</v>
       </c>
       <c r="AG11">
-        <v>192.18</v>
+        <v>191.95</v>
       </c>
       <c r="AH11">
-        <v>167.58</v>
+        <v>166.72</v>
       </c>
       <c r="AI11">
-        <v>186.52</v>
+        <v>186.46</v>
       </c>
       <c r="AJ11" t="s">
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>26.29</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2094,10 +2128,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2460.9</v>
+        <v>2529</v>
       </c>
       <c r="D12">
-        <v>-0.17</v>
+        <v>2.77</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2106,46 +2140,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-23.62</v>
+        <v>-21.5</v>
       </c>
       <c r="H12">
-        <v>24.12</v>
+        <v>27.56</v>
       </c>
       <c r="I12">
-        <v>15.81</v>
+        <v>11.44</v>
       </c>
       <c r="J12">
-        <v>12.37</v>
+        <v>20.14</v>
       </c>
       <c r="K12">
-        <v>9.32</v>
+        <v>13.86</v>
       </c>
       <c r="L12">
-        <v>-13.89</v>
+        <v>-12.12</v>
       </c>
       <c r="M12">
-        <v>-5</v>
+        <v>-3.94</v>
       </c>
       <c r="N12">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="O12">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="P12">
-        <v>2370.02</v>
+        <v>2421.96</v>
       </c>
       <c r="Q12">
-        <v>2161.14</v>
+        <v>2181.15</v>
       </c>
       <c r="R12">
-        <v>2243.38</v>
+        <v>2244.91</v>
       </c>
       <c r="S12">
-        <v>2431.76</v>
+        <v>2428.88</v>
       </c>
       <c r="T12">
-        <v>1.2</v>
+        <v>4.12</v>
       </c>
       <c r="U12" t="s">
         <v>55</v>
@@ -2160,43 +2194,43 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>72.98</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Z12">
-        <v>46.28</v>
+        <v>63.74</v>
       </c>
       <c r="AA12">
-        <v>-3.21</v>
+        <v>10.18</v>
       </c>
       <c r="AB12">
-        <v>49.48</v>
+        <v>53.56</v>
       </c>
       <c r="AC12">
         <v>99.61</v>
       </c>
       <c r="AD12">
-        <v>99.87</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="AE12">
-        <v>74.23999999999999</v>
+        <v>74.11</v>
       </c>
       <c r="AF12">
-        <v>64.95</v>
+        <v>3.41</v>
       </c>
       <c r="AG12">
-        <v>2427.39</v>
+        <v>2493.36</v>
       </c>
       <c r="AH12">
-        <v>1894.89</v>
+        <v>1868.95</v>
       </c>
       <c r="AI12">
-        <v>2241.82</v>
+        <v>2282.56</v>
       </c>
       <c r="AJ12" t="s">
         <v>56</v>
       </c>
       <c r="AK12">
-        <v>54.73</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2207,58 +2241,58 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4424.2</v>
+        <v>4380.9</v>
       </c>
       <c r="D13">
-        <v>-0.46</v>
+        <v>-0.98</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
       </c>
       <c r="F13">
-        <v>3549</v>
+        <v>3640.3</v>
       </c>
       <c r="G13">
-        <v>-14.41</v>
+        <v>-15.25</v>
       </c>
       <c r="H13">
-        <v>24.66</v>
+        <v>20.34</v>
       </c>
       <c r="I13">
-        <v>0.55</v>
+        <v>-2.36</v>
       </c>
       <c r="J13">
-        <v>-8.609999999999999</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K13">
-        <v>-4.72</v>
+        <v>-6.56</v>
       </c>
       <c r="L13">
-        <v>25.07</v>
+        <v>23.44</v>
       </c>
       <c r="M13">
-        <v>12.52</v>
+        <v>13.13</v>
       </c>
       <c r="N13">
         <v>99</v>
       </c>
       <c r="O13">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P13">
-        <v>4451.16</v>
+        <v>4429.94</v>
       </c>
       <c r="Q13">
-        <v>4596.48</v>
+        <v>4571.77</v>
       </c>
       <c r="R13">
-        <v>4858.83</v>
+        <v>4847.63</v>
       </c>
       <c r="S13">
-        <v>4436.56</v>
+        <v>4438.21</v>
       </c>
       <c r="T13">
-        <v>-0.28</v>
+        <v>-1.29</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2273,43 +2307,43 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>33.96</v>
+        <v>31.79</v>
       </c>
       <c r="Z13">
-        <v>-127.92</v>
+        <v>-127.44</v>
       </c>
       <c r="AA13">
-        <v>-125.7</v>
+        <v>-126.05</v>
       </c>
       <c r="AB13">
-        <v>-2.22</v>
+        <v>-1.39</v>
       </c>
       <c r="AC13">
-        <v>64.3</v>
+        <v>66.98</v>
       </c>
       <c r="AD13">
-        <v>56.58</v>
+        <v>61.7</v>
       </c>
       <c r="AE13">
-        <v>90.12</v>
+        <v>90.22</v>
       </c>
       <c r="AF13">
-        <v>-24.18</v>
+        <v>-48.24</v>
       </c>
       <c r="AG13">
-        <v>4995.67</v>
+        <v>4959.38</v>
       </c>
       <c r="AH13">
-        <v>4197.28</v>
+        <v>4184.16</v>
       </c>
       <c r="AI13">
-        <v>4684.57</v>
+        <v>4667.4</v>
       </c>
       <c r="AJ13" t="s">
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>51.88</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2320,10 +2354,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2891.6</v>
+        <v>2822</v>
       </c>
       <c r="D14">
-        <v>-2.27</v>
+        <v>-2.41</v>
       </c>
       <c r="E14">
         <v>4807.3</v>
@@ -2332,25 +2366,25 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-39.85</v>
+        <v>-41.3</v>
       </c>
       <c r="H14">
-        <v>31.8</v>
+        <v>28.63</v>
       </c>
       <c r="I14">
-        <v>-0.73</v>
+        <v>-5.55</v>
       </c>
       <c r="J14">
-        <v>3.68</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K14">
-        <v>-1.17</v>
+        <v>-2.51</v>
       </c>
       <c r="L14">
-        <v>-37.28</v>
+        <v>-40.18</v>
       </c>
       <c r="M14">
-        <v>21.07</v>
+        <v>21.29</v>
       </c>
       <c r="N14">
         <v>44</v>
@@ -2359,19 +2393,19 @@
         <v>29</v>
       </c>
       <c r="P14">
-        <v>2951.76</v>
+        <v>2918.6</v>
       </c>
       <c r="Q14">
-        <v>2802.35</v>
+        <v>2802.67</v>
       </c>
       <c r="R14">
-        <v>2853.93</v>
+        <v>2850.43</v>
       </c>
       <c r="S14">
-        <v>2787.44</v>
+        <v>2780.19</v>
       </c>
       <c r="T14">
-        <v>3.74</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="s">
         <v>55</v>
@@ -2386,34 +2420,34 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>54.3</v>
+        <v>47.86</v>
       </c>
       <c r="Z14">
-        <v>36.13</v>
+        <v>28.53</v>
       </c>
       <c r="AA14">
-        <v>11.74</v>
+        <v>15.1</v>
       </c>
       <c r="AB14">
-        <v>24.39</v>
+        <v>13.43</v>
       </c>
       <c r="AC14">
-        <v>84.38</v>
+        <v>73.55</v>
       </c>
       <c r="AD14">
-        <v>90.40000000000001</v>
+        <v>83.28</v>
       </c>
       <c r="AE14">
-        <v>72.7</v>
+        <v>74.37</v>
       </c>
       <c r="AF14">
-        <v>-27.41</v>
+        <v>-31.13</v>
       </c>
       <c r="AG14">
-        <v>3087.69</v>
+        <v>3088.09</v>
       </c>
       <c r="AH14">
-        <v>2517</v>
+        <v>2517.25</v>
       </c>
       <c r="AI14">
         <v>2752.34</v>
@@ -2422,7 +2456,7 @@
         <v>56</v>
       </c>
       <c r="AK14">
-        <v>38.82</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2433,10 +2467,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>214.98</v>
+        <v>208.7</v>
       </c>
       <c r="D15">
-        <v>-7.5</v>
+        <v>-2.92</v>
       </c>
       <c r="E15">
         <v>342.75</v>
@@ -2445,46 +2479,46 @@
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-37.28</v>
+        <v>-39.11</v>
       </c>
       <c r="H15">
-        <v>12.1</v>
+        <v>8.82</v>
       </c>
       <c r="I15">
-        <v>-5.67</v>
+        <v>-2.85</v>
       </c>
       <c r="J15">
-        <v>-2.05</v>
+        <v>-3.04</v>
       </c>
       <c r="K15">
-        <v>-11.66</v>
+        <v>-14.85</v>
       </c>
       <c r="L15">
-        <v>-35.27</v>
+        <v>-37.94</v>
       </c>
       <c r="M15">
-        <v>8.289999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="N15">
         <v>25</v>
       </c>
       <c r="O15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P15">
-        <v>222.57</v>
+        <v>221.35</v>
       </c>
       <c r="Q15">
-        <v>210.9</v>
+        <v>210.51</v>
       </c>
       <c r="R15">
-        <v>221.06</v>
+        <v>220.58</v>
       </c>
       <c r="S15">
-        <v>244.12</v>
+        <v>243.68</v>
       </c>
       <c r="T15">
-        <v>-11.94</v>
+        <v>-14.35</v>
       </c>
       <c r="U15" t="s">
         <v>55</v>
@@ -2499,34 +2533,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>49.58</v>
+        <v>46.7</v>
       </c>
       <c r="Z15">
-        <v>0.53</v>
+        <v>-0.11</v>
       </c>
       <c r="AA15">
-        <v>-2.49</v>
+        <v>-2.01</v>
       </c>
       <c r="AB15">
-        <v>3.02</v>
+        <v>1.91</v>
       </c>
       <c r="AC15">
-        <v>82.08</v>
+        <v>76.52</v>
       </c>
       <c r="AD15">
-        <v>85.48</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="AE15">
-        <v>13.81</v>
+        <v>13.6</v>
       </c>
       <c r="AF15">
-        <v>-53.09</v>
+        <v>-79.3</v>
       </c>
       <c r="AG15">
-        <v>236.16</v>
+        <v>235.65</v>
       </c>
       <c r="AH15">
-        <v>185.64</v>
+        <v>185.37</v>
       </c>
       <c r="AI15">
         <v>197.45</v>
@@ -2535,7 +2569,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>44.03</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2546,58 +2580,58 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>32.87</v>
+        <v>32.06</v>
       </c>
       <c r="D16">
-        <v>-2.03</v>
+        <v>-2.46</v>
       </c>
       <c r="E16">
-        <v>56.19</v>
+        <v>56.1</v>
       </c>
       <c r="F16">
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-41.5</v>
+        <v>-42.85</v>
       </c>
       <c r="H16">
-        <v>4.82</v>
+        <v>2.23</v>
       </c>
       <c r="I16">
-        <v>-0.45</v>
+        <v>-5.04</v>
       </c>
       <c r="J16">
-        <v>-10.29</v>
+        <v>-10.27</v>
       </c>
       <c r="K16">
-        <v>-18.32</v>
+        <v>-20.15</v>
       </c>
       <c r="L16">
-        <v>-41.16</v>
+        <v>-42.94</v>
       </c>
       <c r="M16">
-        <v>-10.11</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="N16">
         <v>7</v>
       </c>
       <c r="O16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>33.51</v>
+        <v>33.17</v>
       </c>
       <c r="Q16">
-        <v>34.27</v>
+        <v>34.11</v>
       </c>
       <c r="R16">
-        <v>36.23</v>
+        <v>36.09</v>
       </c>
       <c r="S16">
-        <v>40.81</v>
+        <v>40.72</v>
       </c>
       <c r="T16">
-        <v>-19.45</v>
+        <v>-21.27</v>
       </c>
       <c r="U16" t="s">
         <v>55</v>
@@ -2612,43 +2646,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>35.77</v>
+        <v>31.8</v>
       </c>
       <c r="Z16">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="AA16">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="AB16">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AC16">
-        <v>42.09</v>
+        <v>27.77</v>
       </c>
       <c r="AD16">
-        <v>48.34</v>
+        <v>40.24</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>-85.78</v>
+        <v>-83.98</v>
       </c>
       <c r="AG16">
-        <v>36.28</v>
+        <v>36.27</v>
       </c>
       <c r="AH16">
-        <v>32.27</v>
+        <v>31.95</v>
       </c>
       <c r="AI16">
-        <v>36.59</v>
+        <v>35.87</v>
       </c>
       <c r="AJ16" t="s">
         <v>57</v>
       </c>
       <c r="AK16">
-        <v>12.07</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2659,58 +2693,58 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>1019.6</v>
+        <v>998.4</v>
       </c>
       <c r="D17">
-        <v>-0.92</v>
+        <v>-2.08</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
       </c>
       <c r="F17">
-        <v>1019.6</v>
+        <v>998.4</v>
       </c>
       <c r="G17">
-        <v>-34.49</v>
+        <v>-35.85</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>-0.04</v>
+        <v>-4.09</v>
       </c>
       <c r="J17">
-        <v>-10.17</v>
+        <v>-10.13</v>
       </c>
       <c r="K17">
-        <v>-24.89</v>
+        <v>-26.55</v>
       </c>
       <c r="L17">
-        <v>-26.51</v>
+        <v>-29.07</v>
       </c>
       <c r="M17">
-        <v>-4.38</v>
+        <v>-3.03</v>
       </c>
       <c r="N17">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O17">
         <v>14</v>
       </c>
       <c r="P17">
-        <v>1036.3</v>
+        <v>1027.78</v>
       </c>
       <c r="Q17">
-        <v>1070.32</v>
+        <v>1063.14</v>
       </c>
       <c r="R17">
-        <v>1152.98</v>
+        <v>1147.25</v>
       </c>
       <c r="S17">
-        <v>1311.54</v>
+        <v>1309.75</v>
       </c>
       <c r="T17">
-        <v>-22.26</v>
+        <v>-23.77</v>
       </c>
       <c r="U17" t="s">
         <v>55</v>
@@ -2725,43 +2759,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>33.19</v>
+        <v>30.02</v>
       </c>
       <c r="Z17">
-        <v>-36.6</v>
+        <v>-37.84</v>
       </c>
       <c r="AA17">
-        <v>-37.92</v>
+        <v>-37.9</v>
       </c>
       <c r="AB17">
-        <v>1.31</v>
+        <v>0.06</v>
       </c>
       <c r="AC17">
-        <v>51.71</v>
+        <v>32.64</v>
       </c>
       <c r="AD17">
-        <v>51.93</v>
+        <v>45.27</v>
       </c>
       <c r="AE17">
-        <v>28.27</v>
+        <v>29.17</v>
       </c>
       <c r="AF17">
-        <v>-49.56</v>
+        <v>-31.82</v>
       </c>
       <c r="AG17">
-        <v>1150.75</v>
+        <v>1142.23</v>
       </c>
       <c r="AH17">
-        <v>989.89</v>
+        <v>984.04</v>
       </c>
       <c r="AI17">
-        <v>1108.17</v>
+        <v>1093.3</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>53.75</v>
+        <v>55.38</v>
       </c>
     </row>
   </sheetData>
@@ -2902,7 +2936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2942,7 +2976,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2962,1813 +2996,1819 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>72</v>
+      <c r="E5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>8.23</v>
-      </c>
-      <c r="D8" s="7">
-        <v>4.59</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-12.1</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-18.32</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-6.22</v>
+      <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>1.13</v>
+        <v>4.59</v>
       </c>
       <c r="D10" s="7">
-        <v>0.25</v>
+        <v>2.76</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.88</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-13.48</v>
+        <v>-18.32</v>
       </c>
       <c r="D11" s="7">
-        <v>-18.18</v>
+        <v>-25.75</v>
       </c>
       <c r="E11" s="8">
-        <v>-4.7</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-3.14</v>
+        <v>0.25</v>
       </c>
       <c r="D12" s="7">
-        <v>-4.08</v>
+        <v>0.24</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.9399999999999999</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-2.12</v>
+        <v>-18.18</v>
       </c>
       <c r="D13" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.54</v>
+        <v>-12.6</v>
+      </c>
+      <c r="E13" s="9">
+        <v>5.58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>14.14</v>
+        <v>-4.08</v>
       </c>
       <c r="D14" s="7">
-        <v>12.07</v>
+        <v>-4.97</v>
       </c>
       <c r="E14" s="8">
-        <v>-2.07</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-10.03</v>
+        <v>-4.66</v>
       </c>
       <c r="D15" s="7">
-        <v>-15.96</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-5.93</v>
+        <v>-2.55</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2.11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-1.82</v>
+        <v>12.07</v>
       </c>
       <c r="D16" s="7">
-        <v>-4.54</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.72</v>
+        <v>17.81</v>
+      </c>
+      <c r="E16" s="9">
+        <v>5.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-4.1</v>
+        <v>-15.96</v>
       </c>
       <c r="D17" s="7">
-        <v>-7.07</v>
+        <v>-16.44</v>
       </c>
       <c r="E17" s="8">
-        <v>-2.97</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>12.62</v>
+        <v>-4.54</v>
       </c>
       <c r="D18" s="7">
-        <v>12.37</v>
+        <v>-6.08</v>
       </c>
       <c r="E18" s="8">
-        <v>-0.25</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>-9.449999999999999</v>
+        <v>-7.07</v>
       </c>
       <c r="D19" s="7">
-        <v>-8.609999999999999</v>
+        <v>-7.06</v>
       </c>
       <c r="E19" s="9">
-        <v>0.84</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>6.82</v>
+        <v>12.37</v>
       </c>
       <c r="D20" s="7">
-        <v>3.68</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-3.14</v>
+        <v>20.14</v>
+      </c>
+      <c r="E20" s="9">
+        <v>7.77</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>8.609999999999999</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="D21" s="7">
-        <v>-2.05</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="E21" s="8">
-        <v>-10.66</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>-4.74</v>
+        <v>3.68</v>
       </c>
       <c r="D22" s="7">
-        <v>-10.29</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E22" s="8">
-        <v>-5.55</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>-9.01</v>
+        <v>-2.05</v>
       </c>
       <c r="D23" s="7">
-        <v>-10.17</v>
+        <v>-3.04</v>
       </c>
       <c r="E23" s="8">
-        <v>-1.16</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>7.89</v>
+        <v>-10.29</v>
       </c>
       <c r="D24" s="7">
-        <v>6.82</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.07</v>
+        <v>-10.27</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>-3.37</v>
+        <v>-10.17</v>
       </c>
       <c r="D25" s="7">
-        <v>-7.52</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-4.15</v>
+        <v>-10.13</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.04</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>3.47</v>
+        <v>6.82</v>
       </c>
       <c r="D26" s="7">
-        <v>2.27</v>
+        <v>3.98</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.2</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>7.36</v>
+        <v>-7.52</v>
       </c>
       <c r="D27" s="7">
-        <v>0.11</v>
+        <v>-11.86</v>
       </c>
       <c r="E27" s="8">
-        <v>-7.25</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="7">
-        <v>5.2</v>
+        <v>2.27</v>
       </c>
       <c r="D28" s="7">
-        <v>3.36</v>
+        <v>2.12</v>
       </c>
       <c r="E28" s="8">
-        <v>-1.84</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="7">
-        <v>2.5</v>
+        <v>0.11</v>
       </c>
       <c r="D29" s="7">
-        <v>0.8</v>
+        <v>-3.8</v>
       </c>
       <c r="E29" s="8">
-        <v>-1.7</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>23.01</v>
+        <v>3.36</v>
       </c>
       <c r="D30" s="7">
-        <v>16.36</v>
+        <v>1.15</v>
       </c>
       <c r="E30" s="8">
-        <v>-6.65</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>2.39</v>
+        <v>0.8</v>
       </c>
       <c r="D31" s="7">
-        <v>-2.44</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-4.83</v>
+        <v>1.11</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.31</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>3.42</v>
+        <v>16.36</v>
       </c>
       <c r="D32" s="7">
-        <v>2.49</v>
+        <v>12.31</v>
       </c>
       <c r="E32" s="8">
-        <v>-0.93</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>0.98</v>
+        <v>-2.44</v>
       </c>
       <c r="D33" s="7">
-        <v>1.05</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.07000000000000001</v>
+        <v>-5.58</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-3.14</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>14.33</v>
+        <v>2.49</v>
       </c>
       <c r="D34" s="7">
-        <v>15.81</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.48</v>
+        <v>2.03</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>0.79</v>
+        <v>1.05</v>
       </c>
       <c r="D35" s="7">
-        <v>0.55</v>
+        <v>-1.46</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.24</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>1.39</v>
+        <v>15.81</v>
       </c>
       <c r="D36" s="7">
-        <v>-0.73</v>
+        <v>11.44</v>
       </c>
       <c r="E36" s="8">
-        <v>-2.12</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>7.13</v>
+        <v>0.55</v>
       </c>
       <c r="D37" s="7">
-        <v>-5.67</v>
+        <v>-2.36</v>
       </c>
       <c r="E37" s="8">
-        <v>-12.8</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>2.01</v>
+        <v>-0.73</v>
       </c>
       <c r="D38" s="7">
-        <v>-0.45</v>
+        <v>-5.55</v>
       </c>
       <c r="E38" s="8">
-        <v>-2.46</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-0.45</v>
+        <v>-5.67</v>
       </c>
       <c r="D39" s="7">
-        <v>-0.04</v>
+        <v>-2.85</v>
       </c>
       <c r="E39" s="9">
-        <v>0.41</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>6.34</v>
+        <v>-0.45</v>
       </c>
       <c r="D40" s="7">
-        <v>5.39</v>
+        <v>-5.04</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.95</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-5.28</v>
+        <v>-0.04</v>
       </c>
       <c r="D41" s="7">
-        <v>-9.85</v>
+        <v>-4.09</v>
       </c>
       <c r="E41" s="8">
-        <v>-4.57</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="7">
-        <v>-29.58</v>
+        <v>5.39</v>
       </c>
       <c r="D42" s="7">
-        <v>-28.45</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.13</v>
+        <v>3.47</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="7">
-        <v>-29.4</v>
+        <v>-9.85</v>
       </c>
       <c r="D43" s="7">
-        <v>-29.14</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.26</v>
+        <v>-13.53</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-3.68</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="7">
-        <v>-3.08</v>
+        <v>-28.45</v>
       </c>
       <c r="D44" s="7">
-        <v>-8.23</v>
+        <v>-29.52</v>
       </c>
       <c r="E44" s="8">
-        <v>-5.15</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="7">
-        <v>-11.62</v>
+        <v>-29.14</v>
       </c>
       <c r="D45" s="7">
-        <v>-12.89</v>
+        <v>-31.91</v>
       </c>
       <c r="E45" s="8">
-        <v>-1.27</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="7">
-        <v>-26.77</v>
+        <v>-8.23</v>
       </c>
       <c r="D46" s="7">
-        <v>-27.69</v>
+        <v>-13.47</v>
       </c>
       <c r="E46" s="8">
-        <v>-0.92</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="7">
-        <v>-37.84</v>
+        <v>-12.89</v>
       </c>
       <c r="D47" s="7">
-        <v>-41.29</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-3.45</v>
+        <v>-12.15</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.74</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="7">
-        <v>-9.539999999999999</v>
+        <v>-27.69</v>
       </c>
       <c r="D48" s="7">
-        <v>-10.04</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.5</v>
+        <v>-27.01</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.68</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="7">
-        <v>3.52</v>
+        <v>-41.29</v>
       </c>
       <c r="D49" s="7">
-        <v>4.18</v>
+        <v>-37.31</v>
       </c>
       <c r="E49" s="9">
-        <v>0.66</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>-15.09</v>
+        <v>-10.04</v>
       </c>
       <c r="D50" s="7">
-        <v>-13.89</v>
-      </c>
-      <c r="E50" s="9">
-        <v>1.2</v>
+        <v>-11.22</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>25.79</v>
+        <v>4.18</v>
       </c>
       <c r="D51" s="7">
-        <v>25.07</v>
+        <v>1.6</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.72</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>-36.71</v>
+        <v>-13.89</v>
       </c>
       <c r="D52" s="7">
-        <v>-37.28</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.57</v>
+        <v>-12.12</v>
+      </c>
+      <c r="E52" s="9">
+        <v>1.77</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>-31.26</v>
+        <v>25.07</v>
       </c>
       <c r="D53" s="7">
-        <v>-35.27</v>
+        <v>23.44</v>
       </c>
       <c r="E53" s="8">
-        <v>-4.01</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>-41.26</v>
+        <v>-37.28</v>
       </c>
       <c r="D54" s="7">
-        <v>-41.16</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.1</v>
+        <v>-40.18</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-25.11</v>
+        <v>-35.27</v>
       </c>
       <c r="D55" s="7">
-        <v>-26.51</v>
+        <v>-37.94</v>
       </c>
       <c r="E55" s="8">
-        <v>-1.4</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>6.07</v>
+        <v>-41.16</v>
       </c>
       <c r="D56" s="7">
-        <v>4.82</v>
+        <v>-42.94</v>
       </c>
       <c r="E56" s="8">
-        <v>-1.25</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>-4.91</v>
+        <v>-26.51</v>
       </c>
       <c r="D57" s="7">
-        <v>-11.37</v>
+        <v>-29.07</v>
       </c>
       <c r="E57" s="8">
-        <v>-6.46</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="7">
-        <v>-12.4</v>
+        <v>4.82</v>
       </c>
       <c r="D58" s="7">
-        <v>-14.68</v>
+        <v>2.93</v>
       </c>
       <c r="E58" s="8">
-        <v>-2.28</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="7">
-        <v>-9.35</v>
+        <v>-11.37</v>
       </c>
       <c r="D59" s="7">
-        <v>-8.07</v>
-      </c>
-      <c r="E59" s="9">
-        <v>1.28</v>
+        <v>-19.09</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-7.72</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="7">
-        <v>-4.09</v>
+        <v>-14.68</v>
       </c>
       <c r="D60" s="7">
-        <v>-5.71</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.62</v>
+        <v>-10.64</v>
+      </c>
+      <c r="E60" s="9">
+        <v>4.04</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="7">
-        <v>-10.08</v>
+        <v>-8.07</v>
       </c>
       <c r="D61" s="7">
-        <v>-11.48</v>
+        <v>-12.27</v>
       </c>
       <c r="E61" s="8">
-        <v>-1.4</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="7">
-        <v>9.9</v>
+        <v>-5.71</v>
       </c>
       <c r="D62" s="7">
-        <v>7.16</v>
+        <v>-6.99</v>
       </c>
       <c r="E62" s="8">
-        <v>-2.74</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="7">
-        <v>-7.36</v>
+        <v>-11.48</v>
       </c>
       <c r="D63" s="7">
-        <v>-8.69</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-1.33</v>
+        <v>-10.25</v>
+      </c>
+      <c r="E63" s="9">
+        <v>1.23</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="7">
-        <v>-6.2</v>
+        <v>7.16</v>
       </c>
       <c r="D64" s="7">
-        <v>-8.34</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-2.14</v>
+        <v>11.18</v>
+      </c>
+      <c r="E64" s="9">
+        <v>4.02</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="7">
-        <v>-5.59</v>
+        <v>-8.69</v>
       </c>
       <c r="D65" s="7">
-        <v>-6.64</v>
+        <v>-10.67</v>
       </c>
       <c r="E65" s="8">
-        <v>-1.05</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="7">
-        <v>8.640000000000001</v>
+        <v>-8.34</v>
       </c>
       <c r="D66" s="7">
-        <v>9.32</v>
+        <v>-7.72</v>
       </c>
       <c r="E66" s="9">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="7">
-        <v>-4.17</v>
+        <v>-6.64</v>
       </c>
       <c r="D67" s="7">
-        <v>-4.72</v>
+        <v>-7.9</v>
       </c>
       <c r="E67" s="8">
-        <v>-0.55</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="7">
-        <v>4.09</v>
+        <v>9.32</v>
       </c>
       <c r="D68" s="7">
-        <v>-1.17</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-5.26</v>
+        <v>13.86</v>
+      </c>
+      <c r="E68" s="9">
+        <v>4.54</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>-3.88</v>
+        <v>-4.72</v>
       </c>
       <c r="D69" s="7">
-        <v>-11.66</v>
+        <v>-6.56</v>
       </c>
       <c r="E69" s="8">
-        <v>-7.78</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>-16.71</v>
+        <v>-1.17</v>
       </c>
       <c r="D70" s="7">
-        <v>-18.32</v>
+        <v>-2.51</v>
       </c>
       <c r="E70" s="8">
-        <v>-1.61</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>-23.34</v>
+        <v>-11.66</v>
       </c>
       <c r="D71" s="7">
-        <v>-24.89</v>
+        <v>-14.85</v>
       </c>
       <c r="E71" s="8">
-        <v>-1.55</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>0</v>
+        <v>-18.32</v>
       </c>
       <c r="D72" s="7">
-        <v>-1.57</v>
+        <v>-20.15</v>
       </c>
       <c r="E72" s="8">
-        <v>-1.57</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>-23.76</v>
+        <v>-24.89</v>
       </c>
       <c r="D73" s="7">
-        <v>-27.1</v>
+        <v>-26.55</v>
       </c>
       <c r="E73" s="8">
-        <v>-3.34</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="7">
-        <v>-29.72</v>
+        <v>-1.57</v>
       </c>
       <c r="D74" s="7">
-        <v>-29.82</v>
+        <v>-2.47</v>
       </c>
       <c r="E74" s="8">
-        <v>-0.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="7">
-        <v>-30.19</v>
+        <v>-27.1</v>
       </c>
       <c r="D75" s="7">
-        <v>-29.7</v>
-      </c>
-      <c r="E75" s="9">
-        <v>0.49</v>
+        <v>-30.54</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="7">
-        <v>-15.47</v>
+        <v>-29.82</v>
       </c>
       <c r="D76" s="7">
-        <v>-16.65</v>
+        <v>-29.94</v>
       </c>
       <c r="E76" s="8">
-        <v>-1.18</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="7">
-        <v>-22.33</v>
+        <v>-29.7</v>
       </c>
       <c r="D77" s="7">
-        <v>-23.31</v>
+        <v>-33.2</v>
       </c>
       <c r="E77" s="8">
-        <v>-0.98</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="7">
-        <v>-33.04</v>
+        <v>-16.65</v>
       </c>
       <c r="D78" s="7">
-        <v>-34.09</v>
+        <v>-17.95</v>
       </c>
       <c r="E78" s="8">
-        <v>-1.05</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="7">
-        <v>-40.41</v>
+        <v>-23.31</v>
       </c>
       <c r="D79" s="7">
-        <v>-35.43</v>
+        <v>-22.99</v>
       </c>
       <c r="E79" s="9">
-        <v>4.98</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="7">
-        <v>-23.38</v>
+        <v>-34.09</v>
       </c>
       <c r="D80" s="7">
-        <v>-23.72</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-0.34</v>
+        <v>-33.07</v>
+      </c>
+      <c r="E80" s="9">
+        <v>1.02</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="7">
-        <v>-19</v>
+        <v>-35.43</v>
       </c>
       <c r="D81" s="7">
-        <v>-19.67</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-0.67</v>
+        <v>-34.89</v>
+      </c>
+      <c r="E81" s="9">
+        <v>0.54</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="7">
-        <v>-23.49</v>
+        <v>-23.72</v>
       </c>
       <c r="D82" s="7">
-        <v>-23.62</v>
+        <v>-23.78</v>
       </c>
       <c r="E82" s="8">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="7">
-        <v>-14.01</v>
+        <v>-19.67</v>
       </c>
       <c r="D83" s="7">
-        <v>-14.41</v>
+        <v>-20.41</v>
       </c>
       <c r="E83" s="8">
-        <v>-0.4</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="7">
-        <v>-38.45</v>
+        <v>-23.62</v>
       </c>
       <c r="D84" s="7">
-        <v>-39.85</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-1.4</v>
+        <v>-21.5</v>
+      </c>
+      <c r="E84" s="9">
+        <v>2.12</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="7">
-        <v>-32.2</v>
+        <v>-14.41</v>
       </c>
       <c r="D85" s="7">
-        <v>-37.28</v>
+        <v>-15.25</v>
       </c>
       <c r="E85" s="8">
-        <v>-5.08</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="7">
-        <v>-40.29</v>
+        <v>-39.85</v>
       </c>
       <c r="D86" s="7">
-        <v>-41.5</v>
+        <v>-41.3</v>
       </c>
       <c r="E86" s="8">
-        <v>-1.21</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="7">
-        <v>-33.88</v>
+        <v>-37.28</v>
       </c>
       <c r="D87" s="7">
-        <v>-34.49</v>
+        <v>-39.11</v>
       </c>
       <c r="E87" s="8">
-        <v>-0.61</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7">
-        <v>772.1</v>
+        <v>-41.5</v>
       </c>
       <c r="D88" s="7">
-        <v>760</v>
+        <v>-42.85</v>
       </c>
       <c r="E88" s="8">
-        <v>-12.1</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C89" s="7">
-        <v>824.55</v>
+        <v>-34.49</v>
       </c>
       <c r="D89" s="7">
-        <v>788.45</v>
+        <v>-35.85</v>
       </c>
       <c r="E89" s="8">
-        <v>-36.1</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="7">
-        <v>204.93</v>
+        <v>760</v>
       </c>
       <c r="D90" s="7">
-        <v>204.65</v>
+        <v>753</v>
       </c>
       <c r="E90" s="8">
-        <v>-0.28</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="7">
-        <v>633.15</v>
+        <v>788.45</v>
       </c>
       <c r="D91" s="7">
-        <v>637.65</v>
-      </c>
-      <c r="E91" s="9">
-        <v>4.5</v>
+        <v>751.25</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-37.2</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="7">
-        <v>1742.8</v>
+        <v>204.65</v>
       </c>
       <c r="D92" s="7">
-        <v>1718.5</v>
+        <v>204.29</v>
       </c>
       <c r="E92" s="8">
-        <v>-24.3</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="7">
-        <v>978.9</v>
+        <v>637.65</v>
       </c>
       <c r="D93" s="7">
-        <v>966.5</v>
+        <v>605.9</v>
       </c>
       <c r="E93" s="8">
-        <v>-12.4</v>
+        <v>-31.75</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="7">
-        <v>3850.1</v>
+        <v>1718.5</v>
       </c>
       <c r="D94" s="7">
-        <v>3790</v>
+        <v>1691.7</v>
       </c>
       <c r="E94" s="8">
-        <v>-60.1</v>
+        <v>-26.8</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="7">
-        <v>613.55</v>
+        <v>966.5</v>
       </c>
       <c r="D95" s="7">
-        <v>604.5</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-9.050000000000001</v>
+        <v>970.65</v>
+      </c>
+      <c r="E95" s="9">
+        <v>4.15</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="7">
-        <v>353.85</v>
+        <v>3790</v>
       </c>
       <c r="D96" s="7">
-        <v>352.25</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-1.6</v>
+        <v>3848.6</v>
+      </c>
+      <c r="E96" s="9">
+        <v>58.6</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="7">
-        <v>175.5</v>
+        <v>604.5</v>
       </c>
       <c r="D97" s="7">
-        <v>174.04</v>
+        <v>586.85</v>
       </c>
       <c r="E97" s="8">
-        <v>-1.46</v>
+        <v>-17.65</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="7">
-        <v>2465</v>
+        <v>352.25</v>
       </c>
       <c r="D98" s="7">
-        <v>2460.9</v>
+        <v>352</v>
       </c>
       <c r="E98" s="8">
-        <v>-4.1</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="7">
-        <v>4444.8</v>
+        <v>174.04</v>
       </c>
       <c r="D99" s="7">
-        <v>4424.2</v>
+        <v>172.45</v>
       </c>
       <c r="E99" s="8">
-        <v>-20.6</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="7">
-        <v>2958.7</v>
+        <v>2460.9</v>
       </c>
       <c r="D100" s="7">
-        <v>2891.6</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-67.09999999999999</v>
+        <v>2529</v>
+      </c>
+      <c r="E100" s="9">
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="7">
-        <v>232.4</v>
+        <v>4424.2</v>
       </c>
       <c r="D101" s="7">
-        <v>214.98</v>
+        <v>4380.9</v>
       </c>
       <c r="E101" s="8">
-        <v>-17.42</v>
+        <v>-43.3</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="7">
-        <v>33.55</v>
+        <v>2891.6</v>
       </c>
       <c r="D102" s="7">
-        <v>32.87</v>
+        <v>2822</v>
       </c>
       <c r="E102" s="8">
-        <v>-0.68</v>
+        <v>-69.59999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="7">
-        <v>1029.1</v>
+        <v>214.98</v>
       </c>
       <c r="D103" s="7">
-        <v>1019.6</v>
+        <v>208.7</v>
       </c>
       <c r="E103" s="8">
-        <v>-9.5</v>
+        <v>-6.28</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C104" s="7">
-        <v>62</v>
+        <v>32.87</v>
       </c>
       <c r="D104" s="7">
-        <v>50</v>
+        <v>32.06</v>
       </c>
       <c r="E104" s="8">
-        <v>-12</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C105" s="7">
-        <v>32</v>
+        <v>1019.6</v>
       </c>
       <c r="D105" s="7">
-        <v>38</v>
-      </c>
-      <c r="E105" s="9">
-        <v>6</v>
+        <v>998.4</v>
+      </c>
+      <c r="E105" s="8">
+        <v>-21.2</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="7">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="D106" s="7">
-        <v>31</v>
-      </c>
-      <c r="E106" s="9">
-        <v>5</v>
+        <v>87</v>
+      </c>
+      <c r="E106" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="7">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D107" s="7">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="E107" s="8">
-        <v>-5</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="7">
+        <v>38</v>
+      </c>
+      <c r="D108" s="7">
         <v>50</v>
       </c>
-      <c r="D108" s="7">
-        <v>56</v>
-      </c>
       <c r="E108" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D109" s="7">
-        <v>75</v>
-      </c>
-      <c r="E109" s="9">
-        <v>7</v>
+        <v>62</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-7</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C110" s="7">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="D110" s="7">
-        <v>13</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-6</v>
+        <v>81</v>
+      </c>
+      <c r="E110" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C111" s="7">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D111" s="7">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="E111" s="9">
         <v>6</v>
@@ -4776,586 +4816,620 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C112" s="7">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D112" s="7">
-        <v>25</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-13</v>
+        <v>69</v>
+      </c>
+      <c r="E112" s="9">
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="7">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D113" s="7">
-        <v>19</v>
-      </c>
-      <c r="E113" s="9">
-        <v>6</v>
+        <v>75</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C114" s="7">
-        <v>66.45999999999999</v>
+        <v>87</v>
       </c>
       <c r="D114" s="7">
-        <v>60.92</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-5.54</v>
+        <v>93</v>
+      </c>
+      <c r="E114" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C115" s="7">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D115" s="7">
-        <v>28.5</v>
+        <v>13</v>
       </c>
       <c r="E115" s="8">
-        <v>-4.5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="7">
-        <v>55.61</v>
+        <v>60.92</v>
       </c>
       <c r="D116" s="7">
-        <v>54.92</v>
+        <v>57.92</v>
       </c>
       <c r="E116" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="7">
-        <v>49.28</v>
+        <v>28.5</v>
       </c>
       <c r="D117" s="7">
-        <v>50.64</v>
-      </c>
-      <c r="E117" s="9">
-        <v>1.36</v>
+        <v>24.76</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-3.74</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="7">
-        <v>57.16</v>
+        <v>54.92</v>
       </c>
       <c r="D118" s="7">
-        <v>52.75</v>
+        <v>53.99</v>
       </c>
       <c r="E118" s="8">
-        <v>-4.41</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="7">
-        <v>47.64</v>
+        <v>50.64</v>
       </c>
       <c r="D119" s="7">
-        <v>43.64</v>
+        <v>42.04</v>
       </c>
       <c r="E119" s="8">
-        <v>-4</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="7">
-        <v>74.43000000000001</v>
+        <v>52.75</v>
       </c>
       <c r="D120" s="7">
-        <v>70.12</v>
+        <v>48.32</v>
       </c>
       <c r="E120" s="8">
-        <v>-4.31</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="7">
-        <v>41.97</v>
+        <v>43.64</v>
       </c>
       <c r="D121" s="7">
-        <v>39.09</v>
-      </c>
-      <c r="E121" s="8">
-        <v>-2.88</v>
+        <v>45.3</v>
+      </c>
+      <c r="E121" s="9">
+        <v>1.66</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="7">
-        <v>48.04</v>
+        <v>70.12</v>
       </c>
       <c r="D122" s="7">
-        <v>46.65</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-1.39</v>
+        <v>71.83</v>
+      </c>
+      <c r="E122" s="9">
+        <v>1.71</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="7">
-        <v>41.33</v>
+        <v>39.09</v>
       </c>
       <c r="D123" s="7">
-        <v>39.19</v>
+        <v>34.17</v>
       </c>
       <c r="E123" s="8">
-        <v>-2.14</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="7">
-        <v>73.52</v>
+        <v>46.65</v>
       </c>
       <c r="D124" s="7">
-        <v>72.98</v>
+        <v>46.42</v>
       </c>
       <c r="E124" s="8">
-        <v>-0.54</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="7">
-        <v>35.01</v>
+        <v>39.19</v>
       </c>
       <c r="D125" s="7">
-        <v>33.96</v>
+        <v>36.94</v>
       </c>
       <c r="E125" s="8">
-        <v>-1.05</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C126" s="7">
-        <v>61.73</v>
+        <v>72.98</v>
       </c>
       <c r="D126" s="7">
-        <v>54.3</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-7.43</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="E126" s="9">
+        <v>3.12</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C127" s="7">
-        <v>58.93</v>
+        <v>33.96</v>
       </c>
       <c r="D127" s="7">
-        <v>49.58</v>
+        <v>31.79</v>
       </c>
       <c r="E127" s="8">
-        <v>-9.35</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C128" s="7">
-        <v>39.62</v>
+        <v>54.3</v>
       </c>
       <c r="D128" s="7">
-        <v>35.77</v>
+        <v>47.86</v>
       </c>
       <c r="E128" s="8">
-        <v>-3.85</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C129" s="7">
-        <v>34.72</v>
+        <v>49.58</v>
       </c>
       <c r="D129" s="7">
-        <v>33.19</v>
+        <v>46.7</v>
       </c>
       <c r="E129" s="8">
-        <v>-1.53</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C130" s="7">
-        <v>164.5</v>
+        <v>35.77</v>
       </c>
       <c r="D130" s="7">
-        <v>-5.38</v>
+        <v>31.8</v>
       </c>
       <c r="E130" s="8">
-        <v>-169.88</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C131" s="7">
-        <v>-56.86</v>
+        <v>33.19</v>
       </c>
       <c r="D131" s="7">
-        <v>-41.61</v>
-      </c>
-      <c r="E131" s="9">
-        <v>15.25</v>
+        <v>30.02</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="7">
-        <v>-18.98</v>
+        <v>-5.38</v>
       </c>
       <c r="D132" s="7">
-        <v>-8.52</v>
+        <v>25.16</v>
       </c>
       <c r="E132" s="9">
-        <v>10.46</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="7">
-        <v>-71.86</v>
+        <v>-41.61</v>
       </c>
       <c r="D133" s="7">
-        <v>-25.81</v>
+        <v>-19.26</v>
       </c>
       <c r="E133" s="9">
-        <v>46.05</v>
+        <v>22.35</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="7">
-        <v>146.06</v>
+        <v>-8.52</v>
       </c>
       <c r="D134" s="7">
-        <v>-12.03</v>
-      </c>
-      <c r="E134" s="8">
-        <v>-158.09</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E134" s="9">
+        <v>5.47</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="7">
-        <v>7.18</v>
+        <v>-25.81</v>
       </c>
       <c r="D135" s="7">
-        <v>-61.38</v>
+        <v>-55.93</v>
       </c>
       <c r="E135" s="8">
-        <v>-68.56</v>
+        <v>-30.12</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="7">
-        <v>135.41</v>
+        <v>-12.03</v>
       </c>
       <c r="D136" s="7">
-        <v>-22.5</v>
+        <v>-44.84</v>
       </c>
       <c r="E136" s="8">
-        <v>-157.91</v>
+        <v>-32.81</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="7">
-        <v>-75.52</v>
+        <v>-61.38</v>
       </c>
       <c r="D137" s="7">
-        <v>-67.98999999999999</v>
+        <v>-45.76</v>
       </c>
       <c r="E137" s="9">
-        <v>7.53</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="7">
-        <v>-13.57</v>
+        <v>-22.5</v>
       </c>
       <c r="D138" s="7">
-        <v>-19.51</v>
+        <v>-39.01</v>
       </c>
       <c r="E138" s="8">
-        <v>-5.94</v>
+        <v>-16.51</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="7">
-        <v>82.06999999999999</v>
+        <v>-67.98999999999999</v>
       </c>
       <c r="D139" s="7">
-        <v>-47.74</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-129.81</v>
+        <v>-50.66</v>
+      </c>
+      <c r="E139" s="9">
+        <v>17.33</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C140" s="7">
-        <v>152.82</v>
+        <v>-19.51</v>
       </c>
       <c r="D140" s="7">
-        <v>64.95</v>
-      </c>
-      <c r="E140" s="8">
-        <v>-87.87</v>
+        <v>-6.82</v>
+      </c>
+      <c r="E140" s="9">
+        <v>12.69</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C141" s="7">
-        <v>-32.03</v>
+        <v>-47.74</v>
       </c>
       <c r="D141" s="7">
-        <v>-24.18</v>
+        <v>-7.76</v>
       </c>
       <c r="E141" s="9">
-        <v>7.85</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C142" s="7">
-        <v>-53.65</v>
+        <v>64.95</v>
       </c>
       <c r="D142" s="7">
-        <v>-27.41</v>
-      </c>
-      <c r="E142" s="9">
-        <v>26.24</v>
+        <v>3.41</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-61.54</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C143" s="7">
-        <v>111.71</v>
+        <v>-24.18</v>
       </c>
       <c r="D143" s="7">
-        <v>-53.09</v>
+        <v>-48.24</v>
       </c>
       <c r="E143" s="8">
-        <v>-164.8</v>
+        <v>-24.06</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C144" s="7">
-        <v>-85.48</v>
+        <v>-27.41</v>
       </c>
       <c r="D144" s="7">
-        <v>-85.78</v>
+        <v>-31.13</v>
       </c>
       <c r="E144" s="8">
-        <v>-0.3</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C145" s="7">
-        <v>-26.83</v>
+        <v>-53.09</v>
       </c>
       <c r="D145" s="7">
+        <v>-79.3</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-26.21</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="7">
+        <v>-85.78</v>
+      </c>
+      <c r="D146" s="7">
+        <v>-83.98</v>
+      </c>
+      <c r="E146" s="9">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147" s="7">
         <v>-49.56</v>
       </c>
-      <c r="E145" s="8">
-        <v>-22.73</v>
+      <c r="D147" s="7">
+        <v>-31.82</v>
+      </c>
+      <c r="E147" s="9">
+        <v>17.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5379,28 +5453,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5408,22 +5482,22 @@
         <v>53</v>
       </c>
       <c r="B2" s="12">
-        <v>43.72</v>
+        <v>38.76000000000001</v>
       </c>
       <c r="C2" s="13">
         <v>16</v>
       </c>
       <c r="D2" s="12">
-        <v>47.9</v>
+        <v>45.4</v>
       </c>
       <c r="E2" s="12">
-        <v>31.2</v>
+        <v>18.8</v>
       </c>
       <c r="F2" s="12">
-        <v>-4.4</v>
+        <v>-4.2</v>
       </c>
       <c r="G2" s="12">
-        <v>-7.2</v>
+        <v>-8</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -5546,10 +5620,10 @@
         <v>45</v>
       </c>
       <c r="F1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>50</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>41</v>
@@ -5563,34 +5637,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.3206</v>
+        <v>0.3240999999999999</v>
       </c>
       <c r="B2" s="15">
-        <v>0.2982</v>
+        <v>0.2968</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2107</v>
+        <v>0.2129</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1252</v>
+        <v>0.1313</v>
       </c>
       <c r="E2" s="15">
-        <v>0.0953</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F2" s="15">
-        <v>0.08289999999999999</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G2" s="15">
-        <v>0.08109999999999999</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="H2" s="15">
-        <v>0.04019999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="I2" s="15">
-        <v>0.0362</v>
+        <v>0.0442</v>
       </c>
       <c r="J2" s="15">
-        <v>-0.0364</v>
+        <v>-0.0258</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5604,10 +5678,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>43</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>51</v>
@@ -5615,22 +5689,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>-0.0438</v>
+        <v>-0.0303</v>
       </c>
       <c r="B4" s="15">
-        <v>-0.05</v>
+        <v>-0.0394</v>
       </c>
       <c r="C4" s="15">
-        <v>-0.0653</v>
+        <v>-0.0478</v>
       </c>
       <c r="D4" s="15">
-        <v>-0.08699999999999999</v>
+        <v>-0.0727</v>
       </c>
       <c r="E4" s="15">
-        <v>-0.08699999999999999</v>
+        <v>-0.083</v>
       </c>
       <c r="F4" s="15">
-        <v>-0.1011</v>
+        <v>-0.08710000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="87">
   <si>
     <t>Symbol</t>
   </si>
@@ -214,34 +214,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>71.7 → 61.5</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>71.7</t>
-  </si>
-  <si>
-    <t>61.5</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.2 → 35.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>35.4</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.0 → 30.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.0</t>
+  </si>
+  <si>
+    <t>30.6</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>61.9 → 71.6</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>61.9</t>
+  </si>
+  <si>
+    <t>71.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -327,7 +327,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -335,13 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -374,19 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,8 +467,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -980,37 +980,37 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>781.75</v>
+        <v>795.5</v>
       </c>
       <c r="D2">
-        <v>-0.07000000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="E2">
-        <v>782.3</v>
+        <v>795.5</v>
       </c>
       <c r="F2">
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>36.92</v>
+        <v>39.33</v>
       </c>
       <c r="I2">
-        <v>5.44</v>
+        <v>3.03</v>
       </c>
       <c r="J2">
-        <v>6.18</v>
+        <v>6.97</v>
       </c>
       <c r="K2">
-        <v>7.97</v>
+        <v>9.35</v>
       </c>
       <c r="L2">
-        <v>6.3</v>
+        <v>7.07</v>
       </c>
       <c r="M2">
-        <v>31.71</v>
+        <v>31.93</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -1019,19 +1019,19 @@
         <v>83</v>
       </c>
       <c r="P2">
-        <v>769.83</v>
+        <v>774.51</v>
       </c>
       <c r="Q2">
-        <v>734.9400000000001</v>
+        <v>738.28</v>
       </c>
       <c r="R2">
-        <v>728.78</v>
+        <v>730.21</v>
       </c>
       <c r="S2">
-        <v>688.61</v>
+        <v>688.87</v>
       </c>
       <c r="T2">
-        <v>13.53</v>
+        <v>15.48</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1046,34 +1046,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>65.33</v>
+        <v>68.44</v>
       </c>
       <c r="Z2">
-        <v>11.91</v>
+        <v>14.55</v>
       </c>
       <c r="AA2">
-        <v>5.57</v>
+        <v>7.37</v>
       </c>
       <c r="AB2">
-        <v>6.34</v>
+        <v>7.18</v>
       </c>
       <c r="AC2">
-        <v>84.14</v>
+        <v>96.98</v>
       </c>
       <c r="AD2">
-        <v>80.16</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="AE2">
-        <v>21.05</v>
+        <v>21.78</v>
       </c>
       <c r="AF2">
-        <v>133.92</v>
+        <v>13.84</v>
       </c>
       <c r="AG2">
-        <v>780.88</v>
+        <v>791.45</v>
       </c>
       <c r="AH2">
-        <v>689.01</v>
+        <v>685.1</v>
       </c>
       <c r="AI2">
         <v>716.26</v>
@@ -1082,7 +1082,7 @@
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>34.21</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1093,10 +1093,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>692.55</v>
+        <v>700.65</v>
       </c>
       <c r="D3">
-        <v>-6.02</v>
+        <v>1.17</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1105,46 +1105,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-35.96</v>
+        <v>-35.21</v>
       </c>
       <c r="H3">
-        <v>37.04</v>
+        <v>38.64</v>
       </c>
       <c r="I3">
-        <v>-16.7</v>
+        <v>-15.03</v>
       </c>
       <c r="J3">
-        <v>-31.55</v>
+        <v>-31.36</v>
       </c>
       <c r="K3">
-        <v>-25.84</v>
+        <v>-24.89</v>
       </c>
       <c r="L3">
-        <v>-20.22</v>
+        <v>-18.59</v>
       </c>
       <c r="M3">
-        <v>-2.47</v>
+        <v>-2.19</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P3">
-        <v>758.74</v>
+        <v>733.96</v>
       </c>
       <c r="Q3">
-        <v>861.49</v>
+        <v>846.87</v>
       </c>
       <c r="R3">
-        <v>919.84</v>
+        <v>914.37</v>
       </c>
       <c r="S3">
-        <v>772.54</v>
+        <v>772.46</v>
       </c>
       <c r="T3">
-        <v>-10.35</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1159,43 +1159,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>20.03</v>
+        <v>22.27</v>
       </c>
       <c r="Z3">
-        <v>-53.76</v>
+        <v>-58.06</v>
       </c>
       <c r="AA3">
-        <v>-36.04</v>
+        <v>-40.44</v>
       </c>
       <c r="AB3">
-        <v>-17.72</v>
+        <v>-17.62</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AE3">
-        <v>46.89</v>
+        <v>45.66</v>
       </c>
       <c r="AF3">
-        <v>53.62</v>
+        <v>-4.53</v>
       </c>
       <c r="AG3">
-        <v>1015.47</v>
+        <v>1003.75</v>
       </c>
       <c r="AH3">
-        <v>707.51</v>
+        <v>689.99</v>
       </c>
       <c r="AI3">
-        <v>854.8099999999999</v>
+        <v>838.98</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>60.32</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1206,58 +1206,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>194.57</v>
+        <v>192.84</v>
       </c>
       <c r="D4">
-        <v>-4.44</v>
+        <v>-0.89</v>
       </c>
       <c r="E4">
         <v>291.61</v>
       </c>
       <c r="F4">
-        <v>194.57</v>
+        <v>192.84</v>
       </c>
       <c r="G4">
-        <v>-33.28</v>
+        <v>-33.87</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.2</v>
+        <v>-5.9</v>
       </c>
       <c r="J4">
-        <v>-3.65</v>
+        <v>-4.83</v>
       </c>
       <c r="K4">
-        <v>-12.34</v>
+        <v>-11.83</v>
       </c>
       <c r="L4">
-        <v>-30.21</v>
+        <v>-32.3</v>
       </c>
       <c r="M4">
-        <v>-4.71</v>
+        <v>-4.84</v>
       </c>
       <c r="N4">
         <v>44</v>
       </c>
       <c r="O4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>202.41</v>
+        <v>199.99</v>
       </c>
       <c r="Q4">
-        <v>200.34</v>
+        <v>199.97</v>
       </c>
       <c r="R4">
-        <v>204.87</v>
+        <v>204.54</v>
       </c>
       <c r="S4">
-        <v>235.36</v>
+        <v>234.99</v>
       </c>
       <c r="T4">
-        <v>-17.33</v>
+        <v>-17.94</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
@@ -1272,43 +1272,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.39</v>
+        <v>33.19</v>
       </c>
       <c r="Z4">
-        <v>-1.01</v>
+        <v>-1.59</v>
       </c>
       <c r="AA4">
-        <v>-1.36</v>
+        <v>-1.41</v>
       </c>
       <c r="AB4">
-        <v>0.35</v>
+        <v>-0.18</v>
       </c>
       <c r="AC4">
-        <v>70.59</v>
+        <v>42.44</v>
       </c>
       <c r="AD4">
-        <v>87.06999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="AE4">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AF4">
-        <v>395.13</v>
+        <v>-1.34</v>
       </c>
       <c r="AG4">
-        <v>205.84</v>
+        <v>206.41</v>
       </c>
       <c r="AH4">
-        <v>194.84</v>
+        <v>193.52</v>
       </c>
       <c r="AI4">
-        <v>207.87</v>
+        <v>206.85</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>29.46</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1319,10 +1319,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>576.8</v>
+        <v>595.45</v>
       </c>
       <c r="D5">
-        <v>-2.91</v>
+        <v>3.23</v>
       </c>
       <c r="E5">
         <v>899.08</v>
@@ -1331,46 +1331,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-35.85</v>
+        <v>-33.77</v>
       </c>
       <c r="H5">
-        <v>0.41</v>
+        <v>3.66</v>
       </c>
       <c r="I5">
-        <v>-8.199999999999999</v>
+        <v>-5.95</v>
       </c>
       <c r="J5">
-        <v>-14.42</v>
+        <v>-11.11</v>
       </c>
       <c r="K5">
-        <v>-15.1</v>
+        <v>-13.12</v>
       </c>
       <c r="L5">
-        <v>-35.12</v>
+        <v>-33.06</v>
       </c>
       <c r="M5">
-        <v>-8.779999999999999</v>
+        <v>-8.67</v>
       </c>
       <c r="N5">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="O5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P5">
-        <v>609.52</v>
+        <v>601.98</v>
       </c>
       <c r="Q5">
-        <v>618.46</v>
+        <v>615.62</v>
       </c>
       <c r="R5">
-        <v>639.98</v>
+        <v>638.4299999999999</v>
       </c>
       <c r="S5">
-        <v>689.35</v>
+        <v>688.65</v>
       </c>
       <c r="T5">
-        <v>-16.33</v>
+        <v>-13.53</v>
       </c>
       <c r="U5" t="s">
         <v>55</v>
@@ -1385,34 +1385,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35.76</v>
+        <v>41.92</v>
       </c>
       <c r="Z5">
-        <v>-12.72</v>
+        <v>-13.21</v>
       </c>
       <c r="AA5">
-        <v>-10.01</v>
+        <v>-10.65</v>
       </c>
       <c r="AB5">
-        <v>-2.71</v>
+        <v>-2.56</v>
       </c>
       <c r="AC5">
-        <v>20.79</v>
+        <v>21.11</v>
       </c>
       <c r="AD5">
-        <v>51.17</v>
+        <v>32.01</v>
       </c>
       <c r="AE5">
-        <v>25.5</v>
+        <v>27.63</v>
       </c>
       <c r="AF5">
-        <v>-56.92</v>
+        <v>609.33</v>
       </c>
       <c r="AG5">
-        <v>659.01</v>
+        <v>654.12</v>
       </c>
       <c r="AH5">
-        <v>577.92</v>
+        <v>577.13</v>
       </c>
       <c r="AI5">
         <v>660.54</v>
@@ -1421,7 +1421,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>19.04</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1432,10 +1432,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1654.4</v>
+        <v>1681.2</v>
       </c>
       <c r="D6">
-        <v>-1.66</v>
+        <v>1.62</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1444,46 +1444,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-19.76</v>
+        <v>-18.46</v>
       </c>
       <c r="H6">
-        <v>22.74</v>
+        <v>24.73</v>
       </c>
       <c r="I6">
-        <v>-6.2</v>
+        <v>-3.53</v>
       </c>
       <c r="J6">
-        <v>-2.25</v>
+        <v>-1.14</v>
       </c>
       <c r="K6">
-        <v>-8.119999999999999</v>
+        <v>-5.3</v>
       </c>
       <c r="L6">
-        <v>-14.14</v>
+        <v>-11.75</v>
       </c>
       <c r="M6">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="N6">
         <v>62</v>
       </c>
       <c r="O6">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P6">
-        <v>1697.96</v>
+        <v>1685.64</v>
       </c>
       <c r="Q6">
-        <v>1679.29</v>
+        <v>1679.85</v>
       </c>
       <c r="R6">
-        <v>1705.39</v>
+        <v>1704.29</v>
       </c>
       <c r="S6">
-        <v>1697.7</v>
+        <v>1697.09</v>
       </c>
       <c r="T6">
-        <v>-2.55</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>55</v>
@@ -1498,34 +1498,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.64</v>
+        <v>47.5</v>
       </c>
       <c r="Z6">
-        <v>-7</v>
+        <v>-7.13</v>
       </c>
       <c r="AA6">
-        <v>-8.43</v>
+        <v>-8.17</v>
       </c>
       <c r="AB6">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="AC6">
-        <v>30.33</v>
+        <v>27</v>
       </c>
       <c r="AD6">
-        <v>47.48</v>
+        <v>34.99</v>
       </c>
       <c r="AE6">
-        <v>62.15</v>
+        <v>61.8</v>
       </c>
       <c r="AF6">
-        <v>-40.62</v>
+        <v>-56.48</v>
       </c>
       <c r="AG6">
-        <v>1739.31</v>
+        <v>1739.71</v>
       </c>
       <c r="AH6">
-        <v>1619.28</v>
+        <v>1620</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1534,7 +1534,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>29.58</v>
+        <v>25.91</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1545,58 +1545,58 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>963.9</v>
+        <v>936.5</v>
       </c>
       <c r="D7">
-        <v>0.43</v>
+        <v>-2.84</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
       </c>
       <c r="F7">
-        <v>949.5</v>
+        <v>936.5</v>
       </c>
       <c r="G7">
-        <v>-23.52</v>
+        <v>-25.69</v>
       </c>
       <c r="H7">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-2.78</v>
+        <v>-4.33</v>
       </c>
       <c r="J7">
-        <v>-2.05</v>
+        <v>-5.81</v>
       </c>
       <c r="K7">
-        <v>-12.98</v>
+        <v>-13.92</v>
       </c>
       <c r="L7">
-        <v>-16.63</v>
+        <v>-19.72</v>
       </c>
       <c r="M7">
-        <v>4.96</v>
+        <v>3.83</v>
       </c>
       <c r="N7">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O7">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>967.95</v>
+        <v>959.47</v>
       </c>
       <c r="Q7">
-        <v>967.34</v>
+        <v>964.85</v>
       </c>
       <c r="R7">
-        <v>1004.87</v>
+        <v>1002.37</v>
       </c>
       <c r="S7">
-        <v>1094.78</v>
+        <v>1093.6</v>
       </c>
       <c r="T7">
-        <v>-11.96</v>
+        <v>-14.37</v>
       </c>
       <c r="U7" t="s">
         <v>55</v>
@@ -1611,43 +1611,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>43.59</v>
+        <v>35.82</v>
       </c>
       <c r="Z7">
-        <v>-9.91</v>
+        <v>-11.79</v>
       </c>
       <c r="AA7">
-        <v>-12.61</v>
+        <v>-12.44</v>
       </c>
       <c r="AB7">
-        <v>2.69</v>
+        <v>0.65</v>
       </c>
       <c r="AC7">
-        <v>56.98</v>
+        <v>34.01</v>
       </c>
       <c r="AD7">
-        <v>61.94</v>
+        <v>49.97</v>
       </c>
       <c r="AE7">
-        <v>18.96</v>
+        <v>21.03</v>
       </c>
       <c r="AF7">
-        <v>14.73</v>
+        <v>75.75</v>
       </c>
       <c r="AG7">
-        <v>992.83</v>
+        <v>992.2</v>
       </c>
       <c r="AH7">
-        <v>941.85</v>
+        <v>937.49</v>
       </c>
       <c r="AI7">
-        <v>1007.9</v>
+        <v>1001.09</v>
       </c>
       <c r="AJ7" t="s">
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>24.98</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1658,10 +1658,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3700</v>
+        <v>3724</v>
       </c>
       <c r="D8">
-        <v>-3.82</v>
+        <v>0.65</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1670,46 +1670,46 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-35.65</v>
+        <v>-35.23</v>
       </c>
       <c r="H8">
-        <v>23.5</v>
+        <v>24.3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-3.28</v>
       </c>
       <c r="J8">
-        <v>14.91</v>
+        <v>15.94</v>
       </c>
       <c r="K8">
-        <v>9.220000000000001</v>
+        <v>5.26</v>
       </c>
       <c r="L8">
-        <v>-29.86</v>
+        <v>-29.77</v>
       </c>
       <c r="M8">
-        <v>-7.69</v>
+        <v>-7.77</v>
       </c>
       <c r="N8">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="O8">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P8">
-        <v>3807.1</v>
+        <v>3781.88</v>
       </c>
       <c r="Q8">
-        <v>3370.2</v>
+        <v>3397.21</v>
       </c>
       <c r="R8">
-        <v>3474.89</v>
+        <v>3475.13</v>
       </c>
       <c r="S8">
-        <v>4109.83</v>
+        <v>4102.11</v>
       </c>
       <c r="T8">
-        <v>-9.970000000000001</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="U8" t="s">
         <v>55</v>
@@ -1724,34 +1724,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>61.49</v>
+        <v>62.43</v>
       </c>
       <c r="Z8">
-        <v>114.23</v>
+        <v>115.94</v>
       </c>
       <c r="AA8">
-        <v>38.83</v>
+        <v>54.25</v>
       </c>
       <c r="AB8">
-        <v>75.40000000000001</v>
+        <v>61.69</v>
       </c>
       <c r="AC8">
-        <v>88.64</v>
+        <v>82.8</v>
       </c>
       <c r="AD8">
-        <v>92.79000000000001</v>
+        <v>88.48</v>
       </c>
       <c r="AE8">
-        <v>120.5</v>
+        <v>118.58</v>
       </c>
       <c r="AF8">
-        <v>-42.86</v>
+        <v>-64.51000000000001</v>
       </c>
       <c r="AG8">
-        <v>3997.53</v>
+        <v>4037.14</v>
       </c>
       <c r="AH8">
-        <v>2742.86</v>
+        <v>2757.27</v>
       </c>
       <c r="AI8">
         <v>3518.36</v>
@@ -1760,7 +1760,7 @@
         <v>56</v>
       </c>
       <c r="AK8">
-        <v>58.43</v>
+        <v>53.37</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1771,10 +1771,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>548.5</v>
+        <v>553.35</v>
       </c>
       <c r="D9">
-        <v>-2.86</v>
+        <v>0.88</v>
       </c>
       <c r="E9">
         <v>870.51</v>
@@ -1783,46 +1783,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-36.99</v>
+        <v>-36.43</v>
       </c>
       <c r="H9">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="I9">
-        <v>-10.22</v>
+        <v>-9.81</v>
       </c>
       <c r="J9">
-        <v>-19.6</v>
+        <v>-17.94</v>
       </c>
       <c r="K9">
-        <v>-13.24</v>
+        <v>-12.27</v>
       </c>
       <c r="L9">
-        <v>-37.98</v>
+        <v>-30.91</v>
       </c>
       <c r="M9">
-        <v>31.14</v>
+        <v>30.59</v>
       </c>
       <c r="N9">
         <v>19</v>
       </c>
       <c r="O9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P9">
-        <v>583.61</v>
+        <v>571.5700000000001</v>
       </c>
       <c r="Q9">
-        <v>613.5599999999999</v>
+        <v>608.3099999999999</v>
       </c>
       <c r="R9">
-        <v>639.21</v>
+        <v>636.66</v>
       </c>
       <c r="S9">
-        <v>653.92</v>
+        <v>653.22</v>
       </c>
       <c r="T9">
-        <v>-16.12</v>
+        <v>-15.29</v>
       </c>
       <c r="U9" t="s">
         <v>55</v>
@@ -1837,43 +1837,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>26.2</v>
+        <v>28.57</v>
       </c>
       <c r="Z9">
-        <v>-20.18</v>
+        <v>-22.17</v>
       </c>
       <c r="AA9">
-        <v>-14.16</v>
+        <v>-15.76</v>
       </c>
       <c r="AB9">
-        <v>-6.03</v>
+        <v>-6.41</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AD9">
-        <v>17.89</v>
+        <v>6.5</v>
       </c>
       <c r="AE9">
-        <v>20.28</v>
+        <v>20.2</v>
       </c>
       <c r="AF9">
-        <v>25.99</v>
+        <v>-7.26</v>
       </c>
       <c r="AG9">
-        <v>664.9299999999999</v>
+        <v>661.8200000000001</v>
       </c>
       <c r="AH9">
-        <v>562.1900000000001</v>
+        <v>554.8</v>
       </c>
       <c r="AI9">
-        <v>615.87</v>
+        <v>613.48</v>
       </c>
       <c r="AJ9" t="s">
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>28.54</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1884,10 +1884,10 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>348.1</v>
+        <v>338.5</v>
       </c>
       <c r="D10">
-        <v>-1.53</v>
+        <v>-2.76</v>
       </c>
       <c r="E10">
         <v>461.8</v>
@@ -1896,46 +1896,46 @@
         <v>335.65</v>
       </c>
       <c r="G10">
-        <v>-24.62</v>
+        <v>-26.7</v>
       </c>
       <c r="H10">
-        <v>3.71</v>
+        <v>0.85</v>
       </c>
       <c r="I10">
-        <v>-0.49</v>
+        <v>-4.34</v>
       </c>
       <c r="J10">
-        <v>-5.15</v>
+        <v>-8.27</v>
       </c>
       <c r="K10">
-        <v>-7.46</v>
+        <v>-9.59</v>
       </c>
       <c r="L10">
-        <v>-12.49</v>
+        <v>-15.33</v>
       </c>
       <c r="M10">
-        <v>10.89</v>
+        <v>9.09</v>
       </c>
       <c r="N10">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="O10">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P10">
-        <v>351.94</v>
+        <v>348.87</v>
       </c>
       <c r="Q10">
-        <v>351.91</v>
+        <v>350.67</v>
       </c>
       <c r="R10">
-        <v>361.68</v>
+        <v>360.86</v>
       </c>
       <c r="S10">
-        <v>384.38</v>
+        <v>384.13</v>
       </c>
       <c r="T10">
-        <v>-9.44</v>
+        <v>-11.88</v>
       </c>
       <c r="U10" t="s">
         <v>55</v>
@@ -1950,34 +1950,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>42.97</v>
+        <v>35.73</v>
       </c>
       <c r="Z10">
-        <v>-3.53</v>
+        <v>-4.26</v>
       </c>
       <c r="AA10">
-        <v>-4.42</v>
+        <v>-4.39</v>
       </c>
       <c r="AB10">
-        <v>0.9</v>
+        <v>0.13</v>
       </c>
       <c r="AC10">
-        <v>89.33</v>
+        <v>72.33</v>
       </c>
       <c r="AD10">
-        <v>93.23999999999999</v>
+        <v>85.62</v>
       </c>
       <c r="AE10">
-        <v>7.68</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AF10">
-        <v>4.51</v>
+        <v>132.69</v>
       </c>
       <c r="AG10">
-        <v>367.32</v>
+        <v>366.18</v>
       </c>
       <c r="AH10">
-        <v>336.51</v>
+        <v>335.16</v>
       </c>
       <c r="AI10">
         <v>362.14</v>
@@ -1986,7 +1986,7 @@
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>23.4</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1997,10 +1997,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>167.67</v>
+        <v>169.94</v>
       </c>
       <c r="D11">
-        <v>-2.7</v>
+        <v>1.35</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2009,46 +2009,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-22.61</v>
+        <v>-21.56</v>
       </c>
       <c r="H11">
-        <v>6.51</v>
+        <v>7.95</v>
       </c>
       <c r="I11">
-        <v>-4.95</v>
+        <v>-3.17</v>
       </c>
       <c r="J11">
-        <v>-9.35</v>
+        <v>-10.94</v>
       </c>
       <c r="K11">
-        <v>-8.99</v>
+        <v>-6.97</v>
       </c>
       <c r="L11">
-        <v>-0.63</v>
+        <v>0.87</v>
       </c>
       <c r="M11">
-        <v>8.51</v>
+        <v>7.96</v>
       </c>
       <c r="N11">
         <v>75</v>
       </c>
       <c r="O11">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P11">
-        <v>172.4</v>
+        <v>171.29</v>
       </c>
       <c r="Q11">
-        <v>177.55</v>
+        <v>176.64</v>
       </c>
       <c r="R11">
-        <v>182.29</v>
+        <v>181.96</v>
       </c>
       <c r="S11">
-        <v>192.27</v>
+        <v>192.21</v>
       </c>
       <c r="T11">
-        <v>-12.8</v>
+        <v>-11.59</v>
       </c>
       <c r="U11" t="s">
         <v>55</v>
@@ -2063,34 +2063,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>30.79</v>
+        <v>36.23</v>
       </c>
       <c r="Z11">
-        <v>-3.57</v>
+        <v>-3.64</v>
       </c>
       <c r="AA11">
-        <v>-3.02</v>
+        <v>-3.15</v>
       </c>
       <c r="AB11">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="AC11">
-        <v>27.6</v>
+        <v>30.88</v>
       </c>
       <c r="AD11">
-        <v>35.36</v>
+        <v>32.65</v>
       </c>
       <c r="AE11">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="AF11">
-        <v>29.83</v>
+        <v>-5.64</v>
       </c>
       <c r="AG11">
-        <v>189.8</v>
+        <v>188.3</v>
       </c>
       <c r="AH11">
-        <v>165.29</v>
+        <v>164.99</v>
       </c>
       <c r="AI11">
         <v>181.43</v>
@@ -2099,7 +2099,7 @@
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>33.76</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2110,10 +2110,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2530</v>
+        <v>2535</v>
       </c>
       <c r="D12">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2122,46 +2122,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-21.47</v>
+        <v>-21.32</v>
       </c>
       <c r="H12">
-        <v>27.61</v>
+        <v>27.86</v>
       </c>
       <c r="I12">
-        <v>7.66</v>
+        <v>2.84</v>
       </c>
       <c r="J12">
-        <v>20.19</v>
+        <v>21.32</v>
       </c>
       <c r="K12">
-        <v>12.8</v>
+        <v>12.45</v>
       </c>
       <c r="L12">
-        <v>-11.86</v>
+        <v>-13.24</v>
       </c>
       <c r="M12">
-        <v>-3.72</v>
+        <v>-3.62</v>
       </c>
       <c r="N12">
         <v>93</v>
       </c>
       <c r="O12">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P12">
-        <v>2498.36</v>
+        <v>2512.36</v>
       </c>
       <c r="Q12">
-        <v>2223.27</v>
+        <v>2245.67</v>
       </c>
       <c r="R12">
-        <v>2248.22</v>
+        <v>2251.92</v>
       </c>
       <c r="S12">
-        <v>2422.67</v>
+        <v>2419.77</v>
       </c>
       <c r="T12">
-        <v>4.43</v>
+        <v>4.76</v>
       </c>
       <c r="U12" t="s">
         <v>55</v>
@@ -2176,34 +2176,34 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>74.27</v>
+        <v>74.52</v>
       </c>
       <c r="Z12">
-        <v>84.68000000000001</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="AA12">
-        <v>35.44</v>
+        <v>46.7</v>
       </c>
       <c r="AB12">
-        <v>49.24</v>
+        <v>45.06</v>
       </c>
       <c r="AC12">
-        <v>95.94</v>
+        <v>94.55</v>
       </c>
       <c r="AD12">
-        <v>97.56999999999999</v>
+        <v>95.88</v>
       </c>
       <c r="AE12">
-        <v>75.92</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AF12">
-        <v>23.6</v>
+        <v>-24.12</v>
       </c>
       <c r="AG12">
-        <v>2590.66</v>
+        <v>2632.21</v>
       </c>
       <c r="AH12">
-        <v>1855.88</v>
+        <v>1859.13</v>
       </c>
       <c r="AI12">
         <v>2343.34</v>
@@ -2212,7 +2212,7 @@
         <v>56</v>
       </c>
       <c r="AK12">
-        <v>66</v>
+        <v>67.01000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2223,10 +2223,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4299.7</v>
+        <v>4323</v>
       </c>
       <c r="D13">
-        <v>-1.16</v>
+        <v>0.54</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2235,46 +2235,46 @@
         <v>3714.9</v>
       </c>
       <c r="G13">
-        <v>-16.82</v>
+        <v>-16.37</v>
       </c>
       <c r="H13">
-        <v>15.74</v>
+        <v>16.37</v>
       </c>
       <c r="I13">
-        <v>-3.5</v>
+        <v>-2.74</v>
       </c>
       <c r="J13">
-        <v>-12.76</v>
+        <v>-11.41</v>
       </c>
       <c r="K13">
-        <v>-8.460000000000001</v>
+        <v>-7.57</v>
       </c>
       <c r="L13">
-        <v>17.01</v>
+        <v>15.67</v>
       </c>
       <c r="M13">
-        <v>12.88</v>
+        <v>12.28</v>
       </c>
       <c r="N13">
         <v>87</v>
       </c>
       <c r="O13">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P13">
-        <v>4379.92</v>
+        <v>4355.56</v>
       </c>
       <c r="Q13">
-        <v>4513.83</v>
+        <v>4488.36</v>
       </c>
       <c r="R13">
-        <v>4816.26</v>
+        <v>4800.74</v>
       </c>
       <c r="S13">
-        <v>4440.95</v>
+        <v>4442.17</v>
       </c>
       <c r="T13">
-        <v>-3.18</v>
+        <v>-2.68</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2289,34 +2289,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>28.02</v>
+        <v>30.64</v>
       </c>
       <c r="Z13">
-        <v>-131.13</v>
+        <v>-130.17</v>
       </c>
       <c r="AA13">
-        <v>-127.39</v>
+        <v>-127.95</v>
       </c>
       <c r="AB13">
-        <v>-3.74</v>
+        <v>-2.22</v>
       </c>
       <c r="AC13">
-        <v>44.82</v>
+        <v>41.52</v>
       </c>
       <c r="AD13">
-        <v>57.86</v>
+        <v>49.37</v>
       </c>
       <c r="AE13">
-        <v>93.22</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="AF13">
-        <v>-23.36</v>
+        <v>-52.05</v>
       </c>
       <c r="AG13">
-        <v>4853.31</v>
+        <v>4802.69</v>
       </c>
       <c r="AH13">
-        <v>4174.35</v>
+        <v>4174.02</v>
       </c>
       <c r="AI13">
         <v>4559.15</v>
@@ -2325,7 +2325,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>55.77</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2336,58 +2336,58 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2727.5</v>
+        <v>2754</v>
       </c>
       <c r="D14">
-        <v>-1.74</v>
+        <v>0.97</v>
       </c>
       <c r="E14">
-        <v>4795.21</v>
+        <v>4791.62</v>
       </c>
       <c r="F14">
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-43.12</v>
+        <v>-42.52</v>
       </c>
       <c r="H14">
-        <v>24.32</v>
+        <v>25.53</v>
       </c>
       <c r="I14">
-        <v>-7.53</v>
+        <v>-6.92</v>
       </c>
       <c r="J14">
-        <v>-1.99</v>
+        <v>-0.72</v>
       </c>
       <c r="K14">
-        <v>-5.12</v>
+        <v>-4.72</v>
       </c>
       <c r="L14">
-        <v>-43.26</v>
+        <v>-42.57</v>
       </c>
       <c r="M14">
-        <v>21.87</v>
+        <v>21.58</v>
       </c>
       <c r="N14">
         <v>38</v>
       </c>
       <c r="O14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P14">
-        <v>2835.12</v>
+        <v>2794.18</v>
       </c>
       <c r="Q14">
-        <v>2799.99</v>
+        <v>2802.69</v>
       </c>
       <c r="R14">
-        <v>2839.99</v>
+        <v>2835.33</v>
       </c>
       <c r="S14">
-        <v>2778.72</v>
+        <v>2777.75</v>
       </c>
       <c r="T14">
-        <v>-1.84</v>
+        <v>-0.85</v>
       </c>
       <c r="U14" t="s">
         <v>55</v>
@@ -2402,34 +2402,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>40.55</v>
+        <v>43.26</v>
       </c>
       <c r="Z14">
-        <v>6.69</v>
+        <v>-0.57</v>
       </c>
       <c r="AA14">
-        <v>13.97</v>
+        <v>11.06</v>
       </c>
       <c r="AB14">
-        <v>-7.28</v>
+        <v>-11.63</v>
       </c>
       <c r="AC14">
-        <v>47.85</v>
+        <v>32.52</v>
       </c>
       <c r="AD14">
-        <v>60.17</v>
+        <v>46.5</v>
       </c>
       <c r="AE14">
-        <v>75.75</v>
+        <v>76.31</v>
       </c>
       <c r="AF14">
-        <v>-33.82</v>
+        <v>-28.54</v>
       </c>
       <c r="AG14">
-        <v>3087.26</v>
+        <v>3087</v>
       </c>
       <c r="AH14">
-        <v>2512.72</v>
+        <v>2518.38</v>
       </c>
       <c r="AI14">
         <v>2952.95</v>
@@ -2438,7 +2438,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>36.15</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2449,10 +2449,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>197.86</v>
+        <v>207.16</v>
       </c>
       <c r="D15">
-        <v>-5.12</v>
+        <v>4.7</v>
       </c>
       <c r="E15">
         <v>342.75</v>
@@ -2461,46 +2461,46 @@
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-42.27</v>
+        <v>-39.56</v>
       </c>
       <c r="H15">
-        <v>3.17</v>
+        <v>8.02</v>
       </c>
       <c r="I15">
-        <v>-10.24</v>
+        <v>-10.86</v>
       </c>
       <c r="J15">
-        <v>-8.42</v>
+        <v>-4.23</v>
       </c>
       <c r="K15">
-        <v>-14.91</v>
+        <v>-11.07</v>
       </c>
       <c r="L15">
-        <v>-41.44</v>
+        <v>-38.13</v>
       </c>
       <c r="M15">
-        <v>8.6</v>
+        <v>8.75</v>
       </c>
       <c r="N15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="O15">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="P15">
-        <v>212.5</v>
+        <v>207.45</v>
       </c>
       <c r="Q15">
-        <v>209.21</v>
+        <v>208.82</v>
       </c>
       <c r="R15">
-        <v>219.31</v>
+        <v>218.85</v>
       </c>
       <c r="S15">
-        <v>242.68</v>
+        <v>242.2</v>
       </c>
       <c r="T15">
-        <v>-18.47</v>
+        <v>-14.47</v>
       </c>
       <c r="U15" t="s">
         <v>55</v>
@@ -2515,34 +2515,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>41.85</v>
+        <v>46.95</v>
       </c>
       <c r="Z15">
-        <v>-1.87</v>
+        <v>-2.08</v>
       </c>
       <c r="AA15">
-        <v>-1.76</v>
+        <v>-1.83</v>
       </c>
       <c r="AB15">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AC15">
-        <v>58.35</v>
+        <v>56.62</v>
       </c>
       <c r="AD15">
-        <v>67.01000000000001</v>
+        <v>60.38</v>
       </c>
       <c r="AE15">
-        <v>12.87</v>
+        <v>12.93</v>
       </c>
       <c r="AF15">
-        <v>-61.37</v>
+        <v>-55.7</v>
       </c>
       <c r="AG15">
-        <v>234.63</v>
+        <v>234.09</v>
       </c>
       <c r="AH15">
-        <v>183.8</v>
+        <v>183.54</v>
       </c>
       <c r="AI15">
         <v>197.45</v>
@@ -2551,7 +2551,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>32.42</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2562,10 +2562,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>37.68</v>
+        <v>41.53</v>
       </c>
       <c r="D16">
-        <v>-0.87</v>
+        <v>10.22</v>
       </c>
       <c r="E16">
         <v>56.01</v>
@@ -2574,46 +2574,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-32.73</v>
+        <v>-25.85</v>
       </c>
       <c r="H16">
-        <v>20.15</v>
+        <v>32.43</v>
       </c>
       <c r="I16">
-        <v>12.61</v>
+        <v>23.79</v>
       </c>
       <c r="J16">
-        <v>5.78</v>
+        <v>16.56</v>
       </c>
       <c r="K16">
-        <v>-4.37</v>
+        <v>5.46</v>
       </c>
       <c r="L16">
-        <v>-32.07</v>
+        <v>-24.6</v>
       </c>
       <c r="M16">
-        <v>-5.68</v>
+        <v>-4.74</v>
       </c>
       <c r="N16">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="O16">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="P16">
-        <v>34.83</v>
+        <v>36.43</v>
       </c>
       <c r="Q16">
-        <v>34.33</v>
+        <v>34.66</v>
       </c>
       <c r="R16">
-        <v>36.04</v>
+        <v>36.11</v>
       </c>
       <c r="S16">
-        <v>40.6</v>
+        <v>40.56</v>
       </c>
       <c r="T16">
-        <v>-7.2</v>
+        <v>2.39</v>
       </c>
       <c r="U16" t="s">
         <v>55</v>
@@ -2625,46 +2625,46 @@
         <v>55</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>61.94</v>
+        <v>71.62</v>
       </c>
       <c r="Z16">
-        <v>-0.23</v>
+        <v>0.33</v>
       </c>
       <c r="AA16">
-        <v>-0.74</v>
+        <v>-0.53</v>
       </c>
       <c r="AB16">
-        <v>0.51</v>
+        <v>0.86</v>
       </c>
       <c r="AC16">
-        <v>64.86</v>
+        <v>98.19</v>
       </c>
       <c r="AD16">
-        <v>45.85</v>
+        <v>69.33</v>
       </c>
       <c r="AE16">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="AF16">
-        <v>950.4299999999999</v>
+        <v>474.32</v>
       </c>
       <c r="AG16">
-        <v>37.4</v>
+        <v>39.1</v>
       </c>
       <c r="AH16">
-        <v>31.27</v>
+        <v>30.21</v>
       </c>
       <c r="AI16">
-        <v>30.92</v>
+        <v>32.49</v>
       </c>
       <c r="AJ16" t="s">
         <v>56</v>
       </c>
       <c r="AK16">
-        <v>26.74</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2675,58 +2675,58 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>950</v>
+        <v>947.6</v>
       </c>
       <c r="D17">
-        <v>-3.95</v>
+        <v>-0.25</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
       </c>
       <c r="F17">
-        <v>950</v>
+        <v>947.6</v>
       </c>
       <c r="G17">
-        <v>-38.96</v>
+        <v>-39.12</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>-9.699999999999999</v>
+        <v>-7.92</v>
       </c>
       <c r="J17">
-        <v>-13.7</v>
+        <v>-16.14</v>
       </c>
       <c r="K17">
-        <v>-27.49</v>
+        <v>-28.61</v>
       </c>
       <c r="L17">
-        <v>-33.2</v>
+        <v>-34.21</v>
       </c>
       <c r="M17">
-        <v>-3.95</v>
+        <v>-4.06</v>
       </c>
       <c r="N17">
         <v>7</v>
       </c>
       <c r="O17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P17">
-        <v>997.24</v>
+        <v>980.9400000000001</v>
       </c>
       <c r="Q17">
-        <v>1048.55</v>
+        <v>1040.26</v>
       </c>
       <c r="R17">
-        <v>1135.07</v>
+        <v>1128.22</v>
       </c>
       <c r="S17">
-        <v>1305.42</v>
+        <v>1302.79</v>
       </c>
       <c r="T17">
-        <v>-27.23</v>
+        <v>-27.26</v>
       </c>
       <c r="U17" t="s">
         <v>55</v>
@@ -2741,43 +2741,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>24.03</v>
+        <v>23.77</v>
       </c>
       <c r="Z17">
-        <v>-42.8</v>
+        <v>-45.38</v>
       </c>
       <c r="AA17">
-        <v>-39.08</v>
+        <v>-40.34</v>
       </c>
       <c r="AB17">
-        <v>-3.72</v>
+        <v>-5.05</v>
       </c>
       <c r="AC17">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>18.51</v>
+        <v>7.63</v>
       </c>
       <c r="AE17">
-        <v>31</v>
+        <v>30.11</v>
       </c>
       <c r="AF17">
-        <v>-21.66</v>
+        <v>-33.46</v>
       </c>
       <c r="AG17">
-        <v>1137.82</v>
+        <v>1134.81</v>
       </c>
       <c r="AH17">
-        <v>959.28</v>
+        <v>945.71</v>
       </c>
       <c r="AI17">
-        <v>1059.55</v>
+        <v>1031.14</v>
       </c>
       <c r="AJ17" t="s">
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>60.3</v>
+        <v>62.99</v>
       </c>
     </row>
   </sheetData>
@@ -2918,7 +2918,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>69</v>
@@ -3030,13 +3030,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="7">
-        <v>5.01</v>
+        <v>6.18</v>
       </c>
       <c r="D8" s="7">
-        <v>6.18</v>
+        <v>6.97</v>
       </c>
       <c r="E8" s="8">
-        <v>1.17</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3047,13 +3047,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>-25.29</v>
+        <v>-31.55</v>
       </c>
       <c r="D9" s="7">
-        <v>-31.55</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-6.26</v>
+        <v>-31.36</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3064,13 +3064,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>0.72</v>
+        <v>-3.65</v>
       </c>
       <c r="D10" s="7">
-        <v>-3.65</v>
+        <v>-4.83</v>
       </c>
       <c r="E10" s="9">
-        <v>-4.37</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3081,13 +3081,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-14.48</v>
+        <v>-14.42</v>
       </c>
       <c r="D11" s="7">
-        <v>-14.42</v>
+        <v>-11.11</v>
       </c>
       <c r="E11" s="8">
-        <v>0.06</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3098,13 +3098,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-2.9</v>
+        <v>-2.25</v>
       </c>
       <c r="D12" s="7">
-        <v>-2.25</v>
+        <v>-1.14</v>
       </c>
       <c r="E12" s="8">
-        <v>0.65</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3115,13 +3115,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-4.08</v>
+        <v>-2.05</v>
       </c>
       <c r="D13" s="7">
-        <v>-2.05</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.03</v>
+        <v>-5.81</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-3.76</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3132,13 +3132,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>17.03</v>
+        <v>14.91</v>
       </c>
       <c r="D14" s="7">
-        <v>14.91</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-2.12</v>
+        <v>15.94</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.03</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3149,13 +3149,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-17.02</v>
+        <v>-19.6</v>
       </c>
       <c r="D15" s="7">
-        <v>-19.6</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-2.58</v>
+        <v>-17.94</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3166,13 +3166,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-3.72</v>
+        <v>-5.15</v>
       </c>
       <c r="D16" s="7">
-        <v>-5.15</v>
+        <v>-8.27</v>
       </c>
       <c r="E16" s="9">
-        <v>-1.43</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3183,13 +3183,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-6.04</v>
+        <v>-9.35</v>
       </c>
       <c r="D17" s="7">
-        <v>-9.35</v>
+        <v>-10.94</v>
       </c>
       <c r="E17" s="9">
-        <v>-3.31</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3200,13 +3200,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>17.77</v>
+        <v>20.19</v>
       </c>
       <c r="D18" s="7">
-        <v>20.19</v>
+        <v>21.32</v>
       </c>
       <c r="E18" s="8">
-        <v>2.42</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3217,13 +3217,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>-10.77</v>
+        <v>-12.76</v>
       </c>
       <c r="D19" s="7">
-        <v>-12.76</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.99</v>
+        <v>-11.41</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3234,13 +3234,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>-1.41</v>
+        <v>-1.99</v>
       </c>
       <c r="D20" s="7">
-        <v>-1.99</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.58</v>
+        <v>-0.72</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.27</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3251,13 +3251,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-3.65</v>
+        <v>-8.42</v>
       </c>
       <c r="D21" s="7">
-        <v>-8.42</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-4.77</v>
+        <v>-4.23</v>
+      </c>
+      <c r="E21" s="8">
+        <v>4.19</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3268,13 +3268,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>7.49</v>
+        <v>5.78</v>
       </c>
       <c r="D22" s="7">
-        <v>5.78</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.71</v>
+        <v>16.56</v>
+      </c>
+      <c r="E22" s="8">
+        <v>10.78</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3285,13 +3285,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>-13.4</v>
+        <v>-13.7</v>
       </c>
       <c r="D23" s="7">
-        <v>-13.7</v>
+        <v>-16.14</v>
       </c>
       <c r="E23" s="9">
-        <v>-0.3</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3302,13 +3302,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>7.84</v>
+        <v>5.44</v>
       </c>
       <c r="D24" s="7">
-        <v>5.44</v>
+        <v>3.03</v>
       </c>
       <c r="E24" s="9">
-        <v>-2.4</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3319,13 +3319,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-12.73</v>
+        <v>-16.7</v>
       </c>
       <c r="D25" s="7">
-        <v>-16.7</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-3.97</v>
+        <v>-15.03</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.67</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3336,13 +3336,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>0.41</v>
+        <v>-3.2</v>
       </c>
       <c r="D26" s="7">
-        <v>-3.2</v>
+        <v>-5.9</v>
       </c>
       <c r="E26" s="9">
-        <v>-3.61</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3353,13 +3353,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>-5.63</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="D27" s="7">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-2.57</v>
+        <v>-5.95</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2.25</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3370,13 +3370,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="7">
-        <v>1.42</v>
+        <v>-6.2</v>
       </c>
       <c r="D28" s="7">
-        <v>-6.2</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-7.62</v>
+        <v>-3.53</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3387,13 +3387,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="7">
-        <v>-2.84</v>
+        <v>-2.78</v>
       </c>
       <c r="D29" s="7">
-        <v>-2.78</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.06</v>
+        <v>-4.33</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3404,13 +3404,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="D30" s="7">
-        <v>0</v>
+        <v>-3.28</v>
       </c>
       <c r="E30" s="9">
-        <v>-6.17</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3421,13 +3421,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>-8.390000000000001</v>
+        <v>-10.22</v>
       </c>
       <c r="D31" s="7">
-        <v>-10.22</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-1.83</v>
+        <v>-9.81</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.41</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3438,13 +3438,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>0.14</v>
+        <v>-0.49</v>
       </c>
       <c r="D32" s="7">
-        <v>-0.49</v>
+        <v>-4.34</v>
       </c>
       <c r="E32" s="9">
-        <v>-0.63</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3455,13 +3455,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>-1.24</v>
+        <v>-4.95</v>
       </c>
       <c r="D33" s="7">
-        <v>-4.95</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-3.71</v>
+        <v>-3.17</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.78</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3472,13 +3472,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>8.76</v>
+        <v>7.66</v>
       </c>
       <c r="D34" s="7">
-        <v>7.66</v>
+        <v>2.84</v>
       </c>
       <c r="E34" s="9">
-        <v>-1.1</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3489,13 +3489,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>-2.12</v>
+        <v>-3.5</v>
       </c>
       <c r="D35" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.38</v>
+        <v>-2.74</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.76</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3506,13 +3506,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-6.57</v>
+        <v>-7.53</v>
       </c>
       <c r="D36" s="7">
-        <v>-7.53</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.96</v>
+        <v>-6.92</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.61</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3523,13 +3523,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-9.42</v>
+        <v>-10.24</v>
       </c>
       <c r="D37" s="7">
-        <v>-10.24</v>
+        <v>-10.86</v>
       </c>
       <c r="E37" s="9">
-        <v>-0.82</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3540,13 +3540,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>12.06</v>
+        <v>12.61</v>
       </c>
       <c r="D38" s="7">
-        <v>12.61</v>
+        <v>23.79</v>
       </c>
       <c r="E38" s="8">
-        <v>0.55</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3557,13 +3557,13 @@
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-4.88</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="D39" s="7">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-4.82</v>
+        <v>-7.92</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.78</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3574,13 +3574,13 @@
         <v>11</v>
       </c>
       <c r="C40" s="7">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="D40" s="7">
-        <v>6.3</v>
+        <v>7.07</v>
       </c>
       <c r="E40" s="8">
-        <v>0.3</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3591,13 +3591,13 @@
         <v>11</v>
       </c>
       <c r="C41" s="7">
-        <v>-16.86</v>
+        <v>-20.22</v>
       </c>
       <c r="D41" s="7">
-        <v>-20.22</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-3.36</v>
+        <v>-18.59</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.63</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3608,13 +3608,13 @@
         <v>11</v>
       </c>
       <c r="C42" s="7">
-        <v>-27.48</v>
+        <v>-30.21</v>
       </c>
       <c r="D42" s="7">
-        <v>-30.21</v>
+        <v>-32.3</v>
       </c>
       <c r="E42" s="9">
-        <v>-2.73</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3625,13 +3625,13 @@
         <v>11</v>
       </c>
       <c r="C43" s="7">
-        <v>-34.5</v>
+        <v>-35.12</v>
       </c>
       <c r="D43" s="7">
-        <v>-35.12</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.62</v>
+        <v>-33.06</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.06</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3642,13 +3642,13 @@
         <v>11</v>
       </c>
       <c r="C44" s="7">
-        <v>-14.66</v>
+        <v>-14.14</v>
       </c>
       <c r="D44" s="7">
-        <v>-14.14</v>
+        <v>-11.75</v>
       </c>
       <c r="E44" s="8">
-        <v>0.52</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3659,13 +3659,13 @@
         <v>11</v>
       </c>
       <c r="C45" s="7">
-        <v>-15.78</v>
+        <v>-16.63</v>
       </c>
       <c r="D45" s="7">
-        <v>-16.63</v>
+        <v>-19.72</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.85</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3676,13 +3676,13 @@
         <v>11</v>
       </c>
       <c r="C46" s="7">
-        <v>-27.53</v>
+        <v>-29.86</v>
       </c>
       <c r="D46" s="7">
-        <v>-29.86</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-2.33</v>
+        <v>-29.77</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3693,13 +3693,13 @@
         <v>11</v>
       </c>
       <c r="C47" s="7">
-        <v>-37.36</v>
+        <v>-37.98</v>
       </c>
       <c r="D47" s="7">
-        <v>-37.98</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.62</v>
+        <v>-30.91</v>
+      </c>
+      <c r="E47" s="8">
+        <v>7.07</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -3710,13 +3710,13 @@
         <v>11</v>
       </c>
       <c r="C48" s="7">
-        <v>-11.4</v>
+        <v>-12.49</v>
       </c>
       <c r="D48" s="7">
-        <v>-12.49</v>
+        <v>-15.33</v>
       </c>
       <c r="E48" s="9">
-        <v>-1.09</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3727,13 +3727,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="7">
-        <v>1.09</v>
+        <v>-0.63</v>
       </c>
       <c r="D49" s="7">
-        <v>-0.63</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-1.72</v>
+        <v>0.87</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.5</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3744,13 +3744,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>-12.91</v>
+        <v>-11.86</v>
       </c>
       <c r="D50" s="7">
-        <v>-11.86</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.05</v>
+        <v>-13.24</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -3761,13 +3761,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>19.5</v>
+        <v>17.01</v>
       </c>
       <c r="D51" s="7">
-        <v>17.01</v>
+        <v>15.67</v>
       </c>
       <c r="E51" s="9">
-        <v>-2.49</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -3778,13 +3778,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>-42.01</v>
+        <v>-43.26</v>
       </c>
       <c r="D52" s="7">
-        <v>-43.26</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-1.25</v>
+        <v>-42.57</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3795,13 +3795,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>-38.25</v>
+        <v>-41.44</v>
       </c>
       <c r="D53" s="7">
-        <v>-41.44</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-3.19</v>
+        <v>-38.13</v>
+      </c>
+      <c r="E53" s="8">
+        <v>3.31</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -3812,13 +3812,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>-32.25</v>
+        <v>-32.07</v>
       </c>
       <c r="D54" s="7">
-        <v>-32.07</v>
+        <v>-24.6</v>
       </c>
       <c r="E54" s="8">
-        <v>0.18</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3829,13 +3829,13 @@
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-29.91</v>
+        <v>-33.2</v>
       </c>
       <c r="D55" s="7">
-        <v>-33.2</v>
+        <v>-34.21</v>
       </c>
       <c r="E55" s="9">
-        <v>-3.29</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3846,13 +3846,13 @@
         <v>10</v>
       </c>
       <c r="C56" s="7">
-        <v>7.93</v>
+        <v>7.97</v>
       </c>
       <c r="D56" s="7">
-        <v>7.97</v>
+        <v>9.35</v>
       </c>
       <c r="E56" s="8">
-        <v>0.04</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3863,13 +3863,13 @@
         <v>10</v>
       </c>
       <c r="C57" s="7">
-        <v>-21.18</v>
+        <v>-25.84</v>
       </c>
       <c r="D57" s="7">
-        <v>-25.84</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-4.66</v>
+        <v>-24.89</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.95</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3880,13 +3880,13 @@
         <v>10</v>
       </c>
       <c r="C58" s="7">
-        <v>-10.59</v>
+        <v>-12.34</v>
       </c>
       <c r="D58" s="7">
-        <v>-12.34</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1.75</v>
+        <v>-11.83</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3897,13 +3897,13 @@
         <v>10</v>
       </c>
       <c r="C59" s="7">
-        <v>-14.1</v>
+        <v>-15.1</v>
       </c>
       <c r="D59" s="7">
-        <v>-15.1</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-1</v>
+        <v>-13.12</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.98</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3914,13 +3914,13 @@
         <v>10</v>
       </c>
       <c r="C60" s="7">
-        <v>-4.49</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="D60" s="7">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-3.63</v>
+        <v>-5.3</v>
+      </c>
+      <c r="E60" s="8">
+        <v>2.82</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3931,13 +3931,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="7">
-        <v>-12.34</v>
+        <v>-12.98</v>
       </c>
       <c r="D61" s="7">
-        <v>-12.98</v>
+        <v>-13.92</v>
       </c>
       <c r="E61" s="9">
-        <v>-0.64</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3948,13 +3948,13 @@
         <v>10</v>
       </c>
       <c r="C62" s="7">
-        <v>12.92</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D62" s="7">
-        <v>9.220000000000001</v>
+        <v>5.26</v>
       </c>
       <c r="E62" s="9">
-        <v>-3.7</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3965,13 +3965,13 @@
         <v>10</v>
       </c>
       <c r="C63" s="7">
-        <v>-12.12</v>
+        <v>-13.24</v>
       </c>
       <c r="D63" s="7">
-        <v>-13.24</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-1.12</v>
+        <v>-12.27</v>
+      </c>
+      <c r="E63" s="8">
+        <v>0.97</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3982,13 +3982,13 @@
         <v>10</v>
       </c>
       <c r="C64" s="7">
-        <v>-6.62</v>
+        <v>-7.46</v>
       </c>
       <c r="D64" s="7">
-        <v>-7.46</v>
+        <v>-9.59</v>
       </c>
       <c r="E64" s="9">
-        <v>-0.84</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3999,13 +3999,13 @@
         <v>10</v>
       </c>
       <c r="C65" s="7">
-        <v>-7.61</v>
+        <v>-8.99</v>
       </c>
       <c r="D65" s="7">
-        <v>-8.99</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-1.38</v>
+        <v>-6.97</v>
+      </c>
+      <c r="E65" s="8">
+        <v>2.02</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4016,13 +4016,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="7">
-        <v>13.52</v>
+        <v>12.8</v>
       </c>
       <c r="D66" s="7">
-        <v>12.8</v>
+        <v>12.45</v>
       </c>
       <c r="E66" s="9">
-        <v>-0.72</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4033,13 +4033,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="7">
-        <v>-7.67</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="D67" s="7">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-0.79</v>
+        <v>-7.57</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.89</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4050,13 +4050,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="7">
-        <v>-3.86</v>
+        <v>-5.12</v>
       </c>
       <c r="D68" s="7">
-        <v>-5.12</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-1.26</v>
+        <v>-4.72</v>
+      </c>
+      <c r="E68" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>-10.54</v>
+        <v>-14.91</v>
       </c>
       <c r="D69" s="7">
-        <v>-14.91</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-4.37</v>
+        <v>-11.07</v>
+      </c>
+      <c r="E69" s="8">
+        <v>3.84</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4084,13 +4084,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>-6.38</v>
+        <v>-4.37</v>
       </c>
       <c r="D70" s="7">
-        <v>-4.37</v>
+        <v>5.46</v>
       </c>
       <c r="E70" s="8">
-        <v>2.01</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4101,13 +4101,13 @@
         <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>-24.38</v>
+        <v>-27.49</v>
       </c>
       <c r="D71" s="7">
-        <v>-27.49</v>
+        <v>-28.61</v>
       </c>
       <c r="E71" s="9">
-        <v>-3.11</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4118,13 +4118,13 @@
         <v>6</v>
       </c>
       <c r="C72" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="D72" s="7">
         <v>0</v>
       </c>
-      <c r="D72" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-0.07000000000000001</v>
+      <c r="E72" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4135,13 +4135,13 @@
         <v>6</v>
       </c>
       <c r="C73" s="7">
-        <v>-31.86</v>
+        <v>-35.96</v>
       </c>
       <c r="D73" s="7">
-        <v>-35.96</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-4.1</v>
+        <v>-35.21</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0.75</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4152,13 +4152,13 @@
         <v>6</v>
       </c>
       <c r="C74" s="7">
-        <v>-30.18</v>
+        <v>-33.28</v>
       </c>
       <c r="D74" s="7">
-        <v>-33.28</v>
+        <v>-33.87</v>
       </c>
       <c r="E74" s="9">
-        <v>-3.1</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4169,13 +4169,13 @@
         <v>6</v>
       </c>
       <c r="C75" s="7">
-        <v>-33.92</v>
+        <v>-35.85</v>
       </c>
       <c r="D75" s="7">
-        <v>-35.85</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-1.93</v>
+        <v>-33.77</v>
+      </c>
+      <c r="E75" s="8">
+        <v>2.08</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4186,13 +4186,13 @@
         <v>6</v>
       </c>
       <c r="C76" s="7">
-        <v>-18.4</v>
+        <v>-19.76</v>
       </c>
       <c r="D76" s="7">
-        <v>-19.76</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-1.36</v>
+        <v>-18.46</v>
+      </c>
+      <c r="E76" s="8">
+        <v>1.3</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4203,13 +4203,13 @@
         <v>6</v>
       </c>
       <c r="C77" s="7">
-        <v>-23.85</v>
+        <v>-23.52</v>
       </c>
       <c r="D77" s="7">
-        <v>-23.52</v>
-      </c>
-      <c r="E77" s="8">
-        <v>0.33</v>
+        <v>-25.69</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4220,13 +4220,13 @@
         <v>6</v>
       </c>
       <c r="C78" s="7">
-        <v>-33.1</v>
+        <v>-35.65</v>
       </c>
       <c r="D78" s="7">
-        <v>-35.65</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-2.55</v>
+        <v>-35.23</v>
+      </c>
+      <c r="E78" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="C79" s="7">
-        <v>-36.16</v>
+        <v>-36.99</v>
       </c>
       <c r="D79" s="7">
-        <v>-36.99</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-0.83</v>
+        <v>-36.43</v>
+      </c>
+      <c r="E79" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4254,13 +4254,13 @@
         <v>6</v>
       </c>
       <c r="C80" s="7">
-        <v>-23.45</v>
+        <v>-24.62</v>
       </c>
       <c r="D80" s="7">
-        <v>-24.62</v>
+        <v>-26.7</v>
       </c>
       <c r="E80" s="9">
-        <v>-1.17</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4271,13 +4271,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="7">
-        <v>-20.46</v>
+        <v>-22.61</v>
       </c>
       <c r="D81" s="7">
-        <v>-22.61</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-2.15</v>
+        <v>-21.56</v>
+      </c>
+      <c r="E81" s="8">
+        <v>1.05</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4288,13 +4288,13 @@
         <v>6</v>
       </c>
       <c r="C82" s="7">
-        <v>-22.19</v>
+        <v>-21.47</v>
       </c>
       <c r="D82" s="7">
-        <v>-21.47</v>
+        <v>-21.32</v>
       </c>
       <c r="E82" s="8">
-        <v>0.72</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4305,13 +4305,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="7">
-        <v>-15.85</v>
+        <v>-16.82</v>
       </c>
       <c r="D83" s="7">
-        <v>-16.82</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-0.97</v>
+        <v>-16.37</v>
+      </c>
+      <c r="E83" s="8">
+        <v>0.45</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4322,13 +4322,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="7">
-        <v>-42.26</v>
+        <v>-43.12</v>
       </c>
       <c r="D84" s="7">
-        <v>-43.12</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-0.86</v>
+        <v>-42.52</v>
+      </c>
+      <c r="E84" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4339,13 +4339,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="7">
-        <v>-39.16</v>
+        <v>-42.27</v>
       </c>
       <c r="D85" s="7">
-        <v>-42.27</v>
-      </c>
-      <c r="E85" s="9">
-        <v>-3.11</v>
+        <v>-39.56</v>
+      </c>
+      <c r="E85" s="8">
+        <v>2.71</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4356,13 +4356,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="7">
-        <v>-32.14</v>
+        <v>-32.73</v>
       </c>
       <c r="D86" s="7">
-        <v>-32.73</v>
-      </c>
-      <c r="E86" s="9">
-        <v>-0.59</v>
+        <v>-25.85</v>
+      </c>
+      <c r="E86" s="8">
+        <v>6.88</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4373,13 +4373,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="7">
-        <v>-36.45</v>
+        <v>-38.96</v>
       </c>
       <c r="D87" s="7">
-        <v>-38.96</v>
+        <v>-39.12</v>
       </c>
       <c r="E87" s="9">
-        <v>-2.51</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4390,13 +4390,13 @@
         <v>2</v>
       </c>
       <c r="C88" s="7">
-        <v>782.3</v>
+        <v>781.75</v>
       </c>
       <c r="D88" s="7">
-        <v>781.75</v>
-      </c>
-      <c r="E88" s="9">
-        <v>-0.55</v>
+        <v>795.5</v>
+      </c>
+      <c r="E88" s="8">
+        <v>13.75</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4407,13 +4407,13 @@
         <v>2</v>
       </c>
       <c r="C89" s="7">
-        <v>736.9</v>
+        <v>692.55</v>
       </c>
       <c r="D89" s="7">
-        <v>692.55</v>
-      </c>
-      <c r="E89" s="9">
-        <v>-44.35</v>
+        <v>700.65</v>
+      </c>
+      <c r="E89" s="8">
+        <v>8.1</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4424,13 +4424,13 @@
         <v>2</v>
       </c>
       <c r="C90" s="7">
-        <v>203.6</v>
+        <v>194.57</v>
       </c>
       <c r="D90" s="7">
-        <v>194.57</v>
+        <v>192.84</v>
       </c>
       <c r="E90" s="9">
-        <v>-9.029999999999999</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4441,13 +4441,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="7">
-        <v>594.1</v>
+        <v>576.8</v>
       </c>
       <c r="D91" s="7">
-        <v>576.8</v>
-      </c>
-      <c r="E91" s="9">
-        <v>-17.3</v>
+        <v>595.45</v>
+      </c>
+      <c r="E91" s="8">
+        <v>18.65</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4458,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="7">
-        <v>1682.4</v>
+        <v>1654.4</v>
       </c>
       <c r="D92" s="7">
-        <v>1654.4</v>
-      </c>
-      <c r="E92" s="9">
-        <v>-28</v>
+        <v>1681.2</v>
+      </c>
+      <c r="E92" s="8">
+        <v>26.8</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4475,13 +4475,13 @@
         <v>2</v>
       </c>
       <c r="C93" s="7">
-        <v>959.8</v>
+        <v>963.9</v>
       </c>
       <c r="D93" s="7">
-        <v>963.9</v>
-      </c>
-      <c r="E93" s="8">
-        <v>4.1</v>
+        <v>936.5</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-27.4</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4492,13 +4492,13 @@
         <v>2</v>
       </c>
       <c r="C94" s="7">
-        <v>3846.8</v>
+        <v>3700</v>
       </c>
       <c r="D94" s="7">
-        <v>3700</v>
-      </c>
-      <c r="E94" s="9">
-        <v>-146.8</v>
+        <v>3724</v>
+      </c>
+      <c r="E94" s="8">
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4509,13 +4509,13 @@
         <v>2</v>
       </c>
       <c r="C95" s="7">
-        <v>564.65</v>
+        <v>548.5</v>
       </c>
       <c r="D95" s="7">
-        <v>548.5</v>
-      </c>
-      <c r="E95" s="9">
-        <v>-16.15</v>
+        <v>553.35</v>
+      </c>
+      <c r="E95" s="8">
+        <v>4.85</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4526,13 +4526,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="7">
-        <v>353.5</v>
+        <v>348.1</v>
       </c>
       <c r="D96" s="7">
-        <v>348.1</v>
+        <v>338.5</v>
       </c>
       <c r="E96" s="9">
-        <v>-5.4</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4543,13 +4543,13 @@
         <v>2</v>
       </c>
       <c r="C97" s="7">
-        <v>172.33</v>
+        <v>167.67</v>
       </c>
       <c r="D97" s="7">
-        <v>167.67</v>
-      </c>
-      <c r="E97" s="9">
-        <v>-4.66</v>
+        <v>169.94</v>
+      </c>
+      <c r="E97" s="8">
+        <v>2.27</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4560,13 +4560,13 @@
         <v>2</v>
       </c>
       <c r="C98" s="7">
-        <v>2506.9</v>
+        <v>2530</v>
       </c>
       <c r="D98" s="7">
-        <v>2530</v>
+        <v>2535</v>
       </c>
       <c r="E98" s="8">
-        <v>23.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4577,13 +4577,13 @@
         <v>2</v>
       </c>
       <c r="C99" s="7">
-        <v>4350</v>
+        <v>4299.7</v>
       </c>
       <c r="D99" s="7">
-        <v>4299.7</v>
-      </c>
-      <c r="E99" s="9">
-        <v>-50.3</v>
+        <v>4323</v>
+      </c>
+      <c r="E99" s="8">
+        <v>23.3</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4594,13 +4594,13 @@
         <v>2</v>
       </c>
       <c r="C100" s="7">
-        <v>2775.8</v>
+        <v>2727.5</v>
       </c>
       <c r="D100" s="7">
-        <v>2727.5</v>
-      </c>
-      <c r="E100" s="9">
-        <v>-48.3</v>
+        <v>2754</v>
+      </c>
+      <c r="E100" s="8">
+        <v>26.5</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4611,13 +4611,13 @@
         <v>2</v>
       </c>
       <c r="C101" s="7">
-        <v>208.54</v>
+        <v>197.86</v>
       </c>
       <c r="D101" s="7">
-        <v>197.86</v>
-      </c>
-      <c r="E101" s="9">
-        <v>-10.68</v>
+        <v>207.16</v>
+      </c>
+      <c r="E101" s="8">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4628,13 +4628,13 @@
         <v>2</v>
       </c>
       <c r="C102" s="7">
-        <v>38.01</v>
+        <v>37.68</v>
       </c>
       <c r="D102" s="7">
-        <v>37.68</v>
-      </c>
-      <c r="E102" s="9">
-        <v>-0.33</v>
+        <v>41.53</v>
+      </c>
+      <c r="E102" s="8">
+        <v>3.85</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4645,625 +4645,659 @@
         <v>2</v>
       </c>
       <c r="C103" s="7">
-        <v>989.1</v>
+        <v>950</v>
       </c>
       <c r="D103" s="7">
-        <v>950</v>
+        <v>947.6</v>
       </c>
       <c r="E103" s="9">
-        <v>-39.1</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C104" s="7">
+        <v>31</v>
+      </c>
+      <c r="D104" s="7">
         <v>25</v>
       </c>
-      <c r="D104" s="7">
-        <v>13</v>
-      </c>
       <c r="E104" s="9">
-        <v>-12</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C105" s="7">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D105" s="7">
-        <v>31</v>
-      </c>
-      <c r="E105" s="8">
-        <v>12</v>
+        <v>50</v>
+      </c>
+      <c r="E105" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="7">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D106" s="7">
-        <v>19</v>
-      </c>
-      <c r="E106" s="8">
-        <v>6</v>
+        <v>69</v>
+      </c>
+      <c r="E106" s="9">
+        <v>-12</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="7">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D107" s="7">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="E107" s="9">
-        <v>-6</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C108" s="7">
-        <v>65.56999999999999</v>
+        <v>25</v>
       </c>
       <c r="D108" s="7">
-        <v>65.33</v>
-      </c>
-      <c r="E108" s="9">
-        <v>-0.24</v>
+        <v>31</v>
+      </c>
+      <c r="E108" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C109" s="7">
-        <v>23.48</v>
+        <v>50</v>
       </c>
       <c r="D109" s="7">
-        <v>20.03</v>
-      </c>
-      <c r="E109" s="9">
-        <v>-3.45</v>
+        <v>81</v>
+      </c>
+      <c r="E109" s="8">
+        <v>31</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C110" s="7">
-        <v>52.17</v>
+        <v>65.33</v>
       </c>
       <c r="D110" s="7">
-        <v>35.39</v>
-      </c>
-      <c r="E110" s="9">
-        <v>-16.78</v>
+        <v>68.44</v>
+      </c>
+      <c r="E110" s="8">
+        <v>3.11</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C111" s="7">
-        <v>39.36</v>
+        <v>20.03</v>
       </c>
       <c r="D111" s="7">
-        <v>35.76</v>
-      </c>
-      <c r="E111" s="9">
-        <v>-3.6</v>
+        <v>22.27</v>
+      </c>
+      <c r="E111" s="8">
+        <v>2.24</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="7">
-        <v>46.85</v>
+        <v>35.39</v>
       </c>
       <c r="D112" s="7">
-        <v>42.64</v>
+        <v>33.19</v>
       </c>
       <c r="E112" s="9">
-        <v>-4.21</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="7">
-        <v>41.84</v>
+        <v>35.76</v>
       </c>
       <c r="D113" s="7">
-        <v>43.59</v>
+        <v>41.92</v>
       </c>
       <c r="E113" s="8">
-        <v>1.75</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C114" s="7">
-        <v>71.7</v>
+        <v>42.64</v>
       </c>
       <c r="D114" s="7">
-        <v>61.49</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-10.21</v>
+        <v>47.5</v>
+      </c>
+      <c r="E114" s="8">
+        <v>4.86</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C115" s="7">
-        <v>29.19</v>
+        <v>43.59</v>
       </c>
       <c r="D115" s="7">
-        <v>26.2</v>
+        <v>35.82</v>
       </c>
       <c r="E115" s="9">
-        <v>-2.99</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C116" s="7">
-        <v>48.05</v>
+        <v>61.49</v>
       </c>
       <c r="D116" s="7">
-        <v>42.97</v>
-      </c>
-      <c r="E116" s="9">
-        <v>-5.08</v>
+        <v>62.43</v>
+      </c>
+      <c r="E116" s="8">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C117" s="7">
-        <v>36.77</v>
+        <v>26.2</v>
       </c>
       <c r="D117" s="7">
-        <v>30.79</v>
-      </c>
-      <c r="E117" s="9">
-        <v>-5.98</v>
+        <v>28.57</v>
+      </c>
+      <c r="E117" s="8">
+        <v>2.37</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C118" s="7">
-        <v>73.15000000000001</v>
+        <v>42.97</v>
       </c>
       <c r="D118" s="7">
-        <v>74.27</v>
-      </c>
-      <c r="E118" s="8">
-        <v>1.12</v>
+        <v>35.73</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-7.24</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="7">
-        <v>30.31</v>
+        <v>30.79</v>
       </c>
       <c r="D119" s="7">
-        <v>28.02</v>
-      </c>
-      <c r="E119" s="9">
-        <v>-2.29</v>
+        <v>36.23</v>
+      </c>
+      <c r="E119" s="8">
+        <v>5.44</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C120" s="7">
-        <v>44.12</v>
+        <v>74.27</v>
       </c>
       <c r="D120" s="7">
-        <v>40.55</v>
-      </c>
-      <c r="E120" s="9">
-        <v>-3.57</v>
+        <v>74.52</v>
+      </c>
+      <c r="E120" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C121" s="7">
-        <v>46.63</v>
+        <v>28.02</v>
       </c>
       <c r="D121" s="7">
-        <v>41.85</v>
-      </c>
-      <c r="E121" s="9">
-        <v>-4.78</v>
+        <v>30.64</v>
+      </c>
+      <c r="E121" s="8">
+        <v>2.62</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C122" s="7">
-        <v>63.67</v>
+        <v>40.55</v>
       </c>
       <c r="D122" s="7">
-        <v>61.94</v>
-      </c>
-      <c r="E122" s="9">
-        <v>-1.73</v>
+        <v>43.26</v>
+      </c>
+      <c r="E122" s="8">
+        <v>2.71</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C123" s="7">
-        <v>28.73</v>
+        <v>41.85</v>
       </c>
       <c r="D123" s="7">
-        <v>24.03</v>
-      </c>
-      <c r="E123" s="9">
-        <v>-4.7</v>
+        <v>46.95</v>
+      </c>
+      <c r="E123" s="8">
+        <v>5.1</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C124" s="7">
-        <v>413.62</v>
+        <v>61.94</v>
       </c>
       <c r="D124" s="7">
-        <v>133.92</v>
-      </c>
-      <c r="E124" s="9">
-        <v>-279.7</v>
+        <v>71.62</v>
+      </c>
+      <c r="E124" s="8">
+        <v>9.68</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C125" s="7">
-        <v>-36.14</v>
+        <v>24.03</v>
       </c>
       <c r="D125" s="7">
-        <v>53.62</v>
-      </c>
-      <c r="E125" s="8">
-        <v>89.76000000000001</v>
+        <v>23.77</v>
+      </c>
+      <c r="E125" s="9">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C126" s="7">
-        <v>18.34</v>
+        <v>133.92</v>
       </c>
       <c r="D126" s="7">
-        <v>395.13</v>
-      </c>
-      <c r="E126" s="8">
-        <v>376.79</v>
+        <v>13.84</v>
+      </c>
+      <c r="E126" s="9">
+        <v>-120.08</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C127" s="7">
-        <v>-73.22</v>
+        <v>53.62</v>
       </c>
       <c r="D127" s="7">
-        <v>-56.92</v>
-      </c>
-      <c r="E127" s="8">
-        <v>16.3</v>
+        <v>-4.53</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-58.15</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C128" s="7">
-        <v>-11</v>
+        <v>395.13</v>
       </c>
       <c r="D128" s="7">
-        <v>-40.62</v>
+        <v>-1.34</v>
       </c>
       <c r="E128" s="9">
-        <v>-29.62</v>
+        <v>-396.47</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C129" s="7">
-        <v>-44.16</v>
+        <v>-56.92</v>
       </c>
       <c r="D129" s="7">
-        <v>14.73</v>
+        <v>609.33</v>
       </c>
       <c r="E129" s="8">
-        <v>58.89</v>
+        <v>666.25</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C130" s="7">
-        <v>-21.32</v>
+        <v>-40.62</v>
       </c>
       <c r="D130" s="7">
-        <v>-42.86</v>
+        <v>-56.48</v>
       </c>
       <c r="E130" s="9">
-        <v>-21.54</v>
+        <v>-15.86</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C131" s="7">
-        <v>20.08</v>
+        <v>14.73</v>
       </c>
       <c r="D131" s="7">
-        <v>25.99</v>
+        <v>75.75</v>
       </c>
       <c r="E131" s="8">
-        <v>5.91</v>
+        <v>61.02</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C132" s="7">
-        <v>-23.03</v>
+        <v>-42.86</v>
       </c>
       <c r="D132" s="7">
-        <v>4.51</v>
-      </c>
-      <c r="E132" s="8">
-        <v>27.54</v>
+        <v>-64.51000000000001</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-21.65</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C133" s="7">
-        <v>-27.54</v>
+        <v>25.99</v>
       </c>
       <c r="D133" s="7">
-        <v>29.83</v>
-      </c>
-      <c r="E133" s="8">
-        <v>57.37</v>
+        <v>-7.26</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-33.25</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C134" s="7">
-        <v>-23.53</v>
+        <v>4.51</v>
       </c>
       <c r="D134" s="7">
-        <v>23.6</v>
+        <v>132.69</v>
       </c>
       <c r="E134" s="8">
-        <v>47.13</v>
+        <v>128.18</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C135" s="7">
-        <v>-49.11</v>
+        <v>29.83</v>
       </c>
       <c r="D135" s="7">
-        <v>-23.36</v>
-      </c>
-      <c r="E135" s="8">
-        <v>25.75</v>
+        <v>-5.64</v>
+      </c>
+      <c r="E135" s="9">
+        <v>-35.47</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C136" s="7">
-        <v>25.37</v>
+        <v>23.6</v>
       </c>
       <c r="D136" s="7">
-        <v>-33.82</v>
+        <v>-24.12</v>
       </c>
       <c r="E136" s="9">
-        <v>-59.19</v>
+        <v>-47.72</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C137" s="7">
-        <v>-83.13</v>
+        <v>-23.36</v>
       </c>
       <c r="D137" s="7">
-        <v>-61.37</v>
-      </c>
-      <c r="E137" s="8">
-        <v>21.76</v>
+        <v>-52.05</v>
+      </c>
+      <c r="E137" s="9">
+        <v>-28.69</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C138" s="7">
-        <v>3390.55</v>
+        <v>-33.82</v>
       </c>
       <c r="D138" s="7">
-        <v>950.4299999999999</v>
-      </c>
-      <c r="E138" s="9">
-        <v>-2440.12</v>
+        <v>-28.54</v>
+      </c>
+      <c r="E138" s="8">
+        <v>5.28</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C139" s="7">
-        <v>-27.84</v>
+        <v>-61.37</v>
       </c>
       <c r="D139" s="7">
+        <v>-55.7</v>
+      </c>
+      <c r="E139" s="8">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="7">
+        <v>950.4299999999999</v>
+      </c>
+      <c r="D140" s="7">
+        <v>474.32</v>
+      </c>
+      <c r="E140" s="9">
+        <v>-476.11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="7">
         <v>-21.66</v>
       </c>
-      <c r="E139" s="8">
-        <v>6.18</v>
+      <c r="D141" s="7">
+        <v>-33.46</v>
+      </c>
+      <c r="E141" s="9">
+        <v>-11.8</v>
       </c>
     </row>
   </sheetData>
@@ -5322,22 +5356,22 @@
         <v>53</v>
       </c>
       <c r="B2" s="12">
-        <v>36.24</v>
+        <v>38.76000000000001</v>
       </c>
       <c r="C2" s="13">
         <v>16</v>
       </c>
       <c r="D2" s="12">
-        <v>42.2</v>
+        <v>43.9</v>
       </c>
       <c r="E2" s="12">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="F2" s="12">
-        <v>-4.9</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="12">
-        <v>-8.4</v>
+        <v>-7.3</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -5477,34 +5511,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.3171</v>
+        <v>0.3193</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3114</v>
+        <v>0.3059</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2187</v>
+        <v>0.2158</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1288</v>
+        <v>0.1228</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1089</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F2" s="15">
-        <v>0.08599999999999999</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G2" s="15">
-        <v>0.0851</v>
+        <v>0.0796</v>
       </c>
       <c r="H2" s="15">
-        <v>0.0563</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I2" s="15">
-        <v>0.0496</v>
+        <v>0.0383</v>
       </c>
       <c r="J2" s="15">
-        <v>-0.0247</v>
+        <v>-0.0219</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5515,10 +5549,10 @@
         <v>52</v>
       </c>
       <c r="C3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>51</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>43</v>
@@ -5529,22 +5563,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>-0.0372</v>
+        <v>-0.0362</v>
       </c>
       <c r="B4" s="15">
-        <v>-0.0395</v>
+        <v>-0.0406</v>
       </c>
       <c r="C4" s="15">
-        <v>-0.0471</v>
+        <v>-0.0474</v>
       </c>
       <c r="D4" s="15">
-        <v>-0.0568</v>
+        <v>-0.0484</v>
       </c>
       <c r="E4" s="15">
-        <v>-0.07690000000000001</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="F4" s="15">
-        <v>-0.08779999999999999</v>
+        <v>-0.0867</v>
       </c>
     </row>
   </sheetData>

--- a/TATA_GROUP_Technical_Metrics.xlsx
+++ b/TATA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="98">
   <si>
     <t>Symbol</t>
   </si>
@@ -217,73 +217,64 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.5 → 52.7</t>
+    <t>49.5 → 56.7</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>47.5</t>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>56.7</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>23.6 → 42.9</t>
+  </si>
+  <si>
+    <t>23.6</t>
+  </si>
+  <si>
+    <t>42.9</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>71.9 → 68.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>71.9</t>
+  </si>
+  <si>
+    <t>68.3</t>
+  </si>
+  <si>
+    <t>72.3 → 60.4</t>
+  </si>
+  <si>
+    <t>72.3</t>
+  </si>
+  <si>
+    <t>60.4</t>
+  </si>
+  <si>
+    <t>52.7 → 47.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.7</t>
   </si>
   <si>
-    <t>35.8 → 55.6</t>
-  </si>
-  <si>
-    <t>35.8</t>
-  </si>
-  <si>
-    <t>55.6</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.6 → 30.2</t>
-  </si>
-  <si>
-    <t>28.6</t>
-  </si>
-  <si>
-    <t>30.2</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>74.5 → 69.1</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>74.5</t>
-  </si>
-  <si>
-    <t>69.1</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>68.4 → 71.9</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>68.4</t>
-  </si>
-  <si>
-    <t>71.9</t>
+    <t>47.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -335,7 +326,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,20 +374,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -430,12 +414,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,12 +501,12 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -537,7 +515,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1036,10 +1014,10 @@
         <v>53</v>
       </c>
       <c r="C2">
-        <v>812.85</v>
+        <v>805.2</v>
       </c>
       <c r="D2">
-        <v>2.18</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E2">
         <v>812.85</v>
@@ -1048,46 +1026,46 @@
         <v>570.95</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H2">
-        <v>42.37</v>
+        <v>41.03</v>
       </c>
       <c r="I2">
-        <v>6.95</v>
+        <v>6.93</v>
       </c>
       <c r="J2">
-        <v>11.53</v>
+        <v>10.79</v>
       </c>
       <c r="K2">
-        <v>10.78</v>
+        <v>9.6</v>
       </c>
       <c r="L2">
-        <v>9.220000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="M2">
-        <v>32.96</v>
+        <v>33.31</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>785.08</v>
+        <v>795.52</v>
       </c>
       <c r="Q2">
-        <v>742.58</v>
+        <v>747.29</v>
       </c>
       <c r="R2">
-        <v>732.04</v>
+        <v>733.74</v>
       </c>
       <c r="S2">
-        <v>689.3</v>
+        <v>689.75</v>
       </c>
       <c r="T2">
-        <v>17.92</v>
+        <v>16.74</v>
       </c>
       <c r="U2" t="s">
         <v>54</v>
@@ -1102,43 +1080,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>71.87</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="Z2">
-        <v>17.83</v>
+        <v>19.59</v>
       </c>
       <c r="AA2">
-        <v>9.460000000000001</v>
+        <v>11.49</v>
       </c>
       <c r="AB2">
-        <v>8.369999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AC2">
-        <v>98.31</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="AD2">
-        <v>93.14</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="AE2">
-        <v>21.85</v>
+        <v>21.27</v>
       </c>
       <c r="AF2">
-        <v>60.72</v>
+        <v>-33.37</v>
       </c>
       <c r="AG2">
-        <v>804.97</v>
+        <v>813.73</v>
       </c>
       <c r="AH2">
-        <v>680.1900000000001</v>
+        <v>680.85</v>
       </c>
       <c r="AI2">
-        <v>735.9299999999999</v>
+        <v>744.58</v>
       </c>
       <c r="AJ2" t="s">
         <v>56</v>
       </c>
       <c r="AK2">
-        <v>40.22</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1149,10 +1127,10 @@
         <v>53</v>
       </c>
       <c r="C3">
-        <v>707.8</v>
+        <v>709.9</v>
       </c>
       <c r="D3">
-        <v>1.02</v>
+        <v>0.3</v>
       </c>
       <c r="E3">
         <v>1081.5</v>
@@ -1161,46 +1139,46 @@
         <v>505.36</v>
       </c>
       <c r="G3">
-        <v>-34.55</v>
+        <v>-34.36</v>
       </c>
       <c r="H3">
-        <v>40.06</v>
+        <v>40.47</v>
       </c>
       <c r="I3">
-        <v>-10.23</v>
+        <v>-5.5</v>
       </c>
       <c r="J3">
-        <v>-28.72</v>
+        <v>-27.3</v>
       </c>
       <c r="K3">
-        <v>-24.2</v>
+        <v>-26.24</v>
       </c>
       <c r="L3">
-        <v>-18.83</v>
+        <v>-16.98</v>
       </c>
       <c r="M3">
-        <v>-1.17</v>
+        <v>-0.37</v>
       </c>
       <c r="N3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="O3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>717.83</v>
+        <v>709.5599999999999</v>
       </c>
       <c r="Q3">
-        <v>833.4400000000001</v>
+        <v>823.11</v>
       </c>
       <c r="R3">
-        <v>907.5700000000001</v>
+        <v>901.28</v>
       </c>
       <c r="S3">
-        <v>772.4299999999999</v>
+        <v>772.38</v>
       </c>
       <c r="T3">
-        <v>-8.369999999999999</v>
+        <v>-8.09</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1215,43 +1193,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>24.3</v>
+        <v>24.91</v>
       </c>
       <c r="Z3">
-        <v>-60.2</v>
+        <v>-61.02</v>
       </c>
       <c r="AA3">
-        <v>-44.39</v>
+        <v>-47.72</v>
       </c>
       <c r="AB3">
-        <v>-15.81</v>
+        <v>-13.3</v>
       </c>
       <c r="AC3">
-        <v>8.43</v>
+        <v>17.3</v>
       </c>
       <c r="AD3">
-        <v>3.75</v>
+        <v>9.52</v>
       </c>
       <c r="AE3">
-        <v>44.57</v>
+        <v>42.77</v>
       </c>
       <c r="AF3">
-        <v>-37.93</v>
+        <v>-57.07</v>
       </c>
       <c r="AG3">
-        <v>989.6</v>
+        <v>983.42</v>
       </c>
       <c r="AH3">
-        <v>677.27</v>
+        <v>662.8</v>
       </c>
       <c r="AI3">
-        <v>838.98</v>
+        <v>838.0700000000001</v>
       </c>
       <c r="AJ3" t="s">
         <v>57</v>
       </c>
       <c r="AK3">
-        <v>65.05</v>
+        <v>66.02</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1262,58 +1240,58 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>190.33</v>
+        <v>188.72</v>
       </c>
       <c r="D4">
-        <v>-1.3</v>
+        <v>-0.85</v>
       </c>
       <c r="E4">
         <v>291.61</v>
       </c>
       <c r="F4">
-        <v>190.33</v>
+        <v>188.72</v>
       </c>
       <c r="G4">
-        <v>-34.73</v>
+        <v>-35.28</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-7</v>
+        <v>-7.62</v>
       </c>
       <c r="J4">
-        <v>-5.01</v>
+        <v>-5.82</v>
       </c>
       <c r="K4">
-        <v>-14.11</v>
+        <v>-12.47</v>
       </c>
       <c r="L4">
-        <v>-33.25</v>
+        <v>-31.85</v>
       </c>
       <c r="M4">
-        <v>-5.33</v>
+        <v>-5.23</v>
       </c>
       <c r="N4">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>197.13</v>
+        <v>194.01</v>
       </c>
       <c r="Q4">
-        <v>199.46</v>
+        <v>198.93</v>
       </c>
       <c r="R4">
-        <v>204.08</v>
+        <v>203.61</v>
       </c>
       <c r="S4">
-        <v>234.61</v>
+        <v>234.23</v>
       </c>
       <c r="T4">
-        <v>-18.87</v>
+        <v>-19.43</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
@@ -1328,43 +1306,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>30.24</v>
+        <v>28.5</v>
       </c>
       <c r="Z4">
-        <v>-2.22</v>
+        <v>-2.83</v>
       </c>
       <c r="AA4">
-        <v>-1.57</v>
+        <v>-1.82</v>
       </c>
       <c r="AB4">
-        <v>-0.66</v>
+        <v>-1.01</v>
       </c>
       <c r="AC4">
-        <v>13.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD4">
-        <v>42.04</v>
+        <v>19.62</v>
       </c>
       <c r="AE4">
-        <v>5.36</v>
+        <v>5.38</v>
       </c>
       <c r="AF4">
-        <v>-25.8</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="AG4">
-        <v>207.21</v>
+        <v>208.04</v>
       </c>
       <c r="AH4">
-        <v>191.72</v>
+        <v>189.81</v>
       </c>
       <c r="AI4">
-        <v>206.85</v>
+        <v>205.93</v>
       </c>
       <c r="AJ4" t="s">
         <v>57</v>
       </c>
       <c r="AK4">
-        <v>38.21</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1375,10 +1353,10 @@
         <v>53</v>
       </c>
       <c r="C5">
-        <v>599</v>
+        <v>601.95</v>
       </c>
       <c r="D5">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="E5">
         <v>898.6799999999999</v>
@@ -1387,46 +1365,46 @@
         <v>574.42</v>
       </c>
       <c r="G5">
-        <v>-33.35</v>
+        <v>-33.02</v>
       </c>
       <c r="H5">
-        <v>4.28</v>
+        <v>4.79</v>
       </c>
       <c r="I5">
-        <v>-6.06</v>
+        <v>-0.65</v>
       </c>
       <c r="J5">
-        <v>-8.16</v>
+        <v>-6.49</v>
       </c>
       <c r="K5">
-        <v>-14.29</v>
+        <v>-10.73</v>
       </c>
       <c r="L5">
-        <v>-33.38</v>
+        <v>-32.44</v>
       </c>
       <c r="M5">
-        <v>-8.390000000000001</v>
+        <v>-6.21</v>
       </c>
       <c r="N5">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="O5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P5">
-        <v>594.25</v>
+        <v>593.46</v>
       </c>
       <c r="Q5">
-        <v>613.39</v>
+        <v>611.41</v>
       </c>
       <c r="R5">
-        <v>636.97</v>
+        <v>635.59</v>
       </c>
       <c r="S5">
-        <v>687.9299999999999</v>
+        <v>687.08</v>
       </c>
       <c r="T5">
-        <v>-12.93</v>
+        <v>-12.39</v>
       </c>
       <c r="U5" t="s">
         <v>55</v>
@@ -1441,34 +1419,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>43.04</v>
+        <v>44.01</v>
       </c>
       <c r="Z5">
-        <v>-13.16</v>
+        <v>-12.74</v>
       </c>
       <c r="AA5">
-        <v>-11.15</v>
+        <v>-11.47</v>
       </c>
       <c r="AB5">
-        <v>-2.01</v>
+        <v>-1.27</v>
       </c>
       <c r="AC5">
-        <v>30.11</v>
+        <v>48.58</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>33.27</v>
       </c>
       <c r="AE5">
-        <v>27.01</v>
+        <v>25.96</v>
       </c>
       <c r="AF5">
-        <v>-64.94</v>
+        <v>-77.86</v>
       </c>
       <c r="AG5">
-        <v>650.16</v>
+        <v>646.02</v>
       </c>
       <c r="AH5">
-        <v>576.61</v>
+        <v>576.8</v>
       </c>
       <c r="AI5">
         <v>660.54</v>
@@ -1477,7 +1455,7 @@
         <v>57</v>
       </c>
       <c r="AK5">
-        <v>15.28</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1488,10 +1466,10 @@
         <v>53</v>
       </c>
       <c r="C6">
-        <v>1713.5</v>
+        <v>1681</v>
       </c>
       <c r="D6">
-        <v>1.92</v>
+        <v>-1.9</v>
       </c>
       <c r="E6">
         <v>2061.7</v>
@@ -1500,46 +1478,46 @@
         <v>1347.9</v>
       </c>
       <c r="G6">
-        <v>-16.89</v>
+        <v>-18.47</v>
       </c>
       <c r="H6">
-        <v>27.12</v>
+        <v>24.71</v>
       </c>
       <c r="I6">
-        <v>-0.29</v>
+        <v>-0.63</v>
       </c>
       <c r="J6">
-        <v>2.6</v>
+        <v>0.87</v>
       </c>
       <c r="K6">
-        <v>-1.25</v>
+        <v>-4.73</v>
       </c>
       <c r="L6">
-        <v>-10.54</v>
+        <v>-9.24</v>
       </c>
       <c r="M6">
-        <v>6.36</v>
+        <v>6.41</v>
       </c>
       <c r="N6">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O6">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="P6">
-        <v>1684.64</v>
+        <v>1682.5</v>
       </c>
       <c r="Q6">
-        <v>1682.2</v>
+        <v>1683.49</v>
       </c>
       <c r="R6">
-        <v>1703.4</v>
+        <v>1702.66</v>
       </c>
       <c r="S6">
-        <v>1696.64</v>
+        <v>1696.04</v>
       </c>
       <c r="T6">
-        <v>0.99</v>
+        <v>-0.89</v>
       </c>
       <c r="U6" t="s">
         <v>55</v>
@@ -1551,37 +1529,37 @@
         <v>55</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>52.7</v>
+        <v>47.59</v>
       </c>
       <c r="Z6">
-        <v>-4.57</v>
+        <v>-5.11</v>
       </c>
       <c r="AA6">
-        <v>-7.45</v>
+        <v>-6.98</v>
       </c>
       <c r="AB6">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC6">
-        <v>36.14</v>
+        <v>43.17</v>
       </c>
       <c r="AD6">
-        <v>31.16</v>
+        <v>35.44</v>
       </c>
       <c r="AE6">
-        <v>60.94</v>
+        <v>61.22</v>
       </c>
       <c r="AF6">
-        <v>-63.82</v>
+        <v>-74.45</v>
       </c>
       <c r="AG6">
-        <v>1743.53</v>
+        <v>1743.5</v>
       </c>
       <c r="AH6">
-        <v>1620.88</v>
+        <v>1623.48</v>
       </c>
       <c r="AI6">
         <v>1789.55</v>
@@ -1590,7 +1568,7 @@
         <v>57</v>
       </c>
       <c r="AK6">
-        <v>25.29</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1601,10 +1579,10 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>1000.2</v>
       </c>
       <c r="D7">
-        <v>6.78</v>
+        <v>0.02</v>
       </c>
       <c r="E7">
         <v>1260.34</v>
@@ -1613,46 +1591,46 @@
         <v>936.5</v>
       </c>
       <c r="G7">
-        <v>-20.66</v>
+        <v>-20.64</v>
       </c>
       <c r="H7">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>3.47</v>
+        <v>3.04</v>
       </c>
       <c r="J7">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="K7">
-        <v>-9.699999999999999</v>
+        <v>-7.57</v>
       </c>
       <c r="L7">
-        <v>-14.14</v>
+        <v>-13.12</v>
       </c>
       <c r="M7">
-        <v>4.95</v>
+        <v>5.18</v>
       </c>
       <c r="N7">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P7">
-        <v>966.17</v>
+        <v>972.08</v>
       </c>
       <c r="Q7">
-        <v>965.6900000000001</v>
+        <v>967.7</v>
       </c>
       <c r="R7">
-        <v>1000.56</v>
+        <v>998.97</v>
       </c>
       <c r="S7">
-        <v>1092.6</v>
+        <v>1091.59</v>
       </c>
       <c r="T7">
-        <v>-8.48</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="U7" t="s">
         <v>55</v>
@@ -1667,34 +1645,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>55.58</v>
+        <v>55.62</v>
       </c>
       <c r="Z7">
-        <v>-8.06</v>
+        <v>-5.03</v>
       </c>
       <c r="AA7">
-        <v>-11.57</v>
+        <v>-10.26</v>
       </c>
       <c r="AB7">
-        <v>3.51</v>
+        <v>5.23</v>
       </c>
       <c r="AC7">
-        <v>51.86</v>
+        <v>66.67</v>
       </c>
       <c r="AD7">
-        <v>47.62</v>
+        <v>50.85</v>
       </c>
       <c r="AE7">
-        <v>24.06</v>
+        <v>25.41</v>
       </c>
       <c r="AF7">
-        <v>443.78</v>
+        <v>84.12</v>
       </c>
       <c r="AG7">
-        <v>996.26</v>
+        <v>1001.78</v>
       </c>
       <c r="AH7">
-        <v>935.12</v>
+        <v>933.62</v>
       </c>
       <c r="AI7">
         <v>1001.09</v>
@@ -1703,7 +1681,7 @@
         <v>57</v>
       </c>
       <c r="AK7">
-        <v>24.44</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1714,10 +1692,10 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>3723.4</v>
+        <v>3755</v>
       </c>
       <c r="D8">
-        <v>-0.02</v>
+        <v>0.85</v>
       </c>
       <c r="E8">
         <v>5749.89</v>
@@ -1726,46 +1704,46 @@
         <v>2996</v>
       </c>
       <c r="G8">
-        <v>-35.24</v>
+        <v>-34.69</v>
       </c>
       <c r="H8">
-        <v>24.28</v>
+        <v>25.33</v>
       </c>
       <c r="I8">
-        <v>-1.76</v>
+        <v>-2.43</v>
       </c>
       <c r="J8">
-        <v>16.95</v>
+        <v>17.83</v>
       </c>
       <c r="K8">
-        <v>4.75</v>
+        <v>4.84</v>
       </c>
       <c r="L8">
-        <v>-29.22</v>
+        <v>-30.13</v>
       </c>
       <c r="M8">
-        <v>-7.75</v>
+        <v>-7.69</v>
       </c>
       <c r="N8">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="O8">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P8">
-        <v>3768.56</v>
+        <v>3749.84</v>
       </c>
       <c r="Q8">
-        <v>3424.03</v>
+        <v>3452.23</v>
       </c>
       <c r="R8">
-        <v>3474.04</v>
+        <v>3473.69</v>
       </c>
       <c r="S8">
-        <v>4094.47</v>
+        <v>4084.49</v>
       </c>
       <c r="T8">
-        <v>-9.06</v>
+        <v>-8.07</v>
       </c>
       <c r="U8" t="s">
         <v>55</v>
@@ -1780,34 +1758,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>62.39</v>
+        <v>63.74</v>
       </c>
       <c r="Z8">
-        <v>115.9</v>
+        <v>117.08</v>
       </c>
       <c r="AA8">
-        <v>66.58</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="AB8">
-        <v>49.32</v>
+        <v>40.4</v>
       </c>
       <c r="AC8">
-        <v>77.01000000000001</v>
+        <v>78.41</v>
       </c>
       <c r="AD8">
-        <v>82.81</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AE8">
-        <v>117.16</v>
+        <v>118.16</v>
       </c>
       <c r="AF8">
-        <v>-55.45</v>
+        <v>-61.29</v>
       </c>
       <c r="AG8">
-        <v>4071.78</v>
+        <v>4106.34</v>
       </c>
       <c r="AH8">
-        <v>2776.28</v>
+        <v>2798.12</v>
       </c>
       <c r="AI8">
         <v>3518.36</v>
@@ -1816,7 +1794,7 @@
         <v>56</v>
       </c>
       <c r="AK8">
-        <v>49.69</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1827,10 +1805,10 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>556.7</v>
+        <v>561.55</v>
       </c>
       <c r="D9">
-        <v>0.61</v>
+        <v>0.87</v>
       </c>
       <c r="E9">
         <v>834.7</v>
@@ -1839,46 +1817,46 @@
         <v>538.37</v>
       </c>
       <c r="G9">
-        <v>-33.31</v>
+        <v>-32.72</v>
       </c>
       <c r="H9">
-        <v>3.4</v>
+        <v>4.31</v>
       </c>
       <c r="I9">
-        <v>-7.91</v>
+        <v>-4.31</v>
       </c>
       <c r="J9">
-        <v>-15.44</v>
+        <v>-13.82</v>
       </c>
       <c r="K9">
-        <v>-14.35</v>
+        <v>-14.18</v>
       </c>
       <c r="L9">
-        <v>-36.05</v>
+        <v>-31.75</v>
       </c>
       <c r="M9">
-        <v>30.86</v>
+        <v>31.5</v>
       </c>
       <c r="N9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P9">
-        <v>562.01</v>
+        <v>556.95</v>
       </c>
       <c r="Q9">
-        <v>603.5599999999999</v>
+        <v>599.42</v>
       </c>
       <c r="R9">
-        <v>634.3099999999999</v>
+        <v>632.1900000000001</v>
       </c>
       <c r="S9">
-        <v>652.5599999999999</v>
+        <v>651.89</v>
       </c>
       <c r="T9">
-        <v>-14.69</v>
+        <v>-13.86</v>
       </c>
       <c r="U9" t="s">
         <v>55</v>
@@ -1893,34 +1871,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>30.23</v>
+        <v>32.68</v>
       </c>
       <c r="Z9">
-        <v>-23.21</v>
+        <v>-23.37</v>
       </c>
       <c r="AA9">
-        <v>-17.25</v>
+        <v>-18.48</v>
       </c>
       <c r="AB9">
-        <v>-5.96</v>
+        <v>-4.9</v>
       </c>
       <c r="AC9">
-        <v>11.96</v>
+        <v>24.07</v>
       </c>
       <c r="AD9">
-        <v>5.46</v>
+        <v>13.49</v>
       </c>
       <c r="AE9">
-        <v>19.99</v>
+        <v>19.47</v>
       </c>
       <c r="AF9">
-        <v>-0.03</v>
+        <v>-50.58</v>
       </c>
       <c r="AG9">
-        <v>657.74</v>
+        <v>653.11</v>
       </c>
       <c r="AH9">
-        <v>549.39</v>
+        <v>545.73</v>
       </c>
       <c r="AI9">
         <v>613.48</v>
@@ -1929,7 +1907,7 @@
         <v>57</v>
       </c>
       <c r="AK9">
-        <v>37.38</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1940,58 +1918,58 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>339.1</v>
+        <v>335</v>
       </c>
       <c r="D10">
-        <v>0.18</v>
+        <v>-1.21</v>
       </c>
       <c r="E10">
         <v>461.8</v>
       </c>
       <c r="F10">
-        <v>335.65</v>
+        <v>335</v>
       </c>
       <c r="G10">
-        <v>-26.57</v>
+        <v>-27.46</v>
       </c>
       <c r="H10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>-3.73</v>
+        <v>-4.83</v>
       </c>
       <c r="J10">
-        <v>-6.7</v>
+        <v>-8.84</v>
       </c>
       <c r="K10">
-        <v>-10.14</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L10">
-        <v>-14.97</v>
+        <v>-15.76</v>
       </c>
       <c r="M10">
-        <v>9.23</v>
+        <v>9.58</v>
       </c>
       <c r="N10">
         <v>50</v>
       </c>
       <c r="O10">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P10">
-        <v>346.24</v>
+        <v>342.84</v>
       </c>
       <c r="Q10">
-        <v>349.25</v>
+        <v>347.9</v>
       </c>
       <c r="R10">
-        <v>359.99</v>
+        <v>359.05</v>
       </c>
       <c r="S10">
-        <v>383.9</v>
+        <v>383.67</v>
       </c>
       <c r="T10">
-        <v>-11.67</v>
+        <v>-12.68</v>
       </c>
       <c r="U10" t="s">
         <v>55</v>
@@ -2006,43 +1984,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>36.45</v>
+        <v>33.67</v>
       </c>
       <c r="Z10">
-        <v>-4.74</v>
+        <v>-5.38</v>
       </c>
       <c r="AA10">
-        <v>-4.46</v>
+        <v>-4.64</v>
       </c>
       <c r="AB10">
-        <v>-0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AC10">
-        <v>53.88</v>
+        <v>39.1</v>
       </c>
       <c r="AD10">
-        <v>71.84999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="AE10">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AF10">
-        <v>35.75</v>
+        <v>-49.77</v>
       </c>
       <c r="AG10">
-        <v>363.41</v>
+        <v>362.12</v>
       </c>
       <c r="AH10">
-        <v>335.08</v>
+        <v>333.69</v>
       </c>
       <c r="AI10">
-        <v>362.14</v>
+        <v>361.89</v>
       </c>
       <c r="AJ10" t="s">
         <v>57</v>
       </c>
       <c r="AK10">
-        <v>30.2</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2053,10 +2031,10 @@
         <v>53</v>
       </c>
       <c r="C11">
-        <v>171.42</v>
+        <v>169.27</v>
       </c>
       <c r="D11">
-        <v>0.87</v>
+        <v>-1.25</v>
       </c>
       <c r="E11">
         <v>216.66</v>
@@ -2065,46 +2043,46 @@
         <v>157.42</v>
       </c>
       <c r="G11">
-        <v>-20.88</v>
+        <v>-21.87</v>
       </c>
       <c r="H11">
-        <v>8.890000000000001</v>
+        <v>7.53</v>
       </c>
       <c r="I11">
-        <v>-1.51</v>
+        <v>-1.84</v>
       </c>
       <c r="J11">
-        <v>-8.83</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="K11">
-        <v>-6.96</v>
+        <v>-7.32</v>
       </c>
       <c r="L11">
-        <v>1.26</v>
+        <v>-0.8</v>
       </c>
       <c r="M11">
-        <v>8.43</v>
+        <v>8.6</v>
       </c>
       <c r="N11">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O11">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P11">
-        <v>170.76</v>
+        <v>170.13</v>
       </c>
       <c r="Q11">
-        <v>175.82</v>
+        <v>174.96</v>
       </c>
       <c r="R11">
-        <v>181.69</v>
+        <v>181.41</v>
       </c>
       <c r="S11">
-        <v>192.16</v>
+        <v>192.1</v>
       </c>
       <c r="T11">
-        <v>-10.79</v>
+        <v>-11.89</v>
       </c>
       <c r="U11" t="s">
         <v>55</v>
@@ -2119,31 +2097,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>39.56</v>
+        <v>36.57</v>
       </c>
       <c r="Z11">
-        <v>-3.53</v>
+        <v>-3.58</v>
       </c>
       <c r="AA11">
-        <v>-3.22</v>
+        <v>-3.3</v>
       </c>
       <c r="AB11">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="AC11">
-        <v>39.88</v>
+        <v>56.1</v>
       </c>
       <c r="AD11">
-        <v>32.78</v>
+        <v>42.29</v>
       </c>
       <c r="AE11">
-        <v>4.63</v>
+        <v>4.54</v>
       </c>
       <c r="AF11">
-        <v>16.87</v>
+        <v>-45.61</v>
       </c>
       <c r="AG11">
-        <v>186.38</v>
+        <v>184.68</v>
       </c>
       <c r="AH11">
         <v>165.25</v>
@@ -2155,7 +2133,7 @@
         <v>57</v>
       </c>
       <c r="AK11">
-        <v>36.89</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2166,10 +2144,10 @@
         <v>53</v>
       </c>
       <c r="C12">
-        <v>2496.9</v>
+        <v>2460</v>
       </c>
       <c r="D12">
-        <v>-1.5</v>
+        <v>-1.48</v>
       </c>
       <c r="E12">
         <v>3221.85</v>
@@ -2178,46 +2156,46 @@
         <v>1982.6</v>
       </c>
       <c r="G12">
-        <v>-22.5</v>
+        <v>-23.65</v>
       </c>
       <c r="H12">
-        <v>25.94</v>
+        <v>24.08</v>
       </c>
       <c r="I12">
-        <v>1.46</v>
+        <v>-2.73</v>
       </c>
       <c r="J12">
-        <v>19.64</v>
+        <v>18.16</v>
       </c>
       <c r="K12">
-        <v>8.77</v>
+        <v>2.59</v>
       </c>
       <c r="L12">
-        <v>-14.3</v>
+        <v>-17.39</v>
       </c>
       <c r="M12">
-        <v>-3.95</v>
+        <v>-3.86</v>
       </c>
       <c r="N12">
         <v>87</v>
       </c>
       <c r="O12">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P12">
-        <v>2519.56</v>
+        <v>2505.76</v>
       </c>
       <c r="Q12">
-        <v>2266.41</v>
+        <v>2285.88</v>
       </c>
       <c r="R12">
-        <v>2254.36</v>
+        <v>2256.34</v>
       </c>
       <c r="S12">
-        <v>2416.48</v>
+        <v>2412.81</v>
       </c>
       <c r="T12">
-        <v>3.33</v>
+        <v>1.96</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
@@ -2232,34 +2210,34 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>69.06</v>
+        <v>64.16</v>
       </c>
       <c r="Z12">
-        <v>93.22</v>
+        <v>90.36</v>
       </c>
       <c r="AA12">
-        <v>56.01</v>
+        <v>62.88</v>
       </c>
       <c r="AB12">
-        <v>37.21</v>
+        <v>27.48</v>
       </c>
       <c r="AC12">
-        <v>90.8</v>
+        <v>81.89</v>
       </c>
       <c r="AD12">
-        <v>93.77</v>
+        <v>89.08</v>
       </c>
       <c r="AE12">
-        <v>74.29000000000001</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AF12">
-        <v>-25.24</v>
+        <v>-57.12</v>
       </c>
       <c r="AG12">
-        <v>2660.43</v>
+        <v>2677.64</v>
       </c>
       <c r="AH12">
-        <v>1872.4</v>
+        <v>1894.12</v>
       </c>
       <c r="AI12">
         <v>2343.34</v>
@@ -2268,7 +2246,7 @@
         <v>56</v>
       </c>
       <c r="AK12">
-        <v>65.77</v>
+        <v>60.77</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2279,10 +2257,10 @@
         <v>53</v>
       </c>
       <c r="C13">
-        <v>4365.9</v>
+        <v>4337.9</v>
       </c>
       <c r="D13">
-        <v>0.99</v>
+        <v>-0.64</v>
       </c>
       <c r="E13">
         <v>5169.2</v>
@@ -2291,46 +2269,46 @@
         <v>3714.9</v>
       </c>
       <c r="G13">
-        <v>-15.54</v>
+        <v>-16.08</v>
       </c>
       <c r="H13">
-        <v>17.52</v>
+        <v>16.77</v>
       </c>
       <c r="I13">
-        <v>-1.32</v>
+        <v>-0.98</v>
       </c>
       <c r="J13">
-        <v>-9.66</v>
+        <v>-11.18</v>
       </c>
       <c r="K13">
-        <v>-7.89</v>
+        <v>-10.55</v>
       </c>
       <c r="L13">
-        <v>17.08</v>
+        <v>14.99</v>
       </c>
       <c r="M13">
-        <v>12.45</v>
+        <v>13.1</v>
       </c>
       <c r="N13">
         <v>93</v>
       </c>
       <c r="O13">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P13">
-        <v>4343.9</v>
+        <v>4335.3</v>
       </c>
       <c r="Q13">
-        <v>4462.45</v>
+        <v>4438.37</v>
       </c>
       <c r="R13">
-        <v>4786.79</v>
+        <v>4772.42</v>
       </c>
       <c r="S13">
-        <v>4443.44</v>
+        <v>4443.76</v>
       </c>
       <c r="T13">
-        <v>-1.75</v>
+        <v>-2.38</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -2345,34 +2323,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>35.3</v>
+        <v>33.71</v>
       </c>
       <c r="Z13">
-        <v>-124.51</v>
+        <v>-120.89</v>
       </c>
       <c r="AA13">
-        <v>-127.26</v>
+        <v>-125.98</v>
       </c>
       <c r="AB13">
-        <v>2.75</v>
+        <v>5.09</v>
       </c>
       <c r="AC13">
-        <v>55.75</v>
+        <v>71.97</v>
       </c>
       <c r="AD13">
-        <v>47.36</v>
+        <v>56.41</v>
       </c>
       <c r="AE13">
-        <v>91.65000000000001</v>
+        <v>92.97</v>
       </c>
       <c r="AF13">
-        <v>-3.84</v>
+        <v>-33.23</v>
       </c>
       <c r="AG13">
-        <v>4719.71</v>
+        <v>4638.78</v>
       </c>
       <c r="AH13">
-        <v>4205.19</v>
+        <v>4237.96</v>
       </c>
       <c r="AI13">
         <v>4559.15</v>
@@ -2381,7 +2359,7 @@
         <v>57</v>
       </c>
       <c r="AK13">
-        <v>56.02</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2392,10 +2370,10 @@
         <v>53</v>
       </c>
       <c r="C14">
-        <v>2820.6</v>
+        <v>2913.9</v>
       </c>
       <c r="D14">
-        <v>2.42</v>
+        <v>3.31</v>
       </c>
       <c r="E14">
         <v>4791.62</v>
@@ -2404,46 +2382,46 @@
         <v>2193.96</v>
       </c>
       <c r="G14">
-        <v>-41.13</v>
+        <v>-39.19</v>
       </c>
       <c r="H14">
-        <v>28.56</v>
+        <v>32.81</v>
       </c>
       <c r="I14">
-        <v>-2.46</v>
+        <v>3.26</v>
       </c>
       <c r="J14">
-        <v>4.47</v>
+        <v>9.16</v>
       </c>
       <c r="K14">
-        <v>-4.01</v>
+        <v>-0.57</v>
       </c>
       <c r="L14">
-        <v>-41.04</v>
+        <v>-38.99</v>
       </c>
       <c r="M14">
-        <v>22.35</v>
+        <v>23.83</v>
       </c>
       <c r="N14">
         <v>44</v>
       </c>
       <c r="O14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P14">
-        <v>2779.98</v>
+        <v>2798.36</v>
       </c>
       <c r="Q14">
-        <v>2810.26</v>
+        <v>2824.65</v>
       </c>
       <c r="R14">
-        <v>2831.95</v>
+        <v>2830.66</v>
       </c>
       <c r="S14">
-        <v>2778.38</v>
+        <v>2779.43</v>
       </c>
       <c r="T14">
-        <v>1.52</v>
+        <v>4.84</v>
       </c>
       <c r="U14" t="s">
         <v>55</v>
@@ -2458,34 +2436,34 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>49.49</v>
+        <v>56.68</v>
       </c>
       <c r="Z14">
-        <v>-0.9399999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="AA14">
-        <v>8.66</v>
+        <v>8.17</v>
       </c>
       <c r="AB14">
-        <v>-9.6</v>
+        <v>-1.95</v>
       </c>
       <c r="AC14">
-        <v>28.62</v>
+        <v>37.29</v>
       </c>
       <c r="AD14">
-        <v>36.33</v>
+        <v>32.81</v>
       </c>
       <c r="AE14">
-        <v>76.73999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="AF14">
-        <v>-53.56</v>
+        <v>-28.17</v>
       </c>
       <c r="AG14">
-        <v>3087.59</v>
+        <v>3091.4</v>
       </c>
       <c r="AH14">
-        <v>2532.92</v>
+        <v>2557.9</v>
       </c>
       <c r="AI14">
         <v>2952.95</v>
@@ -2494,7 +2472,7 @@
         <v>57</v>
       </c>
       <c r="AK14">
-        <v>34.94</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2505,10 +2483,10 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>200.49</v>
+        <v>200.67</v>
       </c>
       <c r="D15">
-        <v>-3.22</v>
+        <v>0.09</v>
       </c>
       <c r="E15">
         <v>342.75</v>
@@ -2517,46 +2495,46 @@
         <v>191.78</v>
       </c>
       <c r="G15">
-        <v>-41.51</v>
+        <v>-41.45</v>
       </c>
       <c r="H15">
-        <v>4.54</v>
+        <v>4.64</v>
       </c>
       <c r="I15">
-        <v>-6.74</v>
+        <v>-3.85</v>
       </c>
       <c r="J15">
-        <v>-6.81</v>
+        <v>-6.95</v>
       </c>
       <c r="K15">
-        <v>-13.83</v>
+        <v>-11.91</v>
       </c>
       <c r="L15">
-        <v>-41.17</v>
+        <v>-40.96</v>
       </c>
       <c r="M15">
-        <v>8.19</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P15">
-        <v>204.55</v>
+        <v>202.94</v>
       </c>
       <c r="Q15">
-        <v>208.06</v>
+        <v>207.71</v>
       </c>
       <c r="R15">
-        <v>218.21</v>
+        <v>217.61</v>
       </c>
       <c r="S15">
-        <v>241.71</v>
+        <v>241.2</v>
       </c>
       <c r="T15">
-        <v>-17.06</v>
+        <v>-16.8</v>
       </c>
       <c r="U15" t="s">
         <v>55</v>
@@ -2571,34 +2549,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>43.97</v>
+        <v>44.07</v>
       </c>
       <c r="Z15">
-        <v>-2.76</v>
+        <v>-3.24</v>
       </c>
       <c r="AA15">
-        <v>-2.01</v>
+        <v>-2.26</v>
       </c>
       <c r="AB15">
-        <v>-0.75</v>
+        <v>-0.98</v>
       </c>
       <c r="AC15">
-        <v>52.05</v>
+        <v>52.9</v>
       </c>
       <c r="AD15">
-        <v>55.67</v>
+        <v>53.86</v>
       </c>
       <c r="AE15">
-        <v>12.76</v>
+        <v>12.17</v>
       </c>
       <c r="AF15">
-        <v>-55.29</v>
+        <v>-70.79000000000001</v>
       </c>
       <c r="AG15">
-        <v>233.38</v>
+        <v>233.25</v>
       </c>
       <c r="AH15">
-        <v>182.74</v>
+        <v>182.18</v>
       </c>
       <c r="AI15">
         <v>197.45</v>
@@ -2607,7 +2585,7 @@
         <v>56</v>
       </c>
       <c r="AK15">
-        <v>28.8</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2618,10 +2596,10 @@
         <v>53</v>
       </c>
       <c r="C16">
-        <v>41.86</v>
+        <v>39.23</v>
       </c>
       <c r="D16">
-        <v>0.79</v>
+        <v>-6.28</v>
       </c>
       <c r="E16">
         <v>56.01</v>
@@ -2630,46 +2608,46 @@
         <v>31.36</v>
       </c>
       <c r="G16">
-        <v>-25.26</v>
+        <v>-29.96</v>
       </c>
       <c r="H16">
-        <v>33.48</v>
+        <v>25.1</v>
       </c>
       <c r="I16">
-        <v>27.35</v>
+        <v>22.36</v>
       </c>
       <c r="J16">
-        <v>19.53</v>
+        <v>13.91</v>
       </c>
       <c r="K16">
-        <v>6.03</v>
+        <v>0.64</v>
       </c>
       <c r="L16">
-        <v>-25.26</v>
+        <v>-28.71</v>
       </c>
       <c r="M16">
-        <v>-5.5</v>
+        <v>-6</v>
       </c>
       <c r="N16">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="O16">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="P16">
-        <v>38.23</v>
+        <v>39.66</v>
       </c>
       <c r="Q16">
-        <v>35.03</v>
+        <v>35.18</v>
       </c>
       <c r="R16">
-        <v>36.17</v>
+        <v>36.19</v>
       </c>
       <c r="S16">
-        <v>40.53</v>
+        <v>40.48</v>
       </c>
       <c r="T16">
-        <v>3.28</v>
+        <v>-3.1</v>
       </c>
       <c r="U16" t="s">
         <v>55</v>
@@ -2681,37 +2659,37 @@
         <v>55</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>72.27</v>
+        <v>60.38</v>
       </c>
       <c r="Z16">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA16">
-        <v>-0.26</v>
+        <v>-0.02</v>
       </c>
       <c r="AB16">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="AC16">
-        <v>98.19</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="AD16">
-        <v>87.08</v>
+        <v>95.53</v>
       </c>
       <c r="AE16">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AF16">
-        <v>128.81</v>
+        <v>-25.42</v>
       </c>
       <c r="AG16">
-        <v>40.51</v>
+        <v>40.96</v>
       </c>
       <c r="AH16">
-        <v>29.54</v>
+        <v>29.4</v>
       </c>
       <c r="AI16">
         <v>34.32</v>
@@ -2720,7 +2698,7 @@
         <v>56</v>
       </c>
       <c r="AK16">
-        <v>38.08</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2731,10 +2709,10 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>946.2</v>
+        <v>1011.9</v>
       </c>
       <c r="D17">
-        <v>-0.15</v>
+        <v>6.94</v>
       </c>
       <c r="E17">
         <v>1556.41</v>
@@ -2743,46 +2721,46 @@
         <v>946.2</v>
       </c>
       <c r="G17">
-        <v>-39.21</v>
+        <v>-34.98</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="I17">
-        <v>-7.2</v>
+        <v>1.35</v>
       </c>
       <c r="J17">
-        <v>-15.02</v>
+        <v>-9.51</v>
       </c>
       <c r="K17">
-        <v>-28.28</v>
+        <v>-22.82</v>
       </c>
       <c r="L17">
-        <v>-34.8</v>
+        <v>-29.08</v>
       </c>
       <c r="M17">
-        <v>-3.89</v>
+        <v>-2.16</v>
       </c>
       <c r="N17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="P17">
-        <v>966.26</v>
+        <v>968.96</v>
       </c>
       <c r="Q17">
-        <v>1031.66</v>
+        <v>1025.48</v>
       </c>
       <c r="R17">
-        <v>1121.36</v>
+        <v>1115.18</v>
       </c>
       <c r="S17">
-        <v>1300.12</v>
+        <v>1297.66</v>
       </c>
       <c r="T17">
-        <v>-27.22</v>
+        <v>-22.02</v>
       </c>
       <c r="U17" t="s">
         <v>55</v>
@@ -2797,34 +2775,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>23.61</v>
+        <v>42.88</v>
       </c>
       <c r="Z17">
-        <v>-47</v>
+        <v>-42.49</v>
       </c>
       <c r="AA17">
-        <v>-41.67</v>
+        <v>-41.83</v>
       </c>
       <c r="AB17">
-        <v>-5.33</v>
+        <v>-0.66</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AD17">
-        <v>1.35</v>
+        <v>11.11</v>
       </c>
       <c r="AE17">
-        <v>29.18</v>
+        <v>33.49</v>
       </c>
       <c r="AF17">
-        <v>48.58</v>
+        <v>350.39</v>
       </c>
       <c r="AG17">
-        <v>1127.64</v>
+        <v>1108.33</v>
       </c>
       <c r="AH17">
-        <v>935.6799999999999</v>
+        <v>942.63</v>
       </c>
       <c r="AI17">
         <v>1029.6</v>
@@ -2833,7 +2811,7 @@
         <v>57</v>
       </c>
       <c r="AK17">
-        <v>65.18000000000001</v>
+        <v>56.86</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +2992,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -3034,1216 +3012,1213 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>75</v>
       </c>
+      <c r="E5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>54</v>
+      <c r="A6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="A7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="E7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>92</v>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="8">
+        <v>11.53</v>
+      </c>
+      <c r="D11" s="8">
+        <v>10.79</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="8">
-        <v>6.97</v>
+        <v>-28.72</v>
       </c>
       <c r="D12" s="8">
-        <v>11.53</v>
-      </c>
-      <c r="E12" s="9">
-        <v>4.56</v>
+        <v>-27.3</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1.42</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="8">
-        <v>-31.36</v>
+        <v>-5.01</v>
       </c>
       <c r="D13" s="8">
-        <v>-28.72</v>
+        <v>-5.82</v>
       </c>
       <c r="E13" s="9">
-        <v>2.64</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="8">
-        <v>-4.83</v>
+        <v>-8.16</v>
       </c>
       <c r="D14" s="8">
-        <v>-5.01</v>
+        <v>-6.49</v>
       </c>
       <c r="E14" s="10">
-        <v>-0.18</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="8">
-        <v>-11.11</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="8">
-        <v>-8.16</v>
+        <v>0.87</v>
       </c>
       <c r="E15" s="9">
-        <v>2.95</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="8">
-        <v>-1.14</v>
+        <v>1.39</v>
       </c>
       <c r="D16" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="E16" s="9">
-        <v>3.74</v>
+        <v>1.73</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="8">
-        <v>-5.81</v>
+        <v>16.95</v>
       </c>
       <c r="D17" s="8">
-        <v>1.39</v>
-      </c>
-      <c r="E17" s="9">
-        <v>7.2</v>
+        <v>17.83</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0.88</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="8">
-        <v>15.94</v>
+        <v>-15.44</v>
       </c>
       <c r="D18" s="8">
-        <v>16.95</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.01</v>
+        <v>-13.82</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1.62</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="8">
-        <v>-17.94</v>
+        <v>-6.7</v>
       </c>
       <c r="D19" s="8">
-        <v>-15.44</v>
+        <v>-8.84</v>
       </c>
       <c r="E19" s="9">
-        <v>2.5</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="8">
-        <v>-8.27</v>
+        <v>-8.83</v>
       </c>
       <c r="D20" s="8">
-        <v>-6.7</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="E20" s="9">
-        <v>1.57</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="8">
-        <v>-10.94</v>
+        <v>19.64</v>
       </c>
       <c r="D21" s="8">
-        <v>-8.83</v>
+        <v>18.16</v>
       </c>
       <c r="E21" s="9">
-        <v>2.11</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="8">
-        <v>21.32</v>
+        <v>-9.66</v>
       </c>
       <c r="D22" s="8">
-        <v>19.64</v>
-      </c>
-      <c r="E22" s="10">
-        <v>-1.68</v>
+        <v>-11.18</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="8">
-        <v>-11.41</v>
+        <v>4.47</v>
       </c>
       <c r="D23" s="8">
-        <v>-9.66</v>
-      </c>
-      <c r="E23" s="9">
-        <v>1.75</v>
+        <v>9.16</v>
+      </c>
+      <c r="E23" s="10">
+        <v>4.69</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="8">
-        <v>-0.72</v>
+        <v>-6.81</v>
       </c>
       <c r="D24" s="8">
-        <v>4.47</v>
+        <v>-6.95</v>
       </c>
       <c r="E24" s="9">
-        <v>5.19</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="8">
-        <v>-4.23</v>
+        <v>19.53</v>
       </c>
       <c r="D25" s="8">
-        <v>-6.81</v>
-      </c>
-      <c r="E25" s="10">
-        <v>-2.58</v>
+        <v>13.91</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-5.62</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="8">
-        <v>16.56</v>
+        <v>-15.02</v>
       </c>
       <c r="D26" s="8">
-        <v>19.53</v>
-      </c>
-      <c r="E26" s="9">
-        <v>2.97</v>
+        <v>-9.51</v>
+      </c>
+      <c r="E26" s="10">
+        <v>5.51</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="8">
-        <v>-16.14</v>
+        <v>6.95</v>
       </c>
       <c r="D27" s="8">
-        <v>-15.02</v>
+        <v>6.93</v>
       </c>
       <c r="E27" s="9">
-        <v>1.12</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="8">
-        <v>3.03</v>
+        <v>-10.23</v>
       </c>
       <c r="D28" s="8">
-        <v>6.95</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.92</v>
+        <v>-5.5</v>
+      </c>
+      <c r="E28" s="10">
+        <v>4.73</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="8">
-        <v>-15.03</v>
+        <v>-7</v>
       </c>
       <c r="D29" s="8">
-        <v>-10.23</v>
+        <v>-7.62</v>
       </c>
       <c r="E29" s="9">
-        <v>4.8</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="8">
-        <v>-5.9</v>
+        <v>-6.06</v>
       </c>
       <c r="D30" s="8">
-        <v>-7</v>
+        <v>-0.65</v>
       </c>
       <c r="E30" s="10">
-        <v>-1.1</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="8">
-        <v>-5.95</v>
+        <v>-0.29</v>
       </c>
       <c r="D31" s="8">
-        <v>-6.06</v>
-      </c>
-      <c r="E31" s="10">
-        <v>-0.11</v>
+        <v>-0.63</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="8">
-        <v>-3.53</v>
+        <v>3.47</v>
       </c>
       <c r="D32" s="8">
-        <v>-0.29</v>
+        <v>3.04</v>
       </c>
       <c r="E32" s="9">
-        <v>3.24</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="8">
-        <v>-4.33</v>
+        <v>-1.76</v>
       </c>
       <c r="D33" s="8">
-        <v>3.47</v>
+        <v>-2.43</v>
       </c>
       <c r="E33" s="9">
-        <v>7.8</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="8">
-        <v>-3.28</v>
+        <v>-7.91</v>
       </c>
       <c r="D34" s="8">
-        <v>-1.76</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.52</v>
+        <v>-4.31</v>
+      </c>
+      <c r="E34" s="10">
+        <v>3.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="8">
-        <v>-9.81</v>
+        <v>-3.73</v>
       </c>
       <c r="D35" s="8">
-        <v>-7.91</v>
+        <v>-4.83</v>
       </c>
       <c r="E35" s="9">
-        <v>1.9</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="8">
-        <v>-4.34</v>
+        <v>-1.51</v>
       </c>
       <c r="D36" s="8">
-        <v>-3.73</v>
+        <v>-1.84</v>
       </c>
       <c r="E36" s="9">
-        <v>0.61</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="8">
-        <v>-3.17</v>
+        <v>1.46</v>
       </c>
       <c r="D37" s="8">
-        <v>-1.51</v>
+        <v>-2.73</v>
       </c>
       <c r="E37" s="9">
-        <v>1.66</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="8">
-        <v>2.84</v>
+        <v>-1.32</v>
       </c>
       <c r="D38" s="8">
-        <v>1.46</v>
+        <v>-0.98</v>
       </c>
       <c r="E38" s="10">
-        <v>-1.38</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="8">
-        <v>-2.74</v>
+        <v>-2.46</v>
       </c>
       <c r="D39" s="8">
-        <v>-1.32</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.42</v>
+        <v>3.26</v>
+      </c>
+      <c r="E39" s="10">
+        <v>5.72</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="8">
-        <v>-6.92</v>
+        <v>-6.74</v>
       </c>
       <c r="D40" s="8">
-        <v>-2.46</v>
-      </c>
-      <c r="E40" s="9">
-        <v>4.46</v>
+        <v>-3.85</v>
+      </c>
+      <c r="E40" s="10">
+        <v>2.89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="8">
-        <v>-10.86</v>
+        <v>27.35</v>
       </c>
       <c r="D41" s="8">
-        <v>-6.74</v>
+        <v>22.36</v>
       </c>
       <c r="E41" s="9">
-        <v>4.12</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="8">
-        <v>23.79</v>
+        <v>-7.2</v>
       </c>
       <c r="D42" s="8">
-        <v>27.35</v>
-      </c>
-      <c r="E42" s="9">
-        <v>3.56</v>
+        <v>1.35</v>
+      </c>
+      <c r="E42" s="10">
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C43" s="8">
-        <v>-7.92</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D43" s="8">
-        <v>-7.2</v>
+        <v>9.17</v>
       </c>
       <c r="E43" s="9">
-        <v>0.72</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="8">
-        <v>7.07</v>
+        <v>-18.83</v>
       </c>
       <c r="D44" s="8">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="E44" s="9">
-        <v>2.15</v>
+        <v>-16.98</v>
+      </c>
+      <c r="E44" s="10">
+        <v>1.85</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="8">
-        <v>-18.59</v>
+        <v>-33.25</v>
       </c>
       <c r="D45" s="8">
-        <v>-18.83</v>
+        <v>-31.85</v>
       </c>
       <c r="E45" s="10">
-        <v>-0.24</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="8">
-        <v>-32.3</v>
+        <v>-33.38</v>
       </c>
       <c r="D46" s="8">
-        <v>-33.25</v>
+        <v>-32.44</v>
       </c>
       <c r="E46" s="10">
-        <v>-0.95</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="8">
-        <v>-33.06</v>
+        <v>-10.54</v>
       </c>
       <c r="D47" s="8">
-        <v>-33.38</v>
+        <v>-9.24</v>
       </c>
       <c r="E47" s="10">
-        <v>-0.32</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="8">
-        <v>-11.75</v>
+        <v>-14.14</v>
       </c>
       <c r="D48" s="8">
-        <v>-10.54</v>
-      </c>
-      <c r="E48" s="9">
-        <v>1.21</v>
+        <v>-13.12</v>
+      </c>
+      <c r="E48" s="10">
+        <v>1.02</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="8">
-        <v>-19.72</v>
+        <v>-29.22</v>
       </c>
       <c r="D49" s="8">
-        <v>-14.14</v>
+        <v>-30.13</v>
       </c>
       <c r="E49" s="9">
-        <v>5.58</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="8">
-        <v>-29.77</v>
+        <v>-36.05</v>
       </c>
       <c r="D50" s="8">
-        <v>-29.22</v>
-      </c>
-      <c r="E50" s="9">
-        <v>0.55</v>
+        <v>-31.75</v>
+      </c>
+      <c r="E50" s="10">
+        <v>4.3</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="8">
-        <v>-30.91</v>
+        <v>-14.97</v>
       </c>
       <c r="D51" s="8">
-        <v>-36.05</v>
-      </c>
-      <c r="E51" s="10">
-        <v>-5.14</v>
+        <v>-15.76</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="8">
-        <v>-15.33</v>
+        <v>1.26</v>
       </c>
       <c r="D52" s="8">
-        <v>-14.97</v>
+        <v>-0.8</v>
       </c>
       <c r="E52" s="9">
-        <v>0.36</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="8">
-        <v>0.87</v>
+        <v>-14.3</v>
       </c>
       <c r="D53" s="8">
-        <v>1.26</v>
+        <v>-17.39</v>
       </c>
       <c r="E53" s="9">
-        <v>0.39</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="8">
-        <v>-13.24</v>
+        <v>17.08</v>
       </c>
       <c r="D54" s="8">
-        <v>-14.3</v>
-      </c>
-      <c r="E54" s="10">
-        <v>-1.06</v>
+        <v>14.99</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="8">
-        <v>15.67</v>
+        <v>-41.04</v>
       </c>
       <c r="D55" s="8">
-        <v>17.08</v>
-      </c>
-      <c r="E55" s="9">
-        <v>1.41</v>
+        <v>-38.99</v>
+      </c>
+      <c r="E55" s="10">
+        <v>2.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="8">
-        <v>-42.57</v>
+        <v>-41.17</v>
       </c>
       <c r="D56" s="8">
-        <v>-41.04</v>
-      </c>
-      <c r="E56" s="9">
-        <v>1.53</v>
+        <v>-40.96</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.21</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="8">
-        <v>-38.13</v>
+        <v>-25.26</v>
       </c>
       <c r="D57" s="8">
-        <v>-41.17</v>
-      </c>
-      <c r="E57" s="10">
-        <v>-3.04</v>
+        <v>-28.71</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-3.45</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="8">
-        <v>-24.6</v>
+        <v>-34.8</v>
       </c>
       <c r="D58" s="8">
-        <v>-25.26</v>
+        <v>-29.08</v>
       </c>
       <c r="E58" s="10">
-        <v>-0.66</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59" s="8">
-        <v>-34.21</v>
+        <v>10.78</v>
       </c>
       <c r="D59" s="8">
-        <v>-34.8</v>
-      </c>
-      <c r="E59" s="10">
-        <v>-0.59</v>
+        <v>9.6</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="8">
-        <v>9.35</v>
+        <v>-24.2</v>
       </c>
       <c r="D60" s="8">
-        <v>10.78</v>
+        <v>-26.24</v>
       </c>
       <c r="E60" s="9">
-        <v>1.43</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="8">
-        <v>-24.89</v>
+        <v>-14.11</v>
       </c>
       <c r="D61" s="8">
-        <v>-24.2</v>
-      </c>
-      <c r="E61" s="9">
-        <v>0.6899999999999999</v>
+        <v>-12.47</v>
+      </c>
+      <c r="E61" s="10">
+        <v>1.64</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="8">
-        <v>-11.83</v>
+        <v>-14.29</v>
       </c>
       <c r="D62" s="8">
-        <v>-14.11</v>
+        <v>-10.73</v>
       </c>
       <c r="E62" s="10">
-        <v>-2.28</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="8">
-        <v>-13.12</v>
+        <v>-1.25</v>
       </c>
       <c r="D63" s="8">
-        <v>-14.29</v>
-      </c>
-      <c r="E63" s="10">
-        <v>-1.17</v>
+        <v>-4.73</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="8">
-        <v>-5.3</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="D64" s="8">
-        <v>-1.25</v>
-      </c>
-      <c r="E64" s="9">
-        <v>4.05</v>
+        <v>-7.57</v>
+      </c>
+      <c r="E64" s="10">
+        <v>2.13</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="8">
-        <v>-13.92</v>
+        <v>4.75</v>
       </c>
       <c r="D65" s="8">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="E65" s="9">
-        <v>4.22</v>
+        <v>4.84</v>
+      </c>
+      <c r="E65" s="10">
+        <v>0.09</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="8">
-        <v>5.26</v>
+        <v>-14.35</v>
       </c>
       <c r="D66" s="8">
-        <v>4.75</v>
+        <v>-14.18</v>
       </c>
       <c r="E66" s="10">
-        <v>-0.51</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="8">
-        <v>-12.27</v>
+        <v>-10.14</v>
       </c>
       <c r="D67" s="8">
-        <v>-14.35</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="E67" s="10">
-        <v>-2.08</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="8">
-        <v>-9.59</v>
+        <v>-6.96</v>
       </c>
       <c r="D68" s="8">
-        <v>-10.14</v>
-      </c>
-      <c r="E68" s="10">
-        <v>-0.55</v>
+        <v>-7.32</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="8">
-        <v>-6.97</v>
+        <v>8.77</v>
       </c>
       <c r="D69" s="8">
-        <v>-6.96</v>
+        <v>2.59</v>
       </c>
       <c r="E69" s="9">
-        <v>0.01</v>
+        <v>-6.18</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="8">
-        <v>12.45</v>
+        <v>-7.89</v>
       </c>
       <c r="D70" s="8">
-        <v>8.77</v>
-      </c>
-      <c r="E70" s="10">
-        <v>-3.68</v>
+        <v>-10.55</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="8">
-        <v>-7.57</v>
+        <v>-4.01</v>
       </c>
       <c r="D71" s="8">
-        <v>-7.89</v>
+        <v>-0.57</v>
       </c>
       <c r="E71" s="10">
-        <v>-0.32</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="8">
-        <v>-4.72</v>
+        <v>-13.83</v>
       </c>
       <c r="D72" s="8">
-        <v>-4.01</v>
-      </c>
-      <c r="E72" s="9">
-        <v>0.71</v>
+        <v>-11.91</v>
+      </c>
+      <c r="E72" s="10">
+        <v>1.92</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="8">
-        <v>-11.07</v>
+        <v>6.03</v>
       </c>
       <c r="D73" s="8">
-        <v>-13.83</v>
-      </c>
-      <c r="E73" s="10">
-        <v>-2.76</v>
+        <v>0.64</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-5.39</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="8">
+        <v>-28.28</v>
+      </c>
+      <c r="D74" s="8">
+        <v>-22.82</v>
+      </c>
+      <c r="E74" s="10">
         <v>5.46</v>
-      </c>
-      <c r="D74" s="8">
-        <v>6.03</v>
-      </c>
-      <c r="E74" s="9">
-        <v>0.57</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C75" s="8">
-        <v>-28.61</v>
+        <v>0</v>
       </c>
       <c r="D75" s="8">
-        <v>-28.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E75" s="9">
-        <v>0.33</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4254,13 +4229,13 @@
         <v>6</v>
       </c>
       <c r="C76" s="8">
-        <v>-35.21</v>
+        <v>-34.55</v>
       </c>
       <c r="D76" s="8">
-        <v>-34.55</v>
-      </c>
-      <c r="E76" s="9">
-        <v>0.66</v>
+        <v>-34.36</v>
+      </c>
+      <c r="E76" s="10">
+        <v>0.19</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4271,13 +4246,13 @@
         <v>6</v>
       </c>
       <c r="C77" s="8">
-        <v>-33.87</v>
+        <v>-34.73</v>
       </c>
       <c r="D77" s="8">
-        <v>-34.73</v>
-      </c>
-      <c r="E77" s="10">
-        <v>-0.86</v>
+        <v>-35.28</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4288,13 +4263,13 @@
         <v>6</v>
       </c>
       <c r="C78" s="8">
-        <v>-33.77</v>
+        <v>-33.35</v>
       </c>
       <c r="D78" s="8">
-        <v>-33.35</v>
-      </c>
-      <c r="E78" s="9">
-        <v>0.42</v>
+        <v>-33.02</v>
+      </c>
+      <c r="E78" s="10">
+        <v>0.33</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4305,13 +4280,13 @@
         <v>6</v>
       </c>
       <c r="C79" s="8">
-        <v>-18.46</v>
+        <v>-16.89</v>
       </c>
       <c r="D79" s="8">
-        <v>-16.89</v>
+        <v>-18.47</v>
       </c>
       <c r="E79" s="9">
-        <v>1.57</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4322,13 +4297,13 @@
         <v>6</v>
       </c>
       <c r="C80" s="8">
-        <v>-25.69</v>
+        <v>-20.66</v>
       </c>
       <c r="D80" s="8">
-        <v>-20.66</v>
-      </c>
-      <c r="E80" s="9">
-        <v>5.03</v>
+        <v>-20.64</v>
+      </c>
+      <c r="E80" s="10">
+        <v>0.02</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4339,13 +4314,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="8">
-        <v>-35.23</v>
+        <v>-35.24</v>
       </c>
       <c r="D81" s="8">
-        <v>-35.24</v>
+        <v>-34.69</v>
       </c>
       <c r="E81" s="10">
-        <v>-0.01</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4356,13 +4331,13 @@
         <v>6</v>
       </c>
       <c r="C82" s="8">
-        <v>-36.43</v>
+        <v>-33.31</v>
       </c>
       <c r="D82" s="8">
-        <v>-33.31</v>
-      </c>
-      <c r="E82" s="9">
-        <v>3.12</v>
+        <v>-32.72</v>
+      </c>
+      <c r="E82" s="10">
+        <v>0.59</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4373,13 +4348,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="8">
-        <v>-26.7</v>
+        <v>-26.57</v>
       </c>
       <c r="D83" s="8">
-        <v>-26.57</v>
+        <v>-27.46</v>
       </c>
       <c r="E83" s="9">
-        <v>0.13</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4390,13 +4365,13 @@
         <v>6</v>
       </c>
       <c r="C84" s="8">
-        <v>-21.56</v>
+        <v>-20.88</v>
       </c>
       <c r="D84" s="8">
-        <v>-20.88</v>
+        <v>-21.87</v>
       </c>
       <c r="E84" s="9">
-        <v>0.68</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4407,13 +4382,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="8">
-        <v>-21.32</v>
+        <v>-22.5</v>
       </c>
       <c r="D85" s="8">
-        <v>-22.5</v>
-      </c>
-      <c r="E85" s="10">
-        <v>-1.18</v>
+        <v>-23.65</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4424,13 +4399,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="8">
-        <v>-16.37</v>
+        <v>-15.54</v>
       </c>
       <c r="D86" s="8">
-        <v>-15.54</v>
+        <v>-16.08</v>
       </c>
       <c r="E86" s="9">
-        <v>0.83</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4441,13 +4416,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="8">
-        <v>-42.52</v>
+        <v>-41.13</v>
       </c>
       <c r="D87" s="8">
-        <v>-41.13</v>
-      </c>
-      <c r="E87" s="9">
-        <v>1.39</v>
+        <v>-39.19</v>
+      </c>
+      <c r="E87" s="10">
+        <v>1.94</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4458,13 +4433,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="8">
-        <v>-39.56</v>
+        <v>-41.51</v>
       </c>
       <c r="D88" s="8">
-        <v>-41.51</v>
+        <v>-41.45</v>
       </c>
       <c r="E88" s="10">
-        <v>-1.95</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4475,13 +4450,13 @@
         <v>6</v>
       </c>
       <c r="C89" s="8">
-        <v>-25.85</v>
+        <v>-25.26</v>
       </c>
       <c r="D89" s="8">
-        <v>-25.26</v>
+        <v>-29.96</v>
       </c>
       <c r="E89" s="9">
-        <v>0.59</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4492,13 +4467,13 @@
         <v>6</v>
       </c>
       <c r="C90" s="8">
-        <v>-39.12</v>
+        <v>-39.21</v>
       </c>
       <c r="D90" s="8">
-        <v>-39.21</v>
+        <v>-34.98</v>
       </c>
       <c r="E90" s="10">
-        <v>-0.09</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4509,13 +4484,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="8">
-        <v>795.5</v>
+        <v>812.85</v>
       </c>
       <c r="D91" s="8">
-        <v>812.85</v>
+        <v>805.2</v>
       </c>
       <c r="E91" s="9">
-        <v>17.35</v>
+        <v>-7.65</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4526,13 +4501,13 @@
         <v>2</v>
       </c>
       <c r="C92" s="8">
-        <v>700.65</v>
+        <v>707.8</v>
       </c>
       <c r="D92" s="8">
-        <v>707.8</v>
-      </c>
-      <c r="E92" s="9">
-        <v>7.15</v>
+        <v>709.9</v>
+      </c>
+      <c r="E92" s="10">
+        <v>2.1</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4543,13 +4518,13 @@
         <v>2</v>
       </c>
       <c r="C93" s="8">
-        <v>192.84</v>
+        <v>190.33</v>
       </c>
       <c r="D93" s="8">
-        <v>190.33</v>
-      </c>
-      <c r="E93" s="10">
-        <v>-2.51</v>
+        <v>188.72</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4560,13 +4535,13 @@
         <v>2</v>
       </c>
       <c r="C94" s="8">
-        <v>595.45</v>
+        <v>599</v>
       </c>
       <c r="D94" s="8">
-        <v>599</v>
-      </c>
-      <c r="E94" s="9">
-        <v>3.55</v>
+        <v>601.95</v>
+      </c>
+      <c r="E94" s="10">
+        <v>2.95</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4577,13 +4552,13 @@
         <v>2</v>
       </c>
       <c r="C95" s="8">
-        <v>1681.2</v>
+        <v>1713.5</v>
       </c>
       <c r="D95" s="8">
-        <v>1713.5</v>
+        <v>1681</v>
       </c>
       <c r="E95" s="9">
-        <v>32.3</v>
+        <v>-32.5</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4594,13 +4569,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="8">
-        <v>936.5</v>
+        <v>1000</v>
       </c>
       <c r="D96" s="8">
-        <v>1000</v>
-      </c>
-      <c r="E96" s="9">
-        <v>63.5</v>
+        <v>1000.2</v>
+      </c>
+      <c r="E96" s="10">
+        <v>0.2</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4611,13 +4586,13 @@
         <v>2</v>
       </c>
       <c r="C97" s="8">
-        <v>3724</v>
+        <v>3723.4</v>
       </c>
       <c r="D97" s="8">
-        <v>3723.4</v>
+        <v>3755</v>
       </c>
       <c r="E97" s="10">
-        <v>-0.6</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4628,13 +4603,13 @@
         <v>2</v>
       </c>
       <c r="C98" s="8">
-        <v>553.35</v>
+        <v>556.7</v>
       </c>
       <c r="D98" s="8">
-        <v>556.7</v>
-      </c>
-      <c r="E98" s="9">
-        <v>3.35</v>
+        <v>561.55</v>
+      </c>
+      <c r="E98" s="10">
+        <v>4.85</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4645,13 +4620,13 @@
         <v>2</v>
       </c>
       <c r="C99" s="8">
-        <v>338.5</v>
+        <v>339.1</v>
       </c>
       <c r="D99" s="8">
-        <v>339.1</v>
+        <v>335</v>
       </c>
       <c r="E99" s="9">
-        <v>0.6</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4662,13 +4637,13 @@
         <v>2</v>
       </c>
       <c r="C100" s="8">
-        <v>169.94</v>
+        <v>171.42</v>
       </c>
       <c r="D100" s="8">
-        <v>171.42</v>
+        <v>169.27</v>
       </c>
       <c r="E100" s="9">
-        <v>1.48</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4679,13 +4654,13 @@
         <v>2</v>
       </c>
       <c r="C101" s="8">
-        <v>2535</v>
+        <v>2496.9</v>
       </c>
       <c r="D101" s="8">
-        <v>2496.9</v>
-      </c>
-      <c r="E101" s="10">
-        <v>-38.1</v>
+        <v>2460</v>
+      </c>
+      <c r="E101" s="9">
+        <v>-36.9</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4696,13 +4671,13 @@
         <v>2</v>
       </c>
       <c r="C102" s="8">
-        <v>4323</v>
+        <v>4365.9</v>
       </c>
       <c r="D102" s="8">
-        <v>4365.9</v>
+        <v>4337.9</v>
       </c>
       <c r="E102" s="9">
-        <v>42.9</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4713,13 +4688,13 @@
         <v>2</v>
       </c>
       <c r="C103" s="8">
-        <v>2754</v>
+        <v>2820.6</v>
       </c>
       <c r="D103" s="8">
-        <v>2820.6</v>
-      </c>
-      <c r="E103" s="9">
-        <v>66.59999999999999</v>
+        <v>2913.9</v>
+      </c>
+      <c r="E103" s="10">
+        <v>93.3</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4730,13 +4705,13 @@
         <v>2</v>
       </c>
       <c r="C104" s="8">
-        <v>207.16</v>
+        <v>200.49</v>
       </c>
       <c r="D104" s="8">
-        <v>200.49</v>
+        <v>200.67</v>
       </c>
       <c r="E104" s="10">
-        <v>-6.67</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4747,13 +4722,13 @@
         <v>2</v>
       </c>
       <c r="C105" s="8">
-        <v>41.53</v>
+        <v>41.86</v>
       </c>
       <c r="D105" s="8">
-        <v>41.86</v>
+        <v>39.23</v>
       </c>
       <c r="E105" s="9">
-        <v>0.33</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4764,13 +4739,13 @@
         <v>2</v>
       </c>
       <c r="C106" s="8">
-        <v>947.6</v>
+        <v>946.2</v>
       </c>
       <c r="D106" s="8">
-        <v>946.2</v>
+        <v>1011.9</v>
       </c>
       <c r="E106" s="10">
-        <v>-1.4</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="107" spa